--- a/RIMS项目WBS工作分解_AI Native版.xlsx
+++ b/RIMS项目WBS工作分解_AI Native版.xlsx
@@ -9,10 +9,11 @@
   <sheets>
     <sheet name="使用说明" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="WBS分解" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="里程碑计划" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="资源负荷与日历" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="WBS词典" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="进度汇总" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="26项功能覆盖对照" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="里程碑计划" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="资源负荷与日历" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="WBS词典" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="进度汇总" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'WBS分解'!$A$3:$Q$164</definedName>
@@ -30,7 +31,7 @@
     <numFmt numFmtId="166" formatCode="0.##"/>
     <numFmt numFmtId="167" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="9">
+  <fonts count="10">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -65,11 +66,16 @@
     </font>
     <font>
       <i val="1"/>
+      <color rgb="007030A0"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <i val="1"/>
       <color rgb="00808080"/>
       <sz val="9"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -94,6 +100,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EDEDF7"/>
       </patternFill>
     </fill>
   </fills>
@@ -123,7 +134,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -194,8 +205,20 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -207,13 +230,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -620,7 +640,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B27"/>
+  <dimension ref="A1:B28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -905,10 +925,22 @@
     <row r="27" ht="30" customHeight="1">
       <c r="A27" s="3" t="inlineStr">
         <is>
+          <t>功能覆盖对照</t>
+        </is>
+      </c>
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t>「26项功能覆盖对照」页：源文件Scope-Phase1的26项功能（F01-01~F08-05）与WBS任务逐项对照（主开发/界面协作/走查/全量测试/负责人/计划完成日），功能名与源文件一字不差，可直接用于功能完整性验收</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="30" customHeight="1">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
           <t>其他页签</t>
         </is>
       </c>
-      <c r="B27" s="4" t="inlineStr">
+      <c r="B28" s="4" t="inlineStr">
         <is>
           <t>「里程碑计划」「资源负荷与日历」「WBS词典」「进度汇总」配合使用；如需甘特图可将WBS编号+起止日期导出到Project/飞书项目</t>
         </is>
@@ -4265,7 +4297,7 @@
       </c>
       <c r="B54" s="22" t="inlineStr">
         <is>
-          <t>F08-03/04 企业SSO集成+用户身份自动识别关联（后端链路）</t>
+          <t>F08-03/04 企业SSO集成+用户身份自动识别与关联（后端链路）</t>
         </is>
       </c>
       <c r="C54" s="15" t="n">
@@ -5015,7 +5047,7 @@
       </c>
       <c r="B66" s="22" t="inlineStr">
         <is>
-          <t>F05-01/02/03 检索页（关键词/系统名称/业务时间，动态表单）</t>
+          <t>F05-01/02/03 检索页开发：关键词检索+按系统名称检索+按业务时间检索（动态表单）</t>
         </is>
       </c>
       <c r="C66" s="15" t="n">
@@ -5829,7 +5861,7 @@
       </c>
       <c r="B79" s="22" t="inlineStr">
         <is>
-          <t>F06-01/02/03 审计埋点（归档/查询/导出日志）+审计查询界面</t>
+          <t>F06-01/02/03 审计日志：归档操作日志记录+查询操作日志记录+导出操作日志记录+审计查询界面</t>
         </is>
       </c>
       <c r="C79" s="15" t="n">
@@ -6653,7 +6685,7 @@
       </c>
       <c r="B92" s="22" t="inlineStr">
         <is>
-          <t>F03-02 Legal Hold冻结（Hold/Release+豁免+留痕）+处置链路验证（短保留样本→到期→物理清除）</t>
+          <t>F03-02 Legal Hold 冻结（Hold/Release+豁免+留痕）+处置链路验证（短保留样本→到期→物理清除）</t>
         </is>
       </c>
       <c r="C92" s="15" t="n">
@@ -11338,6 +11370,1591 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="007030A0"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K29"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="9" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="42" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="8" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="26" customHeight="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>26项功能覆盖对照（源文件Scope-Phase1 ↔ WBS，逐项可追溯）</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>功能编号</t>
+        </is>
+      </c>
+      <c r="B2" s="7" t="inlineStr">
+        <is>
+          <t>模块</t>
+        </is>
+      </c>
+      <c r="C2" s="7" t="inlineStr">
+        <is>
+          <t>业务场景</t>
+        </is>
+      </c>
+      <c r="D2" s="7" t="inlineStr">
+        <is>
+          <t>关键功能</t>
+        </is>
+      </c>
+      <c r="E2" s="7" t="inlineStr">
+        <is>
+          <t>具体功能（与源文件一致）</t>
+        </is>
+      </c>
+      <c r="F2" s="7" t="inlineStr">
+        <is>
+          <t>功能描述（源文件）</t>
+        </is>
+      </c>
+      <c r="G2" s="7" t="inlineStr">
+        <is>
+          <t>主开发任务(WBS)</t>
+        </is>
+      </c>
+      <c r="H2" s="7" t="inlineStr">
+        <is>
+          <t>界面/协作任务(WBS)</t>
+        </is>
+      </c>
+      <c r="I2" s="7" t="inlineStr">
+        <is>
+          <t>走查任务(WBS)</t>
+        </is>
+      </c>
+      <c r="J2" s="7" t="inlineStr">
+        <is>
+          <t>全量测试</t>
+        </is>
+      </c>
+      <c r="K2" s="7" t="inlineStr">
+        <is>
+          <t>开发负责人 / 计划完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="40" customHeight="1">
+      <c r="A3" s="30" t="inlineStr">
+        <is>
+          <t>F01-01</t>
+        </is>
+      </c>
+      <c r="B3" s="31" t="inlineStr">
+        <is>
+          <t>模块1·存量历史数据迁移与标准化</t>
+        </is>
+      </c>
+      <c r="C3" s="31" t="inlineStr">
+        <is>
+          <t>退役系统历史数据全量入库归档</t>
+        </is>
+      </c>
+      <c r="D3" s="31" t="inlineStr">
+        <is>
+          <t>历史数据批量导入</t>
+        </is>
+      </c>
+      <c r="E3" s="31" t="inlineStr">
+        <is>
+          <t>结构化历史数据批量导入</t>
+        </is>
+      </c>
+      <c r="F3" s="31" t="inlineStr">
+        <is>
+          <t>支持从退役系统批量提取结构化历史数据，并按照既定迁移范围和映射规则导入RIMS。</t>
+        </is>
+      </c>
+      <c r="G3" s="30" t="inlineStr">
+        <is>
+          <t>4.2.1</t>
+        </is>
+      </c>
+      <c r="H3" s="30" t="inlineStr">
+        <is>
+          <t>4.3.1</t>
+        </is>
+      </c>
+      <c r="I3" s="30" t="inlineStr">
+        <is>
+          <t>4.4.4</t>
+        </is>
+      </c>
+      <c r="J3" s="30" t="inlineStr">
+        <is>
+          <t>7.1.1</t>
+        </is>
+      </c>
+      <c r="K3" s="31" t="inlineStr">
+        <is>
+          <t>DevB / 10/13</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="40" customHeight="1">
+      <c r="A4" s="15" t="inlineStr">
+        <is>
+          <t>F01-02</t>
+        </is>
+      </c>
+      <c r="B4" s="32" t="inlineStr">
+        <is>
+          <t>模块1·存量历史数据迁移与标准化</t>
+        </is>
+      </c>
+      <c r="C4" s="32" t="inlineStr">
+        <is>
+          <t>退役系统历史数据全量入库归档</t>
+        </is>
+      </c>
+      <c r="D4" s="32" t="inlineStr">
+        <is>
+          <t>历史数据批量导入</t>
+        </is>
+      </c>
+      <c r="E4" s="32" t="inlineStr">
+        <is>
+          <t>非结构化文件及离线包批量导入</t>
+        </is>
+      </c>
+      <c r="F4" s="32" t="inlineStr">
+        <is>
+          <t>支持从多种文件来源和离线介质批量导入附件、普通文件、数据库备份包及压缩归档包，并保障大文件及传输中断场景下的可靠导入、原始属性保留和文件包解析。</t>
+        </is>
+      </c>
+      <c r="G4" s="15" t="inlineStr">
+        <is>
+          <t>4.2.2</t>
+        </is>
+      </c>
+      <c r="H4" s="15" t="inlineStr">
+        <is>
+          <t>4.3.1</t>
+        </is>
+      </c>
+      <c r="I4" s="15" t="inlineStr">
+        <is>
+          <t>4.4.4</t>
+        </is>
+      </c>
+      <c r="J4" s="15" t="inlineStr">
+        <is>
+          <t>7.1.1</t>
+        </is>
+      </c>
+      <c r="K4" s="32" t="inlineStr">
+        <is>
+          <t>DevB / 10/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="40" customHeight="1">
+      <c r="A5" s="30" t="inlineStr">
+        <is>
+          <t>F01-03</t>
+        </is>
+      </c>
+      <c r="B5" s="31" t="inlineStr">
+        <is>
+          <t>模块1·存量历史数据迁移与标准化</t>
+        </is>
+      </c>
+      <c r="C5" s="31" t="inlineStr">
+        <is>
+          <t>退役系统历史数据全量入库归档</t>
+        </is>
+      </c>
+      <c r="D5" s="31" t="inlineStr">
+        <is>
+          <t>迁移规则配置</t>
+        </is>
+      </c>
+      <c r="E5" s="31" t="inlineStr">
+        <is>
+          <t>数据导入规则配置</t>
+        </is>
+      </c>
+      <c r="F5" s="31" t="inlineStr">
+        <is>
+          <t>面向退役系统迁移项目，配置源数据与RIMS标准字段的对应关系、格式转换和校验规则，并在导入过程中执行。</t>
+        </is>
+      </c>
+      <c r="G5" s="30" t="inlineStr">
+        <is>
+          <t>4.2.3</t>
+        </is>
+      </c>
+      <c r="H5" s="30" t="inlineStr">
+        <is>
+          <t>4.3.1</t>
+        </is>
+      </c>
+      <c r="I5" s="30" t="inlineStr">
+        <is>
+          <t>4.4.4</t>
+        </is>
+      </c>
+      <c r="J5" s="30" t="inlineStr">
+        <is>
+          <t>7.1.1</t>
+        </is>
+      </c>
+      <c r="K5" s="31" t="inlineStr">
+        <is>
+          <t>DevB / 10/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="40" customHeight="1">
+      <c r="A6" s="15" t="inlineStr">
+        <is>
+          <t>F01-04</t>
+        </is>
+      </c>
+      <c r="B6" s="32" t="inlineStr">
+        <is>
+          <t>模块1·存量历史数据迁移与标准化</t>
+        </is>
+      </c>
+      <c r="C6" s="32" t="inlineStr">
+        <is>
+          <t>确保迁移过程数据完整可追溯</t>
+        </is>
+      </c>
+      <c r="D6" s="32" t="inlineStr">
+        <is>
+          <t>迁移完整性校验</t>
+        </is>
+      </c>
+      <c r="E6" s="32" t="inlineStr">
+        <is>
+          <t>迁移前完整性基准记录</t>
+        </is>
+      </c>
+      <c r="F6" s="32" t="inlineStr">
+        <is>
+          <t>在迁移前记录文件或数据集的完整性校验信息，作为迁移完成后的比对基准。</t>
+        </is>
+      </c>
+      <c r="G6" s="15" t="inlineStr">
+        <is>
+          <t>4.2.5</t>
+        </is>
+      </c>
+      <c r="H6" s="15" t="inlineStr">
+        <is>
+          <t>4.3.1</t>
+        </is>
+      </c>
+      <c r="I6" s="15" t="inlineStr">
+        <is>
+          <t>4.4.4</t>
+        </is>
+      </c>
+      <c r="J6" s="15" t="inlineStr">
+        <is>
+          <t>7.1.1</t>
+        </is>
+      </c>
+      <c r="K6" s="32" t="inlineStr">
+        <is>
+          <t>DevB / 10/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="40" customHeight="1">
+      <c r="A7" s="30" t="inlineStr">
+        <is>
+          <t>F01-05</t>
+        </is>
+      </c>
+      <c r="B7" s="31" t="inlineStr">
+        <is>
+          <t>模块1·存量历史数据迁移与标准化</t>
+        </is>
+      </c>
+      <c r="C7" s="31" t="inlineStr">
+        <is>
+          <t>确保迁移过程数据完整可追溯</t>
+        </is>
+      </c>
+      <c r="D7" s="31" t="inlineStr">
+        <is>
+          <t>迁移完整性校验</t>
+        </is>
+      </c>
+      <c r="E7" s="31" t="inlineStr">
+        <is>
+          <t>迁移后完整性比对</t>
+        </is>
+      </c>
+      <c r="F7" s="31" t="inlineStr">
+        <is>
+          <t>迁移完成后对源端与目标端数据进行完整性比对，识别缺失、损坏或异常变更。</t>
+        </is>
+      </c>
+      <c r="G7" s="30" t="inlineStr">
+        <is>
+          <t>4.2.5</t>
+        </is>
+      </c>
+      <c r="H7" s="30" t="inlineStr">
+        <is>
+          <t>4.3.1</t>
+        </is>
+      </c>
+      <c r="I7" s="30" t="inlineStr">
+        <is>
+          <t>4.4.4</t>
+        </is>
+      </c>
+      <c r="J7" s="30" t="inlineStr">
+        <is>
+          <t>7.1.1</t>
+        </is>
+      </c>
+      <c r="K7" s="31" t="inlineStr">
+        <is>
+          <t>DevB / 10/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="40" customHeight="1">
+      <c r="A8" s="15" t="inlineStr">
+        <is>
+          <t>F02-01</t>
+        </is>
+      </c>
+      <c r="B8" s="32" t="inlineStr">
+        <is>
+          <t>模块2·实时数据接入与常态化数据治理</t>
+        </is>
+      </c>
+      <c r="C8" s="32" t="inlineStr">
+        <is>
+          <t>多源异构数据接入与元数据标准化规整</t>
+        </is>
+      </c>
+      <c r="D8" s="32" t="inlineStr">
+        <is>
+          <t>元数据标准与来源管理</t>
+        </is>
+      </c>
+      <c r="E8" s="32" t="inlineStr">
+        <is>
+          <t>统一元数据模型</t>
+        </is>
+      </c>
+      <c r="F8" s="32" t="inlineStr">
+        <is>
+          <t>建立统一元数据字段体系，明确字段定义、数据类型、取值规则和必填要求，包括来源系统、业务域、记录类型、创建时间、责任人、保留等级和密级等。</t>
+        </is>
+      </c>
+      <c r="G8" s="15" t="inlineStr">
+        <is>
+          <t>4.2.6</t>
+        </is>
+      </c>
+      <c r="H8" s="15" t="inlineStr">
+        <is>
+          <t>5.2.1</t>
+        </is>
+      </c>
+      <c r="I8" s="15" t="inlineStr">
+        <is>
+          <t>5.3.2</t>
+        </is>
+      </c>
+      <c r="J8" s="15" t="inlineStr">
+        <is>
+          <t>7.1.1</t>
+        </is>
+      </c>
+      <c r="K8" s="32" t="inlineStr">
+        <is>
+          <t>DevB / 10/22</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="40" customHeight="1">
+      <c r="A9" s="30" t="inlineStr">
+        <is>
+          <t>F02-02</t>
+        </is>
+      </c>
+      <c r="B9" s="31" t="inlineStr">
+        <is>
+          <t>模块2·实时数据接入与常态化数据治理</t>
+        </is>
+      </c>
+      <c r="C9" s="31" t="inlineStr">
+        <is>
+          <t>多源异构数据接入与元数据标准化规整</t>
+        </is>
+      </c>
+      <c r="D9" s="31" t="inlineStr">
+        <is>
+          <t>元数据标准与来源管理</t>
+        </is>
+      </c>
+      <c r="E9" s="31" t="inlineStr">
+        <is>
+          <t>来源系统信息绑定</t>
+        </is>
+      </c>
+      <c r="F9" s="31" t="inlineStr">
+        <is>
+          <t>在记录接入和入库时引用统一源系统编码，并绑定退役项目、迁移批次等来源属性，支持按来源检索和统计。</t>
+        </is>
+      </c>
+      <c r="G9" s="30" t="inlineStr">
+        <is>
+          <t>4.2.6</t>
+        </is>
+      </c>
+      <c r="H9" s="30" t="inlineStr">
+        <is>
+          <t>5.2.1</t>
+        </is>
+      </c>
+      <c r="I9" s="30" t="inlineStr">
+        <is>
+          <t>5.3.2</t>
+        </is>
+      </c>
+      <c r="J9" s="30" t="inlineStr">
+        <is>
+          <t>7.1.1</t>
+        </is>
+      </c>
+      <c r="K9" s="31" t="inlineStr">
+        <is>
+          <t>DevB / 10/22</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="40" customHeight="1">
+      <c r="A10" s="15" t="inlineStr">
+        <is>
+          <t>F03-01</t>
+        </is>
+      </c>
+      <c r="B10" s="32" t="inlineStr">
+        <is>
+          <t>模块3·记录归档与档案全生命周期管理</t>
+        </is>
+      </c>
+      <c r="C10" s="32" t="inlineStr">
+        <is>
+          <t>归档记录定期删除与合规保留</t>
+        </is>
+      </c>
+      <c r="D10" s="32" t="inlineStr">
+        <is>
+          <t>到期处置与Legal Hold管理</t>
+        </is>
+      </c>
+      <c r="E10" s="32" t="inlineStr">
+        <is>
+          <t>保留期限到期自动删除</t>
+        </is>
+      </c>
+      <c r="F10" s="32" t="inlineStr">
+        <is>
+          <t>根据预设保留策略，对到期归档记录执行自动删除或标记销毁。</t>
+        </is>
+      </c>
+      <c r="G10" s="15" t="inlineStr">
+        <is>
+          <t>5.2.5</t>
+        </is>
+      </c>
+      <c r="H10" s="15" t="inlineStr">
+        <is>
+          <t>5.1.5</t>
+        </is>
+      </c>
+      <c r="I10" s="15" t="inlineStr">
+        <is>
+          <t>5.3.9</t>
+        </is>
+      </c>
+      <c r="J10" s="15" t="inlineStr">
+        <is>
+          <t>7.1.1</t>
+        </is>
+      </c>
+      <c r="K10" s="32" t="inlineStr">
+        <is>
+          <t>DevB / 11/04</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="40" customHeight="1">
+      <c r="A11" s="30" t="inlineStr">
+        <is>
+          <t>F03-02</t>
+        </is>
+      </c>
+      <c r="B11" s="31" t="inlineStr">
+        <is>
+          <t>模块3·记录归档与档案全生命周期管理</t>
+        </is>
+      </c>
+      <c r="C11" s="31" t="inlineStr">
+        <is>
+          <t>归档记录定期删除与合规保留</t>
+        </is>
+      </c>
+      <c r="D11" s="31" t="inlineStr">
+        <is>
+          <t>到期处置与Legal Hold管理</t>
+        </is>
+      </c>
+      <c r="E11" s="31" t="inlineStr">
+        <is>
+          <t>Legal Hold 冻结</t>
+        </is>
+      </c>
+      <c r="F11" s="31" t="inlineStr">
+        <is>
+          <t>对涉诉、审计或合规调查中的记录设置Legal Hold，暂停删除和修改。</t>
+        </is>
+      </c>
+      <c r="G11" s="30" t="inlineStr">
+        <is>
+          <t>5.2.6</t>
+        </is>
+      </c>
+      <c r="H11" s="30" t="inlineStr">
+        <is>
+          <t>5.1.5</t>
+        </is>
+      </c>
+      <c r="I11" s="30" t="inlineStr">
+        <is>
+          <t>5.3.9</t>
+        </is>
+      </c>
+      <c r="J11" s="30" t="inlineStr">
+        <is>
+          <t>7.1.1</t>
+        </is>
+      </c>
+      <c r="K11" s="31" t="inlineStr">
+        <is>
+          <t>DevB / 11/05</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="40" customHeight="1">
+      <c r="A12" s="15" t="inlineStr">
+        <is>
+          <t>F04-01</t>
+        </is>
+      </c>
+      <c r="B12" s="32" t="inlineStr">
+        <is>
+          <t>模块4·数据存储与境内数据安全管控</t>
+        </is>
+      </c>
+      <c r="C12" s="32" t="inlineStr">
+        <is>
+          <t>满足数据不出境和本地化合规要求</t>
+        </is>
+      </c>
+      <c r="D12" s="32" t="inlineStr">
+        <is>
+          <t>数据加密与密钥管理</t>
+        </is>
+      </c>
+      <c r="E12" s="32" t="inlineStr">
+        <is>
+          <t>数据加密存储</t>
+        </is>
+      </c>
+      <c r="F12" s="32" t="inlineStr">
+        <is>
+          <t>支持归档数据在存储和传输过程中的加密保护，防止未授权读取和数据泄露。</t>
+        </is>
+      </c>
+      <c r="G12" s="15" t="inlineStr">
+        <is>
+          <t>5.2.2</t>
+        </is>
+      </c>
+      <c r="H12" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I12" s="15" t="inlineStr">
+        <is>
+          <t>5.3.9</t>
+        </is>
+      </c>
+      <c r="J12" s="15" t="inlineStr">
+        <is>
+          <t>7.1.1</t>
+        </is>
+      </c>
+      <c r="K12" s="32" t="inlineStr">
+        <is>
+          <t>DevB / 10/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="40" customHeight="1">
+      <c r="A13" s="30" t="inlineStr">
+        <is>
+          <t>F04-02</t>
+        </is>
+      </c>
+      <c r="B13" s="31" t="inlineStr">
+        <is>
+          <t>模块4·数据存储与境内数据安全管控</t>
+        </is>
+      </c>
+      <c r="C13" s="31" t="inlineStr">
+        <is>
+          <t>满足数据不出境和本地化合规要求</t>
+        </is>
+      </c>
+      <c r="D13" s="31" t="inlineStr">
+        <is>
+          <t>数据加密与密钥管理</t>
+        </is>
+      </c>
+      <c r="E13" s="31" t="inlineStr">
+        <is>
+          <t>密钥管理</t>
+        </is>
+      </c>
+      <c r="F13" s="31" t="inlineStr">
+        <is>
+          <t>支持加密密钥的创建、保管、更新、权限控制和操作审计。</t>
+        </is>
+      </c>
+      <c r="G13" s="30" t="inlineStr">
+        <is>
+          <t>5.2.3</t>
+        </is>
+      </c>
+      <c r="H13" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I13" s="30" t="inlineStr">
+        <is>
+          <t>5.3.9</t>
+        </is>
+      </c>
+      <c r="J13" s="30" t="inlineStr">
+        <is>
+          <t>7.1.1</t>
+        </is>
+      </c>
+      <c r="K13" s="31" t="inlineStr">
+        <is>
+          <t>DevB / 10/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="40" customHeight="1">
+      <c r="A14" s="15" t="inlineStr">
+        <is>
+          <t>F04-03</t>
+        </is>
+      </c>
+      <c r="B14" s="32" t="inlineStr">
+        <is>
+          <t>模块4·数据存储与境内数据安全管控</t>
+        </is>
+      </c>
+      <c r="C14" s="32" t="inlineStr">
+        <is>
+          <t>确保归档数据可恢复</t>
+        </is>
+      </c>
+      <c r="D14" s="32" t="inlineStr">
+        <is>
+          <t>数据备份与灾难恢复</t>
+        </is>
+      </c>
+      <c r="E14" s="32" t="inlineStr">
+        <is>
+          <t>数据备份管理</t>
+        </is>
+      </c>
+      <c r="F14" s="32" t="inlineStr">
+        <is>
+          <t>支持按照备份策略创建和维护归档数据副本，确保数据副本完整、可用并满足恢复需求。</t>
+        </is>
+      </c>
+      <c r="G14" s="15" t="inlineStr">
+        <is>
+          <t>5.2.7</t>
+        </is>
+      </c>
+      <c r="H14" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I14" s="15" t="inlineStr">
+        <is>
+          <t>5.3.9</t>
+        </is>
+      </c>
+      <c r="J14" s="15" t="inlineStr">
+        <is>
+          <t>7.1.1</t>
+        </is>
+      </c>
+      <c r="K14" s="32" t="inlineStr">
+        <is>
+          <t>DevB / 11/06</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="40" customHeight="1">
+      <c r="A15" s="30" t="inlineStr">
+        <is>
+          <t>F04-04</t>
+        </is>
+      </c>
+      <c r="B15" s="31" t="inlineStr">
+        <is>
+          <t>模块4·数据存储与境内数据安全管控</t>
+        </is>
+      </c>
+      <c r="C15" s="31" t="inlineStr">
+        <is>
+          <t>确保归档数据可恢复</t>
+        </is>
+      </c>
+      <c r="D15" s="31" t="inlineStr">
+        <is>
+          <t>数据备份与灾难恢复</t>
+        </is>
+      </c>
+      <c r="E15" s="31" t="inlineStr">
+        <is>
+          <t>异地灾备</t>
+        </is>
+      </c>
+      <c r="F15" s="31" t="inlineStr">
+        <is>
+          <t>支持将数据副本与主要运行环境隔离保存，保障区域性灾害或重大故障情况下的数据恢复。</t>
+        </is>
+      </c>
+      <c r="G15" s="30" t="inlineStr">
+        <is>
+          <t>5.2.8</t>
+        </is>
+      </c>
+      <c r="H15" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I15" s="30" t="inlineStr">
+        <is>
+          <t>5.3.9</t>
+        </is>
+      </c>
+      <c r="J15" s="30" t="inlineStr">
+        <is>
+          <t>7.1.1</t>
+        </is>
+      </c>
+      <c r="K15" s="31" t="inlineStr">
+        <is>
+          <t>DevB / 11/09</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="40" customHeight="1">
+      <c r="A16" s="15" t="inlineStr">
+        <is>
+          <t>F05-01</t>
+        </is>
+      </c>
+      <c r="B16" s="32" t="inlineStr">
+        <is>
+          <t>模块5·档案检索、智能发现与业务利用</t>
+        </is>
+      </c>
+      <c r="C16" s="32" t="inlineStr">
+        <is>
+          <t>QA/IT人员日常基础数据查阅</t>
+        </is>
+      </c>
+      <c r="D16" s="32" t="inlineStr">
+        <is>
+          <t>基础档案检索</t>
+        </is>
+      </c>
+      <c r="E16" s="32" t="inlineStr">
+        <is>
+          <t>关键词检索</t>
+        </is>
+      </c>
+      <c r="F16" s="32" t="inlineStr">
+        <is>
+          <t>支持对归档记录标题、元数据、OCR文本进行关键词检索。</t>
+        </is>
+      </c>
+      <c r="G16" s="15" t="inlineStr">
+        <is>
+          <t>4.3.2</t>
+        </is>
+      </c>
+      <c r="H16" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I16" s="15" t="inlineStr">
+        <is>
+          <t>5.3.4</t>
+        </is>
+      </c>
+      <c r="J16" s="15" t="inlineStr">
+        <is>
+          <t>7.1.1</t>
+        </is>
+      </c>
+      <c r="K16" s="32" t="inlineStr">
+        <is>
+          <t>Wade / 10/22</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="40" customHeight="1">
+      <c r="A17" s="23" t="inlineStr">
+        <is>
+          <t>F05-02</t>
+        </is>
+      </c>
+      <c r="B17" s="33" t="inlineStr">
+        <is>
+          <t>模块5·档案检索、智能发现与业务利用</t>
+        </is>
+      </c>
+      <c r="C17" s="33" t="inlineStr">
+        <is>
+          <t>QA/IT人员日常基础数据查阅</t>
+        </is>
+      </c>
+      <c r="D17" s="33" t="inlineStr">
+        <is>
+          <t>基础档案检索</t>
+        </is>
+      </c>
+      <c r="E17" s="33" t="inlineStr">
+        <is>
+          <t>按系统名称检索</t>
+        </is>
+      </c>
+      <c r="F17" s="33" t="inlineStr">
+        <is>
+          <t>支持按来源系统名称筛选和检索对应归档数据。</t>
+        </is>
+      </c>
+      <c r="G17" s="23" t="inlineStr">
+        <is>
+          <t>4.3.2</t>
+        </is>
+      </c>
+      <c r="H17" s="23" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I17" s="23" t="inlineStr">
+        <is>
+          <t>5.3.4</t>
+        </is>
+      </c>
+      <c r="J17" s="23" t="inlineStr">
+        <is>
+          <t>7.1.1</t>
+        </is>
+      </c>
+      <c r="K17" s="33" t="inlineStr">
+        <is>
+          <t>Wade / 10/22</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="40" customHeight="1">
+      <c r="A18" s="15" t="inlineStr">
+        <is>
+          <t>F05-03</t>
+        </is>
+      </c>
+      <c r="B18" s="32" t="inlineStr">
+        <is>
+          <t>模块5·档案检索、智能发现与业务利用</t>
+        </is>
+      </c>
+      <c r="C18" s="32" t="inlineStr">
+        <is>
+          <t>QA/IT人员日常基础数据查阅</t>
+        </is>
+      </c>
+      <c r="D18" s="32" t="inlineStr">
+        <is>
+          <t>基础档案检索</t>
+        </is>
+      </c>
+      <c r="E18" s="32" t="inlineStr">
+        <is>
+          <t>按业务时间检索</t>
+        </is>
+      </c>
+      <c r="F18" s="32" t="inlineStr">
+        <is>
+          <t>支持按创建时间、修改时间、业务发生时间等时间维度检索。</t>
+        </is>
+      </c>
+      <c r="G18" s="15" t="inlineStr">
+        <is>
+          <t>4.3.2</t>
+        </is>
+      </c>
+      <c r="H18" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I18" s="15" t="inlineStr">
+        <is>
+          <t>5.3.4</t>
+        </is>
+      </c>
+      <c r="J18" s="15" t="inlineStr">
+        <is>
+          <t>7.1.1</t>
+        </is>
+      </c>
+      <c r="K18" s="32" t="inlineStr">
+        <is>
+          <t>Wade / 10/22</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="40" customHeight="1">
+      <c r="A19" s="30" t="inlineStr">
+        <is>
+          <t>F05-04</t>
+        </is>
+      </c>
+      <c r="B19" s="31" t="inlineStr">
+        <is>
+          <t>模块5·档案检索、智能发现与业务利用</t>
+        </is>
+      </c>
+      <c r="C19" s="31" t="inlineStr">
+        <is>
+          <t>QA/IT人员日常基础数据查阅</t>
+        </is>
+      </c>
+      <c r="D19" s="31" t="inlineStr">
+        <is>
+          <t>检索结果展示与预览</t>
+        </is>
+      </c>
+      <c r="E19" s="31" t="inlineStr">
+        <is>
+          <t>检索结果列表展示</t>
+        </is>
+      </c>
+      <c r="F19" s="31" t="inlineStr">
+        <is>
+          <t>以列表形式展示检索结果，支持结果分批查看、排序和关键字段展示。</t>
+        </is>
+      </c>
+      <c r="G19" s="30" t="inlineStr">
+        <is>
+          <t>5.1.1</t>
+        </is>
+      </c>
+      <c r="H19" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I19" s="30" t="inlineStr">
+        <is>
+          <t>5.3.4</t>
+        </is>
+      </c>
+      <c r="J19" s="30" t="inlineStr">
+        <is>
+          <t>7.1.1</t>
+        </is>
+      </c>
+      <c r="K19" s="31" t="inlineStr">
+        <is>
+          <t>Wade / 10/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="40" customHeight="1">
+      <c r="A20" s="15" t="inlineStr">
+        <is>
+          <t>F05-05</t>
+        </is>
+      </c>
+      <c r="B20" s="32" t="inlineStr">
+        <is>
+          <t>模块5·档案检索、智能发现与业务利用</t>
+        </is>
+      </c>
+      <c r="C20" s="32" t="inlineStr">
+        <is>
+          <t>QA/IT人员日常基础数据查阅</t>
+        </is>
+      </c>
+      <c r="D20" s="32" t="inlineStr">
+        <is>
+          <t>检索结果展示与预览</t>
+        </is>
+      </c>
+      <c r="E20" s="32" t="inlineStr">
+        <is>
+          <t>原始文件在线预览</t>
+        </is>
+      </c>
+      <c r="F20" s="32" t="inlineStr">
+        <is>
+          <t>支持常见文档、图片及办公文件在线预览，无需下载即可查看内容。</t>
+        </is>
+      </c>
+      <c r="G20" s="15" t="inlineStr">
+        <is>
+          <t>5.1.2</t>
+        </is>
+      </c>
+      <c r="H20" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I20" s="15" t="inlineStr">
+        <is>
+          <t>5.3.4</t>
+        </is>
+      </c>
+      <c r="J20" s="15" t="inlineStr">
+        <is>
+          <t>7.1.1</t>
+        </is>
+      </c>
+      <c r="K20" s="32" t="inlineStr">
+        <is>
+          <t>Wade / 10/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="40" customHeight="1">
+      <c r="A21" s="30" t="inlineStr">
+        <is>
+          <t>F06-01</t>
+        </is>
+      </c>
+      <c r="B21" s="31" t="inlineStr">
+        <is>
+          <t>模块6·合规管控、审计追踪与合规报表</t>
+        </is>
+      </c>
+      <c r="C21" s="31" t="inlineStr">
+        <is>
+          <t>基础运维核查与简易审计调取</t>
+        </is>
+      </c>
+      <c r="D21" s="31" t="inlineStr">
+        <is>
+          <t>用户操作审计追踪</t>
+        </is>
+      </c>
+      <c r="E21" s="31" t="inlineStr">
+        <is>
+          <t>归档操作日志记录</t>
+        </is>
+      </c>
+      <c r="F21" s="31" t="inlineStr">
+        <is>
+          <t>记录数据导入、上传、归档等操作，包含用户、时间、对象、结果。</t>
+        </is>
+      </c>
+      <c r="G21" s="30" t="inlineStr">
+        <is>
+          <t>5.1.3</t>
+        </is>
+      </c>
+      <c r="H21" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I21" s="30" t="inlineStr">
+        <is>
+          <t>5.3.6</t>
+        </is>
+      </c>
+      <c r="J21" s="30" t="inlineStr">
+        <is>
+          <t>7.1.1</t>
+        </is>
+      </c>
+      <c r="K21" s="31" t="inlineStr">
+        <is>
+          <t>Wade / 11/02</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="40" customHeight="1">
+      <c r="A22" s="15" t="inlineStr">
+        <is>
+          <t>F06-02</t>
+        </is>
+      </c>
+      <c r="B22" s="32" t="inlineStr">
+        <is>
+          <t>模块6·合规管控、审计追踪与合规报表</t>
+        </is>
+      </c>
+      <c r="C22" s="32" t="inlineStr">
+        <is>
+          <t>基础运维核查与简易审计调取</t>
+        </is>
+      </c>
+      <c r="D22" s="32" t="inlineStr">
+        <is>
+          <t>用户操作审计追踪</t>
+        </is>
+      </c>
+      <c r="E22" s="32" t="inlineStr">
+        <is>
+          <t>查询操作日志记录</t>
+        </is>
+      </c>
+      <c r="F22" s="32" t="inlineStr">
+        <is>
+          <t>记录用户的检索、查看、预览行为，支持审计追溯。</t>
+        </is>
+      </c>
+      <c r="G22" s="15" t="inlineStr">
+        <is>
+          <t>5.1.3</t>
+        </is>
+      </c>
+      <c r="H22" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I22" s="15" t="inlineStr">
+        <is>
+          <t>5.3.6</t>
+        </is>
+      </c>
+      <c r="J22" s="15" t="inlineStr">
+        <is>
+          <t>7.1.1</t>
+        </is>
+      </c>
+      <c r="K22" s="32" t="inlineStr">
+        <is>
+          <t>Wade / 11/02</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="40" customHeight="1">
+      <c r="A23" s="30" t="inlineStr">
+        <is>
+          <t>F06-03</t>
+        </is>
+      </c>
+      <c r="B23" s="31" t="inlineStr">
+        <is>
+          <t>模块6·合规管控、审计追踪与合规报表</t>
+        </is>
+      </c>
+      <c r="C23" s="31" t="inlineStr">
+        <is>
+          <t>基础运维核查与简易审计调取</t>
+        </is>
+      </c>
+      <c r="D23" s="31" t="inlineStr">
+        <is>
+          <t>用户操作审计追踪</t>
+        </is>
+      </c>
+      <c r="E23" s="31" t="inlineStr">
+        <is>
+          <t>导出操作日志记录</t>
+        </is>
+      </c>
+      <c r="F23" s="31" t="inlineStr">
+        <is>
+          <t>记录数据导出行为，包含导出范围、导出时间、导出人和下载IP。</t>
+        </is>
+      </c>
+      <c r="G23" s="30" t="inlineStr">
+        <is>
+          <t>5.1.3</t>
+        </is>
+      </c>
+      <c r="H23" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I23" s="30" t="inlineStr">
+        <is>
+          <t>5.3.6</t>
+        </is>
+      </c>
+      <c r="J23" s="30" t="inlineStr">
+        <is>
+          <t>7.1.1</t>
+        </is>
+      </c>
+      <c r="K23" s="31" t="inlineStr">
+        <is>
+          <t>Wade / 11/02</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="40" customHeight="1">
+      <c r="A24" s="15" t="inlineStr">
+        <is>
+          <t>F08-01</t>
+        </is>
+      </c>
+      <c r="B24" s="32" t="inlineStr">
+        <is>
+          <t>模块8·系统全局治理、运维与监控</t>
+        </is>
+      </c>
+      <c r="C24" s="32" t="inlineStr">
+        <is>
+          <t>基础运维核查与简易审计调取</t>
+        </is>
+      </c>
+      <c r="D24" s="32" t="inlineStr">
+        <is>
+          <t>用户与角色管理</t>
+        </is>
+      </c>
+      <c r="E24" s="32" t="inlineStr">
+        <is>
+          <t>基础角色权限配置</t>
+        </is>
+      </c>
+      <c r="F24" s="32" t="inlineStr">
+        <is>
+          <t>配置管理员、查询员、审计员等基础角色，并按角色统一分配菜单权限、数据范围、记录类型和操作权限。</t>
+        </is>
+      </c>
+      <c r="G24" s="15" t="inlineStr">
+        <is>
+          <t>4.1.1</t>
+        </is>
+      </c>
+      <c r="H24" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I24" s="15" t="inlineStr">
+        <is>
+          <t>4.4.4</t>
+        </is>
+      </c>
+      <c r="J24" s="15" t="inlineStr">
+        <is>
+          <t>7.1.1</t>
+        </is>
+      </c>
+      <c r="K24" s="32" t="inlineStr">
+        <is>
+          <t>Wade / 10/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="40" customHeight="1">
+      <c r="A25" s="30" t="inlineStr">
+        <is>
+          <t>F08-02</t>
+        </is>
+      </c>
+      <c r="B25" s="31" t="inlineStr">
+        <is>
+          <t>模块8·系统全局治理、运维与监控</t>
+        </is>
+      </c>
+      <c r="C25" s="31" t="inlineStr">
+        <is>
+          <t>基础运维核查与简易审计调取</t>
+        </is>
+      </c>
+      <c r="D25" s="31" t="inlineStr">
+        <is>
+          <t>用户与角色管理</t>
+        </is>
+      </c>
+      <c r="E25" s="31" t="inlineStr">
+        <is>
+          <t>用户账号管理</t>
+        </is>
+      </c>
+      <c r="F25" s="31" t="inlineStr">
+        <is>
+          <t>支持本地账号创建、启用/禁用、密码重置、账号有效期管理。</t>
+        </is>
+      </c>
+      <c r="G25" s="30" t="inlineStr">
+        <is>
+          <t>4.1.1</t>
+        </is>
+      </c>
+      <c r="H25" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I25" s="30" t="inlineStr">
+        <is>
+          <t>4.4.4</t>
+        </is>
+      </c>
+      <c r="J25" s="30" t="inlineStr">
+        <is>
+          <t>7.1.1</t>
+        </is>
+      </c>
+      <c r="K25" s="31" t="inlineStr">
+        <is>
+          <t>Wade / 10/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="40" customHeight="1">
+      <c r="A26" s="15" t="inlineStr">
+        <is>
+          <t>F08-03</t>
+        </is>
+      </c>
+      <c r="B26" s="32" t="inlineStr">
+        <is>
+          <t>模块8·系统全局治理、运维与监控</t>
+        </is>
+      </c>
+      <c r="C26" s="32" t="inlineStr">
+        <is>
+          <t>企业用户统一身份认证与系统访问</t>
+        </is>
+      </c>
+      <c r="D26" s="32" t="inlineStr">
+        <is>
+          <t>SSO 单点登录</t>
+        </is>
+      </c>
+      <c r="E26" s="32" t="inlineStr">
+        <is>
+          <t>企业SSO集成</t>
+        </is>
+      </c>
+      <c r="F26" s="32" t="inlineStr">
+        <is>
+          <t>对接企业统一身份认证体系，支持用户通过企业账号完成身份认证并登录RIMS，无需维护独立登录凭证。</t>
+        </is>
+      </c>
+      <c r="G26" s="15" t="inlineStr">
+        <is>
+          <t>4.1.2</t>
+        </is>
+      </c>
+      <c r="H26" s="15" t="inlineStr">
+        <is>
+          <t>3.3.1</t>
+        </is>
+      </c>
+      <c r="I26" s="15" t="inlineStr">
+        <is>
+          <t>4.4.4</t>
+        </is>
+      </c>
+      <c r="J26" s="15" t="inlineStr">
+        <is>
+          <t>7.1.1</t>
+        </is>
+      </c>
+      <c r="K26" s="32" t="inlineStr">
+        <is>
+          <t>Wade / 10/16</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="40" customHeight="1">
+      <c r="A27" s="30" t="inlineStr">
+        <is>
+          <t>F08-04</t>
+        </is>
+      </c>
+      <c r="B27" s="31" t="inlineStr">
+        <is>
+          <t>模块8·系统全局治理、运维与监控</t>
+        </is>
+      </c>
+      <c r="C27" s="31" t="inlineStr">
+        <is>
+          <t>企业用户统一身份认证与系统访问</t>
+        </is>
+      </c>
+      <c r="D27" s="31" t="inlineStr">
+        <is>
+          <t>SSO 单点登录</t>
+        </is>
+      </c>
+      <c r="E27" s="31" t="inlineStr">
+        <is>
+          <t>用户身份自动识别与关联</t>
+        </is>
+      </c>
+      <c r="F27" s="31" t="inlineStr">
+        <is>
+          <t>根据企业统一身份信息识别用户，并与RIMS中的用户及角色信息建立关联，为后续权限控制提供身份基础。</t>
+        </is>
+      </c>
+      <c r="G27" s="30" t="inlineStr">
+        <is>
+          <t>4.1.2</t>
+        </is>
+      </c>
+      <c r="H27" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I27" s="30" t="inlineStr">
+        <is>
+          <t>4.4.4</t>
+        </is>
+      </c>
+      <c r="J27" s="30" t="inlineStr">
+        <is>
+          <t>7.1.1</t>
+        </is>
+      </c>
+      <c r="K27" s="31" t="inlineStr">
+        <is>
+          <t>Wade / 10/16</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="40" customHeight="1">
+      <c r="A28" s="15" t="inlineStr">
+        <is>
+          <t>F08-05</t>
+        </is>
+      </c>
+      <c r="B28" s="32" t="inlineStr">
+        <is>
+          <t>模块8·系统全局治理、运维与监控</t>
+        </is>
+      </c>
+      <c r="C28" s="32" t="inlineStr">
+        <is>
+          <t>企业用户统一身份认证与系统访问</t>
+        </is>
+      </c>
+      <c r="D28" s="32" t="inlineStr">
+        <is>
+          <t>SSO 单点登录</t>
+        </is>
+      </c>
+      <c r="E28" s="32" t="inlineStr">
+        <is>
+          <t>登录状态与异常访问控制</t>
+        </is>
+      </c>
+      <c r="F28" s="32" t="inlineStr">
+        <is>
+          <t>对用户登录状态及认证异常进行基础控制，认证失效或账号不可用时限制系统访问。</t>
+        </is>
+      </c>
+      <c r="G28" s="15" t="inlineStr">
+        <is>
+          <t>4.1.3</t>
+        </is>
+      </c>
+      <c r="H28" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I28" s="15" t="inlineStr">
+        <is>
+          <t>4.4.4</t>
+        </is>
+      </c>
+      <c r="J28" s="15" t="inlineStr">
+        <is>
+          <t>7.1.1</t>
+        </is>
+      </c>
+      <c r="K28" s="32" t="inlineStr">
+        <is>
+          <t>Wade / 10/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="34" t="inlineStr">
+        <is>
+          <t>覆盖校验：源文件Scope-Phase1共26项功能，逐项对照WBS开发/协作/走查/测试任务，26/26全覆盖 ✓（本页由源文件自动解析生成，功能名与源文件完全一致）</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="A29:K29"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
     <tabColor rgb="00FFC000"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
@@ -11393,7 +13010,7 @@
       </c>
     </row>
     <row r="3" ht="30" customHeight="1">
-      <c r="A3" s="30" t="inlineStr">
+      <c r="A3" s="33" t="inlineStr">
         <is>
           <t>M1 需求基线冻结</t>
         </is>
@@ -11408,20 +13025,20 @@
           <t>SRS V1.0、基线确认单</t>
         </is>
       </c>
-      <c r="D3" s="30" t="inlineStr">
+      <c r="D3" s="33" t="inlineStr">
         <is>
           <t>SRS评审通过、业务方签字；26项优先级锁定；追踪矩阵建立</t>
         </is>
       </c>
-      <c r="E3" s="30" t="inlineStr">
+      <c r="E3" s="33" t="inlineStr">
         <is>
           <t>Mandy</t>
         </is>
       </c>
-      <c r="F3" s="31" t="n"/>
+      <c r="F3" s="35" t="n"/>
     </row>
     <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="30" t="inlineStr">
+      <c r="A4" s="33" t="inlineStr">
         <is>
           <t>M2 设计评审通过+接口冻结</t>
         </is>
@@ -11436,20 +13053,20 @@
           <t>架构设计文档V1.0、接口定义、数据字典v1</t>
         </is>
       </c>
-      <c r="D4" s="30" t="inlineStr">
+      <c r="D4" s="33" t="inlineStr">
         <is>
           <t>设计评审（含外部架构评审#1意见闭环）通过；模块接口冻结</t>
         </is>
       </c>
-      <c r="E4" s="30" t="inlineStr">
+      <c r="E4" s="33" t="inlineStr">
         <is>
           <t>Wade</t>
         </is>
       </c>
-      <c r="F4" s="31" t="n"/>
+      <c r="F4" s="35" t="n"/>
     </row>
     <row r="5" ht="30" customHeight="1">
-      <c r="A5" s="30" t="inlineStr">
+      <c r="A5" s="33" t="inlineStr">
         <is>
           <t>M3 样本数据端到端MVP</t>
         </is>
@@ -11464,20 +13081,20 @@
           <t>M3演示记录（导入→湖→检索可查）</t>
         </is>
       </c>
-      <c r="D5" s="30" t="inlineStr">
+      <c r="D5" s="33" t="inlineStr">
         <is>
           <t>登录→检索→样本数据可查全链路演示通过；CI/CD四道门禁自动；用例库v1.0完成100%</t>
         </is>
       </c>
-      <c r="E5" s="30" t="inlineStr">
+      <c r="E5" s="33" t="inlineStr">
         <is>
           <t>Wade+DevB</t>
         </is>
       </c>
-      <c r="F5" s="31" t="n"/>
+      <c r="F5" s="35" t="n"/>
     </row>
     <row r="6" ht="30" customHeight="1">
-      <c r="A6" s="30" t="inlineStr">
+      <c r="A6" s="33" t="inlineStr">
         <is>
           <t>M4 26项功能编码完成</t>
         </is>
@@ -11492,20 +13109,20 @@
           <t>走查签字单、追踪矩阵26/26</t>
         </is>
       </c>
-      <c r="D6" s="30" t="inlineStr">
+      <c r="D6" s="33" t="inlineStr">
         <is>
           <t>26项功能编码100%；各模块走查全部签字；无P0缺陷</t>
         </is>
       </c>
-      <c r="E6" s="30" t="inlineStr">
+      <c r="E6" s="33" t="inlineStr">
         <is>
           <t>Mandy</t>
         </is>
       </c>
-      <c r="F6" s="31" t="n"/>
+      <c r="F6" s="35" t="n"/>
     </row>
     <row r="7" ht="30" customHeight="1">
-      <c r="A7" s="30" t="inlineStr">
+      <c r="A7" s="33" t="inlineStr">
         <is>
           <t>M5 代码冻结+CC演练对账通过</t>
         </is>
@@ -11520,20 +13137,20 @@
           <t>全量对账报告、冻结基线、发布包</t>
         </is>
       </c>
-      <c r="D7" s="30" t="inlineStr">
+      <c r="D7" s="33" t="inlineStr">
         <is>
           <t>CC迁移演练完成（600~800表，行数/校验和100%）；P0/P1缺陷清零；代码冻结</t>
         </is>
       </c>
-      <c r="E7" s="30" t="inlineStr">
+      <c r="E7" s="33" t="inlineStr">
         <is>
           <t>DevB</t>
         </is>
       </c>
-      <c r="F7" s="31" t="n"/>
+      <c r="F7" s="35" t="n"/>
     </row>
     <row r="8" ht="30" customHeight="1">
-      <c r="A8" s="30" t="inlineStr">
+      <c r="A8" s="33" t="inlineStr">
         <is>
           <t>M6 系统测试+UAT签字</t>
         </is>
@@ -11548,20 +13165,20 @@
           <t>系统测试报告、UAT报告、手册V1.0</t>
         </is>
       </c>
-      <c r="D8" s="30" t="inlineStr">
+      <c r="D8" s="33" t="inlineStr">
         <is>
           <t>全量测试26项+非功能指标达标（对照2.3.1基线）；业务方UAT签字；缺陷关闭或书面接受；生产就绪评审通过</t>
         </is>
       </c>
-      <c r="E8" s="30" t="inlineStr">
+      <c r="E8" s="33" t="inlineStr">
         <is>
           <t>Mandy</t>
         </is>
       </c>
-      <c r="F8" s="31" t="n"/>
+      <c r="F8" s="35" t="n"/>
     </row>
     <row r="9" ht="30" customHeight="1">
-      <c r="A9" s="30" t="inlineStr">
+      <c r="A9" s="33" t="inlineStr">
         <is>
           <t>M7 生产上线·项目交付</t>
         </is>
@@ -11576,17 +13193,17 @@
           <t>生产系统、终版对账报告、交付确认单</t>
         </is>
       </c>
-      <c r="D9" s="30" t="inlineStr">
+      <c r="D9" s="33" t="inlineStr">
         <is>
           <t>生产部署+CC全量迁移对账通过；核心场景业务确认；交付物归档完成</t>
         </is>
       </c>
-      <c r="E9" s="30" t="inlineStr">
+      <c r="E9" s="33" t="inlineStr">
         <is>
           <t>全员</t>
         </is>
       </c>
-      <c r="F9" s="31" t="n"/>
+      <c r="F9" s="35" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -11596,7 +13213,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="0070AD47"/>
@@ -11689,7 +13306,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="32" t="inlineStr">
+      <c r="A3" s="36" t="inlineStr">
         <is>
           <t>Mark</t>
         </is>
@@ -11704,7 +13321,7 @@
       <c r="G3" s="19" t="n"/>
       <c r="H3" s="19" t="n"/>
       <c r="I3" s="19" t="n"/>
-      <c r="J3" s="33" t="n">
+      <c r="J3" s="37" t="n">
         <v>15</v>
       </c>
       <c r="K3" t="inlineStr">
@@ -11714,7 +13331,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="32" t="inlineStr">
+      <c r="A4" s="36" t="inlineStr">
         <is>
           <t>Mandy</t>
         </is>
@@ -11741,7 +13358,7 @@
       <c r="I4" s="19" t="n">
         <v>3.5</v>
       </c>
-      <c r="J4" s="33" t="n">
+      <c r="J4" s="37" t="n">
         <v>56.5</v>
       </c>
       <c r="K4" t="inlineStr">
@@ -11751,7 +13368,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="32" t="inlineStr">
+      <c r="A5" s="36" t="inlineStr">
         <is>
           <t>Wade</t>
         </is>
@@ -11776,7 +13393,7 @@
       <c r="I5" s="19" t="n">
         <v>5</v>
       </c>
-      <c r="J5" s="33" t="n">
+      <c r="J5" s="37" t="n">
         <v>57.5</v>
       </c>
       <c r="K5" t="inlineStr">
@@ -11786,7 +13403,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="32" t="inlineStr">
+      <c r="A6" s="36" t="inlineStr">
         <is>
           <t>DevB</t>
         </is>
@@ -11811,7 +13428,7 @@
       <c r="I6" s="19" t="n">
         <v>5</v>
       </c>
-      <c r="J6" s="33" t="n">
+      <c r="J6" s="37" t="n">
         <v>58</v>
       </c>
       <c r="K6" t="inlineStr">
@@ -11821,12 +13438,12 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="34" t="inlineStr">
+      <c r="A7" s="38" t="inlineStr">
         <is>
           <t>合计</t>
         </is>
       </c>
-      <c r="J7" s="35" t="n">
+      <c r="J7" s="39" t="n">
         <v>187</v>
       </c>
       <c r="K7" t="inlineStr">
@@ -11843,36 +13460,36 @@
       </c>
     </row>
     <row r="10" ht="28" customHeight="1">
-      <c r="A10" s="34" t="inlineStr">
+      <c r="A10" s="38" t="inlineStr">
         <is>
           <t>项目窗口</t>
         </is>
       </c>
-      <c r="B10" s="36" t="inlineStr">
+      <c r="B10" s="40" t="inlineStr">
         <is>
           <t>2026/9/14（周一）→ 2026/12/11（周五）：89个自然日，59个工作日</t>
         </is>
       </c>
     </row>
     <row r="11" ht="28" customHeight="1">
-      <c r="A11" s="34" t="inlineStr">
+      <c r="A11" s="38" t="inlineStr">
         <is>
           <t>假期扣除</t>
         </is>
       </c>
-      <c r="B11" s="36" t="inlineStr">
+      <c r="B11" s="40" t="inlineStr">
         <is>
           <t>中秋 9/25（五）~9/27（日）；国庆 10/1（四）~10/7（三）；合计损失6个工作日（9/25、10/1、10/2、10/5、10/6、10/7），任务自动顺延</t>
         </is>
       </c>
     </row>
     <row r="12" ht="28" customHeight="1">
-      <c r="A12" s="34" t="inlineStr">
+      <c r="A12" s="38" t="inlineStr">
         <is>
           <t>周末</t>
         </is>
       </c>
-      <c r="B12" s="36" t="inlineStr">
+      <c r="B12" s="40" t="inlineStr">
         <is>
           <t>每周六/日不排任务；官方调休补班日 9/20（日）、10/10（六）逢周末亦不排，可作备用赶工日</t>
         </is>
@@ -11886,60 +13503,60 @@
       </c>
     </row>
     <row r="14" ht="28" customHeight="1">
-      <c r="A14" s="34" t="inlineStr">
+      <c r="A14" s="38" t="inlineStr">
         <is>
           <t>① CC只读账号</t>
         </is>
       </c>
-      <c r="B14" s="36" t="inlineStr">
+      <c r="B14" s="40" t="inlineStr">
         <is>
           <t>9/18提交申请（3.2.3）→ 最迟11/13交付，11/16 CC迁移演练（6.2.1）依赖；责任人DevB；超承诺日3天升级管理层</t>
         </is>
       </c>
     </row>
     <row r="15" ht="28" customHeight="1">
-      <c r="A15" s="34" t="inlineStr">
+      <c r="A15" s="38" t="inlineStr">
         <is>
           <t>② 平台资源交付</t>
         </is>
       </c>
-      <c r="B15" s="36" t="inlineStr">
+      <c r="B15" s="40" t="inlineStr">
         <is>
           <t>ADLS/Databricks/Key Vault等，9/28验收（3.3.3）；责任人Wade</t>
         </is>
       </c>
     </row>
     <row r="16" ht="28" customHeight="1">
-      <c r="A16" s="34" t="inlineStr">
+      <c r="A16" s="38" t="inlineStr">
         <is>
           <t>③ 业务方UAT排期</t>
         </is>
       </c>
-      <c r="B16" s="36" t="inlineStr">
+      <c r="B16" s="40" t="inlineStr">
         <is>
           <t>11/25确认（6.3.4），12/3 UAT执行；责任人Mandy</t>
         </is>
       </c>
     </row>
     <row r="17" ht="28" customHeight="1">
-      <c r="A17" s="34" t="inlineStr">
+      <c r="A17" s="38" t="inlineStr">
         <is>
           <t>④ 生产窗口审批</t>
         </is>
       </c>
-      <c r="B17" s="36" t="inlineStr">
+      <c r="B17" s="40" t="inlineStr">
         <is>
           <t>12/4前完成审批，12/7生产部署（8.1.1）；责任人Mark</t>
         </is>
       </c>
     </row>
     <row r="18" ht="28" customHeight="1">
-      <c r="A18" s="34" t="inlineStr">
+      <c r="A18" s="38" t="inlineStr">
         <is>
           <t>外部评审人（风险缓解）</t>
         </is>
       </c>
-      <c r="B18" s="36" t="inlineStr">
+      <c r="B18" s="40" t="inlineStr">
         <is>
           <t>外部架构评审#1：10/8；外部关键模块评审#2：11/11（RBAC/掩码/加密/处置引擎）；每次2~4小时</t>
         </is>
@@ -11963,7 +13580,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00A6A6A6"/>
@@ -12032,22 +13649,22 @@
           <t>1.1.1</t>
         </is>
       </c>
-      <c r="B3" s="37" t="inlineStr">
+      <c r="B3" s="32" t="inlineStr">
         <is>
           <t>项目启动会与AI Native开发模式对齐</t>
         </is>
       </c>
-      <c r="C3" s="37" t="inlineStr">
+      <c r="C3" s="32" t="inlineStr">
         <is>
           <t>宣布项目范围/里程碑/四道门禁规则/RACI，全员对AI Native协作规约（AI生成+人工审核+门禁合入）达成一致。</t>
         </is>
       </c>
-      <c r="D3" s="37" t="inlineStr">
+      <c r="D3" s="32" t="inlineStr">
         <is>
           <t>启动会纪要、RACI矩阵</t>
         </is>
       </c>
-      <c r="E3" s="37" t="inlineStr">
+      <c r="E3" s="32" t="inlineStr">
         <is>
           <t>全员签认AI协作规约；门禁规则（不可bypass）获管理层授权</t>
         </is>
@@ -12057,7 +13674,7 @@
           <t>Mark</t>
         </is>
       </c>
-      <c r="G3" s="37" t="inlineStr">
+      <c r="G3" s="32" t="inlineStr">
         <is>
           <t>团队3人+PM到岗；AI工具账号就绪</t>
         </is>
@@ -12069,22 +13686,22 @@
           <t>2.2.1</t>
         </is>
       </c>
-      <c r="B4" s="37" t="inlineStr">
+      <c r="B4" s="32" t="inlineStr">
         <is>
           <t>AI生成SRS初稿+人工修订</t>
         </is>
       </c>
-      <c r="C4" s="37" t="inlineStr">
+      <c r="C4" s="32" t="inlineStr">
         <is>
           <t>AI根据访谈纪要与26项功能清单生成SRS（数据流图/归档范围矩阵/保留期矩阵），人工逐条核对覆盖与准确性后修订定稿。</t>
         </is>
       </c>
-      <c r="D4" s="37" t="inlineStr">
+      <c r="D4" s="32" t="inlineStr">
         <is>
           <t>SRS V1.0</t>
         </is>
       </c>
-      <c r="E4" s="37" t="inlineStr">
+      <c r="E4" s="32" t="inlineStr">
         <is>
           <t>26项功能100%覆盖并通过评审；业务方签字冻结基线</t>
         </is>
@@ -12094,7 +13711,7 @@
           <t>Mandy</t>
         </is>
       </c>
-      <c r="G4" s="37" t="inlineStr">
+      <c r="G4" s="32" t="inlineStr">
         <is>
           <t>2.1.1/2.1.2已完成；AI工具可用</t>
         </is>
@@ -12106,22 +13723,22 @@
           <t>2.3.1</t>
         </is>
       </c>
-      <c r="B5" s="37" t="inlineStr">
+      <c r="B5" s="32" t="inlineStr">
         <is>
           <t>非功能需求梳理与验收指标定义</t>
         </is>
       </c>
-      <c r="C5" s="37" t="inlineStr">
+      <c r="C5" s="32" t="inlineStr">
         <is>
           <t>与功能需求同一基线梳理NFR：性能（检索响应/导出吞吐/并发）、安全（加密/越权/审计）、合规（数据不出境）、可用性（备份RPO/RTO）、容量（600~800表及增长），形成可验收指标。</t>
         </is>
       </c>
-      <c r="D5" s="37" t="inlineStr">
+      <c r="D5" s="32" t="inlineStr">
         <is>
           <t>非功能需求指标清单（NFR基线）</t>
         </is>
       </c>
-      <c r="E5" s="37" t="inlineStr">
+      <c r="E5" s="32" t="inlineStr">
         <is>
           <t>每项NFR有量化指标与验收方法；纳入需求基线统一管理</t>
         </is>
@@ -12131,7 +13748,7 @@
           <t>Mandy</t>
         </is>
       </c>
-      <c r="G5" s="37" t="inlineStr">
+      <c r="G5" s="32" t="inlineStr">
         <is>
           <t>SRS基线已冻结</t>
         </is>
@@ -12143,22 +13760,22 @@
           <t>3.1.1</t>
         </is>
       </c>
-      <c r="B6" s="37" t="inlineStr">
+      <c r="B6" s="32" t="inlineStr">
         <is>
           <t>项目初始化</t>
         </is>
       </c>
-      <c r="C6" s="37" t="inlineStr">
+      <c r="C6" s="32" t="inlineStr">
         <is>
           <t>代码仓库与分支策略、开发环境统一（本地Docker+云资源连通）、AI工具账号开通，输出初始化核对清单，项目第一天完成。</t>
         </is>
       </c>
-      <c r="D6" s="37" t="inlineStr">
+      <c r="D6" s="32" t="inlineStr">
         <is>
           <t>初始化核对清单、可用的空仓库与本地环境</t>
         </is>
       </c>
-      <c r="E6" s="37" t="inlineStr">
+      <c r="E6" s="32" t="inlineStr">
         <is>
           <t>前后端仓库/分支策略/本地环境/AI工具账号全部就绪并可验证</t>
         </is>
@@ -12168,7 +13785,7 @@
           <t>Wade</t>
         </is>
       </c>
-      <c r="G6" s="37" t="inlineStr">
+      <c r="G6" s="32" t="inlineStr">
         <is>
           <t>云订阅与AI工具可申请</t>
         </is>
@@ -12180,22 +13797,22 @@
           <t>3.1.2</t>
         </is>
       </c>
-      <c r="B7" s="37" t="inlineStr">
+      <c r="B7" s="32" t="inlineStr">
         <is>
           <t>AI开发工具链与编码规范</t>
         </is>
       </c>
-      <c r="C7" s="37" t="inlineStr">
+      <c r="C7" s="32" t="inlineStr">
         <is>
           <t>搭建AI Coding工作流（工具链/提示词模板库/人机协作规约/ADR规范），为Vibe Coding立规矩。</t>
         </is>
       </c>
-      <c r="D7" s="37" t="inlineStr">
+      <c r="D7" s="32" t="inlineStr">
         <is>
           <t>AI开发规范V1.0、工具链配置</t>
         </is>
       </c>
-      <c r="E7" s="37" t="inlineStr">
+      <c r="E7" s="32" t="inlineStr">
         <is>
           <t>规范评审通过；关键决策以ADR留痕；工具链全员可用</t>
         </is>
@@ -12205,7 +13822,7 @@
           <t>Wade</t>
         </is>
       </c>
-      <c r="G7" s="37" t="inlineStr">
+      <c r="G7" s="32" t="inlineStr">
         <is>
           <t>3.1.1初始化完成；AI工具订阅可用</t>
         </is>
@@ -12217,22 +13834,22 @@
           <t>3.1.3</t>
         </is>
       </c>
-      <c r="B8" s="37" t="inlineStr">
+      <c r="B8" s="32" t="inlineStr">
         <is>
           <t>四道安全门禁CI/CD骨架</t>
         </is>
       </c>
-      <c r="C8" s="37" t="inlineStr">
+      <c r="C8" s="32" t="inlineStr">
         <is>
           <t>Azure DevOps流水线：构建+镜像+SAST静态扫描/依赖扫描/密钥扫描/越权与掩码旁路用例四道硬门禁，任何合入必须过门禁。</t>
         </is>
       </c>
-      <c r="D8" s="37" t="inlineStr">
+      <c r="D8" s="32" t="inlineStr">
         <is>
           <t>CI/CD流水线（4道硬门禁）</t>
         </is>
       </c>
-      <c r="E8" s="37" t="inlineStr">
+      <c r="E8" s="32" t="inlineStr">
         <is>
           <t>演示一次拦截样例；门禁不可bypass（含紧急发布）；集成测试覆盖率红线写入配置</t>
         </is>
@@ -12242,7 +13859,7 @@
           <t>Wade</t>
         </is>
       </c>
-      <c r="G8" s="37" t="inlineStr">
+      <c r="G8" s="32" t="inlineStr">
         <is>
           <t>Azure DevOps权限就绪</t>
         </is>
@@ -12254,22 +13871,22 @@
           <t>3.2.3</t>
         </is>
       </c>
-      <c r="B9" s="37" t="inlineStr">
+      <c r="B9" s="32" t="inlineStr">
         <is>
           <t>外部依赖前置（资源+CC账号申请）</t>
         </is>
       </c>
-      <c r="C9" s="37" t="inlineStr">
+      <c r="C9" s="32" t="inlineStr">
         <is>
           <t>平台资源申请单（区域=境内）与CC只读账号申请当日提交并跟踪，账号周期最长、为11/16演练的关键前置。</t>
         </is>
       </c>
-      <c r="D9" s="37" t="inlineStr">
+      <c r="D9" s="32" t="inlineStr">
         <is>
           <t>申请单、外部依赖清单</t>
         </is>
       </c>
-      <c r="E9" s="37" t="inlineStr">
+      <c r="E9" s="32" t="inlineStr">
         <is>
           <t>申请已受理并有承诺日期；责任人与承诺日期书面确认</t>
         </is>
@@ -12279,7 +13896,7 @@
           <t>DevB</t>
         </is>
       </c>
-      <c r="G9" s="37" t="inlineStr">
+      <c r="G9" s="32" t="inlineStr">
         <is>
           <t>平台团队受理流程正常</t>
         </is>
@@ -12291,22 +13908,22 @@
           <t>3.3.6</t>
         </is>
       </c>
-      <c r="B10" s="37" t="inlineStr">
+      <c r="B10" s="32" t="inlineStr">
         <is>
           <t>设计评审通过+接口冻结◆M2</t>
         </is>
       </c>
-      <c r="C10" s="37" t="inlineStr">
+      <c r="C10" s="32" t="inlineStr">
         <is>
           <t>总体架构定稿（架构图已预确认，本阶段收尾）+模块接口定义冻结，此后变更走变更流程。</t>
         </is>
       </c>
-      <c r="D10" s="37" t="inlineStr">
+      <c r="D10" s="32" t="inlineStr">
         <is>
           <t>架构设计文档V1.0、接口冻结基线</t>
         </is>
       </c>
-      <c r="E10" s="37" t="inlineStr">
+      <c r="E10" s="32" t="inlineStr">
         <is>
           <t>评审通过（含外部评审#1意见闭环）；A/B模块边界书面确认</t>
         </is>
@@ -12316,7 +13933,7 @@
           <t>Wade</t>
         </is>
       </c>
-      <c r="G10" s="37" t="inlineStr">
+      <c r="G10" s="32" t="inlineStr">
         <is>
           <t>外部架构评审人到场</t>
         </is>
@@ -12328,22 +13945,22 @@
           <t>4.3.3</t>
         </is>
       </c>
-      <c r="B11" s="37" t="inlineStr">
+      <c r="B11" s="32" t="inlineStr">
         <is>
           <t>端到端联调◆M3（样本MVP）</t>
         </is>
       </c>
-      <c r="C11" s="37" t="inlineStr">
+      <c r="C11" s="32" t="inlineStr">
         <is>
           <t>登录→检索→样本数据可查全链路演示，并做一次端到端自查，提前暴露分层/权限模型方向性错误（风险A缓解）。</t>
         </is>
       </c>
-      <c r="D11" s="37" t="inlineStr">
+      <c r="D11" s="32" t="inlineStr">
         <is>
           <t>M3演示记录</t>
         </is>
       </c>
-      <c r="E11" s="37" t="inlineStr">
+      <c r="E11" s="32" t="inlineStr">
         <is>
           <t>全链路演示通过；CI/CD全自动；用例库v1.0完成</t>
         </is>
@@ -12353,7 +13970,7 @@
           <t>Wade</t>
         </is>
       </c>
-      <c r="G11" s="37" t="inlineStr">
+      <c r="G11" s="32" t="inlineStr">
         <is>
           <t>模块1/8样本功能完成</t>
         </is>
@@ -12365,22 +13982,22 @@
           <t>4.2.5</t>
         </is>
       </c>
-      <c r="B12" s="37" t="inlineStr">
+      <c r="B12" s="32" t="inlineStr">
         <is>
           <t>F01-04/05 迁移完整性校验</t>
         </is>
       </c>
-      <c r="C12" s="37" t="inlineStr">
+      <c r="C12" s="32" t="inlineStr">
         <is>
           <t>迁移前后完整性基准记录与比对（行数/校验和/SHA-256），形成对账脚本，为CC全量迁移对账复用。</t>
         </is>
       </c>
-      <c r="D12" s="37" t="inlineStr">
+      <c r="D12" s="32" t="inlineStr">
         <is>
           <t>对账脚本、校验报告</t>
         </is>
       </c>
-      <c r="E12" s="37" t="inlineStr">
+      <c r="E12" s="32" t="inlineStr">
         <is>
           <t>样本表比对差异=0；脚本可重复执行并输出报告</t>
         </is>
@@ -12390,7 +14007,7 @@
           <t>DevB</t>
         </is>
       </c>
-      <c r="G12" s="37" t="inlineStr">
+      <c r="G12" s="32" t="inlineStr">
         <is>
           <t>4.2.4 RAW层落地完成</t>
         </is>
@@ -12402,22 +14019,22 @@
           <t>5.2.5</t>
         </is>
       </c>
-      <c r="B13" s="37" t="inlineStr">
+      <c r="B13" s="32" t="inlineStr">
         <is>
           <t>F03-01 到期自动删除处置引擎</t>
         </is>
       </c>
-      <c r="C13" s="37" t="inlineStr">
+      <c r="C13" s="32" t="inlineStr">
         <is>
           <t>处置引擎：扫描到期分区→DROP PARTITION→VACUUM物理清除，配合Legal Hold豁免与留痕。</t>
         </is>
       </c>
-      <c r="D13" s="37" t="inlineStr">
+      <c r="D13" s="32" t="inlineStr">
         <is>
           <t>处置引擎作业</t>
         </is>
       </c>
-      <c r="E13" s="37" t="inlineStr">
+      <c r="E13" s="32" t="inlineStr">
         <is>
           <t>短保留期样本到期被物理清除且留痕完整；Legal Hold记录不被删除</t>
         </is>
@@ -12427,7 +14044,7 @@
           <t>DevB</t>
         </is>
       </c>
-      <c r="G13" s="37" t="inlineStr">
+      <c r="G13" s="32" t="inlineStr">
         <is>
           <t>生命周期分区设计已验证</t>
         </is>
@@ -12439,22 +14056,22 @@
           <t>5.4.1</t>
         </is>
       </c>
-      <c r="B14" s="37" t="inlineStr">
+      <c r="B14" s="32" t="inlineStr">
         <is>
           <t>外部关键模块评审#2</t>
         </is>
       </c>
-      <c r="C14" s="37" t="inlineStr">
+      <c r="C14" s="32" t="inlineStr">
         <is>
           <t>外部评审人审查RBAC/掩码/加密/处置引擎四个关键模块的AI生成代码，弥补无内部代码评审的缺陷拦截缺口。</t>
         </is>
       </c>
-      <c r="D14" s="37" t="inlineStr">
+      <c r="D14" s="32" t="inlineStr">
         <is>
           <t>评审记录、行动项清单</t>
         </is>
       </c>
-      <c r="E14" s="37" t="inlineStr">
+      <c r="E14" s="32" t="inlineStr">
         <is>
           <t>关键模块高严重度问题清零或列入修复计划</t>
         </is>
@@ -12464,7 +14081,7 @@
           <t>Wade</t>
         </is>
       </c>
-      <c r="G14" s="37" t="inlineStr">
+      <c r="G14" s="32" t="inlineStr">
         <is>
           <t>外部评审人每两周4h已授权</t>
         </is>
@@ -12476,22 +14093,22 @@
           <t>6.2.1</t>
         </is>
       </c>
-      <c r="B15" s="37" t="inlineStr">
+      <c r="B15" s="32" t="inlineStr">
         <is>
           <t>CC真实数据迁移演练I</t>
         </is>
       </c>
-      <c r="C15" s="37" t="inlineStr">
+      <c r="C15" s="32" t="inlineStr">
         <is>
           <t>1253表扫描分类→600~800有效表分批迁移实战（F01全链路），作业由AI生成、人工监控。</t>
         </is>
       </c>
-      <c r="D15" s="37" t="inlineStr">
+      <c r="D15" s="32" t="inlineStr">
         <is>
           <t>扫描分类清单、迁移批次计划</t>
         </is>
       </c>
-      <c r="E15" s="37" t="inlineStr">
+      <c r="E15" s="32" t="inlineStr">
         <is>
           <t>首批迁移成功率与吞吐达标；类型映射适配清单输出</t>
         </is>
@@ -12501,7 +14118,7 @@
           <t>DevB</t>
         </is>
       </c>
-      <c r="G15" s="37" t="inlineStr">
+      <c r="G15" s="32" t="inlineStr">
         <is>
           <t>CC只读账号已交付</t>
         </is>
@@ -12513,22 +14130,22 @@
           <t>6.2.3</t>
         </is>
       </c>
-      <c r="B16" s="37" t="inlineStr">
+      <c r="B16" s="32" t="inlineStr">
         <is>
           <t>CC全量对账报告</t>
         </is>
       </c>
-      <c r="C16" s="37" t="inlineStr">
+      <c r="C16" s="32" t="inlineStr">
         <is>
           <t>演练完成后对RAW/CURATED/LAKE/SERVE四层做行数与字节级对账，AI生成报告初稿+差异处理记录。</t>
         </is>
       </c>
-      <c r="D16" s="37" t="inlineStr">
+      <c r="D16" s="32" t="inlineStr">
         <is>
           <t>全量对账报告</t>
         </is>
       </c>
-      <c r="E16" s="37" t="inlineStr">
+      <c r="E16" s="32" t="inlineStr">
         <is>
           <t>行数/校验和100%一致；差异全部闭环并有记录</t>
         </is>
@@ -12538,7 +14155,7 @@
           <t>DevB</t>
         </is>
       </c>
-      <c r="G16" s="37" t="inlineStr">
+      <c r="G16" s="32" t="inlineStr">
         <is>
           <t>6.2.2逐批对账完成</t>
         </is>
@@ -12550,22 +14167,22 @@
           <t>7.1.3</t>
         </is>
       </c>
-      <c r="B17" s="37" t="inlineStr">
+      <c r="B17" s="32" t="inlineStr">
         <is>
           <t>UAT组织与主持◆M6</t>
         </is>
       </c>
-      <c r="C17" s="37" t="inlineStr">
+      <c r="C17" s="32" t="inlineStr">
         <is>
           <t>业务方按CC真实场景执行UAT（检索/预览/导出/处置/审计全场景），BA主持并跟踪问题闭环。</t>
         </is>
       </c>
-      <c r="D17" s="37" t="inlineStr">
+      <c r="D17" s="32" t="inlineStr">
         <is>
           <t>UAT报告、签字</t>
         </is>
       </c>
-      <c r="E17" s="37" t="inlineStr">
+      <c r="E17" s="32" t="inlineStr">
         <is>
           <t>P0/P1问题全部关闭；用户代表签署UAT结论</t>
         </is>
@@ -12575,7 +14192,7 @@
           <t>Mandy</t>
         </is>
       </c>
-      <c r="G17" s="37" t="inlineStr">
+      <c r="G17" s="32" t="inlineStr">
         <is>
           <t>全量测试通过；业务方排期确认</t>
         </is>
@@ -12587,22 +14204,22 @@
           <t>7.2.3/7.2.6</t>
         </is>
       </c>
-      <c r="B18" s="37" t="inlineStr">
+      <c r="B18" s="32" t="inlineStr">
         <is>
           <t>性能与安全可靠性专项验证</t>
         </is>
       </c>
-      <c r="C18" s="37" t="inlineStr">
+      <c r="C18" s="32" t="inlineStr">
         <is>
           <t>对照2.3.1 NFR基线逐项验证：性能（检索响应/预览加载/导出吞吐/并发）实测与调优；安全（越权/掩码旁路用例）执行；可靠性（备份恢复+灾备切换）演练。</t>
         </is>
       </c>
-      <c r="D18" s="37" t="inlineStr">
+      <c r="D18" s="32" t="inlineStr">
         <is>
           <t>性能验证报告、安全可靠性验证报告</t>
         </is>
       </c>
-      <c r="E18" s="37" t="inlineStr">
+      <c r="E18" s="32" t="inlineStr">
         <is>
           <t>NFR指标全部达标或有书面接受；不达标项完成调优并复测</t>
         </is>
@@ -12612,7 +14229,7 @@
           <t>Wade/DevB</t>
         </is>
       </c>
-      <c r="G18" s="37" t="inlineStr">
+      <c r="G18" s="32" t="inlineStr">
         <is>
           <t>全量测试通过；迁移预跑完成</t>
         </is>
@@ -12624,22 +14241,22 @@
           <t>8.1.2</t>
         </is>
       </c>
-      <c r="B19" s="37" t="inlineStr">
+      <c r="B19" s="32" t="inlineStr">
         <is>
           <t>CC生产全量迁移</t>
         </is>
       </c>
-      <c r="C19" s="37" t="inlineStr">
+      <c r="C19" s="32" t="inlineStr">
         <is>
           <t>生产环境分批执行600~800表全量迁移+终版对账，作业自动化执行、人工值守。</t>
         </is>
       </c>
-      <c r="D19" s="37" t="inlineStr">
+      <c r="D19" s="32" t="inlineStr">
         <is>
           <t>终版对账报告</t>
         </is>
       </c>
-      <c r="E19" s="37" t="inlineStr">
+      <c r="E19" s="32" t="inlineStr">
         <is>
           <t>迁移对账差异率=0；回退方案演练就绪</t>
         </is>
@@ -12649,7 +14266,7 @@
           <t>DevB</t>
         </is>
       </c>
-      <c r="G19" s="37" t="inlineStr">
+      <c r="G19" s="32" t="inlineStr">
         <is>
           <t>生产窗口获批；预跑通过</t>
         </is>
@@ -12663,7 +14280,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00ED7D31"/>
@@ -12804,7 +14421,7 @@
           <t>任务完成率</t>
         </is>
       </c>
-      <c r="B10" s="38">
+      <c r="B10" s="41">
         <f>IFERROR(COUNTIF('WBS分解'!$L$4:$L$164,"已完成")/COUNTA('WBS分解'!$A$4:$A$164),0)</f>
         <v/>
       </c>
@@ -12820,7 +14437,7 @@
           <t>整体平均进度</t>
         </is>
       </c>
-      <c r="B11" s="38">
+      <c r="B11" s="41">
         <f>AVERAGE('WBS分解'!$M$4:$M$164)</f>
         <v/>
       </c>
@@ -12927,7 +14544,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="39" t="inlineStr">
+      <c r="A19" s="42" t="inlineStr">
         <is>
           <t>※ 本页自动汇总自「WBS分解」表，请勿手工修改。</t>
         </is>

--- a/RIMS项目WBS工作分解_AI Native版.xlsx
+++ b/RIMS项目WBS工作分解_AI Native版.xlsx
@@ -839,7 +839,7 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>Vibe Coding：AI生成代码+人工审核+四道门禁硬卡点合入；每周五下午固定0.5天技术债偿还；外部关键模块评审2次（10/8、11/11）</t>
+          <t>Vibe Coding：AI生成代码+人工审核+四道门禁硬卡点合入；每周五下午固定0.5天技术债偿还；外部关键模块评审2次（10/9、11/11）</t>
         </is>
       </c>
     </row>
@@ -2958,7 +2958,7 @@
       </c>
       <c r="B33" s="22" t="inlineStr">
         <is>
-          <t>四道安全门禁CI/CD骨架（构建+镜像+SAST/依赖/密钥扫描/越权用例门禁）</t>
+          <t>四道安全门禁CI/CD搭建（构建+镜像+SAST/依赖/密钥扫描/越权用例门禁，4人天：流水线搭建/扫描工具接入/越权用例门禁/拦截样例演示）</t>
         </is>
       </c>
       <c r="C33" s="15" t="n">
@@ -2978,13 +2978,13 @@
         <v>46281</v>
       </c>
       <c r="G33" s="18" t="n">
-        <v>46282</v>
+        <v>46286</v>
       </c>
       <c r="H33" s="15" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I33" s="19" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J33" s="17" t="inlineStr">
         <is>
@@ -3013,7 +3013,7 @@
       <c r="P33" s="21" t="n"/>
       <c r="Q33" s="17" t="inlineStr">
         <is>
-          <t>门禁不可bypass（风险清单B措施）</t>
+          <t>4人天；门禁不可bypass（风险清单B措施），需演示拦截样例</t>
         </is>
       </c>
     </row>
@@ -3042,10 +3042,10 @@
         </is>
       </c>
       <c r="F34" s="18" t="n">
-        <v>46283</v>
+        <v>46287</v>
       </c>
       <c r="G34" s="18" t="n">
-        <v>46283</v>
+        <v>46287</v>
       </c>
       <c r="H34" s="15" t="n">
         <v>1</v>
@@ -3733,10 +3733,10 @@
         </is>
       </c>
       <c r="F45" s="18" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="G45" s="18" t="n">
-        <v>46287</v>
+        <v>46289</v>
       </c>
       <c r="H45" s="15" t="n">
         <v>2</v>
@@ -3800,10 +3800,10 @@
         </is>
       </c>
       <c r="F46" s="18" t="n">
-        <v>46288</v>
+        <v>46293</v>
       </c>
       <c r="G46" s="18" t="n">
-        <v>46289</v>
+        <v>46294</v>
       </c>
       <c r="H46" s="15" t="n">
         <v>2</v>
@@ -3846,7 +3846,7 @@
       </c>
       <c r="B47" s="22" t="inlineStr">
         <is>
-          <t>平台资源验收（ADLS/SQL DB/Databricks/Key Vault连通）</t>
+          <t>平台资源验收（ADLS/SQL DB/Databricks/Key Vault连通性验证）</t>
         </is>
       </c>
       <c r="C47" s="15" t="n">
@@ -3863,16 +3863,16 @@
         </is>
       </c>
       <c r="F47" s="18" t="n">
-        <v>46293</v>
+        <v>46295</v>
       </c>
       <c r="G47" s="18" t="n">
-        <v>46293</v>
+        <v>46295</v>
       </c>
       <c r="H47" s="15" t="n">
         <v>1</v>
       </c>
       <c r="I47" s="19" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="J47" s="17" t="inlineStr">
         <is>
@@ -3901,7 +3901,7 @@
       <c r="P47" s="21" t="n"/>
       <c r="Q47" s="17" t="inlineStr">
         <is>
-          <t>外部依赖：资源交付，逾期3天升级管理层</t>
+          <t>外部依赖：资源交付，逾期3天升级管理层；9/30验收</t>
         </is>
       </c>
     </row>
@@ -3930,16 +3930,16 @@
         </is>
       </c>
       <c r="F48" s="18" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="G48" s="18" t="n">
-        <v>46295</v>
+        <v>46303</v>
       </c>
       <c r="H48" s="15" t="n">
         <v>2</v>
       </c>
       <c r="I48" s="19" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="J48" s="17" t="inlineStr">
         <is>
@@ -3968,7 +3968,7 @@
       <c r="P48" s="21" t="n"/>
       <c r="Q48" s="17" t="inlineStr">
         <is>
-          <t>架构图已预确认，本任务为收尾定稿+ADR留痕</t>
+          <t>架构图已预确认，收尾定稿+ADR留痕，AI辅助成文</t>
         </is>
       </c>
     </row>
@@ -3997,16 +3997,16 @@
         </is>
       </c>
       <c r="F49" s="18" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="G49" s="18" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="H49" s="15" t="n">
         <v>1</v>
       </c>
       <c r="I49" s="19" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="J49" s="17" t="inlineStr">
         <is>
@@ -4035,7 +4035,7 @@
       <c r="P49" s="21" t="n"/>
       <c r="Q49" s="17" t="inlineStr">
         <is>
-          <t>风险缓解A：引入外部对手方挑战架构</t>
+          <t>风险缓解A：引入外部对手方挑战架构；10/9上午</t>
         </is>
       </c>
     </row>
@@ -5544,7 +5544,7 @@
       <c r="P73" s="21" t="n"/>
       <c r="Q73" s="17" t="inlineStr">
         <is>
-          <t>AI从代码+演示反生成，人工润色（风险D缓解）</t>
+          <t>AI从代码与演示反生成，人工润色</t>
         </is>
       </c>
     </row>
@@ -13376,7 +13376,7 @@
       <c r="B5" s="19" t="n"/>
       <c r="C5" s="19" t="n"/>
       <c r="D5" s="19" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="E5" s="19" t="n">
         <v>10</v>
@@ -13394,11 +13394,11 @@
         <v>5</v>
       </c>
       <c r="J5" s="37" t="n">
-        <v>57.5</v>
+        <v>58</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>负荷率 97%（59个工作日）</t>
+          <t>负荷率 98%（59个工作日）</t>
         </is>
       </c>
     </row>
@@ -13444,11 +13444,11 @@
         </is>
       </c>
       <c r="J7" s="39" t="n">
-        <v>187</v>
+        <v>187.5</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>原角色表估算185人天（含交付15）；本版187.0人天，新增项目初始化/非功能专项/会议纪要显式化</t>
+          <t>原角色表估算185人天（含交付15）；本版187.5人天，新增项目初始化/非功能专项/会议纪要显式化</t>
         </is>
       </c>
     </row>
@@ -13522,7 +13522,7 @@
       </c>
       <c r="B15" s="40" t="inlineStr">
         <is>
-          <t>ADLS/Databricks/Key Vault等，9/28验收（3.3.3）；责任人Wade</t>
+          <t>ADLS/Databricks/Key Vault等，9/30验收（3.3.3）；责任人Wade</t>
         </is>
       </c>
     </row>
@@ -13558,7 +13558,7 @@
       </c>
       <c r="B18" s="40" t="inlineStr">
         <is>
-          <t>外部架构评审#1：10/8；外部关键模块评审#2：11/11（RBAC/掩码/加密/处置引擎）；每次2~4小时</t>
+          <t>外部架构评审#1：10/9（与M2设计评审同日）；外部关键模块评审#2：11/11（RBAC/掩码/加密/处置引擎）；每次2~4小时</t>
         </is>
       </c>
     </row>
@@ -13836,12 +13836,12 @@
       </c>
       <c r="B8" s="32" t="inlineStr">
         <is>
-          <t>四道安全门禁CI/CD骨架</t>
+          <t>四道安全门禁CI/CD搭建（4人天）</t>
         </is>
       </c>
       <c r="C8" s="32" t="inlineStr">
         <is>
-          <t>Azure DevOps流水线：构建+镜像+SAST静态扫描/依赖扫描/密钥扫描/越权与掩码旁路用例四道硬门禁，任何合入必须过门禁。</t>
+          <t>Azure DevOps流水线：构建+镜像+SAST静态扫描/依赖扫描/密钥扫描/越权与掩码旁路用例四道硬门禁；含扫描工具接入、越权用例门禁开发与拦截样例演示，任何合入必须过门禁。</t>
         </is>
       </c>
       <c r="D8" s="32" t="inlineStr">
@@ -13861,7 +13861,7 @@
       </c>
       <c r="G8" s="32" t="inlineStr">
         <is>
-          <t>Azure DevOps权限就绪</t>
+          <t>Azure DevOps权限就绪；3.1.2规范已定</t>
         </is>
       </c>
     </row>

--- a/RIMS项目WBS工作分解_AI Native版.xlsx
+++ b/RIMS项目WBS工作分解_AI Native版.xlsx
@@ -3930,16 +3930,16 @@
         </is>
       </c>
       <c r="F48" s="18" t="n">
-        <v>46295</v>
+        <v>46303</v>
       </c>
       <c r="G48" s="18" t="n">
         <v>46303</v>
       </c>
       <c r="H48" s="15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I48" s="19" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="J48" s="17" t="inlineStr">
         <is>
@@ -4073,7 +4073,7 @@
         <v>1</v>
       </c>
       <c r="I50" s="27" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="J50" s="25" t="inlineStr">
         <is>
@@ -4102,7 +4102,7 @@
       <c r="P50" s="29" t="n"/>
       <c r="Q50" s="25" t="inlineStr">
         <is>
-          <t>★M2 10/9；此后接口变更走变更流程</t>
+          <t>★M2 10/9（下午评审会）；此后接口变更走变更流程</t>
         </is>
       </c>
     </row>
@@ -13376,7 +13376,7 @@
       <c r="B5" s="19" t="n"/>
       <c r="C5" s="19" t="n"/>
       <c r="D5" s="19" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E5" s="19" t="n">
         <v>10</v>
@@ -13394,11 +13394,11 @@
         <v>5</v>
       </c>
       <c r="J5" s="37" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>负荷率 98%（59个工作日）</t>
+          <t>负荷率 97%（59个工作日）</t>
         </is>
       </c>
     </row>
@@ -13444,11 +13444,11 @@
         </is>
       </c>
       <c r="J7" s="39" t="n">
-        <v>187.5</v>
+        <v>186.5</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>原角色表估算185人天（含交付15）；本版187.5人天，新增项目初始化/非功能专项/会议纪要显式化</t>
+          <t>原角色表估算185人天（含交付15）；本版186.5人天，新增项目初始化/非功能专项/会议纪要显式化</t>
         </is>
       </c>
     </row>

--- a/RIMS项目WBS工作分解_AI Native版.xlsx
+++ b/RIMS项目WBS工作分解_AI Native版.xlsx
@@ -640,7 +640,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B28"/>
+  <dimension ref="A1:B29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -681,266 +681,278 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>3人×3个月：Mandy（BA/测试/文档）、Wade（开发A：架构+前端+应用API）、DevB（开发B：后端+数据）；PM Mark按约定投入15人天贯穿全程；项目正式文档撰写统一由Mandy执行</t>
+          <t>Mandy（BA/测试/文档）50人天、Wade（开发A：架构+前端+应用API）60人天、DevB（开发B：后端+数据）60人天、PM Mark 15人天，合计185人天——与《项目执行计划》团队角色表估算一致；项目正式文档撰写统一由Mandy执行</t>
         </is>
       </c>
     </row>
     <row r="6" ht="30" customHeight="1">
       <c r="A6" s="3" t="inlineStr">
         <is>
+          <t>Mandy工作量口径</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>50人天封顶：AI Native下纪要/SRS/测试用例/手册初稿由AI生成、Mandy审核润色，12项任务各压缩0.5人天、纪要整理2→1人天</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="30" customHeight="1">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
           <t>PM投入分布</t>
         </is>
       </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>Mark 15人天贯穿式分布：启动会1 + 每周项目例会12次×0.5=6 + 开发期每日任务同步会约2 + 进度/风险跟踪2.5 + 里程碑评审2.5 + 交付确认收尾1（最后1天在12/11项目结束时使用）</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="18" customHeight="1">
-      <c r="A7" s="3" t="inlineStr">
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>Mark 15人天贯穿式分布：启动会1 + 每周项目例会12次×0.5=6 + 开发期每日任务同步会约2 + 进度/风险跟踪2.5 + 里程碑评审2.5 + 交付确认收尾1（最后1天在12/16项目结束时使用）</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="30" customHeight="1">
+      <c r="A8" s="3" t="inlineStr">
         <is>
           <t>周期</t>
         </is>
       </c>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>2026/9/14（周一）启动 → 2026/12/11（周五）交付，共89个自然日、59个工作日（≈12个工作周）</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>2026/9/14（周一）启动 → 2026/12/16（周三）交付，共94个自然日、62个工作日（≈12.5个工作周；因Wade/DevB各铺满60人天，交付较12/11顺延3个工作日）</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="20" customHeight="1">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>二、排期规则</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="18" customHeight="1">
-      <c r="A9" s="3" t="inlineStr">
+    <row r="10" ht="18" customHeight="1">
+      <c r="A10" s="3" t="inlineStr">
         <is>
           <t>开工日</t>
         </is>
       </c>
-      <c r="B9" s="4" t="inlineStr">
+      <c r="B10" s="4" t="inlineStr">
         <is>
           <t>9/14（周一）</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="30" customHeight="1">
-      <c r="A10" s="3" t="inlineStr">
+    <row r="11" ht="30" customHeight="1">
+      <c r="A11" s="3" t="inlineStr">
         <is>
           <t>不排任务日</t>
         </is>
       </c>
-      <c r="B10" s="4" t="inlineStr">
+      <c r="B11" s="4" t="inlineStr">
         <is>
           <t>周末（周六/周日）；中秋节 9/25（周五）~9/27（周日）；国庆节 10/1（周四）~10/7（周三）。假期合计损失6个工作日，任务自动顺延</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="18" customHeight="1">
-      <c r="A11" s="3" t="inlineStr">
+    <row r="12" ht="18" customHeight="1">
+      <c r="A12" s="3" t="inlineStr">
         <is>
           <t>调休补班日</t>
         </is>
       </c>
-      <c r="B11" s="4" t="inlineStr">
+      <c r="B12" s="4" t="inlineStr">
         <is>
           <t>官方补班日 9/20（周日）、10/10（周六）逢周末，按约定同样不排任务；若进度落后可启用为备用赶工日</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="30" customHeight="1">
-      <c r="A12" s="3" t="inlineStr">
+    <row r="13" ht="30" customHeight="1">
+      <c r="A13" s="3" t="inlineStr">
         <is>
           <t>与原计划对应</t>
         </is>
       </c>
-      <c r="B12" s="4" t="inlineStr">
-        <is>
-          <t>原《项目执行计划》W1~W12（60工作日）→ 本版按工作日一一顺延至9/14~12/11（59工作日）；因架构图已预确认，设计收尾较原计划压缩1天</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="20" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>原《项目执行计划》W1~W12（60工作日）→ 本版62个工作日（9/14~12/16）：Wade/DevB按各60人天铺满顺延，M1~M4里程碑不变，M5 11/27→12/1、M6 12/4→12/9、M7 12/11→12/16</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="20" customHeight="1">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>三、AI Native模式（与模板传统模式的差异）</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="30" customHeight="1">
-      <c r="A14" s="3" t="inlineStr">
-        <is>
-          <t>总体</t>
-        </is>
-      </c>
-      <c r="B14" s="4" t="inlineStr">
-        <is>
-          <t>模板为传统瀑布（需求→设计→编码→测试→上线，人工编码+人工评审）；本版按AI Native（Vibe Coding）重排：AI生成+人工审核为主线，质量靠门禁与外部评审兜底</t>
         </is>
       </c>
     </row>
     <row r="15" ht="30" customHeight="1">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>项目初始化</t>
+          <t>总体</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>项目启动即前置（3.1.1~3.1.4、3.2.1）：代码仓库/分支策略/开发环境统一/AI工具账号→AI开发规范→四道门禁CI/CD→前后端工程初始化，先立环境与规矩再生成代码</t>
+          <t>模板为传统瀑布（需求→设计→编码→测试→上线，人工编码+人工评审）；本版按AI Native（Vibe Coding）重排：AI生成+人工审核为主线，质量靠门禁与外部评审兜底</t>
         </is>
       </c>
     </row>
     <row r="16" ht="30" customHeight="1">
       <c r="A16" s="3" t="inlineStr">
         <is>
+          <t>项目初始化</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>项目启动即前置（3.1.1~3.1.4、3.2.1）：代码仓库/分支策略/开发环境统一/AI工具账号→AI开发规范→四道门禁CI/CD→前后端工程初始化，先立环境与规矩再生成代码</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="30" customHeight="1">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
           <t>非功能需求</t>
         </is>
       </c>
-      <c r="B16" s="4" t="inlineStr">
+      <c r="B17" s="4" t="inlineStr">
         <is>
           <t>功能（26项）与非功能统一排程：需求期定义NFR基线（2.3.1：性能/安全/合规/可用性/容量）→设计期定方案（3.2.8）→集成期初验（6.3.2）→测试期专项验证（7.1.1全量+7.2.3性能专项+7.2.6安全可靠性专项）</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="18" customHeight="1">
-      <c r="A17" s="3" t="inlineStr">
+    <row r="18" ht="18" customHeight="1">
+      <c r="A18" s="3" t="inlineStr">
         <is>
           <t>需求</t>
         </is>
       </c>
-      <c r="B17" s="4" t="inlineStr">
+      <c r="B18" s="4" t="inlineStr">
         <is>
           <t>人工访谈澄清优先级后，SRS由AI生成初稿+人工评审基线（🤖见2.2.1）</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="30" customHeight="1">
-      <c r="A18" s="3" t="inlineStr">
-        <is>
-          <t>设计</t>
-        </is>
-      </c>
-      <c r="B18" s="4" t="inlineStr">
-        <is>
-          <t>架构图已预确认→设计阶段仅收尾定稿+ADR留痕；新增「AI工程基线」（3.1.1工具链/规范、3.1.2四道安全门禁CI）替代传统前置详细设计</t>
         </is>
       </c>
     </row>
     <row r="19" ht="30" customHeight="1">
       <c r="A19" s="3" t="inlineStr">
         <is>
+          <t>设计</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>架构图已预确认→设计阶段仅收尾定稿+ADR留痕；新增「AI工程基线」（3.1.1工具链/规范、3.1.2四道安全门禁CI）替代传统前置详细设计</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="30" customHeight="1">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
           <t>开发</t>
         </is>
       </c>
-      <c r="B19" s="4" t="inlineStr">
+      <c r="B20" s="4" t="inlineStr">
         <is>
           <t>Vibe Coding：AI生成代码+人工审核+四道门禁硬卡点合入；每周五下午固定0.5天技术债偿还；外部关键模块评审2次（10/9、11/11）</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="18" customHeight="1">
-      <c r="A20" s="3" t="inlineStr">
-        <is>
-          <t>测试</t>
-        </is>
-      </c>
-      <c r="B20" s="4" t="inlineStr">
-        <is>
-          <t>AI生成测试用例+人工补充边界/越权用例；AI辅助执行与缺陷聚类（轮1、全量、UAT三级）</t>
         </is>
       </c>
     </row>
     <row r="21" ht="18" customHeight="1">
       <c r="A21" s="3" t="inlineStr">
         <is>
+          <t>测试</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>AI生成测试用例+人工补充边界/越权用例；AI辅助执行与缺陷聚类（轮1、全量、UAT三级）</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="18" customHeight="1">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
           <t>文档</t>
         </is>
       </c>
-      <c r="B21" s="4" t="inlineStr">
+      <c r="B22" s="4" t="inlineStr">
         <is>
           <t>AI反生成（代码/演示→手册）+人工润色，随模块滚动产出，不再后置到上线后</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="20" customHeight="1">
-      <c r="A22" s="2" t="inlineStr">
+    <row r="23" ht="20" customHeight="1">
+      <c r="A23" s="2" t="inlineStr">
         <is>
           <t>四、表格说明</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="30" customHeight="1">
-      <c r="A23" s="3" t="inlineStr">
-        <is>
-          <t>新增列</t>
-        </is>
-      </c>
-      <c r="B23" s="4" t="inlineStr">
-        <is>
-          <t>「工作量(人天)」＝实际人力投入（汇总行自动汇总）；「AI参与方式」＝该任务的AI参与程度（AI生成+人工审核 / AI辅助 / 人工主导 / 自动化流水线）</t>
         </is>
       </c>
     </row>
     <row r="24" ht="30" customHeight="1">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>工期(天)</t>
+          <t>新增列</t>
         </is>
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>＝起止日期间的排产工作日数（已扣除周末/中秋/国庆），非自然日跨度；贯穿型任务工期为跨度假定的日历工作跨度，实际投入以工作量列为准</t>
+          <t>「工作量(人天)」＝实际人力投入（汇总行自动汇总）；「AI参与方式」＝该任务的AI参与程度（AI生成+人工审核 / AI辅助 / 人工主导 / 自动化流水线）</t>
         </is>
       </c>
     </row>
     <row r="25" ht="30" customHeight="1">
       <c r="A25" s="3" t="inlineStr">
         <is>
+          <t>工期(天)</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>＝起止日期间的排产工作日数（已扣除周末/中秋/国庆），非自然日跨度；贯穿型任务工期为跨度假定的日历工作跨度，实际投入以工作量列为准</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="30" customHeight="1">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
           <t>里程碑</t>
         </is>
       </c>
-      <c r="B25" s="4" t="inlineStr">
-        <is>
-          <t>任务名称含「◆」且金色底纹＝里程碑（主里程碑M1~M7共7个，另有M5/M6的过程控制点）；M1=9/24（中秋前）、M2=10/9、M3=10/23、M4=11/13、M5=11/27、M6=12/4、M7=12/11</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="18" customHeight="1">
-      <c r="A26" s="3" t="inlineStr">
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t>任务名称含「◆」且金色底纹＝里程碑（主里程碑M1~M7共7个，另有M5/M6的过程控制点）；M1=9/24（中秋前）、M2=10/9、M3=10/23、M4=11/13、M5=12/1、M6=12/9、M7=12/16</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="18" customHeight="1">
+      <c r="A27" s="3" t="inlineStr">
         <is>
           <t>自动化</t>
         </is>
       </c>
-      <c r="B26" s="4" t="inlineStr">
+      <c r="B27" s="4" t="inlineStr">
         <is>
           <t>状态/优先级下拉选择；超期未完成整行自动标红；进度列数据条；一级任务蓝底汇总；「进度汇总」页自动统计</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="30" customHeight="1">
-      <c r="A27" s="3" t="inlineStr">
-        <is>
-          <t>功能覆盖对照</t>
-        </is>
-      </c>
-      <c r="B27" s="4" t="inlineStr">
-        <is>
-          <t>「26项功能覆盖对照」页：源文件Scope-Phase1的26项功能（F01-01~F08-05）与WBS任务逐项对照（主开发/界面协作/走查/全量测试/负责人/计划完成日），功能名与源文件一字不差，可直接用于功能完整性验收</t>
         </is>
       </c>
     </row>
     <row r="28" ht="30" customHeight="1">
       <c r="A28" s="3" t="inlineStr">
         <is>
+          <t>功能覆盖对照</t>
+        </is>
+      </c>
+      <c r="B28" s="4" t="inlineStr">
+        <is>
+          <t>「26项功能覆盖对照」页：源文件Scope-Phase1的26项功能（F01-01~F08-05）与WBS任务逐项对照（主开发/界面协作/走查/全量测试/负责人/计划完成日），功能名与源文件一字不差，可直接用于功能完整性验收</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="30" customHeight="1">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
           <t>其他页签</t>
         </is>
       </c>
-      <c r="B28" s="4" t="inlineStr">
+      <c r="B29" s="4" t="inlineStr">
         <is>
           <t>「里程碑计划」「资源负荷与日历」「WBS词典」「进度汇总」配合使用；如需甘特图可将WBS编号+起止日期导出到Project/飞书项目</t>
         </is>
@@ -948,11 +960,11 @@
     </row>
   </sheetData>
   <mergeCells count="5">
-    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="A14:B14"/>
     <mergeCell ref="A1:B1"/>
-    <mergeCell ref="A8:B8"/>
+    <mergeCell ref="A23:B23"/>
+    <mergeCell ref="A9:B9"/>
     <mergeCell ref="A3:B3"/>
-    <mergeCell ref="A22:B22"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1136,10 +1148,10 @@
         <v>46279</v>
       </c>
       <c r="G4" s="11" t="n">
-        <v>46367</v>
+        <v>46372</v>
       </c>
       <c r="H4" s="8" t="n">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="I4" s="12">
         <f>ROUND(SUMPRODUCT(($C$4:$C$164=3)*(LEFT($A$4:$A$164,LEN(A4))=A4)*$I$4:$I$164),2)</f>
@@ -1315,10 +1327,10 @@
         <v>46286</v>
       </c>
       <c r="G7" s="18" t="n">
-        <v>46366</v>
+        <v>46371</v>
       </c>
       <c r="H7" s="15" t="n">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="I7" s="19">
         <f>ROUND(SUMPRODUCT(($C$4:$C$164=3)*(LEFT($A$4:$A$164,LEN(A7))=A7)*$I$4:$I$164),2)</f>
@@ -1379,10 +1391,10 @@
         <v>46286</v>
       </c>
       <c r="G8" s="18" t="n">
-        <v>46364</v>
+        <v>46366</v>
       </c>
       <c r="H8" s="15" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="I8" s="19" t="n">
         <v>6</v>
@@ -1446,10 +1458,10 @@
         <v>46307</v>
       </c>
       <c r="G9" s="18" t="n">
-        <v>46353</v>
+        <v>46357</v>
       </c>
       <c r="H9" s="15" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="I9" s="19" t="n">
         <v>2</v>
@@ -1481,7 +1493,7 @@
       <c r="P9" s="21" t="n"/>
       <c r="Q9" s="17" t="inlineStr">
         <is>
-          <t>开发执行期（10/12~11/27）每日短会</t>
+          <t>开发执行期（10/12~12/1）每日短会</t>
         </is>
       </c>
     </row>
@@ -1513,10 +1525,10 @@
         <v>46286</v>
       </c>
       <c r="G10" s="18" t="n">
-        <v>46366</v>
+        <v>46371</v>
       </c>
       <c r="H10" s="15" t="n">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="I10" s="19" t="n">
         <v>2.5</v>
@@ -1580,10 +1592,10 @@
         <v>46289</v>
       </c>
       <c r="G11" s="18" t="n">
-        <v>46360</v>
+        <v>46365</v>
       </c>
       <c r="H11" s="15" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="I11" s="19" t="n">
         <v>2.5</v>
@@ -1647,13 +1659,13 @@
         <v>46286</v>
       </c>
       <c r="G12" s="18" t="n">
-        <v>46366</v>
+        <v>46371</v>
       </c>
       <c r="H12" s="15" t="n">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="I12" s="19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J12" s="17" t="inlineStr">
         <is>
@@ -1682,7 +1694,7 @@
       <c r="P12" s="21" t="n"/>
       <c r="Q12" s="17" t="inlineStr">
         <is>
-          <t>每周约0.25天；项目正式文档撰写统一由Mandy执行</t>
+          <t>AI整理纪要+双周集中归档；项目正式文档撰写统一由Mandy执行</t>
         </is>
       </c>
     </row>
@@ -1711,10 +1723,10 @@
         </is>
       </c>
       <c r="F13" s="18" t="n">
-        <v>46367</v>
+        <v>46372</v>
       </c>
       <c r="G13" s="18" t="n">
-        <v>46367</v>
+        <v>46372</v>
       </c>
       <c r="H13" s="15" t="n">
         <v>1</v>
@@ -1767,10 +1779,10 @@
         </is>
       </c>
       <c r="F14" s="26" t="n">
-        <v>46367</v>
+        <v>46372</v>
       </c>
       <c r="G14" s="26" t="n">
-        <v>46367</v>
+        <v>46372</v>
       </c>
       <c r="H14" s="23" t="n">
         <v>1</v>
@@ -1805,7 +1817,7 @@
       <c r="P14" s="29" t="n"/>
       <c r="Q14" s="25" t="inlineStr">
         <is>
-          <t>12/11最后一个PM人天收尾；交付文档由Mandy齐套（8.2.3）</t>
+          <t>12/16最后一个PM人天收尾；交付文档由Mandy齐套（8.2.3）</t>
         </is>
       </c>
     </row>
@@ -2212,7 +2224,7 @@
         <v>3</v>
       </c>
       <c r="I21" s="19" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="J21" s="17" t="inlineStr">
         <is>
@@ -2540,7 +2552,7 @@
         <v>2</v>
       </c>
       <c r="I26" s="19" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="J26" s="17" t="inlineStr">
         <is>
@@ -2667,7 +2679,7 @@
         <v>42</v>
       </c>
       <c r="I28" s="19" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="J28" s="17" t="inlineStr">
         <is>
@@ -3742,7 +3754,7 @@
         <v>2</v>
       </c>
       <c r="I45" s="19" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="J45" s="17" t="inlineStr">
         <is>
@@ -5259,7 +5271,7 @@
         <v>2</v>
       </c>
       <c r="I69" s="19" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="J69" s="17" t="inlineStr">
         <is>
@@ -5322,7 +5334,7 @@
         <v>2</v>
       </c>
       <c r="I70" s="19" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="J70" s="17" t="inlineStr">
         <is>
@@ -5389,7 +5401,7 @@
         <v>2</v>
       </c>
       <c r="I71" s="19" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="J71" s="17" t="inlineStr">
         <is>
@@ -5515,7 +5527,7 @@
         <v>2</v>
       </c>
       <c r="I73" s="19" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="J73" s="17" t="inlineStr">
         <is>
@@ -7153,7 +7165,7 @@
         <v>2</v>
       </c>
       <c r="I99" s="19" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="J99" s="17" t="inlineStr">
         <is>
@@ -7279,7 +7291,7 @@
         <v>1</v>
       </c>
       <c r="I101" s="19" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="J101" s="17" t="inlineStr">
         <is>
@@ -7531,7 +7543,7 @@
         <v>1</v>
       </c>
       <c r="I105" s="19" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="J105" s="17" t="inlineStr">
         <is>
@@ -7720,7 +7732,7 @@
         <v>2</v>
       </c>
       <c r="I108" s="19" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="J108" s="17" t="inlineStr">
         <is>
@@ -8164,10 +8176,10 @@
         <v>46342</v>
       </c>
       <c r="G115" s="11" t="n">
-        <v>46353</v>
+        <v>46357</v>
       </c>
       <c r="H115" s="8" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="I115" s="12">
         <f>ROUND(SUMPRODUCT(($C$4:$C$164=3)*(LEFT($A$4:$A$164,LEN(A115))=A115)*$I$4:$I$164),2)</f>
@@ -8192,7 +8204,7 @@
       <c r="P115" s="14" t="n"/>
       <c r="Q115" s="10" t="inlineStr">
         <is>
-          <t>11/16~11/27；M5=11/27</t>
+          <t>11/16~12/1；M5=12/1</t>
         </is>
       </c>
     </row>
@@ -8224,10 +8236,10 @@
         <v>46342</v>
       </c>
       <c r="G116" s="18" t="n">
-        <v>46353</v>
+        <v>46357</v>
       </c>
       <c r="H116" s="15" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="I116" s="19">
         <f>ROUND(SUMPRODUCT(($C$4:$C$164=3)*(LEFT($A$4:$A$164,LEN(A116))=A116)*$I$4:$I$164),2)</f>
@@ -8347,13 +8359,13 @@
         <v>46344</v>
       </c>
       <c r="G118" s="18" t="n">
-        <v>46345</v>
+        <v>46346</v>
       </c>
       <c r="H118" s="15" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I118" s="19" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J118" s="17" t="inlineStr">
         <is>
@@ -8407,10 +8419,10 @@
         </is>
       </c>
       <c r="F119" s="18" t="n">
-        <v>46346</v>
+        <v>46349</v>
       </c>
       <c r="G119" s="18" t="n">
-        <v>46346</v>
+        <v>46349</v>
       </c>
       <c r="H119" s="15" t="n">
         <v>1</v>
@@ -8470,10 +8482,10 @@
         </is>
       </c>
       <c r="F120" s="18" t="n">
-        <v>46349</v>
+        <v>46350</v>
       </c>
       <c r="G120" s="18" t="n">
-        <v>46350</v>
+        <v>46351</v>
       </c>
       <c r="H120" s="15" t="n">
         <v>2</v>
@@ -8533,10 +8545,10 @@
         </is>
       </c>
       <c r="F121" s="18" t="n">
-        <v>46351</v>
+        <v>46352</v>
       </c>
       <c r="G121" s="18" t="n">
-        <v>46352</v>
+        <v>46353</v>
       </c>
       <c r="H121" s="15" t="n">
         <v>2</v>
@@ -8596,10 +8608,10 @@
         </is>
       </c>
       <c r="F122" s="26" t="n">
-        <v>46353</v>
+        <v>46357</v>
       </c>
       <c r="G122" s="26" t="n">
-        <v>46353</v>
+        <v>46357</v>
       </c>
       <c r="H122" s="23" t="n">
         <v>1</v>
@@ -8634,7 +8646,7 @@
       <c r="P122" s="29" t="n"/>
       <c r="Q122" s="25" t="inlineStr">
         <is>
-          <t>★M5 11/27（与6.2.6同日达成）</t>
+          <t>★M5 12/1（与6.2.6同日达成）</t>
         </is>
       </c>
     </row>
@@ -8666,10 +8678,10 @@
         <v>46342</v>
       </c>
       <c r="G123" s="18" t="n">
-        <v>46353</v>
+        <v>46357</v>
       </c>
       <c r="H123" s="15" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="I123" s="19">
         <f>ROUND(SUMPRODUCT(($C$4:$C$164=3)*(LEFT($A$4:$A$164,LEN(A123))=A123)*$I$4:$I$164),2)</f>
@@ -8722,13 +8734,13 @@
         <v>46342</v>
       </c>
       <c r="G124" s="18" t="n">
-        <v>46344</v>
+        <v>46345</v>
       </c>
       <c r="H124" s="15" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I124" s="19" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="J124" s="17" t="inlineStr">
         <is>
@@ -8786,16 +8798,16 @@
         </is>
       </c>
       <c r="F125" s="18" t="n">
-        <v>46345</v>
+        <v>46346</v>
       </c>
       <c r="G125" s="18" t="n">
-        <v>46346</v>
+        <v>46350</v>
       </c>
       <c r="H125" s="15" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I125" s="19" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="J125" s="17" t="inlineStr">
         <is>
@@ -8849,10 +8861,10 @@
         </is>
       </c>
       <c r="F126" s="18" t="n">
-        <v>46349</v>
+        <v>46351</v>
       </c>
       <c r="G126" s="18" t="n">
-        <v>46349</v>
+        <v>46351</v>
       </c>
       <c r="H126" s="15" t="n">
         <v>1</v>
@@ -8916,10 +8928,10 @@
         </is>
       </c>
       <c r="F127" s="18" t="n">
-        <v>46350</v>
+        <v>46352</v>
       </c>
       <c r="G127" s="18" t="n">
-        <v>46351</v>
+        <v>46353</v>
       </c>
       <c r="H127" s="15" t="n">
         <v>2</v>
@@ -8979,10 +8991,10 @@
         </is>
       </c>
       <c r="F128" s="18" t="n">
-        <v>46352</v>
+        <v>46356</v>
       </c>
       <c r="G128" s="18" t="n">
-        <v>46352</v>
+        <v>46356</v>
       </c>
       <c r="H128" s="15" t="n">
         <v>1</v>
@@ -9042,10 +9054,10 @@
         </is>
       </c>
       <c r="F129" s="26" t="n">
-        <v>46353</v>
+        <v>46357</v>
       </c>
       <c r="G129" s="26" t="n">
-        <v>46353</v>
+        <v>46357</v>
       </c>
       <c r="H129" s="23" t="n">
         <v>1</v>
@@ -9080,7 +9092,7 @@
       <c r="P129" s="29" t="n"/>
       <c r="Q129" s="25" t="inlineStr">
         <is>
-          <t>★M5 11/27</t>
+          <t>★M5 12/1</t>
         </is>
       </c>
     </row>
@@ -9488,13 +9500,13 @@
         </is>
       </c>
       <c r="F136" s="11" t="n">
-        <v>46356</v>
+        <v>46358</v>
       </c>
       <c r="G136" s="11" t="n">
-        <v>46360</v>
+        <v>46365</v>
       </c>
       <c r="H136" s="8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I136" s="12">
         <f>ROUND(SUMPRODUCT(($C$4:$C$164=3)*(LEFT($A$4:$A$164,LEN(A136))=A136)*$I$4:$I$164),2)</f>
@@ -9519,7 +9531,7 @@
       <c r="P136" s="14" t="n"/>
       <c r="Q136" s="10" t="inlineStr">
         <is>
-          <t>11/30~12/4；M6=12/4</t>
+          <t>12/2~12/9；M6=12/9</t>
         </is>
       </c>
     </row>
@@ -9548,10 +9560,10 @@
         </is>
       </c>
       <c r="F137" s="18" t="n">
-        <v>46356</v>
+        <v>46358</v>
       </c>
       <c r="G137" s="18" t="n">
-        <v>46360</v>
+        <v>46364</v>
       </c>
       <c r="H137" s="15" t="n">
         <v>5</v>
@@ -9604,10 +9616,10 @@
         </is>
       </c>
       <c r="F138" s="18" t="n">
-        <v>46356</v>
+        <v>46358</v>
       </c>
       <c r="G138" s="18" t="n">
-        <v>46357</v>
+        <v>46359</v>
       </c>
       <c r="H138" s="15" t="n">
         <v>2</v>
@@ -9671,10 +9683,10 @@
         </is>
       </c>
       <c r="F139" s="18" t="n">
-        <v>46358</v>
+        <v>46360</v>
       </c>
       <c r="G139" s="18" t="n">
-        <v>46358</v>
+        <v>46360</v>
       </c>
       <c r="H139" s="15" t="n">
         <v>1</v>
@@ -9734,10 +9746,10 @@
         </is>
       </c>
       <c r="F140" s="26" t="n">
-        <v>46359</v>
+        <v>46363</v>
       </c>
       <c r="G140" s="26" t="n">
-        <v>46359</v>
+        <v>46363</v>
       </c>
       <c r="H140" s="23" t="n">
         <v>1</v>
@@ -9772,7 +9784,7 @@
       <c r="P140" s="29" t="n"/>
       <c r="Q140" s="25" t="inlineStr">
         <is>
-          <t>★M6·UAT签字 12/3；业务方到场</t>
+          <t>★M6·UAT签字 12/7；业务方到场</t>
         </is>
       </c>
     </row>
@@ -9801,10 +9813,10 @@
         </is>
       </c>
       <c r="F141" s="18" t="n">
-        <v>46360</v>
+        <v>46364</v>
       </c>
       <c r="G141" s="18" t="n">
-        <v>46360</v>
+        <v>46364</v>
       </c>
       <c r="H141" s="15" t="n">
         <v>1</v>
@@ -9839,7 +9851,7 @@
       <c r="P141" s="21" t="n"/>
       <c r="Q141" s="17" t="inlineStr">
         <is>
-          <t>★M6·报告齐套 12/4；AI辅助成文</t>
+          <t>★M6·报告齐套 12/8；AI辅助成文</t>
         </is>
       </c>
     </row>
@@ -9868,13 +9880,13 @@
         </is>
       </c>
       <c r="F142" s="18" t="n">
-        <v>46356</v>
+        <v>46358</v>
       </c>
       <c r="G142" s="18" t="n">
-        <v>46360</v>
+        <v>46365</v>
       </c>
       <c r="H142" s="15" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I142" s="19">
         <f>ROUND(SUMPRODUCT(($C$4:$C$164=3)*(LEFT($A$4:$A$164,LEN(A142))=A142)*$I$4:$I$164),2)</f>
@@ -9924,10 +9936,10 @@
         </is>
       </c>
       <c r="F143" s="18" t="n">
-        <v>46356</v>
+        <v>46358</v>
       </c>
       <c r="G143" s="18" t="n">
-        <v>46356</v>
+        <v>46358</v>
       </c>
       <c r="H143" s="15" t="n">
         <v>1</v>
@@ -9987,16 +9999,16 @@
         </is>
       </c>
       <c r="F144" s="18" t="n">
-        <v>46357</v>
+        <v>46359</v>
       </c>
       <c r="G144" s="18" t="n">
-        <v>46358</v>
+        <v>46360</v>
       </c>
       <c r="H144" s="15" t="n">
         <v>2</v>
       </c>
       <c r="I144" s="19" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="J144" s="17" t="inlineStr">
         <is>
@@ -10050,16 +10062,16 @@
         </is>
       </c>
       <c r="F145" s="18" t="n">
-        <v>46359</v>
+        <v>46363</v>
       </c>
       <c r="G145" s="18" t="n">
-        <v>46359</v>
+        <v>46364</v>
       </c>
       <c r="H145" s="15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I145" s="19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J145" s="17" t="inlineStr">
         <is>
@@ -10117,10 +10129,10 @@
         </is>
       </c>
       <c r="F146" s="18" t="n">
-        <v>46356</v>
+        <v>46358</v>
       </c>
       <c r="G146" s="18" t="n">
-        <v>46356</v>
+        <v>46358</v>
       </c>
       <c r="H146" s="15" t="n">
         <v>1</v>
@@ -10180,16 +10192,16 @@
         </is>
       </c>
       <c r="F147" s="18" t="n">
-        <v>46357</v>
+        <v>46359</v>
       </c>
       <c r="G147" s="18" t="n">
-        <v>46358</v>
+        <v>46360</v>
       </c>
       <c r="H147" s="15" t="n">
         <v>2</v>
       </c>
       <c r="I147" s="19" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="J147" s="17" t="inlineStr">
         <is>
@@ -10243,16 +10255,16 @@
         </is>
       </c>
       <c r="F148" s="18" t="n">
-        <v>46359</v>
+        <v>46363</v>
       </c>
       <c r="G148" s="18" t="n">
-        <v>46359</v>
+        <v>46364</v>
       </c>
       <c r="H148" s="15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I148" s="19" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="J148" s="17" t="inlineStr">
         <is>
@@ -10306,10 +10318,10 @@
         </is>
       </c>
       <c r="F149" s="26" t="n">
-        <v>46360</v>
+        <v>46365</v>
       </c>
       <c r="G149" s="26" t="n">
-        <v>46360</v>
+        <v>46365</v>
       </c>
       <c r="H149" s="23" t="n">
         <v>1</v>
@@ -10344,7 +10356,7 @@
       <c r="P149" s="29" t="n"/>
       <c r="Q149" s="25" t="inlineStr">
         <is>
-          <t>12/4；PM+业务方参加</t>
+          <t>12/9；PM+业务方参加</t>
         </is>
       </c>
     </row>
@@ -10373,10 +10385,10 @@
         </is>
       </c>
       <c r="F150" s="18" t="n">
-        <v>46360</v>
+        <v>46365</v>
       </c>
       <c r="G150" s="18" t="n">
-        <v>46360</v>
+        <v>46365</v>
       </c>
       <c r="H150" s="15" t="n">
         <v>1</v>
@@ -10440,10 +10452,10 @@
         </is>
       </c>
       <c r="F151" s="11" t="n">
-        <v>46363</v>
+        <v>46366</v>
       </c>
       <c r="G151" s="11" t="n">
-        <v>46367</v>
+        <v>46372</v>
       </c>
       <c r="H151" s="8" t="n">
         <v>5</v>
@@ -10471,7 +10483,7 @@
       <c r="P151" s="14" t="n"/>
       <c r="Q151" s="10" t="inlineStr">
         <is>
-          <t>12/7~12/11；M7=12/11</t>
+          <t>12/10~12/16；M7=12/16</t>
         </is>
       </c>
     </row>
@@ -10500,10 +10512,10 @@
         </is>
       </c>
       <c r="F152" s="18" t="n">
-        <v>46363</v>
+        <v>46366</v>
       </c>
       <c r="G152" s="18" t="n">
-        <v>46366</v>
+        <v>46371</v>
       </c>
       <c r="H152" s="15" t="n">
         <v>4</v>
@@ -10560,10 +10572,10 @@
         </is>
       </c>
       <c r="F153" s="18" t="n">
-        <v>46363</v>
+        <v>46366</v>
       </c>
       <c r="G153" s="18" t="n">
-        <v>46363</v>
+        <v>46366</v>
       </c>
       <c r="H153" s="15" t="n">
         <v>1</v>
@@ -10627,10 +10639,10 @@
         </is>
       </c>
       <c r="F154" s="18" t="n">
-        <v>46363</v>
+        <v>46366</v>
       </c>
       <c r="G154" s="18" t="n">
-        <v>46365</v>
+        <v>46370</v>
       </c>
       <c r="H154" s="15" t="n">
         <v>3</v>
@@ -10665,7 +10677,7 @@
       <c r="P154" s="21" t="n"/>
       <c r="Q154" s="17" t="inlineStr">
         <is>
-          <t>12/7~12/9分批执行</t>
+          <t>12/10~12/14分批执行（跨周末）</t>
         </is>
       </c>
     </row>
@@ -10694,10 +10706,10 @@
         </is>
       </c>
       <c r="F155" s="18" t="n">
-        <v>46366</v>
+        <v>46371</v>
       </c>
       <c r="G155" s="18" t="n">
-        <v>46366</v>
+        <v>46371</v>
       </c>
       <c r="H155" s="15" t="n">
         <v>1</v>
@@ -10761,10 +10773,10 @@
         </is>
       </c>
       <c r="F156" s="18" t="n">
-        <v>46364</v>
+        <v>46367</v>
       </c>
       <c r="G156" s="18" t="n">
-        <v>46364</v>
+        <v>46367</v>
       </c>
       <c r="H156" s="15" t="n">
         <v>1</v>
@@ -10824,10 +10836,10 @@
         </is>
       </c>
       <c r="F157" s="18" t="n">
-        <v>46363</v>
+        <v>46366</v>
       </c>
       <c r="G157" s="18" t="n">
-        <v>46367</v>
+        <v>46372</v>
       </c>
       <c r="H157" s="15" t="n">
         <v>5</v>
@@ -10880,10 +10892,10 @@
         </is>
       </c>
       <c r="F158" s="18" t="n">
-        <v>46363</v>
+        <v>46366</v>
       </c>
       <c r="G158" s="18" t="n">
-        <v>46363</v>
+        <v>46366</v>
       </c>
       <c r="H158" s="15" t="n">
         <v>1</v>
@@ -10943,10 +10955,10 @@
         </is>
       </c>
       <c r="F159" s="18" t="n">
-        <v>46364</v>
+        <v>46367</v>
       </c>
       <c r="G159" s="18" t="n">
-        <v>46364</v>
+        <v>46367</v>
       </c>
       <c r="H159" s="15" t="n">
         <v>1</v>
@@ -11006,10 +11018,10 @@
         </is>
       </c>
       <c r="F160" s="18" t="n">
-        <v>46365</v>
+        <v>46370</v>
       </c>
       <c r="G160" s="18" t="n">
-        <v>46366</v>
+        <v>46371</v>
       </c>
       <c r="H160" s="15" t="n">
         <v>2</v>
@@ -11073,10 +11085,10 @@
         </is>
       </c>
       <c r="F161" s="18" t="n">
-        <v>46367</v>
+        <v>46372</v>
       </c>
       <c r="G161" s="18" t="n">
-        <v>46367</v>
+        <v>46372</v>
       </c>
       <c r="H161" s="15" t="n">
         <v>1</v>
@@ -11136,10 +11148,10 @@
         </is>
       </c>
       <c r="F162" s="18" t="n">
-        <v>46365</v>
+        <v>46370</v>
       </c>
       <c r="G162" s="18" t="n">
-        <v>46367</v>
+        <v>46372</v>
       </c>
       <c r="H162" s="15" t="n">
         <v>3</v>
@@ -11174,7 +11186,7 @@
       <c r="P162" s="21" t="n"/>
       <c r="Q162" s="17" t="inlineStr">
         <is>
-          <t>12/9~12/11值守窗口</t>
+          <t>12/14~12/16值守窗口</t>
         </is>
       </c>
     </row>
@@ -11203,10 +11215,10 @@
         </is>
       </c>
       <c r="F163" s="18" t="n">
-        <v>46367</v>
+        <v>46372</v>
       </c>
       <c r="G163" s="18" t="n">
-        <v>46367</v>
+        <v>46372</v>
       </c>
       <c r="H163" s="15" t="n">
         <v>1</v>
@@ -11266,10 +11278,10 @@
         </is>
       </c>
       <c r="F164" s="26" t="n">
-        <v>46367</v>
+        <v>46372</v>
       </c>
       <c r="G164" s="26" t="n">
-        <v>46367</v>
+        <v>46372</v>
       </c>
       <c r="H164" s="23" t="n">
         <v>1</v>
@@ -11304,7 +11316,7 @@
       <c r="P164" s="29" t="n"/>
       <c r="Q164" s="25" t="inlineStr">
         <is>
-          <t>★M7 12/11项目结束；工作量计入1.3.1</t>
+          <t>★M7 12/16项目结束；工作量计入1.3.1</t>
         </is>
       </c>
     </row>
@@ -13129,7 +13141,7 @@
       </c>
       <c r="B7" s="23" t="inlineStr">
         <is>
-          <t>2026/11/27（周五）</t>
+          <t>2026/12/01（周二）</t>
         </is>
       </c>
       <c r="C7" s="23" t="inlineStr">
@@ -13157,7 +13169,7 @@
       </c>
       <c r="B8" s="23" t="inlineStr">
         <is>
-          <t>2026/12/04（周五）</t>
+          <t>2026/12/09（周三）</t>
         </is>
       </c>
       <c r="C8" s="23" t="inlineStr">
@@ -13185,7 +13197,7 @@
       </c>
       <c r="B9" s="23" t="inlineStr">
         <is>
-          <t>2026/12/11（周五）</t>
+          <t>2026/12/16（周三）</t>
         </is>
       </c>
       <c r="C9" s="23" t="inlineStr">
@@ -13326,7 +13338,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>15人天贯穿式分布：启动1+周例会6+每日同步2+进度风险跟踪2.5+里程碑评审2.5+收尾1（12/11）</t>
+          <t>15人天贯穿式分布：启动1+周例会6+每日同步2+进度风险跟踪2.5+里程碑评审2.5+收尾1（12/16）</t>
         </is>
       </c>
     </row>
@@ -13337,17 +13349,17 @@
         </is>
       </c>
       <c r="B4" s="19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C4" s="19" t="n">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="D4" s="19" t="n"/>
       <c r="E4" s="19" t="n">
-        <v>8.5</v>
+        <v>6.5</v>
       </c>
       <c r="F4" s="19" t="n">
-        <v>14.5</v>
+        <v>12.5</v>
       </c>
       <c r="G4" s="19" t="n">
         <v>8.5</v>
@@ -13359,11 +13371,11 @@
         <v>3.5</v>
       </c>
       <c r="J4" s="37" t="n">
-        <v>56.5</v>
+        <v>50</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>负荷率 96%（59个工作日）</t>
+          <t>负荷率 81%（62个工作日）</t>
         </is>
       </c>
     </row>
@@ -13376,7 +13388,7 @@
       <c r="B5" s="19" t="n"/>
       <c r="C5" s="19" t="n"/>
       <c r="D5" s="19" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="E5" s="19" t="n">
         <v>10</v>
@@ -13385,20 +13397,20 @@
         <v>14.5</v>
       </c>
       <c r="G5" s="19" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H5" s="19" t="n">
-        <v>4.5</v>
+        <v>6</v>
       </c>
       <c r="I5" s="19" t="n">
         <v>5</v>
       </c>
       <c r="J5" s="37" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>负荷率 97%（59个工作日）</t>
+          <t>负荷率 97%（62个工作日）</t>
         </is>
       </c>
     </row>
@@ -13420,20 +13432,20 @@
         <v>14.5</v>
       </c>
       <c r="G6" s="19" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H6" s="19" t="n">
-        <v>4.5</v>
+        <v>5.5</v>
       </c>
       <c r="I6" s="19" t="n">
         <v>5</v>
       </c>
       <c r="J6" s="37" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>负荷率 98%（59个工作日）</t>
+          <t>负荷率 97%（62个工作日）</t>
         </is>
       </c>
     </row>
@@ -13444,11 +13456,11 @@
         </is>
       </c>
       <c r="J7" s="39" t="n">
-        <v>186.5</v>
+        <v>185</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>原角色表估算185人天（含交付15）；本版186.5人天，新增项目初始化/非功能专项/会议纪要显式化</t>
+          <t>与原角色表估算185人天一致（Mandy 50+Wade 60+DevB 60+PM 15）；本版185.0人天</t>
         </is>
       </c>
     </row>
@@ -13467,7 +13479,7 @@
       </c>
       <c r="B10" s="40" t="inlineStr">
         <is>
-          <t>2026/9/14（周一）→ 2026/12/11（周五）：89个自然日，59个工作日</t>
+          <t>2026/9/14（周一）→ 2026/12/16（周三）：94个自然日，62个工作日（Wade/DevB按60人天铺满，交付顺延3个工作日）</t>
         </is>
       </c>
     </row>
@@ -13534,7 +13546,7 @@
       </c>
       <c r="B16" s="40" t="inlineStr">
         <is>
-          <t>11/25确认（6.3.4），12/3 UAT执行；责任人Mandy</t>
+          <t>11/25确认（6.3.4），12/7 UAT执行（7.1.3）；责任人Mandy</t>
         </is>
       </c>
     </row>
@@ -13546,7 +13558,7 @@
       </c>
       <c r="B17" s="40" t="inlineStr">
         <is>
-          <t>12/4前完成审批，12/7生产部署（8.1.1）；责任人Mark</t>
+          <t>12/9前完成审批，12/10生产部署（8.1.1）；责任人Mark</t>
         </is>
       </c>
     </row>

--- a/RIMS项目WBS工作分解_AI Native版.xlsx
+++ b/RIMS项目WBS工作分解_AI Native版.xlsx
@@ -654,6 +654,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3" ht="20" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -1154,7 +1155,7 @@
         <v>62</v>
       </c>
       <c r="I4" s="12">
-        <f>ROUND(SUMPRODUCT(($C$4:$C$164=3)*(LEFT($A$4:$A$164,LEN(A4))=A4)*$I$4:$I$164),2)</f>
+        <f>ROUND(SUMPRODUCT(($C$5:$C$14=3)*(LEFT($A$5:$A$14,LEN(A4))=A4)*$I$5:$I$14),2)</f>
         <v/>
       </c>
       <c r="J4" s="10" t="inlineStr"/>
@@ -1214,7 +1215,7 @@
         <v>1</v>
       </c>
       <c r="I5" s="19">
-        <f>ROUND(SUMPRODUCT(($C$4:$C$164=3)*(LEFT($A$4:$A$164,LEN(A5))=A5)*$I$4:$I$164),2)</f>
+        <f>ROUND(SUMPRODUCT(($C$6:$C$6=3)*(LEFT($A$6:$A$6,LEN(A5))=A5)*$I$6:$I$6),2)</f>
         <v/>
       </c>
       <c r="J5" s="17" t="inlineStr"/>
@@ -1333,7 +1334,7 @@
         <v>56</v>
       </c>
       <c r="I7" s="19">
-        <f>ROUND(SUMPRODUCT(($C$4:$C$164=3)*(LEFT($A$4:$A$164,LEN(A7))=A7)*$I$4:$I$164),2)</f>
+        <f>ROUND(SUMPRODUCT(($C$8:$C$12=3)*(LEFT($A$8:$A$12,LEN(A7))=A7)*$I$8:$I$12),2)</f>
         <v/>
       </c>
       <c r="J7" s="17" t="inlineStr"/>
@@ -1732,7 +1733,7 @@
         <v>1</v>
       </c>
       <c r="I13" s="19">
-        <f>ROUND(SUMPRODUCT(($C$4:$C$164=3)*(LEFT($A$4:$A$164,LEN(A13))=A13)*$I$4:$I$164),2)</f>
+        <f>ROUND(SUMPRODUCT(($C$14:$C$14=3)*(LEFT($A$14:$A$14,LEN(A13))=A13)*$I$14:$I$14),2)</f>
         <v/>
       </c>
       <c r="J13" s="17" t="inlineStr"/>
@@ -1855,7 +1856,7 @@
         <v>12</v>
       </c>
       <c r="I15" s="12">
-        <f>ROUND(SUMPRODUCT(($C$4:$C$164=3)*(LEFT($A$4:$A$164,LEN(A15))=A15)*$I$4:$I$164),2)</f>
+        <f>ROUND(SUMPRODUCT(($C$16:$C$28=3)*(LEFT($A$16:$A$28,LEN(A15))=A15)*$I$16:$I$28),2)</f>
         <v/>
       </c>
       <c r="J15" s="10" t="inlineStr"/>
@@ -1915,7 +1916,7 @@
         <v>5</v>
       </c>
       <c r="I16" s="19">
-        <f>ROUND(SUMPRODUCT(($C$4:$C$164=3)*(LEFT($A$4:$A$164,LEN(A16))=A16)*$I$4:$I$164),2)</f>
+        <f>ROUND(SUMPRODUCT(($C$17:$C$19=3)*(LEFT($A$17:$A$19,LEN(A16))=A16)*$I$17:$I$19),2)</f>
         <v/>
       </c>
       <c r="J16" s="17" t="inlineStr"/>
@@ -2168,7 +2169,7 @@
         <v>4</v>
       </c>
       <c r="I20" s="19">
-        <f>ROUND(SUMPRODUCT(($C$4:$C$164=3)*(LEFT($A$4:$A$164,LEN(A20))=A20)*$I$4:$I$164),2)</f>
+        <f>ROUND(SUMPRODUCT(($C$21:$C$22=3)*(LEFT($A$21:$A$22,LEN(A20))=A20)*$I$21:$I$22),2)</f>
         <v/>
       </c>
       <c r="J20" s="17" t="inlineStr"/>
@@ -2358,7 +2359,7 @@
         <v>4</v>
       </c>
       <c r="I23" s="19">
-        <f>ROUND(SUMPRODUCT(($C$4:$C$164=3)*(LEFT($A$4:$A$164,LEN(A23))=A23)*$I$4:$I$164),2)</f>
+        <f>ROUND(SUMPRODUCT(($C$24:$C$26=3)*(LEFT($A$24:$A$26,LEN(A23))=A23)*$I$24:$I$26),2)</f>
         <v/>
       </c>
       <c r="J23" s="17" t="inlineStr"/>
@@ -2619,7 +2620,7 @@
         <v>42</v>
       </c>
       <c r="I27" s="19">
-        <f>ROUND(SUMPRODUCT(($C$4:$C$164=3)*(LEFT($A$4:$A$164,LEN(A27))=A27)*$I$4:$I$164),2)</f>
+        <f>ROUND(SUMPRODUCT(($C$28:$C$28=3)*(LEFT($A$28:$A$28,LEN(A27))=A27)*$I$28:$I$28),2)</f>
         <v/>
       </c>
       <c r="J27" s="17" t="inlineStr"/>
@@ -2746,7 +2747,7 @@
         <v>14</v>
       </c>
       <c r="I29" s="12">
-        <f>ROUND(SUMPRODUCT(($C$4:$C$164=3)*(LEFT($A$4:$A$164,LEN(A29))=A29)*$I$4:$I$164),2)</f>
+        <f>ROUND(SUMPRODUCT(($C$30:$C$50=3)*(LEFT($A$30:$A$50,LEN(A29))=A29)*$I$30:$I$50),2)</f>
         <v/>
       </c>
       <c r="J29" s="10" t="inlineStr"/>
@@ -2806,7 +2807,7 @@
         <v>5</v>
       </c>
       <c r="I30" s="19">
-        <f>ROUND(SUMPRODUCT(($C$4:$C$164=3)*(LEFT($A$4:$A$164,LEN(A30))=A30)*$I$4:$I$164),2)</f>
+        <f>ROUND(SUMPRODUCT(($C$31:$C$34=3)*(LEFT($A$31:$A$34,LEN(A30))=A30)*$I$31:$I$34),2)</f>
         <v/>
       </c>
       <c r="J30" s="17" t="inlineStr"/>
@@ -3130,7 +3131,7 @@
         <v>14</v>
       </c>
       <c r="I35" s="19">
-        <f>ROUND(SUMPRODUCT(($C$4:$C$164=3)*(LEFT($A$4:$A$164,LEN(A35))=A35)*$I$4:$I$164),2)</f>
+        <f>ROUND(SUMPRODUCT(($C$36:$C$43=3)*(LEFT($A$36:$A$43,LEN(A35))=A35)*$I$36:$I$43),2)</f>
         <v/>
       </c>
       <c r="J35" s="17" t="inlineStr"/>
@@ -3698,7 +3699,7 @@
         <v>9</v>
       </c>
       <c r="I44" s="19">
-        <f>ROUND(SUMPRODUCT(($C$4:$C$164=3)*(LEFT($A$4:$A$164,LEN(A44))=A44)*$I$4:$I$164),2)</f>
+        <f>ROUND(SUMPRODUCT(($C$45:$C$50=3)*(LEFT($A$45:$A$50,LEN(A44))=A44)*$I$45:$I$50),2)</f>
         <v/>
       </c>
       <c r="J44" s="17" t="inlineStr"/>
@@ -4152,7 +4153,7 @@
         <v>10</v>
       </c>
       <c r="I51" s="12">
-        <f>ROUND(SUMPRODUCT(($C$4:$C$164=3)*(LEFT($A$4:$A$164,LEN(A51))=A51)*$I$4:$I$164),2)</f>
+        <f>ROUND(SUMPRODUCT(($C$52:$C$74=3)*(LEFT($A$52:$A$74,LEN(A51))=A51)*$I$52:$I$74),2)</f>
         <v/>
       </c>
       <c r="J51" s="10" t="inlineStr"/>
@@ -4212,7 +4213,7 @@
         <v>6</v>
       </c>
       <c r="I52" s="19">
-        <f>ROUND(SUMPRODUCT(($C$4:$C$164=3)*(LEFT($A$4:$A$164,LEN(A52))=A52)*$I$4:$I$164),2)</f>
+        <f>ROUND(SUMPRODUCT(($C$53:$C$55=3)*(LEFT($A$53:$A$55,LEN(A52))=A52)*$I$53:$I$55),2)</f>
         <v/>
       </c>
       <c r="J52" s="17" t="inlineStr"/>
@@ -4469,7 +4470,7 @@
         <v>10</v>
       </c>
       <c r="I56" s="19">
-        <f>ROUND(SUMPRODUCT(($C$4:$C$164=3)*(LEFT($A$4:$A$164,LEN(A56))=A56)*$I$4:$I$164),2)</f>
+        <f>ROUND(SUMPRODUCT(($C$57:$C$63=3)*(LEFT($A$57:$A$63,LEN(A56))=A56)*$I$57:$I$63),2)</f>
         <v/>
       </c>
       <c r="J56" s="17" t="inlineStr"/>
@@ -4966,7 +4967,7 @@
         <v>4</v>
       </c>
       <c r="I64" s="19">
-        <f>ROUND(SUMPRODUCT(($C$4:$C$164=3)*(LEFT($A$4:$A$164,LEN(A64))=A64)*$I$4:$I$164),2)</f>
+        <f>ROUND(SUMPRODUCT(($C$65:$C$67=3)*(LEFT($A$65:$A$67,LEN(A64))=A64)*$I$65:$I$67),2)</f>
         <v/>
       </c>
       <c r="J64" s="17" t="inlineStr"/>
@@ -5215,7 +5216,7 @@
         <v>10</v>
       </c>
       <c r="I68" s="19">
-        <f>ROUND(SUMPRODUCT(($C$4:$C$164=3)*(LEFT($A$4:$A$164,LEN(A68))=A68)*$I$4:$I$164),2)</f>
+        <f>ROUND(SUMPRODUCT(($C$69:$C$74=3)*(LEFT($A$69:$A$74,LEN(A68))=A68)*$I$69:$I$74),2)</f>
         <v/>
       </c>
       <c r="J68" s="17" t="inlineStr"/>
@@ -5657,7 +5658,7 @@
         <v>15</v>
       </c>
       <c r="I75" s="12">
-        <f>ROUND(SUMPRODUCT(($C$4:$C$164=3)*(LEFT($A$4:$A$164,LEN(A75))=A75)*$I$4:$I$164),2)</f>
+        <f>ROUND(SUMPRODUCT(($C$76:$C$114=3)*(LEFT($A$76:$A$114,LEN(A75))=A75)*$I$76:$I$114),2)</f>
         <v/>
       </c>
       <c r="J75" s="10" t="inlineStr"/>
@@ -5717,7 +5718,7 @@
         <v>15</v>
       </c>
       <c r="I76" s="19">
-        <f>ROUND(SUMPRODUCT(($C$4:$C$164=3)*(LEFT($A$4:$A$164,LEN(A76))=A76)*$I$4:$I$164),2)</f>
+        <f>ROUND(SUMPRODUCT(($C$77:$C$85=3)*(LEFT($A$77:$A$85,LEN(A76))=A76)*$I$77:$I$85),2)</f>
         <v/>
       </c>
       <c r="J76" s="17" t="inlineStr"/>
@@ -6348,7 +6349,7 @@
         <v>15</v>
       </c>
       <c r="I86" s="19">
-        <f>ROUND(SUMPRODUCT(($C$4:$C$164=3)*(LEFT($A$4:$A$164,LEN(A86))=A86)*$I$4:$I$164),2)</f>
+        <f>ROUND(SUMPRODUCT(($C$87:$C$97=3)*(LEFT($A$87:$A$97,LEN(A86))=A86)*$I$87:$I$97),2)</f>
         <v/>
       </c>
       <c r="J86" s="17" t="inlineStr"/>
@@ -7105,7 +7106,7 @@
         <v>15</v>
       </c>
       <c r="I98" s="19">
-        <f>ROUND(SUMPRODUCT(($C$4:$C$164=3)*(LEFT($A$4:$A$164,LEN(A98))=A98)*$I$4:$I$164),2)</f>
+        <f>ROUND(SUMPRODUCT(($C$99:$C$111=3)*(LEFT($A$99:$A$111,LEN(A98))=A98)*$I$99:$I$111),2)</f>
         <v/>
       </c>
       <c r="J98" s="17" t="inlineStr"/>
@@ -7988,7 +7989,7 @@
         <v>15</v>
       </c>
       <c r="I112" s="19">
-        <f>ROUND(SUMPRODUCT(($C$4:$C$164=3)*(LEFT($A$4:$A$164,LEN(A112))=A112)*$I$4:$I$164),2)</f>
+        <f>ROUND(SUMPRODUCT(($C$113:$C$114=3)*(LEFT($A$113:$A$114,LEN(A112))=A112)*$I$113:$I$114),2)</f>
         <v/>
       </c>
       <c r="J112" s="17" t="inlineStr"/>
@@ -8182,7 +8183,7 @@
         <v>12</v>
       </c>
       <c r="I115" s="12">
-        <f>ROUND(SUMPRODUCT(($C$4:$C$164=3)*(LEFT($A$4:$A$164,LEN(A115))=A115)*$I$4:$I$164),2)</f>
+        <f>ROUND(SUMPRODUCT(($C$116:$C$135=3)*(LEFT($A$116:$A$135,LEN(A115))=A115)*$I$116:$I$135),2)</f>
         <v/>
       </c>
       <c r="J115" s="10" t="inlineStr"/>
@@ -8242,7 +8243,7 @@
         <v>12</v>
       </c>
       <c r="I116" s="19">
-        <f>ROUND(SUMPRODUCT(($C$4:$C$164=3)*(LEFT($A$4:$A$164,LEN(A116))=A116)*$I$4:$I$164),2)</f>
+        <f>ROUND(SUMPRODUCT(($C$117:$C$122=3)*(LEFT($A$117:$A$122,LEN(A116))=A116)*$I$117:$I$122),2)</f>
         <v/>
       </c>
       <c r="J116" s="17" t="inlineStr"/>
@@ -8684,7 +8685,7 @@
         <v>12</v>
       </c>
       <c r="I123" s="19">
-        <f>ROUND(SUMPRODUCT(($C$4:$C$164=3)*(LEFT($A$4:$A$164,LEN(A123))=A123)*$I$4:$I$164),2)</f>
+        <f>ROUND(SUMPRODUCT(($C$124:$C$129=3)*(LEFT($A$124:$A$129,LEN(A123))=A123)*$I$124:$I$129),2)</f>
         <v/>
       </c>
       <c r="J123" s="17" t="inlineStr"/>
@@ -9130,7 +9131,7 @@
         <v>10</v>
       </c>
       <c r="I130" s="19">
-        <f>ROUND(SUMPRODUCT(($C$4:$C$164=3)*(LEFT($A$4:$A$164,LEN(A130))=A130)*$I$4:$I$164),2)</f>
+        <f>ROUND(SUMPRODUCT(($C$131:$C$135=3)*(LEFT($A$131:$A$135,LEN(A130))=A130)*$I$131:$I$135),2)</f>
         <v/>
       </c>
       <c r="J130" s="17" t="inlineStr"/>
@@ -9509,7 +9510,7 @@
         <v>6</v>
       </c>
       <c r="I136" s="12">
-        <f>ROUND(SUMPRODUCT(($C$4:$C$164=3)*(LEFT($A$4:$A$164,LEN(A136))=A136)*$I$4:$I$164),2)</f>
+        <f>ROUND(SUMPRODUCT(($C$137:$C$150=3)*(LEFT($A$137:$A$150,LEN(A136))=A136)*$I$137:$I$150),2)</f>
         <v/>
       </c>
       <c r="J136" s="10" t="inlineStr"/>
@@ -9569,7 +9570,7 @@
         <v>5</v>
       </c>
       <c r="I137" s="19">
-        <f>ROUND(SUMPRODUCT(($C$4:$C$164=3)*(LEFT($A$4:$A$164,LEN(A137))=A137)*$I$4:$I$164),2)</f>
+        <f>ROUND(SUMPRODUCT(($C$138:$C$141=3)*(LEFT($A$138:$A$141,LEN(A137))=A137)*$I$138:$I$141),2)</f>
         <v/>
       </c>
       <c r="J137" s="17" t="inlineStr"/>
@@ -9889,7 +9890,7 @@
         <v>6</v>
       </c>
       <c r="I142" s="19">
-        <f>ROUND(SUMPRODUCT(($C$4:$C$164=3)*(LEFT($A$4:$A$164,LEN(A142))=A142)*$I$4:$I$164),2)</f>
+        <f>ROUND(SUMPRODUCT(($C$143:$C$150=3)*(LEFT($A$143:$A$150,LEN(A142))=A142)*$I$143:$I$150),2)</f>
         <v/>
       </c>
       <c r="J142" s="17" t="inlineStr"/>
@@ -10461,7 +10462,7 @@
         <v>5</v>
       </c>
       <c r="I151" s="12">
-        <f>ROUND(SUMPRODUCT(($C$4:$C$164=3)*(LEFT($A$4:$A$164,LEN(A151))=A151)*$I$4:$I$164),2)</f>
+        <f>ROUND(SUMPRODUCT(($C$152:$C$164=3)*(LEFT($A$152:$A$164,LEN(A151))=A151)*$I$152:$I$164),2)</f>
         <v/>
       </c>
       <c r="J151" s="10" t="inlineStr"/>
@@ -10521,7 +10522,7 @@
         <v>4</v>
       </c>
       <c r="I152" s="19">
-        <f>ROUND(SUMPRODUCT(($C$4:$C$164=3)*(LEFT($A$4:$A$164,LEN(A152))=A152)*$I$4:$I$164),2)</f>
+        <f>ROUND(SUMPRODUCT(($C$153:$C$156=3)*(LEFT($A$153:$A$156,LEN(A152))=A152)*$I$153:$I$156),2)</f>
         <v/>
       </c>
       <c r="J152" s="17" t="inlineStr"/>
@@ -10845,7 +10846,7 @@
         <v>5</v>
       </c>
       <c r="I157" s="19">
-        <f>ROUND(SUMPRODUCT(($C$4:$C$164=3)*(LEFT($A$4:$A$164,LEN(A157))=A157)*$I$4:$I$164),2)</f>
+        <f>ROUND(SUMPRODUCT(($C$158:$C$164=3)*(LEFT($A$158:$A$164,LEN(A157))=A157)*$I$158:$I$164),2)</f>
         <v/>
       </c>
       <c r="J157" s="17" t="inlineStr"/>
@@ -13464,6 +13465,7 @@
         </is>
       </c>
     </row>
+    <row r="8"/>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
@@ -14555,6 +14557,7 @@
         </is>
       </c>
     </row>
+    <row r="18"/>
     <row r="19">
       <c r="A19" s="42" t="inlineStr">
         <is>

--- a/RIMS项目WBS工作分解_AI Native版.xlsx
+++ b/RIMS项目WBS工作分解_AI Native版.xlsx
@@ -10,14 +10,16 @@
     <sheet name="使用说明" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="WBS分解" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="26项功能覆盖对照" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="里程碑计划" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="资源负荷与日历" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="WBS词典" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="进度汇总" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="功能视角分解" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="里程碑计划" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="资源负荷与日历" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="WBS词典" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="进度汇总" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'WBS分解'!$A$3:$Q$164</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'WBS分解'!$1:$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'功能视角分解'!$A$2:$P$38</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -25,13 +27,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
-    <numFmt numFmtId="165" formatCode="yyyy/m/d"/>
-    <numFmt numFmtId="166" formatCode="0.##"/>
-    <numFmt numFmtId="167" formatCode="0.0%"/>
+  <numFmts count="3">
+    <numFmt numFmtId="164" formatCode="yyyy/m/d"/>
+    <numFmt numFmtId="165" formatCode="0.##"/>
+    <numFmt numFmtId="166" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="10">
+  <fonts count="11">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -74,8 +75,13 @@
       <color rgb="00808080"/>
       <sz val="9"/>
     </font>
+    <font>
+      <i val="1"/>
+      <color rgb="00C00000"/>
+      <sz val="9"/>
+    </font>
   </fonts>
-  <fills count="7">
+  <fills count="12">
     <fill>
       <patternFill/>
     </fill>
@@ -107,6 +113,31 @@
         <fgColor rgb="00EDEDF7"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E2EFDA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FCE4D6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00DDEBF7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E7E6E6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E4DFEC"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -134,7 +165,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="43">
+  <cellXfs count="72">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -158,10 +189,10 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -175,10 +206,10 @@
       <alignment vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -195,10 +226,10 @@
       <alignment vertical="center" indent="2"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -222,18 +253,101 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -640,7 +754,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -654,7 +768,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="20" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -956,6 +1069,30 @@
       <c r="B29" s="4" t="inlineStr">
         <is>
           <t>「里程碑计划」「资源负荷与日历」「WBS词典」「进度汇总」配合使用；如需甘特图可将WBS编号+起止日期导出到Project/飞书项目</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="30" customHeight="1">
+      <c r="A30" s="38" t="inlineStr">
+        <is>
+          <t>功能视角分解</t>
+        </is>
+      </c>
+      <c r="B30" s="4" t="inlineStr">
+        <is>
+          <t>按功能维度查看：26项功能×（BA/开发A/开发B/测试/文档）五类角色各自的工作内容与人天，另有9类公共支撑行（初始化/架构/集成/专项/上线/管理）；底部与185人天自动对账，可与按开发顺序的「WBS分解」页对照使用</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="30" customHeight="1">
+      <c r="A31" s="38" t="inlineStr">
+        <is>
+          <t>功能视角分解</t>
+        </is>
+      </c>
+      <c r="B31" s="4" t="inlineStr">
+        <is>
+          <t>按功能维度查看：26项功能×（BA/开发A/开发B/测试/文档）五类角色各自的工作内容与人天，另有9类公共支撑行（初始化/架构/集成/专项/上线/管理）；底部与185人天自动对账，可与按开发顺序的「WBS分解」页对照使用</t>
         </is>
       </c>
     </row>
@@ -1145,16 +1282,16 @@
           <t>Mark</t>
         </is>
       </c>
-      <c r="F4" s="11" t="n">
+      <c r="F4" s="43" t="n">
         <v>46279</v>
       </c>
-      <c r="G4" s="11" t="n">
+      <c r="G4" s="43" t="n">
         <v>46372</v>
       </c>
       <c r="H4" s="8" t="n">
         <v>62</v>
       </c>
-      <c r="I4" s="12">
+      <c r="I4" s="44">
         <f>ROUND(SUMPRODUCT(($C$5:$C$14=3)*(LEFT($A$5:$A$14,LEN(A4))=A4)*$I$5:$I$14),2)</f>
         <v/>
       </c>
@@ -1205,16 +1342,16 @@
           <t>Mark</t>
         </is>
       </c>
-      <c r="F5" s="18" t="n">
+      <c r="F5" s="45" t="n">
         <v>46279</v>
       </c>
-      <c r="G5" s="18" t="n">
+      <c r="G5" s="45" t="n">
         <v>46279</v>
       </c>
       <c r="H5" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="I5" s="19">
+      <c r="I5" s="46">
         <f>ROUND(SUMPRODUCT(($C$6:$C$6=3)*(LEFT($A$6:$A$6,LEN(A5))=A5)*$I$6:$I$6),2)</f>
         <v/>
       </c>
@@ -1261,16 +1398,16 @@
           <t>Mark</t>
         </is>
       </c>
-      <c r="F6" s="18" t="n">
+      <c r="F6" s="45" t="n">
         <v>46279</v>
       </c>
-      <c r="G6" s="18" t="n">
+      <c r="G6" s="45" t="n">
         <v>46279</v>
       </c>
       <c r="H6" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="I6" s="19" t="n">
+      <c r="I6" s="46" t="n">
         <v>1</v>
       </c>
       <c r="J6" s="17" t="inlineStr">
@@ -1324,16 +1461,16 @@
           <t>Mark</t>
         </is>
       </c>
-      <c r="F7" s="18" t="n">
+      <c r="F7" s="45" t="n">
         <v>46286</v>
       </c>
-      <c r="G7" s="18" t="n">
+      <c r="G7" s="45" t="n">
         <v>46371</v>
       </c>
       <c r="H7" s="15" t="n">
         <v>56</v>
       </c>
-      <c r="I7" s="19">
+      <c r="I7" s="46">
         <f>ROUND(SUMPRODUCT(($C$8:$C$12=3)*(LEFT($A$8:$A$12,LEN(A7))=A7)*$I$8:$I$12),2)</f>
         <v/>
       </c>
@@ -1388,16 +1525,16 @@
           <t>Mark</t>
         </is>
       </c>
-      <c r="F8" s="18" t="n">
+      <c r="F8" s="45" t="n">
         <v>46286</v>
       </c>
-      <c r="G8" s="18" t="n">
+      <c r="G8" s="45" t="n">
         <v>46366</v>
       </c>
       <c r="H8" s="15" t="n">
         <v>53</v>
       </c>
-      <c r="I8" s="19" t="n">
+      <c r="I8" s="46" t="n">
         <v>6</v>
       </c>
       <c r="J8" s="17" t="inlineStr">
@@ -1455,16 +1592,16 @@
           <t>Mark</t>
         </is>
       </c>
-      <c r="F9" s="18" t="n">
+      <c r="F9" s="45" t="n">
         <v>46307</v>
       </c>
-      <c r="G9" s="18" t="n">
+      <c r="G9" s="45" t="n">
         <v>46357</v>
       </c>
       <c r="H9" s="15" t="n">
         <v>37</v>
       </c>
-      <c r="I9" s="19" t="n">
+      <c r="I9" s="46" t="n">
         <v>2</v>
       </c>
       <c r="J9" s="17" t="inlineStr">
@@ -1522,16 +1659,16 @@
           <t>Mark</t>
         </is>
       </c>
-      <c r="F10" s="18" t="n">
+      <c r="F10" s="45" t="n">
         <v>46286</v>
       </c>
-      <c r="G10" s="18" t="n">
+      <c r="G10" s="45" t="n">
         <v>46371</v>
       </c>
       <c r="H10" s="15" t="n">
         <v>56</v>
       </c>
-      <c r="I10" s="19" t="n">
+      <c r="I10" s="46" t="n">
         <v>2.5</v>
       </c>
       <c r="J10" s="17" t="inlineStr">
@@ -1589,16 +1726,16 @@
           <t>Mark</t>
         </is>
       </c>
-      <c r="F11" s="18" t="n">
+      <c r="F11" s="45" t="n">
         <v>46289</v>
       </c>
-      <c r="G11" s="18" t="n">
+      <c r="G11" s="45" t="n">
         <v>46365</v>
       </c>
       <c r="H11" s="15" t="n">
         <v>49</v>
       </c>
-      <c r="I11" s="19" t="n">
+      <c r="I11" s="46" t="n">
         <v>2.5</v>
       </c>
       <c r="J11" s="17" t="inlineStr">
@@ -1656,16 +1793,16 @@
           <t>Mandy</t>
         </is>
       </c>
-      <c r="F12" s="18" t="n">
+      <c r="F12" s="45" t="n">
         <v>46286</v>
       </c>
-      <c r="G12" s="18" t="n">
+      <c r="G12" s="45" t="n">
         <v>46371</v>
       </c>
       <c r="H12" s="15" t="n">
         <v>56</v>
       </c>
-      <c r="I12" s="19" t="n">
+      <c r="I12" s="46" t="n">
         <v>1</v>
       </c>
       <c r="J12" s="17" t="inlineStr">
@@ -1723,16 +1860,16 @@
           <t>Mark</t>
         </is>
       </c>
-      <c r="F13" s="18" t="n">
+      <c r="F13" s="45" t="n">
         <v>46372</v>
       </c>
-      <c r="G13" s="18" t="n">
+      <c r="G13" s="45" t="n">
         <v>46372</v>
       </c>
       <c r="H13" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="I13" s="19">
+      <c r="I13" s="46">
         <f>ROUND(SUMPRODUCT(($C$14:$C$14=3)*(LEFT($A$14:$A$14,LEN(A13))=A13)*$I$14:$I$14),2)</f>
         <v/>
       </c>
@@ -1779,16 +1916,16 @@
           <t>Mark</t>
         </is>
       </c>
-      <c r="F14" s="26" t="n">
+      <c r="F14" s="47" t="n">
         <v>46372</v>
       </c>
-      <c r="G14" s="26" t="n">
+      <c r="G14" s="47" t="n">
         <v>46372</v>
       </c>
       <c r="H14" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="I14" s="27" t="n">
+      <c r="I14" s="48" t="n">
         <v>1</v>
       </c>
       <c r="J14" s="25" t="inlineStr">
@@ -1846,16 +1983,16 @@
           <t>Mandy</t>
         </is>
       </c>
-      <c r="F15" s="11" t="n">
+      <c r="F15" s="43" t="n">
         <v>46279</v>
       </c>
-      <c r="G15" s="11" t="n">
+      <c r="G15" s="43" t="n">
         <v>46295</v>
       </c>
       <c r="H15" s="8" t="n">
         <v>12</v>
       </c>
-      <c r="I15" s="12">
+      <c r="I15" s="44">
         <f>ROUND(SUMPRODUCT(($C$16:$C$28=3)*(LEFT($A$16:$A$28,LEN(A15))=A15)*$I$16:$I$28),2)</f>
         <v/>
       </c>
@@ -1906,16 +2043,16 @@
           <t>Mandy</t>
         </is>
       </c>
-      <c r="F16" s="18" t="n">
+      <c r="F16" s="45" t="n">
         <v>46279</v>
       </c>
-      <c r="G16" s="18" t="n">
+      <c r="G16" s="45" t="n">
         <v>46283</v>
       </c>
       <c r="H16" s="15" t="n">
         <v>5</v>
       </c>
-      <c r="I16" s="19">
+      <c r="I16" s="46">
         <f>ROUND(SUMPRODUCT(($C$17:$C$19=3)*(LEFT($A$17:$A$19,LEN(A16))=A16)*$I$17:$I$19),2)</f>
         <v/>
       </c>
@@ -1962,16 +2099,16 @@
           <t>Mandy</t>
         </is>
       </c>
-      <c r="F17" s="18" t="n">
+      <c r="F17" s="45" t="n">
         <v>46279</v>
       </c>
-      <c r="G17" s="18" t="n">
+      <c r="G17" s="45" t="n">
         <v>46280</v>
       </c>
       <c r="H17" s="15" t="n">
         <v>2</v>
       </c>
-      <c r="I17" s="19" t="n">
+      <c r="I17" s="46" t="n">
         <v>2</v>
       </c>
       <c r="J17" s="17" t="inlineStr">
@@ -2025,16 +2162,16 @@
           <t>Mandy</t>
         </is>
       </c>
-      <c r="F18" s="18" t="n">
+      <c r="F18" s="45" t="n">
         <v>46281</v>
       </c>
-      <c r="G18" s="18" t="n">
+      <c r="G18" s="45" t="n">
         <v>46282</v>
       </c>
       <c r="H18" s="15" t="n">
         <v>2</v>
       </c>
-      <c r="I18" s="19" t="n">
+      <c r="I18" s="46" t="n">
         <v>2</v>
       </c>
       <c r="J18" s="17" t="inlineStr">
@@ -2092,16 +2229,16 @@
           <t>Mandy</t>
         </is>
       </c>
-      <c r="F19" s="18" t="n">
+      <c r="F19" s="45" t="n">
         <v>46283</v>
       </c>
-      <c r="G19" s="18" t="n">
+      <c r="G19" s="45" t="n">
         <v>46283</v>
       </c>
       <c r="H19" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="I19" s="19" t="n">
+      <c r="I19" s="46" t="n">
         <v>1</v>
       </c>
       <c r="J19" s="17" t="inlineStr">
@@ -2159,16 +2296,16 @@
           <t>Mandy</t>
         </is>
       </c>
-      <c r="F20" s="18" t="n">
+      <c r="F20" s="45" t="n">
         <v>46286</v>
       </c>
-      <c r="G20" s="18" t="n">
+      <c r="G20" s="45" t="n">
         <v>46289</v>
       </c>
       <c r="H20" s="15" t="n">
         <v>4</v>
       </c>
-      <c r="I20" s="19">
+      <c r="I20" s="46">
         <f>ROUND(SUMPRODUCT(($C$21:$C$22=3)*(LEFT($A$21:$A$22,LEN(A20))=A20)*$I$21:$I$22),2)</f>
         <v/>
       </c>
@@ -2215,16 +2352,16 @@
           <t>Mandy</t>
         </is>
       </c>
-      <c r="F21" s="18" t="n">
+      <c r="F21" s="45" t="n">
         <v>46286</v>
       </c>
-      <c r="G21" s="18" t="n">
+      <c r="G21" s="45" t="n">
         <v>46288</v>
       </c>
       <c r="H21" s="15" t="n">
         <v>3</v>
       </c>
-      <c r="I21" s="19" t="n">
+      <c r="I21" s="46" t="n">
         <v>2.5</v>
       </c>
       <c r="J21" s="17" t="inlineStr">
@@ -2282,16 +2419,16 @@
           <t>Mandy</t>
         </is>
       </c>
-      <c r="F22" s="26" t="n">
+      <c r="F22" s="47" t="n">
         <v>46289</v>
       </c>
-      <c r="G22" s="26" t="n">
+      <c r="G22" s="47" t="n">
         <v>46289</v>
       </c>
       <c r="H22" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="I22" s="27" t="n">
+      <c r="I22" s="48" t="n">
         <v>1</v>
       </c>
       <c r="J22" s="25" t="inlineStr">
@@ -2349,16 +2486,16 @@
           <t>Mandy</t>
         </is>
       </c>
-      <c r="F23" s="18" t="n">
+      <c r="F23" s="45" t="n">
         <v>46293</v>
       </c>
-      <c r="G23" s="18" t="n">
+      <c r="G23" s="45" t="n">
         <v>46303</v>
       </c>
       <c r="H23" s="15" t="n">
         <v>4</v>
       </c>
-      <c r="I23" s="19">
+      <c r="I23" s="46">
         <f>ROUND(SUMPRODUCT(($C$24:$C$26=3)*(LEFT($A$24:$A$26,LEN(A23))=A23)*$I$24:$I$26),2)</f>
         <v/>
       </c>
@@ -2409,16 +2546,16 @@
           <t>Mandy</t>
         </is>
       </c>
-      <c r="F24" s="18" t="n">
+      <c r="F24" s="45" t="n">
         <v>46293</v>
       </c>
-      <c r="G24" s="18" t="n">
+      <c r="G24" s="45" t="n">
         <v>46293</v>
       </c>
       <c r="H24" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="I24" s="19" t="n">
+      <c r="I24" s="46" t="n">
         <v>1</v>
       </c>
       <c r="J24" s="17" t="inlineStr">
@@ -2476,16 +2613,16 @@
           <t>Mandy</t>
         </is>
       </c>
-      <c r="F25" s="18" t="n">
+      <c r="F25" s="45" t="n">
         <v>46294</v>
       </c>
-      <c r="G25" s="18" t="n">
+      <c r="G25" s="45" t="n">
         <v>46294</v>
       </c>
       <c r="H25" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="I25" s="19" t="n">
+      <c r="I25" s="46" t="n">
         <v>1</v>
       </c>
       <c r="J25" s="17" t="inlineStr">
@@ -2543,16 +2680,16 @@
           <t>Mandy</t>
         </is>
       </c>
-      <c r="F26" s="18" t="n">
+      <c r="F26" s="45" t="n">
         <v>46295</v>
       </c>
-      <c r="G26" s="18" t="n">
+      <c r="G26" s="45" t="n">
         <v>46303</v>
       </c>
       <c r="H26" s="15" t="n">
         <v>2</v>
       </c>
-      <c r="I26" s="19" t="n">
+      <c r="I26" s="46" t="n">
         <v>1.5</v>
       </c>
       <c r="J26" s="17" t="inlineStr">
@@ -2610,16 +2747,16 @@
           <t>Mandy</t>
         </is>
       </c>
-      <c r="F27" s="18" t="n">
+      <c r="F27" s="45" t="n">
         <v>46303</v>
       </c>
-      <c r="G27" s="18" t="n">
+      <c r="G27" s="45" t="n">
         <v>46360</v>
       </c>
       <c r="H27" s="15" t="n">
         <v>42</v>
       </c>
-      <c r="I27" s="19">
+      <c r="I27" s="46">
         <f>ROUND(SUMPRODUCT(($C$28:$C$28=3)*(LEFT($A$28:$A$28,LEN(A27))=A27)*$I$28:$I$28),2)</f>
         <v/>
       </c>
@@ -2670,16 +2807,16 @@
           <t>Mandy</t>
         </is>
       </c>
-      <c r="F28" s="18" t="n">
+      <c r="F28" s="45" t="n">
         <v>46303</v>
       </c>
-      <c r="G28" s="18" t="n">
+      <c r="G28" s="45" t="n">
         <v>46360</v>
       </c>
       <c r="H28" s="15" t="n">
         <v>42</v>
       </c>
-      <c r="I28" s="19" t="n">
+      <c r="I28" s="46" t="n">
         <v>1</v>
       </c>
       <c r="J28" s="17" t="inlineStr">
@@ -2737,16 +2874,16 @@
           <t>Wade/DevB</t>
         </is>
       </c>
-      <c r="F29" s="11" t="n">
+      <c r="F29" s="43" t="n">
         <v>46279</v>
       </c>
-      <c r="G29" s="11" t="n">
+      <c r="G29" s="43" t="n">
         <v>46304</v>
       </c>
       <c r="H29" s="8" t="n">
         <v>14</v>
       </c>
-      <c r="I29" s="12">
+      <c r="I29" s="44">
         <f>ROUND(SUMPRODUCT(($C$30:$C$50=3)*(LEFT($A$30:$A$50,LEN(A29))=A29)*$I$30:$I$50),2)</f>
         <v/>
       </c>
@@ -2797,16 +2934,16 @@
           <t>Wade</t>
         </is>
       </c>
-      <c r="F30" s="18" t="n">
+      <c r="F30" s="45" t="n">
         <v>46279</v>
       </c>
-      <c r="G30" s="18" t="n">
+      <c r="G30" s="45" t="n">
         <v>46283</v>
       </c>
       <c r="H30" s="15" t="n">
         <v>5</v>
       </c>
-      <c r="I30" s="19">
+      <c r="I30" s="46">
         <f>ROUND(SUMPRODUCT(($C$31:$C$34=3)*(LEFT($A$31:$A$34,LEN(A30))=A30)*$I$31:$I$34),2)</f>
         <v/>
       </c>
@@ -2857,16 +2994,16 @@
           <t>Wade</t>
         </is>
       </c>
-      <c r="F31" s="18" t="n">
+      <c r="F31" s="45" t="n">
         <v>46279</v>
       </c>
-      <c r="G31" s="18" t="n">
+      <c r="G31" s="45" t="n">
         <v>46279</v>
       </c>
       <c r="H31" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="I31" s="19" t="n">
+      <c r="I31" s="46" t="n">
         <v>1</v>
       </c>
       <c r="J31" s="17" t="inlineStr">
@@ -2920,16 +3057,16 @@
           <t>Wade</t>
         </is>
       </c>
-      <c r="F32" s="18" t="n">
+      <c r="F32" s="45" t="n">
         <v>46280</v>
       </c>
-      <c r="G32" s="18" t="n">
+      <c r="G32" s="45" t="n">
         <v>46280</v>
       </c>
       <c r="H32" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="I32" s="19" t="n">
+      <c r="I32" s="46" t="n">
         <v>1</v>
       </c>
       <c r="J32" s="17" t="inlineStr">
@@ -2987,16 +3124,16 @@
           <t>Wade</t>
         </is>
       </c>
-      <c r="F33" s="18" t="n">
+      <c r="F33" s="45" t="n">
         <v>46281</v>
       </c>
-      <c r="G33" s="18" t="n">
+      <c r="G33" s="45" t="n">
         <v>46286</v>
       </c>
       <c r="H33" s="15" t="n">
         <v>4</v>
       </c>
-      <c r="I33" s="19" t="n">
+      <c r="I33" s="46" t="n">
         <v>4</v>
       </c>
       <c r="J33" s="17" t="inlineStr">
@@ -3054,16 +3191,16 @@
           <t>Wade</t>
         </is>
       </c>
-      <c r="F34" s="18" t="n">
+      <c r="F34" s="45" t="n">
         <v>46287</v>
       </c>
-      <c r="G34" s="18" t="n">
+      <c r="G34" s="45" t="n">
         <v>46287</v>
       </c>
       <c r="H34" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="I34" s="19" t="n">
+      <c r="I34" s="46" t="n">
         <v>1</v>
       </c>
       <c r="J34" s="17" t="inlineStr">
@@ -3121,16 +3258,16 @@
           <t>DevB</t>
         </is>
       </c>
-      <c r="F35" s="18" t="n">
+      <c r="F35" s="45" t="n">
         <v>46279</v>
       </c>
-      <c r="G35" s="18" t="n">
+      <c r="G35" s="45" t="n">
         <v>46304</v>
       </c>
       <c r="H35" s="15" t="n">
         <v>14</v>
       </c>
-      <c r="I35" s="19">
+      <c r="I35" s="46">
         <f>ROUND(SUMPRODUCT(($C$36:$C$43=3)*(LEFT($A$36:$A$43,LEN(A35))=A35)*$I$36:$I$43),2)</f>
         <v/>
       </c>
@@ -3177,16 +3314,16 @@
           <t>DevB</t>
         </is>
       </c>
-      <c r="F36" s="18" t="n">
+      <c r="F36" s="45" t="n">
         <v>46279</v>
       </c>
-      <c r="G36" s="18" t="n">
+      <c r="G36" s="45" t="n">
         <v>46280</v>
       </c>
       <c r="H36" s="15" t="n">
         <v>2</v>
       </c>
-      <c r="I36" s="19" t="n">
+      <c r="I36" s="46" t="n">
         <v>2</v>
       </c>
       <c r="J36" s="17" t="inlineStr">
@@ -3244,16 +3381,16 @@
           <t>DevB</t>
         </is>
       </c>
-      <c r="F37" s="18" t="n">
+      <c r="F37" s="45" t="n">
         <v>46281</v>
       </c>
-      <c r="G37" s="18" t="n">
+      <c r="G37" s="45" t="n">
         <v>46282</v>
       </c>
       <c r="H37" s="15" t="n">
         <v>2</v>
       </c>
-      <c r="I37" s="19" t="n">
+      <c r="I37" s="46" t="n">
         <v>2</v>
       </c>
       <c r="J37" s="17" t="inlineStr">
@@ -3307,16 +3444,16 @@
           <t>DevB</t>
         </is>
       </c>
-      <c r="F38" s="18" t="n">
+      <c r="F38" s="45" t="n">
         <v>46283</v>
       </c>
-      <c r="G38" s="18" t="n">
+      <c r="G38" s="45" t="n">
         <v>46283</v>
       </c>
       <c r="H38" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="I38" s="19" t="n">
+      <c r="I38" s="46" t="n">
         <v>1</v>
       </c>
       <c r="J38" s="17" t="inlineStr">
@@ -3370,16 +3507,16 @@
           <t>DevB</t>
         </is>
       </c>
-      <c r="F39" s="18" t="n">
+      <c r="F39" s="45" t="n">
         <v>46286</v>
       </c>
-      <c r="G39" s="18" t="n">
+      <c r="G39" s="45" t="n">
         <v>46287</v>
       </c>
       <c r="H39" s="15" t="n">
         <v>2</v>
       </c>
-      <c r="I39" s="19" t="n">
+      <c r="I39" s="46" t="n">
         <v>2</v>
       </c>
       <c r="J39" s="17" t="inlineStr">
@@ -3433,16 +3570,16 @@
           <t>DevB</t>
         </is>
       </c>
-      <c r="F40" s="18" t="n">
+      <c r="F40" s="45" t="n">
         <v>46288</v>
       </c>
-      <c r="G40" s="18" t="n">
+      <c r="G40" s="45" t="n">
         <v>46289</v>
       </c>
       <c r="H40" s="15" t="n">
         <v>2</v>
       </c>
-      <c r="I40" s="19" t="n">
+      <c r="I40" s="46" t="n">
         <v>2</v>
       </c>
       <c r="J40" s="17" t="inlineStr">
@@ -3496,16 +3633,16 @@
           <t>DevB</t>
         </is>
       </c>
-      <c r="F41" s="18" t="n">
+      <c r="F41" s="45" t="n">
         <v>46293</v>
       </c>
-      <c r="G41" s="18" t="n">
+      <c r="G41" s="45" t="n">
         <v>46294</v>
       </c>
       <c r="H41" s="15" t="n">
         <v>2</v>
       </c>
-      <c r="I41" s="19" t="n">
+      <c r="I41" s="46" t="n">
         <v>2</v>
       </c>
       <c r="J41" s="17" t="inlineStr">
@@ -3559,16 +3696,16 @@
           <t>DevB</t>
         </is>
       </c>
-      <c r="F42" s="18" t="n">
+      <c r="F42" s="45" t="n">
         <v>46295</v>
       </c>
-      <c r="G42" s="18" t="n">
+      <c r="G42" s="45" t="n">
         <v>46303</v>
       </c>
       <c r="H42" s="15" t="n">
         <v>2</v>
       </c>
-      <c r="I42" s="19" t="n">
+      <c r="I42" s="46" t="n">
         <v>2</v>
       </c>
       <c r="J42" s="17" t="inlineStr">
@@ -3626,16 +3763,16 @@
           <t>DevB</t>
         </is>
       </c>
-      <c r="F43" s="18" t="n">
+      <c r="F43" s="45" t="n">
         <v>46304</v>
       </c>
-      <c r="G43" s="18" t="n">
+      <c r="G43" s="45" t="n">
         <v>46304</v>
       </c>
       <c r="H43" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="I43" s="19" t="n">
+      <c r="I43" s="46" t="n">
         <v>1</v>
       </c>
       <c r="J43" s="17" t="inlineStr">
@@ -3689,16 +3826,16 @@
           <t>Wade</t>
         </is>
       </c>
-      <c r="F44" s="18" t="n">
+      <c r="F44" s="45" t="n">
         <v>46286</v>
       </c>
-      <c r="G44" s="18" t="n">
+      <c r="G44" s="45" t="n">
         <v>46304</v>
       </c>
       <c r="H44" s="15" t="n">
         <v>9</v>
       </c>
-      <c r="I44" s="19">
+      <c r="I44" s="46">
         <f>ROUND(SUMPRODUCT(($C$45:$C$50=3)*(LEFT($A$45:$A$50,LEN(A44))=A44)*$I$45:$I$50),2)</f>
         <v/>
       </c>
@@ -3745,16 +3882,16 @@
           <t>Wade</t>
         </is>
       </c>
-      <c r="F45" s="18" t="n">
+      <c r="F45" s="45" t="n">
         <v>46288</v>
       </c>
-      <c r="G45" s="18" t="n">
+      <c r="G45" s="45" t="n">
         <v>46289</v>
       </c>
       <c r="H45" s="15" t="n">
         <v>2</v>
       </c>
-      <c r="I45" s="19" t="n">
+      <c r="I45" s="46" t="n">
         <v>2</v>
       </c>
       <c r="J45" s="17" t="inlineStr">
@@ -3812,16 +3949,16 @@
           <t>Wade</t>
         </is>
       </c>
-      <c r="F46" s="18" t="n">
+      <c r="F46" s="45" t="n">
         <v>46293</v>
       </c>
-      <c r="G46" s="18" t="n">
+      <c r="G46" s="45" t="n">
         <v>46294</v>
       </c>
       <c r="H46" s="15" t="n">
         <v>2</v>
       </c>
-      <c r="I46" s="19" t="n">
+      <c r="I46" s="46" t="n">
         <v>2</v>
       </c>
       <c r="J46" s="17" t="inlineStr">
@@ -3875,16 +4012,16 @@
           <t>Wade</t>
         </is>
       </c>
-      <c r="F47" s="18" t="n">
+      <c r="F47" s="45" t="n">
         <v>46295</v>
       </c>
-      <c r="G47" s="18" t="n">
+      <c r="G47" s="45" t="n">
         <v>46295</v>
       </c>
       <c r="H47" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="I47" s="19" t="n">
+      <c r="I47" s="46" t="n">
         <v>0.5</v>
       </c>
       <c r="J47" s="17" t="inlineStr">
@@ -3942,16 +4079,16 @@
           <t>Wade</t>
         </is>
       </c>
-      <c r="F48" s="18" t="n">
+      <c r="F48" s="45" t="n">
         <v>46303</v>
       </c>
-      <c r="G48" s="18" t="n">
+      <c r="G48" s="45" t="n">
         <v>46303</v>
       </c>
       <c r="H48" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="I48" s="19" t="n">
+      <c r="I48" s="46" t="n">
         <v>1</v>
       </c>
       <c r="J48" s="17" t="inlineStr">
@@ -4009,16 +4146,16 @@
           <t>Wade</t>
         </is>
       </c>
-      <c r="F49" s="18" t="n">
+      <c r="F49" s="45" t="n">
         <v>46304</v>
       </c>
-      <c r="G49" s="18" t="n">
+      <c r="G49" s="45" t="n">
         <v>46304</v>
       </c>
       <c r="H49" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="I49" s="19" t="n">
+      <c r="I49" s="46" t="n">
         <v>0.5</v>
       </c>
       <c r="J49" s="17" t="inlineStr">
@@ -4076,16 +4213,16 @@
           <t>Wade</t>
         </is>
       </c>
-      <c r="F50" s="26" t="n">
+      <c r="F50" s="47" t="n">
         <v>46304</v>
       </c>
-      <c r="G50" s="26" t="n">
+      <c r="G50" s="47" t="n">
         <v>46304</v>
       </c>
       <c r="H50" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="I50" s="27" t="n">
+      <c r="I50" s="48" t="n">
         <v>0.5</v>
       </c>
       <c r="J50" s="25" t="inlineStr">
@@ -4143,16 +4280,16 @@
           <t>Wade/DevB/Mandy</t>
         </is>
       </c>
-      <c r="F51" s="11" t="n">
+      <c r="F51" s="43" t="n">
         <v>46307</v>
       </c>
-      <c r="G51" s="11" t="n">
+      <c r="G51" s="43" t="n">
         <v>46318</v>
       </c>
       <c r="H51" s="8" t="n">
         <v>10</v>
       </c>
-      <c r="I51" s="12">
+      <c r="I51" s="44">
         <f>ROUND(SUMPRODUCT(($C$52:$C$74=3)*(LEFT($A$52:$A$74,LEN(A51))=A51)*$I$52:$I$74),2)</f>
         <v/>
       </c>
@@ -4203,16 +4340,16 @@
           <t>Wade</t>
         </is>
       </c>
-      <c r="F52" s="18" t="n">
+      <c r="F52" s="45" t="n">
         <v>46307</v>
       </c>
-      <c r="G52" s="18" t="n">
+      <c r="G52" s="45" t="n">
         <v>46314</v>
       </c>
       <c r="H52" s="15" t="n">
         <v>6</v>
       </c>
-      <c r="I52" s="19">
+      <c r="I52" s="46">
         <f>ROUND(SUMPRODUCT(($C$53:$C$55=3)*(LEFT($A$53:$A$55,LEN(A52))=A52)*$I$53:$I$55),2)</f>
         <v/>
       </c>
@@ -4259,16 +4396,16 @@
           <t>Wade</t>
         </is>
       </c>
-      <c r="F53" s="18" t="n">
+      <c r="F53" s="45" t="n">
         <v>46307</v>
       </c>
-      <c r="G53" s="18" t="n">
+      <c r="G53" s="45" t="n">
         <v>46309</v>
       </c>
       <c r="H53" s="15" t="n">
         <v>3</v>
       </c>
-      <c r="I53" s="19" t="n">
+      <c r="I53" s="46" t="n">
         <v>3</v>
       </c>
       <c r="J53" s="17" t="inlineStr">
@@ -4326,16 +4463,16 @@
           <t>Wade</t>
         </is>
       </c>
-      <c r="F54" s="18" t="n">
+      <c r="F54" s="45" t="n">
         <v>46310</v>
       </c>
-      <c r="G54" s="18" t="n">
+      <c r="G54" s="45" t="n">
         <v>46311</v>
       </c>
       <c r="H54" s="15" t="n">
         <v>2</v>
       </c>
-      <c r="I54" s="19" t="n">
+      <c r="I54" s="46" t="n">
         <v>2</v>
       </c>
       <c r="J54" s="17" t="inlineStr">
@@ -4393,16 +4530,16 @@
           <t>Wade</t>
         </is>
       </c>
-      <c r="F55" s="18" t="n">
+      <c r="F55" s="45" t="n">
         <v>46314</v>
       </c>
-      <c r="G55" s="18" t="n">
+      <c r="G55" s="45" t="n">
         <v>46314</v>
       </c>
       <c r="H55" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="I55" s="19" t="n">
+      <c r="I55" s="46" t="n">
         <v>1</v>
       </c>
       <c r="J55" s="17" t="inlineStr">
@@ -4460,16 +4597,16 @@
           <t>DevB</t>
         </is>
       </c>
-      <c r="F56" s="18" t="n">
+      <c r="F56" s="45" t="n">
         <v>46307</v>
       </c>
-      <c r="G56" s="18" t="n">
+      <c r="G56" s="45" t="n">
         <v>46318</v>
       </c>
       <c r="H56" s="15" t="n">
         <v>10</v>
       </c>
-      <c r="I56" s="19">
+      <c r="I56" s="46">
         <f>ROUND(SUMPRODUCT(($C$57:$C$63=3)*(LEFT($A$57:$A$63,LEN(A56))=A56)*$I$57:$I$63),2)</f>
         <v/>
       </c>
@@ -4516,16 +4653,16 @@
           <t>DevB</t>
         </is>
       </c>
-      <c r="F57" s="18" t="n">
+      <c r="F57" s="45" t="n">
         <v>46307</v>
       </c>
-      <c r="G57" s="18" t="n">
+      <c r="G57" s="45" t="n">
         <v>46308</v>
       </c>
       <c r="H57" s="15" t="n">
         <v>2</v>
       </c>
-      <c r="I57" s="19" t="n">
+      <c r="I57" s="46" t="n">
         <v>2</v>
       </c>
       <c r="J57" s="17" t="inlineStr">
@@ -4579,16 +4716,16 @@
           <t>DevB</t>
         </is>
       </c>
-      <c r="F58" s="18" t="n">
+      <c r="F58" s="45" t="n">
         <v>46309</v>
       </c>
-      <c r="G58" s="18" t="n">
+      <c r="G58" s="45" t="n">
         <v>46309</v>
       </c>
       <c r="H58" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="I58" s="19" t="n">
+      <c r="I58" s="46" t="n">
         <v>1</v>
       </c>
       <c r="J58" s="17" t="inlineStr">
@@ -4642,16 +4779,16 @@
           <t>DevB</t>
         </is>
       </c>
-      <c r="F59" s="18" t="n">
+      <c r="F59" s="45" t="n">
         <v>46310</v>
       </c>
-      <c r="G59" s="18" t="n">
+      <c r="G59" s="45" t="n">
         <v>46310</v>
       </c>
       <c r="H59" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="I59" s="19" t="n">
+      <c r="I59" s="46" t="n">
         <v>1</v>
       </c>
       <c r="J59" s="17" t="inlineStr">
@@ -4705,16 +4842,16 @@
           <t>DevB</t>
         </is>
       </c>
-      <c r="F60" s="18" t="n">
+      <c r="F60" s="45" t="n">
         <v>46311</v>
       </c>
-      <c r="G60" s="18" t="n">
+      <c r="G60" s="45" t="n">
         <v>46311</v>
       </c>
       <c r="H60" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="I60" s="19" t="n">
+      <c r="I60" s="46" t="n">
         <v>1</v>
       </c>
       <c r="J60" s="17" t="inlineStr">
@@ -4768,16 +4905,16 @@
           <t>DevB</t>
         </is>
       </c>
-      <c r="F61" s="18" t="n">
+      <c r="F61" s="45" t="n">
         <v>46314</v>
       </c>
-      <c r="G61" s="18" t="n">
+      <c r="G61" s="45" t="n">
         <v>46315</v>
       </c>
       <c r="H61" s="15" t="n">
         <v>2</v>
       </c>
-      <c r="I61" s="19" t="n">
+      <c r="I61" s="46" t="n">
         <v>2</v>
       </c>
       <c r="J61" s="17" t="inlineStr">
@@ -4831,16 +4968,16 @@
           <t>DevB</t>
         </is>
       </c>
-      <c r="F62" s="18" t="n">
+      <c r="F62" s="45" t="n">
         <v>46316</v>
       </c>
-      <c r="G62" s="18" t="n">
+      <c r="G62" s="45" t="n">
         <v>46317</v>
       </c>
       <c r="H62" s="15" t="n">
         <v>2</v>
       </c>
-      <c r="I62" s="19" t="n">
+      <c r="I62" s="46" t="n">
         <v>2</v>
       </c>
       <c r="J62" s="17" t="inlineStr">
@@ -4894,16 +5031,16 @@
           <t>DevB</t>
         </is>
       </c>
-      <c r="F63" s="18" t="n">
+      <c r="F63" s="45" t="n">
         <v>46318</v>
       </c>
-      <c r="G63" s="18" t="n">
+      <c r="G63" s="45" t="n">
         <v>46318</v>
       </c>
       <c r="H63" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="I63" s="19" t="n">
+      <c r="I63" s="46" t="n">
         <v>1</v>
       </c>
       <c r="J63" s="17" t="inlineStr">
@@ -4957,16 +5094,16 @@
           <t>Wade</t>
         </is>
       </c>
-      <c r="F64" s="18" t="n">
+      <c r="F64" s="45" t="n">
         <v>46315</v>
       </c>
-      <c r="G64" s="18" t="n">
+      <c r="G64" s="45" t="n">
         <v>46318</v>
       </c>
       <c r="H64" s="15" t="n">
         <v>4</v>
       </c>
-      <c r="I64" s="19">
+      <c r="I64" s="46">
         <f>ROUND(SUMPRODUCT(($C$65:$C$67=3)*(LEFT($A$65:$A$67,LEN(A64))=A64)*$I$65:$I$67),2)</f>
         <v/>
       </c>
@@ -5013,16 +5150,16 @@
           <t>Wade</t>
         </is>
       </c>
-      <c r="F65" s="18" t="n">
+      <c r="F65" s="45" t="n">
         <v>46315</v>
       </c>
-      <c r="G65" s="18" t="n">
+      <c r="G65" s="45" t="n">
         <v>46316</v>
       </c>
       <c r="H65" s="15" t="n">
         <v>2</v>
       </c>
-      <c r="I65" s="19" t="n">
+      <c r="I65" s="46" t="n">
         <v>2</v>
       </c>
       <c r="J65" s="17" t="inlineStr">
@@ -5076,16 +5213,16 @@
           <t>Wade</t>
         </is>
       </c>
-      <c r="F66" s="18" t="n">
+      <c r="F66" s="45" t="n">
         <v>46317</v>
       </c>
-      <c r="G66" s="18" t="n">
+      <c r="G66" s="45" t="n">
         <v>46317</v>
       </c>
       <c r="H66" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="I66" s="19" t="n">
+      <c r="I66" s="46" t="n">
         <v>1</v>
       </c>
       <c r="J66" s="17" t="inlineStr">
@@ -5139,16 +5276,16 @@
           <t>Wade</t>
         </is>
       </c>
-      <c r="F67" s="26" t="n">
+      <c r="F67" s="47" t="n">
         <v>46318</v>
       </c>
-      <c r="G67" s="26" t="n">
+      <c r="G67" s="47" t="n">
         <v>46318</v>
       </c>
       <c r="H67" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="I67" s="27" t="n">
+      <c r="I67" s="48" t="n">
         <v>1</v>
       </c>
       <c r="J67" s="25" t="inlineStr">
@@ -5206,16 +5343,16 @@
           <t>Mandy</t>
         </is>
       </c>
-      <c r="F68" s="18" t="n">
+      <c r="F68" s="45" t="n">
         <v>46307</v>
       </c>
-      <c r="G68" s="18" t="n">
+      <c r="G68" s="45" t="n">
         <v>46318</v>
       </c>
       <c r="H68" s="15" t="n">
         <v>10</v>
       </c>
-      <c r="I68" s="19">
+      <c r="I68" s="46">
         <f>ROUND(SUMPRODUCT(($C$69:$C$74=3)*(LEFT($A$69:$A$74,LEN(A68))=A68)*$I$69:$I$74),2)</f>
         <v/>
       </c>
@@ -5262,16 +5399,16 @@
           <t>Mandy</t>
         </is>
       </c>
-      <c r="F69" s="18" t="n">
+      <c r="F69" s="45" t="n">
         <v>46307</v>
       </c>
-      <c r="G69" s="18" t="n">
+      <c r="G69" s="45" t="n">
         <v>46308</v>
       </c>
       <c r="H69" s="15" t="n">
         <v>2</v>
       </c>
-      <c r="I69" s="19" t="n">
+      <c r="I69" s="46" t="n">
         <v>1.5</v>
       </c>
       <c r="J69" s="17" t="inlineStr">
@@ -5325,16 +5462,16 @@
           <t>Mandy</t>
         </is>
       </c>
-      <c r="F70" s="18" t="n">
+      <c r="F70" s="45" t="n">
         <v>46309</v>
       </c>
-      <c r="G70" s="18" t="n">
+      <c r="G70" s="45" t="n">
         <v>46310</v>
       </c>
       <c r="H70" s="15" t="n">
         <v>2</v>
       </c>
-      <c r="I70" s="19" t="n">
+      <c r="I70" s="46" t="n">
         <v>1</v>
       </c>
       <c r="J70" s="17" t="inlineStr">
@@ -5392,16 +5529,16 @@
           <t>Mandy</t>
         </is>
       </c>
-      <c r="F71" s="18" t="n">
+      <c r="F71" s="45" t="n">
         <v>46311</v>
       </c>
-      <c r="G71" s="18" t="n">
+      <c r="G71" s="45" t="n">
         <v>46314</v>
       </c>
       <c r="H71" s="15" t="n">
         <v>2</v>
       </c>
-      <c r="I71" s="19" t="n">
+      <c r="I71" s="46" t="n">
         <v>1</v>
       </c>
       <c r="J71" s="17" t="inlineStr">
@@ -5455,16 +5592,16 @@
           <t>Mandy</t>
         </is>
       </c>
-      <c r="F72" s="18" t="n">
+      <c r="F72" s="45" t="n">
         <v>46317</v>
       </c>
-      <c r="G72" s="18" t="n">
+      <c r="G72" s="45" t="n">
         <v>46317</v>
       </c>
       <c r="H72" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="I72" s="19" t="n">
+      <c r="I72" s="46" t="n">
         <v>1</v>
       </c>
       <c r="J72" s="17" t="inlineStr">
@@ -5518,16 +5655,16 @@
           <t>Mandy</t>
         </is>
       </c>
-      <c r="F73" s="18" t="n">
+      <c r="F73" s="45" t="n">
         <v>46315</v>
       </c>
-      <c r="G73" s="18" t="n">
+      <c r="G73" s="45" t="n">
         <v>46316</v>
       </c>
       <c r="H73" s="15" t="n">
         <v>2</v>
       </c>
-      <c r="I73" s="19" t="n">
+      <c r="I73" s="46" t="n">
         <v>1.5</v>
       </c>
       <c r="J73" s="17" t="inlineStr">
@@ -5585,16 +5722,16 @@
           <t>Mandy</t>
         </is>
       </c>
-      <c r="F74" s="18" t="n">
+      <c r="F74" s="45" t="n">
         <v>46318</v>
       </c>
-      <c r="G74" s="18" t="n">
+      <c r="G74" s="45" t="n">
         <v>46318</v>
       </c>
       <c r="H74" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="I74" s="19" t="n">
+      <c r="I74" s="46" t="n">
         <v>0.5</v>
       </c>
       <c r="J74" s="17" t="inlineStr">
@@ -5648,16 +5785,16 @@
           <t>Wade/DevB/Mandy</t>
         </is>
       </c>
-      <c r="F75" s="11" t="n">
+      <c r="F75" s="43" t="n">
         <v>46321</v>
       </c>
-      <c r="G75" s="11" t="n">
+      <c r="G75" s="43" t="n">
         <v>46339</v>
       </c>
       <c r="H75" s="8" t="n">
         <v>15</v>
       </c>
-      <c r="I75" s="12">
+      <c r="I75" s="44">
         <f>ROUND(SUMPRODUCT(($C$76:$C$114=3)*(LEFT($A$76:$A$114,LEN(A75))=A75)*$I$76:$I$114),2)</f>
         <v/>
       </c>
@@ -5708,16 +5845,16 @@
           <t>Wade</t>
         </is>
       </c>
-      <c r="F76" s="18" t="n">
+      <c r="F76" s="45" t="n">
         <v>46321</v>
       </c>
-      <c r="G76" s="18" t="n">
+      <c r="G76" s="45" t="n">
         <v>46339</v>
       </c>
       <c r="H76" s="15" t="n">
         <v>15</v>
       </c>
-      <c r="I76" s="19">
+      <c r="I76" s="46">
         <f>ROUND(SUMPRODUCT(($C$77:$C$85=3)*(LEFT($A$77:$A$85,LEN(A76))=A76)*$I$77:$I$85),2)</f>
         <v/>
       </c>
@@ -5764,16 +5901,16 @@
           <t>Wade</t>
         </is>
       </c>
-      <c r="F77" s="18" t="n">
+      <c r="F77" s="45" t="n">
         <v>46321</v>
       </c>
-      <c r="G77" s="18" t="n">
+      <c r="G77" s="45" t="n">
         <v>46322</v>
       </c>
       <c r="H77" s="15" t="n">
         <v>2</v>
       </c>
-      <c r="I77" s="19" t="n">
+      <c r="I77" s="46" t="n">
         <v>2</v>
       </c>
       <c r="J77" s="17" t="inlineStr">
@@ -5827,16 +5964,16 @@
           <t>Wade</t>
         </is>
       </c>
-      <c r="F78" s="18" t="n">
+      <c r="F78" s="45" t="n">
         <v>46323</v>
       </c>
-      <c r="G78" s="18" t="n">
+      <c r="G78" s="45" t="n">
         <v>46324</v>
       </c>
       <c r="H78" s="15" t="n">
         <v>2</v>
       </c>
-      <c r="I78" s="19" t="n">
+      <c r="I78" s="46" t="n">
         <v>2</v>
       </c>
       <c r="J78" s="17" t="inlineStr">
@@ -5890,16 +6027,16 @@
           <t>Wade</t>
         </is>
       </c>
-      <c r="F79" s="18" t="n">
+      <c r="F79" s="45" t="n">
         <v>46325</v>
       </c>
-      <c r="G79" s="18" t="n">
+      <c r="G79" s="45" t="n">
         <v>46328</v>
       </c>
       <c r="H79" s="15" t="n">
         <v>2</v>
       </c>
-      <c r="I79" s="19" t="n">
+      <c r="I79" s="46" t="n">
         <v>2</v>
       </c>
       <c r="J79" s="17" t="inlineStr">
@@ -5957,16 +6094,16 @@
           <t>Wade</t>
         </is>
       </c>
-      <c r="F80" s="18" t="n">
+      <c r="F80" s="45" t="n">
         <v>46329</v>
       </c>
-      <c r="G80" s="18" t="n">
+      <c r="G80" s="45" t="n">
         <v>46329</v>
       </c>
       <c r="H80" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="I80" s="19" t="n">
+      <c r="I80" s="46" t="n">
         <v>1</v>
       </c>
       <c r="J80" s="17" t="inlineStr">
@@ -6020,16 +6157,16 @@
           <t>Wade</t>
         </is>
       </c>
-      <c r="F81" s="18" t="n">
+      <c r="F81" s="45" t="n">
         <v>46330</v>
       </c>
-      <c r="G81" s="18" t="n">
+      <c r="G81" s="45" t="n">
         <v>46331</v>
       </c>
       <c r="H81" s="15" t="n">
         <v>2</v>
       </c>
-      <c r="I81" s="19" t="n">
+      <c r="I81" s="46" t="n">
         <v>2</v>
       </c>
       <c r="J81" s="17" t="inlineStr">
@@ -6083,16 +6220,16 @@
           <t>Wade</t>
         </is>
       </c>
-      <c r="F82" s="18" t="n">
+      <c r="F82" s="45" t="n">
         <v>46332</v>
       </c>
-      <c r="G82" s="18" t="n">
+      <c r="G82" s="45" t="n">
         <v>46332</v>
       </c>
       <c r="H82" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="I82" s="19" t="n">
+      <c r="I82" s="46" t="n">
         <v>1</v>
       </c>
       <c r="J82" s="17" t="inlineStr">
@@ -6150,16 +6287,16 @@
           <t>Wade</t>
         </is>
       </c>
-      <c r="F83" s="18" t="n">
+      <c r="F83" s="45" t="n">
         <v>46335</v>
       </c>
-      <c r="G83" s="18" t="n">
+      <c r="G83" s="45" t="n">
         <v>46336</v>
       </c>
       <c r="H83" s="15" t="n">
         <v>2</v>
       </c>
-      <c r="I83" s="19" t="n">
+      <c r="I83" s="46" t="n">
         <v>2</v>
       </c>
       <c r="J83" s="17" t="inlineStr">
@@ -6213,16 +6350,16 @@
           <t>Wade</t>
         </is>
       </c>
-      <c r="F84" s="18" t="n">
+      <c r="F84" s="45" t="n">
         <v>46337</v>
       </c>
-      <c r="G84" s="18" t="n">
+      <c r="G84" s="45" t="n">
         <v>46337</v>
       </c>
       <c r="H84" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="I84" s="19" t="n">
+      <c r="I84" s="46" t="n">
         <v>0.5</v>
       </c>
       <c r="J84" s="17" t="inlineStr">
@@ -6276,16 +6413,16 @@
           <t>Wade</t>
         </is>
       </c>
-      <c r="F85" s="18" t="n">
+      <c r="F85" s="45" t="n">
         <v>46338</v>
       </c>
-      <c r="G85" s="18" t="n">
+      <c r="G85" s="45" t="n">
         <v>46339</v>
       </c>
       <c r="H85" s="15" t="n">
         <v>2</v>
       </c>
-      <c r="I85" s="19" t="n">
+      <c r="I85" s="46" t="n">
         <v>1.5</v>
       </c>
       <c r="J85" s="17" t="inlineStr">
@@ -6339,16 +6476,16 @@
           <t>DevB</t>
         </is>
       </c>
-      <c r="F86" s="18" t="n">
+      <c r="F86" s="45" t="n">
         <v>46321</v>
       </c>
-      <c r="G86" s="18" t="n">
+      <c r="G86" s="45" t="n">
         <v>46339</v>
       </c>
       <c r="H86" s="15" t="n">
         <v>15</v>
       </c>
-      <c r="I86" s="19">
+      <c r="I86" s="46">
         <f>ROUND(SUMPRODUCT(($C$87:$C$97=3)*(LEFT($A$87:$A$97,LEN(A86))=A86)*$I$87:$I$97),2)</f>
         <v/>
       </c>
@@ -6395,16 +6532,16 @@
           <t>DevB</t>
         </is>
       </c>
-      <c r="F87" s="18" t="n">
+      <c r="F87" s="45" t="n">
         <v>46321</v>
       </c>
-      <c r="G87" s="18" t="n">
+      <c r="G87" s="45" t="n">
         <v>46321</v>
       </c>
       <c r="H87" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="I87" s="19" t="n">
+      <c r="I87" s="46" t="n">
         <v>1</v>
       </c>
       <c r="J87" s="17" t="inlineStr">
@@ -6462,16 +6599,16 @@
           <t>DevB</t>
         </is>
       </c>
-      <c r="F88" s="18" t="n">
+      <c r="F88" s="45" t="n">
         <v>46322</v>
       </c>
-      <c r="G88" s="18" t="n">
+      <c r="G88" s="45" t="n">
         <v>46323</v>
       </c>
       <c r="H88" s="15" t="n">
         <v>2</v>
       </c>
-      <c r="I88" s="19" t="n">
+      <c r="I88" s="46" t="n">
         <v>2</v>
       </c>
       <c r="J88" s="17" t="inlineStr">
@@ -6525,16 +6662,16 @@
           <t>DevB</t>
         </is>
       </c>
-      <c r="F89" s="18" t="n">
+      <c r="F89" s="45" t="n">
         <v>46324</v>
       </c>
-      <c r="G89" s="18" t="n">
+      <c r="G89" s="45" t="n">
         <v>46325</v>
       </c>
       <c r="H89" s="15" t="n">
         <v>2</v>
       </c>
-      <c r="I89" s="19" t="n">
+      <c r="I89" s="46" t="n">
         <v>2</v>
       </c>
       <c r="J89" s="17" t="inlineStr">
@@ -6588,16 +6725,16 @@
           <t>DevB</t>
         </is>
       </c>
-      <c r="F90" s="18" t="n">
+      <c r="F90" s="45" t="n">
         <v>46328</v>
       </c>
-      <c r="G90" s="18" t="n">
+      <c r="G90" s="45" t="n">
         <v>46328</v>
       </c>
       <c r="H90" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="I90" s="19" t="n">
+      <c r="I90" s="46" t="n">
         <v>1</v>
       </c>
       <c r="J90" s="17" t="inlineStr">
@@ -6651,16 +6788,16 @@
           <t>DevB</t>
         </is>
       </c>
-      <c r="F91" s="18" t="n">
+      <c r="F91" s="45" t="n">
         <v>46329</v>
       </c>
-      <c r="G91" s="18" t="n">
+      <c r="G91" s="45" t="n">
         <v>46330</v>
       </c>
       <c r="H91" s="15" t="n">
         <v>2</v>
       </c>
-      <c r="I91" s="19" t="n">
+      <c r="I91" s="46" t="n">
         <v>2</v>
       </c>
       <c r="J91" s="17" t="inlineStr">
@@ -6714,16 +6851,16 @@
           <t>DevB</t>
         </is>
       </c>
-      <c r="F92" s="18" t="n">
+      <c r="F92" s="45" t="n">
         <v>46331</v>
       </c>
-      <c r="G92" s="18" t="n">
+      <c r="G92" s="45" t="n">
         <v>46331</v>
       </c>
       <c r="H92" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="I92" s="19" t="n">
+      <c r="I92" s="46" t="n">
         <v>1</v>
       </c>
       <c r="J92" s="17" t="inlineStr">
@@ -6777,16 +6914,16 @@
           <t>DevB</t>
         </is>
       </c>
-      <c r="F93" s="18" t="n">
+      <c r="F93" s="45" t="n">
         <v>46332</v>
       </c>
-      <c r="G93" s="18" t="n">
+      <c r="G93" s="45" t="n">
         <v>46332</v>
       </c>
       <c r="H93" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="I93" s="19" t="n">
+      <c r="I93" s="46" t="n">
         <v>1</v>
       </c>
       <c r="J93" s="17" t="inlineStr">
@@ -6840,16 +6977,16 @@
           <t>DevB</t>
         </is>
       </c>
-      <c r="F94" s="18" t="n">
+      <c r="F94" s="45" t="n">
         <v>46335</v>
       </c>
-      <c r="G94" s="18" t="n">
+      <c r="G94" s="45" t="n">
         <v>46335</v>
       </c>
       <c r="H94" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="I94" s="19" t="n">
+      <c r="I94" s="46" t="n">
         <v>1</v>
       </c>
       <c r="J94" s="17" t="inlineStr">
@@ -6903,16 +7040,16 @@
           <t>DevB</t>
         </is>
       </c>
-      <c r="F95" s="18" t="n">
+      <c r="F95" s="45" t="n">
         <v>46336</v>
       </c>
-      <c r="G95" s="18" t="n">
+      <c r="G95" s="45" t="n">
         <v>46336</v>
       </c>
       <c r="H95" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="I95" s="19" t="n">
+      <c r="I95" s="46" t="n">
         <v>1</v>
       </c>
       <c r="J95" s="17" t="inlineStr">
@@ -6970,16 +7107,16 @@
           <t>DevB</t>
         </is>
       </c>
-      <c r="F96" s="18" t="n">
+      <c r="F96" s="45" t="n">
         <v>46337</v>
       </c>
-      <c r="G96" s="18" t="n">
+      <c r="G96" s="45" t="n">
         <v>46337</v>
       </c>
       <c r="H96" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="I96" s="19" t="n">
+      <c r="I96" s="46" t="n">
         <v>1</v>
       </c>
       <c r="J96" s="17" t="inlineStr">
@@ -7033,16 +7170,16 @@
           <t>DevB</t>
         </is>
       </c>
-      <c r="F97" s="18" t="n">
+      <c r="F97" s="45" t="n">
         <v>46338</v>
       </c>
-      <c r="G97" s="18" t="n">
+      <c r="G97" s="45" t="n">
         <v>46339</v>
       </c>
       <c r="H97" s="15" t="n">
         <v>2</v>
       </c>
-      <c r="I97" s="19" t="n">
+      <c r="I97" s="46" t="n">
         <v>1.5</v>
       </c>
       <c r="J97" s="17" t="inlineStr">
@@ -7096,16 +7233,16 @@
           <t>Mandy</t>
         </is>
       </c>
-      <c r="F98" s="18" t="n">
+      <c r="F98" s="45" t="n">
         <v>46321</v>
       </c>
-      <c r="G98" s="18" t="n">
+      <c r="G98" s="45" t="n">
         <v>46339</v>
       </c>
       <c r="H98" s="15" t="n">
         <v>15</v>
       </c>
-      <c r="I98" s="19">
+      <c r="I98" s="46">
         <f>ROUND(SUMPRODUCT(($C$99:$C$111=3)*(LEFT($A$99:$A$111,LEN(A98))=A98)*$I$99:$I$111),2)</f>
         <v/>
       </c>
@@ -7156,16 +7293,16 @@
           <t>Mandy</t>
         </is>
       </c>
-      <c r="F99" s="18" t="n">
+      <c r="F99" s="45" t="n">
         <v>46321</v>
       </c>
-      <c r="G99" s="18" t="n">
+      <c r="G99" s="45" t="n">
         <v>46322</v>
       </c>
       <c r="H99" s="15" t="n">
         <v>2</v>
       </c>
-      <c r="I99" s="19" t="n">
+      <c r="I99" s="46" t="n">
         <v>1.5</v>
       </c>
       <c r="J99" s="17" t="inlineStr">
@@ -7219,16 +7356,16 @@
           <t>Mandy</t>
         </is>
       </c>
-      <c r="F100" s="18" t="n">
+      <c r="F100" s="45" t="n">
         <v>46323</v>
       </c>
-      <c r="G100" s="18" t="n">
+      <c r="G100" s="45" t="n">
         <v>46323</v>
       </c>
       <c r="H100" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="I100" s="19" t="n">
+      <c r="I100" s="46" t="n">
         <v>1</v>
       </c>
       <c r="J100" s="17" t="inlineStr">
@@ -7282,16 +7419,16 @@
           <t>Mandy</t>
         </is>
       </c>
-      <c r="F101" s="18" t="n">
+      <c r="F101" s="45" t="n">
         <v>46324</v>
       </c>
-      <c r="G101" s="18" t="n">
+      <c r="G101" s="45" t="n">
         <v>46324</v>
       </c>
       <c r="H101" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="I101" s="19" t="n">
+      <c r="I101" s="46" t="n">
         <v>0.5</v>
       </c>
       <c r="J101" s="17" t="inlineStr">
@@ -7345,16 +7482,16 @@
           <t>Mandy</t>
         </is>
       </c>
-      <c r="F102" s="18" t="n">
+      <c r="F102" s="45" t="n">
         <v>46325</v>
       </c>
-      <c r="G102" s="18" t="n">
+      <c r="G102" s="45" t="n">
         <v>46325</v>
       </c>
       <c r="H102" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="I102" s="19" t="n">
+      <c r="I102" s="46" t="n">
         <v>1</v>
       </c>
       <c r="J102" s="17" t="inlineStr">
@@ -7408,16 +7545,16 @@
           <t>Mandy</t>
         </is>
       </c>
-      <c r="F103" s="18" t="n">
+      <c r="F103" s="45" t="n">
         <v>46328</v>
       </c>
-      <c r="G103" s="18" t="n">
+      <c r="G103" s="45" t="n">
         <v>46328</v>
       </c>
       <c r="H103" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="I103" s="19" t="n">
+      <c r="I103" s="46" t="n">
         <v>1</v>
       </c>
       <c r="J103" s="17" t="inlineStr">
@@ -7471,16 +7608,16 @@
           <t>Mandy</t>
         </is>
       </c>
-      <c r="F104" s="18" t="n">
+      <c r="F104" s="45" t="n">
         <v>46329</v>
       </c>
-      <c r="G104" s="18" t="n">
+      <c r="G104" s="45" t="n">
         <v>46329</v>
       </c>
       <c r="H104" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="I104" s="19" t="n">
+      <c r="I104" s="46" t="n">
         <v>1</v>
       </c>
       <c r="J104" s="17" t="inlineStr">
@@ -7534,16 +7671,16 @@
           <t>Mandy</t>
         </is>
       </c>
-      <c r="F105" s="18" t="n">
+      <c r="F105" s="45" t="n">
         <v>46330</v>
       </c>
-      <c r="G105" s="18" t="n">
+      <c r="G105" s="45" t="n">
         <v>46330</v>
       </c>
       <c r="H105" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="I105" s="19" t="n">
+      <c r="I105" s="46" t="n">
         <v>0.5</v>
       </c>
       <c r="J105" s="17" t="inlineStr">
@@ -7597,16 +7734,16 @@
           <t>Mandy</t>
         </is>
       </c>
-      <c r="F106" s="18" t="n">
+      <c r="F106" s="45" t="n">
         <v>46331</v>
       </c>
-      <c r="G106" s="18" t="n">
+      <c r="G106" s="45" t="n">
         <v>46331</v>
       </c>
       <c r="H106" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="I106" s="19" t="n">
+      <c r="I106" s="46" t="n">
         <v>1</v>
       </c>
       <c r="J106" s="17" t="inlineStr">
@@ -7660,16 +7797,16 @@
           <t>Mandy</t>
         </is>
       </c>
-      <c r="F107" s="18" t="n">
+      <c r="F107" s="45" t="n">
         <v>46332</v>
       </c>
-      <c r="G107" s="18" t="n">
+      <c r="G107" s="45" t="n">
         <v>46332</v>
       </c>
       <c r="H107" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="I107" s="19" t="n">
+      <c r="I107" s="46" t="n">
         <v>1</v>
       </c>
       <c r="J107" s="17" t="inlineStr">
@@ -7723,16 +7860,16 @@
           <t>Mandy</t>
         </is>
       </c>
-      <c r="F108" s="18" t="n">
+      <c r="F108" s="45" t="n">
         <v>46335</v>
       </c>
-      <c r="G108" s="18" t="n">
+      <c r="G108" s="45" t="n">
         <v>46336</v>
       </c>
       <c r="H108" s="15" t="n">
         <v>2</v>
       </c>
-      <c r="I108" s="19" t="n">
+      <c r="I108" s="46" t="n">
         <v>1</v>
       </c>
       <c r="J108" s="17" t="inlineStr">
@@ -7786,16 +7923,16 @@
           <t>Mandy</t>
         </is>
       </c>
-      <c r="F109" s="18" t="n">
+      <c r="F109" s="45" t="n">
         <v>46337</v>
       </c>
-      <c r="G109" s="18" t="n">
+      <c r="G109" s="45" t="n">
         <v>46337</v>
       </c>
       <c r="H109" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="I109" s="19" t="n">
+      <c r="I109" s="46" t="n">
         <v>1</v>
       </c>
       <c r="J109" s="17" t="inlineStr">
@@ -7853,16 +7990,16 @@
           <t>Mandy</t>
         </is>
       </c>
-      <c r="F110" s="18" t="n">
+      <c r="F110" s="45" t="n">
         <v>46338</v>
       </c>
-      <c r="G110" s="18" t="n">
+      <c r="G110" s="45" t="n">
         <v>46338</v>
       </c>
       <c r="H110" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="I110" s="19" t="n">
+      <c r="I110" s="46" t="n">
         <v>1</v>
       </c>
       <c r="J110" s="17" t="inlineStr">
@@ -7916,16 +8053,16 @@
           <t>Mandy</t>
         </is>
       </c>
-      <c r="F111" s="18" t="n">
+      <c r="F111" s="45" t="n">
         <v>46336</v>
       </c>
-      <c r="G111" s="18" t="n">
+      <c r="G111" s="45" t="n">
         <v>46339</v>
       </c>
       <c r="H111" s="15" t="n">
         <v>4</v>
       </c>
-      <c r="I111" s="19" t="n">
+      <c r="I111" s="46" t="n">
         <v>0.5</v>
       </c>
       <c r="J111" s="17" t="inlineStr"/>
@@ -7979,16 +8116,16 @@
           <t>Wade/Mandy</t>
         </is>
       </c>
-      <c r="F112" s="18" t="n">
+      <c r="F112" s="45" t="n">
         <v>46321</v>
       </c>
-      <c r="G112" s="18" t="n">
+      <c r="G112" s="45" t="n">
         <v>46339</v>
       </c>
       <c r="H112" s="15" t="n">
         <v>15</v>
       </c>
-      <c r="I112" s="19">
+      <c r="I112" s="46">
         <f>ROUND(SUMPRODUCT(($C$113:$C$114=3)*(LEFT($A$113:$A$114,LEN(A112))=A112)*$I$113:$I$114),2)</f>
         <v/>
       </c>
@@ -8039,16 +8176,16 @@
           <t>Wade</t>
         </is>
       </c>
-      <c r="F113" s="18" t="n">
+      <c r="F113" s="45" t="n">
         <v>46337</v>
       </c>
-      <c r="G113" s="18" t="n">
+      <c r="G113" s="45" t="n">
         <v>46337</v>
       </c>
       <c r="H113" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="I113" s="19" t="n">
+      <c r="I113" s="46" t="n">
         <v>0.5</v>
       </c>
       <c r="J113" s="17" t="inlineStr">
@@ -8106,16 +8243,16 @@
           <t>Mandy</t>
         </is>
       </c>
-      <c r="F114" s="26" t="n">
+      <c r="F114" s="47" t="n">
         <v>46339</v>
       </c>
-      <c r="G114" s="26" t="n">
+      <c r="G114" s="47" t="n">
         <v>46339</v>
       </c>
       <c r="H114" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="I114" s="27" t="n">
+      <c r="I114" s="48" t="n">
         <v>0.5</v>
       </c>
       <c r="J114" s="25" t="inlineStr">
@@ -8173,16 +8310,16 @@
           <t>Wade/DevB/Mandy</t>
         </is>
       </c>
-      <c r="F115" s="11" t="n">
+      <c r="F115" s="43" t="n">
         <v>46342</v>
       </c>
-      <c r="G115" s="11" t="n">
+      <c r="G115" s="43" t="n">
         <v>46357</v>
       </c>
       <c r="H115" s="8" t="n">
         <v>12</v>
       </c>
-      <c r="I115" s="12">
+      <c r="I115" s="44">
         <f>ROUND(SUMPRODUCT(($C$116:$C$135=3)*(LEFT($A$116:$A$135,LEN(A115))=A115)*$I$116:$I$135),2)</f>
         <v/>
       </c>
@@ -8233,16 +8370,16 @@
           <t>Wade</t>
         </is>
       </c>
-      <c r="F116" s="18" t="n">
+      <c r="F116" s="45" t="n">
         <v>46342</v>
       </c>
-      <c r="G116" s="18" t="n">
+      <c r="G116" s="45" t="n">
         <v>46357</v>
       </c>
       <c r="H116" s="15" t="n">
         <v>12</v>
       </c>
-      <c r="I116" s="19">
+      <c r="I116" s="46">
         <f>ROUND(SUMPRODUCT(($C$117:$C$122=3)*(LEFT($A$117:$A$122,LEN(A116))=A116)*$I$117:$I$122),2)</f>
         <v/>
       </c>
@@ -8289,16 +8426,16 @@
           <t>Wade</t>
         </is>
       </c>
-      <c r="F117" s="18" t="n">
+      <c r="F117" s="45" t="n">
         <v>46342</v>
       </c>
-      <c r="G117" s="18" t="n">
+      <c r="G117" s="45" t="n">
         <v>46343</v>
       </c>
       <c r="H117" s="15" t="n">
         <v>2</v>
       </c>
-      <c r="I117" s="19" t="n">
+      <c r="I117" s="46" t="n">
         <v>2</v>
       </c>
       <c r="J117" s="17" t="inlineStr">
@@ -8356,16 +8493,16 @@
           <t>Wade</t>
         </is>
       </c>
-      <c r="F118" s="18" t="n">
+      <c r="F118" s="45" t="n">
         <v>46344</v>
       </c>
-      <c r="G118" s="18" t="n">
+      <c r="G118" s="45" t="n">
         <v>46346</v>
       </c>
       <c r="H118" s="15" t="n">
         <v>3</v>
       </c>
-      <c r="I118" s="19" t="n">
+      <c r="I118" s="46" t="n">
         <v>3</v>
       </c>
       <c r="J118" s="17" t="inlineStr">
@@ -8419,16 +8556,16 @@
           <t>Wade</t>
         </is>
       </c>
-      <c r="F119" s="18" t="n">
+      <c r="F119" s="45" t="n">
         <v>46349</v>
       </c>
-      <c r="G119" s="18" t="n">
+      <c r="G119" s="45" t="n">
         <v>46349</v>
       </c>
       <c r="H119" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="I119" s="19" t="n">
+      <c r="I119" s="46" t="n">
         <v>1</v>
       </c>
       <c r="J119" s="17" t="inlineStr">
@@ -8482,16 +8619,16 @@
           <t>Wade</t>
         </is>
       </c>
-      <c r="F120" s="18" t="n">
+      <c r="F120" s="45" t="n">
         <v>46350</v>
       </c>
-      <c r="G120" s="18" t="n">
+      <c r="G120" s="45" t="n">
         <v>46351</v>
       </c>
       <c r="H120" s="15" t="n">
         <v>2</v>
       </c>
-      <c r="I120" s="19" t="n">
+      <c r="I120" s="46" t="n">
         <v>2</v>
       </c>
       <c r="J120" s="17" t="inlineStr">
@@ -8545,16 +8682,16 @@
           <t>Wade</t>
         </is>
       </c>
-      <c r="F121" s="18" t="n">
+      <c r="F121" s="45" t="n">
         <v>46352</v>
       </c>
-      <c r="G121" s="18" t="n">
+      <c r="G121" s="45" t="n">
         <v>46353</v>
       </c>
       <c r="H121" s="15" t="n">
         <v>2</v>
       </c>
-      <c r="I121" s="19" t="n">
+      <c r="I121" s="46" t="n">
         <v>2</v>
       </c>
       <c r="J121" s="17" t="inlineStr">
@@ -8608,16 +8745,16 @@
           <t>Wade</t>
         </is>
       </c>
-      <c r="F122" s="26" t="n">
+      <c r="F122" s="47" t="n">
         <v>46357</v>
       </c>
-      <c r="G122" s="26" t="n">
+      <c r="G122" s="47" t="n">
         <v>46357</v>
       </c>
       <c r="H122" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="I122" s="27" t="n">
+      <c r="I122" s="48" t="n">
         <v>1</v>
       </c>
       <c r="J122" s="25" t="inlineStr">
@@ -8675,16 +8812,16 @@
           <t>DevB</t>
         </is>
       </c>
-      <c r="F123" s="18" t="n">
+      <c r="F123" s="45" t="n">
         <v>46342</v>
       </c>
-      <c r="G123" s="18" t="n">
+      <c r="G123" s="45" t="n">
         <v>46357</v>
       </c>
       <c r="H123" s="15" t="n">
         <v>12</v>
       </c>
-      <c r="I123" s="19">
+      <c r="I123" s="46">
         <f>ROUND(SUMPRODUCT(($C$124:$C$129=3)*(LEFT($A$124:$A$129,LEN(A123))=A123)*$I$124:$I$129),2)</f>
         <v/>
       </c>
@@ -8731,16 +8868,16 @@
           <t>DevB</t>
         </is>
       </c>
-      <c r="F124" s="18" t="n">
+      <c r="F124" s="45" t="n">
         <v>46342</v>
       </c>
-      <c r="G124" s="18" t="n">
+      <c r="G124" s="45" t="n">
         <v>46345</v>
       </c>
       <c r="H124" s="15" t="n">
         <v>4</v>
       </c>
-      <c r="I124" s="19" t="n">
+      <c r="I124" s="46" t="n">
         <v>3.5</v>
       </c>
       <c r="J124" s="17" t="inlineStr">
@@ -8798,16 +8935,16 @@
           <t>DevB</t>
         </is>
       </c>
-      <c r="F125" s="18" t="n">
+      <c r="F125" s="45" t="n">
         <v>46346</v>
       </c>
-      <c r="G125" s="18" t="n">
+      <c r="G125" s="45" t="n">
         <v>46350</v>
       </c>
       <c r="H125" s="15" t="n">
         <v>3</v>
       </c>
-      <c r="I125" s="19" t="n">
+      <c r="I125" s="46" t="n">
         <v>2.5</v>
       </c>
       <c r="J125" s="17" t="inlineStr">
@@ -8861,16 +8998,16 @@
           <t>DevB</t>
         </is>
       </c>
-      <c r="F126" s="18" t="n">
+      <c r="F126" s="45" t="n">
         <v>46351</v>
       </c>
-      <c r="G126" s="18" t="n">
+      <c r="G126" s="45" t="n">
         <v>46351</v>
       </c>
       <c r="H126" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="I126" s="19" t="n">
+      <c r="I126" s="46" t="n">
         <v>1</v>
       </c>
       <c r="J126" s="17" t="inlineStr">
@@ -8928,16 +9065,16 @@
           <t>DevB</t>
         </is>
       </c>
-      <c r="F127" s="18" t="n">
+      <c r="F127" s="45" t="n">
         <v>46352</v>
       </c>
-      <c r="G127" s="18" t="n">
+      <c r="G127" s="45" t="n">
         <v>46353</v>
       </c>
       <c r="H127" s="15" t="n">
         <v>2</v>
       </c>
-      <c r="I127" s="19" t="n">
+      <c r="I127" s="46" t="n">
         <v>2</v>
       </c>
       <c r="J127" s="17" t="inlineStr">
@@ -8991,16 +9128,16 @@
           <t>DevB</t>
         </is>
       </c>
-      <c r="F128" s="18" t="n">
+      <c r="F128" s="45" t="n">
         <v>46356</v>
       </c>
-      <c r="G128" s="18" t="n">
+      <c r="G128" s="45" t="n">
         <v>46356</v>
       </c>
       <c r="H128" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="I128" s="19" t="n">
+      <c r="I128" s="46" t="n">
         <v>1</v>
       </c>
       <c r="J128" s="17" t="inlineStr">
@@ -9054,16 +9191,16 @@
           <t>DevB</t>
         </is>
       </c>
-      <c r="F129" s="26" t="n">
+      <c r="F129" s="47" t="n">
         <v>46357</v>
       </c>
-      <c r="G129" s="26" t="n">
+      <c r="G129" s="47" t="n">
         <v>46357</v>
       </c>
       <c r="H129" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="I129" s="27" t="n">
+      <c r="I129" s="48" t="n">
         <v>1</v>
       </c>
       <c r="J129" s="25" t="inlineStr">
@@ -9121,16 +9258,16 @@
           <t>Mandy</t>
         </is>
       </c>
-      <c r="F130" s="18" t="n">
+      <c r="F130" s="45" t="n">
         <v>46342</v>
       </c>
-      <c r="G130" s="18" t="n">
+      <c r="G130" s="45" t="n">
         <v>46353</v>
       </c>
       <c r="H130" s="15" t="n">
         <v>10</v>
       </c>
-      <c r="I130" s="19">
+      <c r="I130" s="46">
         <f>ROUND(SUMPRODUCT(($C$131:$C$135=3)*(LEFT($A$131:$A$135,LEN(A130))=A130)*$I$131:$I$135),2)</f>
         <v/>
       </c>
@@ -9177,16 +9314,16 @@
           <t>Mandy</t>
         </is>
       </c>
-      <c r="F131" s="18" t="n">
+      <c r="F131" s="45" t="n">
         <v>46342</v>
       </c>
-      <c r="G131" s="18" t="n">
+      <c r="G131" s="45" t="n">
         <v>46343</v>
       </c>
       <c r="H131" s="15" t="n">
         <v>2</v>
       </c>
-      <c r="I131" s="19" t="n">
+      <c r="I131" s="46" t="n">
         <v>2</v>
       </c>
       <c r="J131" s="17" t="inlineStr">
@@ -9240,16 +9377,16 @@
           <t>Mandy</t>
         </is>
       </c>
-      <c r="F132" s="18" t="n">
+      <c r="F132" s="45" t="n">
         <v>46344</v>
       </c>
-      <c r="G132" s="18" t="n">
+      <c r="G132" s="45" t="n">
         <v>46346</v>
       </c>
       <c r="H132" s="15" t="n">
         <v>3</v>
       </c>
-      <c r="I132" s="19" t="n">
+      <c r="I132" s="46" t="n">
         <v>3</v>
       </c>
       <c r="J132" s="17" t="inlineStr">
@@ -9307,16 +9444,16 @@
           <t>Mandy</t>
         </is>
       </c>
-      <c r="F133" s="18" t="n">
+      <c r="F133" s="45" t="n">
         <v>46349</v>
       </c>
-      <c r="G133" s="18" t="n">
+      <c r="G133" s="45" t="n">
         <v>46350</v>
       </c>
       <c r="H133" s="15" t="n">
         <v>2</v>
       </c>
-      <c r="I133" s="19" t="n">
+      <c r="I133" s="46" t="n">
         <v>1.5</v>
       </c>
       <c r="J133" s="17" t="inlineStr">
@@ -9370,16 +9507,16 @@
           <t>Mandy</t>
         </is>
       </c>
-      <c r="F134" s="18" t="n">
+      <c r="F134" s="45" t="n">
         <v>46351</v>
       </c>
-      <c r="G134" s="18" t="n">
+      <c r="G134" s="45" t="n">
         <v>46351</v>
       </c>
       <c r="H134" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="I134" s="19" t="n">
+      <c r="I134" s="46" t="n">
         <v>1</v>
       </c>
       <c r="J134" s="17" t="inlineStr">
@@ -9437,16 +9574,16 @@
           <t>Mandy</t>
         </is>
       </c>
-      <c r="F135" s="18" t="n">
+      <c r="F135" s="45" t="n">
         <v>46352</v>
       </c>
-      <c r="G135" s="18" t="n">
+      <c r="G135" s="45" t="n">
         <v>46353</v>
       </c>
       <c r="H135" s="15" t="n">
         <v>2</v>
       </c>
-      <c r="I135" s="19" t="n">
+      <c r="I135" s="46" t="n">
         <v>1</v>
       </c>
       <c r="J135" s="17" t="inlineStr">
@@ -9500,16 +9637,16 @@
           <t>Mandy/Wade/DevB</t>
         </is>
       </c>
-      <c r="F136" s="11" t="n">
+      <c r="F136" s="43" t="n">
         <v>46358</v>
       </c>
-      <c r="G136" s="11" t="n">
+      <c r="G136" s="43" t="n">
         <v>46365</v>
       </c>
       <c r="H136" s="8" t="n">
         <v>6</v>
       </c>
-      <c r="I136" s="12">
+      <c r="I136" s="44">
         <f>ROUND(SUMPRODUCT(($C$137:$C$150=3)*(LEFT($A$137:$A$150,LEN(A136))=A136)*$I$137:$I$150),2)</f>
         <v/>
       </c>
@@ -9560,16 +9697,16 @@
           <t>Mandy</t>
         </is>
       </c>
-      <c r="F137" s="18" t="n">
+      <c r="F137" s="45" t="n">
         <v>46358</v>
       </c>
-      <c r="G137" s="18" t="n">
+      <c r="G137" s="45" t="n">
         <v>46364</v>
       </c>
       <c r="H137" s="15" t="n">
         <v>5</v>
       </c>
-      <c r="I137" s="19">
+      <c r="I137" s="46">
         <f>ROUND(SUMPRODUCT(($C$138:$C$141=3)*(LEFT($A$138:$A$141,LEN(A137))=A137)*$I$138:$I$141),2)</f>
         <v/>
       </c>
@@ -9616,16 +9753,16 @@
           <t>Mandy</t>
         </is>
       </c>
-      <c r="F138" s="18" t="n">
+      <c r="F138" s="45" t="n">
         <v>46358</v>
       </c>
-      <c r="G138" s="18" t="n">
+      <c r="G138" s="45" t="n">
         <v>46359</v>
       </c>
       <c r="H138" s="15" t="n">
         <v>2</v>
       </c>
-      <c r="I138" s="19" t="n">
+      <c r="I138" s="46" t="n">
         <v>2</v>
       </c>
       <c r="J138" s="17" t="inlineStr">
@@ -9683,16 +9820,16 @@
           <t>Mandy</t>
         </is>
       </c>
-      <c r="F139" s="18" t="n">
+      <c r="F139" s="45" t="n">
         <v>46360</v>
       </c>
-      <c r="G139" s="18" t="n">
+      <c r="G139" s="45" t="n">
         <v>46360</v>
       </c>
       <c r="H139" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="I139" s="19" t="n">
+      <c r="I139" s="46" t="n">
         <v>1</v>
       </c>
       <c r="J139" s="17" t="inlineStr">
@@ -9746,16 +9883,16 @@
           <t>Mandy</t>
         </is>
       </c>
-      <c r="F140" s="26" t="n">
+      <c r="F140" s="47" t="n">
         <v>46363</v>
       </c>
-      <c r="G140" s="26" t="n">
+      <c r="G140" s="47" t="n">
         <v>46363</v>
       </c>
       <c r="H140" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="I140" s="27" t="n">
+      <c r="I140" s="48" t="n">
         <v>1</v>
       </c>
       <c r="J140" s="25" t="inlineStr">
@@ -9813,16 +9950,16 @@
           <t>Mandy</t>
         </is>
       </c>
-      <c r="F141" s="18" t="n">
+      <c r="F141" s="45" t="n">
         <v>46364</v>
       </c>
-      <c r="G141" s="18" t="n">
+      <c r="G141" s="45" t="n">
         <v>46364</v>
       </c>
       <c r="H141" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="I141" s="19" t="n">
+      <c r="I141" s="46" t="n">
         <v>1</v>
       </c>
       <c r="J141" s="17" t="inlineStr">
@@ -9880,16 +10017,16 @@
           <t>Wade/DevB</t>
         </is>
       </c>
-      <c r="F142" s="18" t="n">
+      <c r="F142" s="45" t="n">
         <v>46358</v>
       </c>
-      <c r="G142" s="18" t="n">
+      <c r="G142" s="45" t="n">
         <v>46365</v>
       </c>
       <c r="H142" s="15" t="n">
         <v>6</v>
       </c>
-      <c r="I142" s="19">
+      <c r="I142" s="46">
         <f>ROUND(SUMPRODUCT(($C$143:$C$150=3)*(LEFT($A$143:$A$150,LEN(A142))=A142)*$I$143:$I$150),2)</f>
         <v/>
       </c>
@@ -9936,16 +10073,16 @@
           <t>Wade</t>
         </is>
       </c>
-      <c r="F143" s="18" t="n">
+      <c r="F143" s="45" t="n">
         <v>46358</v>
       </c>
-      <c r="G143" s="18" t="n">
+      <c r="G143" s="45" t="n">
         <v>46358</v>
       </c>
       <c r="H143" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="I143" s="19" t="n">
+      <c r="I143" s="46" t="n">
         <v>1</v>
       </c>
       <c r="J143" s="17" t="inlineStr">
@@ -9999,16 +10136,16 @@
           <t>Wade</t>
         </is>
       </c>
-      <c r="F144" s="18" t="n">
+      <c r="F144" s="45" t="n">
         <v>46359</v>
       </c>
-      <c r="G144" s="18" t="n">
+      <c r="G144" s="45" t="n">
         <v>46360</v>
       </c>
       <c r="H144" s="15" t="n">
         <v>2</v>
       </c>
-      <c r="I144" s="19" t="n">
+      <c r="I144" s="46" t="n">
         <v>2</v>
       </c>
       <c r="J144" s="17" t="inlineStr">
@@ -10062,16 +10199,16 @@
           <t>Wade</t>
         </is>
       </c>
-      <c r="F145" s="18" t="n">
+      <c r="F145" s="45" t="n">
         <v>46363</v>
       </c>
-      <c r="G145" s="18" t="n">
+      <c r="G145" s="45" t="n">
         <v>46364</v>
       </c>
       <c r="H145" s="15" t="n">
         <v>2</v>
       </c>
-      <c r="I145" s="19" t="n">
+      <c r="I145" s="46" t="n">
         <v>2</v>
       </c>
       <c r="J145" s="17" t="inlineStr">
@@ -10129,16 +10266,16 @@
           <t>DevB</t>
         </is>
       </c>
-      <c r="F146" s="18" t="n">
+      <c r="F146" s="45" t="n">
         <v>46358</v>
       </c>
-      <c r="G146" s="18" t="n">
+      <c r="G146" s="45" t="n">
         <v>46358</v>
       </c>
       <c r="H146" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="I146" s="19" t="n">
+      <c r="I146" s="46" t="n">
         <v>1</v>
       </c>
       <c r="J146" s="17" t="inlineStr">
@@ -10192,16 +10329,16 @@
           <t>DevB</t>
         </is>
       </c>
-      <c r="F147" s="18" t="n">
+      <c r="F147" s="45" t="n">
         <v>46359</v>
       </c>
-      <c r="G147" s="18" t="n">
+      <c r="G147" s="45" t="n">
         <v>46360</v>
       </c>
       <c r="H147" s="15" t="n">
         <v>2</v>
       </c>
-      <c r="I147" s="19" t="n">
+      <c r="I147" s="46" t="n">
         <v>2</v>
       </c>
       <c r="J147" s="17" t="inlineStr">
@@ -10255,16 +10392,16 @@
           <t>DevB</t>
         </is>
       </c>
-      <c r="F148" s="18" t="n">
+      <c r="F148" s="45" t="n">
         <v>46363</v>
       </c>
-      <c r="G148" s="18" t="n">
+      <c r="G148" s="45" t="n">
         <v>46364</v>
       </c>
       <c r="H148" s="15" t="n">
         <v>2</v>
       </c>
-      <c r="I148" s="19" t="n">
+      <c r="I148" s="46" t="n">
         <v>1.5</v>
       </c>
       <c r="J148" s="17" t="inlineStr">
@@ -10318,16 +10455,16 @@
           <t>Wade</t>
         </is>
       </c>
-      <c r="F149" s="26" t="n">
+      <c r="F149" s="47" t="n">
         <v>46365</v>
       </c>
-      <c r="G149" s="26" t="n">
+      <c r="G149" s="47" t="n">
         <v>46365</v>
       </c>
       <c r="H149" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="I149" s="27" t="n">
+      <c r="I149" s="48" t="n">
         <v>1</v>
       </c>
       <c r="J149" s="25" t="inlineStr">
@@ -10385,16 +10522,16 @@
           <t>DevB</t>
         </is>
       </c>
-      <c r="F150" s="18" t="n">
+      <c r="F150" s="45" t="n">
         <v>46365</v>
       </c>
-      <c r="G150" s="18" t="n">
+      <c r="G150" s="45" t="n">
         <v>46365</v>
       </c>
       <c r="H150" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="I150" s="19" t="n">
+      <c r="I150" s="46" t="n">
         <v>1</v>
       </c>
       <c r="J150" s="17" t="inlineStr">
@@ -10452,16 +10589,16 @@
           <t>全员</t>
         </is>
       </c>
-      <c r="F151" s="11" t="n">
+      <c r="F151" s="43" t="n">
         <v>46366</v>
       </c>
-      <c r="G151" s="11" t="n">
+      <c r="G151" s="43" t="n">
         <v>46372</v>
       </c>
       <c r="H151" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="I151" s="12">
+      <c r="I151" s="44">
         <f>ROUND(SUMPRODUCT(($C$152:$C$164=3)*(LEFT($A$152:$A$164,LEN(A151))=A151)*$I$152:$I$164),2)</f>
         <v/>
       </c>
@@ -10512,16 +10649,16 @@
           <t>Wade/DevB</t>
         </is>
       </c>
-      <c r="F152" s="18" t="n">
+      <c r="F152" s="45" t="n">
         <v>46366</v>
       </c>
-      <c r="G152" s="18" t="n">
+      <c r="G152" s="45" t="n">
         <v>46371</v>
       </c>
       <c r="H152" s="15" t="n">
         <v>4</v>
       </c>
-      <c r="I152" s="19">
+      <c r="I152" s="46">
         <f>ROUND(SUMPRODUCT(($C$153:$C$156=3)*(LEFT($A$153:$A$156,LEN(A152))=A152)*$I$153:$I$156),2)</f>
         <v/>
       </c>
@@ -10572,16 +10709,16 @@
           <t>Wade</t>
         </is>
       </c>
-      <c r="F153" s="18" t="n">
+      <c r="F153" s="45" t="n">
         <v>46366</v>
       </c>
-      <c r="G153" s="18" t="n">
+      <c r="G153" s="45" t="n">
         <v>46366</v>
       </c>
       <c r="H153" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="I153" s="19" t="n">
+      <c r="I153" s="46" t="n">
         <v>1</v>
       </c>
       <c r="J153" s="17" t="inlineStr">
@@ -10639,16 +10776,16 @@
           <t>DevB</t>
         </is>
       </c>
-      <c r="F154" s="18" t="n">
+      <c r="F154" s="45" t="n">
         <v>46366</v>
       </c>
-      <c r="G154" s="18" t="n">
+      <c r="G154" s="45" t="n">
         <v>46370</v>
       </c>
       <c r="H154" s="15" t="n">
         <v>3</v>
       </c>
-      <c r="I154" s="19" t="n">
+      <c r="I154" s="46" t="n">
         <v>3</v>
       </c>
       <c r="J154" s="17" t="inlineStr">
@@ -10706,16 +10843,16 @@
           <t>DevB</t>
         </is>
       </c>
-      <c r="F155" s="18" t="n">
+      <c r="F155" s="45" t="n">
         <v>46371</v>
       </c>
-      <c r="G155" s="18" t="n">
+      <c r="G155" s="45" t="n">
         <v>46371</v>
       </c>
       <c r="H155" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="I155" s="19" t="n">
+      <c r="I155" s="46" t="n">
         <v>1</v>
       </c>
       <c r="J155" s="17" t="inlineStr">
@@ -10773,16 +10910,16 @@
           <t>Wade</t>
         </is>
       </c>
-      <c r="F156" s="18" t="n">
+      <c r="F156" s="45" t="n">
         <v>46367</v>
       </c>
-      <c r="G156" s="18" t="n">
+      <c r="G156" s="45" t="n">
         <v>46367</v>
       </c>
       <c r="H156" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="I156" s="19" t="n">
+      <c r="I156" s="46" t="n">
         <v>1</v>
       </c>
       <c r="J156" s="17" t="inlineStr">
@@ -10836,16 +10973,16 @@
           <t>全员</t>
         </is>
       </c>
-      <c r="F157" s="18" t="n">
+      <c r="F157" s="45" t="n">
         <v>46366</v>
       </c>
-      <c r="G157" s="18" t="n">
+      <c r="G157" s="45" t="n">
         <v>46372</v>
       </c>
       <c r="H157" s="15" t="n">
         <v>5</v>
       </c>
-      <c r="I157" s="19">
+      <c r="I157" s="46">
         <f>ROUND(SUMPRODUCT(($C$158:$C$164=3)*(LEFT($A$158:$A$164,LEN(A157))=A157)*$I$158:$I$164),2)</f>
         <v/>
       </c>
@@ -10892,16 +11029,16 @@
           <t>Mandy</t>
         </is>
       </c>
-      <c r="F158" s="18" t="n">
+      <c r="F158" s="45" t="n">
         <v>46366</v>
       </c>
-      <c r="G158" s="18" t="n">
+      <c r="G158" s="45" t="n">
         <v>46366</v>
       </c>
       <c r="H158" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="I158" s="19" t="n">
+      <c r="I158" s="46" t="n">
         <v>0.5</v>
       </c>
       <c r="J158" s="17" t="inlineStr">
@@ -10955,16 +11092,16 @@
           <t>Mandy</t>
         </is>
       </c>
-      <c r="F159" s="18" t="n">
+      <c r="F159" s="45" t="n">
         <v>46367</v>
       </c>
-      <c r="G159" s="18" t="n">
+      <c r="G159" s="45" t="n">
         <v>46367</v>
       </c>
       <c r="H159" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="I159" s="19" t="n">
+      <c r="I159" s="46" t="n">
         <v>1</v>
       </c>
       <c r="J159" s="17" t="inlineStr">
@@ -11018,16 +11155,16 @@
           <t>Mandy</t>
         </is>
       </c>
-      <c r="F160" s="18" t="n">
+      <c r="F160" s="45" t="n">
         <v>46370</v>
       </c>
-      <c r="G160" s="18" t="n">
+      <c r="G160" s="45" t="n">
         <v>46371</v>
       </c>
       <c r="H160" s="15" t="n">
         <v>2</v>
       </c>
-      <c r="I160" s="19" t="n">
+      <c r="I160" s="46" t="n">
         <v>1</v>
       </c>
       <c r="J160" s="17" t="inlineStr">
@@ -11085,16 +11222,16 @@
           <t>Mandy</t>
         </is>
       </c>
-      <c r="F161" s="18" t="n">
+      <c r="F161" s="45" t="n">
         <v>46372</v>
       </c>
-      <c r="G161" s="18" t="n">
+      <c r="G161" s="45" t="n">
         <v>46372</v>
       </c>
       <c r="H161" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="I161" s="19" t="n">
+      <c r="I161" s="46" t="n">
         <v>1</v>
       </c>
       <c r="J161" s="17" t="inlineStr">
@@ -11148,16 +11285,16 @@
           <t>Wade</t>
         </is>
       </c>
-      <c r="F162" s="18" t="n">
+      <c r="F162" s="45" t="n">
         <v>46370</v>
       </c>
-      <c r="G162" s="18" t="n">
+      <c r="G162" s="45" t="n">
         <v>46372</v>
       </c>
       <c r="H162" s="15" t="n">
         <v>3</v>
       </c>
-      <c r="I162" s="19" t="n">
+      <c r="I162" s="46" t="n">
         <v>3</v>
       </c>
       <c r="J162" s="17" t="inlineStr">
@@ -11215,16 +11352,16 @@
           <t>DevB</t>
         </is>
       </c>
-      <c r="F163" s="18" t="n">
+      <c r="F163" s="45" t="n">
         <v>46372</v>
       </c>
-      <c r="G163" s="18" t="n">
+      <c r="G163" s="45" t="n">
         <v>46372</v>
       </c>
       <c r="H163" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="I163" s="19" t="n">
+      <c r="I163" s="46" t="n">
         <v>1</v>
       </c>
       <c r="J163" s="17" t="inlineStr">
@@ -11278,16 +11415,16 @@
           <t>Mark</t>
         </is>
       </c>
-      <c r="F164" s="26" t="n">
+      <c r="F164" s="47" t="n">
         <v>46372</v>
       </c>
-      <c r="G164" s="26" t="n">
+      <c r="G164" s="47" t="n">
         <v>46372</v>
       </c>
       <c r="H164" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="I164" s="27" t="n">
+      <c r="I164" s="48" t="n">
         <v>0</v>
       </c>
       <c r="J164" s="25" t="inlineStr">
@@ -12968,6 +13105,2483 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="00C00000"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:P39"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
+    <col width="7" customWidth="1" min="5" max="5"/>
+    <col width="24" customWidth="1" min="6" max="6"/>
+    <col width="7" customWidth="1" min="7" max="7"/>
+    <col width="24" customWidth="1" min="8" max="8"/>
+    <col width="7" customWidth="1" min="9" max="9"/>
+    <col width="22" customWidth="1" min="10" max="10"/>
+    <col width="7" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="7" customWidth="1" min="13" max="13"/>
+    <col width="8" customWidth="1" min="14" max="14"/>
+    <col width="16" customWidth="1" min="15" max="15"/>
+    <col width="10" customWidth="1" min="16" max="16"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="26" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>功能视角分解（功能×角色矩阵）：每个功能由谁做什么、投入多少人天 — 与WBS/185人天完全对账</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>功能编号</t>
+        </is>
+      </c>
+      <c r="B2" s="7" t="inlineStr">
+        <is>
+          <t>模块</t>
+        </is>
+      </c>
+      <c r="C2" s="7" t="inlineStr">
+        <is>
+          <t>具体功能（与源文件一致）</t>
+        </is>
+      </c>
+      <c r="D2" s="7" t="inlineStr">
+        <is>
+          <t>BA·需求（Mandy）</t>
+        </is>
+      </c>
+      <c r="E2" s="7" t="inlineStr">
+        <is>
+          <t>BA人天</t>
+        </is>
+      </c>
+      <c r="F2" s="7" t="inlineStr">
+        <is>
+          <t>开发A·Wade</t>
+        </is>
+      </c>
+      <c r="G2" s="7" t="inlineStr">
+        <is>
+          <t>A人天</t>
+        </is>
+      </c>
+      <c r="H2" s="7" t="inlineStr">
+        <is>
+          <t>开发B·DevB</t>
+        </is>
+      </c>
+      <c r="I2" s="7" t="inlineStr">
+        <is>
+          <t>B人天</t>
+        </is>
+      </c>
+      <c r="J2" s="7" t="inlineStr">
+        <is>
+          <t>测试·验证（Mandy）</t>
+        </is>
+      </c>
+      <c r="K2" s="7" t="inlineStr">
+        <is>
+          <t>测试人天</t>
+        </is>
+      </c>
+      <c r="L2" s="7" t="inlineStr">
+        <is>
+          <t>文档（Mandy）</t>
+        </is>
+      </c>
+      <c r="M2" s="7" t="inlineStr">
+        <is>
+          <t>文档人天</t>
+        </is>
+      </c>
+      <c r="N2" s="7" t="inlineStr">
+        <is>
+          <t>小计人天</t>
+        </is>
+      </c>
+      <c r="O2" s="7" t="inlineStr">
+        <is>
+          <t>关联WBS任务</t>
+        </is>
+      </c>
+      <c r="P2" s="7" t="inlineStr">
+        <is>
+          <t>计划完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="34" customHeight="1">
+      <c r="A3" s="30" t="inlineStr">
+        <is>
+          <t>F01-01</t>
+        </is>
+      </c>
+      <c r="B3" s="31" t="inlineStr">
+        <is>
+          <t>模块1·存量迁移</t>
+        </is>
+      </c>
+      <c r="C3" s="31" t="inlineStr">
+        <is>
+          <t>结构化历史数据批量导入</t>
+        </is>
+      </c>
+      <c r="D3" s="31" t="inlineStr">
+        <is>
+          <t>迁移范围/映射规则澄清与验收标准</t>
+        </is>
+      </c>
+      <c r="E3" s="49" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="F3" s="31" t="inlineStr">
+        <is>
+          <t>迁移任务管理界面（调度/进度）</t>
+        </is>
+      </c>
+      <c r="G3" s="49" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="H3" s="31" t="inlineStr">
+        <is>
+          <t>SeaTunnel分片/限速/断点批量导入</t>
+        </is>
+      </c>
+      <c r="I3" s="49" t="n">
+        <v>2</v>
+      </c>
+      <c r="J3" s="31" t="inlineStr">
+        <is>
+          <t>导入用例+样本表验证</t>
+        </is>
+      </c>
+      <c r="K3" s="49" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L3" s="31" t="inlineStr">
+        <is>
+          <t>用户手册F01章</t>
+        </is>
+      </c>
+      <c r="M3" s="49" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="N3" s="49" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="O3" s="31" t="inlineStr">
+        <is>
+          <t>4.2.1;4.3.1</t>
+        </is>
+      </c>
+      <c r="P3" s="30" t="inlineStr">
+        <is>
+          <t>10/22</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="34" customHeight="1">
+      <c r="A4" s="30" t="inlineStr">
+        <is>
+          <t>F01-02</t>
+        </is>
+      </c>
+      <c r="B4" s="31" t="inlineStr">
+        <is>
+          <t>模块1·存量迁移</t>
+        </is>
+      </c>
+      <c r="C4" s="31" t="inlineStr">
+        <is>
+          <t>非结构化文件及离线包批量导入</t>
+        </is>
+      </c>
+      <c r="D4" s="31" t="inlineStr">
+        <is>
+          <t>文件来源与离线介质场景澄清</t>
+        </is>
+      </c>
+      <c r="E4" s="49" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="F4" s="31" t="inlineStr">
+        <is>
+          <t>迁移任务界面（文件批次）</t>
+        </is>
+      </c>
+      <c r="G4" s="49" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="H4" s="31" t="inlineStr">
+        <is>
+          <t>多源文件/大文件/属性保留/包解析</t>
+        </is>
+      </c>
+      <c r="I4" s="49" t="n">
+        <v>1</v>
+      </c>
+      <c r="J4" s="31" t="inlineStr">
+        <is>
+          <t>导入与中断恢复用例</t>
+        </is>
+      </c>
+      <c r="K4" s="49" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L4" s="31" t="inlineStr">
+        <is>
+          <t>用户手册F01章</t>
+        </is>
+      </c>
+      <c r="M4" s="49" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="N4" s="49" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="O4" s="31" t="inlineStr">
+        <is>
+          <t>4.2.2;4.3.1</t>
+        </is>
+      </c>
+      <c r="P4" s="30" t="inlineStr">
+        <is>
+          <t>10/22</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="34" customHeight="1">
+      <c r="A5" s="30" t="inlineStr">
+        <is>
+          <t>F01-03</t>
+        </is>
+      </c>
+      <c r="B5" s="31" t="inlineStr">
+        <is>
+          <t>模块1·存量迁移</t>
+        </is>
+      </c>
+      <c r="C5" s="31" t="inlineStr">
+        <is>
+          <t>数据导入规则配置</t>
+        </is>
+      </c>
+      <c r="D5" s="31" t="inlineStr">
+        <is>
+          <t>源→标准字段映射规则定义</t>
+        </is>
+      </c>
+      <c r="E5" s="49" t="n"/>
+      <c r="F5" s="31" t="inlineStr">
+        <is>
+          <t>规则配置界面</t>
+        </is>
+      </c>
+      <c r="G5" s="49" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="H5" s="31" t="inlineStr">
+        <is>
+          <t>规则配置服务（映射/转换/校验）</t>
+        </is>
+      </c>
+      <c r="I5" s="49" t="n">
+        <v>1</v>
+      </c>
+      <c r="J5" s="31" t="inlineStr">
+        <is>
+          <t>规则执行用例</t>
+        </is>
+      </c>
+      <c r="K5" s="49" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="L5" s="31" t="inlineStr">
+        <is>
+          <t>用户手册F01章</t>
+        </is>
+      </c>
+      <c r="M5" s="49" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="N5" s="49" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="O5" s="31" t="inlineStr">
+        <is>
+          <t>4.2.3;4.3.1</t>
+        </is>
+      </c>
+      <c r="P5" s="30" t="inlineStr">
+        <is>
+          <t>10/22</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="34" customHeight="1">
+      <c r="A6" s="30" t="inlineStr">
+        <is>
+          <t>F01-04</t>
+        </is>
+      </c>
+      <c r="B6" s="31" t="inlineStr">
+        <is>
+          <t>模块1·存量迁移</t>
+        </is>
+      </c>
+      <c r="C6" s="31" t="inlineStr">
+        <is>
+          <t>迁移前完整性基准记录</t>
+        </is>
+      </c>
+      <c r="D6" s="31" t="inlineStr">
+        <is>
+          <t>完整性基准口径定义</t>
+        </is>
+      </c>
+      <c r="E6" s="49" t="n"/>
+      <c r="F6" s="31" t="inlineStr">
+        <is>
+          <t>校验结果展示</t>
+        </is>
+      </c>
+      <c r="G6" s="49" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="H6" s="31" t="inlineStr">
+        <is>
+          <t>迁移前基准记录（行数/校验和）</t>
+        </is>
+      </c>
+      <c r="I6" s="49" t="n">
+        <v>1</v>
+      </c>
+      <c r="J6" s="31" t="inlineStr">
+        <is>
+          <t>基准记录用例</t>
+        </is>
+      </c>
+      <c r="K6" s="49" t="n"/>
+      <c r="L6" s="31" t="inlineStr">
+        <is>
+          <t>用户手册F01章</t>
+        </is>
+      </c>
+      <c r="M6" s="49" t="n"/>
+      <c r="N6" s="49" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="O6" s="31" t="inlineStr">
+        <is>
+          <t>4.2.5;4.3.1</t>
+        </is>
+      </c>
+      <c r="P6" s="30" t="inlineStr">
+        <is>
+          <t>10/22</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="34" customHeight="1">
+      <c r="A7" s="30" t="inlineStr">
+        <is>
+          <t>F01-05</t>
+        </is>
+      </c>
+      <c r="B7" s="31" t="inlineStr">
+        <is>
+          <t>模块1·存量迁移</t>
+        </is>
+      </c>
+      <c r="C7" s="31" t="inlineStr">
+        <is>
+          <t>迁移后完整性比对</t>
+        </is>
+      </c>
+      <c r="D7" s="31" t="inlineStr">
+        <is>
+          <t>比对差异处理口径</t>
+        </is>
+      </c>
+      <c r="E7" s="49" t="n"/>
+      <c r="F7" s="31" t="inlineStr">
+        <is>
+          <t>比对结果展示</t>
+        </is>
+      </c>
+      <c r="G7" s="49" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="H7" s="31" t="inlineStr">
+        <is>
+          <t>迁移后比对（SHA-256/差异报告）</t>
+        </is>
+      </c>
+      <c r="I7" s="49" t="n">
+        <v>1</v>
+      </c>
+      <c r="J7" s="31" t="inlineStr">
+        <is>
+          <t>比对用例（CC对账预演）</t>
+        </is>
+      </c>
+      <c r="K7" s="49" t="n"/>
+      <c r="L7" s="31" t="inlineStr">
+        <is>
+          <t>用户手册F01章</t>
+        </is>
+      </c>
+      <c r="M7" s="49" t="n"/>
+      <c r="N7" s="49" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="O7" s="31" t="inlineStr">
+        <is>
+          <t>4.2.5;4.3.1</t>
+        </is>
+      </c>
+      <c r="P7" s="30" t="inlineStr">
+        <is>
+          <t>10/22</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="34" customHeight="1">
+      <c r="A8" s="50" t="inlineStr">
+        <is>
+          <t>F02-01</t>
+        </is>
+      </c>
+      <c r="B8" s="51" t="inlineStr">
+        <is>
+          <t>模块2·元数据</t>
+        </is>
+      </c>
+      <c r="C8" s="51" t="inlineStr">
+        <is>
+          <t>统一元数据模型</t>
+        </is>
+      </c>
+      <c r="D8" s="51" t="inlineStr">
+        <is>
+          <t>元数据字段体系与必填规则</t>
+        </is>
+      </c>
+      <c r="E8" s="52" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="F8" s="51" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G8" s="52" t="n"/>
+      <c r="H8" s="51" t="inlineStr">
+        <is>
+          <t>统一元数据模型API</t>
+        </is>
+      </c>
+      <c r="I8" s="52" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="J8" s="51" t="inlineStr">
+        <is>
+          <t>模块2走查</t>
+        </is>
+      </c>
+      <c r="K8" s="52" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L8" s="51" t="inlineStr">
+        <is>
+          <t>用户手册F02章</t>
+        </is>
+      </c>
+      <c r="M8" s="52" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="N8" s="52" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="O8" s="51" t="inlineStr">
+        <is>
+          <t>4.2.6;5.2.1</t>
+        </is>
+      </c>
+      <c r="P8" s="50" t="inlineStr">
+        <is>
+          <t>10/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="34" customHeight="1">
+      <c r="A9" s="50" t="inlineStr">
+        <is>
+          <t>F02-02</t>
+        </is>
+      </c>
+      <c r="B9" s="51" t="inlineStr">
+        <is>
+          <t>模块2·元数据</t>
+        </is>
+      </c>
+      <c r="C9" s="51" t="inlineStr">
+        <is>
+          <t>来源系统信息绑定</t>
+        </is>
+      </c>
+      <c r="D9" s="51" t="inlineStr">
+        <is>
+          <t>来源系统编码与绑定规则</t>
+        </is>
+      </c>
+      <c r="E9" s="52" t="n"/>
+      <c r="F9" s="51" t="inlineStr">
+        <is>
+          <t>元数据管理界面（协作）</t>
+        </is>
+      </c>
+      <c r="G9" s="52" t="n"/>
+      <c r="H9" s="51" t="inlineStr">
+        <is>
+          <t>来源系统信息绑定API</t>
+        </is>
+      </c>
+      <c r="I9" s="52" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="J9" s="51" t="inlineStr">
+        <is>
+          <t>模块2走查</t>
+        </is>
+      </c>
+      <c r="K9" s="52" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="L9" s="51" t="inlineStr">
+        <is>
+          <t>用户手册F02章</t>
+        </is>
+      </c>
+      <c r="M9" s="52" t="n"/>
+      <c r="N9" s="52" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="O9" s="51" t="inlineStr">
+        <is>
+          <t>4.2.6;5.2.1</t>
+        </is>
+      </c>
+      <c r="P9" s="50" t="inlineStr">
+        <is>
+          <t>10/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="34" customHeight="1">
+      <c r="A10" s="23" t="inlineStr">
+        <is>
+          <t>F03-01</t>
+        </is>
+      </c>
+      <c r="B10" s="33" t="inlineStr">
+        <is>
+          <t>模块3·生命周期处置</t>
+        </is>
+      </c>
+      <c r="C10" s="33" t="inlineStr">
+        <is>
+          <t>保留期限到期自动删除</t>
+        </is>
+      </c>
+      <c r="D10" s="33" t="inlineStr">
+        <is>
+          <t>保留期矩阵与到期处置策略</t>
+        </is>
+      </c>
+      <c r="E10" s="48" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="F10" s="33" t="inlineStr">
+        <is>
+          <t>保留策略配置界面</t>
+        </is>
+      </c>
+      <c r="G10" s="48" t="n">
+        <v>1</v>
+      </c>
+      <c r="H10" s="33" t="inlineStr">
+        <is>
+          <t>处置引擎（扫描→DROP PARTITION→VACUUM）</t>
+        </is>
+      </c>
+      <c r="I10" s="48" t="n">
+        <v>2</v>
+      </c>
+      <c r="J10" s="33" t="inlineStr">
+        <is>
+          <t>到期删除走查</t>
+        </is>
+      </c>
+      <c r="K10" s="48" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L10" s="33" t="inlineStr">
+        <is>
+          <t>用户手册F03章</t>
+        </is>
+      </c>
+      <c r="M10" s="48" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="N10" s="48" t="n">
+        <v>4</v>
+      </c>
+      <c r="O10" s="33" t="inlineStr">
+        <is>
+          <t>5.2.5;5.1.5</t>
+        </is>
+      </c>
+      <c r="P10" s="23" t="inlineStr">
+        <is>
+          <t>11/06</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="34" customHeight="1">
+      <c r="A11" s="23" t="inlineStr">
+        <is>
+          <t>F03-02</t>
+        </is>
+      </c>
+      <c r="B11" s="33" t="inlineStr">
+        <is>
+          <t>模块3·生命周期处置</t>
+        </is>
+      </c>
+      <c r="C11" s="33" t="inlineStr">
+        <is>
+          <t>Legal Hold 冻结</t>
+        </is>
+      </c>
+      <c r="D11" s="33" t="inlineStr">
+        <is>
+          <t>Legal Hold审批流程定义</t>
+        </is>
+      </c>
+      <c r="E11" s="48" t="n"/>
+      <c r="F11" s="33" t="inlineStr">
+        <is>
+          <t>Legal Hold冻结/解除界面</t>
+        </is>
+      </c>
+      <c r="G11" s="48" t="n">
+        <v>1</v>
+      </c>
+      <c r="H11" s="33" t="inlineStr">
+        <is>
+          <t>Hold/Release+豁免+留痕</t>
+        </is>
+      </c>
+      <c r="I11" s="48" t="n">
+        <v>1</v>
+      </c>
+      <c r="J11" s="33" t="inlineStr">
+        <is>
+          <t>冻结/解除走查</t>
+        </is>
+      </c>
+      <c r="K11" s="48" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="L11" s="33" t="inlineStr">
+        <is>
+          <t>用户手册F03章</t>
+        </is>
+      </c>
+      <c r="M11" s="48" t="n"/>
+      <c r="N11" s="48" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="O11" s="33" t="inlineStr">
+        <is>
+          <t>5.2.6;5.1.5</t>
+        </is>
+      </c>
+      <c r="P11" s="23" t="inlineStr">
+        <is>
+          <t>11/06</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="34" customHeight="1">
+      <c r="A12" s="53" t="inlineStr">
+        <is>
+          <t>F04-01</t>
+        </is>
+      </c>
+      <c r="B12" s="54" t="inlineStr">
+        <is>
+          <t>模块4·存储安全</t>
+        </is>
+      </c>
+      <c r="C12" s="54" t="inlineStr">
+        <is>
+          <t>数据加密存储</t>
+        </is>
+      </c>
+      <c r="D12" s="54" t="inlineStr">
+        <is>
+          <t>密级与加密合规要求</t>
+        </is>
+      </c>
+      <c r="E12" s="55" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="F12" s="54" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G12" s="55" t="n"/>
+      <c r="H12" s="54" t="inlineStr">
+        <is>
+          <t>SSE+CMK+PII字段加密</t>
+        </is>
+      </c>
+      <c r="I12" s="55" t="n">
+        <v>2</v>
+      </c>
+      <c r="J12" s="54" t="inlineStr">
+        <is>
+          <t>加密落盘验证</t>
+        </is>
+      </c>
+      <c r="K12" s="55" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L12" s="54" t="inlineStr">
+        <is>
+          <t>用户手册F04章</t>
+        </is>
+      </c>
+      <c r="M12" s="55" t="n"/>
+      <c r="N12" s="55" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="O12" s="54" t="inlineStr">
+        <is>
+          <t>5.2.2</t>
+        </is>
+      </c>
+      <c r="P12" s="53" t="inlineStr">
+        <is>
+          <t>11/06</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="34" customHeight="1">
+      <c r="A13" s="53" t="inlineStr">
+        <is>
+          <t>F04-02</t>
+        </is>
+      </c>
+      <c r="B13" s="54" t="inlineStr">
+        <is>
+          <t>模块4·存储安全</t>
+        </is>
+      </c>
+      <c r="C13" s="54" t="inlineStr">
+        <is>
+          <t>密钥管理</t>
+        </is>
+      </c>
+      <c r="D13" s="54" t="inlineStr">
+        <is>
+          <t>密钥保管与审计要求</t>
+        </is>
+      </c>
+      <c r="E13" s="55" t="n"/>
+      <c r="F13" s="54" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G13" s="55" t="n"/>
+      <c r="H13" s="54" t="inlineStr">
+        <is>
+          <t>Key Vault创建/更新/权限/审计</t>
+        </is>
+      </c>
+      <c r="I13" s="55" t="n">
+        <v>2</v>
+      </c>
+      <c r="J13" s="54" t="inlineStr">
+        <is>
+          <t>密钥轮换用例</t>
+        </is>
+      </c>
+      <c r="K13" s="55" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="L13" s="54" t="inlineStr">
+        <is>
+          <t>用户手册F04章</t>
+        </is>
+      </c>
+      <c r="M13" s="55" t="n"/>
+      <c r="N13" s="55" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="O13" s="54" t="inlineStr">
+        <is>
+          <t>5.2.3</t>
+        </is>
+      </c>
+      <c r="P13" s="53" t="inlineStr">
+        <is>
+          <t>11/06</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="34" customHeight="1">
+      <c r="A14" s="53" t="inlineStr">
+        <is>
+          <t>F04-03</t>
+        </is>
+      </c>
+      <c r="B14" s="54" t="inlineStr">
+        <is>
+          <t>模块4·存储安全</t>
+        </is>
+      </c>
+      <c r="C14" s="54" t="inlineStr">
+        <is>
+          <t>数据备份管理</t>
+        </is>
+      </c>
+      <c r="D14" s="54" t="inlineStr">
+        <is>
+          <t>备份策略要求（RPO）</t>
+        </is>
+      </c>
+      <c r="E14" s="55" t="n"/>
+      <c r="F14" s="54" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G14" s="55" t="n"/>
+      <c r="H14" s="54" t="inlineStr">
+        <is>
+          <t>备份策略配置+副本创建</t>
+        </is>
+      </c>
+      <c r="I14" s="55" t="n">
+        <v>1</v>
+      </c>
+      <c r="J14" s="54" t="inlineStr">
+        <is>
+          <t>备份恢复用例</t>
+        </is>
+      </c>
+      <c r="K14" s="55" t="n"/>
+      <c r="L14" s="54" t="inlineStr">
+        <is>
+          <t>用户手册F04章</t>
+        </is>
+      </c>
+      <c r="M14" s="55" t="n"/>
+      <c r="N14" s="55" t="n">
+        <v>1</v>
+      </c>
+      <c r="O14" s="54" t="inlineStr">
+        <is>
+          <t>5.2.7</t>
+        </is>
+      </c>
+      <c r="P14" s="53" t="inlineStr">
+        <is>
+          <t>11/06</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="34" customHeight="1">
+      <c r="A15" s="53" t="inlineStr">
+        <is>
+          <t>F04-04</t>
+        </is>
+      </c>
+      <c r="B15" s="54" t="inlineStr">
+        <is>
+          <t>模块4·存储安全</t>
+        </is>
+      </c>
+      <c r="C15" s="54" t="inlineStr">
+        <is>
+          <t>异地灾备</t>
+        </is>
+      </c>
+      <c r="D15" s="54" t="inlineStr">
+        <is>
+          <t>灾备要求（RTO）</t>
+        </is>
+      </c>
+      <c r="E15" s="55" t="n"/>
+      <c r="F15" s="54" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G15" s="55" t="n"/>
+      <c r="H15" s="54" t="inlineStr">
+        <is>
+          <t>异地副本+恢复流程演练</t>
+        </is>
+      </c>
+      <c r="I15" s="55" t="n">
+        <v>1</v>
+      </c>
+      <c r="J15" s="54" t="inlineStr">
+        <is>
+          <t>灾备切换用例</t>
+        </is>
+      </c>
+      <c r="K15" s="55" t="n"/>
+      <c r="L15" s="54" t="inlineStr">
+        <is>
+          <t>用户手册F04章</t>
+        </is>
+      </c>
+      <c r="M15" s="55" t="n"/>
+      <c r="N15" s="55" t="n">
+        <v>1</v>
+      </c>
+      <c r="O15" s="54" t="inlineStr">
+        <is>
+          <t>5.2.8</t>
+        </is>
+      </c>
+      <c r="P15" s="53" t="inlineStr">
+        <is>
+          <t>11/09</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="34" customHeight="1">
+      <c r="A16" s="56" t="inlineStr">
+        <is>
+          <t>F05-01</t>
+        </is>
+      </c>
+      <c r="B16" s="57" t="inlineStr">
+        <is>
+          <t>模块5·检索利用</t>
+        </is>
+      </c>
+      <c r="C16" s="57" t="inlineStr">
+        <is>
+          <t>关键词检索</t>
+        </is>
+      </c>
+      <c r="D16" s="57" t="inlineStr">
+        <is>
+          <t>检索需求与查询配置模型</t>
+        </is>
+      </c>
+      <c r="E16" s="58" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="F16" s="57" t="inlineStr">
+        <is>
+          <t>检索页动态表单+关键词检索</t>
+        </is>
+      </c>
+      <c r="G16" s="58" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="H16" s="57" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I16" s="58" t="n"/>
+      <c r="J16" s="57" t="inlineStr">
+        <is>
+          <t>检索用例</t>
+        </is>
+      </c>
+      <c r="K16" s="58" t="n">
+        <v>1</v>
+      </c>
+      <c r="L16" s="57" t="inlineStr">
+        <is>
+          <t>用户手册F05章</t>
+        </is>
+      </c>
+      <c r="M16" s="58" t="n"/>
+      <c r="N16" s="58" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="O16" s="57" t="inlineStr">
+        <is>
+          <t>4.3.2</t>
+        </is>
+      </c>
+      <c r="P16" s="56" t="inlineStr">
+        <is>
+          <t>10/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="34" customHeight="1">
+      <c r="A17" s="56" t="inlineStr">
+        <is>
+          <t>F05-02</t>
+        </is>
+      </c>
+      <c r="B17" s="57" t="inlineStr">
+        <is>
+          <t>模块5·检索利用</t>
+        </is>
+      </c>
+      <c r="C17" s="57" t="inlineStr">
+        <is>
+          <t>按系统名称检索</t>
+        </is>
+      </c>
+      <c r="D17" s="57" t="inlineStr">
+        <is>
+          <t>来源系统筛选需求</t>
+        </is>
+      </c>
+      <c r="E17" s="58" t="n"/>
+      <c r="F17" s="57" t="inlineStr">
+        <is>
+          <t>按系统名称检索</t>
+        </is>
+      </c>
+      <c r="G17" s="58" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="H17" s="57" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I17" s="58" t="n"/>
+      <c r="J17" s="57" t="inlineStr">
+        <is>
+          <t>筛选用例</t>
+        </is>
+      </c>
+      <c r="K17" s="58" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="L17" s="57" t="inlineStr">
+        <is>
+          <t>用户手册F05章</t>
+        </is>
+      </c>
+      <c r="M17" s="58" t="n"/>
+      <c r="N17" s="58" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="O17" s="57" t="inlineStr">
+        <is>
+          <t>4.3.2</t>
+        </is>
+      </c>
+      <c r="P17" s="56" t="inlineStr">
+        <is>
+          <t>10/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="34" customHeight="1">
+      <c r="A18" s="56" t="inlineStr">
+        <is>
+          <t>F05-03</t>
+        </is>
+      </c>
+      <c r="B18" s="57" t="inlineStr">
+        <is>
+          <t>模块5·检索利用</t>
+        </is>
+      </c>
+      <c r="C18" s="57" t="inlineStr">
+        <is>
+          <t>按业务时间检索</t>
+        </is>
+      </c>
+      <c r="D18" s="57" t="inlineStr">
+        <is>
+          <t>时间维度检索需求</t>
+        </is>
+      </c>
+      <c r="E18" s="58" t="n"/>
+      <c r="F18" s="57" t="inlineStr">
+        <is>
+          <t>按业务时间检索</t>
+        </is>
+      </c>
+      <c r="G18" s="58" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="H18" s="57" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I18" s="58" t="n"/>
+      <c r="J18" s="57" t="inlineStr">
+        <is>
+          <t>时间范围用例</t>
+        </is>
+      </c>
+      <c r="K18" s="58" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L18" s="57" t="inlineStr">
+        <is>
+          <t>用户手册F05章</t>
+        </is>
+      </c>
+      <c r="M18" s="58" t="n"/>
+      <c r="N18" s="58" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="O18" s="57" t="inlineStr">
+        <is>
+          <t>4.3.2</t>
+        </is>
+      </c>
+      <c r="P18" s="56" t="inlineStr">
+        <is>
+          <t>10/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="34" customHeight="1">
+      <c r="A19" s="56" t="inlineStr">
+        <is>
+          <t>F05-04</t>
+        </is>
+      </c>
+      <c r="B19" s="57" t="inlineStr">
+        <is>
+          <t>模块5·检索利用</t>
+        </is>
+      </c>
+      <c r="C19" s="57" t="inlineStr">
+        <is>
+          <t>检索结果列表展示</t>
+        </is>
+      </c>
+      <c r="D19" s="57" t="inlineStr">
+        <is>
+          <t>列表字段/排序/导出需求</t>
+        </is>
+      </c>
+      <c r="E19" s="58" t="n"/>
+      <c r="F19" s="57" t="inlineStr">
+        <is>
+          <t>结果列表（分页/排序）+流式导出</t>
+        </is>
+      </c>
+      <c r="G19" s="58" t="n">
+        <v>3</v>
+      </c>
+      <c r="H19" s="57" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I19" s="58" t="n"/>
+      <c r="J19" s="57" t="inlineStr">
+        <is>
+          <t>大批量用例</t>
+        </is>
+      </c>
+      <c r="K19" s="58" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="L19" s="57" t="inlineStr">
+        <is>
+          <t>用户手册F05章</t>
+        </is>
+      </c>
+      <c r="M19" s="58" t="n"/>
+      <c r="N19" s="58" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="O19" s="57" t="inlineStr">
+        <is>
+          <t>5.1.1;5.1.7</t>
+        </is>
+      </c>
+      <c r="P19" s="56" t="inlineStr">
+        <is>
+          <t>11/10</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="34" customHeight="1">
+      <c r="A20" s="56" t="inlineStr">
+        <is>
+          <t>F05-05</t>
+        </is>
+      </c>
+      <c r="B20" s="57" t="inlineStr">
+        <is>
+          <t>模块5·检索利用</t>
+        </is>
+      </c>
+      <c r="C20" s="57" t="inlineStr">
+        <is>
+          <t>原始文件在线预览</t>
+        </is>
+      </c>
+      <c r="D20" s="57" t="inlineStr">
+        <is>
+          <t>预览格式与权限要求</t>
+        </is>
+      </c>
+      <c r="E20" s="58" t="n"/>
+      <c r="F20" s="57" t="inlineStr">
+        <is>
+          <t>在线预览（SAS直连）+大文件优化</t>
+        </is>
+      </c>
+      <c r="G20" s="58" t="n">
+        <v>3</v>
+      </c>
+      <c r="H20" s="57" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I20" s="58" t="n"/>
+      <c r="J20" s="57" t="inlineStr">
+        <is>
+          <t>预览用例</t>
+        </is>
+      </c>
+      <c r="K20" s="58" t="n"/>
+      <c r="L20" s="57" t="inlineStr">
+        <is>
+          <t>用户手册F05章</t>
+        </is>
+      </c>
+      <c r="M20" s="58" t="n"/>
+      <c r="N20" s="58" t="n">
+        <v>3</v>
+      </c>
+      <c r="O20" s="57" t="inlineStr">
+        <is>
+          <t>5.1.2;5.1.7</t>
+        </is>
+      </c>
+      <c r="P20" s="56" t="inlineStr">
+        <is>
+          <t>11/10</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="34" customHeight="1">
+      <c r="A21" s="59" t="inlineStr">
+        <is>
+          <t>F06-01</t>
+        </is>
+      </c>
+      <c r="B21" s="60" t="inlineStr">
+        <is>
+          <t>模块6·审计合规</t>
+        </is>
+      </c>
+      <c r="C21" s="60" t="inlineStr">
+        <is>
+          <t>归档操作日志记录</t>
+        </is>
+      </c>
+      <c r="D21" s="60" t="inlineStr">
+        <is>
+          <t>审计合规要求（归档日志）</t>
+        </is>
+      </c>
+      <c r="E21" s="61" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="F21" s="60" t="inlineStr">
+        <is>
+          <t>归档操作日志+审计查询界面</t>
+        </is>
+      </c>
+      <c r="G21" s="61" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="H21" s="60" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I21" s="61" t="n"/>
+      <c r="J21" s="60" t="inlineStr">
+        <is>
+          <t>审计走查</t>
+        </is>
+      </c>
+      <c r="K21" s="61" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="L21" s="60" t="inlineStr">
+        <is>
+          <t>用户手册F06章</t>
+        </is>
+      </c>
+      <c r="M21" s="61" t="n"/>
+      <c r="N21" s="61" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="O21" s="60" t="inlineStr">
+        <is>
+          <t>5.1.3</t>
+        </is>
+      </c>
+      <c r="P21" s="59" t="inlineStr">
+        <is>
+          <t>11/03</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="34" customHeight="1">
+      <c r="A22" s="59" t="inlineStr">
+        <is>
+          <t>F06-02</t>
+        </is>
+      </c>
+      <c r="B22" s="60" t="inlineStr">
+        <is>
+          <t>模块6·审计合规</t>
+        </is>
+      </c>
+      <c r="C22" s="60" t="inlineStr">
+        <is>
+          <t>查询操作日志记录</t>
+        </is>
+      </c>
+      <c r="D22" s="60" t="inlineStr">
+        <is>
+          <t>查询行为审计要求</t>
+        </is>
+      </c>
+      <c r="E22" s="61" t="n"/>
+      <c r="F22" s="60" t="inlineStr">
+        <is>
+          <t>查询操作日志记录</t>
+        </is>
+      </c>
+      <c r="G22" s="61" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="H22" s="60" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I22" s="61" t="n"/>
+      <c r="J22" s="60" t="inlineStr">
+        <is>
+          <t>审计走查</t>
+        </is>
+      </c>
+      <c r="K22" s="61" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="L22" s="60" t="inlineStr">
+        <is>
+          <t>用户手册F06章</t>
+        </is>
+      </c>
+      <c r="M22" s="61" t="n"/>
+      <c r="N22" s="61" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="O22" s="60" t="inlineStr">
+        <is>
+          <t>5.1.3</t>
+        </is>
+      </c>
+      <c r="P22" s="59" t="inlineStr">
+        <is>
+          <t>11/03</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="34" customHeight="1">
+      <c r="A23" s="59" t="inlineStr">
+        <is>
+          <t>F06-03</t>
+        </is>
+      </c>
+      <c r="B23" s="60" t="inlineStr">
+        <is>
+          <t>模块6·审计合规</t>
+        </is>
+      </c>
+      <c r="C23" s="60" t="inlineStr">
+        <is>
+          <t>导出操作日志记录</t>
+        </is>
+      </c>
+      <c r="D23" s="60" t="inlineStr">
+        <is>
+          <t>导出审计要求（范围/IP）</t>
+        </is>
+      </c>
+      <c r="E23" s="61" t="n"/>
+      <c r="F23" s="60" t="inlineStr">
+        <is>
+          <t>导出操作日志记录</t>
+        </is>
+      </c>
+      <c r="G23" s="61" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="H23" s="60" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I23" s="61" t="n"/>
+      <c r="J23" s="60" t="inlineStr">
+        <is>
+          <t>审计走查</t>
+        </is>
+      </c>
+      <c r="K23" s="61" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="L23" s="60" t="inlineStr">
+        <is>
+          <t>用户手册F06章</t>
+        </is>
+      </c>
+      <c r="M23" s="61" t="n"/>
+      <c r="N23" s="61" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="O23" s="60" t="inlineStr">
+        <is>
+          <t>5.1.3</t>
+        </is>
+      </c>
+      <c r="P23" s="59" t="inlineStr">
+        <is>
+          <t>11/03</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="34" customHeight="1">
+      <c r="A24" s="62" t="inlineStr">
+        <is>
+          <t>F08-01</t>
+        </is>
+      </c>
+      <c r="B24" s="63" t="inlineStr">
+        <is>
+          <t>模块8·全局治理</t>
+        </is>
+      </c>
+      <c r="C24" s="63" t="inlineStr">
+        <is>
+          <t>基础角色权限配置</t>
+        </is>
+      </c>
+      <c r="D24" s="63" t="inlineStr">
+        <is>
+          <t>角色权限矩阵（RBAC）定义</t>
+        </is>
+      </c>
+      <c r="E24" s="64" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="F24" s="63" t="inlineStr">
+        <is>
+          <t>角色权限配置（界面+API）</t>
+        </is>
+      </c>
+      <c r="G24" s="64" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H24" s="63" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I24" s="64" t="n"/>
+      <c r="J24" s="63" t="inlineStr">
+        <is>
+          <t>越权用例</t>
+        </is>
+      </c>
+      <c r="K24" s="64" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L24" s="63" t="inlineStr">
+        <is>
+          <t>用户手册F08章</t>
+        </is>
+      </c>
+      <c r="M24" s="64" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="N24" s="64" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="O24" s="63" t="inlineStr">
+        <is>
+          <t>4.1.1</t>
+        </is>
+      </c>
+      <c r="P24" s="62" t="inlineStr">
+        <is>
+          <t>10/22</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="34" customHeight="1">
+      <c r="A25" s="62" t="inlineStr">
+        <is>
+          <t>F08-02</t>
+        </is>
+      </c>
+      <c r="B25" s="63" t="inlineStr">
+        <is>
+          <t>模块8·全局治理</t>
+        </is>
+      </c>
+      <c r="C25" s="63" t="inlineStr">
+        <is>
+          <t>用户账号管理</t>
+        </is>
+      </c>
+      <c r="D25" s="63" t="inlineStr">
+        <is>
+          <t>账号生命周期策略</t>
+        </is>
+      </c>
+      <c r="E25" s="64" t="n"/>
+      <c r="F25" s="63" t="inlineStr">
+        <is>
+          <t>用户账号管理（界面+API）</t>
+        </is>
+      </c>
+      <c r="G25" s="64" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H25" s="63" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I25" s="64" t="n"/>
+      <c r="J25" s="63" t="inlineStr">
+        <is>
+          <t>账号用例</t>
+        </is>
+      </c>
+      <c r="K25" s="64" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L25" s="63" t="inlineStr">
+        <is>
+          <t>用户手册F08章</t>
+        </is>
+      </c>
+      <c r="M25" s="64" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="N25" s="64" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="O25" s="63" t="inlineStr">
+        <is>
+          <t>4.1.1</t>
+        </is>
+      </c>
+      <c r="P25" s="62" t="inlineStr">
+        <is>
+          <t>10/22</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="34" customHeight="1">
+      <c r="A26" s="62" t="inlineStr">
+        <is>
+          <t>F08-03</t>
+        </is>
+      </c>
+      <c r="B26" s="63" t="inlineStr">
+        <is>
+          <t>模块8·全局治理</t>
+        </is>
+      </c>
+      <c r="C26" s="63" t="inlineStr">
+        <is>
+          <t>企业SSO集成</t>
+        </is>
+      </c>
+      <c r="D26" s="63" t="inlineStr">
+        <is>
+          <t>SSO对接需求（Entra ID）</t>
+        </is>
+      </c>
+      <c r="E26" s="64" t="n"/>
+      <c r="F26" s="63" t="inlineStr">
+        <is>
+          <t>SSO集成（登录页+后端链路）</t>
+        </is>
+      </c>
+      <c r="G26" s="64" t="n">
+        <v>3</v>
+      </c>
+      <c r="H26" s="63" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I26" s="64" t="n"/>
+      <c r="J26" s="63" t="inlineStr">
+        <is>
+          <t>SSO登录用例</t>
+        </is>
+      </c>
+      <c r="K26" s="64" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="L26" s="63" t="inlineStr">
+        <is>
+          <t>用户手册F08章</t>
+        </is>
+      </c>
+      <c r="M26" s="64" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="N26" s="64" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="O26" s="63" t="inlineStr">
+        <is>
+          <t>4.1.2;3.3.1</t>
+        </is>
+      </c>
+      <c r="P26" s="62" t="inlineStr">
+        <is>
+          <t>10/22</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="34" customHeight="1">
+      <c r="A27" s="62" t="inlineStr">
+        <is>
+          <t>F08-04</t>
+        </is>
+      </c>
+      <c r="B27" s="63" t="inlineStr">
+        <is>
+          <t>模块8·全局治理</t>
+        </is>
+      </c>
+      <c r="C27" s="63" t="inlineStr">
+        <is>
+          <t>用户身份自动识别与关联</t>
+        </is>
+      </c>
+      <c r="D27" s="63" t="inlineStr">
+        <is>
+          <t>身份映射规则</t>
+        </is>
+      </c>
+      <c r="E27" s="64" t="n"/>
+      <c r="F27" s="63" t="inlineStr">
+        <is>
+          <t>身份自动识别与关联</t>
+        </is>
+      </c>
+      <c r="G27" s="64" t="n">
+        <v>1</v>
+      </c>
+      <c r="H27" s="63" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I27" s="64" t="n"/>
+      <c r="J27" s="63" t="inlineStr">
+        <is>
+          <t>身份关联用例</t>
+        </is>
+      </c>
+      <c r="K27" s="64" t="n"/>
+      <c r="L27" s="63" t="inlineStr">
+        <is>
+          <t>用户手册F08章</t>
+        </is>
+      </c>
+      <c r="M27" s="64" t="n"/>
+      <c r="N27" s="64" t="n">
+        <v>1</v>
+      </c>
+      <c r="O27" s="63" t="inlineStr">
+        <is>
+          <t>4.1.2</t>
+        </is>
+      </c>
+      <c r="P27" s="62" t="inlineStr">
+        <is>
+          <t>10/22</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="34" customHeight="1">
+      <c r="A28" s="62" t="inlineStr">
+        <is>
+          <t>F08-05</t>
+        </is>
+      </c>
+      <c r="B28" s="63" t="inlineStr">
+        <is>
+          <t>模块8·全局治理</t>
+        </is>
+      </c>
+      <c r="C28" s="63" t="inlineStr">
+        <is>
+          <t>登录状态与异常访问控制</t>
+        </is>
+      </c>
+      <c r="D28" s="63" t="inlineStr">
+        <is>
+          <t>异常访问控制策略</t>
+        </is>
+      </c>
+      <c r="E28" s="64" t="n"/>
+      <c r="F28" s="63" t="inlineStr">
+        <is>
+          <t>超时/锁定/失效控制</t>
+        </is>
+      </c>
+      <c r="G28" s="64" t="n">
+        <v>1</v>
+      </c>
+      <c r="H28" s="63" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I28" s="64" t="n"/>
+      <c r="J28" s="63" t="inlineStr">
+        <is>
+          <t>异常登录用例</t>
+        </is>
+      </c>
+      <c r="K28" s="64" t="n"/>
+      <c r="L28" s="63" t="inlineStr">
+        <is>
+          <t>用户手册F08章</t>
+        </is>
+      </c>
+      <c r="M28" s="64" t="n"/>
+      <c r="N28" s="64" t="n">
+        <v>1</v>
+      </c>
+      <c r="O28" s="63" t="inlineStr">
+        <is>
+          <t>4.1.3</t>
+        </is>
+      </c>
+      <c r="P28" s="62" t="inlineStr">
+        <is>
+          <t>10/22</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="34" customHeight="1">
+      <c r="A29" s="65" t="inlineStr">
+        <is>
+          <t>G1</t>
+        </is>
+      </c>
+      <c r="B29" s="66" t="inlineStr">
+        <is>
+          <t>公共支撑</t>
+        </is>
+      </c>
+      <c r="C29" s="66" t="inlineStr">
+        <is>
+          <t>需求与SRS（跨功能）</t>
+        </is>
+      </c>
+      <c r="D29" s="66" t="inlineStr">
+        <is>
+          <t>业务访谈3场/原型草图/SRS生成与评审/NFR基线/需求贯穿</t>
+        </is>
+      </c>
+      <c r="E29" s="67" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="F29" s="66" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G29" s="67" t="n"/>
+      <c r="H29" s="66" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I29" s="67" t="n"/>
+      <c r="J29" s="66" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K29" s="67" t="n"/>
+      <c r="L29" s="66" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M29" s="67" t="n"/>
+      <c r="N29" s="67" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="O29" s="66" t="inlineStr">
+        <is>
+          <t>2.1.1,2.1.3,2.2.1,2.2.2…</t>
+        </is>
+      </c>
+      <c r="P29" s="65" t="inlineStr">
+        <is>
+          <t>12/04</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="34" customHeight="1">
+      <c r="A30" s="65" t="inlineStr">
+        <is>
+          <t>G2</t>
+        </is>
+      </c>
+      <c r="B30" s="66" t="inlineStr">
+        <is>
+          <t>公共支撑</t>
+        </is>
+      </c>
+      <c r="C30" s="66" t="inlineStr">
+        <is>
+          <t>项目初始化与工程基座</t>
+        </is>
+      </c>
+      <c r="D30" s="66" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E30" s="67" t="n"/>
+      <c r="F30" s="66" t="inlineStr">
+        <is>
+          <t>仓库/分支/环境/AI规范/四道门禁CI-CD/前端骨架</t>
+        </is>
+      </c>
+      <c r="G30" s="67" t="n">
+        <v>7</v>
+      </c>
+      <c r="H30" s="66" t="inlineStr">
+        <is>
+          <t>后端骨架+本地Docker环境</t>
+        </is>
+      </c>
+      <c r="I30" s="67" t="n">
+        <v>2</v>
+      </c>
+      <c r="J30" s="66" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K30" s="67" t="n"/>
+      <c r="L30" s="66" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M30" s="67" t="n"/>
+      <c r="N30" s="67" t="n">
+        <v>9</v>
+      </c>
+      <c r="O30" s="66" t="inlineStr">
+        <is>
+          <t>3.1.1,3.1.2,3.1.3,3.1.4…</t>
+        </is>
+      </c>
+      <c r="P30" s="65" t="inlineStr">
+        <is>
+          <t>09/22</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="34" customHeight="1">
+      <c r="A31" s="65" t="inlineStr">
+        <is>
+          <t>G3</t>
+        </is>
+      </c>
+      <c r="B31" s="66" t="inlineStr">
+        <is>
+          <t>公共支撑</t>
+        </is>
+      </c>
+      <c r="C31" s="66" t="inlineStr">
+        <is>
+          <t>架构与非功能设计</t>
+        </is>
+      </c>
+      <c r="D31" s="66" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E31" s="67" t="n"/>
+      <c r="F31" s="66" t="inlineStr">
+        <is>
+          <t>UC权限与查询模型/资源验收/架构终稿/外部评审#1/M2</t>
+        </is>
+      </c>
+      <c r="G31" s="67" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H31" s="66" t="inlineStr">
+        <is>
+          <t>四层表结构/DDL/分层设计/迁移方案/安全与非功能设计</t>
+        </is>
+      </c>
+      <c r="I31" s="67" t="n">
+        <v>12</v>
+      </c>
+      <c r="J31" s="66" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K31" s="67" t="n"/>
+      <c r="L31" s="66" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M31" s="67" t="n"/>
+      <c r="N31" s="67" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="O31" s="66" t="inlineStr">
+        <is>
+          <t>3.3.2,3.3.3,3.3.4,3.3.5…</t>
+        </is>
+      </c>
+      <c r="P31" s="65" t="inlineStr">
+        <is>
+          <t>10/09</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="34" customHeight="1">
+      <c r="A32" s="65" t="inlineStr">
+        <is>
+          <t>G4</t>
+        </is>
+      </c>
+      <c r="B32" s="66" t="inlineStr">
+        <is>
+          <t>公共支撑</t>
+        </is>
+      </c>
+      <c r="C32" s="66" t="inlineStr">
+        <is>
+          <t>数据与测试基础</t>
+        </is>
+      </c>
+      <c r="D32" s="66" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E32" s="67" t="n"/>
+      <c r="F32" s="66" t="inlineStr">
+        <is>
+          <t>技术债偿还（A侧）</t>
+        </is>
+      </c>
+      <c r="G32" s="67" t="n">
+        <v>1</v>
+      </c>
+      <c r="H32" s="66" t="inlineStr">
+        <is>
+          <t>RAW/四层落地/SERVE物化/增量接入框架</t>
+        </is>
+      </c>
+      <c r="I32" s="67" t="n">
+        <v>3</v>
+      </c>
+      <c r="J32" s="66" t="inlineStr">
+        <is>
+          <t>测试计划/样本数据集</t>
+        </is>
+      </c>
+      <c r="K32" s="67" t="n">
+        <v>2</v>
+      </c>
+      <c r="L32" s="66" t="inlineStr">
+        <is>
+          <t>手册合稿/操作手册</t>
+        </is>
+      </c>
+      <c r="M32" s="67" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="N32" s="67" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="O32" s="66" t="inlineStr">
+        <is>
+          <t>5.1.6,4.2.4,4.2.7,5.2.9…</t>
+        </is>
+      </c>
+      <c r="P32" s="65" t="inlineStr">
+        <is>
+          <t>11/10</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="34" customHeight="1">
+      <c r="A33" s="65" t="inlineStr">
+        <is>
+          <t>G5</t>
+        </is>
+      </c>
+      <c r="B33" s="66" t="inlineStr">
+        <is>
+          <t>公共支撑</t>
+        </is>
+      </c>
+      <c r="C33" s="66" t="inlineStr">
+        <is>
+          <t>系统集成与CC真实数据迁移</t>
+        </is>
+      </c>
+      <c r="D33" s="66" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E33" s="67" t="n"/>
+      <c r="F33" s="66" t="inlineStr">
+        <is>
+          <t>M3端到端联调/全链路走查/CC界面适配/缺陷收敛/发布包/代码冻结M5</t>
+        </is>
+      </c>
+      <c r="G33" s="67" t="n">
+        <v>14</v>
+      </c>
+      <c r="H33" s="66" t="inlineStr">
+        <is>
+          <t>CC迁移演练/逐批对账/全量对账报告/预跑</t>
+        </is>
+      </c>
+      <c r="I33" s="67" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="J33" s="66" t="inlineStr">
+        <is>
+          <t>系统测试轮1+回归</t>
+        </is>
+      </c>
+      <c r="K33" s="67" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="L33" s="66" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M33" s="67" t="n"/>
+      <c r="N33" s="67" t="n">
+        <v>32</v>
+      </c>
+      <c r="O33" s="66" t="inlineStr">
+        <is>
+          <t>4.3.3,5.1.8,5.1.9,6.1.1…</t>
+        </is>
+      </c>
+      <c r="P33" s="65" t="inlineStr">
+        <is>
+          <t>12/01</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="34" customHeight="1">
+      <c r="A34" s="65" t="inlineStr">
+        <is>
+          <t>G6</t>
+        </is>
+      </c>
+      <c r="B34" s="66" t="inlineStr">
+        <is>
+          <t>公共支撑</t>
+        </is>
+      </c>
+      <c r="C34" s="66" t="inlineStr">
+        <is>
+          <t>系统测试与UAT</t>
+        </is>
+      </c>
+      <c r="D34" s="66" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E34" s="67" t="n"/>
+      <c r="F34" s="66" t="inlineStr">
+        <is>
+          <t>前端/应用缺陷修复</t>
+        </is>
+      </c>
+      <c r="G34" s="67" t="n">
+        <v>1</v>
+      </c>
+      <c r="H34" s="66" t="inlineStr">
+        <is>
+          <t>数据/服务缺陷修复</t>
+        </is>
+      </c>
+      <c r="I34" s="67" t="n">
+        <v>1</v>
+      </c>
+      <c r="J34" s="66" t="inlineStr">
+        <is>
+          <t>UAT脚本/全量测试/UAT组织/26项核对</t>
+        </is>
+      </c>
+      <c r="K34" s="67" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="L34" s="66" t="inlineStr">
+        <is>
+          <t>手册评审定稿/复盘</t>
+        </is>
+      </c>
+      <c r="M34" s="67" t="n">
+        <v>3</v>
+      </c>
+      <c r="N34" s="67" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="O34" s="66" t="inlineStr">
+        <is>
+          <t>7.2.1,7.2.4,4.4.6,5.3.8…</t>
+        </is>
+      </c>
+      <c r="P34" s="65" t="inlineStr">
+        <is>
+          <t>12/16</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="34" customHeight="1">
+      <c r="A35" s="65" t="inlineStr">
+        <is>
+          <t>G7</t>
+        </is>
+      </c>
+      <c r="B35" s="66" t="inlineStr">
+        <is>
+          <t>公共支撑</t>
+        </is>
+      </c>
+      <c r="C35" s="66" t="inlineStr">
+        <is>
+          <t>非功能专项验证</t>
+        </is>
+      </c>
+      <c r="D35" s="66" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E35" s="67" t="n"/>
+      <c r="F35" s="66" t="inlineStr">
+        <is>
+          <t>性能粗调/部署预演/性能专项/就绪评审/外部评审#2</t>
+        </is>
+      </c>
+      <c r="G35" s="67" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="H35" s="66" t="inlineStr">
+        <is>
+          <t>ADLS分层/迁移预跑/安全可靠性专项/数据核查</t>
+        </is>
+      </c>
+      <c r="I35" s="67" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="J35" s="66" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K35" s="67" t="n"/>
+      <c r="L35" s="66" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M35" s="67" t="n"/>
+      <c r="N35" s="67" t="n">
+        <v>12</v>
+      </c>
+      <c r="O35" s="66" t="inlineStr">
+        <is>
+          <t>5.1.4,5.4.1,7.2.2,7.2.3…</t>
+        </is>
+      </c>
+      <c r="P35" s="65" t="inlineStr">
+        <is>
+          <t>12/09</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="34" customHeight="1">
+      <c r="A36" s="65" t="inlineStr">
+        <is>
+          <t>G8</t>
+        </is>
+      </c>
+      <c r="B36" s="66" t="inlineStr">
+        <is>
+          <t>公共支撑</t>
+        </is>
+      </c>
+      <c r="C36" s="66" t="inlineStr">
+        <is>
+          <t>部署上线与值守</t>
+        </is>
+      </c>
+      <c r="D36" s="66" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E36" s="67" t="n"/>
+      <c r="F36" s="66" t="inlineStr">
+        <is>
+          <t>生产部署/冒烟验证/应用侧值守</t>
+        </is>
+      </c>
+      <c r="G36" s="67" t="n">
+        <v>5</v>
+      </c>
+      <c r="H36" s="66" t="inlineStr">
+        <is>
+          <t>CC全量迁移/作业启动/数据侧值守</t>
+        </is>
+      </c>
+      <c r="I36" s="67" t="n">
+        <v>5</v>
+      </c>
+      <c r="J36" s="66" t="inlineStr">
+        <is>
+          <t>上线支持/业务确认</t>
+        </is>
+      </c>
+      <c r="K36" s="67" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="L36" s="66" t="inlineStr">
+        <is>
+          <t>交付物核对</t>
+        </is>
+      </c>
+      <c r="M36" s="67" t="n">
+        <v>1</v>
+      </c>
+      <c r="N36" s="67" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="O36" s="66" t="inlineStr">
+        <is>
+          <t>8.1.1,8.1.4,8.2.5,8.1.2…</t>
+        </is>
+      </c>
+      <c r="P36" s="65" t="inlineStr">
+        <is>
+          <t>12/16</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="34" customHeight="1">
+      <c r="A37" s="65" t="inlineStr">
+        <is>
+          <t>G9</t>
+        </is>
+      </c>
+      <c r="B37" s="66" t="inlineStr">
+        <is>
+          <t>公共支撑</t>
+        </is>
+      </c>
+      <c r="C37" s="66" t="inlineStr">
+        <is>
+          <t>项目管理（Mark）</t>
+        </is>
+      </c>
+      <c r="D37" s="66" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E37" s="67" t="n"/>
+      <c r="F37" s="66" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G37" s="67" t="n"/>
+      <c r="H37" s="66" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I37" s="67" t="n"/>
+      <c r="J37" s="66" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K37" s="67" t="n"/>
+      <c r="L37" s="66" t="inlineStr">
+        <is>
+          <t>会议纪要与项目文档整理（配合PM）</t>
+        </is>
+      </c>
+      <c r="M37" s="67" t="n">
+        <v>1</v>
+      </c>
+      <c r="N37" s="67" t="n">
+        <v>16</v>
+      </c>
+      <c r="O37" s="66" t="inlineStr">
+        <is>
+          <t>1.1.1,1.2.1,1.2.2,1.2.3…</t>
+        </is>
+      </c>
+      <c r="P37" s="65" t="inlineStr">
+        <is>
+          <t>12/16</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="8" t="inlineStr">
+        <is>
+          <t>合计</t>
+        </is>
+      </c>
+      <c r="B38" s="8" t="inlineStr"/>
+      <c r="C38" s="8" t="inlineStr">
+        <is>
+          <t>26项功能 + 9类公共支撑</t>
+        </is>
+      </c>
+      <c r="D38" s="8" t="inlineStr">
+        <is>
+          <t>Mandy·BA</t>
+        </is>
+      </c>
+      <c r="E38" s="44" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="F38" s="8" t="inlineStr">
+        <is>
+          <t>Wade（开发A）</t>
+        </is>
+      </c>
+      <c r="G38" s="44" t="n">
+        <v>60</v>
+      </c>
+      <c r="H38" s="8" t="inlineStr">
+        <is>
+          <t>DevB（开发B）</t>
+        </is>
+      </c>
+      <c r="I38" s="44" t="n">
+        <v>60</v>
+      </c>
+      <c r="J38" s="8" t="inlineStr">
+        <is>
+          <t>Mandy·测试</t>
+        </is>
+      </c>
+      <c r="K38" s="44" t="n">
+        <v>29.5</v>
+      </c>
+      <c r="L38" s="8" t="inlineStr">
+        <is>
+          <t>Mandy·文档</t>
+        </is>
+      </c>
+      <c r="M38" s="44" t="n">
+        <v>10</v>
+      </c>
+      <c r="N38" s="44" t="n">
+        <v>185</v>
+      </c>
+      <c r="O38" s="8" t="inlineStr"/>
+      <c r="P38" s="8" t="inlineStr">
+        <is>
+          <t>PM Mark 15.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="68" t="inlineStr">
+        <is>
+          <t>对账：Mandy 50（BA 10.5 + 测试 29.5 + 文档 10.0）+ Wade 60 + DevB 60 + PM 15 = 185人天，与「WBS分解」「资源负荷与日历」完全一致；开发人天按关联WBS任务实际工作量分摊（共享任务按功能均分）；人天为空=该角色此功能无直接投入（工作量计入公共支撑行）</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A2:P38"/>
+  <mergeCells count="1">
+    <mergeCell ref="A1:P1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
     <tabColor rgb="00FFC000"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
@@ -13226,7 +15840,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="0070AD47"/>
@@ -13324,17 +15938,17 @@
           <t>Mark</t>
         </is>
       </c>
-      <c r="B3" s="19" t="n">
+      <c r="B3" s="46" t="n">
         <v>15</v>
       </c>
-      <c r="C3" s="19" t="n"/>
-      <c r="D3" s="19" t="n"/>
-      <c r="E3" s="19" t="n"/>
-      <c r="F3" s="19" t="n"/>
-      <c r="G3" s="19" t="n"/>
-      <c r="H3" s="19" t="n"/>
-      <c r="I3" s="19" t="n"/>
-      <c r="J3" s="37" t="n">
+      <c r="C3" s="46" t="n"/>
+      <c r="D3" s="46" t="n"/>
+      <c r="E3" s="46" t="n"/>
+      <c r="F3" s="46" t="n"/>
+      <c r="G3" s="46" t="n"/>
+      <c r="H3" s="46" t="n"/>
+      <c r="I3" s="46" t="n"/>
+      <c r="J3" s="69" t="n">
         <v>15</v>
       </c>
       <c r="K3" t="inlineStr">
@@ -13349,29 +15963,29 @@
           <t>Mandy</t>
         </is>
       </c>
-      <c r="B4" s="19" t="n">
+      <c r="B4" s="46" t="n">
         <v>1</v>
       </c>
-      <c r="C4" s="19" t="n">
+      <c r="C4" s="46" t="n">
         <v>13</v>
       </c>
-      <c r="D4" s="19" t="n"/>
-      <c r="E4" s="19" t="n">
+      <c r="D4" s="46" t="n"/>
+      <c r="E4" s="46" t="n">
         <v>6.5</v>
       </c>
-      <c r="F4" s="19" t="n">
+      <c r="F4" s="46" t="n">
         <v>12.5</v>
       </c>
-      <c r="G4" s="19" t="n">
+      <c r="G4" s="46" t="n">
         <v>8.5</v>
       </c>
-      <c r="H4" s="19" t="n">
+      <c r="H4" s="46" t="n">
         <v>5</v>
       </c>
-      <c r="I4" s="19" t="n">
+      <c r="I4" s="46" t="n">
         <v>3.5</v>
       </c>
-      <c r="J4" s="37" t="n">
+      <c r="J4" s="69" t="n">
         <v>50</v>
       </c>
       <c r="K4" t="inlineStr">
@@ -13386,27 +16000,27 @@
           <t>Wade</t>
         </is>
       </c>
-      <c r="B5" s="19" t="n"/>
-      <c r="C5" s="19" t="n"/>
-      <c r="D5" s="19" t="n">
+      <c r="B5" s="46" t="n"/>
+      <c r="C5" s="46" t="n"/>
+      <c r="D5" s="46" t="n">
         <v>13.5</v>
       </c>
-      <c r="E5" s="19" t="n">
+      <c r="E5" s="46" t="n">
         <v>10</v>
       </c>
-      <c r="F5" s="19" t="n">
+      <c r="F5" s="46" t="n">
         <v>14.5</v>
       </c>
-      <c r="G5" s="19" t="n">
+      <c r="G5" s="46" t="n">
         <v>11</v>
       </c>
-      <c r="H5" s="19" t="n">
+      <c r="H5" s="46" t="n">
         <v>6</v>
       </c>
-      <c r="I5" s="19" t="n">
+      <c r="I5" s="46" t="n">
         <v>5</v>
       </c>
-      <c r="J5" s="37" t="n">
+      <c r="J5" s="69" t="n">
         <v>60</v>
       </c>
       <c r="K5" t="inlineStr">
@@ -13421,27 +16035,27 @@
           <t>DevB</t>
         </is>
       </c>
-      <c r="B6" s="19" t="n"/>
-      <c r="C6" s="19" t="n"/>
-      <c r="D6" s="19" t="n">
+      <c r="B6" s="46" t="n"/>
+      <c r="C6" s="46" t="n"/>
+      <c r="D6" s="46" t="n">
         <v>14</v>
       </c>
-      <c r="E6" s="19" t="n">
+      <c r="E6" s="46" t="n">
         <v>10</v>
       </c>
-      <c r="F6" s="19" t="n">
+      <c r="F6" s="46" t="n">
         <v>14.5</v>
       </c>
-      <c r="G6" s="19" t="n">
+      <c r="G6" s="46" t="n">
         <v>11</v>
       </c>
-      <c r="H6" s="19" t="n">
+      <c r="H6" s="46" t="n">
         <v>5.5</v>
       </c>
-      <c r="I6" s="19" t="n">
+      <c r="I6" s="46" t="n">
         <v>5</v>
       </c>
-      <c r="J6" s="37" t="n">
+      <c r="J6" s="69" t="n">
         <v>60</v>
       </c>
       <c r="K6" t="inlineStr">
@@ -13456,7 +16070,7 @@
           <t>合计</t>
         </is>
       </c>
-      <c r="J7" s="39" t="n">
+      <c r="J7" s="70" t="n">
         <v>185</v>
       </c>
       <c r="K7" t="inlineStr">
@@ -13465,7 +16079,6 @@
         </is>
       </c>
     </row>
-    <row r="8"/>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
@@ -13578,8 +16191,8 @@
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="B14:K14"/>
     <mergeCell ref="B11:K11"/>
-    <mergeCell ref="B14:K14"/>
     <mergeCell ref="B17:K17"/>
     <mergeCell ref="B18:K18"/>
     <mergeCell ref="B16:K16"/>
@@ -13594,7 +16207,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00A6A6A6"/>
@@ -14294,7 +16907,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00ED7D31"/>
@@ -14435,7 +17048,7 @@
           <t>任务完成率</t>
         </is>
       </c>
-      <c r="B10" s="41">
+      <c r="B10" s="71">
         <f>IFERROR(COUNTIF('WBS分解'!$L$4:$L$164,"已完成")/COUNTA('WBS分解'!$A$4:$A$164),0)</f>
         <v/>
       </c>
@@ -14451,7 +17064,7 @@
           <t>整体平均进度</t>
         </is>
       </c>
-      <c r="B11" s="41">
+      <c r="B11" s="71">
         <f>AVERAGE('WBS分解'!$M$4:$M$164)</f>
         <v/>
       </c>
@@ -14467,7 +17080,7 @@
           <t>工作量合计（人天·仅三级工作包）</t>
         </is>
       </c>
-      <c r="B12" s="19">
+      <c r="B12" s="46">
         <f>SUMPRODUCT(('WBS分解'!$C$4:$C$164=3)*'WBS分解'!$I$4:$I$164)</f>
         <v/>
       </c>
@@ -14483,7 +17096,7 @@
           <t>Mark 工作量（人天）</t>
         </is>
       </c>
-      <c r="B13" s="19">
+      <c r="B13" s="46">
         <f>SUMPRODUCT(('WBS分解'!$C$4:$C$164=3)*('WBS分解'!$E$4:$E$164="Mark")*'WBS分解'!$I$4:$I$164)</f>
         <v/>
       </c>
@@ -14499,7 +17112,7 @@
           <t>Mandy 工作量（人天）</t>
         </is>
       </c>
-      <c r="B14" s="19">
+      <c r="B14" s="46">
         <f>SUMPRODUCT(('WBS分解'!$C$4:$C$164=3)*('WBS分解'!$E$4:$E$164="Mandy")*'WBS分解'!$I$4:$I$164)</f>
         <v/>
       </c>
@@ -14515,7 +17128,7 @@
           <t>Wade 工作量（人天）</t>
         </is>
       </c>
-      <c r="B15" s="19">
+      <c r="B15" s="46">
         <f>SUMPRODUCT(('WBS分解'!$C$4:$C$164=3)*('WBS分解'!$E$4:$E$164="Wade")*'WBS分解'!$I$4:$I$164)</f>
         <v/>
       </c>
@@ -14531,7 +17144,7 @@
           <t>DevB 工作量（人天）</t>
         </is>
       </c>
-      <c r="B16" s="19">
+      <c r="B16" s="46">
         <f>SUMPRODUCT(('WBS分解'!$C$4:$C$164=3)*('WBS分解'!$E$4:$E$164="DevB")*'WBS分解'!$I$4:$I$164)</f>
         <v/>
       </c>
@@ -14547,7 +17160,7 @@
           <t>预算合计（元）</t>
         </is>
       </c>
-      <c r="B17" s="19">
+      <c r="B17" s="46">
         <f>SUM('WBS分解'!$O$4:$O$164)</f>
         <v/>
       </c>
@@ -14557,7 +17170,6 @@
         </is>
       </c>
     </row>
-    <row r="18"/>
     <row r="19">
       <c r="A19" s="42" t="inlineStr">
         <is>

--- a/RIMS项目WBS工作分解_AI Native版.xlsx
+++ b/RIMS项目WBS工作分解_AI Native版.xlsx
@@ -754,7 +754,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B31"/>
+  <dimension ref="A1:B32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1091,6 +1091,18 @@
         </is>
       </c>
       <c r="B31" s="4" t="inlineStr">
+        <is>
+          <t>按功能维度查看：26项功能×（BA/开发A/开发B/测试/文档）五类角色各自的工作内容与人天，另有9类公共支撑行（初始化/架构/集成/专项/上线/管理）；底部与185人天自动对账，可与按开发顺序的「WBS分解」页对照使用</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="30" customHeight="1">
+      <c r="A32" s="38" t="inlineStr">
+        <is>
+          <t>功能视角分解</t>
+        </is>
+      </c>
+      <c r="B32" s="4" t="inlineStr">
         <is>
           <t>按功能维度查看：26项功能×（BA/开发A/开发B/测试/文档）五类角色各自的工作内容与人天，另有9类公共支撑行（初始化/架构/集成/专项/上线/管理）；底部与185人天自动对账，可与按开发顺序的「WBS分解」页对照使用</t>
         </is>
@@ -13269,7 +13281,7 @@
       </c>
       <c r="L3" s="31" t="inlineStr">
         <is>
-          <t>用户手册F01章</t>
+          <t>SLC文档F01章</t>
         </is>
       </c>
       <c r="M3" s="49" t="n">
@@ -13339,7 +13351,7 @@
       </c>
       <c r="L4" s="31" t="inlineStr">
         <is>
-          <t>用户手册F01章</t>
+          <t>SLC文档F01章</t>
         </is>
       </c>
       <c r="M4" s="49" t="n">
@@ -13407,7 +13419,7 @@
       </c>
       <c r="L5" s="31" t="inlineStr">
         <is>
-          <t>用户手册F01章</t>
+          <t>SLC文档F01章</t>
         </is>
       </c>
       <c r="M5" s="49" t="n">
@@ -13473,7 +13485,7 @@
       <c r="K6" s="49" t="n"/>
       <c r="L6" s="31" t="inlineStr">
         <is>
-          <t>用户手册F01章</t>
+          <t>SLC文档F01章</t>
         </is>
       </c>
       <c r="M6" s="49" t="n"/>
@@ -13537,7 +13549,7 @@
       <c r="K7" s="49" t="n"/>
       <c r="L7" s="31" t="inlineStr">
         <is>
-          <t>用户手册F01章</t>
+          <t>SLC文档F01章</t>
         </is>
       </c>
       <c r="M7" s="49" t="n"/>
@@ -13603,7 +13615,7 @@
       </c>
       <c r="L8" s="51" t="inlineStr">
         <is>
-          <t>用户手册F02章</t>
+          <t>SLC文档F02章</t>
         </is>
       </c>
       <c r="M8" s="52" t="n">
@@ -13669,7 +13681,7 @@
       </c>
       <c r="L9" s="51" t="inlineStr">
         <is>
-          <t>用户手册F02章</t>
+          <t>SLC文档F02章</t>
         </is>
       </c>
       <c r="M9" s="52" t="n"/>
@@ -13737,7 +13749,7 @@
       </c>
       <c r="L10" s="33" t="inlineStr">
         <is>
-          <t>用户手册F03章</t>
+          <t>SLC文档F03章</t>
         </is>
       </c>
       <c r="M10" s="48" t="n">
@@ -13805,7 +13817,7 @@
       </c>
       <c r="L11" s="33" t="inlineStr">
         <is>
-          <t>用户手册F03章</t>
+          <t>SLC文档F03章</t>
         </is>
       </c>
       <c r="M11" s="48" t="n"/>
@@ -13871,7 +13883,7 @@
       </c>
       <c r="L12" s="54" t="inlineStr">
         <is>
-          <t>用户手册F04章</t>
+          <t>SLC文档F04章</t>
         </is>
       </c>
       <c r="M12" s="55" t="n"/>
@@ -13935,7 +13947,7 @@
       </c>
       <c r="L13" s="54" t="inlineStr">
         <is>
-          <t>用户手册F04章</t>
+          <t>SLC文档F04章</t>
         </is>
       </c>
       <c r="M13" s="55" t="n"/>
@@ -13997,7 +14009,7 @@
       <c r="K14" s="55" t="n"/>
       <c r="L14" s="54" t="inlineStr">
         <is>
-          <t>用户手册F04章</t>
+          <t>SLC文档F04章</t>
         </is>
       </c>
       <c r="M14" s="55" t="n"/>
@@ -14059,7 +14071,7 @@
       <c r="K15" s="55" t="n"/>
       <c r="L15" s="54" t="inlineStr">
         <is>
-          <t>用户手册F04章</t>
+          <t>SLC文档F04章</t>
         </is>
       </c>
       <c r="M15" s="55" t="n"/>
@@ -14125,7 +14137,7 @@
       </c>
       <c r="L16" s="57" t="inlineStr">
         <is>
-          <t>用户手册F05章</t>
+          <t>SLC文档F05章</t>
         </is>
       </c>
       <c r="M16" s="58" t="n"/>
@@ -14189,7 +14201,7 @@
       </c>
       <c r="L17" s="57" t="inlineStr">
         <is>
-          <t>用户手册F05章</t>
+          <t>SLC文档F05章</t>
         </is>
       </c>
       <c r="M17" s="58" t="n"/>
@@ -14253,7 +14265,7 @@
       </c>
       <c r="L18" s="57" t="inlineStr">
         <is>
-          <t>用户手册F05章</t>
+          <t>SLC文档F05章</t>
         </is>
       </c>
       <c r="M18" s="58" t="n"/>
@@ -14317,7 +14329,7 @@
       </c>
       <c r="L19" s="57" t="inlineStr">
         <is>
-          <t>用户手册F05章</t>
+          <t>SLC文档F05章</t>
         </is>
       </c>
       <c r="M19" s="58" t="n"/>
@@ -14379,7 +14391,7 @@
       <c r="K20" s="58" t="n"/>
       <c r="L20" s="57" t="inlineStr">
         <is>
-          <t>用户手册F05章</t>
+          <t>SLC文档F05章</t>
         </is>
       </c>
       <c r="M20" s="58" t="n"/>
@@ -14445,7 +14457,7 @@
       </c>
       <c r="L21" s="60" t="inlineStr">
         <is>
-          <t>用户手册F06章</t>
+          <t>SLC文档F06章</t>
         </is>
       </c>
       <c r="M21" s="61" t="n"/>
@@ -14509,7 +14521,7 @@
       </c>
       <c r="L22" s="60" t="inlineStr">
         <is>
-          <t>用户手册F06章</t>
+          <t>SLC文档F06章</t>
         </is>
       </c>
       <c r="M22" s="61" t="n"/>
@@ -14573,7 +14585,7 @@
       </c>
       <c r="L23" s="60" t="inlineStr">
         <is>
-          <t>用户手册F06章</t>
+          <t>SLC文档F06章</t>
         </is>
       </c>
       <c r="M23" s="61" t="n"/>
@@ -14639,7 +14651,7 @@
       </c>
       <c r="L24" s="63" t="inlineStr">
         <is>
-          <t>用户手册F08章</t>
+          <t>SLC文档F08章</t>
         </is>
       </c>
       <c r="M24" s="64" t="n">
@@ -14705,7 +14717,7 @@
       </c>
       <c r="L25" s="63" t="inlineStr">
         <is>
-          <t>用户手册F08章</t>
+          <t>SLC文档F08章</t>
         </is>
       </c>
       <c r="M25" s="64" t="n">
@@ -14771,7 +14783,7 @@
       </c>
       <c r="L26" s="63" t="inlineStr">
         <is>
-          <t>用户手册F08章</t>
+          <t>SLC文档F08章</t>
         </is>
       </c>
       <c r="M26" s="64" t="n">
@@ -14835,7 +14847,7 @@
       <c r="K27" s="64" t="n"/>
       <c r="L27" s="63" t="inlineStr">
         <is>
-          <t>用户手册F08章</t>
+          <t>SLC文档F08章</t>
         </is>
       </c>
       <c r="M27" s="64" t="n"/>
@@ -14897,7 +14909,7 @@
       <c r="K28" s="64" t="n"/>
       <c r="L28" s="63" t="inlineStr">
         <is>
-          <t>用户手册F08章</t>
+          <t>SLC文档F08章</t>
         </is>
       </c>
       <c r="M28" s="64" t="n"/>

--- a/RIMS项目WBS工作分解_AI Native版.xlsx
+++ b/RIMS项目WBS工作分解_AI Native版.xlsx
@@ -754,7 +754,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B32"/>
+  <dimension ref="A1:B33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1103,6 +1103,18 @@
         </is>
       </c>
       <c r="B32" s="4" t="inlineStr">
+        <is>
+          <t>按功能维度查看：26项功能×（BA/开发A/开发B/测试/文档）五类角色各自的工作内容与人天，另有9类公共支撑行（初始化/架构/集成/专项/上线/管理）；底部与185人天自动对账，可与按开发顺序的「WBS分解」页对照使用</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="30" customHeight="1">
+      <c r="A33" s="38" t="inlineStr">
+        <is>
+          <t>功能视角分解</t>
+        </is>
+      </c>
+      <c r="B33" s="4" t="inlineStr">
         <is>
           <t>按功能维度查看：26项功能×（BA/开发A/开发B/测试/文档）五类角色各自的工作内容与人天，另有9类公共支撑行（初始化/架构/集成/专项/上线/管理）；底部与185人天自动对账，可与按开发顺序的「WBS分解」页对照使用</t>
         </is>
@@ -13281,7 +13293,7 @@
       </c>
       <c r="L3" s="31" t="inlineStr">
         <is>
-          <t>SLC文档F01章</t>
+          <t>SLC文档</t>
         </is>
       </c>
       <c r="M3" s="49" t="n">
@@ -13351,7 +13363,7 @@
       </c>
       <c r="L4" s="31" t="inlineStr">
         <is>
-          <t>SLC文档F01章</t>
+          <t>SLC文档</t>
         </is>
       </c>
       <c r="M4" s="49" t="n">
@@ -13419,7 +13431,7 @@
       </c>
       <c r="L5" s="31" t="inlineStr">
         <is>
-          <t>SLC文档F01章</t>
+          <t>SLC文档</t>
         </is>
       </c>
       <c r="M5" s="49" t="n">
@@ -13485,7 +13497,7 @@
       <c r="K6" s="49" t="n"/>
       <c r="L6" s="31" t="inlineStr">
         <is>
-          <t>SLC文档F01章</t>
+          <t>SLC文档</t>
         </is>
       </c>
       <c r="M6" s="49" t="n"/>
@@ -13549,7 +13561,7 @@
       <c r="K7" s="49" t="n"/>
       <c r="L7" s="31" t="inlineStr">
         <is>
-          <t>SLC文档F01章</t>
+          <t>SLC文档</t>
         </is>
       </c>
       <c r="M7" s="49" t="n"/>
@@ -13615,7 +13627,7 @@
       </c>
       <c r="L8" s="51" t="inlineStr">
         <is>
-          <t>SLC文档F02章</t>
+          <t>SLC文档</t>
         </is>
       </c>
       <c r="M8" s="52" t="n">
@@ -13681,7 +13693,7 @@
       </c>
       <c r="L9" s="51" t="inlineStr">
         <is>
-          <t>SLC文档F02章</t>
+          <t>SLC文档</t>
         </is>
       </c>
       <c r="M9" s="52" t="n"/>
@@ -13749,7 +13761,7 @@
       </c>
       <c r="L10" s="33" t="inlineStr">
         <is>
-          <t>SLC文档F03章</t>
+          <t>SLC文档</t>
         </is>
       </c>
       <c r="M10" s="48" t="n">
@@ -13817,7 +13829,7 @@
       </c>
       <c r="L11" s="33" t="inlineStr">
         <is>
-          <t>SLC文档F03章</t>
+          <t>SLC文档</t>
         </is>
       </c>
       <c r="M11" s="48" t="n"/>
@@ -13883,7 +13895,7 @@
       </c>
       <c r="L12" s="54" t="inlineStr">
         <is>
-          <t>SLC文档F04章</t>
+          <t>SLC文档</t>
         </is>
       </c>
       <c r="M12" s="55" t="n"/>
@@ -13947,7 +13959,7 @@
       </c>
       <c r="L13" s="54" t="inlineStr">
         <is>
-          <t>SLC文档F04章</t>
+          <t>SLC文档</t>
         </is>
       </c>
       <c r="M13" s="55" t="n"/>
@@ -14009,7 +14021,7 @@
       <c r="K14" s="55" t="n"/>
       <c r="L14" s="54" t="inlineStr">
         <is>
-          <t>SLC文档F04章</t>
+          <t>SLC文档</t>
         </is>
       </c>
       <c r="M14" s="55" t="n"/>
@@ -14071,7 +14083,7 @@
       <c r="K15" s="55" t="n"/>
       <c r="L15" s="54" t="inlineStr">
         <is>
-          <t>SLC文档F04章</t>
+          <t>SLC文档</t>
         </is>
       </c>
       <c r="M15" s="55" t="n"/>
@@ -14137,7 +14149,7 @@
       </c>
       <c r="L16" s="57" t="inlineStr">
         <is>
-          <t>SLC文档F05章</t>
+          <t>SLC文档</t>
         </is>
       </c>
       <c r="M16" s="58" t="n"/>
@@ -14201,7 +14213,7 @@
       </c>
       <c r="L17" s="57" t="inlineStr">
         <is>
-          <t>SLC文档F05章</t>
+          <t>SLC文档</t>
         </is>
       </c>
       <c r="M17" s="58" t="n"/>
@@ -14265,7 +14277,7 @@
       </c>
       <c r="L18" s="57" t="inlineStr">
         <is>
-          <t>SLC文档F05章</t>
+          <t>SLC文档</t>
         </is>
       </c>
       <c r="M18" s="58" t="n"/>
@@ -14329,7 +14341,7 @@
       </c>
       <c r="L19" s="57" t="inlineStr">
         <is>
-          <t>SLC文档F05章</t>
+          <t>SLC文档</t>
         </is>
       </c>
       <c r="M19" s="58" t="n"/>
@@ -14391,7 +14403,7 @@
       <c r="K20" s="58" t="n"/>
       <c r="L20" s="57" t="inlineStr">
         <is>
-          <t>SLC文档F05章</t>
+          <t>SLC文档</t>
         </is>
       </c>
       <c r="M20" s="58" t="n"/>
@@ -14457,7 +14469,7 @@
       </c>
       <c r="L21" s="60" t="inlineStr">
         <is>
-          <t>SLC文档F06章</t>
+          <t>SLC文档</t>
         </is>
       </c>
       <c r="M21" s="61" t="n"/>
@@ -14521,7 +14533,7 @@
       </c>
       <c r="L22" s="60" t="inlineStr">
         <is>
-          <t>SLC文档F06章</t>
+          <t>SLC文档</t>
         </is>
       </c>
       <c r="M22" s="61" t="n"/>
@@ -14585,7 +14597,7 @@
       </c>
       <c r="L23" s="60" t="inlineStr">
         <is>
-          <t>SLC文档F06章</t>
+          <t>SLC文档</t>
         </is>
       </c>
       <c r="M23" s="61" t="n"/>
@@ -14651,7 +14663,7 @@
       </c>
       <c r="L24" s="63" t="inlineStr">
         <is>
-          <t>SLC文档F08章</t>
+          <t>SLC文档</t>
         </is>
       </c>
       <c r="M24" s="64" t="n">
@@ -14717,7 +14729,7 @@
       </c>
       <c r="L25" s="63" t="inlineStr">
         <is>
-          <t>SLC文档F08章</t>
+          <t>SLC文档</t>
         </is>
       </c>
       <c r="M25" s="64" t="n">
@@ -14783,7 +14795,7 @@
       </c>
       <c r="L26" s="63" t="inlineStr">
         <is>
-          <t>SLC文档F08章</t>
+          <t>SLC文档</t>
         </is>
       </c>
       <c r="M26" s="64" t="n">
@@ -14847,7 +14859,7 @@
       <c r="K27" s="64" t="n"/>
       <c r="L27" s="63" t="inlineStr">
         <is>
-          <t>SLC文档F08章</t>
+          <t>SLC文档</t>
         </is>
       </c>
       <c r="M27" s="64" t="n"/>
@@ -14909,7 +14921,7 @@
       <c r="K28" s="64" t="n"/>
       <c r="L28" s="63" t="inlineStr">
         <is>
-          <t>SLC文档F08章</t>
+          <t>SLC文档</t>
         </is>
       </c>
       <c r="M28" s="64" t="n"/>

--- a/RIMS项目WBS工作分解_AI Native版.xlsx
+++ b/RIMS项目WBS工作分解_AI Native版.xlsx
@@ -754,7 +754,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B33"/>
+  <dimension ref="A1:B34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -929,7 +929,7 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>功能（26项）与非功能统一排程：需求期定义NFR基线（2.3.1：性能/安全/合规/可用性/容量）→设计期定方案（3.2.8）→集成期初验（6.3.2）→测试期专项验证（7.1.1全量+7.2.3性能专项+7.2.6安全可靠性专项）</t>
+          <t>功能（26项）与非功能统一排程：NFR基线随SRS一并冻结（2.2.1，M1=9/24）→NFR测试可执行化（2.3.1）→设计期定方案（3.2.8）→集成期初验（6.3.2）→专项验证先于UAT完成（7.2.3性能/7.2.6安全可靠性，12/3~12/4）→生产就绪评审确认达标（7.2.7，12/9）</t>
         </is>
       </c>
     </row>
@@ -1115,6 +1115,18 @@
         </is>
       </c>
       <c r="B33" s="4" t="inlineStr">
+        <is>
+          <t>按功能维度查看：26项功能×（BA/开发A/开发B/测试/文档）五类角色各自的工作内容与人天，另有9类公共支撑行（初始化/架构/集成/专项/上线/管理）；底部与185人天自动对账，可与按开发顺序的「WBS分解」页对照使用</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="30" customHeight="1">
+      <c r="A34" s="38" t="inlineStr">
+        <is>
+          <t>功能视角分解</t>
+        </is>
+      </c>
+      <c r="B34" s="4" t="inlineStr">
         <is>
           <t>按功能维度查看：26项功能×（BA/开发A/开发B/测试/文档）五类角色各自的工作内容与人天，另有9类公共支撑行（初始化/架构/集成/专项/上线/管理）；底部与185人天自动对账，可与按开发顺序的「WBS分解」页对照使用</t>
         </is>
@@ -2360,7 +2372,7 @@
       </c>
       <c r="B21" s="22" t="inlineStr">
         <is>
-          <t>AI生成SRS初稿（数据流图/归档范围矩阵/保留期矩阵）+人工修订</t>
+          <t>AI生成SRS初稿（26项功能+非功能需求NFR：数据流图/归档范围矩阵/保留期矩阵+性能·安全·合规·可用性·容量指标）+人工修订</t>
         </is>
       </c>
       <c r="C21" s="15" t="n">
@@ -2368,7 +2380,7 @@
       </c>
       <c r="D21" s="17" t="inlineStr">
         <is>
-          <t>SRS V1.0</t>
+          <t>SRS V1.0（含NFR基线）</t>
         </is>
       </c>
       <c r="E21" s="15" t="inlineStr">
@@ -2554,7 +2566,7 @@
       </c>
       <c r="B24" s="22" t="inlineStr">
         <is>
-          <t>非功能需求梳理与验收指标定义（性能：检索响应/导出吞吐；安全：加密/越权/审计；合规：数据不出境；可用性：备份RPO/RTO；容量：600~800表增长）</t>
+          <t>NFR测试可执行化（将SRS中NFR基线细化为可测验收标准：检索响应/导出吞吐/并发/越权与掩码旁路用例集/RPO·RTO/容量上限，供6.3.2/7.2.3/7.2.6对照）</t>
         </is>
       </c>
       <c r="C24" s="15" t="n">
@@ -2562,7 +2574,7 @@
       </c>
       <c r="D24" s="17" t="inlineStr">
         <is>
-          <t>非功能需求指标清单（NFR基线）</t>
+          <t>NFR可测验收标准清单</t>
         </is>
       </c>
       <c r="E24" s="15" t="inlineStr">
@@ -2606,7 +2618,11 @@
         </is>
       </c>
       <c r="O24" s="21" t="n"/>
-      <c r="P24" s="21" t="n"/>
+      <c r="P24" s="21" t="inlineStr">
+        <is>
+          <t>NFR基线已随SRS于M1冻结；本任务只做测试化转译，不改变基线</t>
+        </is>
+      </c>
       <c r="Q24" s="17" t="inlineStr">
         <is>
           <t>与26项功能同一基线管理，后续设计/测试逐项对应</t>
@@ -3771,7 +3787,7 @@
       </c>
       <c r="B43" s="22" t="inlineStr">
         <is>
-          <t>F04与非功能设计定稿（加密/密钥/备份灾备方案+性能容量与「数据不出境」合规基线，对应2.3.1 NFR）</t>
+          <t>F04与非功能设计定稿（加密/密钥/备份灾备方案+性能容量与「数据不出境」合规基线，对应2.2.1 NFR基线）</t>
         </is>
       </c>
       <c r="C43" s="15" t="n">
@@ -3806,7 +3822,7 @@
       </c>
       <c r="K43" s="17" t="inlineStr">
         <is>
-          <t>3.2.5;2.3.1</t>
+          <t>3.2.5;2.2.2</t>
         </is>
       </c>
       <c r="L43" s="15" t="inlineStr">
@@ -9761,7 +9777,7 @@
       </c>
       <c r="B138" s="22" t="inlineStr">
         <is>
-          <t>系统测试全量执行（26项逐项+非功能指标验证，CC真实数据：检索/预览/导出/处置/审计）</t>
+          <t>系统测试全量执行（26项逐项+汇总NFR专项结果（7.2.3/7.2.6），CC真实数据：检索/预览/导出/处置/审计）</t>
         </is>
       </c>
       <c r="C138" s="15" t="n">
@@ -10161,10 +10177,10 @@
         </is>
       </c>
       <c r="F144" s="45" t="n">
-        <v>46359</v>
+        <v>46363</v>
       </c>
       <c r="G144" s="45" t="n">
-        <v>46360</v>
+        <v>46364</v>
       </c>
       <c r="H144" s="15" t="n">
         <v>2</v>
@@ -10196,7 +10212,11 @@
         </is>
       </c>
       <c r="O144" s="21" t="n"/>
-      <c r="P144" s="21" t="n"/>
+      <c r="P144" s="21" t="inlineStr">
+        <is>
+          <t>12/7~12/8与UAT并行（staging环境，互不冲突）；回退预案验证</t>
+        </is>
+      </c>
       <c r="Q144" s="17" t="inlineStr"/>
     </row>
     <row r="145">
@@ -10224,10 +10244,10 @@
         </is>
       </c>
       <c r="F145" s="45" t="n">
-        <v>46363</v>
+        <v>46359</v>
       </c>
       <c r="G145" s="45" t="n">
-        <v>46364</v>
+        <v>46360</v>
       </c>
       <c r="H145" s="15" t="n">
         <v>2</v>
@@ -10242,7 +10262,7 @@
       </c>
       <c r="K145" s="17" t="inlineStr">
         <is>
-          <t>7.2.2</t>
+          <t>6.1.6</t>
         </is>
       </c>
       <c r="L145" s="15" t="inlineStr">
@@ -10259,7 +10279,11 @@
         </is>
       </c>
       <c r="O145" s="21" t="n"/>
-      <c r="P145" s="21" t="n"/>
+      <c r="P145" s="21" t="inlineStr">
+        <is>
+          <t>★先于UAT（12/7）完成：不达标则调优复测后再组织UAT；结果提交M6与生产就绪评审</t>
+        </is>
+      </c>
       <c r="Q145" s="17" t="inlineStr">
         <is>
           <t>不达标项现场调优并复测</t>
@@ -10354,10 +10378,10 @@
         </is>
       </c>
       <c r="F147" s="45" t="n">
-        <v>46359</v>
+        <v>46363</v>
       </c>
       <c r="G147" s="45" t="n">
-        <v>46360</v>
+        <v>46364</v>
       </c>
       <c r="H147" s="15" t="n">
         <v>2</v>
@@ -10389,7 +10413,11 @@
         </is>
       </c>
       <c r="O147" s="21" t="n"/>
-      <c r="P147" s="21" t="n"/>
+      <c r="P147" s="21" t="inlineStr">
+        <is>
+          <t>12/7~12/8与UAT并行；全流程dry-run</t>
+        </is>
+      </c>
       <c r="Q147" s="17" t="inlineStr"/>
     </row>
     <row r="148">
@@ -10417,10 +10445,10 @@
         </is>
       </c>
       <c r="F148" s="45" t="n">
-        <v>46363</v>
+        <v>46359</v>
       </c>
       <c r="G148" s="45" t="n">
-        <v>46364</v>
+        <v>46360</v>
       </c>
       <c r="H148" s="15" t="n">
         <v>2</v>
@@ -10435,7 +10463,7 @@
       </c>
       <c r="K148" s="17" t="inlineStr">
         <is>
-          <t>7.2.5</t>
+          <t>6.2.5;7.2.4</t>
         </is>
       </c>
       <c r="L148" s="15" t="inlineStr">
@@ -10452,7 +10480,11 @@
         </is>
       </c>
       <c r="O148" s="21" t="n"/>
-      <c r="P148" s="21" t="n"/>
+      <c r="P148" s="21" t="inlineStr">
+        <is>
+          <t>★先于UAT（12/7）完成：越权/掩码旁路用例全跑+备份恢复与灾备切换演练；结果提交就绪评审</t>
+        </is>
+      </c>
       <c r="Q148" s="17" t="inlineStr"/>
     </row>
     <row r="149">
@@ -15344,7 +15376,7 @@
       </c>
       <c r="C35" s="66" t="inlineStr">
         <is>
-          <t>非功能专项验证</t>
+          <t>非功能与质量专项验证</t>
         </is>
       </c>
       <c r="D35" s="66" t="inlineStr">
@@ -15683,7 +15715,7 @@
       </c>
       <c r="E3" s="33" t="inlineStr">
         <is>
-          <t>Mandy</t>
+          <t>SRS评审通过、业务方签字（SRS含非功能需求NFR基线）；26项优先级锁定；追踪矩阵建立</t>
         </is>
       </c>
       <c r="F3" s="35" t="n"/>
@@ -15823,7 +15855,7 @@
       </c>
       <c r="E8" s="33" t="inlineStr">
         <is>
-          <t>Mandy</t>
+          <t>全量测试26项通过；性能专项（7.2.3）与安全可靠性专项（7.2.6）已于12/4前达标（对照NFR基线2.2.1/2.3.1）；业务方UAT签字（12/7）；缺陷关闭或书面接受；生产就绪评审通过</t>
         </is>
       </c>
       <c r="F8" s="35" t="n"/>
@@ -16376,22 +16408,22 @@
       </c>
       <c r="B5" s="32" t="inlineStr">
         <is>
-          <t>非功能需求梳理与验收指标定义</t>
+          <t>NFR测试可执行化</t>
         </is>
       </c>
       <c r="C5" s="32" t="inlineStr">
         <is>
-          <t>与功能需求同一基线梳理NFR：性能（检索响应/导出吞吐/并发）、安全（加密/越权/审计）、合规（数据不出境）、可用性（备份RPO/RTO）、容量（600~800表及增长），形成可验收指标。</t>
+          <t>将SRS中已冻结的NFR基线（性能/安全/合规/可用性/容量）细化为可测的验收标准与用例集，供集成初验（6.3.2）与专项验证（7.2.3/7.2.6）逐项对照。</t>
         </is>
       </c>
       <c r="D5" s="32" t="inlineStr">
         <is>
-          <t>非功能需求指标清单（NFR基线）</t>
+          <t>NFR可测验收标准清单</t>
         </is>
       </c>
       <c r="E5" s="32" t="inlineStr">
         <is>
-          <t>每项NFR有量化指标与验收方法；纳入需求基线统一管理</t>
+          <t>每项NFR有量化指标、测试方法与通过阈值；与2.2.1基线一一对应，无新增无遗漏</t>
         </is>
       </c>
       <c r="F5" s="15" t="inlineStr">

--- a/RIMS项目WBS工作分解_AI Native版.xlsx
+++ b/RIMS项目WBS工作分解_AI Native版.xlsx
@@ -11,15 +11,17 @@
     <sheet name="WBS分解" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="26项功能覆盖对照" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="功能视角分解" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="里程碑计划" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="资源负荷与日历" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="WBS词典" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="进度汇总" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="功能拆解估算" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="里程碑计划" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="资源负荷与日历" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="WBS词典" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="进度汇总" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'WBS分解'!$A$3:$Q$164</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'WBS分解'!$1:$3</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'功能视角分解'!$A$2:$P$38</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'功能拆解估算'!$A$2:$I$104</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -139,7 +141,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -161,11 +163,44 @@
         <color rgb="00BFBFBF"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00BFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00BFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00BFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="72">
+  <cellXfs count="95">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -347,6 +382,75 @@
     <xf numFmtId="165" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -754,7 +858,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B34"/>
+  <dimension ref="A1:B36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1129,6 +1233,30 @@
       <c r="B34" s="4" t="inlineStr">
         <is>
           <t>按功能维度查看：26项功能×（BA/开发A/开发B/测试/文档）五类角色各自的工作内容与人天，另有9类公共支撑行（初始化/架构/集成/专项/上线/管理）；底部与185人天自动对账，可与按开发顺序的「WBS分解」页对照使用</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="30" customHeight="1">
+      <c r="A35" s="38" t="inlineStr">
+        <is>
+          <t>功能拆解估算</t>
+        </is>
+      </c>
+      <c r="B35" s="4" t="inlineStr">
+        <is>
+          <t>子任务级直估：26项功能下钻到75个子任务/工作包（如F01-01拆为原系统录入/DB连接/表勾选/保留期配置/Iceberg·UC存储落地/导入作业/监控），按BA/开发A/开发B/测试/SLC文档独立估人天，不锚定185人天；底部附与计划口径的对照与差异说明</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="30" customHeight="1">
+      <c r="A36" s="38" t="inlineStr">
+        <is>
+          <t>功能拆解估算</t>
+        </is>
+      </c>
+      <c r="B36" s="4" t="inlineStr">
+        <is>
+          <t>子任务级直估：26项功能下钻到75个子任务/工作包（如F01-01拆为原系统录入/DB连接/表勾选/保留期配置/Iceberg·UC存储落地/导入作业/监控），按BA/开发A/开发B/测试/SLC文档独立估人天，不锚定185人天；底部附与计划口径的对照与差异说明</t>
         </is>
       </c>
     </row>
@@ -15638,6 +15766,3418 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="008FA9DB"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I106"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="11" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="44" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="8" customWidth="1" min="8" max="8"/>
+    <col width="8" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="26" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>功能拆解估算（子任务级直估）：每个功能下钻到子功能/工作包，按角色直估人天 — 独立估算，不锚定排期185人天</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>子任务编号</t>
+        </is>
+      </c>
+      <c r="B2" s="7" t="inlineStr">
+        <is>
+          <t>子任务/工作包</t>
+        </is>
+      </c>
+      <c r="C2" s="7" t="inlineStr">
+        <is>
+          <t>工作内容要点</t>
+        </is>
+      </c>
+      <c r="D2" s="7" t="inlineStr">
+        <is>
+          <t>BA人天</t>
+        </is>
+      </c>
+      <c r="E2" s="7" t="inlineStr">
+        <is>
+          <t>开发A·Wade</t>
+        </is>
+      </c>
+      <c r="F2" s="7" t="inlineStr">
+        <is>
+          <t>开发B·DevB</t>
+        </is>
+      </c>
+      <c r="G2" s="7" t="inlineStr">
+        <is>
+          <t>测试人天</t>
+        </is>
+      </c>
+      <c r="H2" s="7" t="inlineStr">
+        <is>
+          <t>SLC文档</t>
+        </is>
+      </c>
+      <c r="I2" s="7" t="inlineStr">
+        <is>
+          <t>小计</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="72" t="inlineStr">
+        <is>
+          <t>F01-01</t>
+        </is>
+      </c>
+      <c r="B3" s="73" t="inlineStr">
+        <is>
+          <t>结构化历史数据批量导入（模块1·存量历史数据迁移与标准化）· 共7个子任务</t>
+        </is>
+      </c>
+      <c r="C3" s="72" t="n"/>
+      <c r="D3" s="74" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="E3" s="74" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="F3" s="74" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="G3" s="74" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="H3" s="74" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="I3" s="74" t="n">
+        <v>20.75</v>
+      </c>
+    </row>
+    <row r="4" ht="26" customHeight="1">
+      <c r="A4" s="15" t="inlineStr">
+        <is>
+          <t>F01-01-1</t>
+        </is>
+      </c>
+      <c r="B4" s="32" t="inlineStr">
+        <is>
+          <t>原系统基本信息录入</t>
+        </is>
+      </c>
+      <c r="C4" s="32" t="inlineStr">
+        <is>
+          <t>来源系统档案：系统编码/名称/业务域/责任人/退役批次；录入与维护界面+存储API</t>
+        </is>
+      </c>
+      <c r="D4" s="46" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E4" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="F4" s="46" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G4" s="46" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H4" s="46" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="I4" s="46" t="n">
+        <v>2.75</v>
+      </c>
+    </row>
+    <row r="5" ht="26" customHeight="1">
+      <c r="A5" s="15" t="inlineStr">
+        <is>
+          <t>F01-01-2</t>
+        </is>
+      </c>
+      <c r="B5" s="32" t="inlineStr">
+        <is>
+          <t>源库DB连接配置</t>
+        </is>
+      </c>
+      <c r="C5" s="32" t="inlineStr">
+        <is>
+          <t>DB类型/连接串录入，账号密码Key Vault加密存储，连通性测试</t>
+        </is>
+      </c>
+      <c r="D5" s="46" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="E5" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="F5" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="G5" s="46" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H5" s="46" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="I5" s="46" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" ht="26" customHeight="1">
+      <c r="A6" s="15" t="inlineStr">
+        <is>
+          <t>F01-01-3</t>
+        </is>
+      </c>
+      <c r="B6" s="32" t="inlineStr">
+        <is>
+          <t>同步表勾选</t>
+        </is>
+      </c>
+      <c r="C6" s="32" t="inlineStr">
+        <is>
+          <t>拉取源表清单、勾选同步范围、数据量预估与全选过滤</t>
+        </is>
+      </c>
+      <c r="D6" s="46" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="E6" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="F6" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" s="46" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H6" s="46" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="I6" s="46" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7" ht="26" customHeight="1">
+      <c r="A7" s="15" t="inlineStr">
+        <is>
+          <t>F01-01-4</t>
+        </is>
+      </c>
+      <c r="B7" s="32" t="inlineStr">
+        <is>
+          <t>保留期限与迁移参数配置</t>
+        </is>
+      </c>
+      <c r="C7" s="32" t="inlineStr">
+        <is>
+          <t>保留策略绑定、迁移批次命名、并发/限速参数</t>
+        </is>
+      </c>
+      <c r="D7" s="46" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E7" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="F7" s="46" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G7" s="46" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="H7" s="46" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="I7" s="46" t="n">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="8" ht="26" customHeight="1">
+      <c r="A8" s="15" t="inlineStr">
+        <is>
+          <t>F01-01-5</t>
+        </is>
+      </c>
+      <c r="B8" s="32" t="inlineStr">
+        <is>
+          <t>存储落地实现（Iceberg/UC）</t>
+        </is>
+      </c>
+      <c r="C8" s="32" t="inlineStr">
+        <is>
+          <t>磁盘目录布局、Iceberg表属性与分区策略、UC目录/Schema/授权配置化</t>
+        </is>
+      </c>
+      <c r="D8" s="46" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="E8" s="46" t="n"/>
+      <c r="F8" s="46" t="n">
+        <v>2</v>
+      </c>
+      <c r="G8" s="46" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H8" s="46" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I8" s="46" t="n">
+        <v>3.25</v>
+      </c>
+    </row>
+    <row r="9" ht="26" customHeight="1">
+      <c r="A9" s="15" t="inlineStr">
+        <is>
+          <t>F01-01-6</t>
+        </is>
+      </c>
+      <c r="B9" s="32" t="inlineStr">
+        <is>
+          <t>SeaTunnel批量导入作业</t>
+        </is>
+      </c>
+      <c r="C9" s="32" t="inlineStr">
+        <is>
+          <t>作业配置生成器、分片/断点续传/限速执行</t>
+        </is>
+      </c>
+      <c r="D9" s="46" t="n"/>
+      <c r="E9" s="46" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F9" s="46" t="n">
+        <v>2</v>
+      </c>
+      <c r="G9" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="H9" s="46" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I9" s="46" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" ht="26" customHeight="1">
+      <c r="A10" s="15" t="inlineStr">
+        <is>
+          <t>F01-01-7</t>
+        </is>
+      </c>
+      <c r="B10" s="32" t="inlineStr">
+        <is>
+          <t>导入执行与监控</t>
+        </is>
+      </c>
+      <c r="C10" s="32" t="inlineStr">
+        <is>
+          <t>任务状态/进度/失败重试/日志查看</t>
+        </is>
+      </c>
+      <c r="D10" s="46" t="n"/>
+      <c r="E10" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="F10" s="46" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G10" s="46" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H10" s="46" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="I10" s="46" t="n">
+        <v>2.25</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="72" t="inlineStr">
+        <is>
+          <t>F01-02</t>
+        </is>
+      </c>
+      <c r="B11" s="73" t="inlineStr">
+        <is>
+          <t>非结构化文件及离线包批量导入（模块1·存量历史数据迁移与标准化）· 共4个子任务</t>
+        </is>
+      </c>
+      <c r="C11" s="72" t="n"/>
+      <c r="D11" s="74" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E11" s="74" t="n">
+        <v>3</v>
+      </c>
+      <c r="F11" s="74" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="G11" s="74" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="H11" s="74" t="n">
+        <v>1</v>
+      </c>
+      <c r="I11" s="74" t="n">
+        <v>12.75</v>
+      </c>
+    </row>
+    <row r="12" ht="26" customHeight="1">
+      <c r="A12" s="15" t="inlineStr">
+        <is>
+          <t>F01-02-1</t>
+        </is>
+      </c>
+      <c r="B12" s="32" t="inlineStr">
+        <is>
+          <t>文件来源登记与上传通道</t>
+        </is>
+      </c>
+      <c r="C12" s="32" t="inlineStr">
+        <is>
+          <t>在线上传/共享路径挂载/离线介质登记</t>
+        </is>
+      </c>
+      <c r="D12" s="46" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="E12" s="46" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F12" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="G12" s="46" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H12" s="46" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="I12" s="46" t="n">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="13" ht="26" customHeight="1">
+      <c r="A13" s="15" t="inlineStr">
+        <is>
+          <t>F01-02-2</t>
+        </is>
+      </c>
+      <c r="B13" s="32" t="inlineStr">
+        <is>
+          <t>大文件分片上传与断点续传</t>
+        </is>
+      </c>
+      <c r="C13" s="32" t="inlineStr">
+        <is>
+          <t>前端分片上传、后端合并与校验</t>
+        </is>
+      </c>
+      <c r="D13" s="46" t="n"/>
+      <c r="E13" s="46" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F13" s="46" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G13" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="H13" s="46" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="I13" s="46" t="n">
+        <v>4.25</v>
+      </c>
+    </row>
+    <row r="14" ht="26" customHeight="1">
+      <c r="A14" s="15" t="inlineStr">
+        <is>
+          <t>F01-02-3</t>
+        </is>
+      </c>
+      <c r="B14" s="32" t="inlineStr">
+        <is>
+          <t>文件包解析</t>
+        </is>
+      </c>
+      <c r="C14" s="32" t="inlineStr">
+        <is>
+          <t>zip/tar/数据库备份包识别与展开、原始属性保留</t>
+        </is>
+      </c>
+      <c r="D14" s="46" t="n"/>
+      <c r="E14" s="46" t="n"/>
+      <c r="F14" s="46" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G14" s="46" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="H14" s="46" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="I14" s="46" t="n">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="15" ht="26" customHeight="1">
+      <c r="A15" s="15" t="inlineStr">
+        <is>
+          <t>F01-02-4</t>
+        </is>
+      </c>
+      <c r="B15" s="32" t="inlineStr">
+        <is>
+          <t>附件元数据与Blob存储布局</t>
+        </is>
+      </c>
+      <c r="C15" s="32" t="inlineStr">
+        <is>
+          <t>附件索引表、路径规范、与结构化记录关联</t>
+        </is>
+      </c>
+      <c r="D15" s="46" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="E15" s="46" t="n"/>
+      <c r="F15" s="46" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G15" s="46" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H15" s="46" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="I15" s="46" t="n">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="72" t="inlineStr">
+        <is>
+          <t>F01-03</t>
+        </is>
+      </c>
+      <c r="B16" s="73" t="inlineStr">
+        <is>
+          <t>数据导入规则配置（模块1·存量历史数据迁移与标准化）· 共4个子任务</t>
+        </is>
+      </c>
+      <c r="C16" s="72" t="n"/>
+      <c r="D16" s="74" t="n">
+        <v>1</v>
+      </c>
+      <c r="E16" s="74" t="n">
+        <v>3</v>
+      </c>
+      <c r="F16" s="74" t="n">
+        <v>4</v>
+      </c>
+      <c r="G16" s="74" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="H16" s="74" t="n">
+        <v>1</v>
+      </c>
+      <c r="I16" s="74" t="n">
+        <v>11.25</v>
+      </c>
+    </row>
+    <row r="17" ht="26" customHeight="1">
+      <c r="A17" s="15" t="inlineStr">
+        <is>
+          <t>F01-03-1</t>
+        </is>
+      </c>
+      <c r="B17" s="32" t="inlineStr">
+        <is>
+          <t>字段映射规则配置</t>
+        </is>
+      </c>
+      <c r="C17" s="32" t="inlineStr">
+        <is>
+          <t>源字段→标准字段映射界面、自动映射建议</t>
+        </is>
+      </c>
+      <c r="D17" s="46" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E17" s="46" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F17" s="46" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G17" s="46" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H17" s="46" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="I17" s="46" t="n">
+        <v>3.25</v>
+      </c>
+    </row>
+    <row r="18" ht="26" customHeight="1">
+      <c r="A18" s="15" t="inlineStr">
+        <is>
+          <t>F01-03-2</t>
+        </is>
+      </c>
+      <c r="B18" s="32" t="inlineStr">
+        <is>
+          <t>格式转换与清洗规则</t>
+        </is>
+      </c>
+      <c r="C18" s="32" t="inlineStr">
+        <is>
+          <t>类型转换/编码/默认值/脏数据处理策略</t>
+        </is>
+      </c>
+      <c r="D18" s="46" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E18" s="46" t="n"/>
+      <c r="F18" s="46" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G18" s="46" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="H18" s="46" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="I18" s="46" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" ht="26" customHeight="1">
+      <c r="A19" s="15" t="inlineStr">
+        <is>
+          <t>F01-03-3</t>
+        </is>
+      </c>
+      <c r="B19" s="32" t="inlineStr">
+        <is>
+          <t>校验规则配置</t>
+        </is>
+      </c>
+      <c r="C19" s="32" t="inlineStr">
+        <is>
+          <t>必填/唯一/范围/自定义表达式校验</t>
+        </is>
+      </c>
+      <c r="D19" s="46" t="n"/>
+      <c r="E19" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="F19" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="G19" s="46" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H19" s="46" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="I19" s="46" t="n">
+        <v>2.75</v>
+      </c>
+    </row>
+    <row r="20" ht="26" customHeight="1">
+      <c r="A20" s="15" t="inlineStr">
+        <is>
+          <t>F01-03-4</t>
+        </is>
+      </c>
+      <c r="B20" s="32" t="inlineStr">
+        <is>
+          <t>规则版本与试跑预览</t>
+        </is>
+      </c>
+      <c r="C20" s="32" t="inlineStr">
+        <is>
+          <t>规则版本管理、样本试跑与结果预览</t>
+        </is>
+      </c>
+      <c r="D20" s="46" t="n"/>
+      <c r="E20" s="46" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F20" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="G20" s="46" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H20" s="46" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="I20" s="46" t="n">
+        <v>2.25</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="72" t="inlineStr">
+        <is>
+          <t>F01-04</t>
+        </is>
+      </c>
+      <c r="B21" s="73" t="inlineStr">
+        <is>
+          <t>迁移前完整性基准记录（模块1·存量历史数据迁移与标准化）· 共3个子任务</t>
+        </is>
+      </c>
+      <c r="C21" s="72" t="n"/>
+      <c r="D21" s="74" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E21" s="74" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F21" s="74" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="G21" s="74" t="n">
+        <v>1</v>
+      </c>
+      <c r="H21" s="74" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="I21" s="74" t="n">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="22" ht="26" customHeight="1">
+      <c r="A22" s="15" t="inlineStr">
+        <is>
+          <t>F01-04-1</t>
+        </is>
+      </c>
+      <c r="B22" s="32" t="inlineStr">
+        <is>
+          <t>基准采集策略定义</t>
+        </is>
+      </c>
+      <c r="C22" s="32" t="inlineStr">
+        <is>
+          <t>行数/校验和/SHA-256抽样口径</t>
+        </is>
+      </c>
+      <c r="D22" s="46" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E22" s="46" t="n"/>
+      <c r="F22" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="G22" s="46" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="H22" s="46" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="I22" s="46" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="23" ht="26" customHeight="1">
+      <c r="A23" s="15" t="inlineStr">
+        <is>
+          <t>F01-04-2</t>
+        </is>
+      </c>
+      <c r="B23" s="32" t="inlineStr">
+        <is>
+          <t>基准采集作业与存储</t>
+        </is>
+      </c>
+      <c r="C23" s="32" t="inlineStr">
+        <is>
+          <t>源端基准快照生成、基准库表</t>
+        </is>
+      </c>
+      <c r="D23" s="46" t="n"/>
+      <c r="E23" s="46" t="n"/>
+      <c r="F23" s="46" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G23" s="46" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H23" s="46" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="I23" s="46" t="n">
+        <v>2.25</v>
+      </c>
+    </row>
+    <row r="24" ht="26" customHeight="1">
+      <c r="A24" s="15" t="inlineStr">
+        <is>
+          <t>F01-04-3</t>
+        </is>
+      </c>
+      <c r="B24" s="32" t="inlineStr">
+        <is>
+          <t>基准报告查询展示</t>
+        </is>
+      </c>
+      <c r="C24" s="32" t="inlineStr">
+        <is>
+          <t>基准结果展示与导出</t>
+        </is>
+      </c>
+      <c r="D24" s="46" t="n"/>
+      <c r="E24" s="46" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F24" s="46" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="G24" s="46" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="H24" s="46" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="I24" s="46" t="n">
+        <v>1.25</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="72" t="inlineStr">
+        <is>
+          <t>F01-05</t>
+        </is>
+      </c>
+      <c r="B25" s="73" t="inlineStr">
+        <is>
+          <t>迁移后完整性比对（模块1·存量历史数据迁移与标准化）· 共2个子任务</t>
+        </is>
+      </c>
+      <c r="C25" s="72" t="n"/>
+      <c r="D25" s="74" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="E25" s="74" t="n">
+        <v>1</v>
+      </c>
+      <c r="F25" s="74" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="G25" s="74" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="H25" s="74" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I25" s="74" t="n">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="26" ht="26" customHeight="1">
+      <c r="A26" s="15" t="inlineStr">
+        <is>
+          <t>F01-05-1</t>
+        </is>
+      </c>
+      <c r="B26" s="32" t="inlineStr">
+        <is>
+          <t>比对引擎</t>
+        </is>
+      </c>
+      <c r="C26" s="32" t="inlineStr">
+        <is>
+          <t>RAW/CURATED逐层行数与校验和比对、抽样SHA-256</t>
+        </is>
+      </c>
+      <c r="D26" s="46" t="n"/>
+      <c r="E26" s="46" t="n"/>
+      <c r="F26" s="46" t="n">
+        <v>2</v>
+      </c>
+      <c r="G26" s="46" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="H26" s="46" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="I26" s="46" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" ht="26" customHeight="1">
+      <c r="A27" s="15" t="inlineStr">
+        <is>
+          <t>F01-05-2</t>
+        </is>
+      </c>
+      <c r="B27" s="32" t="inlineStr">
+        <is>
+          <t>差异报告与处理流程</t>
+        </is>
+      </c>
+      <c r="C27" s="32" t="inlineStr">
+        <is>
+          <t>差异清单、重迁/豁免记录</t>
+        </is>
+      </c>
+      <c r="D27" s="46" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="E27" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="F27" s="46" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G27" s="46" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H27" s="46" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="I27" s="46" t="n">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="75" t="inlineStr">
+        <is>
+          <t>F02-01</t>
+        </is>
+      </c>
+      <c r="B28" s="76" t="inlineStr">
+        <is>
+          <t>统一元数据模型（模块2·实时数据接入与常态化数据治理）· 共3个子任务</t>
+        </is>
+      </c>
+      <c r="C28" s="75" t="n"/>
+      <c r="D28" s="77" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="E28" s="77" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F28" s="77" t="n">
+        <v>3</v>
+      </c>
+      <c r="G28" s="77" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="H28" s="77" t="n">
+        <v>1</v>
+      </c>
+      <c r="I28" s="77" t="n">
+        <v>8.5</v>
+      </c>
+    </row>
+    <row r="29" ht="26" customHeight="1">
+      <c r="A29" s="15" t="inlineStr">
+        <is>
+          <t>F02-01-1</t>
+        </is>
+      </c>
+      <c r="B29" s="32" t="inlineStr">
+        <is>
+          <t>元数据字段体系定义</t>
+        </is>
+      </c>
+      <c r="C29" s="32" t="inlineStr">
+        <is>
+          <t>字段/类型/必填/密级/保留等级字典</t>
+        </is>
+      </c>
+      <c r="D29" s="46" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="E29" s="46" t="n"/>
+      <c r="F29" s="46" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G29" s="46" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="H29" s="46" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I29" s="46" t="n">
+        <v>2.75</v>
+      </c>
+    </row>
+    <row r="30" ht="26" customHeight="1">
+      <c r="A30" s="15" t="inlineStr">
+        <is>
+          <t>F02-01-2</t>
+        </is>
+      </c>
+      <c r="B30" s="32" t="inlineStr">
+        <is>
+          <t>元数据核心表与API</t>
+        </is>
+      </c>
+      <c r="C30" s="32" t="inlineStr">
+        <is>
+          <t>核心元数据表实现、CRUD API、Migration</t>
+        </is>
+      </c>
+      <c r="D30" s="46" t="n"/>
+      <c r="E30" s="46" t="n"/>
+      <c r="F30" s="46" t="n">
+        <v>2</v>
+      </c>
+      <c r="G30" s="46" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H30" s="46" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="I30" s="46" t="n">
+        <v>2.75</v>
+      </c>
+    </row>
+    <row r="31" ht="26" customHeight="1">
+      <c r="A31" s="15" t="inlineStr">
+        <is>
+          <t>F02-01-3</t>
+        </is>
+      </c>
+      <c r="B31" s="32" t="inlineStr">
+        <is>
+          <t>元数据驱动配置机制</t>
+        </is>
+      </c>
+      <c r="C31" s="32" t="inlineStr">
+        <is>
+          <t>查询配置模型、动态表单渲染协议</t>
+        </is>
+      </c>
+      <c r="D31" s="46" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="E31" s="46" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F31" s="46" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G31" s="46" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H31" s="46" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="I31" s="46" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="75" t="inlineStr">
+        <is>
+          <t>F02-02</t>
+        </is>
+      </c>
+      <c r="B32" s="76" t="inlineStr">
+        <is>
+          <t>来源系统信息绑定（模块2·实时数据接入与常态化数据治理）· 共3个子任务</t>
+        </is>
+      </c>
+      <c r="C32" s="75" t="n"/>
+      <c r="D32" s="77" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E32" s="77" t="n">
+        <v>1</v>
+      </c>
+      <c r="F32" s="77" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="G32" s="77" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="H32" s="77" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="I32" s="77" t="n">
+        <v>5.75</v>
+      </c>
+    </row>
+    <row r="33" ht="26" customHeight="1">
+      <c r="A33" s="15" t="inlineStr">
+        <is>
+          <t>F02-02-1</t>
+        </is>
+      </c>
+      <c r="B33" s="32" t="inlineStr">
+        <is>
+          <t>绑定规则与批次属性</t>
+        </is>
+      </c>
+      <c r="C33" s="32" t="inlineStr">
+        <is>
+          <t>源编码引用、退役项目/迁移批次属性规则</t>
+        </is>
+      </c>
+      <c r="D33" s="46" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E33" s="46" t="n"/>
+      <c r="F33" s="46" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="G33" s="46" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="H33" s="46" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="I33" s="46" t="n">
+        <v>1.75</v>
+      </c>
+    </row>
+    <row r="34" ht="26" customHeight="1">
+      <c r="A34" s="15" t="inlineStr">
+        <is>
+          <t>F02-02-2</t>
+        </is>
+      </c>
+      <c r="B34" s="32" t="inlineStr">
+        <is>
+          <t>接入时自动绑定</t>
+        </is>
+      </c>
+      <c r="C34" s="32" t="inlineStr">
+        <is>
+          <t>导入/上传时来源属性自动写入与校验</t>
+        </is>
+      </c>
+      <c r="D34" s="46" t="n"/>
+      <c r="E34" s="46" t="n"/>
+      <c r="F34" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="G34" s="46" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H34" s="46" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="I34" s="46" t="n">
+        <v>1.75</v>
+      </c>
+    </row>
+    <row r="35" ht="26" customHeight="1">
+      <c r="A35" s="15" t="inlineStr">
+        <is>
+          <t>F02-02-3</t>
+        </is>
+      </c>
+      <c r="B35" s="32" t="inlineStr">
+        <is>
+          <t>按来源检索与统计</t>
+        </is>
+      </c>
+      <c r="C35" s="32" t="inlineStr">
+        <is>
+          <t>来源维度筛选、统计报表</t>
+        </is>
+      </c>
+      <c r="D35" s="46" t="n"/>
+      <c r="E35" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="F35" s="46" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G35" s="46" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H35" s="46" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="I35" s="46" t="n">
+        <v>2.25</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="78" t="inlineStr">
+        <is>
+          <t>F03-01</t>
+        </is>
+      </c>
+      <c r="B36" s="79" t="inlineStr">
+        <is>
+          <t>保留期限到期自动删除（模块3·记录归档与档案全生命周期管理）· 共3个子任务</t>
+        </is>
+      </c>
+      <c r="C36" s="78" t="n"/>
+      <c r="D36" s="80" t="n">
+        <v>1</v>
+      </c>
+      <c r="E36" s="80" t="n">
+        <v>2</v>
+      </c>
+      <c r="F36" s="80" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="G36" s="80" t="n">
+        <v>2</v>
+      </c>
+      <c r="H36" s="80" t="n">
+        <v>1</v>
+      </c>
+      <c r="I36" s="80" t="n">
+        <v>9.5</v>
+      </c>
+    </row>
+    <row r="37" ht="26" customHeight="1">
+      <c r="A37" s="15" t="inlineStr">
+        <is>
+          <t>F03-01-1</t>
+        </is>
+      </c>
+      <c r="B37" s="32" t="inlineStr">
+        <is>
+          <t>保留策略配置</t>
+        </is>
+      </c>
+      <c r="C37" s="32" t="inlineStr">
+        <is>
+          <t>策略规则、继承关系、生效范围</t>
+        </is>
+      </c>
+      <c r="D37" s="46" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="E37" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="F37" s="46" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G37" s="46" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H37" s="46" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="I37" s="46" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="38" ht="26" customHeight="1">
+      <c r="A38" s="15" t="inlineStr">
+        <is>
+          <t>F03-01-2</t>
+        </is>
+      </c>
+      <c r="B38" s="32" t="inlineStr">
+        <is>
+          <t>处置引擎</t>
+        </is>
+      </c>
+      <c r="C38" s="32" t="inlineStr">
+        <is>
+          <t>到期扫描、豁免检查、DROP PARTITION、VACUUM物理清除</t>
+        </is>
+      </c>
+      <c r="D38" s="46" t="n"/>
+      <c r="E38" s="46" t="n"/>
+      <c r="F38" s="46" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="G38" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="H38" s="46" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I38" s="46" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="39" ht="26" customHeight="1">
+      <c r="A39" s="15" t="inlineStr">
+        <is>
+          <t>F03-01-3</t>
+        </is>
+      </c>
+      <c r="B39" s="32" t="inlineStr">
+        <is>
+          <t>处置计划审批与台账</t>
+        </is>
+      </c>
+      <c r="C39" s="32" t="inlineStr">
+        <is>
+          <t>预演清单、审批流、处置留痕台账</t>
+        </is>
+      </c>
+      <c r="D39" s="46" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="E39" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="F39" s="46" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G39" s="46" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H39" s="46" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="I39" s="46" t="n">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="78" t="inlineStr">
+        <is>
+          <t>F03-02</t>
+        </is>
+      </c>
+      <c r="B40" s="79" t="inlineStr">
+        <is>
+          <t>Legal Hold 冻结（模块3·记录归档与档案全生命周期管理）· 共3个子任务</t>
+        </is>
+      </c>
+      <c r="C40" s="78" t="n"/>
+      <c r="D40" s="80" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="E40" s="80" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F40" s="80" t="n">
+        <v>2</v>
+      </c>
+      <c r="G40" s="80" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H40" s="80" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="I40" s="80" t="n">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="41" ht="26" customHeight="1">
+      <c r="A41" s="15" t="inlineStr">
+        <is>
+          <t>F03-02-1</t>
+        </is>
+      </c>
+      <c r="B41" s="32" t="inlineStr">
+        <is>
+          <t>Hold申请与审批流程</t>
+        </is>
+      </c>
+      <c r="C41" s="32" t="inlineStr">
+        <is>
+          <t>涉诉/审计/调查场景、审批链定义</t>
+        </is>
+      </c>
+      <c r="D41" s="46" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="E41" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="F41" s="46" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="G41" s="46" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H41" s="46" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="I41" s="46" t="n">
+        <v>2.75</v>
+      </c>
+    </row>
+    <row r="42" ht="26" customHeight="1">
+      <c r="A42" s="15" t="inlineStr">
+        <is>
+          <t>F03-02-2</t>
+        </is>
+      </c>
+      <c r="B42" s="32" t="inlineStr">
+        <is>
+          <t>Hold生效与解除实现</t>
+        </is>
+      </c>
+      <c r="C42" s="32" t="inlineStr">
+        <is>
+          <t>记录级/表级冻结、处置豁免、操作留痕</t>
+        </is>
+      </c>
+      <c r="D42" s="46" t="n"/>
+      <c r="E42" s="46" t="n"/>
+      <c r="F42" s="46" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G42" s="46" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="H42" s="46" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="I42" s="46" t="n">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="43" ht="26" customHeight="1">
+      <c r="A43" s="15" t="inlineStr">
+        <is>
+          <t>F03-02-3</t>
+        </is>
+      </c>
+      <c r="B43" s="32" t="inlineStr">
+        <is>
+          <t>Hold清单管理与提醒</t>
+        </is>
+      </c>
+      <c r="C43" s="32" t="inlineStr">
+        <is>
+          <t>在Hold清单、解除预警</t>
+        </is>
+      </c>
+      <c r="D43" s="46" t="n"/>
+      <c r="E43" s="46" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F43" s="46" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="G43" s="46" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="H43" s="46" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="I43" s="46" t="n">
+        <v>1.25</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="81" t="inlineStr">
+        <is>
+          <t>F04-01</t>
+        </is>
+      </c>
+      <c r="B44" s="82" t="inlineStr">
+        <is>
+          <t>数据加密存储（模块4·数据存储与境内数据安全管控）· 共3个子任务</t>
+        </is>
+      </c>
+      <c r="C44" s="81" t="n"/>
+      <c r="D44" s="83" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E44" s="83" t="n">
+        <v>0</v>
+      </c>
+      <c r="F44" s="83" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="G44" s="83" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H44" s="83" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="I44" s="83" t="n">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="45" ht="26" customHeight="1">
+      <c r="A45" s="15" t="inlineStr">
+        <is>
+          <t>F04-01-1</t>
+        </is>
+      </c>
+      <c r="B45" s="32" t="inlineStr">
+        <is>
+          <t>加密策略定义</t>
+        </is>
+      </c>
+      <c r="C45" s="32" t="inlineStr">
+        <is>
+          <t>SSE+CMK方案、PII字段清单与字段级加密规则</t>
+        </is>
+      </c>
+      <c r="D45" s="46" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E45" s="46" t="n"/>
+      <c r="F45" s="46" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="G45" s="46" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="H45" s="46" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="I45" s="46" t="n">
+        <v>1.75</v>
+      </c>
+    </row>
+    <row r="46" ht="26" customHeight="1">
+      <c r="A46" s="15" t="inlineStr">
+        <is>
+          <t>F04-01-2</t>
+        </is>
+      </c>
+      <c r="B46" s="32" t="inlineStr">
+        <is>
+          <t>存储层加密落地</t>
+        </is>
+      </c>
+      <c r="C46" s="32" t="inlineStr">
+        <is>
+          <t>ADLS SSE、Key Vault CMK集成、密钥轮换</t>
+        </is>
+      </c>
+      <c r="D46" s="46" t="n"/>
+      <c r="E46" s="46" t="n"/>
+      <c r="F46" s="46" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G46" s="46" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H46" s="46" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="I46" s="46" t="n">
+        <v>2.25</v>
+      </c>
+    </row>
+    <row r="47" ht="26" customHeight="1">
+      <c r="A47" s="15" t="inlineStr">
+        <is>
+          <t>F04-01-3</t>
+        </is>
+      </c>
+      <c r="B47" s="32" t="inlineStr">
+        <is>
+          <t>PII字段级加密服务</t>
+        </is>
+      </c>
+      <c r="C47" s="32" t="inlineStr">
+        <is>
+          <t>应用层加解密、密文索引策略、传输加密验证</t>
+        </is>
+      </c>
+      <c r="D47" s="46" t="n"/>
+      <c r="E47" s="46" t="n"/>
+      <c r="F47" s="46" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G47" s="46" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="H47" s="46" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="I47" s="46" t="n">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="81" t="inlineStr">
+        <is>
+          <t>F04-02</t>
+        </is>
+      </c>
+      <c r="B48" s="82" t="inlineStr">
+        <is>
+          <t>密钥管理（模块4·数据存储与境内数据安全管控）· 共3个子任务</t>
+        </is>
+      </c>
+      <c r="C48" s="81" t="n"/>
+      <c r="D48" s="83" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="E48" s="83" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F48" s="83" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="G48" s="83" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="H48" s="83" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="I48" s="83" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="49" ht="26" customHeight="1">
+      <c r="A49" s="15" t="inlineStr">
+        <is>
+          <t>F04-02-1</t>
+        </is>
+      </c>
+      <c r="B49" s="32" t="inlineStr">
+        <is>
+          <t>密钥全流程管理</t>
+        </is>
+      </c>
+      <c r="C49" s="32" t="inlineStr">
+        <is>
+          <t>创建/保管/更新/吊销/权限控制</t>
+        </is>
+      </c>
+      <c r="D49" s="46" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="E49" s="46" t="n"/>
+      <c r="F49" s="46" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G49" s="46" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H49" s="46" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="I49" s="46" t="n">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="50" ht="26" customHeight="1">
+      <c r="A50" s="15" t="inlineStr">
+        <is>
+          <t>F04-02-2</t>
+        </is>
+      </c>
+      <c r="B50" s="32" t="inlineStr">
+        <is>
+          <t>密钥操作审计与告警</t>
+        </is>
+      </c>
+      <c r="C50" s="32" t="inlineStr">
+        <is>
+          <t>操作日志、异常使用告警</t>
+        </is>
+      </c>
+      <c r="D50" s="46" t="n"/>
+      <c r="E50" s="46" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F50" s="46" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G50" s="46" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H50" s="46" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="I50" s="46" t="n">
+        <v>1.75</v>
+      </c>
+    </row>
+    <row r="51" ht="26" customHeight="1">
+      <c r="A51" s="15" t="inlineStr">
+        <is>
+          <t>F04-02-3</t>
+        </is>
+      </c>
+      <c r="B51" s="32" t="inlineStr">
+        <is>
+          <t>密钥管理界面</t>
+        </is>
+      </c>
+      <c r="C51" s="32" t="inlineStr">
+        <is>
+          <t>密钥清单、版本、权限分配界面</t>
+        </is>
+      </c>
+      <c r="D51" s="46" t="n"/>
+      <c r="E51" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="F51" s="46" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="G51" s="46" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="H51" s="46" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="I51" s="46" t="n">
+        <v>1.75</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="81" t="inlineStr">
+        <is>
+          <t>F04-03</t>
+        </is>
+      </c>
+      <c r="B52" s="82" t="inlineStr">
+        <is>
+          <t>数据备份管理（模块4·数据存储与境内数据安全管控）· 共3个子任务</t>
+        </is>
+      </c>
+      <c r="C52" s="81" t="n"/>
+      <c r="D52" s="83" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E52" s="83" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="F52" s="83" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="G52" s="83" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="H52" s="83" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="I52" s="83" t="n">
+        <v>6.25</v>
+      </c>
+    </row>
+    <row r="53" ht="26" customHeight="1">
+      <c r="A53" s="15" t="inlineStr">
+        <is>
+          <t>F04-03-1</t>
+        </is>
+      </c>
+      <c r="B53" s="32" t="inlineStr">
+        <is>
+          <t>备份策略配置</t>
+        </is>
+      </c>
+      <c r="C53" s="32" t="inlineStr">
+        <is>
+          <t>备份周期/范围/保留期策略</t>
+        </is>
+      </c>
+      <c r="D53" s="46" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E53" s="46" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="F53" s="46" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G53" s="46" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="H53" s="46" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="I53" s="46" t="n">
+        <v>2.25</v>
+      </c>
+    </row>
+    <row r="54" ht="26" customHeight="1">
+      <c r="A54" s="15" t="inlineStr">
+        <is>
+          <t>F04-03-2</t>
+        </is>
+      </c>
+      <c r="B54" s="32" t="inlineStr">
+        <is>
+          <t>备份作业与副本创建</t>
+        </is>
+      </c>
+      <c r="C54" s="32" t="inlineStr">
+        <is>
+          <t>元数据库PITR、湖快照、附件副本</t>
+        </is>
+      </c>
+      <c r="D54" s="46" t="n"/>
+      <c r="E54" s="46" t="n"/>
+      <c r="F54" s="46" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G54" s="46" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H54" s="46" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="I54" s="46" t="n">
+        <v>2.25</v>
+      </c>
+    </row>
+    <row r="55" ht="26" customHeight="1">
+      <c r="A55" s="15" t="inlineStr">
+        <is>
+          <t>F04-03-3</t>
+        </is>
+      </c>
+      <c r="B55" s="32" t="inlineStr">
+        <is>
+          <t>备份监控与恢复操作</t>
+        </is>
+      </c>
+      <c r="C55" s="32" t="inlineStr">
+        <is>
+          <t>备份状态监控、恢复流程</t>
+        </is>
+      </c>
+      <c r="D55" s="46" t="n"/>
+      <c r="E55" s="46" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F55" s="46" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G55" s="46" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H55" s="46" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="I55" s="46" t="n">
+        <v>1.75</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="81" t="inlineStr">
+        <is>
+          <t>F04-04</t>
+        </is>
+      </c>
+      <c r="B56" s="82" t="inlineStr">
+        <is>
+          <t>异地灾备（模块4·数据存储与境内数据安全管控）· 共3个子任务</t>
+        </is>
+      </c>
+      <c r="C56" s="81" t="n"/>
+      <c r="D56" s="83" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E56" s="83" t="n">
+        <v>0</v>
+      </c>
+      <c r="F56" s="83" t="n">
+        <v>3</v>
+      </c>
+      <c r="G56" s="83" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H56" s="83" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="I56" s="83" t="n">
+        <v>5.75</v>
+      </c>
+    </row>
+    <row r="57" ht="26" customHeight="1">
+      <c r="A57" s="15" t="inlineStr">
+        <is>
+          <t>F04-04-1</t>
+        </is>
+      </c>
+      <c r="B57" s="32" t="inlineStr">
+        <is>
+          <t>灾备方案与RTO/RPO定义</t>
+        </is>
+      </c>
+      <c r="C57" s="32" t="inlineStr">
+        <is>
+          <t>灾备架构、恢复目标定义</t>
+        </is>
+      </c>
+      <c r="D57" s="46" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E57" s="46" t="n"/>
+      <c r="F57" s="46" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G57" s="46" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="H57" s="46" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="I57" s="46" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="58" ht="26" customHeight="1">
+      <c r="A58" s="15" t="inlineStr">
+        <is>
+          <t>F04-04-2</t>
+        </is>
+      </c>
+      <c r="B58" s="32" t="inlineStr">
+        <is>
+          <t>异地副本同步</t>
+        </is>
+      </c>
+      <c r="C58" s="32" t="inlineStr">
+        <is>
+          <t>存储异地冗余/复制配置</t>
+        </is>
+      </c>
+      <c r="D58" s="46" t="n"/>
+      <c r="E58" s="46" t="n"/>
+      <c r="F58" s="46" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G58" s="46" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H58" s="46" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="I58" s="46" t="n">
+        <v>2.25</v>
+      </c>
+    </row>
+    <row r="59" ht="26" customHeight="1">
+      <c r="A59" s="15" t="inlineStr">
+        <is>
+          <t>F04-04-3</t>
+        </is>
+      </c>
+      <c r="B59" s="32" t="inlineStr">
+        <is>
+          <t>恢复切换演练</t>
+        </is>
+      </c>
+      <c r="C59" s="32" t="inlineStr">
+        <is>
+          <t>演练脚本、切换/回切流程与报告</t>
+        </is>
+      </c>
+      <c r="D59" s="46" t="n"/>
+      <c r="E59" s="46" t="n"/>
+      <c r="F59" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="G59" s="46" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="H59" s="46" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="I59" s="46" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="84" t="inlineStr">
+        <is>
+          <t>F05-01</t>
+        </is>
+      </c>
+      <c r="B60" s="85" t="inlineStr">
+        <is>
+          <t>关键词检索（模块5·档案检索、智能发现与业务利用）· 共3个子任务</t>
+        </is>
+      </c>
+      <c r="C60" s="84" t="n"/>
+      <c r="D60" s="86" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E60" s="86" t="n">
+        <v>2</v>
+      </c>
+      <c r="F60" s="86" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="G60" s="86" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H60" s="86" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="I60" s="86" t="n">
+        <v>7.25</v>
+      </c>
+    </row>
+    <row r="61" ht="26" customHeight="1">
+      <c r="A61" s="15" t="inlineStr">
+        <is>
+          <t>F05-01-1</t>
+        </is>
+      </c>
+      <c r="B61" s="32" t="inlineStr">
+        <is>
+          <t>检索配置模型</t>
+        </is>
+      </c>
+      <c r="C61" s="32" t="inlineStr">
+        <is>
+          <t>可检索字段、分词策略、OCR文本索引策略</t>
+        </is>
+      </c>
+      <c r="D61" s="46" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E61" s="46" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F61" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="G61" s="46" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="H61" s="46" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="I61" s="46" t="n">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="62" ht="26" customHeight="1">
+      <c r="A62" s="15" t="inlineStr">
+        <is>
+          <t>F05-01-2</t>
+        </is>
+      </c>
+      <c r="B62" s="32" t="inlineStr">
+        <is>
+          <t>检索页动态表单</t>
+        </is>
+      </c>
+      <c r="C62" s="32" t="inlineStr">
+        <is>
+          <t>元数据驱动渲染、关键词与组合查询</t>
+        </is>
+      </c>
+      <c r="D62" s="46" t="n"/>
+      <c r="E62" s="46" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F62" s="46" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="G62" s="46" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H62" s="46" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="I62" s="46" t="n">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="63" ht="26" customHeight="1">
+      <c r="A63" s="15" t="inlineStr">
+        <is>
+          <t>F05-01-3</t>
+        </is>
+      </c>
+      <c r="B63" s="32" t="inlineStr">
+        <is>
+          <t>查询代理与SERVE层对接</t>
+        </is>
+      </c>
+      <c r="C63" s="32" t="inlineStr">
+        <is>
+          <t>查询服务、索引优化、结果高亮</t>
+        </is>
+      </c>
+      <c r="D63" s="46" t="n"/>
+      <c r="E63" s="46" t="n"/>
+      <c r="F63" s="46" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="G63" s="46" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="H63" s="46" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="I63" s="46" t="n">
+        <v>2.25</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="84" t="inlineStr">
+        <is>
+          <t>F05-02</t>
+        </is>
+      </c>
+      <c r="B64" s="85" t="inlineStr">
+        <is>
+          <t>按系统名称检索（模块5·档案检索、智能发现与业务利用）· 共2个子任务</t>
+        </is>
+      </c>
+      <c r="C64" s="84" t="n"/>
+      <c r="D64" s="86" t="n">
+        <v>0</v>
+      </c>
+      <c r="E64" s="86" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="F64" s="86" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G64" s="86" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H64" s="86" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I64" s="86" t="n">
+        <v>2.25</v>
+      </c>
+    </row>
+    <row r="65" ht="26" customHeight="1">
+      <c r="A65" s="15" t="inlineStr">
+        <is>
+          <t>F05-02-1</t>
+        </is>
+      </c>
+      <c r="B65" s="32" t="inlineStr">
+        <is>
+          <t>来源系统筛选组件</t>
+        </is>
+      </c>
+      <c r="C65" s="32" t="inlineStr">
+        <is>
+          <t>来源系统下拉/搜索/多选</t>
+        </is>
+      </c>
+      <c r="D65" s="46" t="n"/>
+      <c r="E65" s="46" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="F65" s="46" t="n"/>
+      <c r="G65" s="46" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="H65" s="46" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="I65" s="46" t="n">
+        <v>1.25</v>
+      </c>
+    </row>
+    <row r="66" ht="26" customHeight="1">
+      <c r="A66" s="15" t="inlineStr">
+        <is>
+          <t>F05-02-2</t>
+        </is>
+      </c>
+      <c r="B66" s="32" t="inlineStr">
+        <is>
+          <t>来源维度查询下推</t>
+        </is>
+      </c>
+      <c r="C66" s="32" t="inlineStr">
+        <is>
+          <t>sys_id过滤、分区裁剪</t>
+        </is>
+      </c>
+      <c r="D66" s="46" t="n"/>
+      <c r="E66" s="46" t="n"/>
+      <c r="F66" s="46" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G66" s="46" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="H66" s="46" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="I66" s="46" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="84" t="inlineStr">
+        <is>
+          <t>F05-03</t>
+        </is>
+      </c>
+      <c r="B67" s="85" t="inlineStr">
+        <is>
+          <t>按业务时间检索（模块5·档案检索、智能发现与业务利用）· 共2个子任务</t>
+        </is>
+      </c>
+      <c r="C67" s="84" t="n"/>
+      <c r="D67" s="86" t="n">
+        <v>0</v>
+      </c>
+      <c r="E67" s="86" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="F67" s="86" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G67" s="86" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H67" s="86" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I67" s="86" t="n">
+        <v>2.25</v>
+      </c>
+    </row>
+    <row r="68" ht="26" customHeight="1">
+      <c r="A68" s="15" t="inlineStr">
+        <is>
+          <t>F05-03-1</t>
+        </is>
+      </c>
+      <c r="B68" s="32" t="inlineStr">
+        <is>
+          <t>时间维度筛选组件</t>
+        </is>
+      </c>
+      <c r="C68" s="32" t="inlineStr">
+        <is>
+          <t>创建/修改/业务发生时间范围选择</t>
+        </is>
+      </c>
+      <c r="D68" s="46" t="n"/>
+      <c r="E68" s="46" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="F68" s="46" t="n"/>
+      <c r="G68" s="46" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="H68" s="46" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="I68" s="46" t="n">
+        <v>1.25</v>
+      </c>
+    </row>
+    <row r="69" ht="26" customHeight="1">
+      <c r="A69" s="15" t="inlineStr">
+        <is>
+          <t>F05-03-2</t>
+        </is>
+      </c>
+      <c r="B69" s="32" t="inlineStr">
+        <is>
+          <t>时间分区下推与索引</t>
+        </is>
+      </c>
+      <c r="C69" s="32" t="inlineStr">
+        <is>
+          <t>分区裁剪、时间索引优化</t>
+        </is>
+      </c>
+      <c r="D69" s="46" t="n"/>
+      <c r="E69" s="46" t="n"/>
+      <c r="F69" s="46" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G69" s="46" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="H69" s="46" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="I69" s="46" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="84" t="inlineStr">
+        <is>
+          <t>F05-04</t>
+        </is>
+      </c>
+      <c r="B70" s="85" t="inlineStr">
+        <is>
+          <t>检索结果列表展示（模块5·档案检索、智能发现与业务利用）· 共2个子任务</t>
+        </is>
+      </c>
+      <c r="C70" s="84" t="n"/>
+      <c r="D70" s="86" t="n">
+        <v>0</v>
+      </c>
+      <c r="E70" s="86" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="F70" s="86" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="G70" s="86" t="n">
+        <v>1</v>
+      </c>
+      <c r="H70" s="86" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I70" s="86" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="71" ht="26" customHeight="1">
+      <c r="A71" s="15" t="inlineStr">
+        <is>
+          <t>F05-04-1</t>
+        </is>
+      </c>
+      <c r="B71" s="32" t="inlineStr">
+        <is>
+          <t>列表展示与分页排序</t>
+        </is>
+      </c>
+      <c r="C71" s="32" t="inlineStr">
+        <is>
+          <t>关键字段展示、分批加载、虚拟滚动</t>
+        </is>
+      </c>
+      <c r="D71" s="46" t="n"/>
+      <c r="E71" s="46" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F71" s="46" t="n"/>
+      <c r="G71" s="46" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H71" s="46" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="I71" s="46" t="n">
+        <v>2.25</v>
+      </c>
+    </row>
+    <row r="72" ht="26" customHeight="1">
+      <c r="A72" s="15" t="inlineStr">
+        <is>
+          <t>F05-04-2</t>
+        </is>
+      </c>
+      <c r="B72" s="32" t="inlineStr">
+        <is>
+          <t>大批量结果性能</t>
+        </is>
+      </c>
+      <c r="C72" s="32" t="inlineStr">
+        <is>
+          <t>异步计数、游标分页、缓存</t>
+        </is>
+      </c>
+      <c r="D72" s="46" t="n"/>
+      <c r="E72" s="46" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="F72" s="46" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="G72" s="46" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H72" s="46" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="I72" s="46" t="n">
+        <v>1.75</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="84" t="inlineStr">
+        <is>
+          <t>F05-05</t>
+        </is>
+      </c>
+      <c r="B73" s="85" t="inlineStr">
+        <is>
+          <t>原始文件在线预览（模块5·档案检索、智能发现与业务利用）· 共3个子任务</t>
+        </is>
+      </c>
+      <c r="C73" s="84" t="n"/>
+      <c r="D73" s="86" t="n">
+        <v>0</v>
+      </c>
+      <c r="E73" s="86" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F73" s="86" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="G73" s="86" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="H73" s="86" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="I73" s="86" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="74" ht="26" customHeight="1">
+      <c r="A74" s="15" t="inlineStr">
+        <is>
+          <t>F05-05-1</t>
+        </is>
+      </c>
+      <c r="B74" s="32" t="inlineStr">
+        <is>
+          <t>预览服务</t>
+        </is>
+      </c>
+      <c r="C74" s="32" t="inlineStr">
+        <is>
+          <t>格式识别、图片/PDF/Office转换</t>
+        </is>
+      </c>
+      <c r="D74" s="46" t="n"/>
+      <c r="E74" s="46" t="n"/>
+      <c r="F74" s="46" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G74" s="46" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H74" s="46" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="I74" s="46" t="n">
+        <v>2.25</v>
+      </c>
+    </row>
+    <row r="75" ht="26" customHeight="1">
+      <c r="A75" s="15" t="inlineStr">
+        <is>
+          <t>F05-05-2</t>
+        </is>
+      </c>
+      <c r="B75" s="32" t="inlineStr">
+        <is>
+          <t>SAS直连与流式加载</t>
+        </is>
+      </c>
+      <c r="C75" s="32" t="inlineStr">
+        <is>
+          <t>临时SAS链接、流式传输、权限校验</t>
+        </is>
+      </c>
+      <c r="D75" s="46" t="n"/>
+      <c r="E75" s="46" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F75" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="G75" s="46" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H75" s="46" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="I75" s="46" t="n">
+        <v>2.25</v>
+      </c>
+    </row>
+    <row r="76" ht="26" customHeight="1">
+      <c r="A76" s="15" t="inlineStr">
+        <is>
+          <t>F05-05-3</t>
+        </is>
+      </c>
+      <c r="B76" s="32" t="inlineStr">
+        <is>
+          <t>前端预览组件</t>
+        </is>
+      </c>
+      <c r="C76" s="32" t="inlineStr">
+        <is>
+          <t>格式适配、缩放、失败降级下载</t>
+        </is>
+      </c>
+      <c r="D76" s="46" t="n"/>
+      <c r="E76" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="F76" s="46" t="n"/>
+      <c r="G76" s="46" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="H76" s="46" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="I76" s="46" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="87" t="inlineStr">
+        <is>
+          <t>F06-01</t>
+        </is>
+      </c>
+      <c r="B77" s="88" t="inlineStr">
+        <is>
+          <t>归档操作日志记录（模块6·合规管控、审计追踪与合规报表）· 共3个子任务</t>
+        </is>
+      </c>
+      <c r="C77" s="87" t="n"/>
+      <c r="D77" s="89" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="E77" s="89" t="n">
+        <v>1</v>
+      </c>
+      <c r="F77" s="89" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="G77" s="89" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="H77" s="89" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="I77" s="89" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="78" ht="26" customHeight="1">
+      <c r="A78" s="15" t="inlineStr">
+        <is>
+          <t>F06-01-1</t>
+        </is>
+      </c>
+      <c r="B78" s="32" t="inlineStr">
+        <is>
+          <t>埋点规范与日志模型</t>
+        </is>
+      </c>
+      <c r="C78" s="32" t="inlineStr">
+        <is>
+          <t>操作对象/用户/时间/结果/IP模型定义</t>
+        </is>
+      </c>
+      <c r="D78" s="46" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="E78" s="46" t="n"/>
+      <c r="F78" s="46" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G78" s="46" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="H78" s="46" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="I78" s="46" t="n">
+        <v>1.25</v>
+      </c>
+    </row>
+    <row r="79" ht="26" customHeight="1">
+      <c r="A79" s="15" t="inlineStr">
+        <is>
+          <t>F06-01-2</t>
+        </is>
+      </c>
+      <c r="B79" s="32" t="inlineStr">
+        <is>
+          <t>操作拦截与落库</t>
+        </is>
+      </c>
+      <c r="C79" s="32" t="inlineStr">
+        <is>
+          <t>归档/导入/上传统一拦截器、异步写入</t>
+        </is>
+      </c>
+      <c r="D79" s="46" t="n"/>
+      <c r="E79" s="46" t="n"/>
+      <c r="F79" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="G79" s="46" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H79" s="46" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="I79" s="46" t="n">
+        <v>1.75</v>
+      </c>
+    </row>
+    <row r="80" ht="26" customHeight="1">
+      <c r="A80" s="15" t="inlineStr">
+        <is>
+          <t>F06-01-3</t>
+        </is>
+      </c>
+      <c r="B80" s="32" t="inlineStr">
+        <is>
+          <t>审计查询界面</t>
+        </is>
+      </c>
+      <c r="C80" s="32" t="inlineStr">
+        <is>
+          <t>多维筛选与导出（覆盖归档/查询/导出三类日志）</t>
+        </is>
+      </c>
+      <c r="D80" s="46" t="n"/>
+      <c r="E80" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="F80" s="46" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="G80" s="46" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H80" s="46" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="I80" s="46" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="87" t="inlineStr">
+        <is>
+          <t>F06-02</t>
+        </is>
+      </c>
+      <c r="B81" s="88" t="inlineStr">
+        <is>
+          <t>查询操作日志记录（模块6·合规管控、审计追踪与合规报表）· 共2个子任务</t>
+        </is>
+      </c>
+      <c r="C81" s="87" t="n"/>
+      <c r="D81" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="E81" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="F81" s="89" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="G81" s="89" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="H81" s="89" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I81" s="89" t="n">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="82" ht="26" customHeight="1">
+      <c r="A82" s="15" t="inlineStr">
+        <is>
+          <t>F06-02-1</t>
+        </is>
+      </c>
+      <c r="B82" s="32" t="inlineStr">
+        <is>
+          <t>查询/预览行为埋点</t>
+        </is>
+      </c>
+      <c r="C82" s="32" t="inlineStr">
+        <is>
+          <t>查询条件脱敏记录、预览行为记录</t>
+        </is>
+      </c>
+      <c r="D82" s="46" t="n"/>
+      <c r="E82" s="46" t="n"/>
+      <c r="F82" s="46" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="G82" s="46" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H82" s="46" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="I82" s="46" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="83" ht="26" customHeight="1">
+      <c r="A83" s="15" t="inlineStr">
+        <is>
+          <t>F06-02-2</t>
+        </is>
+      </c>
+      <c r="B83" s="32" t="inlineStr">
+        <is>
+          <t>异步批量写入</t>
+        </is>
+      </c>
+      <c r="C83" s="32" t="inlineStr">
+        <is>
+          <t>缓冲批量写入、不阻塞查询主链路</t>
+        </is>
+      </c>
+      <c r="D83" s="46" t="n"/>
+      <c r="E83" s="46" t="n"/>
+      <c r="F83" s="46" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G83" s="46" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="H83" s="46" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="I83" s="46" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="87" t="inlineStr">
+        <is>
+          <t>F06-03</t>
+        </is>
+      </c>
+      <c r="B84" s="88" t="inlineStr">
+        <is>
+          <t>导出操作日志记录（模块6·合规管控、审计追踪与合规报表）· 共2个子任务</t>
+        </is>
+      </c>
+      <c r="C84" s="87" t="n"/>
+      <c r="D84" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="E84" s="89" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F84" s="89" t="n">
+        <v>1</v>
+      </c>
+      <c r="G84" s="89" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="H84" s="89" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I84" s="89" t="n">
+        <v>2.75</v>
+      </c>
+    </row>
+    <row r="85" ht="26" customHeight="1">
+      <c r="A85" s="15" t="inlineStr">
+        <is>
+          <t>F06-03-1</t>
+        </is>
+      </c>
+      <c r="B85" s="32" t="inlineStr">
+        <is>
+          <t>导出行为审计</t>
+        </is>
+      </c>
+      <c r="C85" s="32" t="inlineStr">
+        <is>
+          <t>导出范围/条数/导出人/IP/下载链接追踪</t>
+        </is>
+      </c>
+      <c r="D85" s="46" t="n"/>
+      <c r="E85" s="46" t="n"/>
+      <c r="F85" s="46" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="G85" s="46" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H85" s="46" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="I85" s="46" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="86" ht="26" customHeight="1">
+      <c r="A86" s="15" t="inlineStr">
+        <is>
+          <t>F06-03-2</t>
+        </is>
+      </c>
+      <c r="B86" s="32" t="inlineStr">
+        <is>
+          <t>大批量导出告警</t>
+        </is>
+      </c>
+      <c r="C86" s="32" t="inlineStr">
+        <is>
+          <t>阈值告警、审批联动</t>
+        </is>
+      </c>
+      <c r="D86" s="46" t="n"/>
+      <c r="E86" s="46" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F86" s="46" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="G86" s="46" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="H86" s="46" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="I86" s="46" t="n">
+        <v>1.25</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="90" t="inlineStr">
+        <is>
+          <t>F08-01</t>
+        </is>
+      </c>
+      <c r="B87" s="91" t="inlineStr">
+        <is>
+          <t>基础角色权限配置（模块8·系统全局治理、运维与监控）· 共3个子任务</t>
+        </is>
+      </c>
+      <c r="C87" s="90" t="n"/>
+      <c r="D87" s="92" t="n">
+        <v>1</v>
+      </c>
+      <c r="E87" s="92" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F87" s="92" t="n">
+        <v>2</v>
+      </c>
+      <c r="G87" s="92" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H87" s="92" t="n">
+        <v>1</v>
+      </c>
+      <c r="I87" s="92" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="88" ht="26" customHeight="1">
+      <c r="A88" s="15" t="inlineStr">
+        <is>
+          <t>F08-01-1</t>
+        </is>
+      </c>
+      <c r="B88" s="32" t="inlineStr">
+        <is>
+          <t>RBAC模型与权限矩阵</t>
+        </is>
+      </c>
+      <c r="C88" s="32" t="inlineStr">
+        <is>
+          <t>角色/菜单/数据范围/记录类型/操作权限定义</t>
+        </is>
+      </c>
+      <c r="D88" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="E88" s="46" t="n"/>
+      <c r="F88" s="46" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G88" s="46" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="H88" s="46" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I88" s="46" t="n">
+        <v>2.25</v>
+      </c>
+    </row>
+    <row r="89" ht="26" customHeight="1">
+      <c r="A89" s="15" t="inlineStr">
+        <is>
+          <t>F08-01-2</t>
+        </is>
+      </c>
+      <c r="B89" s="32" t="inlineStr">
+        <is>
+          <t>角色管理界面与API</t>
+        </is>
+      </c>
+      <c r="C89" s="32" t="inlineStr">
+        <is>
+          <t>角色CRUD、权限分配界面与接口</t>
+        </is>
+      </c>
+      <c r="D89" s="46" t="n"/>
+      <c r="E89" s="46" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F89" s="46" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G89" s="46" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H89" s="46" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="I89" s="46" t="n">
+        <v>2.75</v>
+      </c>
+    </row>
+    <row r="90" ht="26" customHeight="1">
+      <c r="A90" s="15" t="inlineStr">
+        <is>
+          <t>F08-01-3</t>
+        </is>
+      </c>
+      <c r="B90" s="32" t="inlineStr">
+        <is>
+          <t>权限校验与UC授权映射</t>
+        </is>
+      </c>
+      <c r="C90" s="32" t="inlineStr">
+        <is>
+          <t>菜单/接口级校验中间件、UC权限同步</t>
+        </is>
+      </c>
+      <c r="D90" s="46" t="n"/>
+      <c r="E90" s="46" t="n"/>
+      <c r="F90" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="G90" s="46" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="H90" s="46" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="I90" s="46" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="90" t="inlineStr">
+        <is>
+          <t>F08-02</t>
+        </is>
+      </c>
+      <c r="B91" s="91" t="inlineStr">
+        <is>
+          <t>用户账号管理（模块8·系统全局治理、运维与监控）· 共2个子任务</t>
+        </is>
+      </c>
+      <c r="C91" s="90" t="n"/>
+      <c r="D91" s="92" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="E91" s="92" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F91" s="92" t="n">
+        <v>1</v>
+      </c>
+      <c r="G91" s="92" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="H91" s="92" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I91" s="92" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="92" ht="26" customHeight="1">
+      <c r="A92" s="15" t="inlineStr">
+        <is>
+          <t>F08-02-1</t>
+        </is>
+      </c>
+      <c r="B92" s="32" t="inlineStr">
+        <is>
+          <t>账号CRUD与生命周期</t>
+        </is>
+      </c>
+      <c r="C92" s="32" t="inlineStr">
+        <is>
+          <t>创建/启用禁用/密码重置/有效期</t>
+        </is>
+      </c>
+      <c r="D92" s="46" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="E92" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="F92" s="46" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="G92" s="46" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H92" s="46" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="I92" s="46" t="n">
+        <v>2.75</v>
+      </c>
+    </row>
+    <row r="93" ht="26" customHeight="1">
+      <c r="A93" s="15" t="inlineStr">
+        <is>
+          <t>F08-02-2</t>
+        </is>
+      </c>
+      <c r="B93" s="32" t="inlineStr">
+        <is>
+          <t>账号与角色绑定</t>
+        </is>
+      </c>
+      <c r="C93" s="32" t="inlineStr">
+        <is>
+          <t>分配、批量操作、人员交接</t>
+        </is>
+      </c>
+      <c r="D93" s="46" t="n"/>
+      <c r="E93" s="46" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F93" s="46" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="G93" s="46" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="H93" s="46" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="I93" s="46" t="n">
+        <v>1.25</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="90" t="inlineStr">
+        <is>
+          <t>F08-03</t>
+        </is>
+      </c>
+      <c r="B94" s="91" t="inlineStr">
+        <is>
+          <t>企业SSO集成（模块8·系统全局治理、运维与监控）· 共3个子任务</t>
+        </is>
+      </c>
+      <c r="C94" s="90" t="n"/>
+      <c r="D94" s="92" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="E94" s="92" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="F94" s="92" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G94" s="92" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="H94" s="92" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="I94" s="92" t="n">
+        <v>6.75</v>
+      </c>
+    </row>
+    <row r="95" ht="26" customHeight="1">
+      <c r="A95" s="15" t="inlineStr">
+        <is>
+          <t>F08-03-1</t>
+        </is>
+      </c>
+      <c r="B95" s="32" t="inlineStr">
+        <is>
+          <t>Entra ID对接配置</t>
+        </is>
+      </c>
+      <c r="C95" s="32" t="inlineStr">
+        <is>
+          <t>应用注册、回调配置、claims映射</t>
+        </is>
+      </c>
+      <c r="D95" s="46" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="E95" s="46" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F95" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="G95" s="46" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H95" s="46" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="I95" s="46" t="n">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="96" ht="26" customHeight="1">
+      <c r="A96" s="15" t="inlineStr">
+        <is>
+          <t>F08-03-2</t>
+        </is>
+      </c>
+      <c r="B96" s="32" t="inlineStr">
+        <is>
+          <t>SSO登录链路</t>
+        </is>
+      </c>
+      <c r="C96" s="32" t="inlineStr">
+        <is>
+          <t>登录页、令牌交换、会话管理</t>
+        </is>
+      </c>
+      <c r="D96" s="46" t="n"/>
+      <c r="E96" s="46" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F96" s="46" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G96" s="46" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="H96" s="46" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="I96" s="46" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="97" ht="26" customHeight="1">
+      <c r="A97" s="15" t="inlineStr">
+        <is>
+          <t>F08-03-3</t>
+        </is>
+      </c>
+      <c r="B97" s="32" t="inlineStr">
+        <is>
+          <t>认证异常场景处理</t>
+        </is>
+      </c>
+      <c r="C97" s="32" t="inlineStr">
+        <is>
+          <t>认证失败、账号锁定、多账号冲突</t>
+        </is>
+      </c>
+      <c r="D97" s="46" t="n"/>
+      <c r="E97" s="46" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F97" s="46" t="n"/>
+      <c r="G97" s="46" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H97" s="46" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="I97" s="46" t="n">
+        <v>1.25</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="90" t="inlineStr">
+        <is>
+          <t>F08-04</t>
+        </is>
+      </c>
+      <c r="B98" s="91" t="inlineStr">
+        <is>
+          <t>用户身份自动识别与关联（模块8·系统全局治理、运维与监控）· 共2个子任务</t>
+        </is>
+      </c>
+      <c r="C98" s="90" t="n"/>
+      <c r="D98" s="92" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E98" s="92" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="F98" s="92" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="G98" s="92" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="H98" s="92" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I98" s="92" t="n">
+        <v>3.25</v>
+      </c>
+    </row>
+    <row r="99" ht="26" customHeight="1">
+      <c r="A99" s="15" t="inlineStr">
+        <is>
+          <t>F08-04-1</t>
+        </is>
+      </c>
+      <c r="B99" s="32" t="inlineStr">
+        <is>
+          <t>身份映射规则</t>
+        </is>
+      </c>
+      <c r="C99" s="32" t="inlineStr">
+        <is>
+          <t>企业账号↔RIMS用户映射、自动建号规则</t>
+        </is>
+      </c>
+      <c r="D99" s="46" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E99" s="46" t="n"/>
+      <c r="F99" s="46" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G99" s="46" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="H99" s="46" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="I99" s="46" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="100" ht="26" customHeight="1">
+      <c r="A100" s="15" t="inlineStr">
+        <is>
+          <t>F08-04-2</t>
+        </is>
+      </c>
+      <c r="B100" s="32" t="inlineStr">
+        <is>
+          <t>首登自动关联与角色赋予</t>
+        </is>
+      </c>
+      <c r="C100" s="32" t="inlineStr">
+        <is>
+          <t>默认角色、待分配队列</t>
+        </is>
+      </c>
+      <c r="D100" s="46" t="n"/>
+      <c r="E100" s="46" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="F100" s="46" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="G100" s="46" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H100" s="46" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="I100" s="46" t="n">
+        <v>1.75</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="90" t="inlineStr">
+        <is>
+          <t>F08-05</t>
+        </is>
+      </c>
+      <c r="B101" s="91" t="inlineStr">
+        <is>
+          <t>登录状态与异常访问控制（模块8·系统全局治理、运维与监控）· 共2个子任务</t>
+        </is>
+      </c>
+      <c r="C101" s="90" t="n"/>
+      <c r="D101" s="92" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="E101" s="92" t="n">
+        <v>1</v>
+      </c>
+      <c r="F101" s="92" t="n">
+        <v>1</v>
+      </c>
+      <c r="G101" s="92" t="n">
+        <v>1</v>
+      </c>
+      <c r="H101" s="92" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I101" s="92" t="n">
+        <v>3.75</v>
+      </c>
+    </row>
+    <row r="102" ht="26" customHeight="1">
+      <c r="A102" s="15" t="inlineStr">
+        <is>
+          <t>F08-05-1</t>
+        </is>
+      </c>
+      <c r="B102" s="32" t="inlineStr">
+        <is>
+          <t>会话与超时策略</t>
+        </is>
+      </c>
+      <c r="C102" s="32" t="inlineStr">
+        <is>
+          <t>超时控制、登出、单点登出</t>
+        </is>
+      </c>
+      <c r="D102" s="46" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="E102" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="F102" s="46" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="G102" s="46" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H102" s="46" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="I102" s="46" t="n">
+        <v>2.25</v>
+      </c>
+    </row>
+    <row r="103" ht="26" customHeight="1">
+      <c r="A103" s="15" t="inlineStr">
+        <is>
+          <t>F08-05-2</t>
+        </is>
+      </c>
+      <c r="B103" s="32" t="inlineStr">
+        <is>
+          <t>异常访问控制</t>
+        </is>
+      </c>
+      <c r="C103" s="32" t="inlineStr">
+        <is>
+          <t>账号锁定、认证失效限制访问、IP策略</t>
+        </is>
+      </c>
+      <c r="D103" s="46" t="n"/>
+      <c r="E103" s="46" t="n"/>
+      <c r="F103" s="46" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="G103" s="46" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H103" s="46" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="I103" s="46" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="8" t="inlineStr">
+        <is>
+          <t>总计</t>
+        </is>
+      </c>
+      <c r="B104" s="8" t="inlineStr">
+        <is>
+          <t>26项功能 × 75个子任务</t>
+        </is>
+      </c>
+      <c r="C104" s="93" t="inlineStr">
+        <is>
+          <t>独立直估（不含项目初始化/架构设计/集成/UAT/上线/PM等公共工作）</t>
+        </is>
+      </c>
+      <c r="D104" s="44" t="n">
+        <v>12.75</v>
+      </c>
+      <c r="E104" s="44" t="n">
+        <v>36.75</v>
+      </c>
+      <c r="F104" s="44" t="n">
+        <v>62</v>
+      </c>
+      <c r="G104" s="44" t="n">
+        <v>35.75</v>
+      </c>
+      <c r="H104" s="44" t="n">
+        <v>20</v>
+      </c>
+      <c r="I104" s="44" t="n">
+        <v>167.25</v>
+      </c>
+    </row>
+    <row r="106" ht="52" customHeight="1">
+      <c r="A106" s="94" t="inlineStr">
+        <is>
+          <t>对照说明（两个口径）：① 本表为子任务级独立直估，合计 167.25 人天（BA 12.75 / Wade 36.75 / DevB 62.0 / 测试 35.75 / SLC 20.0），其中「存储落地Iceberg/UC」「元数据驱动」「RBAC」等设计实现类子任务与计划公共行（架构与非功能设计等）存在重叠，且未假设跨功能复用（同一界面/中间件多处计价）。② 排期计划（WBS分解/功能视角分解）中：26项功能直接分摊仅 54.5 人天（大量开发工作量按阶段放在架构设计/集成/专项等公共行，公共合计 130.5 人天），总投入185人天。结论：功能直估 167.25 人天已达计划总投入的 90%，而计划中还有需求8.5/初始化9/PM15及集成·UAT·上线等纯公共工作未包含在本直估内——按传统粒度估算，3人×3个月偏紧，需依赖AI Native复用与生成提效吸收约50人天量级缺口，建议将本表作为功能规模基线并纳入风险跟踪。</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A2:I104"/>
+  <mergeCells count="28">
+    <mergeCell ref="B91:C91"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="B81:C81"/>
+    <mergeCell ref="B56:C56"/>
+    <mergeCell ref="B77:C77"/>
+    <mergeCell ref="B52:C52"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="B48:C48"/>
+    <mergeCell ref="B70:C70"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="B98:C98"/>
+    <mergeCell ref="B67:C67"/>
+    <mergeCell ref="B101:C101"/>
+    <mergeCell ref="B60:C60"/>
+    <mergeCell ref="A106:I106"/>
+    <mergeCell ref="B73:C73"/>
+    <mergeCell ref="B87:C87"/>
+    <mergeCell ref="B44:C44"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="B84:C84"/>
+    <mergeCell ref="B40:C40"/>
+    <mergeCell ref="B64:C64"/>
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="B36:C36"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="B94:C94"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
     <tabColor rgb="00FFC000"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
@@ -15896,7 +19436,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="0070AD47"/>
@@ -16263,7 +19803,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00A6A6A6"/>
@@ -16963,7 +20503,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00ED7D31"/>

--- a/RIMS项目WBS工作分解_AI Native版.xlsx
+++ b/RIMS项目WBS工作分解_AI Native版.xlsx
@@ -21,7 +21,6 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'WBS分解'!$A$3:$Q$164</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'WBS分解'!$1:$3</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'功能视角分解'!$A$2:$P$38</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'功能拆解估算'!$A$2:$I$104</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -141,7 +140,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="8">
     <border>
       <left/>
       <right/>
@@ -196,11 +195,44 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00BFBFBF"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00BFBFBF"/>
+      </left>
+      <right style="thin">
+        <color rgb="00BFBFBF"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00BFBFBF"/>
+      </left>
+      <right style="thin">
+        <color rgb="00BFBFBF"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00BFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="95">
+  <cellXfs count="104">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -452,6 +484,29 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -872,6 +927,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3" ht="20" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -1189,52 +1245,20 @@
       </c>
     </row>
     <row r="31" ht="30" customHeight="1">
-      <c r="A31" s="38" t="inlineStr">
-        <is>
-          <t>功能视角分解</t>
-        </is>
-      </c>
-      <c r="B31" s="4" t="inlineStr">
-        <is>
-          <t>按功能维度查看：26项功能×（BA/开发A/开发B/测试/文档）五类角色各自的工作内容与人天，另有9类公共支撑行（初始化/架构/集成/专项/上线/管理）；底部与185人天自动对账，可与按开发顺序的「WBS分解」页对照使用</t>
-        </is>
-      </c>
+      <c r="A31" s="38" t="n"/>
+      <c r="B31" s="4" t="n"/>
     </row>
     <row r="32" ht="30" customHeight="1">
-      <c r="A32" s="38" t="inlineStr">
-        <is>
-          <t>功能视角分解</t>
-        </is>
-      </c>
-      <c r="B32" s="4" t="inlineStr">
-        <is>
-          <t>按功能维度查看：26项功能×（BA/开发A/开发B/测试/文档）五类角色各自的工作内容与人天，另有9类公共支撑行（初始化/架构/集成/专项/上线/管理）；底部与185人天自动对账，可与按开发顺序的「WBS分解」页对照使用</t>
-        </is>
-      </c>
+      <c r="A32" s="38" t="n"/>
+      <c r="B32" s="4" t="n"/>
     </row>
     <row r="33" ht="30" customHeight="1">
-      <c r="A33" s="38" t="inlineStr">
-        <is>
-          <t>功能视角分解</t>
-        </is>
-      </c>
-      <c r="B33" s="4" t="inlineStr">
-        <is>
-          <t>按功能维度查看：26项功能×（BA/开发A/开发B/测试/文档）五类角色各自的工作内容与人天，另有9类公共支撑行（初始化/架构/集成/专项/上线/管理）；底部与185人天自动对账，可与按开发顺序的「WBS分解」页对照使用</t>
-        </is>
-      </c>
+      <c r="A33" s="38" t="n"/>
+      <c r="B33" s="4" t="n"/>
     </row>
     <row r="34" ht="30" customHeight="1">
-      <c r="A34" s="38" t="inlineStr">
-        <is>
-          <t>功能视角分解</t>
-        </is>
-      </c>
-      <c r="B34" s="4" t="inlineStr">
-        <is>
-          <t>按功能维度查看：26项功能×（BA/开发A/开发B/测试/文档）五类角色各自的工作内容与人天，另有9类公共支撑行（初始化/架构/集成/专项/上线/管理）；底部与185人天自动对账，可与按开发顺序的「WBS分解」页对照使用</t>
-        </is>
-      </c>
+      <c r="A34" s="38" t="n"/>
+      <c r="B34" s="4" t="n"/>
     </row>
     <row r="35" ht="30" customHeight="1">
       <c r="A35" s="38" t="inlineStr">
@@ -1244,21 +1268,13 @@
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>子任务级直估：26项功能下钻到75个子任务/工作包（如F01-01拆为原系统录入/DB连接/表勾选/保留期配置/Iceberg·UC存储落地/导入作业/监控），按BA/开发A/开发B/测试/SLC文档独立估人天，不锚定185人天；底部附与计划口径的对照与差异说明</t>
+          <t>子任务级直估：26项功能下钻到75个子任务/工作包（如F01-01拆为原系统录入/DB连接/表勾选/保留期配置/Iceberg·UC存储落地/导入作业/监控），按BA/开发A/开发B/测试/SLC文档独立估人天，不锚定185人天；功能名称与功能小计为纵向合并单元格；底部附与计划口径的对照与差异说明</t>
         </is>
       </c>
     </row>
     <row r="36" ht="30" customHeight="1">
-      <c r="A36" s="38" t="inlineStr">
-        <is>
-          <t>功能拆解估算</t>
-        </is>
-      </c>
-      <c r="B36" s="4" t="inlineStr">
-        <is>
-          <t>子任务级直估：26项功能下钻到75个子任务/工作包（如F01-01拆为原系统录入/DB连接/表勾选/保留期配置/Iceberg·UC存储落地/导入作业/监控），按BA/开发A/开发B/测试/SLC文档独立估人天，不锚定185人天；底部附与计划口径的对照与差异说明</t>
-        </is>
-      </c>
+      <c r="A36" s="38" t="n"/>
+      <c r="B36" s="4" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -15770,24 +15786,26 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I106"/>
+  <dimension ref="A1:K80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
-    <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="44" customWidth="1" min="3" max="3"/>
-    <col width="8" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
     <col width="8" customWidth="1" min="8" max="8"/>
     <col width="8" customWidth="1" min="9" max="9"/>
+    <col width="8" customWidth="1" min="10" max="10"/>
+    <col width="9" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>功能拆解估算（子任务级直估）：每个功能下钻到子功能/工作包，按角色直估人天 — 独立估算，不锚定排期185人天</t>
+          <t>功能拆解估算（子任务级直估）：功能信息纵向合并对应多个子任务 — 独立估算，不锚定排期185人天</t>
         </is>
       </c>
     </row>
@@ -15799,167 +15817,191 @@
       </c>
       <c r="B2" s="7" t="inlineStr">
         <is>
+          <t>功能名称</t>
+        </is>
+      </c>
+      <c r="C2" s="7" t="inlineStr">
+        <is>
           <t>子任务/工作包</t>
         </is>
       </c>
-      <c r="C2" s="7" t="inlineStr">
+      <c r="D2" s="7" t="inlineStr">
         <is>
           <t>工作内容要点</t>
         </is>
       </c>
-      <c r="D2" s="7" t="inlineStr">
+      <c r="E2" s="7" t="inlineStr">
         <is>
           <t>BA人天</t>
         </is>
       </c>
-      <c r="E2" s="7" t="inlineStr">
+      <c r="F2" s="7" t="inlineStr">
         <is>
           <t>开发A·Wade</t>
         </is>
       </c>
-      <c r="F2" s="7" t="inlineStr">
+      <c r="G2" s="7" t="inlineStr">
         <is>
           <t>开发B·DevB</t>
         </is>
       </c>
-      <c r="G2" s="7" t="inlineStr">
+      <c r="H2" s="7" t="inlineStr">
         <is>
           <t>测试人天</t>
         </is>
       </c>
-      <c r="H2" s="7" t="inlineStr">
+      <c r="I2" s="7" t="inlineStr">
         <is>
           <t>SLC文档</t>
         </is>
       </c>
-      <c r="I2" s="7" t="inlineStr">
+      <c r="J2" s="7" t="inlineStr">
         <is>
           <t>小计</t>
         </is>
       </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="72" t="inlineStr">
-        <is>
-          <t>F01-01</t>
-        </is>
-      </c>
-      <c r="B3" s="73" t="inlineStr">
-        <is>
-          <t>结构化历史数据批量导入（模块1·存量历史数据迁移与标准化）· 共7个子任务</t>
-        </is>
-      </c>
-      <c r="C3" s="72" t="n"/>
-      <c r="D3" s="74" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="E3" s="74" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="F3" s="74" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="G3" s="74" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="H3" s="74" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="I3" s="74" t="n">
+      <c r="K2" s="7" t="inlineStr">
+        <is>
+          <t>功能小计</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="26" customHeight="1">
+      <c r="A3" s="15" t="inlineStr">
+        <is>
+          <t>F01-01-1</t>
+        </is>
+      </c>
+      <c r="B3" s="95" t="inlineStr">
+        <is>
+          <t>结构化历史数据批量导入</t>
+        </is>
+      </c>
+      <c r="C3" s="32" t="inlineStr">
+        <is>
+          <t>原系统基本信息录入</t>
+        </is>
+      </c>
+      <c r="D3" s="32" t="inlineStr">
+        <is>
+          <t>来源系统档案：系统编码/名称/业务域/责任人/退役批次；录入与维护界面+存储API</t>
+        </is>
+      </c>
+      <c r="E3" s="46" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F3" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="G3" s="46" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H3" s="46" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I3" s="46" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="J3" s="46" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="K3" s="74" t="n">
         <v>20.75</v>
       </c>
     </row>
     <row r="4" ht="26" customHeight="1">
       <c r="A4" s="15" t="inlineStr">
         <is>
-          <t>F01-01-1</t>
-        </is>
-      </c>
-      <c r="B4" s="32" t="inlineStr">
-        <is>
-          <t>原系统基本信息录入</t>
-        </is>
-      </c>
+          <t>F01-01-2</t>
+        </is>
+      </c>
+      <c r="B4" s="17" t="n"/>
       <c r="C4" s="32" t="inlineStr">
         <is>
-          <t>来源系统档案：系统编码/名称/业务域/责任人/退役批次；录入与维护界面+存储API</t>
-        </is>
-      </c>
-      <c r="D4" s="46" t="n">
+          <t>源库DB连接配置</t>
+        </is>
+      </c>
+      <c r="D4" s="32" t="inlineStr">
+        <is>
+          <t>DB类型/连接串录入，账号密码Key Vault加密存储，连通性测试</t>
+        </is>
+      </c>
+      <c r="E4" s="46" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="F4" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="G4" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="H4" s="46" t="n">
         <v>0.5</v>
       </c>
-      <c r="E4" s="46" t="n">
-        <v>1</v>
-      </c>
-      <c r="F4" s="46" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G4" s="46" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="H4" s="46" t="n">
+      <c r="I4" s="46" t="n">
         <v>0.25</v>
       </c>
-      <c r="I4" s="46" t="n">
-        <v>2.75</v>
-      </c>
+      <c r="J4" s="46" t="n">
+        <v>3</v>
+      </c>
+      <c r="K4" s="17" t="n"/>
     </row>
     <row r="5" ht="26" customHeight="1">
       <c r="A5" s="15" t="inlineStr">
         <is>
-          <t>F01-01-2</t>
-        </is>
-      </c>
-      <c r="B5" s="32" t="inlineStr">
-        <is>
-          <t>源库DB连接配置</t>
-        </is>
-      </c>
+          <t>F01-01-3</t>
+        </is>
+      </c>
+      <c r="B5" s="17" t="n"/>
       <c r="C5" s="32" t="inlineStr">
         <is>
-          <t>DB类型/连接串录入，账号密码Key Vault加密存储，连通性测试</t>
-        </is>
-      </c>
-      <c r="D5" s="46" t="n">
+          <t>同步表勾选</t>
+        </is>
+      </c>
+      <c r="D5" s="32" t="inlineStr">
+        <is>
+          <t>拉取源表清单、勾选同步范围、数据量预估与全选过滤</t>
+        </is>
+      </c>
+      <c r="E5" s="46" t="n">
         <v>0.25</v>
-      </c>
-      <c r="E5" s="46" t="n">
-        <v>1</v>
       </c>
       <c r="F5" s="46" t="n">
         <v>1</v>
       </c>
       <c r="G5" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="H5" s="46" t="n">
         <v>0.5</v>
       </c>
-      <c r="H5" s="46" t="n">
+      <c r="I5" s="46" t="n">
         <v>0.25</v>
       </c>
-      <c r="I5" s="46" t="n">
+      <c r="J5" s="46" t="n">
         <v>3</v>
       </c>
+      <c r="K5" s="17" t="n"/>
     </row>
     <row r="6" ht="26" customHeight="1">
       <c r="A6" s="15" t="inlineStr">
         <is>
-          <t>F01-01-3</t>
-        </is>
-      </c>
-      <c r="B6" s="32" t="inlineStr">
-        <is>
-          <t>同步表勾选</t>
-        </is>
-      </c>
+          <t>F01-01-4</t>
+        </is>
+      </c>
+      <c r="B6" s="17" t="n"/>
       <c r="C6" s="32" t="inlineStr">
         <is>
-          <t>拉取源表清单、勾选同步范围、数据量预估与全选过滤</t>
-        </is>
-      </c>
-      <c r="D6" s="46" t="n">
-        <v>0.25</v>
+          <t>保留期限与迁移参数配置</t>
+        </is>
+      </c>
+      <c r="D6" s="32" t="inlineStr">
+        <is>
+          <t>保留策略绑定、迁移批次命名、并发/限速参数</t>
+        </is>
       </c>
       <c r="E6" s="46" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F6" s="46" t="n">
         <v>1</v>
@@ -15971,556 +16013,622 @@
         <v>0.25</v>
       </c>
       <c r="I6" s="46" t="n">
-        <v>3</v>
-      </c>
+        <v>0.25</v>
+      </c>
+      <c r="J6" s="46" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="K6" s="17" t="n"/>
     </row>
     <row r="7" ht="26" customHeight="1">
       <c r="A7" s="15" t="inlineStr">
         <is>
-          <t>F01-01-4</t>
-        </is>
-      </c>
-      <c r="B7" s="32" t="inlineStr">
-        <is>
-          <t>保留期限与迁移参数配置</t>
-        </is>
-      </c>
+          <t>F01-01-5</t>
+        </is>
+      </c>
+      <c r="B7" s="17" t="n"/>
       <c r="C7" s="32" t="inlineStr">
         <is>
-          <t>保留策略绑定、迁移批次命名、并发/限速参数</t>
-        </is>
-      </c>
-      <c r="D7" s="46" t="n">
+          <t>存储落地实现（Iceberg/UC）</t>
+        </is>
+      </c>
+      <c r="D7" s="32" t="inlineStr">
+        <is>
+          <t>磁盘目录布局、Iceberg表属性与分区策略、UC目录/Schema/授权配置化</t>
+        </is>
+      </c>
+      <c r="E7" s="46" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="F7" s="46" t="n"/>
+      <c r="G7" s="46" t="n">
+        <v>2</v>
+      </c>
+      <c r="H7" s="46" t="n">
         <v>0.5</v>
       </c>
-      <c r="E7" s="46" t="n">
-        <v>1</v>
-      </c>
-      <c r="F7" s="46" t="n">
+      <c r="I7" s="46" t="n">
         <v>0.5</v>
       </c>
-      <c r="G7" s="46" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="H7" s="46" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="I7" s="46" t="n">
-        <v>2.5</v>
-      </c>
+      <c r="J7" s="46" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="K7" s="17" t="n"/>
     </row>
     <row r="8" ht="26" customHeight="1">
       <c r="A8" s="15" t="inlineStr">
         <is>
-          <t>F01-01-5</t>
-        </is>
-      </c>
-      <c r="B8" s="32" t="inlineStr">
-        <is>
-          <t>存储落地实现（Iceberg/UC）</t>
-        </is>
-      </c>
+          <t>F01-01-6</t>
+        </is>
+      </c>
+      <c r="B8" s="17" t="n"/>
       <c r="C8" s="32" t="inlineStr">
         <is>
-          <t>磁盘目录布局、Iceberg表属性与分区策略、UC目录/Schema/授权配置化</t>
-        </is>
-      </c>
-      <c r="D8" s="46" t="n">
-        <v>0.25</v>
+          <t>SeaTunnel批量导入作业</t>
+        </is>
+      </c>
+      <c r="D8" s="32" t="inlineStr">
+        <is>
+          <t>作业配置生成器、分片/断点续传/限速执行</t>
+        </is>
       </c>
       <c r="E8" s="46" t="n"/>
       <c r="F8" s="46" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G8" s="46" t="n">
         <v>2</v>
       </c>
-      <c r="G8" s="46" t="n">
+      <c r="H8" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="I8" s="46" t="n">
         <v>0.5</v>
       </c>
-      <c r="H8" s="46" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="I8" s="46" t="n">
-        <v>3.25</v>
-      </c>
+      <c r="J8" s="46" t="n">
+        <v>4</v>
+      </c>
+      <c r="K8" s="17" t="n"/>
     </row>
     <row r="9" ht="26" customHeight="1">
       <c r="A9" s="15" t="inlineStr">
         <is>
-          <t>F01-01-6</t>
-        </is>
-      </c>
-      <c r="B9" s="32" t="inlineStr">
-        <is>
-          <t>SeaTunnel批量导入作业</t>
-        </is>
-      </c>
+          <t>F01-01-7</t>
+        </is>
+      </c>
+      <c r="B9" s="17" t="n"/>
       <c r="C9" s="32" t="inlineStr">
         <is>
-          <t>作业配置生成器、分片/断点续传/限速执行</t>
-        </is>
-      </c>
-      <c r="D9" s="46" t="n"/>
-      <c r="E9" s="46" t="n">
+          <t>导入执行与监控</t>
+        </is>
+      </c>
+      <c r="D9" s="32" t="inlineStr">
+        <is>
+          <t>任务状态/进度/失败重试/日志查看</t>
+        </is>
+      </c>
+      <c r="E9" s="46" t="n"/>
+      <c r="F9" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="G9" s="46" t="n">
         <v>0.5</v>
-      </c>
-      <c r="F9" s="46" t="n">
-        <v>2</v>
-      </c>
-      <c r="G9" s="46" t="n">
-        <v>1</v>
       </c>
       <c r="H9" s="46" t="n">
         <v>0.5</v>
       </c>
       <c r="I9" s="46" t="n">
-        <v>4</v>
-      </c>
+        <v>0.25</v>
+      </c>
+      <c r="J9" s="46" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="K9" s="17" t="n"/>
     </row>
     <row r="10" ht="26" customHeight="1">
       <c r="A10" s="15" t="inlineStr">
         <is>
-          <t>F01-01-7</t>
-        </is>
-      </c>
-      <c r="B10" s="32" t="inlineStr">
-        <is>
-          <t>导入执行与监控</t>
+          <t>F01-02-1</t>
+        </is>
+      </c>
+      <c r="B10" s="95" t="inlineStr">
+        <is>
+          <t>非结构化文件及离线包批量导入</t>
         </is>
       </c>
       <c r="C10" s="32" t="inlineStr">
         <is>
-          <t>任务状态/进度/失败重试/日志查看</t>
-        </is>
-      </c>
-      <c r="D10" s="46" t="n"/>
+          <t>文件来源登记与上传通道</t>
+        </is>
+      </c>
+      <c r="D10" s="32" t="inlineStr">
+        <is>
+          <t>在线上传/共享路径挂载/离线介质登记</t>
+        </is>
+      </c>
       <c r="E10" s="46" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="F10" s="46" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G10" s="46" t="n">
         <v>1</v>
       </c>
-      <c r="F10" s="46" t="n">
+      <c r="H10" s="46" t="n">
         <v>0.5</v>
       </c>
-      <c r="G10" s="46" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="H10" s="46" t="n">
+      <c r="I10" s="46" t="n">
         <v>0.25</v>
       </c>
-      <c r="I10" s="46" t="n">
-        <v>2.25</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="72" t="inlineStr">
-        <is>
-          <t>F01-02</t>
-        </is>
-      </c>
-      <c r="B11" s="73" t="inlineStr">
-        <is>
-          <t>非结构化文件及离线包批量导入（模块1·存量历史数据迁移与标准化）· 共4个子任务</t>
-        </is>
-      </c>
-      <c r="C11" s="72" t="n"/>
-      <c r="D11" s="74" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="E11" s="74" t="n">
-        <v>3</v>
-      </c>
-      <c r="F11" s="74" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="G11" s="74" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="H11" s="74" t="n">
+      <c r="J10" s="46" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="K10" s="74" t="n">
+        <v>12.75</v>
+      </c>
+    </row>
+    <row r="11" ht="26" customHeight="1">
+      <c r="A11" s="15" t="inlineStr">
+        <is>
+          <t>F01-02-2</t>
+        </is>
+      </c>
+      <c r="B11" s="17" t="n"/>
+      <c r="C11" s="32" t="inlineStr">
+        <is>
+          <t>大文件分片上传与断点续传</t>
+        </is>
+      </c>
+      <c r="D11" s="32" t="inlineStr">
+        <is>
+          <t>前端分片上传、后端合并与校验</t>
+        </is>
+      </c>
+      <c r="E11" s="46" t="n"/>
+      <c r="F11" s="46" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G11" s="46" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H11" s="46" t="n">
         <v>1</v>
       </c>
-      <c r="I11" s="74" t="n">
-        <v>12.75</v>
-      </c>
+      <c r="I11" s="46" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="J11" s="46" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="K11" s="17" t="n"/>
     </row>
     <row r="12" ht="26" customHeight="1">
       <c r="A12" s="15" t="inlineStr">
         <is>
-          <t>F01-02-1</t>
-        </is>
-      </c>
-      <c r="B12" s="32" t="inlineStr">
-        <is>
-          <t>文件来源登记与上传通道</t>
-        </is>
-      </c>
+          <t>F01-02-3</t>
+        </is>
+      </c>
+      <c r="B12" s="17" t="n"/>
       <c r="C12" s="32" t="inlineStr">
         <is>
-          <t>在线上传/共享路径挂载/离线介质登记</t>
-        </is>
-      </c>
-      <c r="D12" s="46" t="n">
+          <t>文件包解析</t>
+        </is>
+      </c>
+      <c r="D12" s="32" t="inlineStr">
+        <is>
+          <t>zip/tar/数据库备份包识别与展开、原始属性保留</t>
+        </is>
+      </c>
+      <c r="E12" s="46" t="n"/>
+      <c r="F12" s="46" t="n"/>
+      <c r="G12" s="46" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H12" s="46" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="I12" s="46" t="n">
         <v>0.25</v>
       </c>
-      <c r="E12" s="46" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="F12" s="46" t="n">
-        <v>1</v>
-      </c>
-      <c r="G12" s="46" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="H12" s="46" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="I12" s="46" t="n">
-        <v>3.5</v>
-      </c>
+      <c r="J12" s="46" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="K12" s="17" t="n"/>
     </row>
     <row r="13" ht="26" customHeight="1">
       <c r="A13" s="15" t="inlineStr">
         <is>
-          <t>F01-02-2</t>
-        </is>
-      </c>
-      <c r="B13" s="32" t="inlineStr">
-        <is>
-          <t>大文件分片上传与断点续传</t>
-        </is>
-      </c>
+          <t>F01-02-4</t>
+        </is>
+      </c>
+      <c r="B13" s="17" t="n"/>
       <c r="C13" s="32" t="inlineStr">
         <is>
-          <t>前端分片上传、后端合并与校验</t>
-        </is>
-      </c>
-      <c r="D13" s="46" t="n"/>
+          <t>附件元数据与Blob存储布局</t>
+        </is>
+      </c>
+      <c r="D13" s="32" t="inlineStr">
+        <is>
+          <t>附件索引表、路径规范、与结构化记录关联</t>
+        </is>
+      </c>
       <c r="E13" s="46" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="F13" s="46" t="n"/>
+      <c r="G13" s="46" t="n">
         <v>1.5</v>
       </c>
-      <c r="F13" s="46" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="G13" s="46" t="n">
-        <v>1</v>
-      </c>
       <c r="H13" s="46" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I13" s="46" t="n">
         <v>0.25</v>
       </c>
-      <c r="I13" s="46" t="n">
-        <v>4.25</v>
-      </c>
+      <c r="J13" s="46" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="K13" s="17" t="n"/>
     </row>
     <row r="14" ht="26" customHeight="1">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>F01-02-3</t>
-        </is>
-      </c>
-      <c r="B14" s="32" t="inlineStr">
-        <is>
-          <t>文件包解析</t>
+          <t>F01-03-1</t>
+        </is>
+      </c>
+      <c r="B14" s="95" t="inlineStr">
+        <is>
+          <t>数据导入规则配置</t>
         </is>
       </c>
       <c r="C14" s="32" t="inlineStr">
         <is>
-          <t>zip/tar/数据库备份包识别与展开、原始属性保留</t>
-        </is>
-      </c>
-      <c r="D14" s="46" t="n"/>
-      <c r="E14" s="46" t="n"/>
+          <t>字段映射规则配置</t>
+        </is>
+      </c>
+      <c r="D14" s="32" t="inlineStr">
+        <is>
+          <t>源字段→标准字段映射界面、自动映射建议</t>
+        </is>
+      </c>
+      <c r="E14" s="46" t="n">
+        <v>0.5</v>
+      </c>
       <c r="F14" s="46" t="n">
         <v>1.5</v>
       </c>
       <c r="G14" s="46" t="n">
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
       <c r="H14" s="46" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I14" s="46" t="n">
         <v>0.25</v>
       </c>
-      <c r="I14" s="46" t="n">
-        <v>2.5</v>
+      <c r="J14" s="46" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="K14" s="74" t="n">
+        <v>11.25</v>
       </c>
     </row>
     <row r="15" ht="26" customHeight="1">
       <c r="A15" s="15" t="inlineStr">
         <is>
-          <t>F01-02-4</t>
-        </is>
-      </c>
-      <c r="B15" s="32" t="inlineStr">
-        <is>
-          <t>附件元数据与Blob存储布局</t>
-        </is>
-      </c>
+          <t>F01-03-2</t>
+        </is>
+      </c>
+      <c r="B15" s="17" t="n"/>
       <c r="C15" s="32" t="inlineStr">
         <is>
-          <t>附件索引表、路径规范、与结构化记录关联</t>
-        </is>
-      </c>
-      <c r="D15" s="46" t="n">
+          <t>格式转换与清洗规则</t>
+        </is>
+      </c>
+      <c r="D15" s="32" t="inlineStr">
+        <is>
+          <t>类型转换/编码/默认值/脏数据处理策略</t>
+        </is>
+      </c>
+      <c r="E15" s="46" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F15" s="46" t="n"/>
+      <c r="G15" s="46" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H15" s="46" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="I15" s="46" t="n">
         <v>0.25</v>
       </c>
-      <c r="E15" s="46" t="n"/>
-      <c r="F15" s="46" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="G15" s="46" t="n">
+      <c r="J15" s="46" t="n">
+        <v>3</v>
+      </c>
+      <c r="K15" s="17" t="n"/>
+    </row>
+    <row r="16" ht="26" customHeight="1">
+      <c r="A16" s="15" t="inlineStr">
+        <is>
+          <t>F01-03-3</t>
+        </is>
+      </c>
+      <c r="B16" s="17" t="n"/>
+      <c r="C16" s="32" t="inlineStr">
+        <is>
+          <t>校验规则配置</t>
+        </is>
+      </c>
+      <c r="D16" s="32" t="inlineStr">
+        <is>
+          <t>必填/唯一/范围/自定义表达式校验</t>
+        </is>
+      </c>
+      <c r="E16" s="46" t="n"/>
+      <c r="F16" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="G16" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="H16" s="46" t="n">
         <v>0.5</v>
       </c>
-      <c r="H15" s="46" t="n">
+      <c r="I16" s="46" t="n">
         <v>0.25</v>
       </c>
-      <c r="I15" s="46" t="n">
-        <v>2.5</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="72" t="inlineStr">
-        <is>
-          <t>F01-03</t>
-        </is>
-      </c>
-      <c r="B16" s="73" t="inlineStr">
-        <is>
-          <t>数据导入规则配置（模块1·存量历史数据迁移与标准化）· 共4个子任务</t>
-        </is>
-      </c>
-      <c r="C16" s="72" t="n"/>
-      <c r="D16" s="74" t="n">
-        <v>1</v>
-      </c>
-      <c r="E16" s="74" t="n">
-        <v>3</v>
-      </c>
-      <c r="F16" s="74" t="n">
-        <v>4</v>
-      </c>
-      <c r="G16" s="74" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="H16" s="74" t="n">
-        <v>1</v>
-      </c>
-      <c r="I16" s="74" t="n">
-        <v>11.25</v>
-      </c>
+      <c r="J16" s="46" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="K16" s="17" t="n"/>
     </row>
     <row r="17" ht="26" customHeight="1">
       <c r="A17" s="15" t="inlineStr">
         <is>
-          <t>F01-03-1</t>
-        </is>
-      </c>
-      <c r="B17" s="32" t="inlineStr">
-        <is>
-          <t>字段映射规则配置</t>
-        </is>
-      </c>
+          <t>F01-03-4</t>
+        </is>
+      </c>
+      <c r="B17" s="17" t="n"/>
       <c r="C17" s="32" t="inlineStr">
         <is>
-          <t>源字段→标准字段映射界面、自动映射建议</t>
-        </is>
-      </c>
-      <c r="D17" s="46" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="E17" s="46" t="n">
-        <v>1.5</v>
-      </c>
+          <t>规则版本与试跑预览</t>
+        </is>
+      </c>
+      <c r="D17" s="32" t="inlineStr">
+        <is>
+          <t>规则版本管理、样本试跑与结果预览</t>
+        </is>
+      </c>
+      <c r="E17" s="46" t="n"/>
       <c r="F17" s="46" t="n">
         <v>0.5</v>
       </c>
       <c r="G17" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="H17" s="46" t="n">
         <v>0.5</v>
       </c>
-      <c r="H17" s="46" t="n">
+      <c r="I17" s="46" t="n">
         <v>0.25</v>
       </c>
-      <c r="I17" s="46" t="n">
-        <v>3.25</v>
-      </c>
+      <c r="J17" s="46" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="K17" s="17" t="n"/>
     </row>
     <row r="18" ht="26" customHeight="1">
       <c r="A18" s="15" t="inlineStr">
         <is>
-          <t>F01-03-2</t>
-        </is>
-      </c>
-      <c r="B18" s="32" t="inlineStr">
-        <is>
-          <t>格式转换与清洗规则</t>
+          <t>F01-04-1</t>
+        </is>
+      </c>
+      <c r="B18" s="95" t="inlineStr">
+        <is>
+          <t>迁移前完整性基准记录</t>
         </is>
       </c>
       <c r="C18" s="32" t="inlineStr">
         <is>
-          <t>类型转换/编码/默认值/脏数据处理策略</t>
-        </is>
-      </c>
-      <c r="D18" s="46" t="n">
+          <t>基准采集策略定义</t>
+        </is>
+      </c>
+      <c r="D18" s="32" t="inlineStr">
+        <is>
+          <t>行数/校验和/SHA-256抽样口径</t>
+        </is>
+      </c>
+      <c r="E18" s="46" t="n">
         <v>0.5</v>
       </c>
-      <c r="E18" s="46" t="n"/>
-      <c r="F18" s="46" t="n">
-        <v>1.5</v>
-      </c>
+      <c r="F18" s="46" t="n"/>
       <c r="G18" s="46" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="H18" s="46" t="n">
         <v>0.25</v>
       </c>
       <c r="I18" s="46" t="n">
-        <v>3</v>
+        <v>0.25</v>
+      </c>
+      <c r="J18" s="46" t="n">
+        <v>2</v>
+      </c>
+      <c r="K18" s="74" t="n">
+        <v>5.5</v>
       </c>
     </row>
     <row r="19" ht="26" customHeight="1">
       <c r="A19" s="15" t="inlineStr">
         <is>
-          <t>F01-03-3</t>
-        </is>
-      </c>
-      <c r="B19" s="32" t="inlineStr">
-        <is>
-          <t>校验规则配置</t>
-        </is>
-      </c>
+          <t>F01-04-2</t>
+        </is>
+      </c>
+      <c r="B19" s="17" t="n"/>
       <c r="C19" s="32" t="inlineStr">
         <is>
-          <t>必填/唯一/范围/自定义表达式校验</t>
-        </is>
-      </c>
-      <c r="D19" s="46" t="n"/>
-      <c r="E19" s="46" t="n">
-        <v>1</v>
-      </c>
-      <c r="F19" s="46" t="n">
-        <v>1</v>
-      </c>
+          <t>基准采集作业与存储</t>
+        </is>
+      </c>
+      <c r="D19" s="32" t="inlineStr">
+        <is>
+          <t>源端基准快照生成、基准库表</t>
+        </is>
+      </c>
+      <c r="E19" s="46" t="n"/>
+      <c r="F19" s="46" t="n"/>
       <c r="G19" s="46" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H19" s="46" t="n">
         <v>0.5</v>
       </c>
-      <c r="H19" s="46" t="n">
+      <c r="I19" s="46" t="n">
         <v>0.25</v>
       </c>
-      <c r="I19" s="46" t="n">
-        <v>2.75</v>
-      </c>
+      <c r="J19" s="46" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="K19" s="17" t="n"/>
     </row>
     <row r="20" ht="26" customHeight="1">
       <c r="A20" s="15" t="inlineStr">
         <is>
-          <t>F01-03-4</t>
-        </is>
-      </c>
-      <c r="B20" s="32" t="inlineStr">
-        <is>
-          <t>规则版本与试跑预览</t>
-        </is>
-      </c>
+          <t>F01-04-3</t>
+        </is>
+      </c>
+      <c r="B20" s="17" t="n"/>
       <c r="C20" s="32" t="inlineStr">
         <is>
-          <t>规则版本管理、样本试跑与结果预览</t>
-        </is>
-      </c>
-      <c r="D20" s="46" t="n"/>
-      <c r="E20" s="46" t="n">
+          <t>基准报告查询展示</t>
+        </is>
+      </c>
+      <c r="D20" s="32" t="inlineStr">
+        <is>
+          <t>基准结果展示与导出</t>
+        </is>
+      </c>
+      <c r="E20" s="46" t="n"/>
+      <c r="F20" s="46" t="n">
         <v>0.5</v>
       </c>
-      <c r="F20" s="46" t="n">
-        <v>1</v>
-      </c>
       <c r="G20" s="46" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="H20" s="46" t="n">
         <v>0.25</v>
       </c>
       <c r="I20" s="46" t="n">
-        <v>2.25</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="72" t="inlineStr">
-        <is>
-          <t>F01-04</t>
-        </is>
-      </c>
-      <c r="B21" s="73" t="inlineStr">
-        <is>
-          <t>迁移前完整性基准记录（模块1·存量历史数据迁移与标准化）· 共3个子任务</t>
-        </is>
-      </c>
-      <c r="C21" s="72" t="n"/>
-      <c r="D21" s="74" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="E21" s="74" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F21" s="74" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="G21" s="74" t="n">
-        <v>1</v>
-      </c>
-      <c r="H21" s="74" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="J20" s="46" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="K20" s="17" t="n"/>
+    </row>
+    <row r="21" ht="26" customHeight="1">
+      <c r="A21" s="15" t="inlineStr">
+        <is>
+          <t>F01-05-1</t>
+        </is>
+      </c>
+      <c r="B21" s="95" t="inlineStr">
+        <is>
+          <t>迁移后完整性比对</t>
+        </is>
+      </c>
+      <c r="C21" s="32" t="inlineStr">
+        <is>
+          <t>比对引擎</t>
+        </is>
+      </c>
+      <c r="D21" s="32" t="inlineStr">
+        <is>
+          <t>RAW/CURATED逐层行数与校验和比对、抽样SHA-256</t>
+        </is>
+      </c>
+      <c r="E21" s="46" t="n"/>
+      <c r="F21" s="46" t="n"/>
+      <c r="G21" s="46" t="n">
+        <v>2</v>
+      </c>
+      <c r="H21" s="46" t="n">
         <v>0.75</v>
       </c>
-      <c r="I21" s="74" t="n">
+      <c r="I21" s="46" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="J21" s="46" t="n">
+        <v>3</v>
+      </c>
+      <c r="K21" s="74" t="n">
         <v>5.5</v>
       </c>
     </row>
     <row r="22" ht="26" customHeight="1">
       <c r="A22" s="15" t="inlineStr">
         <is>
-          <t>F01-04-1</t>
-        </is>
-      </c>
-      <c r="B22" s="32" t="inlineStr">
-        <is>
-          <t>基准采集策略定义</t>
-        </is>
-      </c>
+          <t>F01-05-2</t>
+        </is>
+      </c>
+      <c r="B22" s="17" t="n"/>
       <c r="C22" s="32" t="inlineStr">
         <is>
-          <t>行数/校验和/SHA-256抽样口径</t>
-        </is>
-      </c>
-      <c r="D22" s="46" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="E22" s="46" t="n"/>
+          <t>差异报告与处理流程</t>
+        </is>
+      </c>
+      <c r="D22" s="32" t="inlineStr">
+        <is>
+          <t>差异清单、重迁/豁免记录</t>
+        </is>
+      </c>
+      <c r="E22" s="46" t="n">
+        <v>0.25</v>
+      </c>
       <c r="F22" s="46" t="n">
         <v>1</v>
       </c>
       <c r="G22" s="46" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H22" s="46" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I22" s="46" t="n">
         <v>0.25</v>
       </c>
-      <c r="H22" s="46" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="I22" s="46" t="n">
-        <v>2</v>
-      </c>
+      <c r="J22" s="46" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="K22" s="17" t="n"/>
     </row>
     <row r="23" ht="26" customHeight="1">
       <c r="A23" s="15" t="inlineStr">
         <is>
-          <t>F01-04-2</t>
-        </is>
-      </c>
-      <c r="B23" s="32" t="inlineStr">
-        <is>
-          <t>基准采集作业与存储</t>
+          <t>F02-01-1</t>
+        </is>
+      </c>
+      <c r="B23" s="96" t="inlineStr">
+        <is>
+          <t>统一元数据模型</t>
         </is>
       </c>
       <c r="C23" s="32" t="inlineStr">
         <is>
-          <t>源端基准快照生成、基准库表</t>
-        </is>
-      </c>
-      <c r="D23" s="46" t="n"/>
-      <c r="E23" s="46" t="n"/>
-      <c r="F23" s="46" t="n">
+          <t>元数据字段体系定义</t>
+        </is>
+      </c>
+      <c r="D23" s="32" t="inlineStr">
+        <is>
+          <t>字段/类型/必填/密级/保留等级字典</t>
+        </is>
+      </c>
+      <c r="E23" s="46" t="n">
         <v>1.5</v>
       </c>
+      <c r="F23" s="46" t="n"/>
       <c r="G23" s="46" t="n">
         <v>0.5</v>
       </c>
@@ -16528,94 +16636,110 @@
         <v>0.25</v>
       </c>
       <c r="I23" s="46" t="n">
-        <v>2.25</v>
+        <v>0.5</v>
+      </c>
+      <c r="J23" s="46" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="K23" s="77" t="n">
+        <v>8.5</v>
       </c>
     </row>
     <row r="24" ht="26" customHeight="1">
       <c r="A24" s="15" t="inlineStr">
         <is>
-          <t>F01-04-3</t>
-        </is>
-      </c>
-      <c r="B24" s="32" t="inlineStr">
-        <is>
-          <t>基准报告查询展示</t>
-        </is>
-      </c>
+          <t>F02-01-2</t>
+        </is>
+      </c>
+      <c r="B24" s="17" t="n"/>
       <c r="C24" s="32" t="inlineStr">
         <is>
-          <t>基准结果展示与导出</t>
-        </is>
-      </c>
-      <c r="D24" s="46" t="n"/>
-      <c r="E24" s="46" t="n">
+          <t>元数据核心表与API</t>
+        </is>
+      </c>
+      <c r="D24" s="32" t="inlineStr">
+        <is>
+          <t>核心元数据表实现、CRUD API、Migration</t>
+        </is>
+      </c>
+      <c r="E24" s="46" t="n"/>
+      <c r="F24" s="46" t="n"/>
+      <c r="G24" s="46" t="n">
+        <v>2</v>
+      </c>
+      <c r="H24" s="46" t="n">
         <v>0.5</v>
       </c>
-      <c r="F24" s="46" t="n">
+      <c r="I24" s="46" t="n">
         <v>0.25</v>
       </c>
-      <c r="G24" s="46" t="n">
+      <c r="J24" s="46" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="K24" s="17" t="n"/>
+    </row>
+    <row r="25" ht="26" customHeight="1">
+      <c r="A25" s="15" t="inlineStr">
+        <is>
+          <t>F02-01-3</t>
+        </is>
+      </c>
+      <c r="B25" s="17" t="n"/>
+      <c r="C25" s="32" t="inlineStr">
+        <is>
+          <t>元数据驱动配置机制</t>
+        </is>
+      </c>
+      <c r="D25" s="32" t="inlineStr">
+        <is>
+          <t>查询配置模型、动态表单渲染协议</t>
+        </is>
+      </c>
+      <c r="E25" s="46" t="n">
         <v>0.25</v>
       </c>
-      <c r="H24" s="46" t="n">
+      <c r="F25" s="46" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G25" s="46" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H25" s="46" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I25" s="46" t="n">
         <v>0.25</v>
       </c>
-      <c r="I24" s="46" t="n">
-        <v>1.25</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="72" t="inlineStr">
-        <is>
-          <t>F01-05</t>
-        </is>
-      </c>
-      <c r="B25" s="73" t="inlineStr">
-        <is>
-          <t>迁移后完整性比对（模块1·存量历史数据迁移与标准化）· 共2个子任务</t>
-        </is>
-      </c>
-      <c r="C25" s="72" t="n"/>
-      <c r="D25" s="74" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="E25" s="74" t="n">
-        <v>1</v>
-      </c>
-      <c r="F25" s="74" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="G25" s="74" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="H25" s="74" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="I25" s="74" t="n">
-        <v>5.5</v>
-      </c>
+      <c r="J25" s="46" t="n">
+        <v>3</v>
+      </c>
+      <c r="K25" s="17" t="n"/>
     </row>
     <row r="26" ht="26" customHeight="1">
       <c r="A26" s="15" t="inlineStr">
         <is>
-          <t>F01-05-1</t>
-        </is>
-      </c>
-      <c r="B26" s="32" t="inlineStr">
-        <is>
-          <t>比对引擎</t>
+          <t>F02-02-1</t>
+        </is>
+      </c>
+      <c r="B26" s="96" t="inlineStr">
+        <is>
+          <t>来源系统信息绑定</t>
         </is>
       </c>
       <c r="C26" s="32" t="inlineStr">
         <is>
-          <t>RAW/CURATED逐层行数与校验和比对、抽样SHA-256</t>
-        </is>
-      </c>
-      <c r="D26" s="46" t="n"/>
-      <c r="E26" s="46" t="n"/>
-      <c r="F26" s="46" t="n">
-        <v>2</v>
-      </c>
+          <t>绑定规则与批次属性</t>
+        </is>
+      </c>
+      <c r="D26" s="32" t="inlineStr">
+        <is>
+          <t>源编码引用、退役项目/迁移批次属性规则</t>
+        </is>
+      </c>
+      <c r="E26" s="46" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F26" s="46" t="n"/>
       <c r="G26" s="46" t="n">
         <v>0.75</v>
       </c>
@@ -16623,421 +16747,473 @@
         <v>0.25</v>
       </c>
       <c r="I26" s="46" t="n">
-        <v>3</v>
+        <v>0.25</v>
+      </c>
+      <c r="J26" s="46" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="K26" s="77" t="n">
+        <v>5.75</v>
       </c>
     </row>
     <row r="27" ht="26" customHeight="1">
       <c r="A27" s="15" t="inlineStr">
         <is>
-          <t>F01-05-2</t>
-        </is>
-      </c>
-      <c r="B27" s="32" t="inlineStr">
-        <is>
-          <t>差异报告与处理流程</t>
-        </is>
-      </c>
+          <t>F02-02-2</t>
+        </is>
+      </c>
+      <c r="B27" s="17" t="n"/>
       <c r="C27" s="32" t="inlineStr">
         <is>
-          <t>差异清单、重迁/豁免记录</t>
-        </is>
-      </c>
-      <c r="D27" s="46" t="n">
+          <t>接入时自动绑定</t>
+        </is>
+      </c>
+      <c r="D27" s="32" t="inlineStr">
+        <is>
+          <t>导入/上传时来源属性自动写入与校验</t>
+        </is>
+      </c>
+      <c r="E27" s="46" t="n"/>
+      <c r="F27" s="46" t="n"/>
+      <c r="G27" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="H27" s="46" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I27" s="46" t="n">
         <v>0.25</v>
       </c>
-      <c r="E27" s="46" t="n">
+      <c r="J27" s="46" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="K27" s="17" t="n"/>
+    </row>
+    <row r="28" ht="26" customHeight="1">
+      <c r="A28" s="15" t="inlineStr">
+        <is>
+          <t>F02-02-3</t>
+        </is>
+      </c>
+      <c r="B28" s="17" t="n"/>
+      <c r="C28" s="32" t="inlineStr">
+        <is>
+          <t>按来源检索与统计</t>
+        </is>
+      </c>
+      <c r="D28" s="32" t="inlineStr">
+        <is>
+          <t>来源维度筛选、统计报表</t>
+        </is>
+      </c>
+      <c r="E28" s="46" t="n"/>
+      <c r="F28" s="46" t="n">
         <v>1</v>
       </c>
-      <c r="F27" s="46" t="n">
+      <c r="G28" s="46" t="n">
         <v>0.5</v>
       </c>
-      <c r="G27" s="46" t="n">
+      <c r="H28" s="46" t="n">
         <v>0.5</v>
       </c>
-      <c r="H27" s="46" t="n">
+      <c r="I28" s="46" t="n">
         <v>0.25</v>
       </c>
-      <c r="I27" s="46" t="n">
-        <v>2.5</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="75" t="inlineStr">
-        <is>
-          <t>F02-01</t>
-        </is>
-      </c>
-      <c r="B28" s="76" t="inlineStr">
-        <is>
-          <t>统一元数据模型（模块2·实时数据接入与常态化数据治理）· 共3个子任务</t>
-        </is>
-      </c>
-      <c r="C28" s="75" t="n"/>
-      <c r="D28" s="77" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="E28" s="77" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="F28" s="77" t="n">
-        <v>3</v>
-      </c>
-      <c r="G28" s="77" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="H28" s="77" t="n">
-        <v>1</v>
-      </c>
-      <c r="I28" s="77" t="n">
-        <v>8.5</v>
-      </c>
+      <c r="J28" s="46" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="K28" s="17" t="n"/>
     </row>
     <row r="29" ht="26" customHeight="1">
       <c r="A29" s="15" t="inlineStr">
         <is>
-          <t>F02-01-1</t>
-        </is>
-      </c>
-      <c r="B29" s="32" t="inlineStr">
-        <is>
-          <t>元数据字段体系定义</t>
+          <t>F03-01-1</t>
+        </is>
+      </c>
+      <c r="B29" s="97" t="inlineStr">
+        <is>
+          <t>保留期限到期自动删除</t>
         </is>
       </c>
       <c r="C29" s="32" t="inlineStr">
         <is>
-          <t>字段/类型/必填/密级/保留等级字典</t>
-        </is>
-      </c>
-      <c r="D29" s="46" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="E29" s="46" t="n"/>
+          <t>保留策略配置</t>
+        </is>
+      </c>
+      <c r="D29" s="32" t="inlineStr">
+        <is>
+          <t>策略规则、继承关系、生效范围</t>
+        </is>
+      </c>
+      <c r="E29" s="46" t="n">
+        <v>0.75</v>
+      </c>
       <c r="F29" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="G29" s="46" t="n">
         <v>0.5</v>
-      </c>
-      <c r="G29" s="46" t="n">
-        <v>0.25</v>
       </c>
       <c r="H29" s="46" t="n">
         <v>0.5</v>
       </c>
       <c r="I29" s="46" t="n">
-        <v>2.75</v>
+        <v>0.25</v>
+      </c>
+      <c r="J29" s="46" t="n">
+        <v>3</v>
+      </c>
+      <c r="K29" s="80" t="n">
+        <v>9.5</v>
       </c>
     </row>
     <row r="30" ht="26" customHeight="1">
       <c r="A30" s="15" t="inlineStr">
         <is>
-          <t>F02-01-2</t>
-        </is>
-      </c>
-      <c r="B30" s="32" t="inlineStr">
-        <is>
-          <t>元数据核心表与API</t>
-        </is>
-      </c>
+          <t>F03-01-2</t>
+        </is>
+      </c>
+      <c r="B30" s="17" t="n"/>
       <c r="C30" s="32" t="inlineStr">
         <is>
-          <t>核心元数据表实现、CRUD API、Migration</t>
-        </is>
-      </c>
-      <c r="D30" s="46" t="n"/>
+          <t>处置引擎</t>
+        </is>
+      </c>
+      <c r="D30" s="32" t="inlineStr">
+        <is>
+          <t>到期扫描、豁免检查、DROP PARTITION、VACUUM物理清除</t>
+        </is>
+      </c>
       <c r="E30" s="46" t="n"/>
-      <c r="F30" s="46" t="n">
-        <v>2</v>
-      </c>
+      <c r="F30" s="46" t="n"/>
       <c r="G30" s="46" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H30" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="I30" s="46" t="n">
         <v>0.5</v>
       </c>
-      <c r="H30" s="46" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="I30" s="46" t="n">
-        <v>2.75</v>
-      </c>
+      <c r="J30" s="46" t="n">
+        <v>4</v>
+      </c>
+      <c r="K30" s="17" t="n"/>
     </row>
     <row r="31" ht="26" customHeight="1">
       <c r="A31" s="15" t="inlineStr">
         <is>
-          <t>F02-01-3</t>
-        </is>
-      </c>
-      <c r="B31" s="32" t="inlineStr">
-        <is>
-          <t>元数据驱动配置机制</t>
-        </is>
-      </c>
+          <t>F03-01-3</t>
+        </is>
+      </c>
+      <c r="B31" s="17" t="n"/>
       <c r="C31" s="32" t="inlineStr">
         <is>
-          <t>查询配置模型、动态表单渲染协议</t>
-        </is>
-      </c>
-      <c r="D31" s="46" t="n">
+          <t>处置计划审批与台账</t>
+        </is>
+      </c>
+      <c r="D31" s="32" t="inlineStr">
+        <is>
+          <t>预演清单、审批流、处置留痕台账</t>
+        </is>
+      </c>
+      <c r="E31" s="46" t="n">
         <v>0.25</v>
       </c>
-      <c r="E31" s="46" t="n">
-        <v>1.5</v>
-      </c>
       <c r="F31" s="46" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="G31" s="46" t="n">
         <v>0.5</v>
       </c>
       <c r="H31" s="46" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I31" s="46" t="n">
         <v>0.25</v>
       </c>
-      <c r="I31" s="46" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="75" t="inlineStr">
-        <is>
-          <t>F02-02</t>
-        </is>
-      </c>
-      <c r="B32" s="76" t="inlineStr">
-        <is>
-          <t>来源系统信息绑定（模块2·实时数据接入与常态化数据治理）· 共3个子任务</t>
-        </is>
-      </c>
-      <c r="C32" s="75" t="n"/>
-      <c r="D32" s="77" t="n">
+      <c r="J31" s="46" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="K31" s="17" t="n"/>
+    </row>
+    <row r="32" ht="26" customHeight="1">
+      <c r="A32" s="15" t="inlineStr">
+        <is>
+          <t>F03-02-1</t>
+        </is>
+      </c>
+      <c r="B32" s="97" t="inlineStr">
+        <is>
+          <t>Legal Hold 冻结</t>
+        </is>
+      </c>
+      <c r="C32" s="32" t="inlineStr">
+        <is>
+          <t>Hold申请与审批流程</t>
+        </is>
+      </c>
+      <c r="D32" s="32" t="inlineStr">
+        <is>
+          <t>涉诉/审计/调查场景、审批链定义</t>
+        </is>
+      </c>
+      <c r="E32" s="46" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="F32" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="G32" s="46" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="H32" s="46" t="n">
         <v>0.5</v>
       </c>
-      <c r="E32" s="77" t="n">
-        <v>1</v>
-      </c>
-      <c r="F32" s="77" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="G32" s="77" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="H32" s="77" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="I32" s="77" t="n">
-        <v>5.75</v>
+      <c r="I32" s="46" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="J32" s="46" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="K32" s="80" t="n">
+        <v>6.5</v>
       </c>
     </row>
     <row r="33" ht="26" customHeight="1">
       <c r="A33" s="15" t="inlineStr">
         <is>
-          <t>F02-02-1</t>
-        </is>
-      </c>
-      <c r="B33" s="32" t="inlineStr">
-        <is>
-          <t>绑定规则与批次属性</t>
-        </is>
-      </c>
+          <t>F03-02-2</t>
+        </is>
+      </c>
+      <c r="B33" s="17" t="n"/>
       <c r="C33" s="32" t="inlineStr">
         <is>
-          <t>源编码引用、退役项目/迁移批次属性规则</t>
-        </is>
-      </c>
-      <c r="D33" s="46" t="n">
-        <v>0.5</v>
+          <t>Hold生效与解除实现</t>
+        </is>
+      </c>
+      <c r="D33" s="32" t="inlineStr">
+        <is>
+          <t>记录级/表级冻结、处置豁免、操作留痕</t>
+        </is>
       </c>
       <c r="E33" s="46" t="n"/>
-      <c r="F33" s="46" t="n">
+      <c r="F33" s="46" t="n"/>
+      <c r="G33" s="46" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H33" s="46" t="n">
         <v>0.75</v>
       </c>
-      <c r="G33" s="46" t="n">
+      <c r="I33" s="46" t="n">
         <v>0.25</v>
       </c>
-      <c r="H33" s="46" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="I33" s="46" t="n">
-        <v>1.75</v>
-      </c>
+      <c r="J33" s="46" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="K33" s="17" t="n"/>
     </row>
     <row r="34" ht="26" customHeight="1">
       <c r="A34" s="15" t="inlineStr">
         <is>
-          <t>F02-02-2</t>
-        </is>
-      </c>
-      <c r="B34" s="32" t="inlineStr">
-        <is>
-          <t>接入时自动绑定</t>
-        </is>
-      </c>
+          <t>F03-02-3</t>
+        </is>
+      </c>
+      <c r="B34" s="17" t="n"/>
       <c r="C34" s="32" t="inlineStr">
         <is>
-          <t>导入/上传时来源属性自动写入与校验</t>
-        </is>
-      </c>
-      <c r="D34" s="46" t="n"/>
+          <t>Hold清单管理与提醒</t>
+        </is>
+      </c>
+      <c r="D34" s="32" t="inlineStr">
+        <is>
+          <t>在Hold清单、解除预警</t>
+        </is>
+      </c>
       <c r="E34" s="46" t="n"/>
       <c r="F34" s="46" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="G34" s="46" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="H34" s="46" t="n">
         <v>0.25</v>
       </c>
       <c r="I34" s="46" t="n">
-        <v>1.75</v>
-      </c>
+        <v>0.25</v>
+      </c>
+      <c r="J34" s="46" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="K34" s="17" t="n"/>
     </row>
     <row r="35" ht="26" customHeight="1">
       <c r="A35" s="15" t="inlineStr">
         <is>
-          <t>F02-02-3</t>
-        </is>
-      </c>
-      <c r="B35" s="32" t="inlineStr">
-        <is>
-          <t>按来源检索与统计</t>
+          <t>F04-01-1</t>
+        </is>
+      </c>
+      <c r="B35" s="98" t="inlineStr">
+        <is>
+          <t>数据加密存储</t>
         </is>
       </c>
       <c r="C35" s="32" t="inlineStr">
         <is>
-          <t>来源维度筛选、统计报表</t>
-        </is>
-      </c>
-      <c r="D35" s="46" t="n"/>
+          <t>加密策略定义</t>
+        </is>
+      </c>
+      <c r="D35" s="32" t="inlineStr">
+        <is>
+          <t>SSE+CMK方案、PII字段清单与字段级加密规则</t>
+        </is>
+      </c>
       <c r="E35" s="46" t="n">
-        <v>1</v>
-      </c>
-      <c r="F35" s="46" t="n">
         <v>0.5</v>
       </c>
+      <c r="F35" s="46" t="n"/>
       <c r="G35" s="46" t="n">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="H35" s="46" t="n">
         <v>0.25</v>
       </c>
       <c r="I35" s="46" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="J35" s="46" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="K35" s="83" t="n">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="36" ht="26" customHeight="1">
+      <c r="A36" s="15" t="inlineStr">
+        <is>
+          <t>F04-01-2</t>
+        </is>
+      </c>
+      <c r="B36" s="17" t="n"/>
+      <c r="C36" s="32" t="inlineStr">
+        <is>
+          <t>存储层加密落地</t>
+        </is>
+      </c>
+      <c r="D36" s="32" t="inlineStr">
+        <is>
+          <t>ADLS SSE、Key Vault CMK集成、密钥轮换</t>
+        </is>
+      </c>
+      <c r="E36" s="46" t="n"/>
+      <c r="F36" s="46" t="n"/>
+      <c r="G36" s="46" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H36" s="46" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I36" s="46" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="J36" s="46" t="n">
         <v>2.25</v>
       </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="78" t="inlineStr">
-        <is>
-          <t>F03-01</t>
-        </is>
-      </c>
-      <c r="B36" s="79" t="inlineStr">
-        <is>
-          <t>保留期限到期自动删除（模块3·记录归档与档案全生命周期管理）· 共3个子任务</t>
-        </is>
-      </c>
-      <c r="C36" s="78" t="n"/>
-      <c r="D36" s="80" t="n">
-        <v>1</v>
-      </c>
-      <c r="E36" s="80" t="n">
-        <v>2</v>
-      </c>
-      <c r="F36" s="80" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="G36" s="80" t="n">
-        <v>2</v>
-      </c>
-      <c r="H36" s="80" t="n">
-        <v>1</v>
-      </c>
-      <c r="I36" s="80" t="n">
-        <v>9.5</v>
-      </c>
+      <c r="K36" s="17" t="n"/>
     </row>
     <row r="37" ht="26" customHeight="1">
       <c r="A37" s="15" t="inlineStr">
         <is>
-          <t>F03-01-1</t>
-        </is>
-      </c>
-      <c r="B37" s="32" t="inlineStr">
-        <is>
-          <t>保留策略配置</t>
-        </is>
-      </c>
+          <t>F04-01-3</t>
+        </is>
+      </c>
+      <c r="B37" s="17" t="n"/>
       <c r="C37" s="32" t="inlineStr">
         <is>
-          <t>策略规则、继承关系、生效范围</t>
-        </is>
-      </c>
-      <c r="D37" s="46" t="n">
+          <t>PII字段级加密服务</t>
+        </is>
+      </c>
+      <c r="D37" s="32" t="inlineStr">
+        <is>
+          <t>应用层加解密、密文索引策略、传输加密验证</t>
+        </is>
+      </c>
+      <c r="E37" s="46" t="n"/>
+      <c r="F37" s="46" t="n"/>
+      <c r="G37" s="46" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H37" s="46" t="n">
         <v>0.75</v>
       </c>
-      <c r="E37" s="46" t="n">
-        <v>1</v>
-      </c>
-      <c r="F37" s="46" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G37" s="46" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="H37" s="46" t="n">
+      <c r="I37" s="46" t="n">
         <v>0.25</v>
       </c>
-      <c r="I37" s="46" t="n">
-        <v>3</v>
-      </c>
+      <c r="J37" s="46" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="K37" s="17" t="n"/>
     </row>
     <row r="38" ht="26" customHeight="1">
       <c r="A38" s="15" t="inlineStr">
         <is>
-          <t>F03-01-2</t>
-        </is>
-      </c>
-      <c r="B38" s="32" t="inlineStr">
-        <is>
-          <t>处置引擎</t>
+          <t>F04-02-1</t>
+        </is>
+      </c>
+      <c r="B38" s="98" t="inlineStr">
+        <is>
+          <t>密钥管理</t>
         </is>
       </c>
       <c r="C38" s="32" t="inlineStr">
         <is>
-          <t>到期扫描、豁免检查、DROP PARTITION、VACUUM物理清除</t>
-        </is>
-      </c>
-      <c r="D38" s="46" t="n"/>
-      <c r="E38" s="46" t="n"/>
-      <c r="F38" s="46" t="n">
-        <v>2.5</v>
-      </c>
+          <t>密钥全流程管理</t>
+        </is>
+      </c>
+      <c r="D38" s="32" t="inlineStr">
+        <is>
+          <t>创建/保管/更新/吊销/权限控制</t>
+        </is>
+      </c>
+      <c r="E38" s="46" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="F38" s="46" t="n"/>
       <c r="G38" s="46" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="H38" s="46" t="n">
         <v>0.5</v>
       </c>
       <c r="I38" s="46" t="n">
-        <v>4</v>
+        <v>0.25</v>
+      </c>
+      <c r="J38" s="46" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="K38" s="83" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="39" ht="26" customHeight="1">
       <c r="A39" s="15" t="inlineStr">
         <is>
-          <t>F03-01-3</t>
-        </is>
-      </c>
-      <c r="B39" s="32" t="inlineStr">
-        <is>
-          <t>处置计划审批与台账</t>
-        </is>
-      </c>
+          <t>F04-02-2</t>
+        </is>
+      </c>
+      <c r="B39" s="17" t="n"/>
       <c r="C39" s="32" t="inlineStr">
         <is>
-          <t>预演清单、审批流、处置留痕台账</t>
-        </is>
-      </c>
-      <c r="D39" s="46" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="E39" s="46" t="n">
-        <v>1</v>
-      </c>
+          <t>密钥操作审计与告警</t>
+        </is>
+      </c>
+      <c r="D39" s="32" t="inlineStr">
+        <is>
+          <t>操作日志、异常使用告警</t>
+        </is>
+      </c>
+      <c r="E39" s="46" t="n"/>
       <c r="F39" s="46" t="n">
         <v>0.5</v>
       </c>
@@ -17045,67 +17221,77 @@
         <v>0.5</v>
       </c>
       <c r="H39" s="46" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I39" s="46" t="n">
         <v>0.25</v>
       </c>
-      <c r="I39" s="46" t="n">
-        <v>2.5</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="78" t="inlineStr">
-        <is>
-          <t>F03-02</t>
-        </is>
-      </c>
-      <c r="B40" s="79" t="inlineStr">
-        <is>
-          <t>Legal Hold 冻结（模块3·记录归档与档案全生命周期管理）· 共3个子任务</t>
-        </is>
-      </c>
-      <c r="C40" s="78" t="n"/>
-      <c r="D40" s="80" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="E40" s="80" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="F40" s="80" t="n">
-        <v>2</v>
-      </c>
-      <c r="G40" s="80" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="H40" s="80" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="I40" s="80" t="n">
-        <v>6.5</v>
-      </c>
+      <c r="J39" s="46" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="K39" s="17" t="n"/>
+    </row>
+    <row r="40" ht="26" customHeight="1">
+      <c r="A40" s="15" t="inlineStr">
+        <is>
+          <t>F04-02-3</t>
+        </is>
+      </c>
+      <c r="B40" s="17" t="n"/>
+      <c r="C40" s="32" t="inlineStr">
+        <is>
+          <t>密钥管理界面</t>
+        </is>
+      </c>
+      <c r="D40" s="32" t="inlineStr">
+        <is>
+          <t>密钥清单、版本、权限分配界面</t>
+        </is>
+      </c>
+      <c r="E40" s="46" t="n"/>
+      <c r="F40" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="G40" s="46" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="H40" s="46" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="I40" s="46" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="J40" s="46" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="K40" s="17" t="n"/>
     </row>
     <row r="41" ht="26" customHeight="1">
       <c r="A41" s="15" t="inlineStr">
         <is>
-          <t>F03-02-1</t>
-        </is>
-      </c>
-      <c r="B41" s="32" t="inlineStr">
-        <is>
-          <t>Hold申请与审批流程</t>
+          <t>F04-03-1</t>
+        </is>
+      </c>
+      <c r="B41" s="98" t="inlineStr">
+        <is>
+          <t>数据备份管理</t>
         </is>
       </c>
       <c r="C41" s="32" t="inlineStr">
         <is>
-          <t>涉诉/审计/调查场景、审批链定义</t>
-        </is>
-      </c>
-      <c r="D41" s="46" t="n">
+          <t>备份策略配置</t>
+        </is>
+      </c>
+      <c r="D41" s="32" t="inlineStr">
+        <is>
+          <t>备份周期/范围/保留期策略</t>
+        </is>
+      </c>
+      <c r="E41" s="46" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F41" s="46" t="n">
         <v>0.75</v>
-      </c>
-      <c r="E41" s="46" t="n">
-        <v>1</v>
-      </c>
-      <c r="F41" s="46" t="n">
-        <v>0.25</v>
       </c>
       <c r="G41" s="46" t="n">
         <v>0.5</v>
@@ -17114,638 +17300,718 @@
         <v>0.25</v>
       </c>
       <c r="I41" s="46" t="n">
-        <v>2.75</v>
+        <v>0.25</v>
+      </c>
+      <c r="J41" s="46" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="K41" s="83" t="n">
+        <v>6.25</v>
       </c>
     </row>
     <row r="42" ht="26" customHeight="1">
       <c r="A42" s="15" t="inlineStr">
         <is>
-          <t>F03-02-2</t>
-        </is>
-      </c>
-      <c r="B42" s="32" t="inlineStr">
-        <is>
-          <t>Hold生效与解除实现</t>
-        </is>
-      </c>
+          <t>F04-03-2</t>
+        </is>
+      </c>
+      <c r="B42" s="17" t="n"/>
       <c r="C42" s="32" t="inlineStr">
         <is>
-          <t>记录级/表级冻结、处置豁免、操作留痕</t>
-        </is>
-      </c>
-      <c r="D42" s="46" t="n"/>
+          <t>备份作业与副本创建</t>
+        </is>
+      </c>
+      <c r="D42" s="32" t="inlineStr">
+        <is>
+          <t>元数据库PITR、湖快照、附件副本</t>
+        </is>
+      </c>
       <c r="E42" s="46" t="n"/>
-      <c r="F42" s="46" t="n">
+      <c r="F42" s="46" t="n"/>
+      <c r="G42" s="46" t="n">
         <v>1.5</v>
       </c>
-      <c r="G42" s="46" t="n">
-        <v>0.75</v>
-      </c>
       <c r="H42" s="46" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I42" s="46" t="n">
         <v>0.25</v>
       </c>
-      <c r="I42" s="46" t="n">
-        <v>2.5</v>
-      </c>
+      <c r="J42" s="46" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="K42" s="17" t="n"/>
     </row>
     <row r="43" ht="26" customHeight="1">
       <c r="A43" s="15" t="inlineStr">
         <is>
-          <t>F03-02-3</t>
-        </is>
-      </c>
-      <c r="B43" s="32" t="inlineStr">
-        <is>
-          <t>Hold清单管理与提醒</t>
-        </is>
-      </c>
+          <t>F04-03-3</t>
+        </is>
+      </c>
+      <c r="B43" s="17" t="n"/>
       <c r="C43" s="32" t="inlineStr">
         <is>
-          <t>在Hold清单、解除预警</t>
-        </is>
-      </c>
-      <c r="D43" s="46" t="n"/>
-      <c r="E43" s="46" t="n">
+          <t>备份监控与恢复操作</t>
+        </is>
+      </c>
+      <c r="D43" s="32" t="inlineStr">
+        <is>
+          <t>备份状态监控、恢复流程</t>
+        </is>
+      </c>
+      <c r="E43" s="46" t="n"/>
+      <c r="F43" s="46" t="n">
         <v>0.5</v>
       </c>
-      <c r="F43" s="46" t="n">
+      <c r="G43" s="46" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H43" s="46" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I43" s="46" t="n">
         <v>0.25</v>
       </c>
-      <c r="G43" s="46" t="n">
+      <c r="J43" s="46" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="K43" s="17" t="n"/>
+    </row>
+    <row r="44" ht="26" customHeight="1">
+      <c r="A44" s="15" t="inlineStr">
+        <is>
+          <t>F04-04-1</t>
+        </is>
+      </c>
+      <c r="B44" s="98" t="inlineStr">
+        <is>
+          <t>异地灾备</t>
+        </is>
+      </c>
+      <c r="C44" s="32" t="inlineStr">
+        <is>
+          <t>灾备方案与RTO/RPO定义</t>
+        </is>
+      </c>
+      <c r="D44" s="32" t="inlineStr">
+        <is>
+          <t>灾备架构、恢复目标定义</t>
+        </is>
+      </c>
+      <c r="E44" s="46" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F44" s="46" t="n"/>
+      <c r="G44" s="46" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H44" s="46" t="n">
         <v>0.25</v>
       </c>
-      <c r="H43" s="46" t="n">
+      <c r="I44" s="46" t="n">
         <v>0.25</v>
       </c>
-      <c r="I43" s="46" t="n">
-        <v>1.25</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="81" t="inlineStr">
-        <is>
-          <t>F04-01</t>
-        </is>
-      </c>
-      <c r="B44" s="82" t="inlineStr">
-        <is>
-          <t>数据加密存储（模块4·数据存储与境内数据安全管控）· 共3个子任务</t>
-        </is>
-      </c>
-      <c r="C44" s="81" t="n"/>
-      <c r="D44" s="83" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="E44" s="83" t="n">
-        <v>0</v>
-      </c>
-      <c r="F44" s="83" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="G44" s="83" t="n">
+      <c r="J44" s="46" t="n">
         <v>1.5</v>
       </c>
-      <c r="H44" s="83" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="I44" s="83" t="n">
-        <v>6.5</v>
+      <c r="K44" s="83" t="n">
+        <v>5.75</v>
       </c>
     </row>
     <row r="45" ht="26" customHeight="1">
       <c r="A45" s="15" t="inlineStr">
         <is>
-          <t>F04-01-1</t>
-        </is>
-      </c>
-      <c r="B45" s="32" t="inlineStr">
-        <is>
-          <t>加密策略定义</t>
-        </is>
-      </c>
+          <t>F04-04-2</t>
+        </is>
+      </c>
+      <c r="B45" s="17" t="n"/>
       <c r="C45" s="32" t="inlineStr">
         <is>
-          <t>SSE+CMK方案、PII字段清单与字段级加密规则</t>
-        </is>
-      </c>
-      <c r="D45" s="46" t="n">
+          <t>异地副本同步</t>
+        </is>
+      </c>
+      <c r="D45" s="32" t="inlineStr">
+        <is>
+          <t>存储异地冗余/复制配置</t>
+        </is>
+      </c>
+      <c r="E45" s="46" t="n"/>
+      <c r="F45" s="46" t="n"/>
+      <c r="G45" s="46" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H45" s="46" t="n">
         <v>0.5</v>
       </c>
-      <c r="E45" s="46" t="n"/>
-      <c r="F45" s="46" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="G45" s="46" t="n">
+      <c r="I45" s="46" t="n">
         <v>0.25</v>
       </c>
-      <c r="H45" s="46" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="I45" s="46" t="n">
-        <v>1.75</v>
-      </c>
+      <c r="J45" s="46" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="K45" s="17" t="n"/>
     </row>
     <row r="46" ht="26" customHeight="1">
       <c r="A46" s="15" t="inlineStr">
         <is>
-          <t>F04-01-2</t>
-        </is>
-      </c>
-      <c r="B46" s="32" t="inlineStr">
-        <is>
-          <t>存储层加密落地</t>
-        </is>
-      </c>
+          <t>F04-04-3</t>
+        </is>
+      </c>
+      <c r="B46" s="17" t="n"/>
       <c r="C46" s="32" t="inlineStr">
         <is>
-          <t>ADLS SSE、Key Vault CMK集成、密钥轮换</t>
-        </is>
-      </c>
-      <c r="D46" s="46" t="n"/>
+          <t>恢复切换演练</t>
+        </is>
+      </c>
+      <c r="D46" s="32" t="inlineStr">
+        <is>
+          <t>演练脚本、切换/回切流程与报告</t>
+        </is>
+      </c>
       <c r="E46" s="46" t="n"/>
-      <c r="F46" s="46" t="n">
-        <v>1.5</v>
-      </c>
+      <c r="F46" s="46" t="n"/>
       <c r="G46" s="46" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="H46" s="46" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="I46" s="46" t="n">
         <v>0.25</v>
       </c>
-      <c r="I46" s="46" t="n">
-        <v>2.25</v>
-      </c>
+      <c r="J46" s="46" t="n">
+        <v>2</v>
+      </c>
+      <c r="K46" s="17" t="n"/>
     </row>
     <row r="47" ht="26" customHeight="1">
       <c r="A47" s="15" t="inlineStr">
         <is>
-          <t>F04-01-3</t>
-        </is>
-      </c>
-      <c r="B47" s="32" t="inlineStr">
-        <is>
-          <t>PII字段级加密服务</t>
+          <t>F05-01-1</t>
+        </is>
+      </c>
+      <c r="B47" s="99" t="inlineStr">
+        <is>
+          <t>关键词检索</t>
         </is>
       </c>
       <c r="C47" s="32" t="inlineStr">
         <is>
-          <t>应用层加解密、密文索引策略、传输加密验证</t>
-        </is>
-      </c>
-      <c r="D47" s="46" t="n"/>
-      <c r="E47" s="46" t="n"/>
+          <t>检索配置模型</t>
+        </is>
+      </c>
+      <c r="D47" s="32" t="inlineStr">
+        <is>
+          <t>可检索字段、分词策略、OCR文本索引策略</t>
+        </is>
+      </c>
+      <c r="E47" s="46" t="n">
+        <v>0.5</v>
+      </c>
       <c r="F47" s="46" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="G47" s="46" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="H47" s="46" t="n">
         <v>0.25</v>
       </c>
       <c r="I47" s="46" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="J47" s="46" t="n">
         <v>2.5</v>
       </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="81" t="inlineStr">
-        <is>
-          <t>F04-02</t>
-        </is>
-      </c>
-      <c r="B48" s="82" t="inlineStr">
-        <is>
-          <t>密钥管理（模块4·数据存储与境内数据安全管控）· 共3个子任务</t>
-        </is>
-      </c>
-      <c r="C48" s="81" t="n"/>
-      <c r="D48" s="83" t="n">
+      <c r="K47" s="86" t="n">
+        <v>7.25</v>
+      </c>
+    </row>
+    <row r="48" ht="26" customHeight="1">
+      <c r="A48" s="15" t="inlineStr">
+        <is>
+          <t>F05-01-2</t>
+        </is>
+      </c>
+      <c r="B48" s="17" t="n"/>
+      <c r="C48" s="32" t="inlineStr">
+        <is>
+          <t>检索页动态表单</t>
+        </is>
+      </c>
+      <c r="D48" s="32" t="inlineStr">
+        <is>
+          <t>元数据驱动渲染、关键词与组合查询</t>
+        </is>
+      </c>
+      <c r="E48" s="46" t="n"/>
+      <c r="F48" s="46" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G48" s="46" t="n">
         <v>0.25</v>
       </c>
-      <c r="E48" s="83" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="F48" s="83" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="G48" s="83" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="H48" s="83" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="I48" s="83" t="n">
-        <v>6</v>
-      </c>
+      <c r="H48" s="46" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I48" s="46" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="J48" s="46" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="K48" s="17" t="n"/>
     </row>
     <row r="49" ht="26" customHeight="1">
       <c r="A49" s="15" t="inlineStr">
         <is>
-          <t>F04-02-1</t>
-        </is>
-      </c>
-      <c r="B49" s="32" t="inlineStr">
-        <is>
-          <t>密钥全流程管理</t>
-        </is>
-      </c>
+          <t>F05-01-3</t>
+        </is>
+      </c>
+      <c r="B49" s="17" t="n"/>
       <c r="C49" s="32" t="inlineStr">
         <is>
-          <t>创建/保管/更新/吊销/权限控制</t>
-        </is>
-      </c>
-      <c r="D49" s="46" t="n">
+          <t>查询代理与SERVE层对接</t>
+        </is>
+      </c>
+      <c r="D49" s="32" t="inlineStr">
+        <is>
+          <t>查询服务、索引优化、结果高亮</t>
+        </is>
+      </c>
+      <c r="E49" s="46" t="n"/>
+      <c r="F49" s="46" t="n"/>
+      <c r="G49" s="46" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="H49" s="46" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="I49" s="46" t="n">
         <v>0.25</v>
       </c>
-      <c r="E49" s="46" t="n"/>
-      <c r="F49" s="46" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="G49" s="46" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="H49" s="46" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="I49" s="46" t="n">
-        <v>2.5</v>
-      </c>
+      <c r="J49" s="46" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="K49" s="17" t="n"/>
     </row>
     <row r="50" ht="26" customHeight="1">
       <c r="A50" s="15" t="inlineStr">
         <is>
-          <t>F04-02-2</t>
-        </is>
-      </c>
-      <c r="B50" s="32" t="inlineStr">
-        <is>
-          <t>密钥操作审计与告警</t>
+          <t>F05-02-1</t>
+        </is>
+      </c>
+      <c r="B50" s="99" t="inlineStr">
+        <is>
+          <t>按系统名称检索</t>
         </is>
       </c>
       <c r="C50" s="32" t="inlineStr">
         <is>
-          <t>操作日志、异常使用告警</t>
-        </is>
-      </c>
-      <c r="D50" s="46" t="n"/>
-      <c r="E50" s="46" t="n">
-        <v>0.5</v>
-      </c>
+          <t>来源系统筛选组件</t>
+        </is>
+      </c>
+      <c r="D50" s="32" t="inlineStr">
+        <is>
+          <t>来源系统下拉/搜索/多选</t>
+        </is>
+      </c>
+      <c r="E50" s="46" t="n"/>
       <c r="F50" s="46" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G50" s="46" t="n">
-        <v>0.5</v>
-      </c>
+        <v>0.75</v>
+      </c>
+      <c r="G50" s="46" t="n"/>
       <c r="H50" s="46" t="n">
         <v>0.25</v>
       </c>
       <c r="I50" s="46" t="n">
-        <v>1.75</v>
+        <v>0.25</v>
+      </c>
+      <c r="J50" s="46" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="K50" s="86" t="n">
+        <v>2.25</v>
       </c>
     </row>
     <row r="51" ht="26" customHeight="1">
       <c r="A51" s="15" t="inlineStr">
         <is>
-          <t>F04-02-3</t>
-        </is>
-      </c>
-      <c r="B51" s="32" t="inlineStr">
-        <is>
-          <t>密钥管理界面</t>
-        </is>
-      </c>
+          <t>F05-02-2</t>
+        </is>
+      </c>
+      <c r="B51" s="17" t="n"/>
       <c r="C51" s="32" t="inlineStr">
         <is>
-          <t>密钥清单、版本、权限分配界面</t>
-        </is>
-      </c>
-      <c r="D51" s="46" t="n"/>
-      <c r="E51" s="46" t="n">
-        <v>1</v>
-      </c>
-      <c r="F51" s="46" t="n">
-        <v>0.25</v>
-      </c>
+          <t>来源维度查询下推</t>
+        </is>
+      </c>
+      <c r="D51" s="32" t="inlineStr">
+        <is>
+          <t>sys_id过滤、分区裁剪</t>
+        </is>
+      </c>
+      <c r="E51" s="46" t="n"/>
+      <c r="F51" s="46" t="n"/>
       <c r="G51" s="46" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="H51" s="46" t="n">
         <v>0.25</v>
       </c>
       <c r="I51" s="46" t="n">
-        <v>1.75</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="81" t="inlineStr">
-        <is>
-          <t>F04-03</t>
-        </is>
-      </c>
-      <c r="B52" s="82" t="inlineStr">
-        <is>
-          <t>数据备份管理（模块4·数据存储与境内数据安全管控）· 共3个子任务</t>
-        </is>
-      </c>
-      <c r="C52" s="81" t="n"/>
-      <c r="D52" s="83" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="E52" s="83" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="J51" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="K51" s="17" t="n"/>
+    </row>
+    <row r="52" ht="26" customHeight="1">
+      <c r="A52" s="15" t="inlineStr">
+        <is>
+          <t>F05-03-1</t>
+        </is>
+      </c>
+      <c r="B52" s="99" t="inlineStr">
+        <is>
+          <t>按业务时间检索</t>
+        </is>
+      </c>
+      <c r="C52" s="32" t="inlineStr">
+        <is>
+          <t>时间维度筛选组件</t>
+        </is>
+      </c>
+      <c r="D52" s="32" t="inlineStr">
+        <is>
+          <t>创建/修改/业务发生时间范围选择</t>
+        </is>
+      </c>
+      <c r="E52" s="46" t="n"/>
+      <c r="F52" s="46" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="G52" s="46" t="n"/>
+      <c r="H52" s="46" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="I52" s="46" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="J52" s="46" t="n">
         <v>1.25</v>
       </c>
-      <c r="F52" s="83" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="G52" s="83" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="H52" s="83" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="I52" s="83" t="n">
-        <v>6.25</v>
+      <c r="K52" s="86" t="n">
+        <v>2.25</v>
       </c>
     </row>
     <row r="53" ht="26" customHeight="1">
       <c r="A53" s="15" t="inlineStr">
         <is>
-          <t>F04-03-1</t>
-        </is>
-      </c>
-      <c r="B53" s="32" t="inlineStr">
-        <is>
-          <t>备份策略配置</t>
-        </is>
-      </c>
+          <t>F05-03-2</t>
+        </is>
+      </c>
+      <c r="B53" s="17" t="n"/>
       <c r="C53" s="32" t="inlineStr">
         <is>
-          <t>备份周期/范围/保留期策略</t>
-        </is>
-      </c>
-      <c r="D53" s="46" t="n">
+          <t>时间分区下推与索引</t>
+        </is>
+      </c>
+      <c r="D53" s="32" t="inlineStr">
+        <is>
+          <t>分区裁剪、时间索引优化</t>
+        </is>
+      </c>
+      <c r="E53" s="46" t="n"/>
+      <c r="F53" s="46" t="n"/>
+      <c r="G53" s="46" t="n">
         <v>0.5</v>
-      </c>
-      <c r="E53" s="46" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="F53" s="46" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G53" s="46" t="n">
-        <v>0.25</v>
       </c>
       <c r="H53" s="46" t="n">
         <v>0.25</v>
       </c>
       <c r="I53" s="46" t="n">
-        <v>2.25</v>
-      </c>
+        <v>0.25</v>
+      </c>
+      <c r="J53" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="K53" s="17" t="n"/>
     </row>
     <row r="54" ht="26" customHeight="1">
       <c r="A54" s="15" t="inlineStr">
         <is>
-          <t>F04-03-2</t>
-        </is>
-      </c>
-      <c r="B54" s="32" t="inlineStr">
-        <is>
-          <t>备份作业与副本创建</t>
+          <t>F05-04-1</t>
+        </is>
+      </c>
+      <c r="B54" s="99" t="inlineStr">
+        <is>
+          <t>检索结果列表展示</t>
         </is>
       </c>
       <c r="C54" s="32" t="inlineStr">
         <is>
-          <t>元数据库PITR、湖快照、附件副本</t>
-        </is>
-      </c>
-      <c r="D54" s="46" t="n"/>
+          <t>列表展示与分页排序</t>
+        </is>
+      </c>
+      <c r="D54" s="32" t="inlineStr">
+        <is>
+          <t>关键字段展示、分批加载、虚拟滚动</t>
+        </is>
+      </c>
       <c r="E54" s="46" t="n"/>
       <c r="F54" s="46" t="n">
         <v>1.5</v>
       </c>
-      <c r="G54" s="46" t="n">
+      <c r="G54" s="46" t="n"/>
+      <c r="H54" s="46" t="n">
         <v>0.5</v>
       </c>
-      <c r="H54" s="46" t="n">
+      <c r="I54" s="46" t="n">
         <v>0.25</v>
       </c>
-      <c r="I54" s="46" t="n">
+      <c r="J54" s="46" t="n">
         <v>2.25</v>
+      </c>
+      <c r="K54" s="86" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="55" ht="26" customHeight="1">
       <c r="A55" s="15" t="inlineStr">
         <is>
-          <t>F04-03-3</t>
-        </is>
-      </c>
-      <c r="B55" s="32" t="inlineStr">
-        <is>
-          <t>备份监控与恢复操作</t>
-        </is>
-      </c>
+          <t>F05-04-2</t>
+        </is>
+      </c>
+      <c r="B55" s="17" t="n"/>
       <c r="C55" s="32" t="inlineStr">
         <is>
-          <t>备份状态监控、恢复流程</t>
-        </is>
-      </c>
-      <c r="D55" s="46" t="n"/>
-      <c r="E55" s="46" t="n">
+          <t>大批量结果性能</t>
+        </is>
+      </c>
+      <c r="D55" s="32" t="inlineStr">
+        <is>
+          <t>异步计数、游标分页、缓存</t>
+        </is>
+      </c>
+      <c r="E55" s="46" t="n"/>
+      <c r="F55" s="46" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="G55" s="46" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="H55" s="46" t="n">
         <v>0.5</v>
       </c>
-      <c r="F55" s="46" t="n">
+      <c r="I55" s="46" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="J55" s="46" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="K55" s="17" t="n"/>
+    </row>
+    <row r="56" ht="26" customHeight="1">
+      <c r="A56" s="15" t="inlineStr">
+        <is>
+          <t>F05-05-1</t>
+        </is>
+      </c>
+      <c r="B56" s="99" t="inlineStr">
+        <is>
+          <t>原始文件在线预览</t>
+        </is>
+      </c>
+      <c r="C56" s="32" t="inlineStr">
+        <is>
+          <t>预览服务</t>
+        </is>
+      </c>
+      <c r="D56" s="32" t="inlineStr">
+        <is>
+          <t>格式识别、图片/PDF/Office转换</t>
+        </is>
+      </c>
+      <c r="E56" s="46" t="n"/>
+      <c r="F56" s="46" t="n"/>
+      <c r="G56" s="46" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H56" s="46" t="n">
         <v>0.5</v>
       </c>
-      <c r="G55" s="46" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="H55" s="46" t="n">
+      <c r="I56" s="46" t="n">
         <v>0.25</v>
       </c>
-      <c r="I55" s="46" t="n">
-        <v>1.75</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="81" t="inlineStr">
-        <is>
-          <t>F04-04</t>
-        </is>
-      </c>
-      <c r="B56" s="82" t="inlineStr">
-        <is>
-          <t>异地灾备（模块4·数据存储与境内数据安全管控）· 共3个子任务</t>
-        </is>
-      </c>
-      <c r="C56" s="81" t="n"/>
-      <c r="D56" s="83" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="E56" s="83" t="n">
-        <v>0</v>
-      </c>
-      <c r="F56" s="83" t="n">
-        <v>3</v>
-      </c>
-      <c r="G56" s="83" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="H56" s="83" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="I56" s="83" t="n">
-        <v>5.75</v>
+      <c r="J56" s="46" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="K56" s="86" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="57" ht="26" customHeight="1">
       <c r="A57" s="15" t="inlineStr">
         <is>
-          <t>F04-04-1</t>
-        </is>
-      </c>
-      <c r="B57" s="32" t="inlineStr">
-        <is>
-          <t>灾备方案与RTO/RPO定义</t>
-        </is>
-      </c>
+          <t>F05-05-2</t>
+        </is>
+      </c>
+      <c r="B57" s="17" t="n"/>
       <c r="C57" s="32" t="inlineStr">
         <is>
-          <t>灾备架构、恢复目标定义</t>
-        </is>
-      </c>
-      <c r="D57" s="46" t="n">
-        <v>0.5</v>
+          <t>SAS直连与流式加载</t>
+        </is>
+      </c>
+      <c r="D57" s="32" t="inlineStr">
+        <is>
+          <t>临时SAS链接、流式传输、权限校验</t>
+        </is>
       </c>
       <c r="E57" s="46" t="n"/>
       <c r="F57" s="46" t="n">
         <v>0.5</v>
       </c>
       <c r="G57" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="H57" s="46" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I57" s="46" t="n">
         <v>0.25</v>
       </c>
-      <c r="H57" s="46" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="I57" s="46" t="n">
-        <v>1.5</v>
-      </c>
+      <c r="J57" s="46" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="K57" s="17" t="n"/>
     </row>
     <row r="58" ht="26" customHeight="1">
       <c r="A58" s="15" t="inlineStr">
         <is>
-          <t>F04-04-2</t>
-        </is>
-      </c>
-      <c r="B58" s="32" t="inlineStr">
-        <is>
-          <t>异地副本同步</t>
-        </is>
-      </c>
+          <t>F05-05-3</t>
+        </is>
+      </c>
+      <c r="B58" s="17" t="n"/>
       <c r="C58" s="32" t="inlineStr">
         <is>
-          <t>存储异地冗余/复制配置</t>
-        </is>
-      </c>
-      <c r="D58" s="46" t="n"/>
+          <t>前端预览组件</t>
+        </is>
+      </c>
+      <c r="D58" s="32" t="inlineStr">
+        <is>
+          <t>格式适配、缩放、失败降级下载</t>
+        </is>
+      </c>
       <c r="E58" s="46" t="n"/>
       <c r="F58" s="46" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="G58" s="46" t="n">
-        <v>0.5</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="G58" s="46" t="n"/>
       <c r="H58" s="46" t="n">
         <v>0.25</v>
       </c>
       <c r="I58" s="46" t="n">
-        <v>2.25</v>
-      </c>
+        <v>0.25</v>
+      </c>
+      <c r="J58" s="46" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="K58" s="17" t="n"/>
     </row>
     <row r="59" ht="26" customHeight="1">
       <c r="A59" s="15" t="inlineStr">
         <is>
-          <t>F04-04-3</t>
-        </is>
-      </c>
-      <c r="B59" s="32" t="inlineStr">
-        <is>
-          <t>恢复切换演练</t>
+          <t>F06-01-1</t>
+        </is>
+      </c>
+      <c r="B59" s="100" t="inlineStr">
+        <is>
+          <t>归档操作日志记录</t>
         </is>
       </c>
       <c r="C59" s="32" t="inlineStr">
         <is>
-          <t>演练脚本、切换/回切流程与报告</t>
-        </is>
-      </c>
-      <c r="D59" s="46" t="n"/>
-      <c r="E59" s="46" t="n"/>
-      <c r="F59" s="46" t="n">
-        <v>1</v>
-      </c>
+          <t>埋点规范与日志模型</t>
+        </is>
+      </c>
+      <c r="D59" s="32" t="inlineStr">
+        <is>
+          <t>操作对象/用户/时间/结果/IP模型定义</t>
+        </is>
+      </c>
+      <c r="E59" s="46" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="F59" s="46" t="n"/>
       <c r="G59" s="46" t="n">
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
       <c r="H59" s="46" t="n">
         <v>0.25</v>
       </c>
       <c r="I59" s="46" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="84" t="inlineStr">
-        <is>
-          <t>F05-01</t>
-        </is>
-      </c>
-      <c r="B60" s="85" t="inlineStr">
-        <is>
-          <t>关键词检索（模块5·档案检索、智能发现与业务利用）· 共3个子任务</t>
-        </is>
-      </c>
-      <c r="C60" s="84" t="n"/>
-      <c r="D60" s="86" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="J59" s="46" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="K59" s="89" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="60" ht="26" customHeight="1">
+      <c r="A60" s="15" t="inlineStr">
+        <is>
+          <t>F06-01-2</t>
+        </is>
+      </c>
+      <c r="B60" s="17" t="n"/>
+      <c r="C60" s="32" t="inlineStr">
+        <is>
+          <t>操作拦截与落库</t>
+        </is>
+      </c>
+      <c r="D60" s="32" t="inlineStr">
+        <is>
+          <t>归档/导入/上传统一拦截器、异步写入</t>
+        </is>
+      </c>
+      <c r="E60" s="46" t="n"/>
+      <c r="F60" s="46" t="n"/>
+      <c r="G60" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="H60" s="46" t="n">
         <v>0.5</v>
       </c>
-      <c r="E60" s="86" t="n">
-        <v>2</v>
-      </c>
-      <c r="F60" s="86" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="G60" s="86" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="H60" s="86" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="I60" s="86" t="n">
-        <v>7.25</v>
-      </c>
+      <c r="I60" s="46" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="J60" s="46" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="K60" s="17" t="n"/>
     </row>
     <row r="61" ht="26" customHeight="1">
       <c r="A61" s="15" t="inlineStr">
         <is>
-          <t>F05-01-1</t>
-        </is>
-      </c>
-      <c r="B61" s="32" t="inlineStr">
-        <is>
-          <t>检索配置模型</t>
-        </is>
-      </c>
+          <t>F06-01-3</t>
+        </is>
+      </c>
+      <c r="B61" s="17" t="n"/>
       <c r="C61" s="32" t="inlineStr">
         <is>
-          <t>可检索字段、分词策略、OCR文本索引策略</t>
-        </is>
-      </c>
-      <c r="D61" s="46" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="E61" s="46" t="n">
-        <v>0.5</v>
-      </c>
+          <t>审计查询界面</t>
+        </is>
+      </c>
+      <c r="D61" s="32" t="inlineStr">
+        <is>
+          <t>多维筛选与导出（覆盖归档/查询/导出三类日志）</t>
+        </is>
+      </c>
+      <c r="E61" s="46" t="n"/>
       <c r="F61" s="46" t="n">
         <v>1</v>
       </c>
@@ -17753,128 +18019,148 @@
         <v>0.25</v>
       </c>
       <c r="H61" s="46" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I61" s="46" t="n">
         <v>0.25</v>
       </c>
-      <c r="I61" s="46" t="n">
-        <v>2.5</v>
-      </c>
+      <c r="J61" s="46" t="n">
+        <v>2</v>
+      </c>
+      <c r="K61" s="17" t="n"/>
     </row>
     <row r="62" ht="26" customHeight="1">
       <c r="A62" s="15" t="inlineStr">
         <is>
-          <t>F05-01-2</t>
-        </is>
-      </c>
-      <c r="B62" s="32" t="inlineStr">
-        <is>
-          <t>检索页动态表单</t>
+          <t>F06-02-1</t>
+        </is>
+      </c>
+      <c r="B62" s="100" t="inlineStr">
+        <is>
+          <t>查询操作日志记录</t>
         </is>
       </c>
       <c r="C62" s="32" t="inlineStr">
         <is>
-          <t>元数据驱动渲染、关键词与组合查询</t>
-        </is>
-      </c>
-      <c r="D62" s="46" t="n"/>
-      <c r="E62" s="46" t="n">
+          <t>查询/预览行为埋点</t>
+        </is>
+      </c>
+      <c r="D62" s="32" t="inlineStr">
+        <is>
+          <t>查询条件脱敏记录、预览行为记录</t>
+        </is>
+      </c>
+      <c r="E62" s="46" t="n"/>
+      <c r="F62" s="46" t="n"/>
+      <c r="G62" s="46" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="H62" s="46" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I62" s="46" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="J62" s="46" t="n">
         <v>1.5</v>
       </c>
-      <c r="F62" s="46" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="G62" s="46" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="H62" s="46" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="I62" s="46" t="n">
+      <c r="K62" s="89" t="n">
         <v>2.5</v>
       </c>
     </row>
     <row r="63" ht="26" customHeight="1">
       <c r="A63" s="15" t="inlineStr">
         <is>
-          <t>F05-01-3</t>
-        </is>
-      </c>
-      <c r="B63" s="32" t="inlineStr">
-        <is>
-          <t>查询代理与SERVE层对接</t>
-        </is>
-      </c>
+          <t>F06-02-2</t>
+        </is>
+      </c>
+      <c r="B63" s="17" t="n"/>
       <c r="C63" s="32" t="inlineStr">
         <is>
-          <t>查询服务、索引优化、结果高亮</t>
-        </is>
-      </c>
-      <c r="D63" s="46" t="n"/>
+          <t>异步批量写入</t>
+        </is>
+      </c>
+      <c r="D63" s="32" t="inlineStr">
+        <is>
+          <t>缓冲批量写入、不阻塞查询主链路</t>
+        </is>
+      </c>
       <c r="E63" s="46" t="n"/>
-      <c r="F63" s="46" t="n">
-        <v>1.25</v>
-      </c>
+      <c r="F63" s="46" t="n"/>
       <c r="G63" s="46" t="n">
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
       <c r="H63" s="46" t="n">
         <v>0.25</v>
       </c>
       <c r="I63" s="46" t="n">
-        <v>2.25</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="84" t="inlineStr">
-        <is>
-          <t>F05-02</t>
-        </is>
-      </c>
-      <c r="B64" s="85" t="inlineStr">
-        <is>
-          <t>按系统名称检索（模块5·档案检索、智能发现与业务利用）· 共2个子任务</t>
-        </is>
-      </c>
-      <c r="C64" s="84" t="n"/>
-      <c r="D64" s="86" t="n">
-        <v>0</v>
-      </c>
-      <c r="E64" s="86" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="J63" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="K63" s="17" t="n"/>
+    </row>
+    <row r="64" ht="26" customHeight="1">
+      <c r="A64" s="15" t="inlineStr">
+        <is>
+          <t>F06-03-1</t>
+        </is>
+      </c>
+      <c r="B64" s="100" t="inlineStr">
+        <is>
+          <t>导出操作日志记录</t>
+        </is>
+      </c>
+      <c r="C64" s="32" t="inlineStr">
+        <is>
+          <t>导出行为审计</t>
+        </is>
+      </c>
+      <c r="D64" s="32" t="inlineStr">
+        <is>
+          <t>导出范围/条数/导出人/IP/下载链接追踪</t>
+        </is>
+      </c>
+      <c r="E64" s="46" t="n"/>
+      <c r="F64" s="46" t="n"/>
+      <c r="G64" s="46" t="n">
         <v>0.75</v>
       </c>
-      <c r="F64" s="86" t="n">
+      <c r="H64" s="46" t="n">
         <v>0.5</v>
       </c>
-      <c r="G64" s="86" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="H64" s="86" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="I64" s="86" t="n">
-        <v>2.25</v>
+      <c r="I64" s="46" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="J64" s="46" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="K64" s="89" t="n">
+        <v>2.75</v>
       </c>
     </row>
     <row r="65" ht="26" customHeight="1">
       <c r="A65" s="15" t="inlineStr">
         <is>
-          <t>F05-02-1</t>
-        </is>
-      </c>
-      <c r="B65" s="32" t="inlineStr">
-        <is>
-          <t>来源系统筛选组件</t>
-        </is>
-      </c>
+          <t>F06-03-2</t>
+        </is>
+      </c>
+      <c r="B65" s="17" t="n"/>
       <c r="C65" s="32" t="inlineStr">
         <is>
-          <t>来源系统下拉/搜索/多选</t>
-        </is>
-      </c>
-      <c r="D65" s="46" t="n"/>
-      <c r="E65" s="46" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="F65" s="46" t="n"/>
+          <t>大批量导出告警</t>
+        </is>
+      </c>
+      <c r="D65" s="32" t="inlineStr">
+        <is>
+          <t>阈值告警、审批联动</t>
+        </is>
+      </c>
+      <c r="E65" s="46" t="n"/>
+      <c r="F65" s="46" t="n">
+        <v>0.5</v>
+      </c>
       <c r="G65" s="46" t="n">
         <v>0.25</v>
       </c>
@@ -17882,280 +18168,336 @@
         <v>0.25</v>
       </c>
       <c r="I65" s="46" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="J65" s="46" t="n">
         <v>1.25</v>
       </c>
+      <c r="K65" s="17" t="n"/>
     </row>
     <row r="66" ht="26" customHeight="1">
       <c r="A66" s="15" t="inlineStr">
         <is>
-          <t>F05-02-2</t>
-        </is>
-      </c>
-      <c r="B66" s="32" t="inlineStr">
-        <is>
-          <t>来源维度查询下推</t>
+          <t>F08-01-1</t>
+        </is>
+      </c>
+      <c r="B66" s="101" t="inlineStr">
+        <is>
+          <t>基础角色权限配置</t>
         </is>
       </c>
       <c r="C66" s="32" t="inlineStr">
         <is>
-          <t>sys_id过滤、分区裁剪</t>
-        </is>
-      </c>
-      <c r="D66" s="46" t="n"/>
-      <c r="E66" s="46" t="n"/>
-      <c r="F66" s="46" t="n">
+          <t>RBAC模型与权限矩阵</t>
+        </is>
+      </c>
+      <c r="D66" s="32" t="inlineStr">
+        <is>
+          <t>角色/菜单/数据范围/记录类型/操作权限定义</t>
+        </is>
+      </c>
+      <c r="E66" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="F66" s="46" t="n"/>
+      <c r="G66" s="46" t="n">
         <v>0.5</v>
-      </c>
-      <c r="G66" s="46" t="n">
-        <v>0.25</v>
       </c>
       <c r="H66" s="46" t="n">
         <v>0.25</v>
       </c>
       <c r="I66" s="46" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="84" t="inlineStr">
-        <is>
-          <t>F05-03</t>
-        </is>
-      </c>
-      <c r="B67" s="85" t="inlineStr">
-        <is>
-          <t>按业务时间检索（模块5·档案检索、智能发现与业务利用）· 共2个子任务</t>
-        </is>
-      </c>
-      <c r="C67" s="84" t="n"/>
-      <c r="D67" s="86" t="n">
-        <v>0</v>
-      </c>
-      <c r="E67" s="86" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="F67" s="86" t="n">
         <v>0.5</v>
       </c>
-      <c r="G67" s="86" t="n">
+      <c r="J66" s="46" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="K66" s="92" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="67" ht="26" customHeight="1">
+      <c r="A67" s="15" t="inlineStr">
+        <is>
+          <t>F08-01-2</t>
+        </is>
+      </c>
+      <c r="B67" s="17" t="n"/>
+      <c r="C67" s="32" t="inlineStr">
+        <is>
+          <t>角色管理界面与API</t>
+        </is>
+      </c>
+      <c r="D67" s="32" t="inlineStr">
+        <is>
+          <t>角色CRUD、权限分配界面与接口</t>
+        </is>
+      </c>
+      <c r="E67" s="46" t="n"/>
+      <c r="F67" s="46" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G67" s="46" t="n">
         <v>0.5</v>
       </c>
-      <c r="H67" s="86" t="n">
+      <c r="H67" s="46" t="n">
         <v>0.5</v>
       </c>
-      <c r="I67" s="86" t="n">
-        <v>2.25</v>
-      </c>
+      <c r="I67" s="46" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="J67" s="46" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="K67" s="17" t="n"/>
     </row>
     <row r="68" ht="26" customHeight="1">
       <c r="A68" s="15" t="inlineStr">
         <is>
-          <t>F05-03-1</t>
-        </is>
-      </c>
-      <c r="B68" s="32" t="inlineStr">
-        <is>
-          <t>时间维度筛选组件</t>
-        </is>
-      </c>
+          <t>F08-01-3</t>
+        </is>
+      </c>
+      <c r="B68" s="17" t="n"/>
       <c r="C68" s="32" t="inlineStr">
         <is>
-          <t>创建/修改/业务发生时间范围选择</t>
-        </is>
-      </c>
-      <c r="D68" s="46" t="n"/>
-      <c r="E68" s="46" t="n">
-        <v>0.75</v>
-      </c>
+          <t>权限校验与UC授权映射</t>
+        </is>
+      </c>
+      <c r="D68" s="32" t="inlineStr">
+        <is>
+          <t>菜单/接口级校验中间件、UC权限同步</t>
+        </is>
+      </c>
+      <c r="E68" s="46" t="n"/>
       <c r="F68" s="46" t="n"/>
       <c r="G68" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="H68" s="46" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="I68" s="46" t="n">
         <v>0.25</v>
       </c>
-      <c r="H68" s="46" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="I68" s="46" t="n">
-        <v>1.25</v>
-      </c>
+      <c r="J68" s="46" t="n">
+        <v>2</v>
+      </c>
+      <c r="K68" s="17" t="n"/>
     </row>
     <row r="69" ht="26" customHeight="1">
       <c r="A69" s="15" t="inlineStr">
         <is>
-          <t>F05-03-2</t>
-        </is>
-      </c>
-      <c r="B69" s="32" t="inlineStr">
-        <is>
-          <t>时间分区下推与索引</t>
+          <t>F08-02-1</t>
+        </is>
+      </c>
+      <c r="B69" s="101" t="inlineStr">
+        <is>
+          <t>用户账号管理</t>
         </is>
       </c>
       <c r="C69" s="32" t="inlineStr">
         <is>
-          <t>分区裁剪、时间索引优化</t>
-        </is>
-      </c>
-      <c r="D69" s="46" t="n"/>
-      <c r="E69" s="46" t="n"/>
+          <t>账号CRUD与生命周期</t>
+        </is>
+      </c>
+      <c r="D69" s="32" t="inlineStr">
+        <is>
+          <t>创建/启用禁用/密码重置/有效期</t>
+        </is>
+      </c>
+      <c r="E69" s="46" t="n">
+        <v>0.25</v>
+      </c>
       <c r="F69" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="G69" s="46" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="H69" s="46" t="n">
         <v>0.5</v>
       </c>
-      <c r="G69" s="46" t="n">
+      <c r="I69" s="46" t="n">
         <v>0.25</v>
       </c>
-      <c r="H69" s="46" t="n">
+      <c r="J69" s="46" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="K69" s="92" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="70" ht="26" customHeight="1">
+      <c r="A70" s="15" t="inlineStr">
+        <is>
+          <t>F08-02-2</t>
+        </is>
+      </c>
+      <c r="B70" s="17" t="n"/>
+      <c r="C70" s="32" t="inlineStr">
+        <is>
+          <t>账号与角色绑定</t>
+        </is>
+      </c>
+      <c r="D70" s="32" t="inlineStr">
+        <is>
+          <t>分配、批量操作、人员交接</t>
+        </is>
+      </c>
+      <c r="E70" s="46" t="n"/>
+      <c r="F70" s="46" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G70" s="46" t="n">
         <v>0.25</v>
       </c>
-      <c r="I69" s="46" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="84" t="inlineStr">
-        <is>
-          <t>F05-04</t>
-        </is>
-      </c>
-      <c r="B70" s="85" t="inlineStr">
-        <is>
-          <t>检索结果列表展示（模块5·档案检索、智能发现与业务利用）· 共2个子任务</t>
-        </is>
-      </c>
-      <c r="C70" s="84" t="n"/>
-      <c r="D70" s="86" t="n">
-        <v>0</v>
-      </c>
-      <c r="E70" s="86" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="F70" s="86" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="G70" s="86" t="n">
-        <v>1</v>
-      </c>
-      <c r="H70" s="86" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="I70" s="86" t="n">
-        <v>4</v>
-      </c>
+      <c r="H70" s="46" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="I70" s="46" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="J70" s="46" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="K70" s="17" t="n"/>
     </row>
     <row r="71" ht="26" customHeight="1">
       <c r="A71" s="15" t="inlineStr">
         <is>
-          <t>F05-04-1</t>
-        </is>
-      </c>
-      <c r="B71" s="32" t="inlineStr">
-        <is>
-          <t>列表展示与分页排序</t>
+          <t>F08-03-1</t>
+        </is>
+      </c>
+      <c r="B71" s="101" t="inlineStr">
+        <is>
+          <t>企业SSO集成</t>
         </is>
       </c>
       <c r="C71" s="32" t="inlineStr">
         <is>
-          <t>关键字段展示、分批加载、虚拟滚动</t>
-        </is>
-      </c>
-      <c r="D71" s="46" t="n"/>
+          <t>Entra ID对接配置</t>
+        </is>
+      </c>
+      <c r="D71" s="32" t="inlineStr">
+        <is>
+          <t>应用注册、回调配置、claims映射</t>
+        </is>
+      </c>
       <c r="E71" s="46" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="F71" s="46" t="n"/>
+        <v>0.25</v>
+      </c>
+      <c r="F71" s="46" t="n">
+        <v>0.5</v>
+      </c>
       <c r="G71" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="H71" s="46" t="n">
         <v>0.5</v>
       </c>
-      <c r="H71" s="46" t="n">
+      <c r="I71" s="46" t="n">
         <v>0.25</v>
       </c>
-      <c r="I71" s="46" t="n">
-        <v>2.25</v>
+      <c r="J71" s="46" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="K71" s="92" t="n">
+        <v>6.75</v>
       </c>
     </row>
     <row r="72" ht="26" customHeight="1">
       <c r="A72" s="15" t="inlineStr">
         <is>
-          <t>F05-04-2</t>
-        </is>
-      </c>
-      <c r="B72" s="32" t="inlineStr">
-        <is>
-          <t>大批量结果性能</t>
-        </is>
-      </c>
+          <t>F08-03-2</t>
+        </is>
+      </c>
+      <c r="B72" s="17" t="n"/>
       <c r="C72" s="32" t="inlineStr">
         <is>
-          <t>异步计数、游标分页、缓存</t>
-        </is>
-      </c>
-      <c r="D72" s="46" t="n"/>
-      <c r="E72" s="46" t="n">
-        <v>0.25</v>
-      </c>
+          <t>SSO登录链路</t>
+        </is>
+      </c>
+      <c r="D72" s="32" t="inlineStr">
+        <is>
+          <t>登录页、令牌交换、会话管理</t>
+        </is>
+      </c>
+      <c r="E72" s="46" t="n"/>
       <c r="F72" s="46" t="n">
-        <v>0.75</v>
+        <v>1.5</v>
       </c>
       <c r="G72" s="46" t="n">
         <v>0.5</v>
       </c>
       <c r="H72" s="46" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="I72" s="46" t="n">
         <v>0.25</v>
       </c>
-      <c r="I72" s="46" t="n">
-        <v>1.75</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="84" t="inlineStr">
-        <is>
-          <t>F05-05</t>
-        </is>
-      </c>
-      <c r="B73" s="85" t="inlineStr">
-        <is>
-          <t>原始文件在线预览（模块5·档案检索、智能发现与业务利用）· 共3个子任务</t>
-        </is>
-      </c>
-      <c r="C73" s="84" t="n"/>
-      <c r="D73" s="86" t="n">
-        <v>0</v>
-      </c>
-      <c r="E73" s="86" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="F73" s="86" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="G73" s="86" t="n">
+      <c r="J72" s="46" t="n">
+        <v>3</v>
+      </c>
+      <c r="K72" s="17" t="n"/>
+    </row>
+    <row r="73" ht="26" customHeight="1">
+      <c r="A73" s="15" t="inlineStr">
+        <is>
+          <t>F08-03-3</t>
+        </is>
+      </c>
+      <c r="B73" s="17" t="n"/>
+      <c r="C73" s="32" t="inlineStr">
+        <is>
+          <t>认证异常场景处理</t>
+        </is>
+      </c>
+      <c r="D73" s="32" t="inlineStr">
+        <is>
+          <t>认证失败、账号锁定、多账号冲突</t>
+        </is>
+      </c>
+      <c r="E73" s="46" t="n"/>
+      <c r="F73" s="46" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G73" s="46" t="n"/>
+      <c r="H73" s="46" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I73" s="46" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="J73" s="46" t="n">
         <v>1.25</v>
       </c>
-      <c r="H73" s="86" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="I73" s="86" t="n">
-        <v>6</v>
-      </c>
+      <c r="K73" s="17" t="n"/>
     </row>
     <row r="74" ht="26" customHeight="1">
       <c r="A74" s="15" t="inlineStr">
         <is>
-          <t>F05-05-1</t>
-        </is>
-      </c>
-      <c r="B74" s="32" t="inlineStr">
-        <is>
-          <t>预览服务</t>
+          <t>F08-04-1</t>
+        </is>
+      </c>
+      <c r="B74" s="101" t="inlineStr">
+        <is>
+          <t>用户身份自动识别与关联</t>
         </is>
       </c>
       <c r="C74" s="32" t="inlineStr">
         <is>
-          <t>格式识别、图片/PDF/Office转换</t>
-        </is>
-      </c>
-      <c r="D74" s="46" t="n"/>
-      <c r="E74" s="46" t="n"/>
-      <c r="F74" s="46" t="n">
-        <v>1.5</v>
-      </c>
+          <t>身份映射规则</t>
+        </is>
+      </c>
+      <c r="D74" s="32" t="inlineStr">
+        <is>
+          <t>企业账号↔RIMS用户映射、自动建号规则</t>
+        </is>
+      </c>
+      <c r="E74" s="46" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F74" s="46" t="n"/>
       <c r="G74" s="46" t="n">
         <v>0.5</v>
       </c>
@@ -18163,1013 +18505,226 @@
         <v>0.25</v>
       </c>
       <c r="I74" s="46" t="n">
-        <v>2.25</v>
+        <v>0.25</v>
+      </c>
+      <c r="J74" s="46" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="K74" s="92" t="n">
+        <v>3.25</v>
       </c>
     </row>
     <row r="75" ht="26" customHeight="1">
       <c r="A75" s="15" t="inlineStr">
         <is>
-          <t>F05-05-2</t>
-        </is>
-      </c>
-      <c r="B75" s="32" t="inlineStr">
-        <is>
-          <t>SAS直连与流式加载</t>
-        </is>
-      </c>
+          <t>F08-04-2</t>
+        </is>
+      </c>
+      <c r="B75" s="17" t="n"/>
       <c r="C75" s="32" t="inlineStr">
         <is>
-          <t>临时SAS链接、流式传输、权限校验</t>
-        </is>
-      </c>
-      <c r="D75" s="46" t="n"/>
-      <c r="E75" s="46" t="n">
+          <t>首登自动关联与角色赋予</t>
+        </is>
+      </c>
+      <c r="D75" s="32" t="inlineStr">
+        <is>
+          <t>默认角色、待分配队列</t>
+        </is>
+      </c>
+      <c r="E75" s="46" t="n"/>
+      <c r="F75" s="46" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="G75" s="46" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="H75" s="46" t="n">
         <v>0.5</v>
       </c>
-      <c r="F75" s="46" t="n">
-        <v>1</v>
-      </c>
-      <c r="G75" s="46" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="H75" s="46" t="n">
+      <c r="I75" s="46" t="n">
         <v>0.25</v>
       </c>
-      <c r="I75" s="46" t="n">
-        <v>2.25</v>
-      </c>
+      <c r="J75" s="46" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="K75" s="17" t="n"/>
     </row>
     <row r="76" ht="26" customHeight="1">
       <c r="A76" s="15" t="inlineStr">
         <is>
-          <t>F05-05-3</t>
-        </is>
-      </c>
-      <c r="B76" s="32" t="inlineStr">
-        <is>
-          <t>前端预览组件</t>
+          <t>F08-05-1</t>
+        </is>
+      </c>
+      <c r="B76" s="101" t="inlineStr">
+        <is>
+          <t>登录状态与异常访问控制</t>
         </is>
       </c>
       <c r="C76" s="32" t="inlineStr">
         <is>
-          <t>格式适配、缩放、失败降级下载</t>
-        </is>
-      </c>
-      <c r="D76" s="46" t="n"/>
+          <t>会话与超时策略</t>
+        </is>
+      </c>
+      <c r="D76" s="32" t="inlineStr">
+        <is>
+          <t>超时控制、登出、单点登出</t>
+        </is>
+      </c>
       <c r="E76" s="46" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="F76" s="46" t="n">
         <v>1</v>
       </c>
-      <c r="F76" s="46" t="n"/>
       <c r="G76" s="46" t="n">
         <v>0.25</v>
       </c>
       <c r="H76" s="46" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I76" s="46" t="n">
         <v>0.25</v>
       </c>
-      <c r="I76" s="46" t="n">
+      <c r="J76" s="46" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="K76" s="92" t="n">
+        <v>3.75</v>
+      </c>
+    </row>
+    <row r="77" ht="26" customHeight="1">
+      <c r="A77" s="15" t="inlineStr">
+        <is>
+          <t>F08-05-2</t>
+        </is>
+      </c>
+      <c r="B77" s="17" t="n"/>
+      <c r="C77" s="32" t="inlineStr">
+        <is>
+          <t>异常访问控制</t>
+        </is>
+      </c>
+      <c r="D77" s="32" t="inlineStr">
+        <is>
+          <t>账号锁定、认证失效限制访问、IP策略</t>
+        </is>
+      </c>
+      <c r="E77" s="46" t="n"/>
+      <c r="F77" s="46" t="n"/>
+      <c r="G77" s="46" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="H77" s="46" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I77" s="46" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="J77" s="46" t="n">
         <v>1.5</v>
       </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="87" t="inlineStr">
-        <is>
-          <t>F06-01</t>
-        </is>
-      </c>
-      <c r="B77" s="88" t="inlineStr">
-        <is>
-          <t>归档操作日志记录（模块6·合规管控、审计追踪与合规报表）· 共3个子任务</t>
-        </is>
-      </c>
-      <c r="C77" s="87" t="n"/>
-      <c r="D77" s="89" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="E77" s="89" t="n">
-        <v>1</v>
-      </c>
-      <c r="F77" s="89" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="G77" s="89" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="H77" s="89" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="I77" s="89" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="78" ht="26" customHeight="1">
-      <c r="A78" s="15" t="inlineStr">
-        <is>
-          <t>F06-01-1</t>
-        </is>
-      </c>
-      <c r="B78" s="32" t="inlineStr">
-        <is>
-          <t>埋点规范与日志模型</t>
-        </is>
-      </c>
-      <c r="C78" s="32" t="inlineStr">
-        <is>
-          <t>操作对象/用户/时间/结果/IP模型定义</t>
-        </is>
-      </c>
-      <c r="D78" s="46" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="E78" s="46" t="n"/>
-      <c r="F78" s="46" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G78" s="46" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="H78" s="46" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="I78" s="46" t="n">
-        <v>1.25</v>
-      </c>
-    </row>
-    <row r="79" ht="26" customHeight="1">
-      <c r="A79" s="15" t="inlineStr">
-        <is>
-          <t>F06-01-2</t>
-        </is>
-      </c>
-      <c r="B79" s="32" t="inlineStr">
-        <is>
-          <t>操作拦截与落库</t>
-        </is>
-      </c>
-      <c r="C79" s="32" t="inlineStr">
-        <is>
-          <t>归档/导入/上传统一拦截器、异步写入</t>
-        </is>
-      </c>
-      <c r="D79" s="46" t="n"/>
-      <c r="E79" s="46" t="n"/>
-      <c r="F79" s="46" t="n">
-        <v>1</v>
-      </c>
-      <c r="G79" s="46" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="H79" s="46" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="I79" s="46" t="n">
-        <v>1.75</v>
-      </c>
-    </row>
-    <row r="80" ht="26" customHeight="1">
-      <c r="A80" s="15" t="inlineStr">
-        <is>
-          <t>F06-01-3</t>
-        </is>
-      </c>
-      <c r="B80" s="32" t="inlineStr">
-        <is>
-          <t>审计查询界面</t>
-        </is>
-      </c>
-      <c r="C80" s="32" t="inlineStr">
-        <is>
-          <t>多维筛选与导出（覆盖归档/查询/导出三类日志）</t>
-        </is>
-      </c>
-      <c r="D80" s="46" t="n"/>
-      <c r="E80" s="46" t="n">
-        <v>1</v>
-      </c>
-      <c r="F80" s="46" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="G80" s="46" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="H80" s="46" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="I80" s="46" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" s="87" t="inlineStr">
-        <is>
-          <t>F06-02</t>
-        </is>
-      </c>
-      <c r="B81" s="88" t="inlineStr">
-        <is>
-          <t>查询操作日志记录（模块6·合规管控、审计追踪与合规报表）· 共2个子任务</t>
-        </is>
-      </c>
-      <c r="C81" s="87" t="n"/>
-      <c r="D81" s="89" t="n">
-        <v>0</v>
-      </c>
-      <c r="E81" s="89" t="n">
-        <v>0</v>
-      </c>
-      <c r="F81" s="89" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="G81" s="89" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="H81" s="89" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="I81" s="89" t="n">
-        <v>2.5</v>
-      </c>
-    </row>
-    <row r="82" ht="26" customHeight="1">
-      <c r="A82" s="15" t="inlineStr">
-        <is>
-          <t>F06-02-1</t>
-        </is>
-      </c>
-      <c r="B82" s="32" t="inlineStr">
-        <is>
-          <t>查询/预览行为埋点</t>
-        </is>
-      </c>
-      <c r="C82" s="32" t="inlineStr">
-        <is>
-          <t>查询条件脱敏记录、预览行为记录</t>
-        </is>
-      </c>
-      <c r="D82" s="46" t="n"/>
-      <c r="E82" s="46" t="n"/>
-      <c r="F82" s="46" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="G82" s="46" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="H82" s="46" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="I82" s="46" t="n">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="83" ht="26" customHeight="1">
-      <c r="A83" s="15" t="inlineStr">
-        <is>
-          <t>F06-02-2</t>
-        </is>
-      </c>
-      <c r="B83" s="32" t="inlineStr">
-        <is>
-          <t>异步批量写入</t>
-        </is>
-      </c>
-      <c r="C83" s="32" t="inlineStr">
-        <is>
-          <t>缓冲批量写入、不阻塞查询主链路</t>
-        </is>
-      </c>
-      <c r="D83" s="46" t="n"/>
-      <c r="E83" s="46" t="n"/>
-      <c r="F83" s="46" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G83" s="46" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="H83" s="46" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="I83" s="46" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" s="87" t="inlineStr">
-        <is>
-          <t>F06-03</t>
-        </is>
-      </c>
-      <c r="B84" s="88" t="inlineStr">
-        <is>
-          <t>导出操作日志记录（模块6·合规管控、审计追踪与合规报表）· 共2个子任务</t>
-        </is>
-      </c>
-      <c r="C84" s="87" t="n"/>
-      <c r="D84" s="89" t="n">
-        <v>0</v>
-      </c>
-      <c r="E84" s="89" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F84" s="89" t="n">
-        <v>1</v>
-      </c>
-      <c r="G84" s="89" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="H84" s="89" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="I84" s="89" t="n">
-        <v>2.75</v>
-      </c>
-    </row>
-    <row r="85" ht="26" customHeight="1">
-      <c r="A85" s="15" t="inlineStr">
-        <is>
-          <t>F06-03-1</t>
-        </is>
-      </c>
-      <c r="B85" s="32" t="inlineStr">
-        <is>
-          <t>导出行为审计</t>
-        </is>
-      </c>
-      <c r="C85" s="32" t="inlineStr">
-        <is>
-          <t>导出范围/条数/导出人/IP/下载链接追踪</t>
-        </is>
-      </c>
-      <c r="D85" s="46" t="n"/>
-      <c r="E85" s="46" t="n"/>
-      <c r="F85" s="46" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="G85" s="46" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="H85" s="46" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="I85" s="46" t="n">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="86" ht="26" customHeight="1">
-      <c r="A86" s="15" t="inlineStr">
-        <is>
-          <t>F06-03-2</t>
-        </is>
-      </c>
-      <c r="B86" s="32" t="inlineStr">
-        <is>
-          <t>大批量导出告警</t>
-        </is>
-      </c>
-      <c r="C86" s="32" t="inlineStr">
-        <is>
-          <t>阈值告警、审批联动</t>
-        </is>
-      </c>
-      <c r="D86" s="46" t="n"/>
-      <c r="E86" s="46" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F86" s="46" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="G86" s="46" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="H86" s="46" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="I86" s="46" t="n">
-        <v>1.25</v>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" s="90" t="inlineStr">
-        <is>
-          <t>F08-01</t>
-        </is>
-      </c>
-      <c r="B87" s="91" t="inlineStr">
-        <is>
-          <t>基础角色权限配置（模块8·系统全局治理、运维与监控）· 共3个子任务</t>
-        </is>
-      </c>
-      <c r="C87" s="90" t="n"/>
-      <c r="D87" s="92" t="n">
-        <v>1</v>
-      </c>
-      <c r="E87" s="92" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="F87" s="92" t="n">
-        <v>2</v>
-      </c>
-      <c r="G87" s="92" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="H87" s="92" t="n">
-        <v>1</v>
-      </c>
-      <c r="I87" s="92" t="n">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="88" ht="26" customHeight="1">
-      <c r="A88" s="15" t="inlineStr">
-        <is>
-          <t>F08-01-1</t>
-        </is>
-      </c>
-      <c r="B88" s="32" t="inlineStr">
-        <is>
-          <t>RBAC模型与权限矩阵</t>
-        </is>
-      </c>
-      <c r="C88" s="32" t="inlineStr">
-        <is>
-          <t>角色/菜单/数据范围/记录类型/操作权限定义</t>
-        </is>
-      </c>
-      <c r="D88" s="46" t="n">
-        <v>1</v>
-      </c>
-      <c r="E88" s="46" t="n"/>
-      <c r="F88" s="46" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G88" s="46" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="H88" s="46" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="I88" s="46" t="n">
-        <v>2.25</v>
-      </c>
-    </row>
-    <row r="89" ht="26" customHeight="1">
-      <c r="A89" s="15" t="inlineStr">
-        <is>
-          <t>F08-01-2</t>
-        </is>
-      </c>
-      <c r="B89" s="32" t="inlineStr">
-        <is>
-          <t>角色管理界面与API</t>
-        </is>
-      </c>
-      <c r="C89" s="32" t="inlineStr">
-        <is>
-          <t>角色CRUD、权限分配界面与接口</t>
-        </is>
-      </c>
-      <c r="D89" s="46" t="n"/>
-      <c r="E89" s="46" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="F89" s="46" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G89" s="46" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="H89" s="46" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="I89" s="46" t="n">
-        <v>2.75</v>
-      </c>
-    </row>
-    <row r="90" ht="26" customHeight="1">
-      <c r="A90" s="15" t="inlineStr">
-        <is>
-          <t>F08-01-3</t>
-        </is>
-      </c>
-      <c r="B90" s="32" t="inlineStr">
-        <is>
-          <t>权限校验与UC授权映射</t>
-        </is>
-      </c>
-      <c r="C90" s="32" t="inlineStr">
-        <is>
-          <t>菜单/接口级校验中间件、UC权限同步</t>
-        </is>
-      </c>
-      <c r="D90" s="46" t="n"/>
-      <c r="E90" s="46" t="n"/>
-      <c r="F90" s="46" t="n">
-        <v>1</v>
-      </c>
-      <c r="G90" s="46" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="H90" s="46" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="I90" s="46" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" s="90" t="inlineStr">
-        <is>
-          <t>F08-02</t>
-        </is>
-      </c>
-      <c r="B91" s="91" t="inlineStr">
-        <is>
-          <t>用户账号管理（模块8·系统全局治理、运维与监控）· 共2个子任务</t>
-        </is>
-      </c>
-      <c r="C91" s="90" t="n"/>
-      <c r="D91" s="92" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="E91" s="92" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="F91" s="92" t="n">
-        <v>1</v>
-      </c>
-      <c r="G91" s="92" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="H91" s="92" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="I91" s="92" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="92" ht="26" customHeight="1">
-      <c r="A92" s="15" t="inlineStr">
-        <is>
-          <t>F08-02-1</t>
-        </is>
-      </c>
-      <c r="B92" s="32" t="inlineStr">
-        <is>
-          <t>账号CRUD与生命周期</t>
-        </is>
-      </c>
-      <c r="C92" s="32" t="inlineStr">
-        <is>
-          <t>创建/启用禁用/密码重置/有效期</t>
-        </is>
-      </c>
-      <c r="D92" s="46" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="E92" s="46" t="n">
-        <v>1</v>
-      </c>
-      <c r="F92" s="46" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="G92" s="46" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="H92" s="46" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="I92" s="46" t="n">
-        <v>2.75</v>
-      </c>
-    </row>
-    <row r="93" ht="26" customHeight="1">
-      <c r="A93" s="15" t="inlineStr">
-        <is>
-          <t>F08-02-2</t>
-        </is>
-      </c>
-      <c r="B93" s="32" t="inlineStr">
-        <is>
-          <t>账号与角色绑定</t>
-        </is>
-      </c>
-      <c r="C93" s="32" t="inlineStr">
-        <is>
-          <t>分配、批量操作、人员交接</t>
-        </is>
-      </c>
-      <c r="D93" s="46" t="n"/>
-      <c r="E93" s="46" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F93" s="46" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="G93" s="46" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="H93" s="46" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="I93" s="46" t="n">
-        <v>1.25</v>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" s="90" t="inlineStr">
-        <is>
-          <t>F08-03</t>
-        </is>
-      </c>
-      <c r="B94" s="91" t="inlineStr">
-        <is>
-          <t>企业SSO集成（模块8·系统全局治理、运维与监控）· 共3个子任务</t>
-        </is>
-      </c>
-      <c r="C94" s="90" t="n"/>
-      <c r="D94" s="92" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="E94" s="92" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="F94" s="92" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="G94" s="92" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="H94" s="92" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="I94" s="92" t="n">
-        <v>6.75</v>
-      </c>
-    </row>
-    <row r="95" ht="26" customHeight="1">
-      <c r="A95" s="15" t="inlineStr">
-        <is>
-          <t>F08-03-1</t>
-        </is>
-      </c>
-      <c r="B95" s="32" t="inlineStr">
-        <is>
-          <t>Entra ID对接配置</t>
-        </is>
-      </c>
-      <c r="C95" s="32" t="inlineStr">
-        <is>
-          <t>应用注册、回调配置、claims映射</t>
-        </is>
-      </c>
-      <c r="D95" s="46" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="E95" s="46" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F95" s="46" t="n">
-        <v>1</v>
-      </c>
-      <c r="G95" s="46" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="H95" s="46" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="I95" s="46" t="n">
-        <v>2.5</v>
-      </c>
-    </row>
-    <row r="96" ht="26" customHeight="1">
-      <c r="A96" s="15" t="inlineStr">
-        <is>
-          <t>F08-03-2</t>
-        </is>
-      </c>
-      <c r="B96" s="32" t="inlineStr">
-        <is>
-          <t>SSO登录链路</t>
-        </is>
-      </c>
-      <c r="C96" s="32" t="inlineStr">
-        <is>
-          <t>登录页、令牌交换、会话管理</t>
-        </is>
-      </c>
-      <c r="D96" s="46" t="n"/>
-      <c r="E96" s="46" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="F96" s="46" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G96" s="46" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="H96" s="46" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="I96" s="46" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="97" ht="26" customHeight="1">
-      <c r="A97" s="15" t="inlineStr">
-        <is>
-          <t>F08-03-3</t>
-        </is>
-      </c>
-      <c r="B97" s="32" t="inlineStr">
-        <is>
-          <t>认证异常场景处理</t>
-        </is>
-      </c>
-      <c r="C97" s="32" t="inlineStr">
-        <is>
-          <t>认证失败、账号锁定、多账号冲突</t>
-        </is>
-      </c>
-      <c r="D97" s="46" t="n"/>
-      <c r="E97" s="46" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F97" s="46" t="n"/>
-      <c r="G97" s="46" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="H97" s="46" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="I97" s="46" t="n">
-        <v>1.25</v>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" s="90" t="inlineStr">
-        <is>
-          <t>F08-04</t>
-        </is>
-      </c>
-      <c r="B98" s="91" t="inlineStr">
-        <is>
-          <t>用户身份自动识别与关联（模块8·系统全局治理、运维与监控）· 共2个子任务</t>
-        </is>
-      </c>
-      <c r="C98" s="90" t="n"/>
-      <c r="D98" s="92" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="E98" s="92" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="F98" s="92" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="G98" s="92" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="H98" s="92" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="I98" s="92" t="n">
-        <v>3.25</v>
-      </c>
-    </row>
-    <row r="99" ht="26" customHeight="1">
-      <c r="A99" s="15" t="inlineStr">
-        <is>
-          <t>F08-04-1</t>
-        </is>
-      </c>
-      <c r="B99" s="32" t="inlineStr">
-        <is>
-          <t>身份映射规则</t>
-        </is>
-      </c>
-      <c r="C99" s="32" t="inlineStr">
-        <is>
-          <t>企业账号↔RIMS用户映射、自动建号规则</t>
-        </is>
-      </c>
-      <c r="D99" s="46" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="E99" s="46" t="n"/>
-      <c r="F99" s="46" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G99" s="46" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="H99" s="46" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="I99" s="46" t="n">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="100" ht="26" customHeight="1">
-      <c r="A100" s="15" t="inlineStr">
-        <is>
-          <t>F08-04-2</t>
-        </is>
-      </c>
-      <c r="B100" s="32" t="inlineStr">
-        <is>
-          <t>首登自动关联与角色赋予</t>
-        </is>
-      </c>
-      <c r="C100" s="32" t="inlineStr">
-        <is>
-          <t>默认角色、待分配队列</t>
-        </is>
-      </c>
-      <c r="D100" s="46" t="n"/>
-      <c r="E100" s="46" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="F100" s="46" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="G100" s="46" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="H100" s="46" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="I100" s="46" t="n">
-        <v>1.75</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" s="90" t="inlineStr">
-        <is>
-          <t>F08-05</t>
-        </is>
-      </c>
-      <c r="B101" s="91" t="inlineStr">
-        <is>
-          <t>登录状态与异常访问控制（模块8·系统全局治理、运维与监控）· 共2个子任务</t>
-        </is>
-      </c>
-      <c r="C101" s="90" t="n"/>
-      <c r="D101" s="92" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="E101" s="92" t="n">
-        <v>1</v>
-      </c>
-      <c r="F101" s="92" t="n">
-        <v>1</v>
-      </c>
-      <c r="G101" s="92" t="n">
-        <v>1</v>
-      </c>
-      <c r="H101" s="92" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="I101" s="92" t="n">
-        <v>3.75</v>
-      </c>
-    </row>
-    <row r="102" ht="26" customHeight="1">
-      <c r="A102" s="15" t="inlineStr">
-        <is>
-          <t>F08-05-1</t>
-        </is>
-      </c>
-      <c r="B102" s="32" t="inlineStr">
-        <is>
-          <t>会话与超时策略</t>
-        </is>
-      </c>
-      <c r="C102" s="32" t="inlineStr">
-        <is>
-          <t>超时控制、登出、单点登出</t>
-        </is>
-      </c>
-      <c r="D102" s="46" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="E102" s="46" t="n">
-        <v>1</v>
-      </c>
-      <c r="F102" s="46" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="G102" s="46" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="H102" s="46" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="I102" s="46" t="n">
-        <v>2.25</v>
-      </c>
-    </row>
-    <row r="103" ht="26" customHeight="1">
-      <c r="A103" s="15" t="inlineStr">
-        <is>
-          <t>F08-05-2</t>
-        </is>
-      </c>
-      <c r="B103" s="32" t="inlineStr">
-        <is>
-          <t>异常访问控制</t>
-        </is>
-      </c>
-      <c r="C103" s="32" t="inlineStr">
-        <is>
-          <t>账号锁定、认证失效限制访问、IP策略</t>
-        </is>
-      </c>
-      <c r="D103" s="46" t="n"/>
-      <c r="E103" s="46" t="n"/>
-      <c r="F103" s="46" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="G103" s="46" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="H103" s="46" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="I103" s="46" t="n">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" s="8" t="inlineStr">
+      <c r="K77" s="17" t="n"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="8" t="inlineStr"/>
+      <c r="B78" s="8" t="inlineStr">
         <is>
           <t>总计</t>
         </is>
       </c>
-      <c r="B104" s="8" t="inlineStr">
+      <c r="C78" s="93" t="inlineStr">
         <is>
           <t>26项功能 × 75个子任务</t>
         </is>
       </c>
-      <c r="C104" s="93" t="inlineStr">
+      <c r="D78" s="93" t="inlineStr">
         <is>
           <t>独立直估（不含项目初始化/架构设计/集成/UAT/上线/PM等公共工作）</t>
         </is>
       </c>
-      <c r="D104" s="44" t="n">
+      <c r="E78" s="44" t="n">
         <v>12.75</v>
       </c>
-      <c r="E104" s="44" t="n">
+      <c r="F78" s="44" t="n">
         <v>36.75</v>
       </c>
-      <c r="F104" s="44" t="n">
+      <c r="G78" s="44" t="n">
         <v>62</v>
       </c>
-      <c r="G104" s="44" t="n">
+      <c r="H78" s="44" t="n">
         <v>35.75</v>
       </c>
-      <c r="H104" s="44" t="n">
+      <c r="I78" s="44" t="n">
         <v>20</v>
       </c>
-      <c r="I104" s="44" t="n">
+      <c r="J78" s="44" t="n">
         <v>167.25</v>
       </c>
-    </row>
-    <row r="106" ht="52" customHeight="1">
-      <c r="A106" s="94" t="inlineStr">
+      <c r="K78" s="8" t="inlineStr"/>
+    </row>
+    <row r="80" ht="52" customHeight="1">
+      <c r="A80" s="94" t="inlineStr">
         <is>
           <t>对照说明（两个口径）：① 本表为子任务级独立直估，合计 167.25 人天（BA 12.75 / Wade 36.75 / DevB 62.0 / 测试 35.75 / SLC 20.0），其中「存储落地Iceberg/UC」「元数据驱动」「RBAC」等设计实现类子任务与计划公共行（架构与非功能设计等）存在重叠，且未假设跨功能复用（同一界面/中间件多处计价）。② 排期计划（WBS分解/功能视角分解）中：26项功能直接分摊仅 54.5 人天（大量开发工作量按阶段放在架构设计/集成/专项等公共行，公共合计 130.5 人天），总投入185人天。结论：功能直估 167.25 人天已达计划总投入的 90%，而计划中还有需求8.5/初始化9/PM15及集成·UAT·上线等纯公共工作未包含在本直估内——按传统粒度估算，3人×3个月偏紧，需依赖AI Native复用与生成提效吸收约50人天量级缺口，建议将本表作为功能规模基线并纳入风险跟踪。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:I104"/>
-  <mergeCells count="28">
-    <mergeCell ref="B91:C91"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="B3:C3"/>
-    <mergeCell ref="B81:C81"/>
-    <mergeCell ref="B56:C56"/>
-    <mergeCell ref="B77:C77"/>
-    <mergeCell ref="B52:C52"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="B48:C48"/>
-    <mergeCell ref="B70:C70"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="B98:C98"/>
-    <mergeCell ref="B67:C67"/>
-    <mergeCell ref="B101:C101"/>
-    <mergeCell ref="B60:C60"/>
-    <mergeCell ref="A106:I106"/>
-    <mergeCell ref="B73:C73"/>
-    <mergeCell ref="B87:C87"/>
-    <mergeCell ref="B44:C44"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="B84:C84"/>
-    <mergeCell ref="B40:C40"/>
-    <mergeCell ref="B64:C64"/>
-    <mergeCell ref="A1:I1"/>
-    <mergeCell ref="B36:C36"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="B94:C94"/>
+  <mergeCells count="54">
+    <mergeCell ref="K54:K55"/>
+    <mergeCell ref="K76:K77"/>
+    <mergeCell ref="B62:B63"/>
+    <mergeCell ref="K21:K22"/>
+    <mergeCell ref="B52:B53"/>
+    <mergeCell ref="K38:K40"/>
+    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="K23:K25"/>
+    <mergeCell ref="K50:K51"/>
+    <mergeCell ref="B14:B17"/>
+    <mergeCell ref="K66:K68"/>
+    <mergeCell ref="B35:B37"/>
+    <mergeCell ref="B26:B28"/>
+    <mergeCell ref="B66:B68"/>
+    <mergeCell ref="B69:B70"/>
+    <mergeCell ref="B56:B58"/>
+    <mergeCell ref="K3:K9"/>
+    <mergeCell ref="B41:B43"/>
+    <mergeCell ref="B47:B49"/>
+    <mergeCell ref="B32:B34"/>
+    <mergeCell ref="A80:K80"/>
+    <mergeCell ref="B10:B13"/>
+    <mergeCell ref="B59:B61"/>
+    <mergeCell ref="K18:K20"/>
+    <mergeCell ref="K52:K53"/>
+    <mergeCell ref="B74:B75"/>
+    <mergeCell ref="B64:B65"/>
+    <mergeCell ref="K44:K46"/>
+    <mergeCell ref="K69:K70"/>
+    <mergeCell ref="K29:K31"/>
+    <mergeCell ref="B71:B73"/>
+    <mergeCell ref="B3:B9"/>
+    <mergeCell ref="K56:K58"/>
+    <mergeCell ref="K14:K17"/>
+    <mergeCell ref="B54:B55"/>
+    <mergeCell ref="B18:B20"/>
+    <mergeCell ref="K41:K43"/>
+    <mergeCell ref="K59:K61"/>
+    <mergeCell ref="K32:K34"/>
+    <mergeCell ref="K35:K37"/>
+    <mergeCell ref="K62:K63"/>
+    <mergeCell ref="B23:B25"/>
+    <mergeCell ref="K10:K13"/>
+    <mergeCell ref="K26:K28"/>
+    <mergeCell ref="B76:B77"/>
+    <mergeCell ref="K71:K73"/>
+    <mergeCell ref="B44:B46"/>
+    <mergeCell ref="K47:K49"/>
+    <mergeCell ref="K74:K75"/>
+    <mergeCell ref="B29:B31"/>
+    <mergeCell ref="B38:B40"/>
+    <mergeCell ref="B50:B51"/>
+    <mergeCell ref="K64:K65"/>
+    <mergeCell ref="B21:B22"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/RIMS项目WBS工作分解_AI Native版.xlsx
+++ b/RIMS项目WBS工作分解_AI Native版.xlsx
@@ -232,7 +232,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="104">
+  <cellXfs count="106">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -507,6 +507,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1268,7 +1274,7 @@
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>子任务级直估：26项功能下钻到75个子任务/工作包（如F01-01拆为原系统录入/DB连接/表勾选/保留期配置/Iceberg·UC存储落地/导入作业/监控），按BA/开发A/开发B/测试/SLC文档独立估人天，不锚定185人天；功能名称与功能小计为纵向合并单元格；底部附与计划口径的对照与差异说明</t>
+          <t>子任务级直估：26项功能×75子任务 + 非功能与工程支撑×18子任务（N1框架初始化与基座/N2 ESLint·SonarLint·SAST代码质量治理/N3性能·鉴权·可观测·容量/N4部署运维），按BA/开发A/开发B/测试/SLC文档独立估人天；功能/组名称与小计为纵向合并单元格；底部附与计划口径对照</t>
         </is>
       </c>
     </row>
@@ -15786,7 +15792,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K80"/>
+  <dimension ref="A1:K98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -15805,7 +15811,7 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>功能拆解估算（子任务级直估）：功能信息纵向合并对应多个子任务 — 独立估算，不锚定排期185人天</t>
+          <t>功能拆解估算（子任务级直估）：26项功能×75子任务 + 非功能与工程支撑×18子任务 — 独立估算，不锚定排期185人天</t>
         </is>
       </c>
     </row>
@@ -15817,7 +15823,7 @@
       </c>
       <c r="B2" s="7" t="inlineStr">
         <is>
-          <t>功能名称</t>
+          <t>功能/组名称</t>
         </is>
       </c>
       <c r="C2" s="7" t="inlineStr">
@@ -15862,7 +15868,7 @@
       </c>
       <c r="K2" s="7" t="inlineStr">
         <is>
-          <t>功能小计</t>
+          <t>功能/组小计</t>
         </is>
       </c>
     </row>
@@ -15874,7 +15880,7 @@
       </c>
       <c r="B3" s="95" t="inlineStr">
         <is>
-          <t>结构化历史数据批量导入</t>
+          <t>结构化历史数据批量导入（模块1·存量历史数据迁移与标准化）</t>
         </is>
       </c>
       <c r="C3" s="32" t="inlineStr">
@@ -15891,7 +15897,7 @@
         <v>0.5</v>
       </c>
       <c r="F3" s="46" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="G3" s="46" t="n">
         <v>0.5</v>
@@ -15903,10 +15909,10 @@
         <v>0.25</v>
       </c>
       <c r="J3" s="46" t="n">
-        <v>2.75</v>
+        <v>3.25</v>
       </c>
       <c r="K3" s="74" t="n">
-        <v>20.75</v>
+        <v>22.75</v>
       </c>
     </row>
     <row r="4" ht="26" customHeight="1">
@@ -15930,7 +15936,7 @@
         <v>0.25</v>
       </c>
       <c r="F4" s="46" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="G4" s="46" t="n">
         <v>1</v>
@@ -15942,7 +15948,7 @@
         <v>0.25</v>
       </c>
       <c r="J4" s="46" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="K4" s="17" t="n"/>
     </row>
@@ -15967,7 +15973,7 @@
         <v>0.25</v>
       </c>
       <c r="F5" s="46" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="G5" s="46" t="n">
         <v>1</v>
@@ -15979,7 +15985,7 @@
         <v>0.25</v>
       </c>
       <c r="J5" s="46" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="K5" s="17" t="n"/>
     </row>
@@ -16109,7 +16115,7 @@
       </c>
       <c r="E9" s="46" t="n"/>
       <c r="F9" s="46" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="G9" s="46" t="n">
         <v>0.5</v>
@@ -16121,7 +16127,7 @@
         <v>0.25</v>
       </c>
       <c r="J9" s="46" t="n">
-        <v>2.25</v>
+        <v>2.75</v>
       </c>
       <c r="K9" s="17" t="n"/>
     </row>
@@ -16133,7 +16139,7 @@
       </c>
       <c r="B10" s="95" t="inlineStr">
         <is>
-          <t>非结构化文件及离线包批量导入</t>
+          <t>非结构化文件及离线包批量导入（模块1·存量历史数据迁移与标准化）</t>
         </is>
       </c>
       <c r="C10" s="32" t="inlineStr">
@@ -16150,7 +16156,7 @@
         <v>0.25</v>
       </c>
       <c r="F10" s="46" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="G10" s="46" t="n">
         <v>1</v>
@@ -16162,10 +16168,10 @@
         <v>0.25</v>
       </c>
       <c r="J10" s="46" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="K10" s="74" t="n">
-        <v>12.75</v>
+        <v>13.25</v>
       </c>
     </row>
     <row r="11" ht="26" customHeight="1">
@@ -16279,7 +16285,7 @@
       </c>
       <c r="B14" s="95" t="inlineStr">
         <is>
-          <t>数据导入规则配置</t>
+          <t>数据导入规则配置（模块1·存量历史数据迁移与标准化）</t>
         </is>
       </c>
       <c r="C14" s="32" t="inlineStr">
@@ -16296,7 +16302,7 @@
         <v>0.5</v>
       </c>
       <c r="F14" s="46" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="G14" s="46" t="n">
         <v>0.5</v>
@@ -16308,10 +16314,10 @@
         <v>0.25</v>
       </c>
       <c r="J14" s="46" t="n">
-        <v>3.25</v>
+        <v>3.75</v>
       </c>
       <c r="K14" s="74" t="n">
-        <v>11.25</v>
+        <v>11.75</v>
       </c>
     </row>
     <row r="15" ht="26" customHeight="1">
@@ -16427,7 +16433,7 @@
       </c>
       <c r="B18" s="95" t="inlineStr">
         <is>
-          <t>迁移前完整性基准记录</t>
+          <t>迁移前完整性基准记录（模块1·存量历史数据迁移与标准化）</t>
         </is>
       </c>
       <c r="C18" s="32" t="inlineStr">
@@ -16536,7 +16542,7 @@
       </c>
       <c r="B21" s="95" t="inlineStr">
         <is>
-          <t>迁移后完整性比对</t>
+          <t>迁移后完整性比对（模块1·存量历史数据迁移与标准化）</t>
         </is>
       </c>
       <c r="C21" s="32" t="inlineStr">
@@ -16612,7 +16618,7 @@
       </c>
       <c r="B23" s="96" t="inlineStr">
         <is>
-          <t>统一元数据模型</t>
+          <t>统一元数据模型（模块2·实时数据接入与常态化数据治理）</t>
         </is>
       </c>
       <c r="C23" s="32" t="inlineStr">
@@ -16642,7 +16648,7 @@
         <v>2.75</v>
       </c>
       <c r="K23" s="77" t="n">
-        <v>8.5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="24" ht="26" customHeight="1">
@@ -16699,7 +16705,7 @@
         <v>0.25</v>
       </c>
       <c r="F25" s="46" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="G25" s="46" t="n">
         <v>0.5</v>
@@ -16711,7 +16717,7 @@
         <v>0.25</v>
       </c>
       <c r="J25" s="46" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="K25" s="17" t="n"/>
     </row>
@@ -16723,7 +16729,7 @@
       </c>
       <c r="B26" s="96" t="inlineStr">
         <is>
-          <t>来源系统信息绑定</t>
+          <t>来源系统信息绑定（模块2·实时数据接入与常态化数据治理）</t>
         </is>
       </c>
       <c r="C26" s="32" t="inlineStr">
@@ -16832,7 +16838,7 @@
       </c>
       <c r="B29" s="97" t="inlineStr">
         <is>
-          <t>保留期限到期自动删除</t>
+          <t>保留期限到期自动删除（模块3·记录归档与档案全生命周期管理）</t>
         </is>
       </c>
       <c r="C29" s="32" t="inlineStr">
@@ -16864,7 +16870,7 @@
         <v>3</v>
       </c>
       <c r="K29" s="80" t="n">
-        <v>9.5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="30" ht="26" customHeight="1">
@@ -16921,7 +16927,7 @@
         <v>0.25</v>
       </c>
       <c r="F31" s="46" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="G31" s="46" t="n">
         <v>0.5</v>
@@ -16933,7 +16939,7 @@
         <v>0.25</v>
       </c>
       <c r="J31" s="46" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="K31" s="17" t="n"/>
     </row>
@@ -16945,7 +16951,7 @@
       </c>
       <c r="B32" s="97" t="inlineStr">
         <is>
-          <t>Legal Hold 冻结</t>
+          <t>Legal Hold 冻结（模块3·记录归档与档案全生命周期管理）</t>
         </is>
       </c>
       <c r="C32" s="32" t="inlineStr">
@@ -17056,7 +17062,7 @@
       </c>
       <c r="B35" s="98" t="inlineStr">
         <is>
-          <t>数据加密存储</t>
+          <t>数据加密存储（模块4·数据存储与境内数据安全管控）</t>
         </is>
       </c>
       <c r="C35" s="32" t="inlineStr">
@@ -17163,7 +17169,7 @@
       </c>
       <c r="B38" s="98" t="inlineStr">
         <is>
-          <t>密钥管理</t>
+          <t>密钥管理（模块4·数据存储与境内数据安全管控）</t>
         </is>
       </c>
       <c r="C38" s="32" t="inlineStr">
@@ -17274,7 +17280,7 @@
       </c>
       <c r="B41" s="98" t="inlineStr">
         <is>
-          <t>数据备份管理</t>
+          <t>数据备份管理（模块4·数据存储与境内数据安全管控）</t>
         </is>
       </c>
       <c r="C41" s="32" t="inlineStr">
@@ -17385,7 +17391,7 @@
       </c>
       <c r="B44" s="98" t="inlineStr">
         <is>
-          <t>异地灾备</t>
+          <t>异地灾备（模块4·数据存储与境内数据安全管控）</t>
         </is>
       </c>
       <c r="C44" s="32" t="inlineStr">
@@ -17490,9 +17496,9 @@
           <t>F05-01-1</t>
         </is>
       </c>
-      <c r="B47" s="99" t="inlineStr">
-        <is>
-          <t>关键词检索</t>
+      <c r="B47" s="104" t="inlineStr">
+        <is>
+          <t>关键词检索（模块5·档案检索、智能发现与业务利用）</t>
         </is>
       </c>
       <c r="C47" s="32" t="inlineStr">
@@ -17523,8 +17529,8 @@
       <c r="J47" s="46" t="n">
         <v>2.5</v>
       </c>
-      <c r="K47" s="86" t="n">
-        <v>7.25</v>
+      <c r="K47" s="105" t="n">
+        <v>7.75</v>
       </c>
     </row>
     <row r="48" ht="26" customHeight="1">
@@ -17546,7 +17552,7 @@
       </c>
       <c r="E48" s="46" t="n"/>
       <c r="F48" s="46" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="G48" s="46" t="n">
         <v>0.25</v>
@@ -17558,7 +17564,7 @@
         <v>0.25</v>
       </c>
       <c r="J48" s="46" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="K48" s="17" t="n"/>
     </row>
@@ -17601,9 +17607,9 @@
           <t>F05-02-1</t>
         </is>
       </c>
-      <c r="B50" s="99" t="inlineStr">
-        <is>
-          <t>按系统名称检索</t>
+      <c r="B50" s="104" t="inlineStr">
+        <is>
+          <t>按系统名称检索（模块5·档案检索、智能发现与业务利用）</t>
         </is>
       </c>
       <c r="C50" s="32" t="inlineStr">
@@ -17630,7 +17636,7 @@
       <c r="J50" s="46" t="n">
         <v>1.25</v>
       </c>
-      <c r="K50" s="86" t="n">
+      <c r="K50" s="105" t="n">
         <v>2.25</v>
       </c>
     </row>
@@ -17673,9 +17679,9 @@
           <t>F05-03-1</t>
         </is>
       </c>
-      <c r="B52" s="99" t="inlineStr">
-        <is>
-          <t>按业务时间检索</t>
+      <c r="B52" s="104" t="inlineStr">
+        <is>
+          <t>按业务时间检索（模块5·档案检索、智能发现与业务利用）</t>
         </is>
       </c>
       <c r="C52" s="32" t="inlineStr">
@@ -17702,7 +17708,7 @@
       <c r="J52" s="46" t="n">
         <v>1.25</v>
       </c>
-      <c r="K52" s="86" t="n">
+      <c r="K52" s="105" t="n">
         <v>2.25</v>
       </c>
     </row>
@@ -17745,9 +17751,9 @@
           <t>F05-04-1</t>
         </is>
       </c>
-      <c r="B54" s="99" t="inlineStr">
-        <is>
-          <t>检索结果列表展示</t>
+      <c r="B54" s="104" t="inlineStr">
+        <is>
+          <t>检索结果列表展示（模块5·档案检索、智能发现与业务利用）</t>
         </is>
       </c>
       <c r="C54" s="32" t="inlineStr">
@@ -17762,7 +17768,7 @@
       </c>
       <c r="E54" s="46" t="n"/>
       <c r="F54" s="46" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="G54" s="46" t="n"/>
       <c r="H54" s="46" t="n">
@@ -17772,10 +17778,10 @@
         <v>0.25</v>
       </c>
       <c r="J54" s="46" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="K54" s="86" t="n">
-        <v>4</v>
+        <v>2.75</v>
+      </c>
+      <c r="K54" s="105" t="n">
+        <v>4.5</v>
       </c>
     </row>
     <row r="55" ht="26" customHeight="1">
@@ -17819,9 +17825,9 @@
           <t>F05-05-1</t>
         </is>
       </c>
-      <c r="B56" s="99" t="inlineStr">
-        <is>
-          <t>原始文件在线预览</t>
+      <c r="B56" s="104" t="inlineStr">
+        <is>
+          <t>原始文件在线预览（模块5·档案检索、智能发现与业务利用）</t>
         </is>
       </c>
       <c r="C56" s="32" t="inlineStr">
@@ -17848,8 +17854,8 @@
       <c r="J56" s="46" t="n">
         <v>2.25</v>
       </c>
-      <c r="K56" s="86" t="n">
-        <v>6</v>
+      <c r="K56" s="105" t="n">
+        <v>6.5</v>
       </c>
     </row>
     <row r="57" ht="26" customHeight="1">
@@ -17906,7 +17912,7 @@
       </c>
       <c r="E58" s="46" t="n"/>
       <c r="F58" s="46" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="G58" s="46" t="n"/>
       <c r="H58" s="46" t="n">
@@ -17916,7 +17922,7 @@
         <v>0.25</v>
       </c>
       <c r="J58" s="46" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="K58" s="17" t="n"/>
     </row>
@@ -17928,7 +17934,7 @@
       </c>
       <c r="B59" s="100" t="inlineStr">
         <is>
-          <t>归档操作日志记录</t>
+          <t>归档操作日志记录（模块6·合规管控、审计追踪与合规报表）</t>
         </is>
       </c>
       <c r="C59" s="32" t="inlineStr">
@@ -17958,7 +17964,7 @@
         <v>1.25</v>
       </c>
       <c r="K59" s="89" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="60" ht="26" customHeight="1">
@@ -18013,7 +18019,7 @@
       </c>
       <c r="E61" s="46" t="n"/>
       <c r="F61" s="46" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="G61" s="46" t="n">
         <v>0.25</v>
@@ -18025,7 +18031,7 @@
         <v>0.25</v>
       </c>
       <c r="J61" s="46" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="K61" s="17" t="n"/>
     </row>
@@ -18037,7 +18043,7 @@
       </c>
       <c r="B62" s="100" t="inlineStr">
         <is>
-          <t>查询操作日志记录</t>
+          <t>查询操作日志记录（模块6·合规管控、审计追踪与合规报表）</t>
         </is>
       </c>
       <c r="C62" s="32" t="inlineStr">
@@ -18109,7 +18115,7 @@
       </c>
       <c r="B64" s="100" t="inlineStr">
         <is>
-          <t>导出操作日志记录</t>
+          <t>导出操作日志记录（模块6·合规管控、审计追踪与合规报表）</t>
         </is>
       </c>
       <c r="C64" s="32" t="inlineStr">
@@ -18183,7 +18189,7 @@
       </c>
       <c r="B66" s="101" t="inlineStr">
         <is>
-          <t>基础角色权限配置</t>
+          <t>基础角色权限配置（模块8·系统全局治理、运维与监控）</t>
         </is>
       </c>
       <c r="C66" s="32" t="inlineStr">
@@ -18213,7 +18219,7 @@
         <v>2.25</v>
       </c>
       <c r="K66" s="92" t="n">
-        <v>7</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="67" ht="26" customHeight="1">
@@ -18235,7 +18241,7 @@
       </c>
       <c r="E67" s="46" t="n"/>
       <c r="F67" s="46" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="G67" s="46" t="n">
         <v>0.5</v>
@@ -18247,7 +18253,7 @@
         <v>0.25</v>
       </c>
       <c r="J67" s="46" t="n">
-        <v>2.75</v>
+        <v>3.25</v>
       </c>
       <c r="K67" s="17" t="n"/>
     </row>
@@ -18292,7 +18298,7 @@
       </c>
       <c r="B69" s="101" t="inlineStr">
         <is>
-          <t>用户账号管理</t>
+          <t>用户账号管理（模块8·系统全局治理、运维与监控）</t>
         </is>
       </c>
       <c r="C69" s="32" t="inlineStr">
@@ -18370,7 +18376,7 @@
       </c>
       <c r="B71" s="101" t="inlineStr">
         <is>
-          <t>企业SSO集成</t>
+          <t>企业SSO集成（模块8·系统全局治理、运维与监控）</t>
         </is>
       </c>
       <c r="C71" s="32" t="inlineStr">
@@ -18402,7 +18408,7 @@
         <v>2.5</v>
       </c>
       <c r="K71" s="92" t="n">
-        <v>6.75</v>
+        <v>7.25</v>
       </c>
     </row>
     <row r="72" ht="26" customHeight="1">
@@ -18424,7 +18430,7 @@
       </c>
       <c r="E72" s="46" t="n"/>
       <c r="F72" s="46" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="G72" s="46" t="n">
         <v>0.5</v>
@@ -18436,7 +18442,7 @@
         <v>0.25</v>
       </c>
       <c r="J72" s="46" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="K72" s="17" t="n"/>
     </row>
@@ -18481,7 +18487,7 @@
       </c>
       <c r="B74" s="101" t="inlineStr">
         <is>
-          <t>用户身份自动识别与关联</t>
+          <t>用户身份自动识别与关联（模块8·系统全局治理、运维与监控）</t>
         </is>
       </c>
       <c r="C74" s="32" t="inlineStr">
@@ -18557,7 +18563,7 @@
       </c>
       <c r="B76" s="101" t="inlineStr">
         <is>
-          <t>登录状态与异常访问控制</t>
+          <t>登录状态与异常访问控制（模块8·系统全局治理、运维与监控）</t>
         </is>
       </c>
       <c r="C76" s="32" t="inlineStr">
@@ -18625,57 +18631,666 @@
       </c>
       <c r="K77" s="17" t="n"/>
     </row>
-    <row r="78">
-      <c r="A78" s="8" t="inlineStr"/>
-      <c r="B78" s="8" t="inlineStr">
+    <row r="78" ht="26" customHeight="1">
+      <c r="A78" s="15" t="inlineStr">
+        <is>
+          <t>N1-1</t>
+        </is>
+      </c>
+      <c r="B78" s="99" t="inlineStr">
+        <is>
+          <t>【非功能】工程初始化与开发基座</t>
+        </is>
+      </c>
+      <c r="C78" s="32" t="inlineStr">
+        <is>
+          <t>项目初始化</t>
+        </is>
+      </c>
+      <c r="D78" s="32" t="inlineStr">
+        <is>
+          <t>代码仓库/分支策略/开发环境统一/AI工具账号开通</t>
+        </is>
+      </c>
+      <c r="E78" s="46" t="n"/>
+      <c r="F78" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="G78" s="46" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="H78" s="46" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="I78" s="46" t="n"/>
+      <c r="J78" s="46" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="K78" s="86" t="n">
+        <v>10.75</v>
+      </c>
+    </row>
+    <row r="79" ht="26" customHeight="1">
+      <c r="A79" s="15" t="inlineStr">
+        <is>
+          <t>N1-2</t>
+        </is>
+      </c>
+      <c r="B79" s="17" t="n"/>
+      <c r="C79" s="32" t="inlineStr">
+        <is>
+          <t>前端工程初始化</t>
+        </is>
+      </c>
+      <c r="D79" s="32" t="inlineStr">
+        <is>
+          <t>React骨架/路由/布局/组件库/状态管理/构建链</t>
+        </is>
+      </c>
+      <c r="E79" s="46" t="n"/>
+      <c r="F79" s="46" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G79" s="46" t="n"/>
+      <c r="H79" s="46" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="I79" s="46" t="n"/>
+      <c r="J79" s="46" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="K79" s="17" t="n"/>
+    </row>
+    <row r="80" ht="26" customHeight="1">
+      <c r="A80" s="15" t="inlineStr">
+        <is>
+          <t>N1-3</t>
+        </is>
+      </c>
+      <c r="B80" s="17" t="n"/>
+      <c r="C80" s="32" t="inlineStr">
+        <is>
+          <t>后端工程初始化</t>
+        </is>
+      </c>
+      <c r="D80" s="32" t="inlineStr">
+        <is>
+          <t>.NET Clean Architecture/EF Core/Docker Compose本地环境</t>
+        </is>
+      </c>
+      <c r="E80" s="46" t="n"/>
+      <c r="F80" s="46" t="n"/>
+      <c r="G80" s="46" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H80" s="46" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="I80" s="46" t="n"/>
+      <c r="J80" s="46" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="K80" s="17" t="n"/>
+    </row>
+    <row r="81" ht="26" customHeight="1">
+      <c r="A81" s="15" t="inlineStr">
+        <is>
+          <t>N1-4</t>
+        </is>
+      </c>
+      <c r="B81" s="17" t="n"/>
+      <c r="C81" s="32" t="inlineStr">
+        <is>
+          <t>AI开发工具链与编码规范</t>
+        </is>
+      </c>
+      <c r="D81" s="32" t="inlineStr">
+        <is>
+          <t>提示词模板库/人机协作规约/ADR规范</t>
+        </is>
+      </c>
+      <c r="E81" s="46" t="n"/>
+      <c r="F81" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="G81" s="46" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="H81" s="46" t="n"/>
+      <c r="I81" s="46" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="J81" s="46" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="K81" s="17" t="n"/>
+    </row>
+    <row r="82" ht="26" customHeight="1">
+      <c r="A82" s="15" t="inlineStr">
+        <is>
+          <t>N1-5</t>
+        </is>
+      </c>
+      <c r="B82" s="17" t="n"/>
+      <c r="C82" s="32" t="inlineStr">
+        <is>
+          <t>四道安全门禁CI/CD</t>
+        </is>
+      </c>
+      <c r="D82" s="32" t="inlineStr">
+        <is>
+          <t>构建/镜像/SAST·依赖·密钥扫描/越权用例门禁，流水线落地与拦截演示</t>
+        </is>
+      </c>
+      <c r="E82" s="46" t="n"/>
+      <c r="F82" s="46" t="n">
+        <v>3</v>
+      </c>
+      <c r="G82" s="46" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H82" s="46" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I82" s="46" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="J82" s="46" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="K82" s="17" t="n"/>
+    </row>
+    <row r="83" ht="26" customHeight="1">
+      <c r="A83" s="15" t="inlineStr">
+        <is>
+          <t>N2-1</t>
+        </is>
+      </c>
+      <c r="B83" s="99" t="inlineStr">
+        <is>
+          <t>【非功能】代码质量与静态扫描治理</t>
+        </is>
+      </c>
+      <c r="C83" s="32" t="inlineStr">
+        <is>
+          <t>前端ESLint/Prettier规约</t>
+        </is>
+      </c>
+      <c r="D83" s="32" t="inlineStr">
+        <is>
+          <t>规则集接入CI、存量告警清零、格式统一</t>
+        </is>
+      </c>
+      <c r="E83" s="46" t="n"/>
+      <c r="F83" s="46" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G83" s="46" t="n"/>
+      <c r="H83" s="46" t="n"/>
+      <c r="I83" s="46" t="n"/>
+      <c r="J83" s="46" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="K83" s="86" t="n">
+        <v>8.75</v>
+      </c>
+    </row>
+    <row r="84" ht="26" customHeight="1">
+      <c r="A84" s="15" t="inlineStr">
+        <is>
+          <t>N2-2</t>
+        </is>
+      </c>
+      <c r="B84" s="17" t="n"/>
+      <c r="C84" s="32" t="inlineStr">
+        <is>
+          <t>后端SonarLint规约</t>
+        </is>
+      </c>
+      <c r="D84" s="32" t="inlineStr">
+        <is>
+          <t>代码异味/重复块/复杂度阈值治理清零</t>
+        </is>
+      </c>
+      <c r="E84" s="46" t="n"/>
+      <c r="F84" s="46" t="n"/>
+      <c r="G84" s="46" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H84" s="46" t="n"/>
+      <c r="I84" s="46" t="n"/>
+      <c r="J84" s="46" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="K84" s="17" t="n"/>
+    </row>
+    <row r="85" ht="26" customHeight="1">
+      <c r="A85" s="15" t="inlineStr">
+        <is>
+          <t>N2-3</t>
+        </is>
+      </c>
+      <c r="B85" s="17" t="n"/>
+      <c r="C85" s="32" t="inlineStr">
+        <is>
+          <t>SAST安全告警修复</t>
+        </is>
+      </c>
+      <c r="D85" s="32" t="inlineStr">
+        <is>
+          <t>硬编码密钥/注入/越权路径等静态安全缺陷修复</t>
+        </is>
+      </c>
+      <c r="E85" s="46" t="n"/>
+      <c r="F85" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="G85" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="H85" s="46" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="I85" s="46" t="n"/>
+      <c r="J85" s="46" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="K85" s="17" t="n"/>
+    </row>
+    <row r="86" ht="26" customHeight="1">
+      <c r="A86" s="15" t="inlineStr">
+        <is>
+          <t>N2-4</t>
+        </is>
+      </c>
+      <c r="B86" s="17" t="n"/>
+      <c r="C86" s="32" t="inlineStr">
+        <is>
+          <t>依赖漏洞治理（SCA）</t>
+        </is>
+      </c>
+      <c r="D86" s="32" t="inlineStr">
+        <is>
+          <t>依赖版本锁定、漏洞升级、SBOM产出</t>
+        </is>
+      </c>
+      <c r="E86" s="46" t="n"/>
+      <c r="F86" s="46" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G86" s="46" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H86" s="46" t="n"/>
+      <c r="I86" s="46" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="J86" s="46" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="K86" s="17" t="n"/>
+    </row>
+    <row r="87" ht="26" customHeight="1">
+      <c r="A87" s="15" t="inlineStr">
+        <is>
+          <t>N2-5</t>
+        </is>
+      </c>
+      <c r="B87" s="17" t="n"/>
+      <c r="C87" s="32" t="inlineStr">
+        <is>
+          <t>技术债偿还与外部评审落实</t>
+        </is>
+      </c>
+      <c r="D87" s="32" t="inlineStr">
+        <is>
+          <t>每周固定还债窗口、关键模块重构、评审意见闭环</t>
+        </is>
+      </c>
+      <c r="E87" s="46" t="n"/>
+      <c r="F87" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="G87" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="H87" s="46" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="I87" s="46" t="n"/>
+      <c r="J87" s="46" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="K87" s="17" t="n"/>
+    </row>
+    <row r="88" ht="26" customHeight="1">
+      <c r="A88" s="15" t="inlineStr">
+        <is>
+          <t>N3-1</t>
+        </is>
+      </c>
+      <c r="B88" s="99" t="inlineStr">
+        <is>
+          <t>【非功能】全局非功能实现与优化</t>
+        </is>
+      </c>
+      <c r="C88" s="32" t="inlineStr">
+        <is>
+          <t>前端性能优化</t>
+        </is>
+      </c>
+      <c r="D88" s="32" t="inlineStr">
+        <is>
+          <t>懒加载/虚拟滚动/缓存/首屏指标（对照NFR基线）</t>
+        </is>
+      </c>
+      <c r="E88" s="46" t="n"/>
+      <c r="F88" s="46" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G88" s="46" t="n"/>
+      <c r="H88" s="46" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I88" s="46" t="n"/>
+      <c r="J88" s="46" t="n">
+        <v>2</v>
+      </c>
+      <c r="K88" s="86" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="89" ht="26" customHeight="1">
+      <c r="A89" s="15" t="inlineStr">
+        <is>
+          <t>N3-2</t>
+        </is>
+      </c>
+      <c r="B89" s="17" t="n"/>
+      <c r="C89" s="32" t="inlineStr">
+        <is>
+          <t>查询与数据性能</t>
+        </is>
+      </c>
+      <c r="D89" s="32" t="inlineStr">
+        <is>
+          <t>分区裁剪/Z-Order/Compaction/小文件治理</t>
+        </is>
+      </c>
+      <c r="E89" s="46" t="n"/>
+      <c r="F89" s="46" t="n"/>
+      <c r="G89" s="46" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H89" s="46" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I89" s="46" t="n"/>
+      <c r="J89" s="46" t="n">
+        <v>2</v>
+      </c>
+      <c r="K89" s="17" t="n"/>
+    </row>
+    <row r="90" ht="26" customHeight="1">
+      <c r="A90" s="15" t="inlineStr">
+        <is>
+          <t>N3-3</t>
+        </is>
+      </c>
+      <c r="B90" s="17" t="n"/>
+      <c r="C90" s="32" t="inlineStr">
+        <is>
+          <t>统一鉴权与数据掩码中间件</t>
+        </is>
+      </c>
+      <c r="D90" s="32" t="inlineStr">
+        <is>
+          <t>菜单/API/行级三层校验、掩码旁路防护</t>
+        </is>
+      </c>
+      <c r="E90" s="46" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="F90" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="G90" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="H90" s="46" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="I90" s="46" t="n"/>
+      <c r="J90" s="46" t="n">
+        <v>3</v>
+      </c>
+      <c r="K90" s="17" t="n"/>
+    </row>
+    <row r="91" ht="26" customHeight="1">
+      <c r="A91" s="15" t="inlineStr">
+        <is>
+          <t>N3-4</t>
+        </is>
+      </c>
+      <c r="B91" s="17" t="n"/>
+      <c r="C91" s="32" t="inlineStr">
+        <is>
+          <t>可观测性（日志/监控/告警）</t>
+        </is>
+      </c>
+      <c r="D91" s="32" t="inlineStr">
+        <is>
+          <t>应用日志规范、作业监控、异常告警通道</t>
+        </is>
+      </c>
+      <c r="E91" s="46" t="n"/>
+      <c r="F91" s="46" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G91" s="46" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H91" s="46" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="I91" s="46" t="n"/>
+      <c r="J91" s="46" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="K91" s="17" t="n"/>
+    </row>
+    <row r="92" ht="26" customHeight="1">
+      <c r="A92" s="15" t="inlineStr">
+        <is>
+          <t>N3-5</t>
+        </is>
+      </c>
+      <c r="B92" s="17" t="n"/>
+      <c r="C92" s="32" t="inlineStr">
+        <is>
+          <t>容量与增长验证</t>
+        </is>
+      </c>
+      <c r="D92" s="32" t="inlineStr">
+        <is>
+          <t>600~800表规模扩容压测与容量报告</t>
+        </is>
+      </c>
+      <c r="E92" s="46" t="n"/>
+      <c r="F92" s="46" t="n"/>
+      <c r="G92" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="H92" s="46" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I92" s="46" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="J92" s="46" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="K92" s="17" t="n"/>
+    </row>
+    <row r="93" ht="26" customHeight="1">
+      <c r="A93" s="15" t="inlineStr">
+        <is>
+          <t>N4-1</t>
+        </is>
+      </c>
+      <c r="B93" s="99" t="inlineStr">
+        <is>
+          <t>【非功能】部署与运维支撑</t>
+        </is>
+      </c>
+      <c r="C93" s="32" t="inlineStr">
+        <is>
+          <t>Helm发布包与values</t>
+        </is>
+      </c>
+      <c r="D93" s="32" t="inlineStr">
+        <is>
+          <t>生产values/镜像标签策略/发布Runbook</t>
+        </is>
+      </c>
+      <c r="E93" s="46" t="n"/>
+      <c r="F93" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="G93" s="46" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="H93" s="46" t="n"/>
+      <c r="I93" s="46" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="J93" s="46" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="K93" s="86" t="n">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="94" ht="26" customHeight="1">
+      <c r="A94" s="15" t="inlineStr">
+        <is>
+          <t>N4-2</t>
+        </is>
+      </c>
+      <c r="B94" s="17" t="n"/>
+      <c r="C94" s="32" t="inlineStr">
+        <is>
+          <t>部署预演与回退预案</t>
+        </is>
+      </c>
+      <c r="D94" s="32" t="inlineStr">
+        <is>
+          <t>Staging完整演练、回退验证</t>
+        </is>
+      </c>
+      <c r="E94" s="46" t="n"/>
+      <c r="F94" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="G94" s="46" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H94" s="46" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="I94" s="46" t="n"/>
+      <c r="J94" s="46" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="K94" s="17" t="n"/>
+    </row>
+    <row r="95" ht="26" customHeight="1">
+      <c r="A95" s="15" t="inlineStr">
+        <is>
+          <t>N4-3</t>
+        </is>
+      </c>
+      <c r="B95" s="17" t="n"/>
+      <c r="C95" s="32" t="inlineStr">
+        <is>
+          <t>上线值守与运维交接</t>
+        </is>
+      </c>
+      <c r="D95" s="32" t="inlineStr">
+        <is>
+          <t>上线窗口值守、运维交接与培训材料</t>
+        </is>
+      </c>
+      <c r="E95" s="46" t="n"/>
+      <c r="F95" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="G95" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="H95" s="46" t="n"/>
+      <c r="I95" s="46" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="J95" s="46" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="K95" s="17" t="n"/>
+    </row>
+    <row r="96">
+      <c r="A96" s="8" t="inlineStr"/>
+      <c r="B96" s="8" t="inlineStr">
         <is>
           <t>总计</t>
         </is>
       </c>
-      <c r="C78" s="93" t="inlineStr">
-        <is>
-          <t>26项功能 × 75个子任务</t>
-        </is>
-      </c>
-      <c r="D78" s="93" t="inlineStr">
-        <is>
-          <t>独立直估（不含项目初始化/架构设计/集成/UAT/上线/PM等公共工作）</t>
-        </is>
-      </c>
-      <c r="E78" s="44" t="n">
-        <v>12.75</v>
-      </c>
-      <c r="F78" s="44" t="n">
-        <v>36.75</v>
-      </c>
-      <c r="G78" s="44" t="n">
-        <v>62</v>
-      </c>
-      <c r="H78" s="44" t="n">
-        <v>35.75</v>
-      </c>
-      <c r="I78" s="44" t="n">
-        <v>20</v>
-      </c>
-      <c r="J78" s="44" t="n">
-        <v>167.25</v>
-      </c>
-      <c r="K78" s="8" t="inlineStr"/>
-    </row>
-    <row r="80" ht="52" customHeight="1">
-      <c r="A80" s="94" t="inlineStr">
-        <is>
-          <t>对照说明（两个口径）：① 本表为子任务级独立直估，合计 167.25 人天（BA 12.75 / Wade 36.75 / DevB 62.0 / 测试 35.75 / SLC 20.0），其中「存储落地Iceberg/UC」「元数据驱动」「RBAC」等设计实现类子任务与计划公共行（架构与非功能设计等）存在重叠，且未假设跨功能复用（同一界面/中间件多处计价）。② 排期计划（WBS分解/功能视角分解）中：26项功能直接分摊仅 54.5 人天（大量开发工作量按阶段放在架构设计/集成/专项等公共行，公共合计 130.5 人天），总投入185人天。结论：功能直估 167.25 人天已达计划总投入的 90%，而计划中还有需求8.5/初始化9/PM15及集成·UAT·上线等纯公共工作未包含在本直估内——按传统粒度估算，3人×3个月偏紧，需依赖AI Native复用与生成提效吸收约50人天量级缺口，建议将本表作为功能规模基线并纳入风险跟踪。</t>
+      <c r="C96" s="93" t="inlineStr">
+        <is>
+          <t>26项功能×75子任务 + 非功能工程×18子任务</t>
+        </is>
+      </c>
+      <c r="D96" s="93" t="inlineStr">
+        <is>
+          <t>独立直估（另含少量需求/PM等工作未列入本表）</t>
+        </is>
+      </c>
+      <c r="E96" s="44" t="n">
+        <v>13</v>
+      </c>
+      <c r="F96" s="44" t="n">
+        <v>60.25</v>
+      </c>
+      <c r="G96" s="44" t="n">
+        <v>75.25</v>
+      </c>
+      <c r="H96" s="44" t="n">
+        <v>40.25</v>
+      </c>
+      <c r="I96" s="44" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="J96" s="44" t="n">
+        <v>210.25</v>
+      </c>
+      <c r="K96" s="8" t="inlineStr"/>
+    </row>
+    <row r="98" ht="56" customHeight="1">
+      <c r="A98" s="94" t="inlineStr">
+        <is>
+          <t>对照说明（三个口径）：① 功能直估 174.25 人天（BA 12.75 / Wade 43.75 / DevB 62.0 / 测试 35.75 / SLC 20.0）——本版已按配置界面/动态表单复杂度上调前端工作量；② 非功能与工程支撑直估 36.0 人天（N1初始化与基座/N2 ESLint·SonarLint·SAST·依赖治理/N3性能·鉴权掩码·可观测·容量/N4部署运维）——此前缺失，现已补齐；③ 合计 210.25 人天 vs 排期计划185人天：Wade 60.25≈计划60 ✓；DevB 75.25超计划60约 15.25 人天，数据/ETL侧为最大风险口，需靠AI生成ETL与SQL提效吸收；总缺口约 25.25 人天（12%），建议以本表为规模基线纳入风险跟踪，必要时启用备用赶工日（9/20、10/10）。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="54">
+  <mergeCells count="62">
     <mergeCell ref="K54:K55"/>
+    <mergeCell ref="B88:B92"/>
     <mergeCell ref="K76:K77"/>
     <mergeCell ref="B62:B63"/>
     <mergeCell ref="K21:K22"/>
+    <mergeCell ref="B78:B82"/>
     <mergeCell ref="B52:B53"/>
+    <mergeCell ref="A98:K98"/>
     <mergeCell ref="K38:K40"/>
     <mergeCell ref="A1:K1"/>
     <mergeCell ref="K23:K25"/>
@@ -18683,6 +19298,7 @@
     <mergeCell ref="B14:B17"/>
     <mergeCell ref="K66:K68"/>
     <mergeCell ref="B35:B37"/>
+    <mergeCell ref="B83:B87"/>
     <mergeCell ref="B26:B28"/>
     <mergeCell ref="B66:B68"/>
     <mergeCell ref="B69:B70"/>
@@ -18690,12 +19306,15 @@
     <mergeCell ref="K3:K9"/>
     <mergeCell ref="B41:B43"/>
     <mergeCell ref="B47:B49"/>
+    <mergeCell ref="B93:B95"/>
     <mergeCell ref="B32:B34"/>
-    <mergeCell ref="A80:K80"/>
+    <mergeCell ref="K93:K95"/>
     <mergeCell ref="B10:B13"/>
     <mergeCell ref="B59:B61"/>
     <mergeCell ref="K18:K20"/>
+    <mergeCell ref="K78:K82"/>
     <mergeCell ref="K52:K53"/>
+    <mergeCell ref="K83:K87"/>
     <mergeCell ref="B74:B75"/>
     <mergeCell ref="B64:B65"/>
     <mergeCell ref="K44:K46"/>
@@ -18716,6 +19335,7 @@
     <mergeCell ref="K10:K13"/>
     <mergeCell ref="K26:K28"/>
     <mergeCell ref="B76:B77"/>
+    <mergeCell ref="K88:K92"/>
     <mergeCell ref="K71:K73"/>
     <mergeCell ref="B44:B46"/>
     <mergeCell ref="K47:K49"/>

--- a/RIMS项目WBS工作分解_AI Native版.xlsx
+++ b/RIMS项目WBS工作分解_AI Native版.xlsx
@@ -232,7 +232,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="106">
+  <cellXfs count="114">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -512,6 +512,30 @@
     </xf>
     <xf numFmtId="165" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1274,7 +1298,7 @@
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>子任务级直估：26项功能×75子任务 + 非功能与工程支撑×18子任务（N1框架初始化与基座/N2 ESLint·SonarLint·SAST代码质量治理/N3性能·鉴权·可观测·容量/N4部署运维），按BA/开发A/开发B/测试/SLC文档独立估人天；功能/组名称与小计为纵向合并单元格；底部附与计划口径对照</t>
+          <t>子任务级直估：模块→功能→子任务三层结构（模块列与功能列均为纵向合并单元格），26项功能×75子任务 + 非功能与工程支撑×18子任务（N1框架初始化与基座/N2 ESLint·SonarLint·SAST代码质量治理/N3性能·鉴权·可观测·容量/N4部署运维），按BA/开发A/开发B/测试/SLC文档独立估人天；底部附与计划口径对照</t>
         </is>
       </c>
     </row>
@@ -15792,26 +15816,27 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K98"/>
+  <dimension ref="A1:L98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="24" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
-    <col width="8" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="17" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="8" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
     <col width="8" customWidth="1" min="9" max="9"/>
     <col width="8" customWidth="1" min="10" max="10"/>
-    <col width="9" customWidth="1" min="11" max="11"/>
+    <col width="8" customWidth="1" min="11" max="11"/>
+    <col width="9" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>功能拆解估算（子任务级直估）：26项功能×75子任务 + 非功能与工程支撑×18子任务 — 独立估算，不锚定排期185人天</t>
+          <t>功能拆解估算（子任务级直估）：模块→功能→子任务三层结构，26项功能×75子任务 + 非功能与工程支撑×18子任务 — 独立估算，不锚定排期185人天</t>
         </is>
       </c>
     </row>
@@ -15823,50 +15848,55 @@
       </c>
       <c r="B2" s="7" t="inlineStr">
         <is>
+          <t>模块</t>
+        </is>
+      </c>
+      <c r="C2" s="7" t="inlineStr">
+        <is>
           <t>功能/组名称</t>
         </is>
       </c>
-      <c r="C2" s="7" t="inlineStr">
+      <c r="D2" s="7" t="inlineStr">
         <is>
           <t>子任务/工作包</t>
         </is>
       </c>
-      <c r="D2" s="7" t="inlineStr">
+      <c r="E2" s="7" t="inlineStr">
         <is>
           <t>工作内容要点</t>
         </is>
       </c>
-      <c r="E2" s="7" t="inlineStr">
+      <c r="F2" s="7" t="inlineStr">
         <is>
           <t>BA人天</t>
         </is>
       </c>
-      <c r="F2" s="7" t="inlineStr">
+      <c r="G2" s="7" t="inlineStr">
         <is>
           <t>开发A·Wade</t>
         </is>
       </c>
-      <c r="G2" s="7" t="inlineStr">
+      <c r="H2" s="7" t="inlineStr">
         <is>
           <t>开发B·DevB</t>
         </is>
       </c>
-      <c r="H2" s="7" t="inlineStr">
+      <c r="I2" s="7" t="inlineStr">
         <is>
           <t>测试人天</t>
         </is>
       </c>
-      <c r="I2" s="7" t="inlineStr">
+      <c r="J2" s="7" t="inlineStr">
         <is>
           <t>SLC文档</t>
         </is>
       </c>
-      <c r="J2" s="7" t="inlineStr">
+      <c r="K2" s="7" t="inlineStr">
         <is>
           <t>小计</t>
         </is>
       </c>
-      <c r="K2" s="7" t="inlineStr">
+      <c r="L2" s="7" t="inlineStr">
         <is>
           <t>功能/组小计</t>
         </is>
@@ -15878,40 +15908,45 @@
           <t>F01-01-1</t>
         </is>
       </c>
-      <c r="B3" s="95" t="inlineStr">
-        <is>
-          <t>结构化历史数据批量导入（模块1·存量历史数据迁移与标准化）</t>
-        </is>
-      </c>
-      <c r="C3" s="32" t="inlineStr">
+      <c r="B3" s="106" t="inlineStr">
+        <is>
+          <t>模块1·存量历史数据迁移与标准化</t>
+        </is>
+      </c>
+      <c r="C3" s="95" t="inlineStr">
+        <is>
+          <t>结构化历史数据批量导入</t>
+        </is>
+      </c>
+      <c r="D3" s="32" t="inlineStr">
         <is>
           <t>原系统基本信息录入</t>
         </is>
       </c>
-      <c r="D3" s="32" t="inlineStr">
+      <c r="E3" s="32" t="inlineStr">
         <is>
           <t>来源系统档案：系统编码/名称/业务域/责任人/退役批次；录入与维护界面+存储API</t>
         </is>
       </c>
-      <c r="E3" s="46" t="n">
+      <c r="F3" s="46" t="n">
         <v>0.5</v>
       </c>
-      <c r="F3" s="46" t="n">
+      <c r="G3" s="46" t="n">
         <v>1.5</v>
-      </c>
-      <c r="G3" s="46" t="n">
-        <v>0.5</v>
       </c>
       <c r="H3" s="46" t="n">
         <v>0.5</v>
       </c>
       <c r="I3" s="46" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J3" s="46" t="n">
         <v>0.25</v>
       </c>
-      <c r="J3" s="46" t="n">
+      <c r="K3" s="46" t="n">
         <v>3.25</v>
       </c>
-      <c r="K3" s="74" t="n">
+      <c r="L3" s="74" t="n">
         <v>22.75</v>
       </c>
     </row>
@@ -15921,36 +15956,37 @@
           <t>F01-01-2</t>
         </is>
       </c>
-      <c r="B4" s="17" t="n"/>
-      <c r="C4" s="32" t="inlineStr">
+      <c r="B4" s="102" t="n"/>
+      <c r="C4" s="17" t="n"/>
+      <c r="D4" s="32" t="inlineStr">
         <is>
           <t>源库DB连接配置</t>
         </is>
       </c>
-      <c r="D4" s="32" t="inlineStr">
+      <c r="E4" s="32" t="inlineStr">
         <is>
           <t>DB类型/连接串录入，账号密码Key Vault加密存储，连通性测试</t>
         </is>
       </c>
-      <c r="E4" s="46" t="n">
+      <c r="F4" s="46" t="n">
         <v>0.25</v>
       </c>
-      <c r="F4" s="46" t="n">
+      <c r="G4" s="46" t="n">
         <v>1.5</v>
       </c>
-      <c r="G4" s="46" t="n">
+      <c r="H4" s="46" t="n">
         <v>1</v>
       </c>
-      <c r="H4" s="46" t="n">
+      <c r="I4" s="46" t="n">
         <v>0.5</v>
       </c>
-      <c r="I4" s="46" t="n">
+      <c r="J4" s="46" t="n">
         <v>0.25</v>
       </c>
-      <c r="J4" s="46" t="n">
+      <c r="K4" s="46" t="n">
         <v>3.5</v>
       </c>
-      <c r="K4" s="17" t="n"/>
+      <c r="L4" s="17" t="n"/>
     </row>
     <row r="5" ht="26" customHeight="1">
       <c r="A5" s="15" t="inlineStr">
@@ -15958,36 +15994,37 @@
           <t>F01-01-3</t>
         </is>
       </c>
-      <c r="B5" s="17" t="n"/>
-      <c r="C5" s="32" t="inlineStr">
+      <c r="B5" s="102" t="n"/>
+      <c r="C5" s="17" t="n"/>
+      <c r="D5" s="32" t="inlineStr">
         <is>
           <t>同步表勾选</t>
         </is>
       </c>
-      <c r="D5" s="32" t="inlineStr">
+      <c r="E5" s="32" t="inlineStr">
         <is>
           <t>拉取源表清单、勾选同步范围、数据量预估与全选过滤</t>
         </is>
       </c>
-      <c r="E5" s="46" t="n">
+      <c r="F5" s="46" t="n">
         <v>0.25</v>
       </c>
-      <c r="F5" s="46" t="n">
+      <c r="G5" s="46" t="n">
         <v>1.5</v>
       </c>
-      <c r="G5" s="46" t="n">
+      <c r="H5" s="46" t="n">
         <v>1</v>
       </c>
-      <c r="H5" s="46" t="n">
+      <c r="I5" s="46" t="n">
         <v>0.5</v>
       </c>
-      <c r="I5" s="46" t="n">
+      <c r="J5" s="46" t="n">
         <v>0.25</v>
       </c>
-      <c r="J5" s="46" t="n">
+      <c r="K5" s="46" t="n">
         <v>3.5</v>
       </c>
-      <c r="K5" s="17" t="n"/>
+      <c r="L5" s="17" t="n"/>
     </row>
     <row r="6" ht="26" customHeight="1">
       <c r="A6" s="15" t="inlineStr">
@@ -15995,36 +16032,37 @@
           <t>F01-01-4</t>
         </is>
       </c>
-      <c r="B6" s="17" t="n"/>
-      <c r="C6" s="32" t="inlineStr">
+      <c r="B6" s="102" t="n"/>
+      <c r="C6" s="17" t="n"/>
+      <c r="D6" s="32" t="inlineStr">
         <is>
           <t>保留期限与迁移参数配置</t>
         </is>
       </c>
-      <c r="D6" s="32" t="inlineStr">
+      <c r="E6" s="32" t="inlineStr">
         <is>
           <t>保留策略绑定、迁移批次命名、并发/限速参数</t>
         </is>
       </c>
-      <c r="E6" s="46" t="n">
+      <c r="F6" s="46" t="n">
         <v>0.5</v>
       </c>
-      <c r="F6" s="46" t="n">
+      <c r="G6" s="46" t="n">
         <v>1</v>
       </c>
-      <c r="G6" s="46" t="n">
+      <c r="H6" s="46" t="n">
         <v>0.5</v>
-      </c>
-      <c r="H6" s="46" t="n">
-        <v>0.25</v>
       </c>
       <c r="I6" s="46" t="n">
         <v>0.25</v>
       </c>
       <c r="J6" s="46" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="K6" s="46" t="n">
         <v>2.5</v>
       </c>
-      <c r="K6" s="17" t="n"/>
+      <c r="L6" s="17" t="n"/>
     </row>
     <row r="7" ht="26" customHeight="1">
       <c r="A7" s="15" t="inlineStr">
@@ -16032,34 +16070,35 @@
           <t>F01-01-5</t>
         </is>
       </c>
-      <c r="B7" s="17" t="n"/>
-      <c r="C7" s="32" t="inlineStr">
+      <c r="B7" s="102" t="n"/>
+      <c r="C7" s="17" t="n"/>
+      <c r="D7" s="32" t="inlineStr">
         <is>
           <t>存储落地实现（Iceberg/UC）</t>
         </is>
       </c>
-      <c r="D7" s="32" t="inlineStr">
+      <c r="E7" s="32" t="inlineStr">
         <is>
           <t>磁盘目录布局、Iceberg表属性与分区策略、UC目录/Schema/授权配置化</t>
         </is>
       </c>
-      <c r="E7" s="46" t="n">
+      <c r="F7" s="46" t="n">
         <v>0.25</v>
       </c>
-      <c r="F7" s="46" t="n"/>
-      <c r="G7" s="46" t="n">
+      <c r="G7" s="46" t="n"/>
+      <c r="H7" s="46" t="n">
         <v>2</v>
-      </c>
-      <c r="H7" s="46" t="n">
-        <v>0.5</v>
       </c>
       <c r="I7" s="46" t="n">
         <v>0.5</v>
       </c>
       <c r="J7" s="46" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K7" s="46" t="n">
         <v>3.25</v>
       </c>
-      <c r="K7" s="17" t="n"/>
+      <c r="L7" s="17" t="n"/>
     </row>
     <row r="8" ht="26" customHeight="1">
       <c r="A8" s="15" t="inlineStr">
@@ -16067,34 +16106,35 @@
           <t>F01-01-6</t>
         </is>
       </c>
-      <c r="B8" s="17" t="n"/>
-      <c r="C8" s="32" t="inlineStr">
+      <c r="B8" s="102" t="n"/>
+      <c r="C8" s="17" t="n"/>
+      <c r="D8" s="32" t="inlineStr">
         <is>
           <t>SeaTunnel批量导入作业</t>
         </is>
       </c>
-      <c r="D8" s="32" t="inlineStr">
+      <c r="E8" s="32" t="inlineStr">
         <is>
           <t>作业配置生成器、分片/断点续传/限速执行</t>
         </is>
       </c>
-      <c r="E8" s="46" t="n"/>
-      <c r="F8" s="46" t="n">
+      <c r="F8" s="46" t="n"/>
+      <c r="G8" s="46" t="n">
         <v>0.5</v>
       </c>
-      <c r="G8" s="46" t="n">
+      <c r="H8" s="46" t="n">
         <v>2</v>
       </c>
-      <c r="H8" s="46" t="n">
+      <c r="I8" s="46" t="n">
         <v>1</v>
       </c>
-      <c r="I8" s="46" t="n">
+      <c r="J8" s="46" t="n">
         <v>0.5</v>
       </c>
-      <c r="J8" s="46" t="n">
+      <c r="K8" s="46" t="n">
         <v>4</v>
       </c>
-      <c r="K8" s="17" t="n"/>
+      <c r="L8" s="17" t="n"/>
     </row>
     <row r="9" ht="26" customHeight="1">
       <c r="A9" s="15" t="inlineStr">
@@ -16102,34 +16142,35 @@
           <t>F01-01-7</t>
         </is>
       </c>
-      <c r="B9" s="17" t="n"/>
-      <c r="C9" s="32" t="inlineStr">
+      <c r="B9" s="102" t="n"/>
+      <c r="C9" s="17" t="n"/>
+      <c r="D9" s="32" t="inlineStr">
         <is>
           <t>导入执行与监控</t>
         </is>
       </c>
-      <c r="D9" s="32" t="inlineStr">
+      <c r="E9" s="32" t="inlineStr">
         <is>
           <t>任务状态/进度/失败重试/日志查看</t>
         </is>
       </c>
-      <c r="E9" s="46" t="n"/>
-      <c r="F9" s="46" t="n">
+      <c r="F9" s="46" t="n"/>
+      <c r="G9" s="46" t="n">
         <v>1.5</v>
-      </c>
-      <c r="G9" s="46" t="n">
-        <v>0.5</v>
       </c>
       <c r="H9" s="46" t="n">
         <v>0.5</v>
       </c>
       <c r="I9" s="46" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J9" s="46" t="n">
         <v>0.25</v>
       </c>
-      <c r="J9" s="46" t="n">
+      <c r="K9" s="46" t="n">
         <v>2.75</v>
       </c>
-      <c r="K9" s="17" t="n"/>
+      <c r="L9" s="17" t="n"/>
     </row>
     <row r="10" ht="26" customHeight="1">
       <c r="A10" s="15" t="inlineStr">
@@ -16137,40 +16178,41 @@
           <t>F01-02-1</t>
         </is>
       </c>
-      <c r="B10" s="95" t="inlineStr">
-        <is>
-          <t>非结构化文件及离线包批量导入（模块1·存量历史数据迁移与标准化）</t>
-        </is>
-      </c>
-      <c r="C10" s="32" t="inlineStr">
+      <c r="B10" s="102" t="n"/>
+      <c r="C10" s="95" t="inlineStr">
+        <is>
+          <t>非结构化文件及离线包批量导入</t>
+        </is>
+      </c>
+      <c r="D10" s="32" t="inlineStr">
         <is>
           <t>文件来源登记与上传通道</t>
         </is>
       </c>
-      <c r="D10" s="32" t="inlineStr">
+      <c r="E10" s="32" t="inlineStr">
         <is>
           <t>在线上传/共享路径挂载/离线介质登记</t>
         </is>
       </c>
-      <c r="E10" s="46" t="n">
+      <c r="F10" s="46" t="n">
         <v>0.25</v>
       </c>
-      <c r="F10" s="46" t="n">
+      <c r="G10" s="46" t="n">
         <v>2</v>
       </c>
-      <c r="G10" s="46" t="n">
+      <c r="H10" s="46" t="n">
         <v>1</v>
       </c>
-      <c r="H10" s="46" t="n">
+      <c r="I10" s="46" t="n">
         <v>0.5</v>
       </c>
-      <c r="I10" s="46" t="n">
+      <c r="J10" s="46" t="n">
         <v>0.25</v>
       </c>
-      <c r="J10" s="46" t="n">
+      <c r="K10" s="46" t="n">
         <v>4</v>
       </c>
-      <c r="K10" s="74" t="n">
+      <c r="L10" s="74" t="n">
         <v>13.25</v>
       </c>
     </row>
@@ -16180,34 +16222,35 @@
           <t>F01-02-2</t>
         </is>
       </c>
-      <c r="B11" s="17" t="n"/>
-      <c r="C11" s="32" t="inlineStr">
+      <c r="B11" s="102" t="n"/>
+      <c r="C11" s="17" t="n"/>
+      <c r="D11" s="32" t="inlineStr">
         <is>
           <t>大文件分片上传与断点续传</t>
         </is>
       </c>
-      <c r="D11" s="32" t="inlineStr">
+      <c r="E11" s="32" t="inlineStr">
         <is>
           <t>前端分片上传、后端合并与校验</t>
         </is>
       </c>
-      <c r="E11" s="46" t="n"/>
-      <c r="F11" s="46" t="n">
-        <v>1.5</v>
-      </c>
+      <c r="F11" s="46" t="n"/>
       <c r="G11" s="46" t="n">
         <v>1.5</v>
       </c>
       <c r="H11" s="46" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I11" s="46" t="n">
         <v>1</v>
       </c>
-      <c r="I11" s="46" t="n">
+      <c r="J11" s="46" t="n">
         <v>0.25</v>
       </c>
-      <c r="J11" s="46" t="n">
+      <c r="K11" s="46" t="n">
         <v>4.25</v>
       </c>
-      <c r="K11" s="17" t="n"/>
+      <c r="L11" s="17" t="n"/>
     </row>
     <row r="12" ht="26" customHeight="1">
       <c r="A12" s="15" t="inlineStr">
@@ -16215,32 +16258,33 @@
           <t>F01-02-3</t>
         </is>
       </c>
-      <c r="B12" s="17" t="n"/>
-      <c r="C12" s="32" t="inlineStr">
+      <c r="B12" s="102" t="n"/>
+      <c r="C12" s="17" t="n"/>
+      <c r="D12" s="32" t="inlineStr">
         <is>
           <t>文件包解析</t>
         </is>
       </c>
-      <c r="D12" s="32" t="inlineStr">
+      <c r="E12" s="32" t="inlineStr">
         <is>
           <t>zip/tar/数据库备份包识别与展开、原始属性保留</t>
         </is>
       </c>
-      <c r="E12" s="46" t="n"/>
       <c r="F12" s="46" t="n"/>
-      <c r="G12" s="46" t="n">
+      <c r="G12" s="46" t="n"/>
+      <c r="H12" s="46" t="n">
         <v>1.5</v>
       </c>
-      <c r="H12" s="46" t="n">
+      <c r="I12" s="46" t="n">
         <v>0.75</v>
       </c>
-      <c r="I12" s="46" t="n">
+      <c r="J12" s="46" t="n">
         <v>0.25</v>
       </c>
-      <c r="J12" s="46" t="n">
+      <c r="K12" s="46" t="n">
         <v>2.5</v>
       </c>
-      <c r="K12" s="17" t="n"/>
+      <c r="L12" s="17" t="n"/>
     </row>
     <row r="13" ht="26" customHeight="1">
       <c r="A13" s="15" t="inlineStr">
@@ -16248,34 +16292,35 @@
           <t>F01-02-4</t>
         </is>
       </c>
-      <c r="B13" s="17" t="n"/>
-      <c r="C13" s="32" t="inlineStr">
+      <c r="B13" s="102" t="n"/>
+      <c r="C13" s="17" t="n"/>
+      <c r="D13" s="32" t="inlineStr">
         <is>
           <t>附件元数据与Blob存储布局</t>
         </is>
       </c>
-      <c r="D13" s="32" t="inlineStr">
+      <c r="E13" s="32" t="inlineStr">
         <is>
           <t>附件索引表、路径规范、与结构化记录关联</t>
         </is>
       </c>
-      <c r="E13" s="46" t="n">
+      <c r="F13" s="46" t="n">
         <v>0.25</v>
       </c>
-      <c r="F13" s="46" t="n"/>
-      <c r="G13" s="46" t="n">
+      <c r="G13" s="46" t="n"/>
+      <c r="H13" s="46" t="n">
         <v>1.5</v>
       </c>
-      <c r="H13" s="46" t="n">
+      <c r="I13" s="46" t="n">
         <v>0.5</v>
       </c>
-      <c r="I13" s="46" t="n">
+      <c r="J13" s="46" t="n">
         <v>0.25</v>
       </c>
-      <c r="J13" s="46" t="n">
+      <c r="K13" s="46" t="n">
         <v>2.5</v>
       </c>
-      <c r="K13" s="17" t="n"/>
+      <c r="L13" s="17" t="n"/>
     </row>
     <row r="14" ht="26" customHeight="1">
       <c r="A14" s="15" t="inlineStr">
@@ -16283,40 +16328,41 @@
           <t>F01-03-1</t>
         </is>
       </c>
-      <c r="B14" s="95" t="inlineStr">
-        <is>
-          <t>数据导入规则配置（模块1·存量历史数据迁移与标准化）</t>
-        </is>
-      </c>
-      <c r="C14" s="32" t="inlineStr">
+      <c r="B14" s="102" t="n"/>
+      <c r="C14" s="95" t="inlineStr">
+        <is>
+          <t>数据导入规则配置</t>
+        </is>
+      </c>
+      <c r="D14" s="32" t="inlineStr">
         <is>
           <t>字段映射规则配置</t>
         </is>
       </c>
-      <c r="D14" s="32" t="inlineStr">
+      <c r="E14" s="32" t="inlineStr">
         <is>
           <t>源字段→标准字段映射界面、自动映射建议</t>
         </is>
       </c>
-      <c r="E14" s="46" t="n">
+      <c r="F14" s="46" t="n">
         <v>0.5</v>
       </c>
-      <c r="F14" s="46" t="n">
+      <c r="G14" s="46" t="n">
         <v>2</v>
-      </c>
-      <c r="G14" s="46" t="n">
-        <v>0.5</v>
       </c>
       <c r="H14" s="46" t="n">
         <v>0.5</v>
       </c>
       <c r="I14" s="46" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J14" s="46" t="n">
         <v>0.25</v>
       </c>
-      <c r="J14" s="46" t="n">
+      <c r="K14" s="46" t="n">
         <v>3.75</v>
       </c>
-      <c r="K14" s="74" t="n">
+      <c r="L14" s="74" t="n">
         <v>11.75</v>
       </c>
     </row>
@@ -16326,34 +16372,35 @@
           <t>F01-03-2</t>
         </is>
       </c>
-      <c r="B15" s="17" t="n"/>
-      <c r="C15" s="32" t="inlineStr">
+      <c r="B15" s="102" t="n"/>
+      <c r="C15" s="17" t="n"/>
+      <c r="D15" s="32" t="inlineStr">
         <is>
           <t>格式转换与清洗规则</t>
         </is>
       </c>
-      <c r="D15" s="32" t="inlineStr">
+      <c r="E15" s="32" t="inlineStr">
         <is>
           <t>类型转换/编码/默认值/脏数据处理策略</t>
         </is>
       </c>
-      <c r="E15" s="46" t="n">
+      <c r="F15" s="46" t="n">
         <v>0.5</v>
       </c>
-      <c r="F15" s="46" t="n"/>
-      <c r="G15" s="46" t="n">
+      <c r="G15" s="46" t="n"/>
+      <c r="H15" s="46" t="n">
         <v>1.5</v>
       </c>
-      <c r="H15" s="46" t="n">
+      <c r="I15" s="46" t="n">
         <v>0.75</v>
       </c>
-      <c r="I15" s="46" t="n">
+      <c r="J15" s="46" t="n">
         <v>0.25</v>
       </c>
-      <c r="J15" s="46" t="n">
+      <c r="K15" s="46" t="n">
         <v>3</v>
       </c>
-      <c r="K15" s="17" t="n"/>
+      <c r="L15" s="17" t="n"/>
     </row>
     <row r="16" ht="26" customHeight="1">
       <c r="A16" s="15" t="inlineStr">
@@ -16361,34 +16408,35 @@
           <t>F01-03-3</t>
         </is>
       </c>
-      <c r="B16" s="17" t="n"/>
-      <c r="C16" s="32" t="inlineStr">
+      <c r="B16" s="102" t="n"/>
+      <c r="C16" s="17" t="n"/>
+      <c r="D16" s="32" t="inlineStr">
         <is>
           <t>校验规则配置</t>
         </is>
       </c>
-      <c r="D16" s="32" t="inlineStr">
+      <c r="E16" s="32" t="inlineStr">
         <is>
           <t>必填/唯一/范围/自定义表达式校验</t>
         </is>
       </c>
-      <c r="E16" s="46" t="n"/>
-      <c r="F16" s="46" t="n">
-        <v>1</v>
-      </c>
+      <c r="F16" s="46" t="n"/>
       <c r="G16" s="46" t="n">
         <v>1</v>
       </c>
       <c r="H16" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="I16" s="46" t="n">
         <v>0.5</v>
       </c>
-      <c r="I16" s="46" t="n">
+      <c r="J16" s="46" t="n">
         <v>0.25</v>
       </c>
-      <c r="J16" s="46" t="n">
+      <c r="K16" s="46" t="n">
         <v>2.75</v>
       </c>
-      <c r="K16" s="17" t="n"/>
+      <c r="L16" s="17" t="n"/>
     </row>
     <row r="17" ht="26" customHeight="1">
       <c r="A17" s="15" t="inlineStr">
@@ -16396,34 +16444,35 @@
           <t>F01-03-4</t>
         </is>
       </c>
-      <c r="B17" s="17" t="n"/>
-      <c r="C17" s="32" t="inlineStr">
+      <c r="B17" s="102" t="n"/>
+      <c r="C17" s="17" t="n"/>
+      <c r="D17" s="32" t="inlineStr">
         <is>
           <t>规则版本与试跑预览</t>
         </is>
       </c>
-      <c r="D17" s="32" t="inlineStr">
+      <c r="E17" s="32" t="inlineStr">
         <is>
           <t>规则版本管理、样本试跑与结果预览</t>
         </is>
       </c>
-      <c r="E17" s="46" t="n"/>
-      <c r="F17" s="46" t="n">
+      <c r="F17" s="46" t="n"/>
+      <c r="G17" s="46" t="n">
         <v>0.5</v>
       </c>
-      <c r="G17" s="46" t="n">
+      <c r="H17" s="46" t="n">
         <v>1</v>
       </c>
-      <c r="H17" s="46" t="n">
+      <c r="I17" s="46" t="n">
         <v>0.5</v>
       </c>
-      <c r="I17" s="46" t="n">
+      <c r="J17" s="46" t="n">
         <v>0.25</v>
       </c>
-      <c r="J17" s="46" t="n">
+      <c r="K17" s="46" t="n">
         <v>2.25</v>
       </c>
-      <c r="K17" s="17" t="n"/>
+      <c r="L17" s="17" t="n"/>
     </row>
     <row r="18" ht="26" customHeight="1">
       <c r="A18" s="15" t="inlineStr">
@@ -16431,38 +16480,39 @@
           <t>F01-04-1</t>
         </is>
       </c>
-      <c r="B18" s="95" t="inlineStr">
-        <is>
-          <t>迁移前完整性基准记录（模块1·存量历史数据迁移与标准化）</t>
-        </is>
-      </c>
-      <c r="C18" s="32" t="inlineStr">
+      <c r="B18" s="102" t="n"/>
+      <c r="C18" s="95" t="inlineStr">
+        <is>
+          <t>迁移前完整性基准记录</t>
+        </is>
+      </c>
+      <c r="D18" s="32" t="inlineStr">
         <is>
           <t>基准采集策略定义</t>
         </is>
       </c>
-      <c r="D18" s="32" t="inlineStr">
+      <c r="E18" s="32" t="inlineStr">
         <is>
           <t>行数/校验和/SHA-256抽样口径</t>
         </is>
       </c>
-      <c r="E18" s="46" t="n">
+      <c r="F18" s="46" t="n">
         <v>0.5</v>
       </c>
-      <c r="F18" s="46" t="n"/>
-      <c r="G18" s="46" t="n">
+      <c r="G18" s="46" t="n"/>
+      <c r="H18" s="46" t="n">
         <v>1</v>
-      </c>
-      <c r="H18" s="46" t="n">
-        <v>0.25</v>
       </c>
       <c r="I18" s="46" t="n">
         <v>0.25</v>
       </c>
       <c r="J18" s="46" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="K18" s="46" t="n">
         <v>2</v>
       </c>
-      <c r="K18" s="74" t="n">
+      <c r="L18" s="74" t="n">
         <v>5.5</v>
       </c>
     </row>
@@ -16472,32 +16522,33 @@
           <t>F01-04-2</t>
         </is>
       </c>
-      <c r="B19" s="17" t="n"/>
-      <c r="C19" s="32" t="inlineStr">
+      <c r="B19" s="102" t="n"/>
+      <c r="C19" s="17" t="n"/>
+      <c r="D19" s="32" t="inlineStr">
         <is>
           <t>基准采集作业与存储</t>
         </is>
       </c>
-      <c r="D19" s="32" t="inlineStr">
+      <c r="E19" s="32" t="inlineStr">
         <is>
           <t>源端基准快照生成、基准库表</t>
         </is>
       </c>
-      <c r="E19" s="46" t="n"/>
       <c r="F19" s="46" t="n"/>
-      <c r="G19" s="46" t="n">
+      <c r="G19" s="46" t="n"/>
+      <c r="H19" s="46" t="n">
         <v>1.5</v>
       </c>
-      <c r="H19" s="46" t="n">
+      <c r="I19" s="46" t="n">
         <v>0.5</v>
       </c>
-      <c r="I19" s="46" t="n">
+      <c r="J19" s="46" t="n">
         <v>0.25</v>
       </c>
-      <c r="J19" s="46" t="n">
+      <c r="K19" s="46" t="n">
         <v>2.25</v>
       </c>
-      <c r="K19" s="17" t="n"/>
+      <c r="L19" s="17" t="n"/>
     </row>
     <row r="20" ht="26" customHeight="1">
       <c r="A20" s="15" t="inlineStr">
@@ -16505,23 +16556,21 @@
           <t>F01-04-3</t>
         </is>
       </c>
-      <c r="B20" s="17" t="n"/>
-      <c r="C20" s="32" t="inlineStr">
+      <c r="B20" s="102" t="n"/>
+      <c r="C20" s="17" t="n"/>
+      <c r="D20" s="32" t="inlineStr">
         <is>
           <t>基准报告查询展示</t>
         </is>
       </c>
-      <c r="D20" s="32" t="inlineStr">
+      <c r="E20" s="32" t="inlineStr">
         <is>
           <t>基准结果展示与导出</t>
         </is>
       </c>
-      <c r="E20" s="46" t="n"/>
-      <c r="F20" s="46" t="n">
+      <c r="F20" s="46" t="n"/>
+      <c r="G20" s="46" t="n">
         <v>0.5</v>
-      </c>
-      <c r="G20" s="46" t="n">
-        <v>0.25</v>
       </c>
       <c r="H20" s="46" t="n">
         <v>0.25</v>
@@ -16530,9 +16579,12 @@
         <v>0.25</v>
       </c>
       <c r="J20" s="46" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="K20" s="46" t="n">
         <v>1.25</v>
       </c>
-      <c r="K20" s="17" t="n"/>
+      <c r="L20" s="17" t="n"/>
     </row>
     <row r="21" ht="26" customHeight="1">
       <c r="A21" s="15" t="inlineStr">
@@ -16540,36 +16592,37 @@
           <t>F01-05-1</t>
         </is>
       </c>
-      <c r="B21" s="95" t="inlineStr">
-        <is>
-          <t>迁移后完整性比对（模块1·存量历史数据迁移与标准化）</t>
-        </is>
-      </c>
-      <c r="C21" s="32" t="inlineStr">
+      <c r="B21" s="102" t="n"/>
+      <c r="C21" s="95" t="inlineStr">
+        <is>
+          <t>迁移后完整性比对</t>
+        </is>
+      </c>
+      <c r="D21" s="32" t="inlineStr">
         <is>
           <t>比对引擎</t>
         </is>
       </c>
-      <c r="D21" s="32" t="inlineStr">
+      <c r="E21" s="32" t="inlineStr">
         <is>
           <t>RAW/CURATED逐层行数与校验和比对、抽样SHA-256</t>
         </is>
       </c>
-      <c r="E21" s="46" t="n"/>
       <c r="F21" s="46" t="n"/>
-      <c r="G21" s="46" t="n">
+      <c r="G21" s="46" t="n"/>
+      <c r="H21" s="46" t="n">
         <v>2</v>
       </c>
-      <c r="H21" s="46" t="n">
+      <c r="I21" s="46" t="n">
         <v>0.75</v>
       </c>
-      <c r="I21" s="46" t="n">
+      <c r="J21" s="46" t="n">
         <v>0.25</v>
       </c>
-      <c r="J21" s="46" t="n">
+      <c r="K21" s="46" t="n">
         <v>3</v>
       </c>
-      <c r="K21" s="74" t="n">
+      <c r="L21" s="74" t="n">
         <v>5.5</v>
       </c>
     </row>
@@ -16579,36 +16632,37 @@
           <t>F01-05-2</t>
         </is>
       </c>
-      <c r="B22" s="17" t="n"/>
-      <c r="C22" s="32" t="inlineStr">
+      <c r="B22" s="103" t="n"/>
+      <c r="C22" s="17" t="n"/>
+      <c r="D22" s="32" t="inlineStr">
         <is>
           <t>差异报告与处理流程</t>
         </is>
       </c>
-      <c r="D22" s="32" t="inlineStr">
+      <c r="E22" s="32" t="inlineStr">
         <is>
           <t>差异清单、重迁/豁免记录</t>
         </is>
       </c>
-      <c r="E22" s="46" t="n">
+      <c r="F22" s="46" t="n">
         <v>0.25</v>
       </c>
-      <c r="F22" s="46" t="n">
+      <c r="G22" s="46" t="n">
         <v>1</v>
-      </c>
-      <c r="G22" s="46" t="n">
-        <v>0.5</v>
       </c>
       <c r="H22" s="46" t="n">
         <v>0.5</v>
       </c>
       <c r="I22" s="46" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J22" s="46" t="n">
         <v>0.25</v>
       </c>
-      <c r="J22" s="46" t="n">
+      <c r="K22" s="46" t="n">
         <v>2.5</v>
       </c>
-      <c r="K22" s="17" t="n"/>
+      <c r="L22" s="17" t="n"/>
     </row>
     <row r="23" ht="26" customHeight="1">
       <c r="A23" s="15" t="inlineStr">
@@ -16616,38 +16670,43 @@
           <t>F02-01-1</t>
         </is>
       </c>
-      <c r="B23" s="96" t="inlineStr">
-        <is>
-          <t>统一元数据模型（模块2·实时数据接入与常态化数据治理）</t>
-        </is>
-      </c>
-      <c r="C23" s="32" t="inlineStr">
+      <c r="B23" s="107" t="inlineStr">
+        <is>
+          <t>模块2·实时数据接入与常态化数据治理</t>
+        </is>
+      </c>
+      <c r="C23" s="96" t="inlineStr">
+        <is>
+          <t>统一元数据模型</t>
+        </is>
+      </c>
+      <c r="D23" s="32" t="inlineStr">
         <is>
           <t>元数据字段体系定义</t>
         </is>
       </c>
-      <c r="D23" s="32" t="inlineStr">
+      <c r="E23" s="32" t="inlineStr">
         <is>
           <t>字段/类型/必填/密级/保留等级字典</t>
         </is>
       </c>
-      <c r="E23" s="46" t="n">
+      <c r="F23" s="46" t="n">
         <v>1.5</v>
       </c>
-      <c r="F23" s="46" t="n"/>
-      <c r="G23" s="46" t="n">
+      <c r="G23" s="46" t="n"/>
+      <c r="H23" s="46" t="n">
         <v>0.5</v>
       </c>
-      <c r="H23" s="46" t="n">
+      <c r="I23" s="46" t="n">
         <v>0.25</v>
       </c>
-      <c r="I23" s="46" t="n">
+      <c r="J23" s="46" t="n">
         <v>0.5</v>
       </c>
-      <c r="J23" s="46" t="n">
+      <c r="K23" s="46" t="n">
         <v>2.75</v>
       </c>
-      <c r="K23" s="77" t="n">
+      <c r="L23" s="77" t="n">
         <v>9</v>
       </c>
     </row>
@@ -16657,32 +16716,33 @@
           <t>F02-01-2</t>
         </is>
       </c>
-      <c r="B24" s="17" t="n"/>
-      <c r="C24" s="32" t="inlineStr">
+      <c r="B24" s="102" t="n"/>
+      <c r="C24" s="17" t="n"/>
+      <c r="D24" s="32" t="inlineStr">
         <is>
           <t>元数据核心表与API</t>
         </is>
       </c>
-      <c r="D24" s="32" t="inlineStr">
+      <c r="E24" s="32" t="inlineStr">
         <is>
           <t>核心元数据表实现、CRUD API、Migration</t>
         </is>
       </c>
-      <c r="E24" s="46" t="n"/>
       <c r="F24" s="46" t="n"/>
-      <c r="G24" s="46" t="n">
+      <c r="G24" s="46" t="n"/>
+      <c r="H24" s="46" t="n">
         <v>2</v>
       </c>
-      <c r="H24" s="46" t="n">
+      <c r="I24" s="46" t="n">
         <v>0.5</v>
       </c>
-      <c r="I24" s="46" t="n">
+      <c r="J24" s="46" t="n">
         <v>0.25</v>
       </c>
-      <c r="J24" s="46" t="n">
+      <c r="K24" s="46" t="n">
         <v>2.75</v>
       </c>
-      <c r="K24" s="17" t="n"/>
+      <c r="L24" s="17" t="n"/>
     </row>
     <row r="25" ht="26" customHeight="1">
       <c r="A25" s="15" t="inlineStr">
@@ -16690,36 +16750,37 @@
           <t>F02-01-3</t>
         </is>
       </c>
-      <c r="B25" s="17" t="n"/>
-      <c r="C25" s="32" t="inlineStr">
+      <c r="B25" s="102" t="n"/>
+      <c r="C25" s="17" t="n"/>
+      <c r="D25" s="32" t="inlineStr">
         <is>
           <t>元数据驱动配置机制</t>
         </is>
       </c>
-      <c r="D25" s="32" t="inlineStr">
+      <c r="E25" s="32" t="inlineStr">
         <is>
           <t>查询配置模型、动态表单渲染协议</t>
         </is>
       </c>
-      <c r="E25" s="46" t="n">
+      <c r="F25" s="46" t="n">
         <v>0.25</v>
       </c>
-      <c r="F25" s="46" t="n">
+      <c r="G25" s="46" t="n">
         <v>2</v>
-      </c>
-      <c r="G25" s="46" t="n">
-        <v>0.5</v>
       </c>
       <c r="H25" s="46" t="n">
         <v>0.5</v>
       </c>
       <c r="I25" s="46" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J25" s="46" t="n">
         <v>0.25</v>
       </c>
-      <c r="J25" s="46" t="n">
+      <c r="K25" s="46" t="n">
         <v>3.5</v>
       </c>
-      <c r="K25" s="17" t="n"/>
+      <c r="L25" s="17" t="n"/>
     </row>
     <row r="26" ht="26" customHeight="1">
       <c r="A26" s="15" t="inlineStr">
@@ -16727,38 +16788,39 @@
           <t>F02-02-1</t>
         </is>
       </c>
-      <c r="B26" s="96" t="inlineStr">
-        <is>
-          <t>来源系统信息绑定（模块2·实时数据接入与常态化数据治理）</t>
-        </is>
-      </c>
-      <c r="C26" s="32" t="inlineStr">
+      <c r="B26" s="102" t="n"/>
+      <c r="C26" s="96" t="inlineStr">
+        <is>
+          <t>来源系统信息绑定</t>
+        </is>
+      </c>
+      <c r="D26" s="32" t="inlineStr">
         <is>
           <t>绑定规则与批次属性</t>
         </is>
       </c>
-      <c r="D26" s="32" t="inlineStr">
+      <c r="E26" s="32" t="inlineStr">
         <is>
           <t>源编码引用、退役项目/迁移批次属性规则</t>
         </is>
       </c>
-      <c r="E26" s="46" t="n">
+      <c r="F26" s="46" t="n">
         <v>0.5</v>
       </c>
-      <c r="F26" s="46" t="n"/>
-      <c r="G26" s="46" t="n">
+      <c r="G26" s="46" t="n"/>
+      <c r="H26" s="46" t="n">
         <v>0.75</v>
-      </c>
-      <c r="H26" s="46" t="n">
-        <v>0.25</v>
       </c>
       <c r="I26" s="46" t="n">
         <v>0.25</v>
       </c>
       <c r="J26" s="46" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="K26" s="46" t="n">
         <v>1.75</v>
       </c>
-      <c r="K26" s="77" t="n">
+      <c r="L26" s="77" t="n">
         <v>5.75</v>
       </c>
     </row>
@@ -16768,32 +16830,33 @@
           <t>F02-02-2</t>
         </is>
       </c>
-      <c r="B27" s="17" t="n"/>
-      <c r="C27" s="32" t="inlineStr">
+      <c r="B27" s="102" t="n"/>
+      <c r="C27" s="17" t="n"/>
+      <c r="D27" s="32" t="inlineStr">
         <is>
           <t>接入时自动绑定</t>
         </is>
       </c>
-      <c r="D27" s="32" t="inlineStr">
+      <c r="E27" s="32" t="inlineStr">
         <is>
           <t>导入/上传时来源属性自动写入与校验</t>
         </is>
       </c>
-      <c r="E27" s="46" t="n"/>
       <c r="F27" s="46" t="n"/>
-      <c r="G27" s="46" t="n">
+      <c r="G27" s="46" t="n"/>
+      <c r="H27" s="46" t="n">
         <v>1</v>
       </c>
-      <c r="H27" s="46" t="n">
+      <c r="I27" s="46" t="n">
         <v>0.5</v>
       </c>
-      <c r="I27" s="46" t="n">
+      <c r="J27" s="46" t="n">
         <v>0.25</v>
       </c>
-      <c r="J27" s="46" t="n">
+      <c r="K27" s="46" t="n">
         <v>1.75</v>
       </c>
-      <c r="K27" s="17" t="n"/>
+      <c r="L27" s="17" t="n"/>
     </row>
     <row r="28" ht="26" customHeight="1">
       <c r="A28" s="15" t="inlineStr">
@@ -16801,34 +16864,35 @@
           <t>F02-02-3</t>
         </is>
       </c>
-      <c r="B28" s="17" t="n"/>
-      <c r="C28" s="32" t="inlineStr">
+      <c r="B28" s="103" t="n"/>
+      <c r="C28" s="17" t="n"/>
+      <c r="D28" s="32" t="inlineStr">
         <is>
           <t>按来源检索与统计</t>
         </is>
       </c>
-      <c r="D28" s="32" t="inlineStr">
+      <c r="E28" s="32" t="inlineStr">
         <is>
           <t>来源维度筛选、统计报表</t>
         </is>
       </c>
-      <c r="E28" s="46" t="n"/>
-      <c r="F28" s="46" t="n">
+      <c r="F28" s="46" t="n"/>
+      <c r="G28" s="46" t="n">
         <v>1</v>
-      </c>
-      <c r="G28" s="46" t="n">
-        <v>0.5</v>
       </c>
       <c r="H28" s="46" t="n">
         <v>0.5</v>
       </c>
       <c r="I28" s="46" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J28" s="46" t="n">
         <v>0.25</v>
       </c>
-      <c r="J28" s="46" t="n">
+      <c r="K28" s="46" t="n">
         <v>2.25</v>
       </c>
-      <c r="K28" s="17" t="n"/>
+      <c r="L28" s="17" t="n"/>
     </row>
     <row r="29" ht="26" customHeight="1">
       <c r="A29" s="15" t="inlineStr">
@@ -16836,40 +16900,45 @@
           <t>F03-01-1</t>
         </is>
       </c>
-      <c r="B29" s="97" t="inlineStr">
-        <is>
-          <t>保留期限到期自动删除（模块3·记录归档与档案全生命周期管理）</t>
-        </is>
-      </c>
-      <c r="C29" s="32" t="inlineStr">
+      <c r="B29" s="108" t="inlineStr">
+        <is>
+          <t>模块3·记录归档与档案全生命周期管理</t>
+        </is>
+      </c>
+      <c r="C29" s="97" t="inlineStr">
+        <is>
+          <t>保留期限到期自动删除</t>
+        </is>
+      </c>
+      <c r="D29" s="32" t="inlineStr">
         <is>
           <t>保留策略配置</t>
         </is>
       </c>
-      <c r="D29" s="32" t="inlineStr">
+      <c r="E29" s="32" t="inlineStr">
         <is>
           <t>策略规则、继承关系、生效范围</t>
         </is>
       </c>
-      <c r="E29" s="46" t="n">
+      <c r="F29" s="46" t="n">
         <v>0.75</v>
       </c>
-      <c r="F29" s="46" t="n">
+      <c r="G29" s="46" t="n">
         <v>1</v>
-      </c>
-      <c r="G29" s="46" t="n">
-        <v>0.5</v>
       </c>
       <c r="H29" s="46" t="n">
         <v>0.5</v>
       </c>
       <c r="I29" s="46" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J29" s="46" t="n">
         <v>0.25</v>
       </c>
-      <c r="J29" s="46" t="n">
+      <c r="K29" s="46" t="n">
         <v>3</v>
       </c>
-      <c r="K29" s="80" t="n">
+      <c r="L29" s="80" t="n">
         <v>10</v>
       </c>
     </row>
@@ -16879,32 +16948,33 @@
           <t>F03-01-2</t>
         </is>
       </c>
-      <c r="B30" s="17" t="n"/>
-      <c r="C30" s="32" t="inlineStr">
+      <c r="B30" s="102" t="n"/>
+      <c r="C30" s="17" t="n"/>
+      <c r="D30" s="32" t="inlineStr">
         <is>
           <t>处置引擎</t>
         </is>
       </c>
-      <c r="D30" s="32" t="inlineStr">
+      <c r="E30" s="32" t="inlineStr">
         <is>
           <t>到期扫描、豁免检查、DROP PARTITION、VACUUM物理清除</t>
         </is>
       </c>
-      <c r="E30" s="46" t="n"/>
       <c r="F30" s="46" t="n"/>
-      <c r="G30" s="46" t="n">
+      <c r="G30" s="46" t="n"/>
+      <c r="H30" s="46" t="n">
         <v>2.5</v>
       </c>
-      <c r="H30" s="46" t="n">
+      <c r="I30" s="46" t="n">
         <v>1</v>
       </c>
-      <c r="I30" s="46" t="n">
+      <c r="J30" s="46" t="n">
         <v>0.5</v>
       </c>
-      <c r="J30" s="46" t="n">
+      <c r="K30" s="46" t="n">
         <v>4</v>
       </c>
-      <c r="K30" s="17" t="n"/>
+      <c r="L30" s="17" t="n"/>
     </row>
     <row r="31" ht="26" customHeight="1">
       <c r="A31" s="15" t="inlineStr">
@@ -16912,36 +16982,37 @@
           <t>F03-01-3</t>
         </is>
       </c>
-      <c r="B31" s="17" t="n"/>
-      <c r="C31" s="32" t="inlineStr">
+      <c r="B31" s="102" t="n"/>
+      <c r="C31" s="17" t="n"/>
+      <c r="D31" s="32" t="inlineStr">
         <is>
           <t>处置计划审批与台账</t>
         </is>
       </c>
-      <c r="D31" s="32" t="inlineStr">
+      <c r="E31" s="32" t="inlineStr">
         <is>
           <t>预演清单、审批流、处置留痕台账</t>
         </is>
       </c>
-      <c r="E31" s="46" t="n">
+      <c r="F31" s="46" t="n">
         <v>0.25</v>
       </c>
-      <c r="F31" s="46" t="n">
+      <c r="G31" s="46" t="n">
         <v>1.5</v>
-      </c>
-      <c r="G31" s="46" t="n">
-        <v>0.5</v>
       </c>
       <c r="H31" s="46" t="n">
         <v>0.5</v>
       </c>
       <c r="I31" s="46" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J31" s="46" t="n">
         <v>0.25</v>
       </c>
-      <c r="J31" s="46" t="n">
+      <c r="K31" s="46" t="n">
         <v>3</v>
       </c>
-      <c r="K31" s="17" t="n"/>
+      <c r="L31" s="17" t="n"/>
     </row>
     <row r="32" ht="26" customHeight="1">
       <c r="A32" s="15" t="inlineStr">
@@ -16949,40 +17020,41 @@
           <t>F03-02-1</t>
         </is>
       </c>
-      <c r="B32" s="97" t="inlineStr">
-        <is>
-          <t>Legal Hold 冻结（模块3·记录归档与档案全生命周期管理）</t>
-        </is>
-      </c>
-      <c r="C32" s="32" t="inlineStr">
+      <c r="B32" s="102" t="n"/>
+      <c r="C32" s="97" t="inlineStr">
+        <is>
+          <t>Legal Hold 冻结</t>
+        </is>
+      </c>
+      <c r="D32" s="32" t="inlineStr">
         <is>
           <t>Hold申请与审批流程</t>
         </is>
       </c>
-      <c r="D32" s="32" t="inlineStr">
+      <c r="E32" s="32" t="inlineStr">
         <is>
           <t>涉诉/审计/调查场景、审批链定义</t>
         </is>
       </c>
-      <c r="E32" s="46" t="n">
+      <c r="F32" s="46" t="n">
         <v>0.75</v>
       </c>
-      <c r="F32" s="46" t="n">
+      <c r="G32" s="46" t="n">
         <v>1</v>
       </c>
-      <c r="G32" s="46" t="n">
+      <c r="H32" s="46" t="n">
         <v>0.25</v>
       </c>
-      <c r="H32" s="46" t="n">
+      <c r="I32" s="46" t="n">
         <v>0.5</v>
       </c>
-      <c r="I32" s="46" t="n">
+      <c r="J32" s="46" t="n">
         <v>0.25</v>
       </c>
-      <c r="J32" s="46" t="n">
+      <c r="K32" s="46" t="n">
         <v>2.75</v>
       </c>
-      <c r="K32" s="80" t="n">
+      <c r="L32" s="80" t="n">
         <v>6.5</v>
       </c>
     </row>
@@ -16992,32 +17064,33 @@
           <t>F03-02-2</t>
         </is>
       </c>
-      <c r="B33" s="17" t="n"/>
-      <c r="C33" s="32" t="inlineStr">
+      <c r="B33" s="102" t="n"/>
+      <c r="C33" s="17" t="n"/>
+      <c r="D33" s="32" t="inlineStr">
         <is>
           <t>Hold生效与解除实现</t>
         </is>
       </c>
-      <c r="D33" s="32" t="inlineStr">
+      <c r="E33" s="32" t="inlineStr">
         <is>
           <t>记录级/表级冻结、处置豁免、操作留痕</t>
         </is>
       </c>
-      <c r="E33" s="46" t="n"/>
       <c r="F33" s="46" t="n"/>
-      <c r="G33" s="46" t="n">
+      <c r="G33" s="46" t="n"/>
+      <c r="H33" s="46" t="n">
         <v>1.5</v>
       </c>
-      <c r="H33" s="46" t="n">
+      <c r="I33" s="46" t="n">
         <v>0.75</v>
       </c>
-      <c r="I33" s="46" t="n">
+      <c r="J33" s="46" t="n">
         <v>0.25</v>
       </c>
-      <c r="J33" s="46" t="n">
+      <c r="K33" s="46" t="n">
         <v>2.5</v>
       </c>
-      <c r="K33" s="17" t="n"/>
+      <c r="L33" s="17" t="n"/>
     </row>
     <row r="34" ht="26" customHeight="1">
       <c r="A34" s="15" t="inlineStr">
@@ -17025,23 +17098,21 @@
           <t>F03-02-3</t>
         </is>
       </c>
-      <c r="B34" s="17" t="n"/>
-      <c r="C34" s="32" t="inlineStr">
+      <c r="B34" s="103" t="n"/>
+      <c r="C34" s="17" t="n"/>
+      <c r="D34" s="32" t="inlineStr">
         <is>
           <t>Hold清单管理与提醒</t>
         </is>
       </c>
-      <c r="D34" s="32" t="inlineStr">
+      <c r="E34" s="32" t="inlineStr">
         <is>
           <t>在Hold清单、解除预警</t>
         </is>
       </c>
-      <c r="E34" s="46" t="n"/>
-      <c r="F34" s="46" t="n">
+      <c r="F34" s="46" t="n"/>
+      <c r="G34" s="46" t="n">
         <v>0.5</v>
-      </c>
-      <c r="G34" s="46" t="n">
-        <v>0.25</v>
       </c>
       <c r="H34" s="46" t="n">
         <v>0.25</v>
@@ -17050,9 +17121,12 @@
         <v>0.25</v>
       </c>
       <c r="J34" s="46" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="K34" s="46" t="n">
         <v>1.25</v>
       </c>
-      <c r="K34" s="17" t="n"/>
+      <c r="L34" s="17" t="n"/>
     </row>
     <row r="35" ht="26" customHeight="1">
       <c r="A35" s="15" t="inlineStr">
@@ -17060,38 +17134,43 @@
           <t>F04-01-1</t>
         </is>
       </c>
-      <c r="B35" s="98" t="inlineStr">
-        <is>
-          <t>数据加密存储（模块4·数据存储与境内数据安全管控）</t>
-        </is>
-      </c>
-      <c r="C35" s="32" t="inlineStr">
+      <c r="B35" s="109" t="inlineStr">
+        <is>
+          <t>模块4·数据存储与境内数据安全管控</t>
+        </is>
+      </c>
+      <c r="C35" s="98" t="inlineStr">
+        <is>
+          <t>数据加密存储</t>
+        </is>
+      </c>
+      <c r="D35" s="32" t="inlineStr">
         <is>
           <t>加密策略定义</t>
         </is>
       </c>
-      <c r="D35" s="32" t="inlineStr">
+      <c r="E35" s="32" t="inlineStr">
         <is>
           <t>SSE+CMK方案、PII字段清单与字段级加密规则</t>
         </is>
       </c>
-      <c r="E35" s="46" t="n">
+      <c r="F35" s="46" t="n">
         <v>0.5</v>
       </c>
-      <c r="F35" s="46" t="n"/>
-      <c r="G35" s="46" t="n">
+      <c r="G35" s="46" t="n"/>
+      <c r="H35" s="46" t="n">
         <v>0.75</v>
-      </c>
-      <c r="H35" s="46" t="n">
-        <v>0.25</v>
       </c>
       <c r="I35" s="46" t="n">
         <v>0.25</v>
       </c>
       <c r="J35" s="46" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="K35" s="46" t="n">
         <v>1.75</v>
       </c>
-      <c r="K35" s="83" t="n">
+      <c r="L35" s="83" t="n">
         <v>6.5</v>
       </c>
     </row>
@@ -17101,32 +17180,33 @@
           <t>F04-01-2</t>
         </is>
       </c>
-      <c r="B36" s="17" t="n"/>
-      <c r="C36" s="32" t="inlineStr">
+      <c r="B36" s="102" t="n"/>
+      <c r="C36" s="17" t="n"/>
+      <c r="D36" s="32" t="inlineStr">
         <is>
           <t>存储层加密落地</t>
         </is>
       </c>
-      <c r="D36" s="32" t="inlineStr">
+      <c r="E36" s="32" t="inlineStr">
         <is>
           <t>ADLS SSE、Key Vault CMK集成、密钥轮换</t>
         </is>
       </c>
-      <c r="E36" s="46" t="n"/>
       <c r="F36" s="46" t="n"/>
-      <c r="G36" s="46" t="n">
+      <c r="G36" s="46" t="n"/>
+      <c r="H36" s="46" t="n">
         <v>1.5</v>
       </c>
-      <c r="H36" s="46" t="n">
+      <c r="I36" s="46" t="n">
         <v>0.5</v>
       </c>
-      <c r="I36" s="46" t="n">
+      <c r="J36" s="46" t="n">
         <v>0.25</v>
       </c>
-      <c r="J36" s="46" t="n">
+      <c r="K36" s="46" t="n">
         <v>2.25</v>
       </c>
-      <c r="K36" s="17" t="n"/>
+      <c r="L36" s="17" t="n"/>
     </row>
     <row r="37" ht="26" customHeight="1">
       <c r="A37" s="15" t="inlineStr">
@@ -17134,32 +17214,33 @@
           <t>F04-01-3</t>
         </is>
       </c>
-      <c r="B37" s="17" t="n"/>
-      <c r="C37" s="32" t="inlineStr">
+      <c r="B37" s="102" t="n"/>
+      <c r="C37" s="17" t="n"/>
+      <c r="D37" s="32" t="inlineStr">
         <is>
           <t>PII字段级加密服务</t>
         </is>
       </c>
-      <c r="D37" s="32" t="inlineStr">
+      <c r="E37" s="32" t="inlineStr">
         <is>
           <t>应用层加解密、密文索引策略、传输加密验证</t>
         </is>
       </c>
-      <c r="E37" s="46" t="n"/>
       <c r="F37" s="46" t="n"/>
-      <c r="G37" s="46" t="n">
+      <c r="G37" s="46" t="n"/>
+      <c r="H37" s="46" t="n">
         <v>1.5</v>
       </c>
-      <c r="H37" s="46" t="n">
+      <c r="I37" s="46" t="n">
         <v>0.75</v>
       </c>
-      <c r="I37" s="46" t="n">
+      <c r="J37" s="46" t="n">
         <v>0.25</v>
       </c>
-      <c r="J37" s="46" t="n">
+      <c r="K37" s="46" t="n">
         <v>2.5</v>
       </c>
-      <c r="K37" s="17" t="n"/>
+      <c r="L37" s="17" t="n"/>
     </row>
     <row r="38" ht="26" customHeight="1">
       <c r="A38" s="15" t="inlineStr">
@@ -17167,38 +17248,39 @@
           <t>F04-02-1</t>
         </is>
       </c>
-      <c r="B38" s="98" t="inlineStr">
-        <is>
-          <t>密钥管理（模块4·数据存储与境内数据安全管控）</t>
-        </is>
-      </c>
-      <c r="C38" s="32" t="inlineStr">
+      <c r="B38" s="102" t="n"/>
+      <c r="C38" s="98" t="inlineStr">
+        <is>
+          <t>密钥管理</t>
+        </is>
+      </c>
+      <c r="D38" s="32" t="inlineStr">
         <is>
           <t>密钥全流程管理</t>
         </is>
       </c>
-      <c r="D38" s="32" t="inlineStr">
+      <c r="E38" s="32" t="inlineStr">
         <is>
           <t>创建/保管/更新/吊销/权限控制</t>
         </is>
       </c>
-      <c r="E38" s="46" t="n">
+      <c r="F38" s="46" t="n">
         <v>0.25</v>
       </c>
-      <c r="F38" s="46" t="n"/>
-      <c r="G38" s="46" t="n">
+      <c r="G38" s="46" t="n"/>
+      <c r="H38" s="46" t="n">
         <v>1.5</v>
       </c>
-      <c r="H38" s="46" t="n">
+      <c r="I38" s="46" t="n">
         <v>0.5</v>
       </c>
-      <c r="I38" s="46" t="n">
+      <c r="J38" s="46" t="n">
         <v>0.25</v>
       </c>
-      <c r="J38" s="46" t="n">
+      <c r="K38" s="46" t="n">
         <v>2.5</v>
       </c>
-      <c r="K38" s="83" t="n">
+      <c r="L38" s="83" t="n">
         <v>6</v>
       </c>
     </row>
@@ -17208,21 +17290,19 @@
           <t>F04-02-2</t>
         </is>
       </c>
-      <c r="B39" s="17" t="n"/>
-      <c r="C39" s="32" t="inlineStr">
+      <c r="B39" s="102" t="n"/>
+      <c r="C39" s="17" t="n"/>
+      <c r="D39" s="32" t="inlineStr">
         <is>
           <t>密钥操作审计与告警</t>
         </is>
       </c>
-      <c r="D39" s="32" t="inlineStr">
+      <c r="E39" s="32" t="inlineStr">
         <is>
           <t>操作日志、异常使用告警</t>
         </is>
       </c>
-      <c r="E39" s="46" t="n"/>
-      <c r="F39" s="46" t="n">
-        <v>0.5</v>
-      </c>
+      <c r="F39" s="46" t="n"/>
       <c r="G39" s="46" t="n">
         <v>0.5</v>
       </c>
@@ -17230,12 +17310,15 @@
         <v>0.5</v>
       </c>
       <c r="I39" s="46" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J39" s="46" t="n">
         <v>0.25</v>
       </c>
-      <c r="J39" s="46" t="n">
+      <c r="K39" s="46" t="n">
         <v>1.75</v>
       </c>
-      <c r="K39" s="17" t="n"/>
+      <c r="L39" s="17" t="n"/>
     </row>
     <row r="40" ht="26" customHeight="1">
       <c r="A40" s="15" t="inlineStr">
@@ -17243,23 +17326,21 @@
           <t>F04-02-3</t>
         </is>
       </c>
-      <c r="B40" s="17" t="n"/>
-      <c r="C40" s="32" t="inlineStr">
+      <c r="B40" s="102" t="n"/>
+      <c r="C40" s="17" t="n"/>
+      <c r="D40" s="32" t="inlineStr">
         <is>
           <t>密钥管理界面</t>
         </is>
       </c>
-      <c r="D40" s="32" t="inlineStr">
+      <c r="E40" s="32" t="inlineStr">
         <is>
           <t>密钥清单、版本、权限分配界面</t>
         </is>
       </c>
-      <c r="E40" s="46" t="n"/>
-      <c r="F40" s="46" t="n">
+      <c r="F40" s="46" t="n"/>
+      <c r="G40" s="46" t="n">
         <v>1</v>
-      </c>
-      <c r="G40" s="46" t="n">
-        <v>0.25</v>
       </c>
       <c r="H40" s="46" t="n">
         <v>0.25</v>
@@ -17268,9 +17349,12 @@
         <v>0.25</v>
       </c>
       <c r="J40" s="46" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="K40" s="46" t="n">
         <v>1.75</v>
       </c>
-      <c r="K40" s="17" t="n"/>
+      <c r="L40" s="17" t="n"/>
     </row>
     <row r="41" ht="26" customHeight="1">
       <c r="A41" s="15" t="inlineStr">
@@ -17278,40 +17362,41 @@
           <t>F04-03-1</t>
         </is>
       </c>
-      <c r="B41" s="98" t="inlineStr">
-        <is>
-          <t>数据备份管理（模块4·数据存储与境内数据安全管控）</t>
-        </is>
-      </c>
-      <c r="C41" s="32" t="inlineStr">
+      <c r="B41" s="102" t="n"/>
+      <c r="C41" s="98" t="inlineStr">
+        <is>
+          <t>数据备份管理</t>
+        </is>
+      </c>
+      <c r="D41" s="32" t="inlineStr">
         <is>
           <t>备份策略配置</t>
         </is>
       </c>
-      <c r="D41" s="32" t="inlineStr">
+      <c r="E41" s="32" t="inlineStr">
         <is>
           <t>备份周期/范围/保留期策略</t>
         </is>
       </c>
-      <c r="E41" s="46" t="n">
+      <c r="F41" s="46" t="n">
         <v>0.5</v>
       </c>
-      <c r="F41" s="46" t="n">
+      <c r="G41" s="46" t="n">
         <v>0.75</v>
       </c>
-      <c r="G41" s="46" t="n">
+      <c r="H41" s="46" t="n">
         <v>0.5</v>
-      </c>
-      <c r="H41" s="46" t="n">
-        <v>0.25</v>
       </c>
       <c r="I41" s="46" t="n">
         <v>0.25</v>
       </c>
       <c r="J41" s="46" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="K41" s="46" t="n">
         <v>2.25</v>
       </c>
-      <c r="K41" s="83" t="n">
+      <c r="L41" s="83" t="n">
         <v>6.25</v>
       </c>
     </row>
@@ -17321,32 +17406,33 @@
           <t>F04-03-2</t>
         </is>
       </c>
-      <c r="B42" s="17" t="n"/>
-      <c r="C42" s="32" t="inlineStr">
+      <c r="B42" s="102" t="n"/>
+      <c r="C42" s="17" t="n"/>
+      <c r="D42" s="32" t="inlineStr">
         <is>
           <t>备份作业与副本创建</t>
         </is>
       </c>
-      <c r="D42" s="32" t="inlineStr">
+      <c r="E42" s="32" t="inlineStr">
         <is>
           <t>元数据库PITR、湖快照、附件副本</t>
         </is>
       </c>
-      <c r="E42" s="46" t="n"/>
       <c r="F42" s="46" t="n"/>
-      <c r="G42" s="46" t="n">
+      <c r="G42" s="46" t="n"/>
+      <c r="H42" s="46" t="n">
         <v>1.5</v>
       </c>
-      <c r="H42" s="46" t="n">
+      <c r="I42" s="46" t="n">
         <v>0.5</v>
       </c>
-      <c r="I42" s="46" t="n">
+      <c r="J42" s="46" t="n">
         <v>0.25</v>
       </c>
-      <c r="J42" s="46" t="n">
+      <c r="K42" s="46" t="n">
         <v>2.25</v>
       </c>
-      <c r="K42" s="17" t="n"/>
+      <c r="L42" s="17" t="n"/>
     </row>
     <row r="43" ht="26" customHeight="1">
       <c r="A43" s="15" t="inlineStr">
@@ -17354,21 +17440,19 @@
           <t>F04-03-3</t>
         </is>
       </c>
-      <c r="B43" s="17" t="n"/>
-      <c r="C43" s="32" t="inlineStr">
+      <c r="B43" s="102" t="n"/>
+      <c r="C43" s="17" t="n"/>
+      <c r="D43" s="32" t="inlineStr">
         <is>
           <t>备份监控与恢复操作</t>
         </is>
       </c>
-      <c r="D43" s="32" t="inlineStr">
+      <c r="E43" s="32" t="inlineStr">
         <is>
           <t>备份状态监控、恢复流程</t>
         </is>
       </c>
-      <c r="E43" s="46" t="n"/>
-      <c r="F43" s="46" t="n">
-        <v>0.5</v>
-      </c>
+      <c r="F43" s="46" t="n"/>
       <c r="G43" s="46" t="n">
         <v>0.5</v>
       </c>
@@ -17376,12 +17460,15 @@
         <v>0.5</v>
       </c>
       <c r="I43" s="46" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J43" s="46" t="n">
         <v>0.25</v>
       </c>
-      <c r="J43" s="46" t="n">
+      <c r="K43" s="46" t="n">
         <v>1.75</v>
       </c>
-      <c r="K43" s="17" t="n"/>
+      <c r="L43" s="17" t="n"/>
     </row>
     <row r="44" ht="26" customHeight="1">
       <c r="A44" s="15" t="inlineStr">
@@ -17389,38 +17476,39 @@
           <t>F04-04-1</t>
         </is>
       </c>
-      <c r="B44" s="98" t="inlineStr">
-        <is>
-          <t>异地灾备（模块4·数据存储与境内数据安全管控）</t>
-        </is>
-      </c>
-      <c r="C44" s="32" t="inlineStr">
+      <c r="B44" s="102" t="n"/>
+      <c r="C44" s="98" t="inlineStr">
+        <is>
+          <t>异地灾备</t>
+        </is>
+      </c>
+      <c r="D44" s="32" t="inlineStr">
         <is>
           <t>灾备方案与RTO/RPO定义</t>
         </is>
       </c>
-      <c r="D44" s="32" t="inlineStr">
+      <c r="E44" s="32" t="inlineStr">
         <is>
           <t>灾备架构、恢复目标定义</t>
         </is>
       </c>
-      <c r="E44" s="46" t="n">
+      <c r="F44" s="46" t="n">
         <v>0.5</v>
       </c>
-      <c r="F44" s="46" t="n"/>
-      <c r="G44" s="46" t="n">
+      <c r="G44" s="46" t="n"/>
+      <c r="H44" s="46" t="n">
         <v>0.5</v>
-      </c>
-      <c r="H44" s="46" t="n">
-        <v>0.25</v>
       </c>
       <c r="I44" s="46" t="n">
         <v>0.25</v>
       </c>
       <c r="J44" s="46" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="K44" s="46" t="n">
         <v>1.5</v>
       </c>
-      <c r="K44" s="83" t="n">
+      <c r="L44" s="83" t="n">
         <v>5.75</v>
       </c>
     </row>
@@ -17430,32 +17518,33 @@
           <t>F04-04-2</t>
         </is>
       </c>
-      <c r="B45" s="17" t="n"/>
-      <c r="C45" s="32" t="inlineStr">
+      <c r="B45" s="102" t="n"/>
+      <c r="C45" s="17" t="n"/>
+      <c r="D45" s="32" t="inlineStr">
         <is>
           <t>异地副本同步</t>
         </is>
       </c>
-      <c r="D45" s="32" t="inlineStr">
+      <c r="E45" s="32" t="inlineStr">
         <is>
           <t>存储异地冗余/复制配置</t>
         </is>
       </c>
-      <c r="E45" s="46" t="n"/>
       <c r="F45" s="46" t="n"/>
-      <c r="G45" s="46" t="n">
+      <c r="G45" s="46" t="n"/>
+      <c r="H45" s="46" t="n">
         <v>1.5</v>
       </c>
-      <c r="H45" s="46" t="n">
+      <c r="I45" s="46" t="n">
         <v>0.5</v>
       </c>
-      <c r="I45" s="46" t="n">
+      <c r="J45" s="46" t="n">
         <v>0.25</v>
       </c>
-      <c r="J45" s="46" t="n">
+      <c r="K45" s="46" t="n">
         <v>2.25</v>
       </c>
-      <c r="K45" s="17" t="n"/>
+      <c r="L45" s="17" t="n"/>
     </row>
     <row r="46" ht="26" customHeight="1">
       <c r="A46" s="15" t="inlineStr">
@@ -17463,32 +17552,33 @@
           <t>F04-04-3</t>
         </is>
       </c>
-      <c r="B46" s="17" t="n"/>
-      <c r="C46" s="32" t="inlineStr">
+      <c r="B46" s="103" t="n"/>
+      <c r="C46" s="17" t="n"/>
+      <c r="D46" s="32" t="inlineStr">
         <is>
           <t>恢复切换演练</t>
         </is>
       </c>
-      <c r="D46" s="32" t="inlineStr">
+      <c r="E46" s="32" t="inlineStr">
         <is>
           <t>演练脚本、切换/回切流程与报告</t>
         </is>
       </c>
-      <c r="E46" s="46" t="n"/>
       <c r="F46" s="46" t="n"/>
-      <c r="G46" s="46" t="n">
+      <c r="G46" s="46" t="n"/>
+      <c r="H46" s="46" t="n">
         <v>1</v>
       </c>
-      <c r="H46" s="46" t="n">
+      <c r="I46" s="46" t="n">
         <v>0.75</v>
       </c>
-      <c r="I46" s="46" t="n">
+      <c r="J46" s="46" t="n">
         <v>0.25</v>
       </c>
-      <c r="J46" s="46" t="n">
+      <c r="K46" s="46" t="n">
         <v>2</v>
       </c>
-      <c r="K46" s="17" t="n"/>
+      <c r="L46" s="17" t="n"/>
     </row>
     <row r="47" ht="26" customHeight="1">
       <c r="A47" s="15" t="inlineStr">
@@ -17496,40 +17586,45 @@
           <t>F05-01-1</t>
         </is>
       </c>
-      <c r="B47" s="104" t="inlineStr">
-        <is>
-          <t>关键词检索（模块5·档案检索、智能发现与业务利用）</t>
-        </is>
-      </c>
-      <c r="C47" s="32" t="inlineStr">
+      <c r="B47" s="110" t="inlineStr">
+        <is>
+          <t>模块5·档案检索、智能发现与业务利用</t>
+        </is>
+      </c>
+      <c r="C47" s="104" t="inlineStr">
+        <is>
+          <t>关键词检索</t>
+        </is>
+      </c>
+      <c r="D47" s="32" t="inlineStr">
         <is>
           <t>检索配置模型</t>
         </is>
       </c>
-      <c r="D47" s="32" t="inlineStr">
+      <c r="E47" s="32" t="inlineStr">
         <is>
           <t>可检索字段、分词策略、OCR文本索引策略</t>
         </is>
-      </c>
-      <c r="E47" s="46" t="n">
-        <v>0.5</v>
       </c>
       <c r="F47" s="46" t="n">
         <v>0.5</v>
       </c>
       <c r="G47" s="46" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H47" s="46" t="n">
         <v>1</v>
-      </c>
-      <c r="H47" s="46" t="n">
-        <v>0.25</v>
       </c>
       <c r="I47" s="46" t="n">
         <v>0.25</v>
       </c>
       <c r="J47" s="46" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="K47" s="46" t="n">
         <v>2.5</v>
       </c>
-      <c r="K47" s="105" t="n">
+      <c r="L47" s="105" t="n">
         <v>7.75</v>
       </c>
     </row>
@@ -17539,34 +17634,35 @@
           <t>F05-01-2</t>
         </is>
       </c>
-      <c r="B48" s="17" t="n"/>
-      <c r="C48" s="32" t="inlineStr">
+      <c r="B48" s="102" t="n"/>
+      <c r="C48" s="17" t="n"/>
+      <c r="D48" s="32" t="inlineStr">
         <is>
           <t>检索页动态表单</t>
         </is>
       </c>
-      <c r="D48" s="32" t="inlineStr">
+      <c r="E48" s="32" t="inlineStr">
         <is>
           <t>元数据驱动渲染、关键词与组合查询</t>
         </is>
       </c>
-      <c r="E48" s="46" t="n"/>
-      <c r="F48" s="46" t="n">
+      <c r="F48" s="46" t="n"/>
+      <c r="G48" s="46" t="n">
         <v>2</v>
       </c>
-      <c r="G48" s="46" t="n">
+      <c r="H48" s="46" t="n">
         <v>0.25</v>
       </c>
-      <c r="H48" s="46" t="n">
+      <c r="I48" s="46" t="n">
         <v>0.5</v>
       </c>
-      <c r="I48" s="46" t="n">
+      <c r="J48" s="46" t="n">
         <v>0.25</v>
       </c>
-      <c r="J48" s="46" t="n">
+      <c r="K48" s="46" t="n">
         <v>3</v>
       </c>
-      <c r="K48" s="17" t="n"/>
+      <c r="L48" s="17" t="n"/>
     </row>
     <row r="49" ht="26" customHeight="1">
       <c r="A49" s="15" t="inlineStr">
@@ -17574,32 +17670,33 @@
           <t>F05-01-3</t>
         </is>
       </c>
-      <c r="B49" s="17" t="n"/>
-      <c r="C49" s="32" t="inlineStr">
+      <c r="B49" s="102" t="n"/>
+      <c r="C49" s="17" t="n"/>
+      <c r="D49" s="32" t="inlineStr">
         <is>
           <t>查询代理与SERVE层对接</t>
         </is>
       </c>
-      <c r="D49" s="32" t="inlineStr">
+      <c r="E49" s="32" t="inlineStr">
         <is>
           <t>查询服务、索引优化、结果高亮</t>
         </is>
       </c>
-      <c r="E49" s="46" t="n"/>
       <c r="F49" s="46" t="n"/>
-      <c r="G49" s="46" t="n">
+      <c r="G49" s="46" t="n"/>
+      <c r="H49" s="46" t="n">
         <v>1.25</v>
       </c>
-      <c r="H49" s="46" t="n">
+      <c r="I49" s="46" t="n">
         <v>0.75</v>
       </c>
-      <c r="I49" s="46" t="n">
+      <c r="J49" s="46" t="n">
         <v>0.25</v>
       </c>
-      <c r="J49" s="46" t="n">
+      <c r="K49" s="46" t="n">
         <v>2.25</v>
       </c>
-      <c r="K49" s="17" t="n"/>
+      <c r="L49" s="17" t="n"/>
     </row>
     <row r="50" ht="26" customHeight="1">
       <c r="A50" s="15" t="inlineStr">
@@ -17607,36 +17704,37 @@
           <t>F05-02-1</t>
         </is>
       </c>
-      <c r="B50" s="104" t="inlineStr">
-        <is>
-          <t>按系统名称检索（模块5·档案检索、智能发现与业务利用）</t>
-        </is>
-      </c>
-      <c r="C50" s="32" t="inlineStr">
+      <c r="B50" s="102" t="n"/>
+      <c r="C50" s="104" t="inlineStr">
+        <is>
+          <t>按系统名称检索</t>
+        </is>
+      </c>
+      <c r="D50" s="32" t="inlineStr">
         <is>
           <t>来源系统筛选组件</t>
         </is>
       </c>
-      <c r="D50" s="32" t="inlineStr">
+      <c r="E50" s="32" t="inlineStr">
         <is>
           <t>来源系统下拉/搜索/多选</t>
         </is>
       </c>
-      <c r="E50" s="46" t="n"/>
-      <c r="F50" s="46" t="n">
+      <c r="F50" s="46" t="n"/>
+      <c r="G50" s="46" t="n">
         <v>0.75</v>
       </c>
-      <c r="G50" s="46" t="n"/>
-      <c r="H50" s="46" t="n">
-        <v>0.25</v>
-      </c>
+      <c r="H50" s="46" t="n"/>
       <c r="I50" s="46" t="n">
         <v>0.25</v>
       </c>
       <c r="J50" s="46" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="K50" s="46" t="n">
         <v>1.25</v>
       </c>
-      <c r="K50" s="105" t="n">
+      <c r="L50" s="105" t="n">
         <v>2.25</v>
       </c>
     </row>
@@ -17646,32 +17744,33 @@
           <t>F05-02-2</t>
         </is>
       </c>
-      <c r="B51" s="17" t="n"/>
-      <c r="C51" s="32" t="inlineStr">
+      <c r="B51" s="102" t="n"/>
+      <c r="C51" s="17" t="n"/>
+      <c r="D51" s="32" t="inlineStr">
         <is>
           <t>来源维度查询下推</t>
         </is>
       </c>
-      <c r="D51" s="32" t="inlineStr">
+      <c r="E51" s="32" t="inlineStr">
         <is>
           <t>sys_id过滤、分区裁剪</t>
         </is>
       </c>
-      <c r="E51" s="46" t="n"/>
       <c r="F51" s="46" t="n"/>
-      <c r="G51" s="46" t="n">
+      <c r="G51" s="46" t="n"/>
+      <c r="H51" s="46" t="n">
         <v>0.5</v>
-      </c>
-      <c r="H51" s="46" t="n">
-        <v>0.25</v>
       </c>
       <c r="I51" s="46" t="n">
         <v>0.25</v>
       </c>
       <c r="J51" s="46" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="K51" s="46" t="n">
         <v>1</v>
       </c>
-      <c r="K51" s="17" t="n"/>
+      <c r="L51" s="17" t="n"/>
     </row>
     <row r="52" ht="26" customHeight="1">
       <c r="A52" s="15" t="inlineStr">
@@ -17679,36 +17778,37 @@
           <t>F05-03-1</t>
         </is>
       </c>
-      <c r="B52" s="104" t="inlineStr">
-        <is>
-          <t>按业务时间检索（模块5·档案检索、智能发现与业务利用）</t>
-        </is>
-      </c>
-      <c r="C52" s="32" t="inlineStr">
+      <c r="B52" s="102" t="n"/>
+      <c r="C52" s="104" t="inlineStr">
+        <is>
+          <t>按业务时间检索</t>
+        </is>
+      </c>
+      <c r="D52" s="32" t="inlineStr">
         <is>
           <t>时间维度筛选组件</t>
         </is>
       </c>
-      <c r="D52" s="32" t="inlineStr">
+      <c r="E52" s="32" t="inlineStr">
         <is>
           <t>创建/修改/业务发生时间范围选择</t>
         </is>
       </c>
-      <c r="E52" s="46" t="n"/>
-      <c r="F52" s="46" t="n">
+      <c r="F52" s="46" t="n"/>
+      <c r="G52" s="46" t="n">
         <v>0.75</v>
       </c>
-      <c r="G52" s="46" t="n"/>
-      <c r="H52" s="46" t="n">
-        <v>0.25</v>
-      </c>
+      <c r="H52" s="46" t="n"/>
       <c r="I52" s="46" t="n">
         <v>0.25</v>
       </c>
       <c r="J52" s="46" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="K52" s="46" t="n">
         <v>1.25</v>
       </c>
-      <c r="K52" s="105" t="n">
+      <c r="L52" s="105" t="n">
         <v>2.25</v>
       </c>
     </row>
@@ -17718,32 +17818,33 @@
           <t>F05-03-2</t>
         </is>
       </c>
-      <c r="B53" s="17" t="n"/>
-      <c r="C53" s="32" t="inlineStr">
+      <c r="B53" s="102" t="n"/>
+      <c r="C53" s="17" t="n"/>
+      <c r="D53" s="32" t="inlineStr">
         <is>
           <t>时间分区下推与索引</t>
         </is>
       </c>
-      <c r="D53" s="32" t="inlineStr">
+      <c r="E53" s="32" t="inlineStr">
         <is>
           <t>分区裁剪、时间索引优化</t>
         </is>
       </c>
-      <c r="E53" s="46" t="n"/>
       <c r="F53" s="46" t="n"/>
-      <c r="G53" s="46" t="n">
+      <c r="G53" s="46" t="n"/>
+      <c r="H53" s="46" t="n">
         <v>0.5</v>
-      </c>
-      <c r="H53" s="46" t="n">
-        <v>0.25</v>
       </c>
       <c r="I53" s="46" t="n">
         <v>0.25</v>
       </c>
       <c r="J53" s="46" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="K53" s="46" t="n">
         <v>1</v>
       </c>
-      <c r="K53" s="17" t="n"/>
+      <c r="L53" s="17" t="n"/>
     </row>
     <row r="54" ht="26" customHeight="1">
       <c r="A54" s="15" t="inlineStr">
@@ -17751,36 +17852,37 @@
           <t>F05-04-1</t>
         </is>
       </c>
-      <c r="B54" s="104" t="inlineStr">
-        <is>
-          <t>检索结果列表展示（模块5·档案检索、智能发现与业务利用）</t>
-        </is>
-      </c>
-      <c r="C54" s="32" t="inlineStr">
+      <c r="B54" s="102" t="n"/>
+      <c r="C54" s="104" t="inlineStr">
+        <is>
+          <t>检索结果列表展示</t>
+        </is>
+      </c>
+      <c r="D54" s="32" t="inlineStr">
         <is>
           <t>列表展示与分页排序</t>
         </is>
       </c>
-      <c r="D54" s="32" t="inlineStr">
+      <c r="E54" s="32" t="inlineStr">
         <is>
           <t>关键字段展示、分批加载、虚拟滚动</t>
         </is>
       </c>
-      <c r="E54" s="46" t="n"/>
-      <c r="F54" s="46" t="n">
+      <c r="F54" s="46" t="n"/>
+      <c r="G54" s="46" t="n">
         <v>2</v>
       </c>
-      <c r="G54" s="46" t="n"/>
-      <c r="H54" s="46" t="n">
+      <c r="H54" s="46" t="n"/>
+      <c r="I54" s="46" t="n">
         <v>0.5</v>
       </c>
-      <c r="I54" s="46" t="n">
+      <c r="J54" s="46" t="n">
         <v>0.25</v>
       </c>
-      <c r="J54" s="46" t="n">
+      <c r="K54" s="46" t="n">
         <v>2.75</v>
       </c>
-      <c r="K54" s="105" t="n">
+      <c r="L54" s="105" t="n">
         <v>4.5</v>
       </c>
     </row>
@@ -17790,34 +17892,35 @@
           <t>F05-04-2</t>
         </is>
       </c>
-      <c r="B55" s="17" t="n"/>
-      <c r="C55" s="32" t="inlineStr">
+      <c r="B55" s="102" t="n"/>
+      <c r="C55" s="17" t="n"/>
+      <c r="D55" s="32" t="inlineStr">
         <is>
           <t>大批量结果性能</t>
         </is>
       </c>
-      <c r="D55" s="32" t="inlineStr">
+      <c r="E55" s="32" t="inlineStr">
         <is>
           <t>异步计数、游标分页、缓存</t>
         </is>
       </c>
-      <c r="E55" s="46" t="n"/>
-      <c r="F55" s="46" t="n">
+      <c r="F55" s="46" t="n"/>
+      <c r="G55" s="46" t="n">
         <v>0.25</v>
       </c>
-      <c r="G55" s="46" t="n">
+      <c r="H55" s="46" t="n">
         <v>0.75</v>
       </c>
-      <c r="H55" s="46" t="n">
+      <c r="I55" s="46" t="n">
         <v>0.5</v>
       </c>
-      <c r="I55" s="46" t="n">
+      <c r="J55" s="46" t="n">
         <v>0.25</v>
       </c>
-      <c r="J55" s="46" t="n">
+      <c r="K55" s="46" t="n">
         <v>1.75</v>
       </c>
-      <c r="K55" s="17" t="n"/>
+      <c r="L55" s="17" t="n"/>
     </row>
     <row r="56" ht="26" customHeight="1">
       <c r="A56" s="15" t="inlineStr">
@@ -17825,36 +17928,37 @@
           <t>F05-05-1</t>
         </is>
       </c>
-      <c r="B56" s="104" t="inlineStr">
-        <is>
-          <t>原始文件在线预览（模块5·档案检索、智能发现与业务利用）</t>
-        </is>
-      </c>
-      <c r="C56" s="32" t="inlineStr">
+      <c r="B56" s="102" t="n"/>
+      <c r="C56" s="104" t="inlineStr">
+        <is>
+          <t>原始文件在线预览</t>
+        </is>
+      </c>
+      <c r="D56" s="32" t="inlineStr">
         <is>
           <t>预览服务</t>
         </is>
       </c>
-      <c r="D56" s="32" t="inlineStr">
+      <c r="E56" s="32" t="inlineStr">
         <is>
           <t>格式识别、图片/PDF/Office转换</t>
         </is>
       </c>
-      <c r="E56" s="46" t="n"/>
       <c r="F56" s="46" t="n"/>
-      <c r="G56" s="46" t="n">
+      <c r="G56" s="46" t="n"/>
+      <c r="H56" s="46" t="n">
         <v>1.5</v>
       </c>
-      <c r="H56" s="46" t="n">
+      <c r="I56" s="46" t="n">
         <v>0.5</v>
       </c>
-      <c r="I56" s="46" t="n">
+      <c r="J56" s="46" t="n">
         <v>0.25</v>
       </c>
-      <c r="J56" s="46" t="n">
+      <c r="K56" s="46" t="n">
         <v>2.25</v>
       </c>
-      <c r="K56" s="105" t="n">
+      <c r="L56" s="105" t="n">
         <v>6.5</v>
       </c>
     </row>
@@ -17864,34 +17968,35 @@
           <t>F05-05-2</t>
         </is>
       </c>
-      <c r="B57" s="17" t="n"/>
-      <c r="C57" s="32" t="inlineStr">
+      <c r="B57" s="102" t="n"/>
+      <c r="C57" s="17" t="n"/>
+      <c r="D57" s="32" t="inlineStr">
         <is>
           <t>SAS直连与流式加载</t>
         </is>
       </c>
-      <c r="D57" s="32" t="inlineStr">
+      <c r="E57" s="32" t="inlineStr">
         <is>
           <t>临时SAS链接、流式传输、权限校验</t>
         </is>
       </c>
-      <c r="E57" s="46" t="n"/>
-      <c r="F57" s="46" t="n">
+      <c r="F57" s="46" t="n"/>
+      <c r="G57" s="46" t="n">
         <v>0.5</v>
       </c>
-      <c r="G57" s="46" t="n">
+      <c r="H57" s="46" t="n">
         <v>1</v>
       </c>
-      <c r="H57" s="46" t="n">
+      <c r="I57" s="46" t="n">
         <v>0.5</v>
       </c>
-      <c r="I57" s="46" t="n">
+      <c r="J57" s="46" t="n">
         <v>0.25</v>
       </c>
-      <c r="J57" s="46" t="n">
+      <c r="K57" s="46" t="n">
         <v>2.25</v>
       </c>
-      <c r="K57" s="17" t="n"/>
+      <c r="L57" s="17" t="n"/>
     </row>
     <row r="58" ht="26" customHeight="1">
       <c r="A58" s="15" t="inlineStr">
@@ -17899,32 +18004,33 @@
           <t>F05-05-3</t>
         </is>
       </c>
-      <c r="B58" s="17" t="n"/>
-      <c r="C58" s="32" t="inlineStr">
+      <c r="B58" s="103" t="n"/>
+      <c r="C58" s="17" t="n"/>
+      <c r="D58" s="32" t="inlineStr">
         <is>
           <t>前端预览组件</t>
         </is>
       </c>
-      <c r="D58" s="32" t="inlineStr">
+      <c r="E58" s="32" t="inlineStr">
         <is>
           <t>格式适配、缩放、失败降级下载</t>
         </is>
       </c>
-      <c r="E58" s="46" t="n"/>
-      <c r="F58" s="46" t="n">
+      <c r="F58" s="46" t="n"/>
+      <c r="G58" s="46" t="n">
         <v>1.5</v>
       </c>
-      <c r="G58" s="46" t="n"/>
-      <c r="H58" s="46" t="n">
-        <v>0.25</v>
-      </c>
+      <c r="H58" s="46" t="n"/>
       <c r="I58" s="46" t="n">
         <v>0.25</v>
       </c>
       <c r="J58" s="46" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="K58" s="46" t="n">
         <v>2</v>
       </c>
-      <c r="K58" s="17" t="n"/>
+      <c r="L58" s="17" t="n"/>
     </row>
     <row r="59" ht="26" customHeight="1">
       <c r="A59" s="15" t="inlineStr">
@@ -17932,38 +18038,43 @@
           <t>F06-01-1</t>
         </is>
       </c>
-      <c r="B59" s="100" t="inlineStr">
-        <is>
-          <t>归档操作日志记录（模块6·合规管控、审计追踪与合规报表）</t>
-        </is>
-      </c>
-      <c r="C59" s="32" t="inlineStr">
+      <c r="B59" s="111" t="inlineStr">
+        <is>
+          <t>模块6·合规管控、审计追踪与合规报表</t>
+        </is>
+      </c>
+      <c r="C59" s="100" t="inlineStr">
+        <is>
+          <t>归档操作日志记录</t>
+        </is>
+      </c>
+      <c r="D59" s="32" t="inlineStr">
         <is>
           <t>埋点规范与日志模型</t>
         </is>
       </c>
-      <c r="D59" s="32" t="inlineStr">
+      <c r="E59" s="32" t="inlineStr">
         <is>
           <t>操作对象/用户/时间/结果/IP模型定义</t>
         </is>
       </c>
-      <c r="E59" s="46" t="n">
+      <c r="F59" s="46" t="n">
         <v>0.25</v>
       </c>
-      <c r="F59" s="46" t="n"/>
-      <c r="G59" s="46" t="n">
+      <c r="G59" s="46" t="n"/>
+      <c r="H59" s="46" t="n">
         <v>0.5</v>
-      </c>
-      <c r="H59" s="46" t="n">
-        <v>0.25</v>
       </c>
       <c r="I59" s="46" t="n">
         <v>0.25</v>
       </c>
       <c r="J59" s="46" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="K59" s="46" t="n">
         <v>1.25</v>
       </c>
-      <c r="K59" s="89" t="n">
+      <c r="L59" s="89" t="n">
         <v>5.5</v>
       </c>
     </row>
@@ -17973,32 +18084,33 @@
           <t>F06-01-2</t>
         </is>
       </c>
-      <c r="B60" s="17" t="n"/>
-      <c r="C60" s="32" t="inlineStr">
+      <c r="B60" s="102" t="n"/>
+      <c r="C60" s="17" t="n"/>
+      <c r="D60" s="32" t="inlineStr">
         <is>
           <t>操作拦截与落库</t>
         </is>
       </c>
-      <c r="D60" s="32" t="inlineStr">
+      <c r="E60" s="32" t="inlineStr">
         <is>
           <t>归档/导入/上传统一拦截器、异步写入</t>
         </is>
       </c>
-      <c r="E60" s="46" t="n"/>
       <c r="F60" s="46" t="n"/>
-      <c r="G60" s="46" t="n">
+      <c r="G60" s="46" t="n"/>
+      <c r="H60" s="46" t="n">
         <v>1</v>
       </c>
-      <c r="H60" s="46" t="n">
+      <c r="I60" s="46" t="n">
         <v>0.5</v>
       </c>
-      <c r="I60" s="46" t="n">
+      <c r="J60" s="46" t="n">
         <v>0.25</v>
       </c>
-      <c r="J60" s="46" t="n">
+      <c r="K60" s="46" t="n">
         <v>1.75</v>
       </c>
-      <c r="K60" s="17" t="n"/>
+      <c r="L60" s="17" t="n"/>
     </row>
     <row r="61" ht="26" customHeight="1">
       <c r="A61" s="15" t="inlineStr">
@@ -18006,34 +18118,35 @@
           <t>F06-01-3</t>
         </is>
       </c>
-      <c r="B61" s="17" t="n"/>
-      <c r="C61" s="32" t="inlineStr">
+      <c r="B61" s="102" t="n"/>
+      <c r="C61" s="17" t="n"/>
+      <c r="D61" s="32" t="inlineStr">
         <is>
           <t>审计查询界面</t>
         </is>
       </c>
-      <c r="D61" s="32" t="inlineStr">
+      <c r="E61" s="32" t="inlineStr">
         <is>
           <t>多维筛选与导出（覆盖归档/查询/导出三类日志）</t>
         </is>
       </c>
-      <c r="E61" s="46" t="n"/>
-      <c r="F61" s="46" t="n">
+      <c r="F61" s="46" t="n"/>
+      <c r="G61" s="46" t="n">
         <v>1.5</v>
       </c>
-      <c r="G61" s="46" t="n">
+      <c r="H61" s="46" t="n">
         <v>0.25</v>
       </c>
-      <c r="H61" s="46" t="n">
+      <c r="I61" s="46" t="n">
         <v>0.5</v>
       </c>
-      <c r="I61" s="46" t="n">
+      <c r="J61" s="46" t="n">
         <v>0.25</v>
       </c>
-      <c r="J61" s="46" t="n">
+      <c r="K61" s="46" t="n">
         <v>2.5</v>
       </c>
-      <c r="K61" s="17" t="n"/>
+      <c r="L61" s="17" t="n"/>
     </row>
     <row r="62" ht="26" customHeight="1">
       <c r="A62" s="15" t="inlineStr">
@@ -18041,36 +18154,37 @@
           <t>F06-02-1</t>
         </is>
       </c>
-      <c r="B62" s="100" t="inlineStr">
-        <is>
-          <t>查询操作日志记录（模块6·合规管控、审计追踪与合规报表）</t>
-        </is>
-      </c>
-      <c r="C62" s="32" t="inlineStr">
+      <c r="B62" s="102" t="n"/>
+      <c r="C62" s="100" t="inlineStr">
+        <is>
+          <t>查询操作日志记录</t>
+        </is>
+      </c>
+      <c r="D62" s="32" t="inlineStr">
         <is>
           <t>查询/预览行为埋点</t>
         </is>
       </c>
-      <c r="D62" s="32" t="inlineStr">
+      <c r="E62" s="32" t="inlineStr">
         <is>
           <t>查询条件脱敏记录、预览行为记录</t>
         </is>
       </c>
-      <c r="E62" s="46" t="n"/>
       <c r="F62" s="46" t="n"/>
-      <c r="G62" s="46" t="n">
+      <c r="G62" s="46" t="n"/>
+      <c r="H62" s="46" t="n">
         <v>0.75</v>
       </c>
-      <c r="H62" s="46" t="n">
+      <c r="I62" s="46" t="n">
         <v>0.5</v>
       </c>
-      <c r="I62" s="46" t="n">
+      <c r="J62" s="46" t="n">
         <v>0.25</v>
       </c>
-      <c r="J62" s="46" t="n">
+      <c r="K62" s="46" t="n">
         <v>1.5</v>
       </c>
-      <c r="K62" s="89" t="n">
+      <c r="L62" s="89" t="n">
         <v>2.5</v>
       </c>
     </row>
@@ -18080,32 +18194,33 @@
           <t>F06-02-2</t>
         </is>
       </c>
-      <c r="B63" s="17" t="n"/>
-      <c r="C63" s="32" t="inlineStr">
+      <c r="B63" s="102" t="n"/>
+      <c r="C63" s="17" t="n"/>
+      <c r="D63" s="32" t="inlineStr">
         <is>
           <t>异步批量写入</t>
         </is>
       </c>
-      <c r="D63" s="32" t="inlineStr">
+      <c r="E63" s="32" t="inlineStr">
         <is>
           <t>缓冲批量写入、不阻塞查询主链路</t>
         </is>
       </c>
-      <c r="E63" s="46" t="n"/>
       <c r="F63" s="46" t="n"/>
-      <c r="G63" s="46" t="n">
+      <c r="G63" s="46" t="n"/>
+      <c r="H63" s="46" t="n">
         <v>0.5</v>
-      </c>
-      <c r="H63" s="46" t="n">
-        <v>0.25</v>
       </c>
       <c r="I63" s="46" t="n">
         <v>0.25</v>
       </c>
       <c r="J63" s="46" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="K63" s="46" t="n">
         <v>1</v>
       </c>
-      <c r="K63" s="17" t="n"/>
+      <c r="L63" s="17" t="n"/>
     </row>
     <row r="64" ht="26" customHeight="1">
       <c r="A64" s="15" t="inlineStr">
@@ -18113,36 +18228,37 @@
           <t>F06-03-1</t>
         </is>
       </c>
-      <c r="B64" s="100" t="inlineStr">
-        <is>
-          <t>导出操作日志记录（模块6·合规管控、审计追踪与合规报表）</t>
-        </is>
-      </c>
-      <c r="C64" s="32" t="inlineStr">
+      <c r="B64" s="102" t="n"/>
+      <c r="C64" s="100" t="inlineStr">
+        <is>
+          <t>导出操作日志记录</t>
+        </is>
+      </c>
+      <c r="D64" s="32" t="inlineStr">
         <is>
           <t>导出行为审计</t>
         </is>
       </c>
-      <c r="D64" s="32" t="inlineStr">
+      <c r="E64" s="32" t="inlineStr">
         <is>
           <t>导出范围/条数/导出人/IP/下载链接追踪</t>
         </is>
       </c>
-      <c r="E64" s="46" t="n"/>
       <c r="F64" s="46" t="n"/>
-      <c r="G64" s="46" t="n">
+      <c r="G64" s="46" t="n"/>
+      <c r="H64" s="46" t="n">
         <v>0.75</v>
       </c>
-      <c r="H64" s="46" t="n">
+      <c r="I64" s="46" t="n">
         <v>0.5</v>
       </c>
-      <c r="I64" s="46" t="n">
+      <c r="J64" s="46" t="n">
         <v>0.25</v>
       </c>
-      <c r="J64" s="46" t="n">
+      <c r="K64" s="46" t="n">
         <v>1.5</v>
       </c>
-      <c r="K64" s="89" t="n">
+      <c r="L64" s="89" t="n">
         <v>2.75</v>
       </c>
     </row>
@@ -18152,23 +18268,21 @@
           <t>F06-03-2</t>
         </is>
       </c>
-      <c r="B65" s="17" t="n"/>
-      <c r="C65" s="32" t="inlineStr">
+      <c r="B65" s="103" t="n"/>
+      <c r="C65" s="17" t="n"/>
+      <c r="D65" s="32" t="inlineStr">
         <is>
           <t>大批量导出告警</t>
         </is>
       </c>
-      <c r="D65" s="32" t="inlineStr">
+      <c r="E65" s="32" t="inlineStr">
         <is>
           <t>阈值告警、审批联动</t>
         </is>
       </c>
-      <c r="E65" s="46" t="n"/>
-      <c r="F65" s="46" t="n">
+      <c r="F65" s="46" t="n"/>
+      <c r="G65" s="46" t="n">
         <v>0.5</v>
-      </c>
-      <c r="G65" s="46" t="n">
-        <v>0.25</v>
       </c>
       <c r="H65" s="46" t="n">
         <v>0.25</v>
@@ -18177,9 +18291,12 @@
         <v>0.25</v>
       </c>
       <c r="J65" s="46" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="K65" s="46" t="n">
         <v>1.25</v>
       </c>
-      <c r="K65" s="17" t="n"/>
+      <c r="L65" s="17" t="n"/>
     </row>
     <row r="66" ht="26" customHeight="1">
       <c r="A66" s="15" t="inlineStr">
@@ -18187,38 +18304,43 @@
           <t>F08-01-1</t>
         </is>
       </c>
-      <c r="B66" s="101" t="inlineStr">
-        <is>
-          <t>基础角色权限配置（模块8·系统全局治理、运维与监控）</t>
-        </is>
-      </c>
-      <c r="C66" s="32" t="inlineStr">
+      <c r="B66" s="112" t="inlineStr">
+        <is>
+          <t>模块8·系统全局治理、运维与监控</t>
+        </is>
+      </c>
+      <c r="C66" s="101" t="inlineStr">
+        <is>
+          <t>基础角色权限配置</t>
+        </is>
+      </c>
+      <c r="D66" s="32" t="inlineStr">
         <is>
           <t>RBAC模型与权限矩阵</t>
         </is>
       </c>
-      <c r="D66" s="32" t="inlineStr">
+      <c r="E66" s="32" t="inlineStr">
         <is>
           <t>角色/菜单/数据范围/记录类型/操作权限定义</t>
         </is>
       </c>
-      <c r="E66" s="46" t="n">
+      <c r="F66" s="46" t="n">
         <v>1</v>
       </c>
-      <c r="F66" s="46" t="n"/>
-      <c r="G66" s="46" t="n">
+      <c r="G66" s="46" t="n"/>
+      <c r="H66" s="46" t="n">
         <v>0.5</v>
       </c>
-      <c r="H66" s="46" t="n">
+      <c r="I66" s="46" t="n">
         <v>0.25</v>
       </c>
-      <c r="I66" s="46" t="n">
+      <c r="J66" s="46" t="n">
         <v>0.5</v>
       </c>
-      <c r="J66" s="46" t="n">
+      <c r="K66" s="46" t="n">
         <v>2.25</v>
       </c>
-      <c r="K66" s="92" t="n">
+      <c r="L66" s="92" t="n">
         <v>7.5</v>
       </c>
     </row>
@@ -18228,34 +18350,35 @@
           <t>F08-01-2</t>
         </is>
       </c>
-      <c r="B67" s="17" t="n"/>
-      <c r="C67" s="32" t="inlineStr">
+      <c r="B67" s="102" t="n"/>
+      <c r="C67" s="17" t="n"/>
+      <c r="D67" s="32" t="inlineStr">
         <is>
           <t>角色管理界面与API</t>
         </is>
       </c>
-      <c r="D67" s="32" t="inlineStr">
+      <c r="E67" s="32" t="inlineStr">
         <is>
           <t>角色CRUD、权限分配界面与接口</t>
         </is>
       </c>
-      <c r="E67" s="46" t="n"/>
-      <c r="F67" s="46" t="n">
+      <c r="F67" s="46" t="n"/>
+      <c r="G67" s="46" t="n">
         <v>2</v>
-      </c>
-      <c r="G67" s="46" t="n">
-        <v>0.5</v>
       </c>
       <c r="H67" s="46" t="n">
         <v>0.5</v>
       </c>
       <c r="I67" s="46" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J67" s="46" t="n">
         <v>0.25</v>
       </c>
-      <c r="J67" s="46" t="n">
+      <c r="K67" s="46" t="n">
         <v>3.25</v>
       </c>
-      <c r="K67" s="17" t="n"/>
+      <c r="L67" s="17" t="n"/>
     </row>
     <row r="68" ht="26" customHeight="1">
       <c r="A68" s="15" t="inlineStr">
@@ -18263,32 +18386,33 @@
           <t>F08-01-3</t>
         </is>
       </c>
-      <c r="B68" s="17" t="n"/>
-      <c r="C68" s="32" t="inlineStr">
+      <c r="B68" s="102" t="n"/>
+      <c r="C68" s="17" t="n"/>
+      <c r="D68" s="32" t="inlineStr">
         <is>
           <t>权限校验与UC授权映射</t>
         </is>
       </c>
-      <c r="D68" s="32" t="inlineStr">
+      <c r="E68" s="32" t="inlineStr">
         <is>
           <t>菜单/接口级校验中间件、UC权限同步</t>
         </is>
       </c>
-      <c r="E68" s="46" t="n"/>
       <c r="F68" s="46" t="n"/>
-      <c r="G68" s="46" t="n">
+      <c r="G68" s="46" t="n"/>
+      <c r="H68" s="46" t="n">
         <v>1</v>
       </c>
-      <c r="H68" s="46" t="n">
+      <c r="I68" s="46" t="n">
         <v>0.75</v>
       </c>
-      <c r="I68" s="46" t="n">
+      <c r="J68" s="46" t="n">
         <v>0.25</v>
       </c>
-      <c r="J68" s="46" t="n">
+      <c r="K68" s="46" t="n">
         <v>2</v>
       </c>
-      <c r="K68" s="17" t="n"/>
+      <c r="L68" s="17" t="n"/>
     </row>
     <row r="69" ht="26" customHeight="1">
       <c r="A69" s="15" t="inlineStr">
@@ -18296,40 +18420,41 @@
           <t>F08-02-1</t>
         </is>
       </c>
-      <c r="B69" s="101" t="inlineStr">
-        <is>
-          <t>用户账号管理（模块8·系统全局治理、运维与监控）</t>
-        </is>
-      </c>
-      <c r="C69" s="32" t="inlineStr">
+      <c r="B69" s="102" t="n"/>
+      <c r="C69" s="101" t="inlineStr">
+        <is>
+          <t>用户账号管理</t>
+        </is>
+      </c>
+      <c r="D69" s="32" t="inlineStr">
         <is>
           <t>账号CRUD与生命周期</t>
         </is>
       </c>
-      <c r="D69" s="32" t="inlineStr">
+      <c r="E69" s="32" t="inlineStr">
         <is>
           <t>创建/启用禁用/密码重置/有效期</t>
         </is>
       </c>
-      <c r="E69" s="46" t="n">
+      <c r="F69" s="46" t="n">
         <v>0.25</v>
       </c>
-      <c r="F69" s="46" t="n">
+      <c r="G69" s="46" t="n">
         <v>1</v>
       </c>
-      <c r="G69" s="46" t="n">
+      <c r="H69" s="46" t="n">
         <v>0.75</v>
       </c>
-      <c r="H69" s="46" t="n">
+      <c r="I69" s="46" t="n">
         <v>0.5</v>
       </c>
-      <c r="I69" s="46" t="n">
+      <c r="J69" s="46" t="n">
         <v>0.25</v>
       </c>
-      <c r="J69" s="46" t="n">
+      <c r="K69" s="46" t="n">
         <v>2.75</v>
       </c>
-      <c r="K69" s="92" t="n">
+      <c r="L69" s="92" t="n">
         <v>4</v>
       </c>
     </row>
@@ -18339,23 +18464,21 @@
           <t>F08-02-2</t>
         </is>
       </c>
-      <c r="B70" s="17" t="n"/>
-      <c r="C70" s="32" t="inlineStr">
+      <c r="B70" s="102" t="n"/>
+      <c r="C70" s="17" t="n"/>
+      <c r="D70" s="32" t="inlineStr">
         <is>
           <t>账号与角色绑定</t>
         </is>
       </c>
-      <c r="D70" s="32" t="inlineStr">
+      <c r="E70" s="32" t="inlineStr">
         <is>
           <t>分配、批量操作、人员交接</t>
         </is>
       </c>
-      <c r="E70" s="46" t="n"/>
-      <c r="F70" s="46" t="n">
+      <c r="F70" s="46" t="n"/>
+      <c r="G70" s="46" t="n">
         <v>0.5</v>
-      </c>
-      <c r="G70" s="46" t="n">
-        <v>0.25</v>
       </c>
       <c r="H70" s="46" t="n">
         <v>0.25</v>
@@ -18364,9 +18487,12 @@
         <v>0.25</v>
       </c>
       <c r="J70" s="46" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="K70" s="46" t="n">
         <v>1.25</v>
       </c>
-      <c r="K70" s="17" t="n"/>
+      <c r="L70" s="17" t="n"/>
     </row>
     <row r="71" ht="26" customHeight="1">
       <c r="A71" s="15" t="inlineStr">
@@ -18374,40 +18500,41 @@
           <t>F08-03-1</t>
         </is>
       </c>
-      <c r="B71" s="101" t="inlineStr">
-        <is>
-          <t>企业SSO集成（模块8·系统全局治理、运维与监控）</t>
-        </is>
-      </c>
-      <c r="C71" s="32" t="inlineStr">
+      <c r="B71" s="102" t="n"/>
+      <c r="C71" s="101" t="inlineStr">
+        <is>
+          <t>企业SSO集成</t>
+        </is>
+      </c>
+      <c r="D71" s="32" t="inlineStr">
         <is>
           <t>Entra ID对接配置</t>
         </is>
       </c>
-      <c r="D71" s="32" t="inlineStr">
+      <c r="E71" s="32" t="inlineStr">
         <is>
           <t>应用注册、回调配置、claims映射</t>
         </is>
       </c>
-      <c r="E71" s="46" t="n">
+      <c r="F71" s="46" t="n">
         <v>0.25</v>
       </c>
-      <c r="F71" s="46" t="n">
+      <c r="G71" s="46" t="n">
         <v>0.5</v>
       </c>
-      <c r="G71" s="46" t="n">
+      <c r="H71" s="46" t="n">
         <v>1</v>
       </c>
-      <c r="H71" s="46" t="n">
+      <c r="I71" s="46" t="n">
         <v>0.5</v>
       </c>
-      <c r="I71" s="46" t="n">
+      <c r="J71" s="46" t="n">
         <v>0.25</v>
       </c>
-      <c r="J71" s="46" t="n">
+      <c r="K71" s="46" t="n">
         <v>2.5</v>
       </c>
-      <c r="K71" s="92" t="n">
+      <c r="L71" s="92" t="n">
         <v>7.25</v>
       </c>
     </row>
@@ -18417,34 +18544,35 @@
           <t>F08-03-2</t>
         </is>
       </c>
-      <c r="B72" s="17" t="n"/>
-      <c r="C72" s="32" t="inlineStr">
+      <c r="B72" s="102" t="n"/>
+      <c r="C72" s="17" t="n"/>
+      <c r="D72" s="32" t="inlineStr">
         <is>
           <t>SSO登录链路</t>
         </is>
       </c>
-      <c r="D72" s="32" t="inlineStr">
+      <c r="E72" s="32" t="inlineStr">
         <is>
           <t>登录页、令牌交换、会话管理</t>
         </is>
       </c>
-      <c r="E72" s="46" t="n"/>
-      <c r="F72" s="46" t="n">
+      <c r="F72" s="46" t="n"/>
+      <c r="G72" s="46" t="n">
         <v>2</v>
       </c>
-      <c r="G72" s="46" t="n">
+      <c r="H72" s="46" t="n">
         <v>0.5</v>
       </c>
-      <c r="H72" s="46" t="n">
+      <c r="I72" s="46" t="n">
         <v>0.75</v>
       </c>
-      <c r="I72" s="46" t="n">
+      <c r="J72" s="46" t="n">
         <v>0.25</v>
       </c>
-      <c r="J72" s="46" t="n">
+      <c r="K72" s="46" t="n">
         <v>3.5</v>
       </c>
-      <c r="K72" s="17" t="n"/>
+      <c r="L72" s="17" t="n"/>
     </row>
     <row r="73" ht="26" customHeight="1">
       <c r="A73" s="15" t="inlineStr">
@@ -18452,32 +18580,33 @@
           <t>F08-03-3</t>
         </is>
       </c>
-      <c r="B73" s="17" t="n"/>
-      <c r="C73" s="32" t="inlineStr">
+      <c r="B73" s="102" t="n"/>
+      <c r="C73" s="17" t="n"/>
+      <c r="D73" s="32" t="inlineStr">
         <is>
           <t>认证异常场景处理</t>
         </is>
       </c>
-      <c r="D73" s="32" t="inlineStr">
+      <c r="E73" s="32" t="inlineStr">
         <is>
           <t>认证失败、账号锁定、多账号冲突</t>
         </is>
       </c>
-      <c r="E73" s="46" t="n"/>
-      <c r="F73" s="46" t="n">
+      <c r="F73" s="46" t="n"/>
+      <c r="G73" s="46" t="n">
         <v>0.5</v>
       </c>
-      <c r="G73" s="46" t="n"/>
-      <c r="H73" s="46" t="n">
+      <c r="H73" s="46" t="n"/>
+      <c r="I73" s="46" t="n">
         <v>0.5</v>
       </c>
-      <c r="I73" s="46" t="n">
+      <c r="J73" s="46" t="n">
         <v>0.25</v>
       </c>
-      <c r="J73" s="46" t="n">
+      <c r="K73" s="46" t="n">
         <v>1.25</v>
       </c>
-      <c r="K73" s="17" t="n"/>
+      <c r="L73" s="17" t="n"/>
     </row>
     <row r="74" ht="26" customHeight="1">
       <c r="A74" s="15" t="inlineStr">
@@ -18485,38 +18614,39 @@
           <t>F08-04-1</t>
         </is>
       </c>
-      <c r="B74" s="101" t="inlineStr">
-        <is>
-          <t>用户身份自动识别与关联（模块8·系统全局治理、运维与监控）</t>
-        </is>
-      </c>
-      <c r="C74" s="32" t="inlineStr">
+      <c r="B74" s="102" t="n"/>
+      <c r="C74" s="101" t="inlineStr">
+        <is>
+          <t>用户身份自动识别与关联</t>
+        </is>
+      </c>
+      <c r="D74" s="32" t="inlineStr">
         <is>
           <t>身份映射规则</t>
         </is>
       </c>
-      <c r="D74" s="32" t="inlineStr">
+      <c r="E74" s="32" t="inlineStr">
         <is>
           <t>企业账号↔RIMS用户映射、自动建号规则</t>
         </is>
       </c>
-      <c r="E74" s="46" t="n">
+      <c r="F74" s="46" t="n">
         <v>0.5</v>
       </c>
-      <c r="F74" s="46" t="n"/>
-      <c r="G74" s="46" t="n">
+      <c r="G74" s="46" t="n"/>
+      <c r="H74" s="46" t="n">
         <v>0.5</v>
-      </c>
-      <c r="H74" s="46" t="n">
-        <v>0.25</v>
       </c>
       <c r="I74" s="46" t="n">
         <v>0.25</v>
       </c>
       <c r="J74" s="46" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="K74" s="46" t="n">
         <v>1.5</v>
       </c>
-      <c r="K74" s="92" t="n">
+      <c r="L74" s="92" t="n">
         <v>3.25</v>
       </c>
     </row>
@@ -18526,34 +18656,35 @@
           <t>F08-04-2</t>
         </is>
       </c>
-      <c r="B75" s="17" t="n"/>
-      <c r="C75" s="32" t="inlineStr">
+      <c r="B75" s="102" t="n"/>
+      <c r="C75" s="17" t="n"/>
+      <c r="D75" s="32" t="inlineStr">
         <is>
           <t>首登自动关联与角色赋予</t>
         </is>
       </c>
-      <c r="D75" s="32" t="inlineStr">
+      <c r="E75" s="32" t="inlineStr">
         <is>
           <t>默认角色、待分配队列</t>
         </is>
       </c>
-      <c r="E75" s="46" t="n"/>
-      <c r="F75" s="46" t="n">
+      <c r="F75" s="46" t="n"/>
+      <c r="G75" s="46" t="n">
         <v>0.25</v>
       </c>
-      <c r="G75" s="46" t="n">
+      <c r="H75" s="46" t="n">
         <v>0.75</v>
       </c>
-      <c r="H75" s="46" t="n">
+      <c r="I75" s="46" t="n">
         <v>0.5</v>
       </c>
-      <c r="I75" s="46" t="n">
+      <c r="J75" s="46" t="n">
         <v>0.25</v>
       </c>
-      <c r="J75" s="46" t="n">
+      <c r="K75" s="46" t="n">
         <v>1.75</v>
       </c>
-      <c r="K75" s="17" t="n"/>
+      <c r="L75" s="17" t="n"/>
     </row>
     <row r="76" ht="26" customHeight="1">
       <c r="A76" s="15" t="inlineStr">
@@ -18561,40 +18692,41 @@
           <t>F08-05-1</t>
         </is>
       </c>
-      <c r="B76" s="101" t="inlineStr">
-        <is>
-          <t>登录状态与异常访问控制（模块8·系统全局治理、运维与监控）</t>
-        </is>
-      </c>
-      <c r="C76" s="32" t="inlineStr">
+      <c r="B76" s="102" t="n"/>
+      <c r="C76" s="101" t="inlineStr">
+        <is>
+          <t>登录状态与异常访问控制</t>
+        </is>
+      </c>
+      <c r="D76" s="32" t="inlineStr">
         <is>
           <t>会话与超时策略</t>
         </is>
       </c>
-      <c r="D76" s="32" t="inlineStr">
+      <c r="E76" s="32" t="inlineStr">
         <is>
           <t>超时控制、登出、单点登出</t>
         </is>
       </c>
-      <c r="E76" s="46" t="n">
+      <c r="F76" s="46" t="n">
         <v>0.25</v>
       </c>
-      <c r="F76" s="46" t="n">
+      <c r="G76" s="46" t="n">
         <v>1</v>
       </c>
-      <c r="G76" s="46" t="n">
+      <c r="H76" s="46" t="n">
         <v>0.25</v>
       </c>
-      <c r="H76" s="46" t="n">
+      <c r="I76" s="46" t="n">
         <v>0.5</v>
       </c>
-      <c r="I76" s="46" t="n">
+      <c r="J76" s="46" t="n">
         <v>0.25</v>
       </c>
-      <c r="J76" s="46" t="n">
+      <c r="K76" s="46" t="n">
         <v>2.25</v>
       </c>
-      <c r="K76" s="92" t="n">
+      <c r="L76" s="92" t="n">
         <v>3.75</v>
       </c>
     </row>
@@ -18604,32 +18736,33 @@
           <t>F08-05-2</t>
         </is>
       </c>
-      <c r="B77" s="17" t="n"/>
-      <c r="C77" s="32" t="inlineStr">
+      <c r="B77" s="103" t="n"/>
+      <c r="C77" s="17" t="n"/>
+      <c r="D77" s="32" t="inlineStr">
         <is>
           <t>异常访问控制</t>
         </is>
       </c>
-      <c r="D77" s="32" t="inlineStr">
+      <c r="E77" s="32" t="inlineStr">
         <is>
           <t>账号锁定、认证失效限制访问、IP策略</t>
         </is>
       </c>
-      <c r="E77" s="46" t="n"/>
       <c r="F77" s="46" t="n"/>
-      <c r="G77" s="46" t="n">
+      <c r="G77" s="46" t="n"/>
+      <c r="H77" s="46" t="n">
         <v>0.75</v>
       </c>
-      <c r="H77" s="46" t="n">
+      <c r="I77" s="46" t="n">
         <v>0.5</v>
       </c>
-      <c r="I77" s="46" t="n">
+      <c r="J77" s="46" t="n">
         <v>0.25</v>
       </c>
-      <c r="J77" s="46" t="n">
+      <c r="K77" s="46" t="n">
         <v>1.5</v>
       </c>
-      <c r="K77" s="17" t="n"/>
+      <c r="L77" s="17" t="n"/>
     </row>
     <row r="78" ht="26" customHeight="1">
       <c r="A78" s="15" t="inlineStr">
@@ -18637,36 +18770,41 @@
           <t>N1-1</t>
         </is>
       </c>
-      <c r="B78" s="99" t="inlineStr">
-        <is>
-          <t>【非功能】工程初始化与开发基座</t>
-        </is>
-      </c>
-      <c r="C78" s="32" t="inlineStr">
+      <c r="B78" s="113" t="inlineStr">
+        <is>
+          <t>非功能与工程支撑</t>
+        </is>
+      </c>
+      <c r="C78" s="99" t="inlineStr">
+        <is>
+          <t>工程初始化与开发基座</t>
+        </is>
+      </c>
+      <c r="D78" s="32" t="inlineStr">
         <is>
           <t>项目初始化</t>
         </is>
       </c>
-      <c r="D78" s="32" t="inlineStr">
+      <c r="E78" s="32" t="inlineStr">
         <is>
           <t>代码仓库/分支策略/开发环境统一/AI工具账号开通</t>
         </is>
       </c>
-      <c r="E78" s="46" t="n"/>
-      <c r="F78" s="46" t="n">
+      <c r="F78" s="46" t="n"/>
+      <c r="G78" s="46" t="n">
         <v>1</v>
-      </c>
-      <c r="G78" s="46" t="n">
-        <v>0.25</v>
       </c>
       <c r="H78" s="46" t="n">
         <v>0.25</v>
       </c>
-      <c r="I78" s="46" t="n"/>
-      <c r="J78" s="46" t="n">
+      <c r="I78" s="46" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="J78" s="46" t="n"/>
+      <c r="K78" s="46" t="n">
         <v>1.5</v>
       </c>
-      <c r="K78" s="86" t="n">
+      <c r="L78" s="86" t="n">
         <v>10.75</v>
       </c>
     </row>
@@ -18676,30 +18814,31 @@
           <t>N1-2</t>
         </is>
       </c>
-      <c r="B79" s="17" t="n"/>
-      <c r="C79" s="32" t="inlineStr">
+      <c r="B79" s="102" t="n"/>
+      <c r="C79" s="17" t="n"/>
+      <c r="D79" s="32" t="inlineStr">
         <is>
           <t>前端工程初始化</t>
         </is>
       </c>
-      <c r="D79" s="32" t="inlineStr">
+      <c r="E79" s="32" t="inlineStr">
         <is>
           <t>React骨架/路由/布局/组件库/状态管理/构建链</t>
         </is>
       </c>
-      <c r="E79" s="46" t="n"/>
-      <c r="F79" s="46" t="n">
+      <c r="F79" s="46" t="n"/>
+      <c r="G79" s="46" t="n">
         <v>1.5</v>
       </c>
-      <c r="G79" s="46" t="n"/>
-      <c r="H79" s="46" t="n">
+      <c r="H79" s="46" t="n"/>
+      <c r="I79" s="46" t="n">
         <v>0.25</v>
       </c>
-      <c r="I79" s="46" t="n"/>
-      <c r="J79" s="46" t="n">
+      <c r="J79" s="46" t="n"/>
+      <c r="K79" s="46" t="n">
         <v>1.75</v>
       </c>
-      <c r="K79" s="17" t="n"/>
+      <c r="L79" s="17" t="n"/>
     </row>
     <row r="80" ht="26" customHeight="1">
       <c r="A80" s="15" t="inlineStr">
@@ -18707,30 +18846,31 @@
           <t>N1-3</t>
         </is>
       </c>
-      <c r="B80" s="17" t="n"/>
-      <c r="C80" s="32" t="inlineStr">
+      <c r="B80" s="102" t="n"/>
+      <c r="C80" s="17" t="n"/>
+      <c r="D80" s="32" t="inlineStr">
         <is>
           <t>后端工程初始化</t>
         </is>
       </c>
-      <c r="D80" s="32" t="inlineStr">
+      <c r="E80" s="32" t="inlineStr">
         <is>
           <t>.NET Clean Architecture/EF Core/Docker Compose本地环境</t>
         </is>
       </c>
-      <c r="E80" s="46" t="n"/>
       <c r="F80" s="46" t="n"/>
-      <c r="G80" s="46" t="n">
+      <c r="G80" s="46" t="n"/>
+      <c r="H80" s="46" t="n">
         <v>1.5</v>
       </c>
-      <c r="H80" s="46" t="n">
+      <c r="I80" s="46" t="n">
         <v>0.25</v>
       </c>
-      <c r="I80" s="46" t="n"/>
-      <c r="J80" s="46" t="n">
+      <c r="J80" s="46" t="n"/>
+      <c r="K80" s="46" t="n">
         <v>1.75</v>
       </c>
-      <c r="K80" s="17" t="n"/>
+      <c r="L80" s="17" t="n"/>
     </row>
     <row r="81" ht="26" customHeight="1">
       <c r="A81" s="15" t="inlineStr">
@@ -18738,32 +18878,33 @@
           <t>N1-4</t>
         </is>
       </c>
-      <c r="B81" s="17" t="n"/>
-      <c r="C81" s="32" t="inlineStr">
+      <c r="B81" s="102" t="n"/>
+      <c r="C81" s="17" t="n"/>
+      <c r="D81" s="32" t="inlineStr">
         <is>
           <t>AI开发工具链与编码规范</t>
         </is>
       </c>
-      <c r="D81" s="32" t="inlineStr">
+      <c r="E81" s="32" t="inlineStr">
         <is>
           <t>提示词模板库/人机协作规约/ADR规范</t>
         </is>
       </c>
-      <c r="E81" s="46" t="n"/>
-      <c r="F81" s="46" t="n">
+      <c r="F81" s="46" t="n"/>
+      <c r="G81" s="46" t="n">
         <v>1</v>
       </c>
-      <c r="G81" s="46" t="n">
+      <c r="H81" s="46" t="n">
         <v>0.25</v>
       </c>
-      <c r="H81" s="46" t="n"/>
-      <c r="I81" s="46" t="n">
+      <c r="I81" s="46" t="n"/>
+      <c r="J81" s="46" t="n">
         <v>0.25</v>
       </c>
-      <c r="J81" s="46" t="n">
+      <c r="K81" s="46" t="n">
         <v>1.5</v>
       </c>
-      <c r="K81" s="17" t="n"/>
+      <c r="L81" s="17" t="n"/>
     </row>
     <row r="82" ht="26" customHeight="1">
       <c r="A82" s="15" t="inlineStr">
@@ -18771,34 +18912,35 @@
           <t>N1-5</t>
         </is>
       </c>
-      <c r="B82" s="17" t="n"/>
-      <c r="C82" s="32" t="inlineStr">
+      <c r="B82" s="102" t="n"/>
+      <c r="C82" s="17" t="n"/>
+      <c r="D82" s="32" t="inlineStr">
         <is>
           <t>四道安全门禁CI/CD</t>
         </is>
       </c>
-      <c r="D82" s="32" t="inlineStr">
+      <c r="E82" s="32" t="inlineStr">
         <is>
           <t>构建/镜像/SAST·依赖·密钥扫描/越权用例门禁，流水线落地与拦截演示</t>
         </is>
       </c>
-      <c r="E82" s="46" t="n"/>
-      <c r="F82" s="46" t="n">
+      <c r="F82" s="46" t="n"/>
+      <c r="G82" s="46" t="n">
         <v>3</v>
-      </c>
-      <c r="G82" s="46" t="n">
-        <v>0.5</v>
       </c>
       <c r="H82" s="46" t="n">
         <v>0.5</v>
       </c>
       <c r="I82" s="46" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J82" s="46" t="n">
         <v>0.25</v>
       </c>
-      <c r="J82" s="46" t="n">
+      <c r="K82" s="46" t="n">
         <v>4.25</v>
       </c>
-      <c r="K82" s="17" t="n"/>
+      <c r="L82" s="17" t="n"/>
     </row>
     <row r="83" ht="26" customHeight="1">
       <c r="A83" s="15" t="inlineStr">
@@ -18806,32 +18948,33 @@
           <t>N2-1</t>
         </is>
       </c>
-      <c r="B83" s="99" t="inlineStr">
-        <is>
-          <t>【非功能】代码质量与静态扫描治理</t>
-        </is>
-      </c>
-      <c r="C83" s="32" t="inlineStr">
+      <c r="B83" s="102" t="n"/>
+      <c r="C83" s="99" t="inlineStr">
+        <is>
+          <t>代码质量与静态扫描治理</t>
+        </is>
+      </c>
+      <c r="D83" s="32" t="inlineStr">
         <is>
           <t>前端ESLint/Prettier规约</t>
         </is>
       </c>
-      <c r="D83" s="32" t="inlineStr">
+      <c r="E83" s="32" t="inlineStr">
         <is>
           <t>规则集接入CI、存量告警清零、格式统一</t>
         </is>
       </c>
-      <c r="E83" s="46" t="n"/>
-      <c r="F83" s="46" t="n">
+      <c r="F83" s="46" t="n"/>
+      <c r="G83" s="46" t="n">
         <v>1.5</v>
       </c>
-      <c r="G83" s="46" t="n"/>
       <c r="H83" s="46" t="n"/>
       <c r="I83" s="46" t="n"/>
-      <c r="J83" s="46" t="n">
+      <c r="J83" s="46" t="n"/>
+      <c r="K83" s="46" t="n">
         <v>1.5</v>
       </c>
-      <c r="K83" s="86" t="n">
+      <c r="L83" s="86" t="n">
         <v>8.75</v>
       </c>
     </row>
@@ -18841,28 +18984,29 @@
           <t>N2-2</t>
         </is>
       </c>
-      <c r="B84" s="17" t="n"/>
-      <c r="C84" s="32" t="inlineStr">
+      <c r="B84" s="102" t="n"/>
+      <c r="C84" s="17" t="n"/>
+      <c r="D84" s="32" t="inlineStr">
         <is>
           <t>后端SonarLint规约</t>
         </is>
       </c>
-      <c r="D84" s="32" t="inlineStr">
+      <c r="E84" s="32" t="inlineStr">
         <is>
           <t>代码异味/重复块/复杂度阈值治理清零</t>
         </is>
       </c>
-      <c r="E84" s="46" t="n"/>
       <c r="F84" s="46" t="n"/>
-      <c r="G84" s="46" t="n">
+      <c r="G84" s="46" t="n"/>
+      <c r="H84" s="46" t="n">
         <v>1.5</v>
       </c>
-      <c r="H84" s="46" t="n"/>
       <c r="I84" s="46" t="n"/>
-      <c r="J84" s="46" t="n">
+      <c r="J84" s="46" t="n"/>
+      <c r="K84" s="46" t="n">
         <v>1.5</v>
       </c>
-      <c r="K84" s="17" t="n"/>
+      <c r="L84" s="17" t="n"/>
     </row>
     <row r="85" ht="26" customHeight="1">
       <c r="A85" s="15" t="inlineStr">
@@ -18870,32 +19014,33 @@
           <t>N2-3</t>
         </is>
       </c>
-      <c r="B85" s="17" t="n"/>
-      <c r="C85" s="32" t="inlineStr">
+      <c r="B85" s="102" t="n"/>
+      <c r="C85" s="17" t="n"/>
+      <c r="D85" s="32" t="inlineStr">
         <is>
           <t>SAST安全告警修复</t>
         </is>
       </c>
-      <c r="D85" s="32" t="inlineStr">
+      <c r="E85" s="32" t="inlineStr">
         <is>
           <t>硬编码密钥/注入/越权路径等静态安全缺陷修复</t>
         </is>
       </c>
-      <c r="E85" s="46" t="n"/>
-      <c r="F85" s="46" t="n">
-        <v>1</v>
-      </c>
+      <c r="F85" s="46" t="n"/>
       <c r="G85" s="46" t="n">
         <v>1</v>
       </c>
       <c r="H85" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="I85" s="46" t="n">
         <v>0.25</v>
       </c>
-      <c r="I85" s="46" t="n"/>
-      <c r="J85" s="46" t="n">
+      <c r="J85" s="46" t="n"/>
+      <c r="K85" s="46" t="n">
         <v>2.25</v>
       </c>
-      <c r="K85" s="17" t="n"/>
+      <c r="L85" s="17" t="n"/>
     </row>
     <row r="86" ht="26" customHeight="1">
       <c r="A86" s="15" t="inlineStr">
@@ -18903,32 +19048,33 @@
           <t>N2-4</t>
         </is>
       </c>
-      <c r="B86" s="17" t="n"/>
-      <c r="C86" s="32" t="inlineStr">
+      <c r="B86" s="102" t="n"/>
+      <c r="C86" s="17" t="n"/>
+      <c r="D86" s="32" t="inlineStr">
         <is>
           <t>依赖漏洞治理（SCA）</t>
         </is>
       </c>
-      <c r="D86" s="32" t="inlineStr">
+      <c r="E86" s="32" t="inlineStr">
         <is>
           <t>依赖版本锁定、漏洞升级、SBOM产出</t>
         </is>
       </c>
-      <c r="E86" s="46" t="n"/>
-      <c r="F86" s="46" t="n">
-        <v>0.5</v>
-      </c>
+      <c r="F86" s="46" t="n"/>
       <c r="G86" s="46" t="n">
         <v>0.5</v>
       </c>
-      <c r="H86" s="46" t="n"/>
-      <c r="I86" s="46" t="n">
+      <c r="H86" s="46" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I86" s="46" t="n"/>
+      <c r="J86" s="46" t="n">
         <v>0.25</v>
       </c>
-      <c r="J86" s="46" t="n">
+      <c r="K86" s="46" t="n">
         <v>1.25</v>
       </c>
-      <c r="K86" s="17" t="n"/>
+      <c r="L86" s="17" t="n"/>
     </row>
     <row r="87" ht="26" customHeight="1">
       <c r="A87" s="15" t="inlineStr">
@@ -18936,32 +19082,33 @@
           <t>N2-5</t>
         </is>
       </c>
-      <c r="B87" s="17" t="n"/>
-      <c r="C87" s="32" t="inlineStr">
+      <c r="B87" s="102" t="n"/>
+      <c r="C87" s="17" t="n"/>
+      <c r="D87" s="32" t="inlineStr">
         <is>
           <t>技术债偿还与外部评审落实</t>
         </is>
       </c>
-      <c r="D87" s="32" t="inlineStr">
+      <c r="E87" s="32" t="inlineStr">
         <is>
           <t>每周固定还债窗口、关键模块重构、评审意见闭环</t>
         </is>
       </c>
-      <c r="E87" s="46" t="n"/>
-      <c r="F87" s="46" t="n">
-        <v>1</v>
-      </c>
+      <c r="F87" s="46" t="n"/>
       <c r="G87" s="46" t="n">
         <v>1</v>
       </c>
       <c r="H87" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="I87" s="46" t="n">
         <v>0.25</v>
       </c>
-      <c r="I87" s="46" t="n"/>
-      <c r="J87" s="46" t="n">
+      <c r="J87" s="46" t="n"/>
+      <c r="K87" s="46" t="n">
         <v>2.25</v>
       </c>
-      <c r="K87" s="17" t="n"/>
+      <c r="L87" s="17" t="n"/>
     </row>
     <row r="88" ht="26" customHeight="1">
       <c r="A88" s="15" t="inlineStr">
@@ -18969,34 +19116,35 @@
           <t>N3-1</t>
         </is>
       </c>
-      <c r="B88" s="99" t="inlineStr">
-        <is>
-          <t>【非功能】全局非功能实现与优化</t>
-        </is>
-      </c>
-      <c r="C88" s="32" t="inlineStr">
+      <c r="B88" s="102" t="n"/>
+      <c r="C88" s="99" t="inlineStr">
+        <is>
+          <t>全局非功能实现与优化</t>
+        </is>
+      </c>
+      <c r="D88" s="32" t="inlineStr">
         <is>
           <t>前端性能优化</t>
         </is>
       </c>
-      <c r="D88" s="32" t="inlineStr">
+      <c r="E88" s="32" t="inlineStr">
         <is>
           <t>懒加载/虚拟滚动/缓存/首屏指标（对照NFR基线）</t>
         </is>
       </c>
-      <c r="E88" s="46" t="n"/>
-      <c r="F88" s="46" t="n">
+      <c r="F88" s="46" t="n"/>
+      <c r="G88" s="46" t="n">
         <v>1.5</v>
       </c>
-      <c r="G88" s="46" t="n"/>
-      <c r="H88" s="46" t="n">
+      <c r="H88" s="46" t="n"/>
+      <c r="I88" s="46" t="n">
         <v>0.5</v>
       </c>
-      <c r="I88" s="46" t="n"/>
-      <c r="J88" s="46" t="n">
+      <c r="J88" s="46" t="n"/>
+      <c r="K88" s="46" t="n">
         <v>2</v>
       </c>
-      <c r="K88" s="86" t="n">
+      <c r="L88" s="86" t="n">
         <v>11</v>
       </c>
     </row>
@@ -19006,30 +19154,31 @@
           <t>N3-2</t>
         </is>
       </c>
-      <c r="B89" s="17" t="n"/>
-      <c r="C89" s="32" t="inlineStr">
+      <c r="B89" s="102" t="n"/>
+      <c r="C89" s="17" t="n"/>
+      <c r="D89" s="32" t="inlineStr">
         <is>
           <t>查询与数据性能</t>
         </is>
       </c>
-      <c r="D89" s="32" t="inlineStr">
+      <c r="E89" s="32" t="inlineStr">
         <is>
           <t>分区裁剪/Z-Order/Compaction/小文件治理</t>
         </is>
       </c>
-      <c r="E89" s="46" t="n"/>
       <c r="F89" s="46" t="n"/>
-      <c r="G89" s="46" t="n">
+      <c r="G89" s="46" t="n"/>
+      <c r="H89" s="46" t="n">
         <v>1.5</v>
       </c>
-      <c r="H89" s="46" t="n">
+      <c r="I89" s="46" t="n">
         <v>0.5</v>
       </c>
-      <c r="I89" s="46" t="n"/>
-      <c r="J89" s="46" t="n">
+      <c r="J89" s="46" t="n"/>
+      <c r="K89" s="46" t="n">
         <v>2</v>
       </c>
-      <c r="K89" s="17" t="n"/>
+      <c r="L89" s="17" t="n"/>
     </row>
     <row r="90" ht="26" customHeight="1">
       <c r="A90" s="15" t="inlineStr">
@@ -19037,34 +19186,35 @@
           <t>N3-3</t>
         </is>
       </c>
-      <c r="B90" s="17" t="n"/>
-      <c r="C90" s="32" t="inlineStr">
+      <c r="B90" s="102" t="n"/>
+      <c r="C90" s="17" t="n"/>
+      <c r="D90" s="32" t="inlineStr">
         <is>
           <t>统一鉴权与数据掩码中间件</t>
         </is>
       </c>
-      <c r="D90" s="32" t="inlineStr">
+      <c r="E90" s="32" t="inlineStr">
         <is>
           <t>菜单/API/行级三层校验、掩码旁路防护</t>
         </is>
       </c>
-      <c r="E90" s="46" t="n">
+      <c r="F90" s="46" t="n">
         <v>0.25</v>
-      </c>
-      <c r="F90" s="46" t="n">
-        <v>1</v>
       </c>
       <c r="G90" s="46" t="n">
         <v>1</v>
       </c>
       <c r="H90" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="I90" s="46" t="n">
         <v>0.75</v>
       </c>
-      <c r="I90" s="46" t="n"/>
-      <c r="J90" s="46" t="n">
+      <c r="J90" s="46" t="n"/>
+      <c r="K90" s="46" t="n">
         <v>3</v>
       </c>
-      <c r="K90" s="17" t="n"/>
+      <c r="L90" s="17" t="n"/>
     </row>
     <row r="91" ht="26" customHeight="1">
       <c r="A91" s="15" t="inlineStr">
@@ -19072,32 +19222,33 @@
           <t>N3-4</t>
         </is>
       </c>
-      <c r="B91" s="17" t="n"/>
-      <c r="C91" s="32" t="inlineStr">
+      <c r="B91" s="102" t="n"/>
+      <c r="C91" s="17" t="n"/>
+      <c r="D91" s="32" t="inlineStr">
         <is>
           <t>可观测性（日志/监控/告警）</t>
         </is>
       </c>
-      <c r="D91" s="32" t="inlineStr">
+      <c r="E91" s="32" t="inlineStr">
         <is>
           <t>应用日志规范、作业监控、异常告警通道</t>
         </is>
       </c>
-      <c r="E91" s="46" t="n"/>
-      <c r="F91" s="46" t="n">
+      <c r="F91" s="46" t="n"/>
+      <c r="G91" s="46" t="n">
         <v>0.5</v>
       </c>
-      <c r="G91" s="46" t="n">
+      <c r="H91" s="46" t="n">
         <v>1.5</v>
       </c>
-      <c r="H91" s="46" t="n">
+      <c r="I91" s="46" t="n">
         <v>0.25</v>
       </c>
-      <c r="I91" s="46" t="n"/>
-      <c r="J91" s="46" t="n">
+      <c r="J91" s="46" t="n"/>
+      <c r="K91" s="46" t="n">
         <v>2.25</v>
       </c>
-      <c r="K91" s="17" t="n"/>
+      <c r="L91" s="17" t="n"/>
     </row>
     <row r="92" ht="26" customHeight="1">
       <c r="A92" s="15" t="inlineStr">
@@ -19105,32 +19256,33 @@
           <t>N3-5</t>
         </is>
       </c>
-      <c r="B92" s="17" t="n"/>
-      <c r="C92" s="32" t="inlineStr">
+      <c r="B92" s="102" t="n"/>
+      <c r="C92" s="17" t="n"/>
+      <c r="D92" s="32" t="inlineStr">
         <is>
           <t>容量与增长验证</t>
         </is>
       </c>
-      <c r="D92" s="32" t="inlineStr">
+      <c r="E92" s="32" t="inlineStr">
         <is>
           <t>600~800表规模扩容压测与容量报告</t>
         </is>
       </c>
-      <c r="E92" s="46" t="n"/>
       <c r="F92" s="46" t="n"/>
-      <c r="G92" s="46" t="n">
+      <c r="G92" s="46" t="n"/>
+      <c r="H92" s="46" t="n">
         <v>1</v>
       </c>
-      <c r="H92" s="46" t="n">
+      <c r="I92" s="46" t="n">
         <v>0.5</v>
       </c>
-      <c r="I92" s="46" t="n">
+      <c r="J92" s="46" t="n">
         <v>0.25</v>
       </c>
-      <c r="J92" s="46" t="n">
+      <c r="K92" s="46" t="n">
         <v>1.75</v>
       </c>
-      <c r="K92" s="17" t="n"/>
+      <c r="L92" s="17" t="n"/>
     </row>
     <row r="93" ht="26" customHeight="1">
       <c r="A93" s="15" t="inlineStr">
@@ -19138,36 +19290,37 @@
           <t>N4-1</t>
         </is>
       </c>
-      <c r="B93" s="99" t="inlineStr">
-        <is>
-          <t>【非功能】部署与运维支撑</t>
-        </is>
-      </c>
-      <c r="C93" s="32" t="inlineStr">
+      <c r="B93" s="102" t="n"/>
+      <c r="C93" s="99" t="inlineStr">
+        <is>
+          <t>部署与运维支撑</t>
+        </is>
+      </c>
+      <c r="D93" s="32" t="inlineStr">
         <is>
           <t>Helm发布包与values</t>
         </is>
       </c>
-      <c r="D93" s="32" t="inlineStr">
+      <c r="E93" s="32" t="inlineStr">
         <is>
           <t>生产values/镜像标签策略/发布Runbook</t>
         </is>
       </c>
-      <c r="E93" s="46" t="n"/>
-      <c r="F93" s="46" t="n">
+      <c r="F93" s="46" t="n"/>
+      <c r="G93" s="46" t="n">
         <v>1</v>
       </c>
-      <c r="G93" s="46" t="n">
+      <c r="H93" s="46" t="n">
         <v>0.25</v>
       </c>
-      <c r="H93" s="46" t="n"/>
-      <c r="I93" s="46" t="n">
+      <c r="I93" s="46" t="n"/>
+      <c r="J93" s="46" t="n">
         <v>0.25</v>
       </c>
-      <c r="J93" s="46" t="n">
+      <c r="K93" s="46" t="n">
         <v>1.5</v>
       </c>
-      <c r="K93" s="86" t="n">
+      <c r="L93" s="86" t="n">
         <v>5.5</v>
       </c>
     </row>
@@ -19177,32 +19330,33 @@
           <t>N4-2</t>
         </is>
       </c>
-      <c r="B94" s="17" t="n"/>
-      <c r="C94" s="32" t="inlineStr">
+      <c r="B94" s="102" t="n"/>
+      <c r="C94" s="17" t="n"/>
+      <c r="D94" s="32" t="inlineStr">
         <is>
           <t>部署预演与回退预案</t>
         </is>
       </c>
-      <c r="D94" s="32" t="inlineStr">
+      <c r="E94" s="32" t="inlineStr">
         <is>
           <t>Staging完整演练、回退验证</t>
         </is>
       </c>
-      <c r="E94" s="46" t="n"/>
-      <c r="F94" s="46" t="n">
+      <c r="F94" s="46" t="n"/>
+      <c r="G94" s="46" t="n">
         <v>1</v>
       </c>
-      <c r="G94" s="46" t="n">
+      <c r="H94" s="46" t="n">
         <v>0.5</v>
       </c>
-      <c r="H94" s="46" t="n">
+      <c r="I94" s="46" t="n">
         <v>0.25</v>
       </c>
-      <c r="I94" s="46" t="n"/>
-      <c r="J94" s="46" t="n">
+      <c r="J94" s="46" t="n"/>
+      <c r="K94" s="46" t="n">
         <v>1.75</v>
       </c>
-      <c r="K94" s="17" t="n"/>
+      <c r="L94" s="17" t="n"/>
     </row>
     <row r="95" ht="26" customHeight="1">
       <c r="A95" s="15" t="inlineStr">
@@ -19210,32 +19364,33 @@
           <t>N4-3</t>
         </is>
       </c>
-      <c r="B95" s="17" t="n"/>
-      <c r="C95" s="32" t="inlineStr">
+      <c r="B95" s="103" t="n"/>
+      <c r="C95" s="17" t="n"/>
+      <c r="D95" s="32" t="inlineStr">
         <is>
           <t>上线值守与运维交接</t>
         </is>
       </c>
-      <c r="D95" s="32" t="inlineStr">
+      <c r="E95" s="32" t="inlineStr">
         <is>
           <t>上线窗口值守、运维交接与培训材料</t>
         </is>
       </c>
-      <c r="E95" s="46" t="n"/>
-      <c r="F95" s="46" t="n">
-        <v>1</v>
-      </c>
+      <c r="F95" s="46" t="n"/>
       <c r="G95" s="46" t="n">
         <v>1</v>
       </c>
-      <c r="H95" s="46" t="n"/>
-      <c r="I95" s="46" t="n">
+      <c r="H95" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="I95" s="46" t="n"/>
+      <c r="J95" s="46" t="n">
         <v>0.25</v>
       </c>
-      <c r="J95" s="46" t="n">
+      <c r="K95" s="46" t="n">
         <v>2.25</v>
       </c>
-      <c r="K95" s="17" t="n"/>
+      <c r="L95" s="17" t="n"/>
     </row>
     <row r="96">
       <c r="A96" s="8" t="inlineStr"/>
@@ -19244,35 +19399,36 @@
           <t>总计</t>
         </is>
       </c>
-      <c r="C96" s="93" t="inlineStr">
+      <c r="C96" s="8" t="inlineStr"/>
+      <c r="D96" s="93" t="inlineStr">
         <is>
           <t>26项功能×75子任务 + 非功能工程×18子任务</t>
         </is>
       </c>
-      <c r="D96" s="93" t="inlineStr">
+      <c r="E96" s="93" t="inlineStr">
         <is>
           <t>独立直估（另含少量需求/PM等工作未列入本表）</t>
         </is>
       </c>
-      <c r="E96" s="44" t="n">
+      <c r="F96" s="44" t="n">
         <v>13</v>
       </c>
-      <c r="F96" s="44" t="n">
+      <c r="G96" s="44" t="n">
         <v>60.25</v>
       </c>
-      <c r="G96" s="44" t="n">
+      <c r="H96" s="44" t="n">
         <v>75.25</v>
       </c>
-      <c r="H96" s="44" t="n">
+      <c r="I96" s="44" t="n">
         <v>40.25</v>
       </c>
-      <c r="I96" s="44" t="n">
+      <c r="J96" s="44" t="n">
         <v>21.5</v>
       </c>
-      <c r="J96" s="44" t="n">
+      <c r="K96" s="44" t="n">
         <v>210.25</v>
       </c>
-      <c r="K96" s="8" t="inlineStr"/>
+      <c r="L96" s="8" t="inlineStr"/>
     </row>
     <row r="98" ht="56" customHeight="1">
       <c r="A98" s="94" t="inlineStr">
@@ -19282,69 +19438,77 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="62">
-    <mergeCell ref="K54:K55"/>
-    <mergeCell ref="B88:B92"/>
-    <mergeCell ref="K76:K77"/>
-    <mergeCell ref="B62:B63"/>
-    <mergeCell ref="K21:K22"/>
-    <mergeCell ref="B78:B82"/>
-    <mergeCell ref="B52:B53"/>
-    <mergeCell ref="A98:K98"/>
-    <mergeCell ref="K38:K40"/>
-    <mergeCell ref="A1:K1"/>
-    <mergeCell ref="K23:K25"/>
-    <mergeCell ref="K50:K51"/>
-    <mergeCell ref="B14:B17"/>
-    <mergeCell ref="K66:K68"/>
-    <mergeCell ref="B35:B37"/>
-    <mergeCell ref="B83:B87"/>
-    <mergeCell ref="B26:B28"/>
-    <mergeCell ref="B66:B68"/>
-    <mergeCell ref="B69:B70"/>
-    <mergeCell ref="B56:B58"/>
-    <mergeCell ref="K3:K9"/>
-    <mergeCell ref="B41:B43"/>
-    <mergeCell ref="B47:B49"/>
-    <mergeCell ref="B93:B95"/>
-    <mergeCell ref="B32:B34"/>
-    <mergeCell ref="K93:K95"/>
-    <mergeCell ref="B10:B13"/>
-    <mergeCell ref="B59:B61"/>
-    <mergeCell ref="K18:K20"/>
-    <mergeCell ref="K78:K82"/>
-    <mergeCell ref="K52:K53"/>
-    <mergeCell ref="K83:K87"/>
-    <mergeCell ref="B74:B75"/>
-    <mergeCell ref="B64:B65"/>
-    <mergeCell ref="K44:K46"/>
-    <mergeCell ref="K69:K70"/>
-    <mergeCell ref="K29:K31"/>
-    <mergeCell ref="B71:B73"/>
-    <mergeCell ref="B3:B9"/>
-    <mergeCell ref="K56:K58"/>
-    <mergeCell ref="K14:K17"/>
-    <mergeCell ref="B54:B55"/>
-    <mergeCell ref="B18:B20"/>
-    <mergeCell ref="K41:K43"/>
-    <mergeCell ref="K59:K61"/>
-    <mergeCell ref="K32:K34"/>
-    <mergeCell ref="K35:K37"/>
-    <mergeCell ref="K62:K63"/>
-    <mergeCell ref="B23:B25"/>
-    <mergeCell ref="K10:K13"/>
-    <mergeCell ref="K26:K28"/>
-    <mergeCell ref="B76:B77"/>
-    <mergeCell ref="K88:K92"/>
-    <mergeCell ref="K71:K73"/>
-    <mergeCell ref="B44:B46"/>
-    <mergeCell ref="K47:K49"/>
-    <mergeCell ref="K74:K75"/>
-    <mergeCell ref="B29:B31"/>
-    <mergeCell ref="B38:B40"/>
-    <mergeCell ref="B50:B51"/>
-    <mergeCell ref="K64:K65"/>
-    <mergeCell ref="B21:B22"/>
+  <mergeCells count="70">
+    <mergeCell ref="C56:C58"/>
+    <mergeCell ref="C14:C17"/>
+    <mergeCell ref="L59:L61"/>
+    <mergeCell ref="L35:L37"/>
+    <mergeCell ref="L83:L87"/>
+    <mergeCell ref="L62:L63"/>
+    <mergeCell ref="L26:L28"/>
+    <mergeCell ref="L44:L46"/>
+    <mergeCell ref="B78:B95"/>
+    <mergeCell ref="L56:L58"/>
+    <mergeCell ref="L41:L43"/>
+    <mergeCell ref="C23:C25"/>
+    <mergeCell ref="C32:C34"/>
+    <mergeCell ref="C38:C40"/>
+    <mergeCell ref="C50:C51"/>
+    <mergeCell ref="C10:C13"/>
+    <mergeCell ref="C54:C55"/>
+    <mergeCell ref="C66:C68"/>
+    <mergeCell ref="L88:L92"/>
+    <mergeCell ref="B35:B46"/>
+    <mergeCell ref="L74:L75"/>
+    <mergeCell ref="B66:B77"/>
+    <mergeCell ref="L64:L65"/>
+    <mergeCell ref="C21:C22"/>
+    <mergeCell ref="B47:B58"/>
+    <mergeCell ref="L54:L55"/>
+    <mergeCell ref="L14:L17"/>
+    <mergeCell ref="L76:L77"/>
+    <mergeCell ref="C18:C20"/>
+    <mergeCell ref="B23:B28"/>
+    <mergeCell ref="C76:C77"/>
+    <mergeCell ref="L32:L34"/>
+    <mergeCell ref="C52:C53"/>
+    <mergeCell ref="B29:B34"/>
+    <mergeCell ref="L10:L13"/>
+    <mergeCell ref="C78:C82"/>
+    <mergeCell ref="L66:L68"/>
+    <mergeCell ref="C3:C9"/>
+    <mergeCell ref="L69:L70"/>
+    <mergeCell ref="L47:L49"/>
+    <mergeCell ref="C29:C31"/>
+    <mergeCell ref="L50:L51"/>
+    <mergeCell ref="L21:L22"/>
+    <mergeCell ref="L93:L95"/>
+    <mergeCell ref="C41:C43"/>
+    <mergeCell ref="B3:B22"/>
+    <mergeCell ref="B59:B65"/>
+    <mergeCell ref="C35:C37"/>
+    <mergeCell ref="L71:L73"/>
+    <mergeCell ref="C62:C63"/>
+    <mergeCell ref="C26:C28"/>
+    <mergeCell ref="C44:C46"/>
+    <mergeCell ref="C59:C61"/>
+    <mergeCell ref="C83:C87"/>
+    <mergeCell ref="L18:L20"/>
+    <mergeCell ref="L78:L82"/>
+    <mergeCell ref="C88:C92"/>
+    <mergeCell ref="C93:C95"/>
+    <mergeCell ref="L52:L53"/>
+    <mergeCell ref="C69:C70"/>
+    <mergeCell ref="A98:L98"/>
+    <mergeCell ref="L3:L9"/>
+    <mergeCell ref="C47:C49"/>
+    <mergeCell ref="A1:L1"/>
+    <mergeCell ref="C74:C75"/>
+    <mergeCell ref="C64:C65"/>
+    <mergeCell ref="L38:L40"/>
+    <mergeCell ref="L29:L31"/>
+    <mergeCell ref="C71:C73"/>
+    <mergeCell ref="L23:L25"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/RIMS项目WBS工作分解_AI Native版.xlsx
+++ b/RIMS项目WBS工作分解_AI Native版.xlsx
@@ -943,7 +943,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B36"/>
+  <dimension ref="A1:B37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1305,6 +1305,18 @@
     <row r="36" ht="30" customHeight="1">
       <c r="A36" s="38" t="n"/>
       <c r="B36" s="4" t="n"/>
+    </row>
+    <row r="37" ht="30" customHeight="1">
+      <c r="A37" s="38" t="inlineStr">
+        <is>
+          <t>功能视角分解</t>
+        </is>
+      </c>
+      <c r="B37" s="4" t="inlineStr">
+        <is>
+          <t>按功能维度查看：26项功能×（BA/开发A/开发B/测试/文档）五类角色各自的工作内容与人天，另有9类公共支撑行（初始化/架构/集成/专项/上线/管理）；底部与185人天自动对账，可与按开发顺序的「WBS分解」页对照使用</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -7175,7 +7187,7 @@
       </c>
       <c r="B94" s="22" t="inlineStr">
         <is>
-          <t>F04-04 异地灾备（副本隔离保存+恢复流程演练）</t>
+          <t>F04-04 异地灾备（Azure Blob原生异地冗余GRS/RA-GRS配置+恢复流程演练，非自研）</t>
         </is>
       </c>
       <c r="C94" s="15" t="n">
@@ -7183,7 +7195,7 @@
       </c>
       <c r="D94" s="17" t="inlineStr">
         <is>
-          <t>灾备恢复记录</t>
+          <t>灾备配置与恢复演练记录</t>
         </is>
       </c>
       <c r="E94" s="15" t="inlineStr">
@@ -7227,7 +7239,11 @@
         </is>
       </c>
       <c r="O94" s="21" t="n"/>
-      <c r="P94" s="21" t="n"/>
+      <c r="P94" s="21" t="inlineStr">
+        <is>
+          <t>Azure Blob原生能力（GRS）：仅配置冗余选项+恢复演练验证，开发量极小；10/27完成</t>
+        </is>
+      </c>
       <c r="Q94" s="17" t="inlineStr"/>
     </row>
     <row r="95">
@@ -14275,7 +14291,7 @@
       <c r="G15" s="55" t="n"/>
       <c r="H15" s="54" t="inlineStr">
         <is>
-          <t>异地副本+恢复流程演练</t>
+          <t>Azure Blob原生冗余(GRS)配置+恢复演练</t>
         </is>
       </c>
       <c r="I15" s="55" t="n">
@@ -15816,7 +15832,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L98"/>
+  <dimension ref="A1:L95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -15836,7 +15852,7 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>功能拆解估算（子任务级直估）：模块→功能→子任务三层结构，26项功能×75子任务 + 非功能与工程支撑×18子任务 — 独立估算，不锚定排期185人天</t>
+          <t>功能拆解估算（子任务级直估）：模块→功能→子任务三层结构，25项功能×72子任务 + 非功能与工程支撑×18子任务（F04-04异地灾备=Azure Blob原生能力，不计开发）— 独立估算，不锚定排期185人天</t>
         </is>
       </c>
     </row>
@@ -17440,7 +17456,7 @@
           <t>F04-03-3</t>
         </is>
       </c>
-      <c r="B43" s="102" t="n"/>
+      <c r="B43" s="103" t="n"/>
       <c r="C43" s="17" t="n"/>
       <c r="D43" s="32" t="inlineStr">
         <is>
@@ -17473,31 +17489,37 @@
     <row r="44" ht="26" customHeight="1">
       <c r="A44" s="15" t="inlineStr">
         <is>
-          <t>F04-04-1</t>
-        </is>
-      </c>
-      <c r="B44" s="102" t="n"/>
-      <c r="C44" s="98" t="inlineStr">
-        <is>
-          <t>异地灾备</t>
+          <t>F05-01-1</t>
+        </is>
+      </c>
+      <c r="B44" s="110" t="inlineStr">
+        <is>
+          <t>模块5·档案检索、智能发现与业务利用</t>
+        </is>
+      </c>
+      <c r="C44" s="104" t="inlineStr">
+        <is>
+          <t>关键词检索</t>
         </is>
       </c>
       <c r="D44" s="32" t="inlineStr">
         <is>
-          <t>灾备方案与RTO/RPO定义</t>
+          <t>检索配置模型</t>
         </is>
       </c>
       <c r="E44" s="32" t="inlineStr">
         <is>
-          <t>灾备架构、恢复目标定义</t>
+          <t>可检索字段、分词策略、OCR文本索引策略</t>
         </is>
       </c>
       <c r="F44" s="46" t="n">
         <v>0.5</v>
       </c>
-      <c r="G44" s="46" t="n"/>
+      <c r="G44" s="46" t="n">
+        <v>0.5</v>
+      </c>
       <c r="H44" s="46" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="I44" s="46" t="n">
         <v>0.25</v>
@@ -17506,34 +17528,36 @@
         <v>0.25</v>
       </c>
       <c r="K44" s="46" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="L44" s="83" t="n">
-        <v>5.75</v>
+        <v>2.5</v>
+      </c>
+      <c r="L44" s="105" t="n">
+        <v>7.75</v>
       </c>
     </row>
     <row r="45" ht="26" customHeight="1">
       <c r="A45" s="15" t="inlineStr">
         <is>
-          <t>F04-04-2</t>
+          <t>F05-01-2</t>
         </is>
       </c>
       <c r="B45" s="102" t="n"/>
       <c r="C45" s="17" t="n"/>
       <c r="D45" s="32" t="inlineStr">
         <is>
-          <t>异地副本同步</t>
+          <t>检索页动态表单</t>
         </is>
       </c>
       <c r="E45" s="32" t="inlineStr">
         <is>
-          <t>存储异地冗余/复制配置</t>
+          <t>元数据驱动渲染、关键词与组合查询</t>
         </is>
       </c>
       <c r="F45" s="46" t="n"/>
-      <c r="G45" s="46" t="n"/>
+      <c r="G45" s="46" t="n">
+        <v>2</v>
+      </c>
       <c r="H45" s="46" t="n">
-        <v>1.5</v>
+        <v>0.25</v>
       </c>
       <c r="I45" s="46" t="n">
         <v>0.5</v>
@@ -17542,32 +17566,32 @@
         <v>0.25</v>
       </c>
       <c r="K45" s="46" t="n">
-        <v>2.25</v>
+        <v>3</v>
       </c>
       <c r="L45" s="17" t="n"/>
     </row>
     <row r="46" ht="26" customHeight="1">
       <c r="A46" s="15" t="inlineStr">
         <is>
-          <t>F04-04-3</t>
-        </is>
-      </c>
-      <c r="B46" s="103" t="n"/>
+          <t>F05-01-3</t>
+        </is>
+      </c>
+      <c r="B46" s="102" t="n"/>
       <c r="C46" s="17" t="n"/>
       <c r="D46" s="32" t="inlineStr">
         <is>
-          <t>恢复切换演练</t>
+          <t>查询代理与SERVE层对接</t>
         </is>
       </c>
       <c r="E46" s="32" t="inlineStr">
         <is>
-          <t>演练脚本、切换/回切流程与报告</t>
+          <t>查询服务、索引优化、结果高亮</t>
         </is>
       </c>
       <c r="F46" s="46" t="n"/>
       <c r="G46" s="46" t="n"/>
       <c r="H46" s="46" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="I46" s="46" t="n">
         <v>0.75</v>
@@ -17576,45 +17600,37 @@
         <v>0.25</v>
       </c>
       <c r="K46" s="46" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="L46" s="17" t="n"/>
     </row>
     <row r="47" ht="26" customHeight="1">
       <c r="A47" s="15" t="inlineStr">
         <is>
-          <t>F05-01-1</t>
-        </is>
-      </c>
-      <c r="B47" s="110" t="inlineStr">
-        <is>
-          <t>模块5·档案检索、智能发现与业务利用</t>
-        </is>
-      </c>
+          <t>F05-02-1</t>
+        </is>
+      </c>
+      <c r="B47" s="102" t="n"/>
       <c r="C47" s="104" t="inlineStr">
         <is>
-          <t>关键词检索</t>
+          <t>按系统名称检索</t>
         </is>
       </c>
       <c r="D47" s="32" t="inlineStr">
         <is>
-          <t>检索配置模型</t>
+          <t>来源系统筛选组件</t>
         </is>
       </c>
       <c r="E47" s="32" t="inlineStr">
         <is>
-          <t>可检索字段、分词策略、OCR文本索引策略</t>
-        </is>
-      </c>
-      <c r="F47" s="46" t="n">
-        <v>0.5</v>
-      </c>
+          <t>来源系统下拉/搜索/多选</t>
+        </is>
+      </c>
+      <c r="F47" s="46" t="n"/>
       <c r="G47" s="46" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="H47" s="46" t="n">
-        <v>1</v>
-      </c>
+        <v>0.75</v>
+      </c>
+      <c r="H47" s="46" t="n"/>
       <c r="I47" s="46" t="n">
         <v>0.25</v>
       </c>
@@ -17622,109 +17638,109 @@
         <v>0.25</v>
       </c>
       <c r="K47" s="46" t="n">
-        <v>2.5</v>
+        <v>1.25</v>
       </c>
       <c r="L47" s="105" t="n">
-        <v>7.75</v>
+        <v>2.25</v>
       </c>
     </row>
     <row r="48" ht="26" customHeight="1">
       <c r="A48" s="15" t="inlineStr">
         <is>
-          <t>F05-01-2</t>
+          <t>F05-02-2</t>
         </is>
       </c>
       <c r="B48" s="102" t="n"/>
       <c r="C48" s="17" t="n"/>
       <c r="D48" s="32" t="inlineStr">
         <is>
-          <t>检索页动态表单</t>
+          <t>来源维度查询下推</t>
         </is>
       </c>
       <c r="E48" s="32" t="inlineStr">
         <is>
-          <t>元数据驱动渲染、关键词与组合查询</t>
+          <t>sys_id过滤、分区裁剪</t>
         </is>
       </c>
       <c r="F48" s="46" t="n"/>
-      <c r="G48" s="46" t="n">
-        <v>2</v>
-      </c>
+      <c r="G48" s="46" t="n"/>
       <c r="H48" s="46" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I48" s="46" t="n">
         <v>0.25</v>
-      </c>
-      <c r="I48" s="46" t="n">
-        <v>0.5</v>
       </c>
       <c r="J48" s="46" t="n">
         <v>0.25</v>
       </c>
       <c r="K48" s="46" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L48" s="17" t="n"/>
     </row>
     <row r="49" ht="26" customHeight="1">
       <c r="A49" s="15" t="inlineStr">
         <is>
-          <t>F05-01-3</t>
+          <t>F05-03-1</t>
         </is>
       </c>
       <c r="B49" s="102" t="n"/>
-      <c r="C49" s="17" t="n"/>
+      <c r="C49" s="104" t="inlineStr">
+        <is>
+          <t>按业务时间检索</t>
+        </is>
+      </c>
       <c r="D49" s="32" t="inlineStr">
         <is>
-          <t>查询代理与SERVE层对接</t>
+          <t>时间维度筛选组件</t>
         </is>
       </c>
       <c r="E49" s="32" t="inlineStr">
         <is>
-          <t>查询服务、索引优化、结果高亮</t>
+          <t>创建/修改/业务发生时间范围选择</t>
         </is>
       </c>
       <c r="F49" s="46" t="n"/>
-      <c r="G49" s="46" t="n"/>
-      <c r="H49" s="46" t="n">
-        <v>1.25</v>
-      </c>
+      <c r="G49" s="46" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="H49" s="46" t="n"/>
       <c r="I49" s="46" t="n">
-        <v>0.75</v>
+        <v>0.25</v>
       </c>
       <c r="J49" s="46" t="n">
         <v>0.25</v>
       </c>
       <c r="K49" s="46" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="L49" s="105" t="n">
         <v>2.25</v>
       </c>
-      <c r="L49" s="17" t="n"/>
     </row>
     <row r="50" ht="26" customHeight="1">
       <c r="A50" s="15" t="inlineStr">
         <is>
-          <t>F05-02-1</t>
+          <t>F05-03-2</t>
         </is>
       </c>
       <c r="B50" s="102" t="n"/>
-      <c r="C50" s="104" t="inlineStr">
-        <is>
-          <t>按系统名称检索</t>
-        </is>
-      </c>
+      <c r="C50" s="17" t="n"/>
       <c r="D50" s="32" t="inlineStr">
         <is>
-          <t>来源系统筛选组件</t>
+          <t>时间分区下推与索引</t>
         </is>
       </c>
       <c r="E50" s="32" t="inlineStr">
         <is>
-          <t>来源系统下拉/搜索/多选</t>
+          <t>分区裁剪、时间索引优化</t>
         </is>
       </c>
       <c r="F50" s="46" t="n"/>
-      <c r="G50" s="46" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="H50" s="46" t="n"/>
+      <c r="G50" s="46" t="n"/>
+      <c r="H50" s="46" t="n">
+        <v>0.5</v>
+      </c>
       <c r="I50" s="46" t="n">
         <v>0.25</v>
       </c>
@@ -17732,147 +17748,151 @@
         <v>0.25</v>
       </c>
       <c r="K50" s="46" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="L50" s="105" t="n">
-        <v>2.25</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="L50" s="17" t="n"/>
     </row>
     <row r="51" ht="26" customHeight="1">
       <c r="A51" s="15" t="inlineStr">
         <is>
-          <t>F05-02-2</t>
+          <t>F05-04-1</t>
         </is>
       </c>
       <c r="B51" s="102" t="n"/>
-      <c r="C51" s="17" t="n"/>
+      <c r="C51" s="104" t="inlineStr">
+        <is>
+          <t>检索结果列表展示</t>
+        </is>
+      </c>
       <c r="D51" s="32" t="inlineStr">
         <is>
-          <t>来源维度查询下推</t>
+          <t>列表展示与分页排序</t>
         </is>
       </c>
       <c r="E51" s="32" t="inlineStr">
         <is>
-          <t>sys_id过滤、分区裁剪</t>
+          <t>关键字段展示、分批加载、虚拟滚动</t>
         </is>
       </c>
       <c r="F51" s="46" t="n"/>
-      <c r="G51" s="46" t="n"/>
-      <c r="H51" s="46" t="n">
+      <c r="G51" s="46" t="n">
+        <v>2</v>
+      </c>
+      <c r="H51" s="46" t="n"/>
+      <c r="I51" s="46" t="n">
         <v>0.5</v>
-      </c>
-      <c r="I51" s="46" t="n">
-        <v>0.25</v>
       </c>
       <c r="J51" s="46" t="n">
         <v>0.25</v>
       </c>
       <c r="K51" s="46" t="n">
-        <v>1</v>
-      </c>
-      <c r="L51" s="17" t="n"/>
+        <v>2.75</v>
+      </c>
+      <c r="L51" s="105" t="n">
+        <v>4.5</v>
+      </c>
     </row>
     <row r="52" ht="26" customHeight="1">
       <c r="A52" s="15" t="inlineStr">
         <is>
-          <t>F05-03-1</t>
+          <t>F05-04-2</t>
         </is>
       </c>
       <c r="B52" s="102" t="n"/>
-      <c r="C52" s="104" t="inlineStr">
-        <is>
-          <t>按业务时间检索</t>
-        </is>
-      </c>
+      <c r="C52" s="17" t="n"/>
       <c r="D52" s="32" t="inlineStr">
         <is>
-          <t>时间维度筛选组件</t>
+          <t>大批量结果性能</t>
         </is>
       </c>
       <c r="E52" s="32" t="inlineStr">
         <is>
-          <t>创建/修改/业务发生时间范围选择</t>
+          <t>异步计数、游标分页、缓存</t>
         </is>
       </c>
       <c r="F52" s="46" t="n"/>
       <c r="G52" s="46" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="H52" s="46" t="n">
         <v>0.75</v>
       </c>
-      <c r="H52" s="46" t="n"/>
       <c r="I52" s="46" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="J52" s="46" t="n">
         <v>0.25</v>
       </c>
       <c r="K52" s="46" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="L52" s="105" t="n">
-        <v>2.25</v>
-      </c>
+        <v>1.75</v>
+      </c>
+      <c r="L52" s="17" t="n"/>
     </row>
     <row r="53" ht="26" customHeight="1">
       <c r="A53" s="15" t="inlineStr">
         <is>
-          <t>F05-03-2</t>
+          <t>F05-05-1</t>
         </is>
       </c>
       <c r="B53" s="102" t="n"/>
-      <c r="C53" s="17" t="n"/>
+      <c r="C53" s="104" t="inlineStr">
+        <is>
+          <t>原始文件在线预览</t>
+        </is>
+      </c>
       <c r="D53" s="32" t="inlineStr">
         <is>
-          <t>时间分区下推与索引</t>
+          <t>预览服务</t>
         </is>
       </c>
       <c r="E53" s="32" t="inlineStr">
         <is>
-          <t>分区裁剪、时间索引优化</t>
+          <t>格式识别、图片/PDF/Office转换</t>
         </is>
       </c>
       <c r="F53" s="46" t="n"/>
       <c r="G53" s="46" t="n"/>
       <c r="H53" s="46" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I53" s="46" t="n">
         <v>0.5</v>
-      </c>
-      <c r="I53" s="46" t="n">
-        <v>0.25</v>
       </c>
       <c r="J53" s="46" t="n">
         <v>0.25</v>
       </c>
       <c r="K53" s="46" t="n">
-        <v>1</v>
-      </c>
-      <c r="L53" s="17" t="n"/>
+        <v>2.25</v>
+      </c>
+      <c r="L53" s="105" t="n">
+        <v>6.5</v>
+      </c>
     </row>
     <row r="54" ht="26" customHeight="1">
       <c r="A54" s="15" t="inlineStr">
         <is>
-          <t>F05-04-1</t>
+          <t>F05-05-2</t>
         </is>
       </c>
       <c r="B54" s="102" t="n"/>
-      <c r="C54" s="104" t="inlineStr">
-        <is>
-          <t>检索结果列表展示</t>
-        </is>
-      </c>
+      <c r="C54" s="17" t="n"/>
       <c r="D54" s="32" t="inlineStr">
         <is>
-          <t>列表展示与分页排序</t>
+          <t>SAS直连与流式加载</t>
         </is>
       </c>
       <c r="E54" s="32" t="inlineStr">
         <is>
-          <t>关键字段展示、分批加载、虚拟滚动</t>
+          <t>临时SAS链接、流式传输、权限校验</t>
         </is>
       </c>
       <c r="F54" s="46" t="n"/>
       <c r="G54" s="46" t="n">
-        <v>2</v>
-      </c>
-      <c r="H54" s="46" t="n"/>
+        <v>0.5</v>
+      </c>
+      <c r="H54" s="46" t="n">
+        <v>1</v>
+      </c>
       <c r="I54" s="46" t="n">
         <v>0.5</v>
       </c>
@@ -17880,110 +17900,110 @@
         <v>0.25</v>
       </c>
       <c r="K54" s="46" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="L54" s="105" t="n">
-        <v>4.5</v>
-      </c>
+        <v>2.25</v>
+      </c>
+      <c r="L54" s="17" t="n"/>
     </row>
     <row r="55" ht="26" customHeight="1">
       <c r="A55" s="15" t="inlineStr">
         <is>
-          <t>F05-04-2</t>
-        </is>
-      </c>
-      <c r="B55" s="102" t="n"/>
+          <t>F05-05-3</t>
+        </is>
+      </c>
+      <c r="B55" s="103" t="n"/>
       <c r="C55" s="17" t="n"/>
       <c r="D55" s="32" t="inlineStr">
         <is>
-          <t>大批量结果性能</t>
+          <t>前端预览组件</t>
         </is>
       </c>
       <c r="E55" s="32" t="inlineStr">
         <is>
-          <t>异步计数、游标分页、缓存</t>
+          <t>格式适配、缩放、失败降级下载</t>
         </is>
       </c>
       <c r="F55" s="46" t="n"/>
       <c r="G55" s="46" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H55" s="46" t="n"/>
+      <c r="I55" s="46" t="n">
         <v>0.25</v>
-      </c>
-      <c r="H55" s="46" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="I55" s="46" t="n">
-        <v>0.5</v>
       </c>
       <c r="J55" s="46" t="n">
         <v>0.25</v>
       </c>
       <c r="K55" s="46" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="L55" s="17" t="n"/>
     </row>
     <row r="56" ht="26" customHeight="1">
       <c r="A56" s="15" t="inlineStr">
         <is>
-          <t>F05-05-1</t>
-        </is>
-      </c>
-      <c r="B56" s="102" t="n"/>
-      <c r="C56" s="104" t="inlineStr">
-        <is>
-          <t>原始文件在线预览</t>
+          <t>F06-01-1</t>
+        </is>
+      </c>
+      <c r="B56" s="111" t="inlineStr">
+        <is>
+          <t>模块6·合规管控、审计追踪与合规报表</t>
+        </is>
+      </c>
+      <c r="C56" s="100" t="inlineStr">
+        <is>
+          <t>归档操作日志记录</t>
         </is>
       </c>
       <c r="D56" s="32" t="inlineStr">
         <is>
-          <t>预览服务</t>
+          <t>埋点规范与日志模型</t>
         </is>
       </c>
       <c r="E56" s="32" t="inlineStr">
         <is>
-          <t>格式识别、图片/PDF/Office转换</t>
-        </is>
-      </c>
-      <c r="F56" s="46" t="n"/>
+          <t>操作对象/用户/时间/结果/IP模型定义</t>
+        </is>
+      </c>
+      <c r="F56" s="46" t="n">
+        <v>0.25</v>
+      </c>
       <c r="G56" s="46" t="n"/>
       <c r="H56" s="46" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="I56" s="46" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="J56" s="46" t="n">
         <v>0.25</v>
       </c>
       <c r="K56" s="46" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="L56" s="105" t="n">
-        <v>6.5</v>
+        <v>1.25</v>
+      </c>
+      <c r="L56" s="89" t="n">
+        <v>5.5</v>
       </c>
     </row>
     <row r="57" ht="26" customHeight="1">
       <c r="A57" s="15" t="inlineStr">
         <is>
-          <t>F05-05-2</t>
+          <t>F06-01-2</t>
         </is>
       </c>
       <c r="B57" s="102" t="n"/>
       <c r="C57" s="17" t="n"/>
       <c r="D57" s="32" t="inlineStr">
         <is>
-          <t>SAS直连与流式加载</t>
+          <t>操作拦截与落库</t>
         </is>
       </c>
       <c r="E57" s="32" t="inlineStr">
         <is>
-          <t>临时SAS链接、流式传输、权限校验</t>
+          <t>归档/导入/上传统一拦截器、异步写入</t>
         </is>
       </c>
       <c r="F57" s="46" t="n"/>
-      <c r="G57" s="46" t="n">
-        <v>0.5</v>
-      </c>
+      <c r="G57" s="46" t="n"/>
       <c r="H57" s="46" t="n">
         <v>1</v>
       </c>
@@ -17994,148 +18014,146 @@
         <v>0.25</v>
       </c>
       <c r="K57" s="46" t="n">
-        <v>2.25</v>
+        <v>1.75</v>
       </c>
       <c r="L57" s="17" t="n"/>
     </row>
     <row r="58" ht="26" customHeight="1">
       <c r="A58" s="15" t="inlineStr">
         <is>
-          <t>F05-05-3</t>
-        </is>
-      </c>
-      <c r="B58" s="103" t="n"/>
+          <t>F06-01-3</t>
+        </is>
+      </c>
+      <c r="B58" s="102" t="n"/>
       <c r="C58" s="17" t="n"/>
       <c r="D58" s="32" t="inlineStr">
         <is>
-          <t>前端预览组件</t>
+          <t>审计查询界面</t>
         </is>
       </c>
       <c r="E58" s="32" t="inlineStr">
         <is>
-          <t>格式适配、缩放、失败降级下载</t>
+          <t>多维筛选与导出（覆盖归档/查询/导出三类日志）</t>
         </is>
       </c>
       <c r="F58" s="46" t="n"/>
       <c r="G58" s="46" t="n">
         <v>1.5</v>
       </c>
-      <c r="H58" s="46" t="n"/>
+      <c r="H58" s="46" t="n">
+        <v>0.25</v>
+      </c>
       <c r="I58" s="46" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="J58" s="46" t="n">
         <v>0.25</v>
       </c>
       <c r="K58" s="46" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="L58" s="17" t="n"/>
     </row>
     <row r="59" ht="26" customHeight="1">
       <c r="A59" s="15" t="inlineStr">
         <is>
-          <t>F06-01-1</t>
-        </is>
-      </c>
-      <c r="B59" s="111" t="inlineStr">
-        <is>
-          <t>模块6·合规管控、审计追踪与合规报表</t>
-        </is>
-      </c>
+          <t>F06-02-1</t>
+        </is>
+      </c>
+      <c r="B59" s="102" t="n"/>
       <c r="C59" s="100" t="inlineStr">
         <is>
-          <t>归档操作日志记录</t>
+          <t>查询操作日志记录</t>
         </is>
       </c>
       <c r="D59" s="32" t="inlineStr">
         <is>
-          <t>埋点规范与日志模型</t>
+          <t>查询/预览行为埋点</t>
         </is>
       </c>
       <c r="E59" s="32" t="inlineStr">
         <is>
-          <t>操作对象/用户/时间/结果/IP模型定义</t>
-        </is>
-      </c>
-      <c r="F59" s="46" t="n">
-        <v>0.25</v>
-      </c>
+          <t>查询条件脱敏记录、预览行为记录</t>
+        </is>
+      </c>
+      <c r="F59" s="46" t="n"/>
       <c r="G59" s="46" t="n"/>
       <c r="H59" s="46" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="I59" s="46" t="n">
         <v>0.5</v>
-      </c>
-      <c r="I59" s="46" t="n">
-        <v>0.25</v>
       </c>
       <c r="J59" s="46" t="n">
         <v>0.25</v>
       </c>
       <c r="K59" s="46" t="n">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="L59" s="89" t="n">
-        <v>5.5</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="60" ht="26" customHeight="1">
       <c r="A60" s="15" t="inlineStr">
         <is>
-          <t>F06-01-2</t>
+          <t>F06-02-2</t>
         </is>
       </c>
       <c r="B60" s="102" t="n"/>
       <c r="C60" s="17" t="n"/>
       <c r="D60" s="32" t="inlineStr">
         <is>
-          <t>操作拦截与落库</t>
+          <t>异步批量写入</t>
         </is>
       </c>
       <c r="E60" s="32" t="inlineStr">
         <is>
-          <t>归档/导入/上传统一拦截器、异步写入</t>
+          <t>缓冲批量写入、不阻塞查询主链路</t>
         </is>
       </c>
       <c r="F60" s="46" t="n"/>
       <c r="G60" s="46" t="n"/>
       <c r="H60" s="46" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="I60" s="46" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="J60" s="46" t="n">
         <v>0.25</v>
       </c>
       <c r="K60" s="46" t="n">
-        <v>1.75</v>
+        <v>1</v>
       </c>
       <c r="L60" s="17" t="n"/>
     </row>
     <row r="61" ht="26" customHeight="1">
       <c r="A61" s="15" t="inlineStr">
         <is>
-          <t>F06-01-3</t>
+          <t>F06-03-1</t>
         </is>
       </c>
       <c r="B61" s="102" t="n"/>
-      <c r="C61" s="17" t="n"/>
+      <c r="C61" s="100" t="inlineStr">
+        <is>
+          <t>导出操作日志记录</t>
+        </is>
+      </c>
       <c r="D61" s="32" t="inlineStr">
         <is>
-          <t>审计查询界面</t>
+          <t>导出行为审计</t>
         </is>
       </c>
       <c r="E61" s="32" t="inlineStr">
         <is>
-          <t>多维筛选与导出（覆盖归档/查询/导出三类日志）</t>
+          <t>导出范围/条数/导出人/IP/下载链接追踪</t>
         </is>
       </c>
       <c r="F61" s="46" t="n"/>
-      <c r="G61" s="46" t="n">
-        <v>1.5</v>
-      </c>
+      <c r="G61" s="46" t="n"/>
       <c r="H61" s="46" t="n">
-        <v>0.25</v>
+        <v>0.75</v>
       </c>
       <c r="I61" s="46" t="n">
         <v>0.5</v>
@@ -18144,69 +18162,77 @@
         <v>0.25</v>
       </c>
       <c r="K61" s="46" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="L61" s="17" t="n"/>
+        <v>1.5</v>
+      </c>
+      <c r="L61" s="89" t="n">
+        <v>2.75</v>
+      </c>
     </row>
     <row r="62" ht="26" customHeight="1">
       <c r="A62" s="15" t="inlineStr">
         <is>
-          <t>F06-02-1</t>
-        </is>
-      </c>
-      <c r="B62" s="102" t="n"/>
-      <c r="C62" s="100" t="inlineStr">
-        <is>
-          <t>查询操作日志记录</t>
-        </is>
-      </c>
+          <t>F06-03-2</t>
+        </is>
+      </c>
+      <c r="B62" s="103" t="n"/>
+      <c r="C62" s="17" t="n"/>
       <c r="D62" s="32" t="inlineStr">
         <is>
-          <t>查询/预览行为埋点</t>
+          <t>大批量导出告警</t>
         </is>
       </c>
       <c r="E62" s="32" t="inlineStr">
         <is>
-          <t>查询条件脱敏记录、预览行为记录</t>
+          <t>阈值告警、审批联动</t>
         </is>
       </c>
       <c r="F62" s="46" t="n"/>
-      <c r="G62" s="46" t="n"/>
+      <c r="G62" s="46" t="n">
+        <v>0.5</v>
+      </c>
       <c r="H62" s="46" t="n">
-        <v>0.75</v>
+        <v>0.25</v>
       </c>
       <c r="I62" s="46" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="J62" s="46" t="n">
         <v>0.25</v>
       </c>
       <c r="K62" s="46" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="L62" s="89" t="n">
-        <v>2.5</v>
-      </c>
+        <v>1.25</v>
+      </c>
+      <c r="L62" s="17" t="n"/>
     </row>
     <row r="63" ht="26" customHeight="1">
       <c r="A63" s="15" t="inlineStr">
         <is>
-          <t>F06-02-2</t>
-        </is>
-      </c>
-      <c r="B63" s="102" t="n"/>
-      <c r="C63" s="17" t="n"/>
+          <t>F08-01-1</t>
+        </is>
+      </c>
+      <c r="B63" s="112" t="inlineStr">
+        <is>
+          <t>模块8·系统全局治理、运维与监控</t>
+        </is>
+      </c>
+      <c r="C63" s="101" t="inlineStr">
+        <is>
+          <t>基础角色权限配置</t>
+        </is>
+      </c>
       <c r="D63" s="32" t="inlineStr">
         <is>
-          <t>异步批量写入</t>
+          <t>RBAC模型与权限矩阵</t>
         </is>
       </c>
       <c r="E63" s="32" t="inlineStr">
         <is>
-          <t>缓冲批量写入、不阻塞查询主链路</t>
-        </is>
-      </c>
-      <c r="F63" s="46" t="n"/>
+          <t>角色/菜单/数据范围/记录类型/操作权限定义</t>
+        </is>
+      </c>
+      <c r="F63" s="46" t="n">
+        <v>1</v>
+      </c>
       <c r="G63" s="46" t="n"/>
       <c r="H63" s="46" t="n">
         <v>0.5</v>
@@ -18215,39 +18241,39 @@
         <v>0.25</v>
       </c>
       <c r="J63" s="46" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="K63" s="46" t="n">
-        <v>1</v>
-      </c>
-      <c r="L63" s="17" t="n"/>
+        <v>2.25</v>
+      </c>
+      <c r="L63" s="92" t="n">
+        <v>7.5</v>
+      </c>
     </row>
     <row r="64" ht="26" customHeight="1">
       <c r="A64" s="15" t="inlineStr">
         <is>
-          <t>F06-03-1</t>
+          <t>F08-01-2</t>
         </is>
       </c>
       <c r="B64" s="102" t="n"/>
-      <c r="C64" s="100" t="inlineStr">
-        <is>
-          <t>导出操作日志记录</t>
-        </is>
-      </c>
+      <c r="C64" s="17" t="n"/>
       <c r="D64" s="32" t="inlineStr">
         <is>
-          <t>导出行为审计</t>
+          <t>角色管理界面与API</t>
         </is>
       </c>
       <c r="E64" s="32" t="inlineStr">
         <is>
-          <t>导出范围/条数/导出人/IP/下载链接追踪</t>
+          <t>角色CRUD、权限分配界面与接口</t>
         </is>
       </c>
       <c r="F64" s="46" t="n"/>
-      <c r="G64" s="46" t="n"/>
+      <c r="G64" s="46" t="n">
+        <v>2</v>
+      </c>
       <c r="H64" s="46" t="n">
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
       <c r="I64" s="46" t="n">
         <v>0.5</v>
@@ -18256,235 +18282,229 @@
         <v>0.25</v>
       </c>
       <c r="K64" s="46" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="L64" s="89" t="n">
-        <v>2.75</v>
-      </c>
+        <v>3.25</v>
+      </c>
+      <c r="L64" s="17" t="n"/>
     </row>
     <row r="65" ht="26" customHeight="1">
       <c r="A65" s="15" t="inlineStr">
         <is>
-          <t>F06-03-2</t>
-        </is>
-      </c>
-      <c r="B65" s="103" t="n"/>
+          <t>F08-01-3</t>
+        </is>
+      </c>
+      <c r="B65" s="102" t="n"/>
       <c r="C65" s="17" t="n"/>
       <c r="D65" s="32" t="inlineStr">
         <is>
-          <t>大批量导出告警</t>
+          <t>权限校验与UC授权映射</t>
         </is>
       </c>
       <c r="E65" s="32" t="inlineStr">
         <is>
-          <t>阈值告警、审批联动</t>
+          <t>菜单/接口级校验中间件、UC权限同步</t>
         </is>
       </c>
       <c r="F65" s="46" t="n"/>
-      <c r="G65" s="46" t="n">
-        <v>0.5</v>
-      </c>
+      <c r="G65" s="46" t="n"/>
       <c r="H65" s="46" t="n">
-        <v>0.25</v>
+        <v>1</v>
       </c>
       <c r="I65" s="46" t="n">
-        <v>0.25</v>
+        <v>0.75</v>
       </c>
       <c r="J65" s="46" t="n">
         <v>0.25</v>
       </c>
       <c r="K65" s="46" t="n">
-        <v>1.25</v>
+        <v>2</v>
       </c>
       <c r="L65" s="17" t="n"/>
     </row>
     <row r="66" ht="26" customHeight="1">
       <c r="A66" s="15" t="inlineStr">
         <is>
-          <t>F08-01-1</t>
-        </is>
-      </c>
-      <c r="B66" s="112" t="inlineStr">
-        <is>
-          <t>模块8·系统全局治理、运维与监控</t>
-        </is>
-      </c>
+          <t>F08-02-1</t>
+        </is>
+      </c>
+      <c r="B66" s="102" t="n"/>
       <c r="C66" s="101" t="inlineStr">
         <is>
-          <t>基础角色权限配置</t>
+          <t>用户账号管理</t>
         </is>
       </c>
       <c r="D66" s="32" t="inlineStr">
         <is>
-          <t>RBAC模型与权限矩阵</t>
+          <t>账号CRUD与生命周期</t>
         </is>
       </c>
       <c r="E66" s="32" t="inlineStr">
         <is>
-          <t>角色/菜单/数据范围/记录类型/操作权限定义</t>
+          <t>创建/启用禁用/密码重置/有效期</t>
         </is>
       </c>
       <c r="F66" s="46" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="G66" s="46" t="n">
         <v>1</v>
       </c>
-      <c r="G66" s="46" t="n"/>
       <c r="H66" s="46" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="I66" s="46" t="n">
         <v>0.5</v>
       </c>
-      <c r="I66" s="46" t="n">
+      <c r="J66" s="46" t="n">
         <v>0.25</v>
       </c>
-      <c r="J66" s="46" t="n">
-        <v>0.5</v>
-      </c>
       <c r="K66" s="46" t="n">
-        <v>2.25</v>
+        <v>2.75</v>
       </c>
       <c r="L66" s="92" t="n">
-        <v>7.5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="67" ht="26" customHeight="1">
       <c r="A67" s="15" t="inlineStr">
         <is>
-          <t>F08-01-2</t>
+          <t>F08-02-2</t>
         </is>
       </c>
       <c r="B67" s="102" t="n"/>
       <c r="C67" s="17" t="n"/>
       <c r="D67" s="32" t="inlineStr">
         <is>
-          <t>角色管理界面与API</t>
+          <t>账号与角色绑定</t>
         </is>
       </c>
       <c r="E67" s="32" t="inlineStr">
         <is>
-          <t>角色CRUD、权限分配界面与接口</t>
+          <t>分配、批量操作、人员交接</t>
         </is>
       </c>
       <c r="F67" s="46" t="n"/>
       <c r="G67" s="46" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="H67" s="46" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="I67" s="46" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="J67" s="46" t="n">
         <v>0.25</v>
       </c>
       <c r="K67" s="46" t="n">
-        <v>3.25</v>
+        <v>1.25</v>
       </c>
       <c r="L67" s="17" t="n"/>
     </row>
     <row r="68" ht="26" customHeight="1">
       <c r="A68" s="15" t="inlineStr">
         <is>
-          <t>F08-01-3</t>
+          <t>F08-03-1</t>
         </is>
       </c>
       <c r="B68" s="102" t="n"/>
-      <c r="C68" s="17" t="n"/>
+      <c r="C68" s="101" t="inlineStr">
+        <is>
+          <t>企业SSO集成</t>
+        </is>
+      </c>
       <c r="D68" s="32" t="inlineStr">
         <is>
-          <t>权限校验与UC授权映射</t>
+          <t>Entra ID对接配置</t>
         </is>
       </c>
       <c r="E68" s="32" t="inlineStr">
         <is>
-          <t>菜单/接口级校验中间件、UC权限同步</t>
-        </is>
-      </c>
-      <c r="F68" s="46" t="n"/>
-      <c r="G68" s="46" t="n"/>
+          <t>应用注册、回调配置、claims映射</t>
+        </is>
+      </c>
+      <c r="F68" s="46" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="G68" s="46" t="n">
+        <v>0.5</v>
+      </c>
       <c r="H68" s="46" t="n">
         <v>1</v>
       </c>
       <c r="I68" s="46" t="n">
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
       <c r="J68" s="46" t="n">
         <v>0.25</v>
       </c>
       <c r="K68" s="46" t="n">
-        <v>2</v>
-      </c>
-      <c r="L68" s="17" t="n"/>
+        <v>2.5</v>
+      </c>
+      <c r="L68" s="92" t="n">
+        <v>7.25</v>
+      </c>
     </row>
     <row r="69" ht="26" customHeight="1">
       <c r="A69" s="15" t="inlineStr">
         <is>
-          <t>F08-02-1</t>
+          <t>F08-03-2</t>
         </is>
       </c>
       <c r="B69" s="102" t="n"/>
-      <c r="C69" s="101" t="inlineStr">
-        <is>
-          <t>用户账号管理</t>
-        </is>
-      </c>
+      <c r="C69" s="17" t="n"/>
       <c r="D69" s="32" t="inlineStr">
         <is>
-          <t>账号CRUD与生命周期</t>
+          <t>SSO登录链路</t>
         </is>
       </c>
       <c r="E69" s="32" t="inlineStr">
         <is>
-          <t>创建/启用禁用/密码重置/有效期</t>
-        </is>
-      </c>
-      <c r="F69" s="46" t="n">
-        <v>0.25</v>
-      </c>
+          <t>登录页、令牌交换、会话管理</t>
+        </is>
+      </c>
+      <c r="F69" s="46" t="n"/>
       <c r="G69" s="46" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H69" s="46" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I69" s="46" t="n">
         <v>0.75</v>
-      </c>
-      <c r="I69" s="46" t="n">
-        <v>0.5</v>
       </c>
       <c r="J69" s="46" t="n">
         <v>0.25</v>
       </c>
       <c r="K69" s="46" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="L69" s="92" t="n">
-        <v>4</v>
-      </c>
+        <v>3.5</v>
+      </c>
+      <c r="L69" s="17" t="n"/>
     </row>
     <row r="70" ht="26" customHeight="1">
       <c r="A70" s="15" t="inlineStr">
         <is>
-          <t>F08-02-2</t>
+          <t>F08-03-3</t>
         </is>
       </c>
       <c r="B70" s="102" t="n"/>
       <c r="C70" s="17" t="n"/>
       <c r="D70" s="32" t="inlineStr">
         <is>
-          <t>账号与角色绑定</t>
+          <t>认证异常场景处理</t>
         </is>
       </c>
       <c r="E70" s="32" t="inlineStr">
         <is>
-          <t>分配、批量操作、人员交接</t>
+          <t>认证失败、账号锁定、多账号冲突</t>
         </is>
       </c>
       <c r="F70" s="46" t="n"/>
       <c r="G70" s="46" t="n">
         <v>0.5</v>
       </c>
-      <c r="H70" s="46" t="n">
-        <v>0.25</v>
-      </c>
+      <c r="H70" s="46" t="n"/>
       <c r="I70" s="46" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="J70" s="46" t="n">
         <v>0.25</v>
@@ -18497,106 +18517,112 @@
     <row r="71" ht="26" customHeight="1">
       <c r="A71" s="15" t="inlineStr">
         <is>
-          <t>F08-03-1</t>
+          <t>F08-04-1</t>
         </is>
       </c>
       <c r="B71" s="102" t="n"/>
       <c r="C71" s="101" t="inlineStr">
         <is>
-          <t>企业SSO集成</t>
+          <t>用户身份自动识别与关联</t>
         </is>
       </c>
       <c r="D71" s="32" t="inlineStr">
         <is>
-          <t>Entra ID对接配置</t>
+          <t>身份映射规则</t>
         </is>
       </c>
       <c r="E71" s="32" t="inlineStr">
         <is>
-          <t>应用注册、回调配置、claims映射</t>
+          <t>企业账号↔RIMS用户映射、自动建号规则</t>
         </is>
       </c>
       <c r="F71" s="46" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G71" s="46" t="n"/>
+      <c r="H71" s="46" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I71" s="46" t="n">
         <v>0.25</v>
-      </c>
-      <c r="G71" s="46" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="H71" s="46" t="n">
-        <v>1</v>
-      </c>
-      <c r="I71" s="46" t="n">
-        <v>0.5</v>
       </c>
       <c r="J71" s="46" t="n">
         <v>0.25</v>
       </c>
       <c r="K71" s="46" t="n">
-        <v>2.5</v>
+        <v>1.5</v>
       </c>
       <c r="L71" s="92" t="n">
-        <v>7.25</v>
+        <v>3.25</v>
       </c>
     </row>
     <row r="72" ht="26" customHeight="1">
       <c r="A72" s="15" t="inlineStr">
         <is>
-          <t>F08-03-2</t>
+          <t>F08-04-2</t>
         </is>
       </c>
       <c r="B72" s="102" t="n"/>
       <c r="C72" s="17" t="n"/>
       <c r="D72" s="32" t="inlineStr">
         <is>
-          <t>SSO登录链路</t>
+          <t>首登自动关联与角色赋予</t>
         </is>
       </c>
       <c r="E72" s="32" t="inlineStr">
         <is>
-          <t>登录页、令牌交换、会话管理</t>
+          <t>默认角色、待分配队列</t>
         </is>
       </c>
       <c r="F72" s="46" t="n"/>
       <c r="G72" s="46" t="n">
-        <v>2</v>
+        <v>0.25</v>
       </c>
       <c r="H72" s="46" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="I72" s="46" t="n">
         <v>0.5</v>
-      </c>
-      <c r="I72" s="46" t="n">
-        <v>0.75</v>
       </c>
       <c r="J72" s="46" t="n">
         <v>0.25</v>
       </c>
       <c r="K72" s="46" t="n">
-        <v>3.5</v>
+        <v>1.75</v>
       </c>
       <c r="L72" s="17" t="n"/>
     </row>
     <row r="73" ht="26" customHeight="1">
       <c r="A73" s="15" t="inlineStr">
         <is>
-          <t>F08-03-3</t>
+          <t>F08-05-1</t>
         </is>
       </c>
       <c r="B73" s="102" t="n"/>
-      <c r="C73" s="17" t="n"/>
+      <c r="C73" s="101" t="inlineStr">
+        <is>
+          <t>登录状态与异常访问控制</t>
+        </is>
+      </c>
       <c r="D73" s="32" t="inlineStr">
         <is>
-          <t>认证异常场景处理</t>
+          <t>会话与超时策略</t>
         </is>
       </c>
       <c r="E73" s="32" t="inlineStr">
         <is>
-          <t>认证失败、账号锁定、多账号冲突</t>
-        </is>
-      </c>
-      <c r="F73" s="46" t="n"/>
+          <t>超时控制、登出、单点登出</t>
+        </is>
+      </c>
+      <c r="F73" s="46" t="n">
+        <v>0.25</v>
+      </c>
       <c r="G73" s="46" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="H73" s="46" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="H73" s="46" t="n">
+        <v>0.25</v>
+      </c>
       <c r="I73" s="46" t="n">
         <v>0.5</v>
       </c>
@@ -18604,41 +18630,37 @@
         <v>0.25</v>
       </c>
       <c r="K73" s="46" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="L73" s="17" t="n"/>
+        <v>2.25</v>
+      </c>
+      <c r="L73" s="92" t="n">
+        <v>3.75</v>
+      </c>
     </row>
     <row r="74" ht="26" customHeight="1">
       <c r="A74" s="15" t="inlineStr">
         <is>
-          <t>F08-04-1</t>
-        </is>
-      </c>
-      <c r="B74" s="102" t="n"/>
-      <c r="C74" s="101" t="inlineStr">
-        <is>
-          <t>用户身份自动识别与关联</t>
-        </is>
-      </c>
+          <t>F08-05-2</t>
+        </is>
+      </c>
+      <c r="B74" s="103" t="n"/>
+      <c r="C74" s="17" t="n"/>
       <c r="D74" s="32" t="inlineStr">
         <is>
-          <t>身份映射规则</t>
+          <t>异常访问控制</t>
         </is>
       </c>
       <c r="E74" s="32" t="inlineStr">
         <is>
-          <t>企业账号↔RIMS用户映射、自动建号规则</t>
-        </is>
-      </c>
-      <c r="F74" s="46" t="n">
-        <v>0.5</v>
-      </c>
+          <t>账号锁定、认证失效限制访问、IP策略</t>
+        </is>
+      </c>
+      <c r="F74" s="46" t="n"/>
       <c r="G74" s="46" t="n"/>
       <c r="H74" s="46" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="I74" s="46" t="n">
         <v>0.5</v>
-      </c>
-      <c r="I74" s="46" t="n">
-        <v>0.25</v>
       </c>
       <c r="J74" s="46" t="n">
         <v>0.25</v>
@@ -18646,148 +18668,132 @@
       <c r="K74" s="46" t="n">
         <v>1.5</v>
       </c>
-      <c r="L74" s="92" t="n">
-        <v>3.25</v>
-      </c>
+      <c r="L74" s="17" t="n"/>
     </row>
     <row r="75" ht="26" customHeight="1">
       <c r="A75" s="15" t="inlineStr">
         <is>
-          <t>F08-04-2</t>
-        </is>
-      </c>
-      <c r="B75" s="102" t="n"/>
-      <c r="C75" s="17" t="n"/>
+          <t>N1-1</t>
+        </is>
+      </c>
+      <c r="B75" s="113" t="inlineStr">
+        <is>
+          <t>非功能与工程支撑</t>
+        </is>
+      </c>
+      <c r="C75" s="99" t="inlineStr">
+        <is>
+          <t>工程初始化与开发基座</t>
+        </is>
+      </c>
       <c r="D75" s="32" t="inlineStr">
         <is>
-          <t>首登自动关联与角色赋予</t>
+          <t>项目初始化</t>
         </is>
       </c>
       <c r="E75" s="32" t="inlineStr">
         <is>
-          <t>默认角色、待分配队列</t>
+          <t>代码仓库/分支策略/开发环境统一/AI工具账号开通</t>
         </is>
       </c>
       <c r="F75" s="46" t="n"/>
       <c r="G75" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="H75" s="46" t="n">
         <v>0.25</v>
       </c>
-      <c r="H75" s="46" t="n">
-        <v>0.75</v>
-      </c>
       <c r="I75" s="46" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="J75" s="46" t="n">
         <v>0.25</v>
       </c>
+      <c r="J75" s="46" t="n"/>
       <c r="K75" s="46" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="L75" s="17" t="n"/>
+        <v>1.5</v>
+      </c>
+      <c r="L75" s="86" t="n">
+        <v>10.75</v>
+      </c>
     </row>
     <row r="76" ht="26" customHeight="1">
       <c r="A76" s="15" t="inlineStr">
         <is>
-          <t>F08-05-1</t>
+          <t>N1-2</t>
         </is>
       </c>
       <c r="B76" s="102" t="n"/>
-      <c r="C76" s="101" t="inlineStr">
-        <is>
-          <t>登录状态与异常访问控制</t>
-        </is>
-      </c>
+      <c r="C76" s="17" t="n"/>
       <c r="D76" s="32" t="inlineStr">
         <is>
-          <t>会话与超时策略</t>
+          <t>前端工程初始化</t>
         </is>
       </c>
       <c r="E76" s="32" t="inlineStr">
         <is>
-          <t>超时控制、登出、单点登出</t>
-        </is>
-      </c>
-      <c r="F76" s="46" t="n">
+          <t>React骨架/路由/布局/组件库/状态管理/构建链</t>
+        </is>
+      </c>
+      <c r="F76" s="46" t="n"/>
+      <c r="G76" s="46" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H76" s="46" t="n"/>
+      <c r="I76" s="46" t="n">
         <v>0.25</v>
       </c>
-      <c r="G76" s="46" t="n">
-        <v>1</v>
-      </c>
-      <c r="H76" s="46" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="I76" s="46" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="J76" s="46" t="n">
-        <v>0.25</v>
-      </c>
+      <c r="J76" s="46" t="n"/>
       <c r="K76" s="46" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="L76" s="92" t="n">
-        <v>3.75</v>
-      </c>
+        <v>1.75</v>
+      </c>
+      <c r="L76" s="17" t="n"/>
     </row>
     <row r="77" ht="26" customHeight="1">
       <c r="A77" s="15" t="inlineStr">
         <is>
-          <t>F08-05-2</t>
-        </is>
-      </c>
-      <c r="B77" s="103" t="n"/>
+          <t>N1-3</t>
+        </is>
+      </c>
+      <c r="B77" s="102" t="n"/>
       <c r="C77" s="17" t="n"/>
       <c r="D77" s="32" t="inlineStr">
         <is>
-          <t>异常访问控制</t>
+          <t>后端工程初始化</t>
         </is>
       </c>
       <c r="E77" s="32" t="inlineStr">
         <is>
-          <t>账号锁定、认证失效限制访问、IP策略</t>
+          <t>.NET Clean Architecture/EF Core/Docker Compose本地环境</t>
         </is>
       </c>
       <c r="F77" s="46" t="n"/>
       <c r="G77" s="46" t="n"/>
       <c r="H77" s="46" t="n">
-        <v>0.75</v>
+        <v>1.5</v>
       </c>
       <c r="I77" s="46" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="J77" s="46" t="n">
         <v>0.25</v>
       </c>
+      <c r="J77" s="46" t="n"/>
       <c r="K77" s="46" t="n">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="L77" s="17" t="n"/>
     </row>
     <row r="78" ht="26" customHeight="1">
       <c r="A78" s="15" t="inlineStr">
         <is>
-          <t>N1-1</t>
-        </is>
-      </c>
-      <c r="B78" s="113" t="inlineStr">
-        <is>
-          <t>非功能与工程支撑</t>
-        </is>
-      </c>
-      <c r="C78" s="99" t="inlineStr">
-        <is>
-          <t>工程初始化与开发基座</t>
-        </is>
-      </c>
+          <t>N1-4</t>
+        </is>
+      </c>
+      <c r="B78" s="102" t="n"/>
+      <c r="C78" s="17" t="n"/>
       <c r="D78" s="32" t="inlineStr">
         <is>
-          <t>项目初始化</t>
+          <t>AI开发工具链与编码规范</t>
         </is>
       </c>
       <c r="E78" s="32" t="inlineStr">
         <is>
-          <t>代码仓库/分支策略/开发环境统一/AI工具账号开通</t>
+          <t>提示词模板库/人机协作规约/ADR规范</t>
         </is>
       </c>
       <c r="F78" s="46" t="n"/>
@@ -18797,110 +18803,112 @@
       <c r="H78" s="46" t="n">
         <v>0.25</v>
       </c>
-      <c r="I78" s="46" t="n">
+      <c r="I78" s="46" t="n"/>
+      <c r="J78" s="46" t="n">
         <v>0.25</v>
       </c>
-      <c r="J78" s="46" t="n"/>
       <c r="K78" s="46" t="n">
         <v>1.5</v>
       </c>
-      <c r="L78" s="86" t="n">
-        <v>10.75</v>
-      </c>
+      <c r="L78" s="17" t="n"/>
     </row>
     <row r="79" ht="26" customHeight="1">
       <c r="A79" s="15" t="inlineStr">
         <is>
-          <t>N1-2</t>
+          <t>N1-5</t>
         </is>
       </c>
       <c r="B79" s="102" t="n"/>
       <c r="C79" s="17" t="n"/>
       <c r="D79" s="32" t="inlineStr">
         <is>
-          <t>前端工程初始化</t>
+          <t>四道安全门禁CI/CD</t>
         </is>
       </c>
       <c r="E79" s="32" t="inlineStr">
         <is>
-          <t>React骨架/路由/布局/组件库/状态管理/构建链</t>
+          <t>构建/镜像/SAST·依赖·密钥扫描/越权用例门禁，流水线落地与拦截演示</t>
         </is>
       </c>
       <c r="F79" s="46" t="n"/>
       <c r="G79" s="46" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="H79" s="46" t="n"/>
+        <v>3</v>
+      </c>
+      <c r="H79" s="46" t="n">
+        <v>0.5</v>
+      </c>
       <c r="I79" s="46" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J79" s="46" t="n">
         <v>0.25</v>
       </c>
-      <c r="J79" s="46" t="n"/>
       <c r="K79" s="46" t="n">
-        <v>1.75</v>
+        <v>4.25</v>
       </c>
       <c r="L79" s="17" t="n"/>
     </row>
     <row r="80" ht="26" customHeight="1">
       <c r="A80" s="15" t="inlineStr">
         <is>
-          <t>N1-3</t>
+          <t>N2-1</t>
         </is>
       </c>
       <c r="B80" s="102" t="n"/>
-      <c r="C80" s="17" t="n"/>
+      <c r="C80" s="99" t="inlineStr">
+        <is>
+          <t>代码质量与静态扫描治理</t>
+        </is>
+      </c>
       <c r="D80" s="32" t="inlineStr">
         <is>
-          <t>后端工程初始化</t>
+          <t>前端ESLint/Prettier规约</t>
         </is>
       </c>
       <c r="E80" s="32" t="inlineStr">
         <is>
-          <t>.NET Clean Architecture/EF Core/Docker Compose本地环境</t>
+          <t>规则集接入CI、存量告警清零、格式统一</t>
         </is>
       </c>
       <c r="F80" s="46" t="n"/>
-      <c r="G80" s="46" t="n"/>
-      <c r="H80" s="46" t="n">
+      <c r="G80" s="46" t="n">
         <v>1.5</v>
       </c>
-      <c r="I80" s="46" t="n">
-        <v>0.25</v>
-      </c>
+      <c r="H80" s="46" t="n"/>
+      <c r="I80" s="46" t="n"/>
       <c r="J80" s="46" t="n"/>
       <c r="K80" s="46" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="L80" s="17" t="n"/>
+        <v>1.5</v>
+      </c>
+      <c r="L80" s="86" t="n">
+        <v>8.75</v>
+      </c>
     </row>
     <row r="81" ht="26" customHeight="1">
       <c r="A81" s="15" t="inlineStr">
         <is>
-          <t>N1-4</t>
+          <t>N2-2</t>
         </is>
       </c>
       <c r="B81" s="102" t="n"/>
       <c r="C81" s="17" t="n"/>
       <c r="D81" s="32" t="inlineStr">
         <is>
-          <t>AI开发工具链与编码规范</t>
+          <t>后端SonarLint规约</t>
         </is>
       </c>
       <c r="E81" s="32" t="inlineStr">
         <is>
-          <t>提示词模板库/人机协作规约/ADR规范</t>
+          <t>代码异味/重复块/复杂度阈值治理清零</t>
         </is>
       </c>
       <c r="F81" s="46" t="n"/>
-      <c r="G81" s="46" t="n">
-        <v>1</v>
-      </c>
+      <c r="G81" s="46" t="n"/>
       <c r="H81" s="46" t="n">
-        <v>0.25</v>
+        <v>1.5</v>
       </c>
       <c r="I81" s="46" t="n"/>
-      <c r="J81" s="46" t="n">
-        <v>0.25</v>
-      </c>
+      <c r="J81" s="46" t="n"/>
       <c r="K81" s="46" t="n">
         <v>1.5</v>
       </c>
@@ -18909,192 +18917,196 @@
     <row r="82" ht="26" customHeight="1">
       <c r="A82" s="15" t="inlineStr">
         <is>
-          <t>N1-5</t>
+          <t>N2-3</t>
         </is>
       </c>
       <c r="B82" s="102" t="n"/>
       <c r="C82" s="17" t="n"/>
       <c r="D82" s="32" t="inlineStr">
         <is>
-          <t>四道安全门禁CI/CD</t>
+          <t>SAST安全告警修复</t>
         </is>
       </c>
       <c r="E82" s="32" t="inlineStr">
         <is>
-          <t>构建/镜像/SAST·依赖·密钥扫描/越权用例门禁，流水线落地与拦截演示</t>
+          <t>硬编码密钥/注入/越权路径等静态安全缺陷修复</t>
         </is>
       </c>
       <c r="F82" s="46" t="n"/>
       <c r="G82" s="46" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H82" s="46" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="I82" s="46" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="J82" s="46" t="n">
         <v>0.25</v>
       </c>
+      <c r="J82" s="46" t="n"/>
       <c r="K82" s="46" t="n">
-        <v>4.25</v>
+        <v>2.25</v>
       </c>
       <c r="L82" s="17" t="n"/>
     </row>
     <row r="83" ht="26" customHeight="1">
       <c r="A83" s="15" t="inlineStr">
         <is>
-          <t>N2-1</t>
+          <t>N2-4</t>
         </is>
       </c>
       <c r="B83" s="102" t="n"/>
-      <c r="C83" s="99" t="inlineStr">
-        <is>
-          <t>代码质量与静态扫描治理</t>
-        </is>
-      </c>
+      <c r="C83" s="17" t="n"/>
       <c r="D83" s="32" t="inlineStr">
         <is>
-          <t>前端ESLint/Prettier规约</t>
+          <t>依赖漏洞治理（SCA）</t>
         </is>
       </c>
       <c r="E83" s="32" t="inlineStr">
         <is>
-          <t>规则集接入CI、存量告警清零、格式统一</t>
+          <t>依赖版本锁定、漏洞升级、SBOM产出</t>
         </is>
       </c>
       <c r="F83" s="46" t="n"/>
       <c r="G83" s="46" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="H83" s="46" t="n"/>
+        <v>0.5</v>
+      </c>
+      <c r="H83" s="46" t="n">
+        <v>0.5</v>
+      </c>
       <c r="I83" s="46" t="n"/>
-      <c r="J83" s="46" t="n"/>
+      <c r="J83" s="46" t="n">
+        <v>0.25</v>
+      </c>
       <c r="K83" s="46" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="L83" s="86" t="n">
-        <v>8.75</v>
-      </c>
+        <v>1.25</v>
+      </c>
+      <c r="L83" s="17" t="n"/>
     </row>
     <row r="84" ht="26" customHeight="1">
       <c r="A84" s="15" t="inlineStr">
         <is>
-          <t>N2-2</t>
+          <t>N2-5</t>
         </is>
       </c>
       <c r="B84" s="102" t="n"/>
       <c r="C84" s="17" t="n"/>
       <c r="D84" s="32" t="inlineStr">
         <is>
-          <t>后端SonarLint规约</t>
+          <t>技术债偿还与外部评审落实</t>
         </is>
       </c>
       <c r="E84" s="32" t="inlineStr">
         <is>
-          <t>代码异味/重复块/复杂度阈值治理清零</t>
+          <t>每周固定还债窗口、关键模块重构、评审意见闭环</t>
         </is>
       </c>
       <c r="F84" s="46" t="n"/>
-      <c r="G84" s="46" t="n"/>
+      <c r="G84" s="46" t="n">
+        <v>1</v>
+      </c>
       <c r="H84" s="46" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="I84" s="46" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="I84" s="46" t="n">
+        <v>0.25</v>
+      </c>
       <c r="J84" s="46" t="n"/>
       <c r="K84" s="46" t="n">
-        <v>1.5</v>
+        <v>2.25</v>
       </c>
       <c r="L84" s="17" t="n"/>
     </row>
     <row r="85" ht="26" customHeight="1">
       <c r="A85" s="15" t="inlineStr">
         <is>
-          <t>N2-3</t>
+          <t>N3-1</t>
         </is>
       </c>
       <c r="B85" s="102" t="n"/>
-      <c r="C85" s="17" t="n"/>
+      <c r="C85" s="99" t="inlineStr">
+        <is>
+          <t>全局非功能实现与优化</t>
+        </is>
+      </c>
       <c r="D85" s="32" t="inlineStr">
         <is>
-          <t>SAST安全告警修复</t>
+          <t>前端性能优化</t>
         </is>
       </c>
       <c r="E85" s="32" t="inlineStr">
         <is>
-          <t>硬编码密钥/注入/越权路径等静态安全缺陷修复</t>
+          <t>懒加载/虚拟滚动/缓存/首屏指标（对照NFR基线）</t>
         </is>
       </c>
       <c r="F85" s="46" t="n"/>
       <c r="G85" s="46" t="n">
-        <v>1</v>
-      </c>
-      <c r="H85" s="46" t="n">
-        <v>1</v>
-      </c>
+        <v>1.5</v>
+      </c>
+      <c r="H85" s="46" t="n"/>
       <c r="I85" s="46" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="J85" s="46" t="n"/>
       <c r="K85" s="46" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="L85" s="17" t="n"/>
+        <v>2</v>
+      </c>
+      <c r="L85" s="86" t="n">
+        <v>11</v>
+      </c>
     </row>
     <row r="86" ht="26" customHeight="1">
       <c r="A86" s="15" t="inlineStr">
         <is>
-          <t>N2-4</t>
+          <t>N3-2</t>
         </is>
       </c>
       <c r="B86" s="102" t="n"/>
       <c r="C86" s="17" t="n"/>
       <c r="D86" s="32" t="inlineStr">
         <is>
-          <t>依赖漏洞治理（SCA）</t>
+          <t>查询与数据性能</t>
         </is>
       </c>
       <c r="E86" s="32" t="inlineStr">
         <is>
-          <t>依赖版本锁定、漏洞升级、SBOM产出</t>
+          <t>分区裁剪/Z-Order/Compaction/小文件治理</t>
         </is>
       </c>
       <c r="F86" s="46" t="n"/>
-      <c r="G86" s="46" t="n">
+      <c r="G86" s="46" t="n"/>
+      <c r="H86" s="46" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I86" s="46" t="n">
         <v>0.5</v>
       </c>
-      <c r="H86" s="46" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="I86" s="46" t="n"/>
-      <c r="J86" s="46" t="n">
-        <v>0.25</v>
-      </c>
+      <c r="J86" s="46" t="n"/>
       <c r="K86" s="46" t="n">
-        <v>1.25</v>
+        <v>2</v>
       </c>
       <c r="L86" s="17" t="n"/>
     </row>
     <row r="87" ht="26" customHeight="1">
       <c r="A87" s="15" t="inlineStr">
         <is>
-          <t>N2-5</t>
+          <t>N3-3</t>
         </is>
       </c>
       <c r="B87" s="102" t="n"/>
       <c r="C87" s="17" t="n"/>
       <c r="D87" s="32" t="inlineStr">
         <is>
-          <t>技术债偿还与外部评审落实</t>
+          <t>统一鉴权与数据掩码中间件</t>
         </is>
       </c>
       <c r="E87" s="32" t="inlineStr">
         <is>
-          <t>每周固定还债窗口、关键模块重构、评审意见闭环</t>
-        </is>
-      </c>
-      <c r="F87" s="46" t="n"/>
+          <t>菜单/API/行级三层校验、掩码旁路防护</t>
+        </is>
+      </c>
+      <c r="F87" s="46" t="n">
+        <v>0.25</v>
+      </c>
       <c r="G87" s="46" t="n">
         <v>1</v>
       </c>
@@ -19102,413 +19114,305 @@
         <v>1</v>
       </c>
       <c r="I87" s="46" t="n">
-        <v>0.25</v>
+        <v>0.75</v>
       </c>
       <c r="J87" s="46" t="n"/>
       <c r="K87" s="46" t="n">
-        <v>2.25</v>
+        <v>3</v>
       </c>
       <c r="L87" s="17" t="n"/>
     </row>
     <row r="88" ht="26" customHeight="1">
       <c r="A88" s="15" t="inlineStr">
         <is>
-          <t>N3-1</t>
+          <t>N3-4</t>
         </is>
       </c>
       <c r="B88" s="102" t="n"/>
-      <c r="C88" s="99" t="inlineStr">
-        <is>
-          <t>全局非功能实现与优化</t>
-        </is>
-      </c>
+      <c r="C88" s="17" t="n"/>
       <c r="D88" s="32" t="inlineStr">
         <is>
-          <t>前端性能优化</t>
+          <t>可观测性（日志/监控/告警）</t>
         </is>
       </c>
       <c r="E88" s="32" t="inlineStr">
         <is>
-          <t>懒加载/虚拟滚动/缓存/首屏指标（对照NFR基线）</t>
+          <t>应用日志规范、作业监控、异常告警通道</t>
         </is>
       </c>
       <c r="F88" s="46" t="n"/>
       <c r="G88" s="46" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H88" s="46" t="n">
         <v>1.5</v>
       </c>
-      <c r="H88" s="46" t="n"/>
       <c r="I88" s="46" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="J88" s="46" t="n"/>
       <c r="K88" s="46" t="n">
-        <v>2</v>
-      </c>
-      <c r="L88" s="86" t="n">
-        <v>11</v>
-      </c>
+        <v>2.25</v>
+      </c>
+      <c r="L88" s="17" t="n"/>
     </row>
     <row r="89" ht="26" customHeight="1">
       <c r="A89" s="15" t="inlineStr">
         <is>
-          <t>N3-2</t>
+          <t>N3-5</t>
         </is>
       </c>
       <c r="B89" s="102" t="n"/>
       <c r="C89" s="17" t="n"/>
       <c r="D89" s="32" t="inlineStr">
         <is>
-          <t>查询与数据性能</t>
+          <t>容量与增长验证</t>
         </is>
       </c>
       <c r="E89" s="32" t="inlineStr">
         <is>
-          <t>分区裁剪/Z-Order/Compaction/小文件治理</t>
+          <t>600~800表规模扩容压测与容量报告</t>
         </is>
       </c>
       <c r="F89" s="46" t="n"/>
       <c r="G89" s="46" t="n"/>
       <c r="H89" s="46" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="I89" s="46" t="n">
         <v>0.5</v>
       </c>
-      <c r="J89" s="46" t="n"/>
+      <c r="J89" s="46" t="n">
+        <v>0.25</v>
+      </c>
       <c r="K89" s="46" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="L89" s="17" t="n"/>
     </row>
     <row r="90" ht="26" customHeight="1">
       <c r="A90" s="15" t="inlineStr">
         <is>
-          <t>N3-3</t>
+          <t>N4-1</t>
         </is>
       </c>
       <c r="B90" s="102" t="n"/>
-      <c r="C90" s="17" t="n"/>
+      <c r="C90" s="99" t="inlineStr">
+        <is>
+          <t>部署与运维支撑</t>
+        </is>
+      </c>
       <c r="D90" s="32" t="inlineStr">
         <is>
-          <t>统一鉴权与数据掩码中间件</t>
+          <t>Helm发布包与values</t>
         </is>
       </c>
       <c r="E90" s="32" t="inlineStr">
         <is>
-          <t>菜单/API/行级三层校验、掩码旁路防护</t>
-        </is>
-      </c>
-      <c r="F90" s="46" t="n">
-        <v>0.25</v>
-      </c>
+          <t>生产values/镜像标签策略/发布Runbook</t>
+        </is>
+      </c>
+      <c r="F90" s="46" t="n"/>
       <c r="G90" s="46" t="n">
         <v>1</v>
       </c>
       <c r="H90" s="46" t="n">
-        <v>1</v>
-      </c>
-      <c r="I90" s="46" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="J90" s="46" t="n"/>
+        <v>0.25</v>
+      </c>
+      <c r="I90" s="46" t="n"/>
+      <c r="J90" s="46" t="n">
+        <v>0.25</v>
+      </c>
       <c r="K90" s="46" t="n">
-        <v>3</v>
-      </c>
-      <c r="L90" s="17" t="n"/>
+        <v>1.5</v>
+      </c>
+      <c r="L90" s="86" t="n">
+        <v>5.5</v>
+      </c>
     </row>
     <row r="91" ht="26" customHeight="1">
       <c r="A91" s="15" t="inlineStr">
         <is>
-          <t>N3-4</t>
+          <t>N4-2</t>
         </is>
       </c>
       <c r="B91" s="102" t="n"/>
       <c r="C91" s="17" t="n"/>
       <c r="D91" s="32" t="inlineStr">
         <is>
-          <t>可观测性（日志/监控/告警）</t>
+          <t>部署预演与回退预案</t>
         </is>
       </c>
       <c r="E91" s="32" t="inlineStr">
         <is>
-          <t>应用日志规范、作业监控、异常告警通道</t>
+          <t>Staging完整演练、回退验证</t>
         </is>
       </c>
       <c r="F91" s="46" t="n"/>
       <c r="G91" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="H91" s="46" t="n">
         <v>0.5</v>
-      </c>
-      <c r="H91" s="46" t="n">
-        <v>1.5</v>
       </c>
       <c r="I91" s="46" t="n">
         <v>0.25</v>
       </c>
       <c r="J91" s="46" t="n"/>
       <c r="K91" s="46" t="n">
-        <v>2.25</v>
+        <v>1.75</v>
       </c>
       <c r="L91" s="17" t="n"/>
     </row>
     <row r="92" ht="26" customHeight="1">
       <c r="A92" s="15" t="inlineStr">
         <is>
-          <t>N3-5</t>
-        </is>
-      </c>
-      <c r="B92" s="102" t="n"/>
+          <t>N4-3</t>
+        </is>
+      </c>
+      <c r="B92" s="103" t="n"/>
       <c r="C92" s="17" t="n"/>
       <c r="D92" s="32" t="inlineStr">
         <is>
-          <t>容量与增长验证</t>
+          <t>上线值守与运维交接</t>
         </is>
       </c>
       <c r="E92" s="32" t="inlineStr">
         <is>
-          <t>600~800表规模扩容压测与容量报告</t>
+          <t>上线窗口值守、运维交接与培训材料</t>
         </is>
       </c>
       <c r="F92" s="46" t="n"/>
-      <c r="G92" s="46" t="n"/>
+      <c r="G92" s="46" t="n">
+        <v>1</v>
+      </c>
       <c r="H92" s="46" t="n">
         <v>1</v>
       </c>
-      <c r="I92" s="46" t="n">
-        <v>0.5</v>
-      </c>
+      <c r="I92" s="46" t="n"/>
       <c r="J92" s="46" t="n">
         <v>0.25</v>
       </c>
       <c r="K92" s="46" t="n">
-        <v>1.75</v>
+        <v>2.25</v>
       </c>
       <c r="L92" s="17" t="n"/>
     </row>
-    <row r="93" ht="26" customHeight="1">
-      <c r="A93" s="15" t="inlineStr">
-        <is>
-          <t>N4-1</t>
-        </is>
-      </c>
-      <c r="B93" s="102" t="n"/>
-      <c r="C93" s="99" t="inlineStr">
-        <is>
-          <t>部署与运维支撑</t>
-        </is>
-      </c>
-      <c r="D93" s="32" t="inlineStr">
-        <is>
-          <t>Helm发布包与values</t>
-        </is>
-      </c>
-      <c r="E93" s="32" t="inlineStr">
-        <is>
-          <t>生产values/镜像标签策略/发布Runbook</t>
-        </is>
-      </c>
-      <c r="F93" s="46" t="n"/>
-      <c r="G93" s="46" t="n">
-        <v>1</v>
-      </c>
-      <c r="H93" s="46" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="I93" s="46" t="n"/>
-      <c r="J93" s="46" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="K93" s="46" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="L93" s="86" t="n">
-        <v>5.5</v>
-      </c>
-    </row>
-    <row r="94" ht="26" customHeight="1">
-      <c r="A94" s="15" t="inlineStr">
-        <is>
-          <t>N4-2</t>
-        </is>
-      </c>
-      <c r="B94" s="102" t="n"/>
-      <c r="C94" s="17" t="n"/>
-      <c r="D94" s="32" t="inlineStr">
-        <is>
-          <t>部署预演与回退预案</t>
-        </is>
-      </c>
-      <c r="E94" s="32" t="inlineStr">
-        <is>
-          <t>Staging完整演练、回退验证</t>
-        </is>
-      </c>
-      <c r="F94" s="46" t="n"/>
-      <c r="G94" s="46" t="n">
-        <v>1</v>
-      </c>
-      <c r="H94" s="46" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="I94" s="46" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="J94" s="46" t="n"/>
-      <c r="K94" s="46" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="L94" s="17" t="n"/>
-    </row>
-    <row r="95" ht="26" customHeight="1">
-      <c r="A95" s="15" t="inlineStr">
-        <is>
-          <t>N4-3</t>
-        </is>
-      </c>
-      <c r="B95" s="103" t="n"/>
-      <c r="C95" s="17" t="n"/>
-      <c r="D95" s="32" t="inlineStr">
-        <is>
-          <t>上线值守与运维交接</t>
-        </is>
-      </c>
-      <c r="E95" s="32" t="inlineStr">
-        <is>
-          <t>上线窗口值守、运维交接与培训材料</t>
-        </is>
-      </c>
-      <c r="F95" s="46" t="n"/>
-      <c r="G95" s="46" t="n">
-        <v>1</v>
-      </c>
-      <c r="H95" s="46" t="n">
-        <v>1</v>
-      </c>
-      <c r="I95" s="46" t="n"/>
-      <c r="J95" s="46" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="K95" s="46" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="L95" s="17" t="n"/>
-    </row>
-    <row r="96">
-      <c r="A96" s="8" t="inlineStr"/>
-      <c r="B96" s="8" t="inlineStr">
+    <row r="93">
+      <c r="A93" s="8" t="inlineStr"/>
+      <c r="B93" s="8" t="inlineStr">
         <is>
           <t>总计</t>
         </is>
       </c>
-      <c r="C96" s="8" t="inlineStr"/>
-      <c r="D96" s="93" t="inlineStr">
-        <is>
-          <t>26项功能×75子任务 + 非功能工程×18子任务</t>
-        </is>
-      </c>
-      <c r="E96" s="93" t="inlineStr">
+      <c r="C93" s="8" t="inlineStr"/>
+      <c r="D93" s="93" t="inlineStr">
+        <is>
+          <t>25项功能×72子任务 + 非功能工程×18子任务（F04-04=Azure原生能力，不计开发）</t>
+        </is>
+      </c>
+      <c r="E93" s="93" t="inlineStr">
         <is>
           <t>独立直估（另含少量需求/PM等工作未列入本表）</t>
         </is>
       </c>
-      <c r="F96" s="44" t="n">
-        <v>13</v>
-      </c>
-      <c r="G96" s="44" t="n">
+      <c r="F93" s="44" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="G93" s="44" t="n">
         <v>60.25</v>
       </c>
-      <c r="H96" s="44" t="n">
-        <v>75.25</v>
-      </c>
-      <c r="I96" s="44" t="n">
-        <v>40.25</v>
-      </c>
-      <c r="J96" s="44" t="n">
-        <v>21.5</v>
-      </c>
-      <c r="K96" s="44" t="n">
-        <v>210.25</v>
-      </c>
-      <c r="L96" s="8" t="inlineStr"/>
-    </row>
-    <row r="98" ht="56" customHeight="1">
-      <c r="A98" s="94" t="inlineStr">
-        <is>
-          <t>对照说明（三个口径）：① 功能直估 174.25 人天（BA 12.75 / Wade 43.75 / DevB 62.0 / 测试 35.75 / SLC 20.0）——本版已按配置界面/动态表单复杂度上调前端工作量；② 非功能与工程支撑直估 36.0 人天（N1初始化与基座/N2 ESLint·SonarLint·SAST·依赖治理/N3性能·鉴权掩码·可观测·容量/N4部署运维）——此前缺失，现已补齐；③ 合计 210.25 人天 vs 排期计划185人天：Wade 60.25≈计划60 ✓；DevB 75.25超计划60约 15.25 人天，数据/ETL侧为最大风险口，需靠AI生成ETL与SQL提效吸收；总缺口约 25.25 人天（12%），建议以本表为规模基线纳入风险跟踪，必要时启用备用赶工日（9/20、10/10）。</t>
+      <c r="H93" s="44" t="n">
+        <v>72.25</v>
+      </c>
+      <c r="I93" s="44" t="n">
+        <v>38.75</v>
+      </c>
+      <c r="J93" s="44" t="n">
+        <v>20.75</v>
+      </c>
+      <c r="K93" s="44" t="n">
+        <v>204.5</v>
+      </c>
+      <c r="L93" s="8" t="inlineStr"/>
+    </row>
+    <row r="95" ht="56" customHeight="1">
+      <c r="A95" s="94" t="inlineStr">
+        <is>
+          <t>对照说明（三个口径）：① 功能直估 168.5 人天（BA 12.25 / Wade 43.75 / DevB 59.0 / 测试 34.25 / SLC 19.25）——本版已按配置界面/动态表单复杂度上调前端工作量；② 非功能与工程支撑直估 36.0 人天（N1初始化与基座/N2 ESLint·SonarLint·SAST·依赖治理/N3性能·鉴权掩码·可观测·容量/N4部署运维）——此前缺失，现已补齐；③ 合计 204.5 人天 vs 排期计划185人天：Wade 60.25≈计划60 ✓；DevB 72.25超计划60约 12.25 人天，数据/ETL侧为最大风险口，需靠AI生成ETL与SQL提效吸收；总缺口约 19.5 人天（10%），建议以本表为规模基线纳入风险跟踪，必要时启用备用赶工日（9/20、10/10）。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="70">
+  <mergeCells count="68">
     <mergeCell ref="C56:C58"/>
     <mergeCell ref="C14:C17"/>
-    <mergeCell ref="L59:L61"/>
     <mergeCell ref="L35:L37"/>
-    <mergeCell ref="L83:L87"/>
-    <mergeCell ref="L62:L63"/>
+    <mergeCell ref="L66:L67"/>
     <mergeCell ref="L26:L28"/>
     <mergeCell ref="L44:L46"/>
-    <mergeCell ref="B78:B95"/>
+    <mergeCell ref="C73:C74"/>
+    <mergeCell ref="L71:L72"/>
+    <mergeCell ref="L47:L48"/>
     <mergeCell ref="L56:L58"/>
+    <mergeCell ref="L63:L65"/>
     <mergeCell ref="L41:L43"/>
+    <mergeCell ref="L85:L89"/>
     <mergeCell ref="C23:C25"/>
     <mergeCell ref="C32:C34"/>
     <mergeCell ref="C38:C40"/>
-    <mergeCell ref="C50:C51"/>
+    <mergeCell ref="L90:L92"/>
     <mergeCell ref="C10:C13"/>
-    <mergeCell ref="C54:C55"/>
-    <mergeCell ref="C66:C68"/>
-    <mergeCell ref="L88:L92"/>
-    <mergeCell ref="B35:B46"/>
-    <mergeCell ref="L74:L75"/>
-    <mergeCell ref="B66:B77"/>
-    <mergeCell ref="L64:L65"/>
+    <mergeCell ref="C59:C60"/>
+    <mergeCell ref="B63:B74"/>
+    <mergeCell ref="A95:L95"/>
+    <mergeCell ref="C53:C55"/>
+    <mergeCell ref="C71:C72"/>
+    <mergeCell ref="C47:C48"/>
+    <mergeCell ref="L73:L74"/>
     <mergeCell ref="C21:C22"/>
-    <mergeCell ref="B47:B58"/>
-    <mergeCell ref="L54:L55"/>
+    <mergeCell ref="C68:C70"/>
+    <mergeCell ref="L80:L84"/>
     <mergeCell ref="L14:L17"/>
-    <mergeCell ref="L76:L77"/>
+    <mergeCell ref="B29:B34"/>
     <mergeCell ref="C18:C20"/>
     <mergeCell ref="B23:B28"/>
-    <mergeCell ref="C76:C77"/>
     <mergeCell ref="L32:L34"/>
-    <mergeCell ref="C52:C53"/>
-    <mergeCell ref="B29:B34"/>
     <mergeCell ref="L10:L13"/>
-    <mergeCell ref="C78:C82"/>
-    <mergeCell ref="L66:L68"/>
+    <mergeCell ref="C61:C62"/>
+    <mergeCell ref="C51:C52"/>
+    <mergeCell ref="B75:B92"/>
+    <mergeCell ref="L51:L52"/>
     <mergeCell ref="C3:C9"/>
-    <mergeCell ref="L69:L70"/>
-    <mergeCell ref="L47:L49"/>
+    <mergeCell ref="L53:L55"/>
+    <mergeCell ref="C66:C67"/>
+    <mergeCell ref="B56:B62"/>
     <mergeCell ref="C29:C31"/>
-    <mergeCell ref="L50:L51"/>
     <mergeCell ref="L21:L22"/>
-    <mergeCell ref="L93:L95"/>
+    <mergeCell ref="L59:L60"/>
     <mergeCell ref="C41:C43"/>
+    <mergeCell ref="C63:C65"/>
+    <mergeCell ref="L75:L79"/>
+    <mergeCell ref="C35:C37"/>
+    <mergeCell ref="L49:L50"/>
     <mergeCell ref="B3:B22"/>
-    <mergeCell ref="B59:B65"/>
-    <mergeCell ref="C35:C37"/>
-    <mergeCell ref="L71:L73"/>
-    <mergeCell ref="C62:C63"/>
     <mergeCell ref="C26:C28"/>
     <mergeCell ref="C44:C46"/>
-    <mergeCell ref="C59:C61"/>
-    <mergeCell ref="C83:C87"/>
+    <mergeCell ref="B35:B43"/>
     <mergeCell ref="L18:L20"/>
-    <mergeCell ref="L78:L82"/>
-    <mergeCell ref="C88:C92"/>
-    <mergeCell ref="C93:C95"/>
-    <mergeCell ref="L52:L53"/>
-    <mergeCell ref="C69:C70"/>
-    <mergeCell ref="A98:L98"/>
     <mergeCell ref="L3:L9"/>
-    <mergeCell ref="C47:C49"/>
+    <mergeCell ref="L61:L62"/>
+    <mergeCell ref="L68:L70"/>
     <mergeCell ref="A1:L1"/>
-    <mergeCell ref="C74:C75"/>
-    <mergeCell ref="C64:C65"/>
+    <mergeCell ref="C80:C84"/>
+    <mergeCell ref="B44:B55"/>
+    <mergeCell ref="C85:C89"/>
+    <mergeCell ref="C90:C92"/>
     <mergeCell ref="L38:L40"/>
     <mergeCell ref="L29:L31"/>
-    <mergeCell ref="C71:C73"/>
+    <mergeCell ref="C49:C50"/>
     <mergeCell ref="L23:L25"/>
+    <mergeCell ref="C75:C79"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/RIMS项目WBS工作分解_AI Native版.xlsx
+++ b/RIMS项目WBS工作分解_AI Native版.xlsx
@@ -943,7 +943,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B37"/>
+  <dimension ref="A1:B38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1313,6 +1313,18 @@
         </is>
       </c>
       <c r="B37" s="4" t="inlineStr">
+        <is>
+          <t>按功能维度查看：26项功能×（BA/开发A/开发B/测试/文档）五类角色各自的工作内容与人天，另有9类公共支撑行（初始化/架构/集成/专项/上线/管理）；底部与185人天自动对账，可与按开发顺序的「WBS分解」页对照使用</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="30" customHeight="1">
+      <c r="A38" s="38" t="inlineStr">
+        <is>
+          <t>功能视角分解</t>
+        </is>
+      </c>
+      <c r="B38" s="4" t="inlineStr">
         <is>
           <t>按功能维度查看：26项功能×（BA/开发A/开发B/测试/文档）五类角色各自的工作内容与人天，另有9类公共支撑行（初始化/架构/集成/专项/上线/管理）；底部与185人天自动对账，可与按开发顺序的「WBS分解」页对照使用</t>
         </is>
@@ -6809,7 +6821,7 @@
       </c>
       <c r="B88" s="22" t="inlineStr">
         <is>
-          <t>F04-01 数据加密存储（SSE+CMK+PII字段加密落盘验证/密钥版本化）</t>
+          <t>F04-01 数据加密存储（ADLS原生SSE+CMK配置+PII字段加密落盘验证/密钥版本化）</t>
         </is>
       </c>
       <c r="C88" s="15" t="n">
@@ -6872,7 +6884,7 @@
       </c>
       <c r="B89" s="22" t="inlineStr">
         <is>
-          <t>F04-02 密钥管理（Key Vault创建/保管/更新/权限/操作审计）</t>
+          <t>F04-02 密钥管理（Key Vault原生服务+RBAC配置+应用Managed Identity集成与审计对接）</t>
         </is>
       </c>
       <c r="C89" s="15" t="n">
@@ -6924,7 +6936,11 @@
         </is>
       </c>
       <c r="O89" s="21" t="n"/>
-      <c r="P89" s="21" t="n"/>
+      <c r="P89" s="21" t="inlineStr">
+        <is>
+          <t>创建/保管/轮换/权限均为Key Vault原生能力；开发仅集成与审计对接</t>
+        </is>
+      </c>
       <c r="Q89" s="17" t="inlineStr"/>
     </row>
     <row r="90">
@@ -14101,7 +14117,7 @@
       <c r="G12" s="55" t="n"/>
       <c r="H12" s="54" t="inlineStr">
         <is>
-          <t>SSE+CMK+PII字段加密</t>
+          <t>ADLS原生SSE/CMK配置+PII字段级加密</t>
         </is>
       </c>
       <c r="I12" s="55" t="n">
@@ -14165,7 +14181,7 @@
       <c r="G13" s="55" t="n"/>
       <c r="H13" s="54" t="inlineStr">
         <is>
-          <t>Key Vault创建/更新/权限/审计</t>
+          <t>Key Vault原生(RBAC)+应用Managed Identity集成</t>
         </is>
       </c>
       <c r="I13" s="55" t="n">
@@ -14229,7 +14245,7 @@
       <c r="G14" s="55" t="n"/>
       <c r="H14" s="54" t="inlineStr">
         <is>
-          <t>备份策略配置+副本创建</t>
+          <t>SQL PITR/ADLS原生备份策略配置</t>
         </is>
       </c>
       <c r="I14" s="55" t="n">
@@ -14995,7 +15011,7 @@
       <c r="E26" s="64" t="n"/>
       <c r="F26" s="63" t="inlineStr">
         <is>
-          <t>SSO集成（登录页+后端链路）</t>
+          <t>SSO集成（Entra ID+MSAL中间件）</t>
         </is>
       </c>
       <c r="G26" s="64" t="n">
@@ -17187,7 +17203,7 @@
         <v>1.75</v>
       </c>
       <c r="L35" s="83" t="n">
-        <v>6.5</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="36" ht="26" customHeight="1">
@@ -17200,18 +17216,18 @@
       <c r="C36" s="17" t="n"/>
       <c r="D36" s="32" t="inlineStr">
         <is>
-          <t>存储层加密落地</t>
+          <t>存储层加密落地【原生】</t>
         </is>
       </c>
       <c r="E36" s="32" t="inlineStr">
         <is>
-          <t>ADLS SSE、Key Vault CMK集成、密钥轮换</t>
+          <t>ADLS SSE+CMK为存储账户原生选项：启用/托管密钥绑定/轮换/传输加密验证（配置为主）</t>
         </is>
       </c>
       <c r="F36" s="46" t="n"/>
       <c r="G36" s="46" t="n"/>
       <c r="H36" s="46" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="I36" s="46" t="n">
         <v>0.5</v>
@@ -17220,7 +17236,7 @@
         <v>0.25</v>
       </c>
       <c r="K36" s="46" t="n">
-        <v>2.25</v>
+        <v>1.25</v>
       </c>
       <c r="L36" s="17" t="n"/>
     </row>
@@ -17272,12 +17288,12 @@
       </c>
       <c r="D38" s="32" t="inlineStr">
         <is>
-          <t>密钥全流程管理</t>
+          <t>密钥全流程管理【原生】</t>
         </is>
       </c>
       <c r="E38" s="32" t="inlineStr">
         <is>
-          <t>创建/保管/更新/吊销/权限控制</t>
+          <t>Key Vault原生服务：创建/保管/轮换/吊销/权限=Key Vault+RBAC配置；开发仅应用侧Managed Identity集成与密钥引用</t>
         </is>
       </c>
       <c r="F38" s="46" t="n">
@@ -17285,7 +17301,7 @@
       </c>
       <c r="G38" s="46" t="n"/>
       <c r="H38" s="46" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="I38" s="46" t="n">
         <v>0.5</v>
@@ -17294,10 +17310,10 @@
         <v>0.25</v>
       </c>
       <c r="K38" s="46" t="n">
-        <v>2.5</v>
+        <v>1.5</v>
       </c>
       <c r="L38" s="83" t="n">
-        <v>6</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="39" ht="26" customHeight="1">
@@ -17310,20 +17326,20 @@
       <c r="C39" s="17" t="n"/>
       <c r="D39" s="32" t="inlineStr">
         <is>
-          <t>密钥操作审计与告警</t>
+          <t>密钥操作审计与告警【原生】</t>
         </is>
       </c>
       <c r="E39" s="32" t="inlineStr">
         <is>
-          <t>操作日志、异常使用告警</t>
+          <t>Key Vault诊断日志+Azure Monitor原生告警，开发仅对接审计页</t>
         </is>
       </c>
       <c r="F39" s="46" t="n"/>
       <c r="G39" s="46" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="H39" s="46" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="I39" s="46" t="n">
         <v>0.5</v>
@@ -17332,7 +17348,7 @@
         <v>0.25</v>
       </c>
       <c r="K39" s="46" t="n">
-        <v>1.75</v>
+        <v>1.25</v>
       </c>
       <c r="L39" s="17" t="n"/>
     </row>
@@ -17346,21 +17362,19 @@
       <c r="C40" s="17" t="n"/>
       <c r="D40" s="32" t="inlineStr">
         <is>
-          <t>密钥管理界面</t>
+          <t>密钥状态展示（不自研管理界面）【原生】</t>
         </is>
       </c>
       <c r="E40" s="32" t="inlineStr">
         <is>
-          <t>密钥清单、版本、权限分配界面</t>
+          <t>密钥操作走Azure门户/CLI+RBAC，不自研管理界面；系统内仅密钥状态只读展示</t>
         </is>
       </c>
       <c r="F40" s="46" t="n"/>
       <c r="G40" s="46" t="n">
-        <v>1</v>
-      </c>
-      <c r="H40" s="46" t="n">
         <v>0.25</v>
       </c>
+      <c r="H40" s="46" t="n"/>
       <c r="I40" s="46" t="n">
         <v>0.25</v>
       </c>
@@ -17368,7 +17382,7 @@
         <v>0.25</v>
       </c>
       <c r="K40" s="46" t="n">
-        <v>1.75</v>
+        <v>0.75</v>
       </c>
       <c r="L40" s="17" t="n"/>
     </row>
@@ -17413,7 +17427,7 @@
         <v>2.25</v>
       </c>
       <c r="L41" s="83" t="n">
-        <v>6.25</v>
+        <v>4.75</v>
       </c>
     </row>
     <row r="42" ht="26" customHeight="1">
@@ -17426,18 +17440,18 @@
       <c r="C42" s="17" t="n"/>
       <c r="D42" s="32" t="inlineStr">
         <is>
-          <t>备份作业与副本创建</t>
+          <t>备份作业与副本创建【原生】</t>
         </is>
       </c>
       <c r="E42" s="32" t="inlineStr">
         <is>
-          <t>元数据库PITR、湖快照、附件副本</t>
+          <t>SQL DB PITR/ADLS生命周期与副本均为原生策略：仅策略配置与脚本化启用</t>
         </is>
       </c>
       <c r="F42" s="46" t="n"/>
       <c r="G42" s="46" t="n"/>
       <c r="H42" s="46" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="I42" s="46" t="n">
         <v>0.5</v>
@@ -17446,7 +17460,7 @@
         <v>0.25</v>
       </c>
       <c r="K42" s="46" t="n">
-        <v>2.25</v>
+        <v>1.25</v>
       </c>
       <c r="L42" s="17" t="n"/>
     </row>
@@ -17460,20 +17474,20 @@
       <c r="C43" s="17" t="n"/>
       <c r="D43" s="32" t="inlineStr">
         <is>
-          <t>备份监控与恢复操作</t>
+          <t>备份监控与恢复操作【原生】</t>
         </is>
       </c>
       <c r="E43" s="32" t="inlineStr">
         <is>
-          <t>备份状态监控、恢复流程</t>
+          <t>Azure Monitor原生备份告警+恢复流程验证演练</t>
         </is>
       </c>
       <c r="F43" s="46" t="n"/>
       <c r="G43" s="46" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="H43" s="46" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="I43" s="46" t="n">
         <v>0.5</v>
@@ -17482,7 +17496,7 @@
         <v>0.25</v>
       </c>
       <c r="K43" s="46" t="n">
-        <v>1.75</v>
+        <v>1.25</v>
       </c>
       <c r="L43" s="17" t="n"/>
     </row>
@@ -18414,12 +18428,12 @@
       </c>
       <c r="D68" s="32" t="inlineStr">
         <is>
-          <t>Entra ID对接配置</t>
+          <t>Entra ID对接配置【原生】</t>
         </is>
       </c>
       <c r="E68" s="32" t="inlineStr">
         <is>
-          <t>应用注册、回调配置、claims映射</t>
+          <t>应用注册/回调/claims为Entra控制台配置，开发仅环境参数化</t>
         </is>
       </c>
       <c r="F68" s="46" t="n">
@@ -18429,7 +18443,7 @@
         <v>0.5</v>
       </c>
       <c r="H68" s="46" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="I68" s="46" t="n">
         <v>0.5</v>
@@ -18438,10 +18452,10 @@
         <v>0.25</v>
       </c>
       <c r="K68" s="46" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="L68" s="92" t="n">
-        <v>7.25</v>
+        <v>6</v>
       </c>
     </row>
     <row r="69" ht="26" customHeight="1">
@@ -18454,17 +18468,17 @@
       <c r="C69" s="17" t="n"/>
       <c r="D69" s="32" t="inlineStr">
         <is>
-          <t>SSO登录链路</t>
+          <t>SSO登录链路【中间件】</t>
         </is>
       </c>
       <c r="E69" s="32" t="inlineStr">
         <is>
-          <t>登录页、令牌交换、会话管理</t>
+          <t>MSAL/OIDC标准库承载认证流，自研仅登录页/会话与定制逻辑</t>
         </is>
       </c>
       <c r="F69" s="46" t="n"/>
       <c r="G69" s="46" t="n">
-        <v>2</v>
+        <v>1.25</v>
       </c>
       <c r="H69" s="46" t="n">
         <v>0.5</v>
@@ -18476,7 +18490,7 @@
         <v>0.25</v>
       </c>
       <c r="K69" s="46" t="n">
-        <v>3.5</v>
+        <v>2.75</v>
       </c>
       <c r="L69" s="17" t="n"/>
     </row>
@@ -19051,7 +19065,7 @@
         <v>2</v>
       </c>
       <c r="L85" s="86" t="n">
-        <v>11</v>
+        <v>10.25</v>
       </c>
     </row>
     <row r="86" ht="26" customHeight="1">
@@ -19132,12 +19146,12 @@
       <c r="C88" s="17" t="n"/>
       <c r="D88" s="32" t="inlineStr">
         <is>
-          <t>可观测性（日志/监控/告警）</t>
+          <t>可观测性（日志/监控/告警）【原生】</t>
         </is>
       </c>
       <c r="E88" s="32" t="inlineStr">
         <is>
-          <t>应用日志规范、作业监控、异常告警通道</t>
+          <t>App Insights/Log Analytics/Azure Monitor原生：开发仅SDK插桩、作业监控对接与仪表盘</t>
         </is>
       </c>
       <c r="F88" s="46" t="n"/>
@@ -19145,14 +19159,14 @@
         <v>0.5</v>
       </c>
       <c r="H88" s="46" t="n">
-        <v>1.5</v>
+        <v>0.75</v>
       </c>
       <c r="I88" s="46" t="n">
         <v>0.25</v>
       </c>
       <c r="J88" s="46" t="n"/>
       <c r="K88" s="46" t="n">
-        <v>2.25</v>
+        <v>1.5</v>
       </c>
       <c r="L88" s="17" t="n"/>
     </row>
@@ -19320,10 +19334,10 @@
         <v>12.5</v>
       </c>
       <c r="G93" s="44" t="n">
-        <v>60.25</v>
+        <v>58.25</v>
       </c>
       <c r="H93" s="44" t="n">
-        <v>72.25</v>
+        <v>67.25</v>
       </c>
       <c r="I93" s="44" t="n">
         <v>38.75</v>
@@ -19332,14 +19346,14 @@
         <v>20.75</v>
       </c>
       <c r="K93" s="44" t="n">
-        <v>204.5</v>
+        <v>197.5</v>
       </c>
       <c r="L93" s="8" t="inlineStr"/>
     </row>
     <row r="95" ht="56" customHeight="1">
       <c r="A95" s="94" t="inlineStr">
         <is>
-          <t>对照说明（三个口径）：① 功能直估 168.5 人天（BA 12.25 / Wade 43.75 / DevB 59.0 / 测试 34.25 / SLC 19.25）——本版已按配置界面/动态表单复杂度上调前端工作量；② 非功能与工程支撑直估 36.0 人天（N1初始化与基座/N2 ESLint·SonarLint·SAST·依赖治理/N3性能·鉴权掩码·可观测·容量/N4部署运维）——此前缺失，现已补齐；③ 合计 204.5 人天 vs 排期计划185人天：Wade 60.25≈计划60 ✓；DevB 72.25超计划60约 12.25 人天，数据/ETL侧为最大风险口，需靠AI生成ETL与SQL提效吸收；总缺口约 19.5 人天（10%），建议以本表为规模基线纳入风险跟踪，必要时启用备用赶工日（9/20、10/10）。</t>
+          <t>对照说明（三个口径）：① 功能直估 162.25 人天（BA 12.25 / Wade 41.75 / DevB 54.75 / 测试 34.25 / SLC 19.25）——本版已按配置界面/动态表单复杂度上调前端工作量；② 非功能与工程支撑直估 35.25 人天（N1初始化与基座/N2 ESLint·SonarLint·SAST·依赖治理/N3性能·鉴权掩码·可观测·容量/N4部署运维）——此前缺失，现已补齐；③ 已识别原生组件能力（按配置+验证计价，不再计自研开发，子任务标注【原生】/【中间件】）：ADLS SSE/CMK加密、ADLS GRS异地冗余、Key Vault密钥管理、SQL DB PITR备份与Monitor告警、Entra ID+MSAL单点登录、App Insights/Log Analytics可观测性、Unity Catalog授权、Azure DevOps扫描门禁；④ 合计 197.5 人天 vs 排期计划185人天：Wade 58.25；DevB 67.25仍超计划60约 7.25 人天（数据/ETL侧，靠AI生成ETL/SQL提效吸收）；总缺口约 12.5 人天（6%），建议以本表为规模基线纳入风险跟踪，必要时启用备用赶工日（9/20、10/10）。</t>
         </is>
       </c>
     </row>

--- a/RIMS项目WBS工作分解_AI Native版.xlsx
+++ b/RIMS项目WBS工作分解_AI Native版.xlsx
@@ -33,7 +33,7 @@
     <numFmt numFmtId="165" formatCode="0.##"/>
     <numFmt numFmtId="166" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="11">
+  <fonts count="13">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -79,6 +79,15 @@
     <font>
       <i val="1"/>
       <color rgb="00C00000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="001F4E79"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <color rgb="001F4E79"/>
       <sz val="9"/>
     </font>
   </fonts>
@@ -232,7 +241,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="114">
+  <cellXfs count="116">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -536,6 +545,12 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1307,28 +1322,12 @@
       <c r="B36" s="4" t="n"/>
     </row>
     <row r="37" ht="30" customHeight="1">
-      <c r="A37" s="38" t="inlineStr">
-        <is>
-          <t>功能视角分解</t>
-        </is>
-      </c>
-      <c r="B37" s="4" t="inlineStr">
-        <is>
-          <t>按功能维度查看：26项功能×（BA/开发A/开发B/测试/文档）五类角色各自的工作内容与人天，另有9类公共支撑行（初始化/架构/集成/专项/上线/管理）；底部与185人天自动对账，可与按开发顺序的「WBS分解」页对照使用</t>
-        </is>
-      </c>
+      <c r="A37" s="38" t="n"/>
+      <c r="B37" s="4" t="n"/>
     </row>
     <row r="38" ht="30" customHeight="1">
-      <c r="A38" s="38" t="inlineStr">
-        <is>
-          <t>功能视角分解</t>
-        </is>
-      </c>
-      <c r="B38" s="4" t="inlineStr">
-        <is>
-          <t>按功能维度查看：26项功能×（BA/开发A/开发B/测试/文档）五类角色各自的工作内容与人天，另有9类公共支撑行（初始化/架构/集成/专项/上线/管理）；底部与185人天自动对账，可与按开发顺序的「WBS分解」页对照使用</t>
-        </is>
-      </c>
+      <c r="A38" s="38" t="n"/>
+      <c r="B38" s="4" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -7257,7 +7256,7 @@
       <c r="O94" s="21" t="n"/>
       <c r="P94" s="21" t="inlineStr">
         <is>
-          <t>Azure Blob原生能力（GRS）：仅配置冗余选项+恢复演练验证，开发量极小；10/27完成</t>
+          <t>Azure Blob原生能力（GRS）：仅配置冗余选项+恢复演练验证，开发量极小；11/9完成</t>
         </is>
       </c>
       <c r="Q94" s="17" t="inlineStr"/>
@@ -15848,7 +15847,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L95"/>
+  <dimension ref="A1:L101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -19353,12 +19352,47 @@
     <row r="95" ht="56" customHeight="1">
       <c r="A95" s="94" t="inlineStr">
         <is>
-          <t>对照说明（三个口径）：① 功能直估 162.25 人天（BA 12.25 / Wade 41.75 / DevB 54.75 / 测试 34.25 / SLC 19.25）——本版已按配置界面/动态表单复杂度上调前端工作量；② 非功能与工程支撑直估 35.25 人天（N1初始化与基座/N2 ESLint·SonarLint·SAST·依赖治理/N3性能·鉴权掩码·可观测·容量/N4部署运维）——此前缺失，现已补齐；③ 已识别原生组件能力（按配置+验证计价，不再计自研开发，子任务标注【原生】/【中间件】）：ADLS SSE/CMK加密、ADLS GRS异地冗余、Key Vault密钥管理、SQL DB PITR备份与Monitor告警、Entra ID+MSAL单点登录、App Insights/Log Analytics可观测性、Unity Catalog授权、Azure DevOps扫描门禁；④ 合计 197.5 人天 vs 排期计划185人天：Wade 58.25；DevB 67.25仍超计划60约 7.25 人天（数据/ETL侧，靠AI生成ETL/SQL提效吸收）；总缺口约 12.5 人天（6%），建议以本表为规模基线纳入风险跟踪，必要时启用备用赶工日（9/20、10/10）。</t>
+          <t>对照说明（四个口径）：① 功能直估 162.25 人天（BA 12.25 / Wade 41.75 / DevB 54.75 / 测试 34.25 / SLC 19.25）——已按配置界面/动态表单复杂度上调前端工作量；② 非功能与工程支撑直估 35.25 人天（N1初始化与基座/N2 ESLint·SonarLint·SAST·依赖治理/N3性能·鉴权掩码·可观测·容量/N4部署运维）；③ 已识别原生组件能力（按配置+验证计价，子任务标注【原生】/【中间件】）：ADLS SSE/CMK加密、ADLS GRS异地冗余、Key Vault密钥管理、SQL DB PITR备份与Monitor告警、Entra ID+MSAL单点登录、App Insights/Log Analytics可观测性、Unity Catalog授权、Azure DevOps扫描门禁；④ 合计 197.5 人天 vs 计划185：Wade 58.25（计划60，有余量）；DevB 67.25（超计划60约7.25）；Mandy三职 72.0（BA 12.5 + 测试 38.75 + SLC 20.75，超计划50约22.0）——角色级差异的吸收路径见下方「AI Native提效折算对照」。</t>
+        </is>
+      </c>
+    </row>
+    <row r="97" ht="16" customHeight="1">
+      <c r="A97" s="114" t="inlineStr">
+        <is>
+          <t>AI Native提效折算对照（直估→计划185的吸收路径）：</t>
+        </is>
+      </c>
+    </row>
+    <row r="98" ht="16" customHeight="1">
+      <c r="A98" s="115" t="inlineStr">
+        <is>
+          <t>· Mandy：直估 72.0（BA 12.5 + 测试 38.75 + SLC 20.75）→ 测试×0.65（AI生成用例+人工审校执行）、SLC×0.6（AI反生成+人工润色）、BA不折减 → ≈50.14 ≈ 计划50 ✓</t>
+        </is>
+      </c>
+    </row>
+    <row r="99" ht="16" customHeight="1">
+      <c r="A99" s="115" t="inlineStr">
+        <is>
+          <t>· Wade：直估 58.25 → 无需折减 → 计划60，余 1.75 缓冲 ✓</t>
+        </is>
+      </c>
+    </row>
+    <row r="100" ht="16" customHeight="1">
+      <c r="A100" s="115" t="inlineStr">
+        <is>
+          <t>· DevB：直估 67.25 → ETL/SQL/作业配置AI生成×0.85 → ≈57.16 ≈ 计划60 ✓（最大风险假设：AI生成ETL需有效落地，纳入风险跟踪）</t>
+        </is>
+      </c>
+    </row>
+    <row r="101" ht="16" customHeight="1">
+      <c r="A101" s="115" t="inlineStr">
+        <is>
+          <t>· 合计：直估 197.5 → 折算 ≈165.55 + PM 15 = 180.55 ≤ 185，余 ≈4.45 人天缓冲；若提效不达标，启用备用赶工日（9/20、10/10）</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="68">
+  <mergeCells count="73">
     <mergeCell ref="C56:C58"/>
     <mergeCell ref="C14:C17"/>
     <mergeCell ref="L35:L37"/>
@@ -19368,6 +19402,7 @@
     <mergeCell ref="C73:C74"/>
     <mergeCell ref="L71:L72"/>
     <mergeCell ref="L47:L48"/>
+    <mergeCell ref="A99:L99"/>
     <mergeCell ref="L56:L58"/>
     <mergeCell ref="L63:L65"/>
     <mergeCell ref="L41:L43"/>
@@ -19380,6 +19415,7 @@
     <mergeCell ref="C59:C60"/>
     <mergeCell ref="B63:B74"/>
     <mergeCell ref="A95:L95"/>
+    <mergeCell ref="A101:L101"/>
     <mergeCell ref="C53:C55"/>
     <mergeCell ref="C71:C72"/>
     <mergeCell ref="C47:C48"/>
@@ -19387,11 +19423,13 @@
     <mergeCell ref="C21:C22"/>
     <mergeCell ref="C68:C70"/>
     <mergeCell ref="L80:L84"/>
+    <mergeCell ref="A97:L97"/>
     <mergeCell ref="L14:L17"/>
     <mergeCell ref="B29:B34"/>
     <mergeCell ref="C18:C20"/>
     <mergeCell ref="B23:B28"/>
     <mergeCell ref="L32:L34"/>
+    <mergeCell ref="A100:L100"/>
     <mergeCell ref="L10:L13"/>
     <mergeCell ref="C61:C62"/>
     <mergeCell ref="C51:C52"/>
@@ -19414,6 +19452,7 @@
     <mergeCell ref="C44:C46"/>
     <mergeCell ref="B35:B43"/>
     <mergeCell ref="L18:L20"/>
+    <mergeCell ref="A98:L98"/>
     <mergeCell ref="L3:L9"/>
     <mergeCell ref="L61:L62"/>
     <mergeCell ref="L68:L70"/>

--- a/RIMS项目WBS工作分解_AI Native版.xlsx
+++ b/RIMS项目WBS工作分解_AI Native版.xlsx
@@ -1313,7 +1313,7 @@
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>子任务级直估：模块→功能→子任务三层结构（模块列与功能列均为纵向合并单元格），26项功能×75子任务 + 非功能与工程支撑×18子任务（N1框架初始化与基座/N2 ESLint·SonarLint·SAST代码质量治理/N3性能·鉴权·可观测·容量/N4部署运维），按BA/开发A/开发B/测试/SLC文档独立估人天；底部附与计划口径对照</t>
+          <t>子任务级直估：模块→功能→子任务三层结构（模块列与功能列均为纵向合并单元格），26项功能×75子任务 + 非功能与工程支撑×21子任务（N1框架初始化与基座/N2 ESLint·SonarLint·SAST代码质量治理/N3性能·鉴权·可观测·容量/N4部署运维），按BA/开发A/开发B/测试/SLC文档独立估人天；底部附与计划口径对照</t>
         </is>
       </c>
     </row>
@@ -15847,7 +15847,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L101"/>
+  <dimension ref="A1:L104"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -15867,7 +15867,7 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>功能拆解估算（子任务级直估）：模块→功能→子任务三层结构，25项功能×72子任务 + 非功能与工程支撑×18子任务（F04-04异地灾备=Azure Blob原生能力，不计开发）— 独立估算，不锚定排期185人天</t>
+          <t>功能拆解估算（子任务级直估）：模块→功能→子任务三层结构，25项功能×72子任务 + 非功能与工程支撑×21子任务（F04-04异地灾备=Azure Blob原生能力，不计开发）— 独立估算，不锚定排期185人天</t>
         </is>
       </c>
     </row>
@@ -15919,7 +15919,7 @@
       </c>
       <c r="J2" s="7" t="inlineStr">
         <is>
-          <t>SLC文档</t>
+          <t>SLC人天（按功能）</t>
         </is>
       </c>
       <c r="K2" s="7" t="inlineStr">
@@ -15971,14 +15971,14 @@
       <c r="I3" s="46" t="n">
         <v>0.5</v>
       </c>
-      <c r="J3" s="46" t="n">
-        <v>0.25</v>
+      <c r="J3" s="74" t="n">
+        <v>1</v>
       </c>
       <c r="K3" s="46" t="n">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="L3" s="74" t="n">
-        <v>22.75</v>
+        <v>21.5</v>
       </c>
     </row>
     <row r="4" ht="26" customHeight="1">
@@ -16011,11 +16011,9 @@
       <c r="I4" s="46" t="n">
         <v>0.5</v>
       </c>
-      <c r="J4" s="46" t="n">
-        <v>0.25</v>
-      </c>
+      <c r="J4" s="17" t="n"/>
       <c r="K4" s="46" t="n">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="L4" s="17" t="n"/>
     </row>
@@ -16049,11 +16047,9 @@
       <c r="I5" s="46" t="n">
         <v>0.5</v>
       </c>
-      <c r="J5" s="46" t="n">
-        <v>0.25</v>
-      </c>
+      <c r="J5" s="17" t="n"/>
       <c r="K5" s="46" t="n">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="L5" s="17" t="n"/>
     </row>
@@ -16087,11 +16083,9 @@
       <c r="I6" s="46" t="n">
         <v>0.25</v>
       </c>
-      <c r="J6" s="46" t="n">
-        <v>0.25</v>
-      </c>
+      <c r="J6" s="17" t="n"/>
       <c r="K6" s="46" t="n">
-        <v>2.5</v>
+        <v>2.25</v>
       </c>
       <c r="L6" s="17" t="n"/>
     </row>
@@ -16123,11 +16117,9 @@
       <c r="I7" s="46" t="n">
         <v>0.5</v>
       </c>
-      <c r="J7" s="46" t="n">
-        <v>0.5</v>
-      </c>
+      <c r="J7" s="17" t="n"/>
       <c r="K7" s="46" t="n">
-        <v>3.25</v>
+        <v>2.75</v>
       </c>
       <c r="L7" s="17" t="n"/>
     </row>
@@ -16159,11 +16151,9 @@
       <c r="I8" s="46" t="n">
         <v>1</v>
       </c>
-      <c r="J8" s="46" t="n">
-        <v>0.5</v>
-      </c>
+      <c r="J8" s="17" t="n"/>
       <c r="K8" s="46" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="L8" s="17" t="n"/>
     </row>
@@ -16195,11 +16185,9 @@
       <c r="I9" s="46" t="n">
         <v>0.5</v>
       </c>
-      <c r="J9" s="46" t="n">
-        <v>0.25</v>
-      </c>
+      <c r="J9" s="17" t="n"/>
       <c r="K9" s="46" t="n">
-        <v>2.75</v>
+        <v>2.5</v>
       </c>
       <c r="L9" s="17" t="n"/>
     </row>
@@ -16237,14 +16225,14 @@
       <c r="I10" s="46" t="n">
         <v>0.5</v>
       </c>
-      <c r="J10" s="46" t="n">
-        <v>0.25</v>
+      <c r="J10" s="74" t="n">
+        <v>0.5</v>
       </c>
       <c r="K10" s="46" t="n">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="L10" s="74" t="n">
-        <v>13.25</v>
+        <v>12.75</v>
       </c>
     </row>
     <row r="11" ht="26" customHeight="1">
@@ -16275,11 +16263,9 @@
       <c r="I11" s="46" t="n">
         <v>1</v>
       </c>
-      <c r="J11" s="46" t="n">
-        <v>0.25</v>
-      </c>
+      <c r="J11" s="17" t="n"/>
       <c r="K11" s="46" t="n">
-        <v>4.25</v>
+        <v>4</v>
       </c>
       <c r="L11" s="17" t="n"/>
     </row>
@@ -16309,11 +16295,9 @@
       <c r="I12" s="46" t="n">
         <v>0.75</v>
       </c>
-      <c r="J12" s="46" t="n">
-        <v>0.25</v>
-      </c>
+      <c r="J12" s="17" t="n"/>
       <c r="K12" s="46" t="n">
-        <v>2.5</v>
+        <v>2.25</v>
       </c>
       <c r="L12" s="17" t="n"/>
     </row>
@@ -16345,11 +16329,9 @@
       <c r="I13" s="46" t="n">
         <v>0.5</v>
       </c>
-      <c r="J13" s="46" t="n">
-        <v>0.25</v>
-      </c>
+      <c r="J13" s="17" t="n"/>
       <c r="K13" s="46" t="n">
-        <v>2.5</v>
+        <v>2.25</v>
       </c>
       <c r="L13" s="17" t="n"/>
     </row>
@@ -16387,14 +16369,14 @@
       <c r="I14" s="46" t="n">
         <v>0.5</v>
       </c>
-      <c r="J14" s="46" t="n">
-        <v>0.25</v>
+      <c r="J14" s="74" t="n">
+        <v>0.5</v>
       </c>
       <c r="K14" s="46" t="n">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="L14" s="74" t="n">
-        <v>11.75</v>
+        <v>11.25</v>
       </c>
     </row>
     <row r="15" ht="26" customHeight="1">
@@ -16425,11 +16407,9 @@
       <c r="I15" s="46" t="n">
         <v>0.75</v>
       </c>
-      <c r="J15" s="46" t="n">
-        <v>0.25</v>
-      </c>
+      <c r="J15" s="17" t="n"/>
       <c r="K15" s="46" t="n">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="L15" s="17" t="n"/>
     </row>
@@ -16461,11 +16441,9 @@
       <c r="I16" s="46" t="n">
         <v>0.5</v>
       </c>
-      <c r="J16" s="46" t="n">
-        <v>0.25</v>
-      </c>
+      <c r="J16" s="17" t="n"/>
       <c r="K16" s="46" t="n">
-        <v>2.75</v>
+        <v>2.5</v>
       </c>
       <c r="L16" s="17" t="n"/>
     </row>
@@ -16497,11 +16475,9 @@
       <c r="I17" s="46" t="n">
         <v>0.5</v>
       </c>
-      <c r="J17" s="46" t="n">
-        <v>0.25</v>
-      </c>
+      <c r="J17" s="17" t="n"/>
       <c r="K17" s="46" t="n">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="L17" s="17" t="n"/>
     </row>
@@ -16537,14 +16513,14 @@
       <c r="I18" s="46" t="n">
         <v>0.25</v>
       </c>
-      <c r="J18" s="46" t="n">
-        <v>0.25</v>
+      <c r="J18" s="74" t="n">
+        <v>0.5</v>
       </c>
       <c r="K18" s="46" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="L18" s="74" t="n">
-        <v>5.5</v>
+        <v>5.25</v>
       </c>
     </row>
     <row r="19" ht="26" customHeight="1">
@@ -16573,11 +16549,9 @@
       <c r="I19" s="46" t="n">
         <v>0.5</v>
       </c>
-      <c r="J19" s="46" t="n">
-        <v>0.25</v>
-      </c>
+      <c r="J19" s="17" t="n"/>
       <c r="K19" s="46" t="n">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="L19" s="17" t="n"/>
     </row>
@@ -16609,11 +16583,9 @@
       <c r="I20" s="46" t="n">
         <v>0.25</v>
       </c>
-      <c r="J20" s="46" t="n">
-        <v>0.25</v>
-      </c>
+      <c r="J20" s="17" t="n"/>
       <c r="K20" s="46" t="n">
-        <v>1.25</v>
+        <v>1</v>
       </c>
       <c r="L20" s="17" t="n"/>
     </row>
@@ -16647,11 +16619,11 @@
       <c r="I21" s="46" t="n">
         <v>0.75</v>
       </c>
-      <c r="J21" s="46" t="n">
-        <v>0.25</v>
+      <c r="J21" s="74" t="n">
+        <v>0.5</v>
       </c>
       <c r="K21" s="46" t="n">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="L21" s="74" t="n">
         <v>5.5</v>
@@ -16687,11 +16659,9 @@
       <c r="I22" s="46" t="n">
         <v>0.5</v>
       </c>
-      <c r="J22" s="46" t="n">
-        <v>0.25</v>
-      </c>
+      <c r="J22" s="17" t="n"/>
       <c r="K22" s="46" t="n">
-        <v>2.5</v>
+        <v>2.25</v>
       </c>
       <c r="L22" s="17" t="n"/>
     </row>
@@ -16731,14 +16701,14 @@
       <c r="I23" s="46" t="n">
         <v>0.25</v>
       </c>
-      <c r="J23" s="46" t="n">
+      <c r="J23" s="77" t="n">
         <v>0.5</v>
       </c>
       <c r="K23" s="46" t="n">
-        <v>2.75</v>
+        <v>2.25</v>
       </c>
       <c r="L23" s="77" t="n">
-        <v>9</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="24" ht="26" customHeight="1">
@@ -16767,11 +16737,9 @@
       <c r="I24" s="46" t="n">
         <v>0.5</v>
       </c>
-      <c r="J24" s="46" t="n">
-        <v>0.25</v>
-      </c>
+      <c r="J24" s="17" t="n"/>
       <c r="K24" s="46" t="n">
-        <v>2.75</v>
+        <v>2.5</v>
       </c>
       <c r="L24" s="17" t="n"/>
     </row>
@@ -16805,11 +16773,9 @@
       <c r="I25" s="46" t="n">
         <v>0.5</v>
       </c>
-      <c r="J25" s="46" t="n">
-        <v>0.25</v>
-      </c>
+      <c r="J25" s="17" t="n"/>
       <c r="K25" s="46" t="n">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="L25" s="17" t="n"/>
     </row>
@@ -16845,14 +16811,14 @@
       <c r="I26" s="46" t="n">
         <v>0.25</v>
       </c>
-      <c r="J26" s="46" t="n">
-        <v>0.25</v>
+      <c r="J26" s="77" t="n">
+        <v>0.5</v>
       </c>
       <c r="K26" s="46" t="n">
-        <v>1.75</v>
+        <v>1.5</v>
       </c>
       <c r="L26" s="77" t="n">
-        <v>5.75</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="27" ht="26" customHeight="1">
@@ -16881,11 +16847,9 @@
       <c r="I27" s="46" t="n">
         <v>0.5</v>
       </c>
-      <c r="J27" s="46" t="n">
-        <v>0.25</v>
-      </c>
+      <c r="J27" s="17" t="n"/>
       <c r="K27" s="46" t="n">
-        <v>1.75</v>
+        <v>1.5</v>
       </c>
       <c r="L27" s="17" t="n"/>
     </row>
@@ -16917,11 +16881,9 @@
       <c r="I28" s="46" t="n">
         <v>0.5</v>
       </c>
-      <c r="J28" s="46" t="n">
-        <v>0.25</v>
-      </c>
+      <c r="J28" s="17" t="n"/>
       <c r="K28" s="46" t="n">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="L28" s="17" t="n"/>
     </row>
@@ -16963,14 +16925,14 @@
       <c r="I29" s="46" t="n">
         <v>0.5</v>
       </c>
-      <c r="J29" s="46" t="n">
-        <v>0.25</v>
+      <c r="J29" s="80" t="n">
+        <v>0.5</v>
       </c>
       <c r="K29" s="46" t="n">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="L29" s="80" t="n">
-        <v>10</v>
+        <v>9.5</v>
       </c>
     </row>
     <row r="30" ht="26" customHeight="1">
@@ -16999,11 +16961,9 @@
       <c r="I30" s="46" t="n">
         <v>1</v>
       </c>
-      <c r="J30" s="46" t="n">
-        <v>0.5</v>
-      </c>
+      <c r="J30" s="17" t="n"/>
       <c r="K30" s="46" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="L30" s="17" t="n"/>
     </row>
@@ -17037,11 +16997,9 @@
       <c r="I31" s="46" t="n">
         <v>0.5</v>
       </c>
-      <c r="J31" s="46" t="n">
-        <v>0.25</v>
-      </c>
+      <c r="J31" s="17" t="n"/>
       <c r="K31" s="46" t="n">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="L31" s="17" t="n"/>
     </row>
@@ -17079,14 +17037,14 @@
       <c r="I32" s="46" t="n">
         <v>0.5</v>
       </c>
-      <c r="J32" s="46" t="n">
-        <v>0.25</v>
+      <c r="J32" s="80" t="n">
+        <v>0.5</v>
       </c>
       <c r="K32" s="46" t="n">
-        <v>2.75</v>
+        <v>2.5</v>
       </c>
       <c r="L32" s="80" t="n">
-        <v>6.5</v>
+        <v>6.25</v>
       </c>
     </row>
     <row r="33" ht="26" customHeight="1">
@@ -17115,11 +17073,9 @@
       <c r="I33" s="46" t="n">
         <v>0.75</v>
       </c>
-      <c r="J33" s="46" t="n">
-        <v>0.25</v>
-      </c>
+      <c r="J33" s="17" t="n"/>
       <c r="K33" s="46" t="n">
-        <v>2.5</v>
+        <v>2.25</v>
       </c>
       <c r="L33" s="17" t="n"/>
     </row>
@@ -17151,11 +17107,9 @@
       <c r="I34" s="46" t="n">
         <v>0.25</v>
       </c>
-      <c r="J34" s="46" t="n">
-        <v>0.25</v>
-      </c>
+      <c r="J34" s="17" t="n"/>
       <c r="K34" s="46" t="n">
-        <v>1.25</v>
+        <v>1</v>
       </c>
       <c r="L34" s="17" t="n"/>
     </row>
@@ -17195,14 +17149,14 @@
       <c r="I35" s="46" t="n">
         <v>0.25</v>
       </c>
-      <c r="J35" s="46" t="n">
-        <v>0.25</v>
+      <c r="J35" s="83" t="n">
+        <v>0.5</v>
       </c>
       <c r="K35" s="46" t="n">
-        <v>1.75</v>
+        <v>1.5</v>
       </c>
       <c r="L35" s="83" t="n">
-        <v>5.5</v>
+        <v>5.25</v>
       </c>
     </row>
     <row r="36" ht="26" customHeight="1">
@@ -17231,11 +17185,9 @@
       <c r="I36" s="46" t="n">
         <v>0.5</v>
       </c>
-      <c r="J36" s="46" t="n">
-        <v>0.25</v>
-      </c>
+      <c r="J36" s="17" t="n"/>
       <c r="K36" s="46" t="n">
-        <v>1.25</v>
+        <v>1</v>
       </c>
       <c r="L36" s="17" t="n"/>
     </row>
@@ -17265,11 +17217,9 @@
       <c r="I37" s="46" t="n">
         <v>0.75</v>
       </c>
-      <c r="J37" s="46" t="n">
-        <v>0.25</v>
-      </c>
+      <c r="J37" s="17" t="n"/>
       <c r="K37" s="46" t="n">
-        <v>2.5</v>
+        <v>2.25</v>
       </c>
       <c r="L37" s="17" t="n"/>
     </row>
@@ -17305,14 +17255,14 @@
       <c r="I38" s="46" t="n">
         <v>0.5</v>
       </c>
-      <c r="J38" s="46" t="n">
-        <v>0.25</v>
+      <c r="J38" s="83" t="n">
+        <v>0.5</v>
       </c>
       <c r="K38" s="46" t="n">
-        <v>1.5</v>
+        <v>1.25</v>
       </c>
       <c r="L38" s="83" t="n">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
     </row>
     <row r="39" ht="26" customHeight="1">
@@ -17343,11 +17293,9 @@
       <c r="I39" s="46" t="n">
         <v>0.5</v>
       </c>
-      <c r="J39" s="46" t="n">
-        <v>0.25</v>
-      </c>
+      <c r="J39" s="17" t="n"/>
       <c r="K39" s="46" t="n">
-        <v>1.25</v>
+        <v>1</v>
       </c>
       <c r="L39" s="17" t="n"/>
     </row>
@@ -17377,11 +17325,9 @@
       <c r="I40" s="46" t="n">
         <v>0.25</v>
       </c>
-      <c r="J40" s="46" t="n">
-        <v>0.25</v>
-      </c>
+      <c r="J40" s="17" t="n"/>
       <c r="K40" s="46" t="n">
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
       <c r="L40" s="17" t="n"/>
     </row>
@@ -17419,14 +17365,14 @@
       <c r="I41" s="46" t="n">
         <v>0.25</v>
       </c>
-      <c r="J41" s="46" t="n">
-        <v>0.25</v>
+      <c r="J41" s="83" t="n">
+        <v>0.5</v>
       </c>
       <c r="K41" s="46" t="n">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="L41" s="83" t="n">
-        <v>4.75</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="42" ht="26" customHeight="1">
@@ -17455,11 +17401,9 @@
       <c r="I42" s="46" t="n">
         <v>0.5</v>
       </c>
-      <c r="J42" s="46" t="n">
-        <v>0.25</v>
-      </c>
+      <c r="J42" s="17" t="n"/>
       <c r="K42" s="46" t="n">
-        <v>1.25</v>
+        <v>1</v>
       </c>
       <c r="L42" s="17" t="n"/>
     </row>
@@ -17491,11 +17435,9 @@
       <c r="I43" s="46" t="n">
         <v>0.5</v>
       </c>
-      <c r="J43" s="46" t="n">
-        <v>0.25</v>
-      </c>
+      <c r="J43" s="17" t="n"/>
       <c r="K43" s="46" t="n">
-        <v>1.25</v>
+        <v>1</v>
       </c>
       <c r="L43" s="17" t="n"/>
     </row>
@@ -17537,14 +17479,14 @@
       <c r="I44" s="46" t="n">
         <v>0.25</v>
       </c>
-      <c r="J44" s="46" t="n">
-        <v>0.25</v>
+      <c r="J44" s="105" t="n">
+        <v>0.5</v>
       </c>
       <c r="K44" s="46" t="n">
-        <v>2.5</v>
+        <v>2.25</v>
       </c>
       <c r="L44" s="105" t="n">
-        <v>7.75</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="45" ht="26" customHeight="1">
@@ -17575,11 +17517,9 @@
       <c r="I45" s="46" t="n">
         <v>0.5</v>
       </c>
-      <c r="J45" s="46" t="n">
-        <v>0.25</v>
-      </c>
+      <c r="J45" s="17" t="n"/>
       <c r="K45" s="46" t="n">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="L45" s="17" t="n"/>
     </row>
@@ -17609,11 +17549,9 @@
       <c r="I46" s="46" t="n">
         <v>0.75</v>
       </c>
-      <c r="J46" s="46" t="n">
-        <v>0.25</v>
-      </c>
+      <c r="J46" s="17" t="n"/>
       <c r="K46" s="46" t="n">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="L46" s="17" t="n"/>
     </row>
@@ -17647,14 +17585,14 @@
       <c r="I47" s="46" t="n">
         <v>0.25</v>
       </c>
-      <c r="J47" s="46" t="n">
+      <c r="J47" s="105" t="n">
         <v>0.25</v>
       </c>
       <c r="K47" s="46" t="n">
-        <v>1.25</v>
+        <v>1</v>
       </c>
       <c r="L47" s="105" t="n">
-        <v>2.25</v>
+        <v>2</v>
       </c>
     </row>
     <row r="48" ht="26" customHeight="1">
@@ -17683,11 +17621,9 @@
       <c r="I48" s="46" t="n">
         <v>0.25</v>
       </c>
-      <c r="J48" s="46" t="n">
-        <v>0.25</v>
-      </c>
+      <c r="J48" s="17" t="n"/>
       <c r="K48" s="46" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="L48" s="17" t="n"/>
     </row>
@@ -17721,14 +17657,14 @@
       <c r="I49" s="46" t="n">
         <v>0.25</v>
       </c>
-      <c r="J49" s="46" t="n">
+      <c r="J49" s="105" t="n">
         <v>0.25</v>
       </c>
       <c r="K49" s="46" t="n">
-        <v>1.25</v>
+        <v>1</v>
       </c>
       <c r="L49" s="105" t="n">
-        <v>2.25</v>
+        <v>2</v>
       </c>
     </row>
     <row r="50" ht="26" customHeight="1">
@@ -17757,11 +17693,9 @@
       <c r="I50" s="46" t="n">
         <v>0.25</v>
       </c>
-      <c r="J50" s="46" t="n">
-        <v>0.25</v>
-      </c>
+      <c r="J50" s="17" t="n"/>
       <c r="K50" s="46" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="L50" s="17" t="n"/>
     </row>
@@ -17795,11 +17729,11 @@
       <c r="I51" s="46" t="n">
         <v>0.5</v>
       </c>
-      <c r="J51" s="46" t="n">
-        <v>0.25</v>
+      <c r="J51" s="105" t="n">
+        <v>0.5</v>
       </c>
       <c r="K51" s="46" t="n">
-        <v>2.75</v>
+        <v>2.5</v>
       </c>
       <c r="L51" s="105" t="n">
         <v>4.5</v>
@@ -17833,11 +17767,9 @@
       <c r="I52" s="46" t="n">
         <v>0.5</v>
       </c>
-      <c r="J52" s="46" t="n">
-        <v>0.25</v>
-      </c>
+      <c r="J52" s="17" t="n"/>
       <c r="K52" s="46" t="n">
-        <v>1.75</v>
+        <v>1.5</v>
       </c>
       <c r="L52" s="17" t="n"/>
     </row>
@@ -17871,14 +17803,14 @@
       <c r="I53" s="46" t="n">
         <v>0.5</v>
       </c>
-      <c r="J53" s="46" t="n">
-        <v>0.25</v>
+      <c r="J53" s="105" t="n">
+        <v>0.5</v>
       </c>
       <c r="K53" s="46" t="n">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="L53" s="105" t="n">
-        <v>6.5</v>
+        <v>6.25</v>
       </c>
     </row>
     <row r="54" ht="26" customHeight="1">
@@ -17909,11 +17841,9 @@
       <c r="I54" s="46" t="n">
         <v>0.5</v>
       </c>
-      <c r="J54" s="46" t="n">
-        <v>0.25</v>
-      </c>
+      <c r="J54" s="17" t="n"/>
       <c r="K54" s="46" t="n">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="L54" s="17" t="n"/>
     </row>
@@ -17943,11 +17873,9 @@
       <c r="I55" s="46" t="n">
         <v>0.25</v>
       </c>
-      <c r="J55" s="46" t="n">
-        <v>0.25</v>
-      </c>
+      <c r="J55" s="17" t="n"/>
       <c r="K55" s="46" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="L55" s="17" t="n"/>
     </row>
@@ -17987,14 +17915,14 @@
       <c r="I56" s="46" t="n">
         <v>0.25</v>
       </c>
-      <c r="J56" s="46" t="n">
-        <v>0.25</v>
+      <c r="J56" s="89" t="n">
+        <v>0.5</v>
       </c>
       <c r="K56" s="46" t="n">
-        <v>1.25</v>
+        <v>1</v>
       </c>
       <c r="L56" s="89" t="n">
-        <v>5.5</v>
+        <v>5.25</v>
       </c>
     </row>
     <row r="57" ht="26" customHeight="1">
@@ -18023,11 +17951,9 @@
       <c r="I57" s="46" t="n">
         <v>0.5</v>
       </c>
-      <c r="J57" s="46" t="n">
-        <v>0.25</v>
-      </c>
+      <c r="J57" s="17" t="n"/>
       <c r="K57" s="46" t="n">
-        <v>1.75</v>
+        <v>1.5</v>
       </c>
       <c r="L57" s="17" t="n"/>
     </row>
@@ -18059,11 +17985,9 @@
       <c r="I58" s="46" t="n">
         <v>0.5</v>
       </c>
-      <c r="J58" s="46" t="n">
-        <v>0.25</v>
-      </c>
+      <c r="J58" s="17" t="n"/>
       <c r="K58" s="46" t="n">
-        <v>2.5</v>
+        <v>2.25</v>
       </c>
       <c r="L58" s="17" t="n"/>
     </row>
@@ -18097,14 +18021,14 @@
       <c r="I59" s="46" t="n">
         <v>0.5</v>
       </c>
-      <c r="J59" s="46" t="n">
+      <c r="J59" s="89" t="n">
         <v>0.25</v>
       </c>
       <c r="K59" s="46" t="n">
-        <v>1.5</v>
+        <v>1.25</v>
       </c>
       <c r="L59" s="89" t="n">
-        <v>2.5</v>
+        <v>2.25</v>
       </c>
     </row>
     <row r="60" ht="26" customHeight="1">
@@ -18133,11 +18057,9 @@
       <c r="I60" s="46" t="n">
         <v>0.25</v>
       </c>
-      <c r="J60" s="46" t="n">
-        <v>0.25</v>
-      </c>
+      <c r="J60" s="17" t="n"/>
       <c r="K60" s="46" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="L60" s="17" t="n"/>
     </row>
@@ -18171,14 +18093,14 @@
       <c r="I61" s="46" t="n">
         <v>0.5</v>
       </c>
-      <c r="J61" s="46" t="n">
+      <c r="J61" s="89" t="n">
         <v>0.25</v>
       </c>
       <c r="K61" s="46" t="n">
-        <v>1.5</v>
+        <v>1.25</v>
       </c>
       <c r="L61" s="89" t="n">
-        <v>2.75</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="62" ht="26" customHeight="1">
@@ -18209,11 +18131,9 @@
       <c r="I62" s="46" t="n">
         <v>0.25</v>
       </c>
-      <c r="J62" s="46" t="n">
-        <v>0.25</v>
-      </c>
+      <c r="J62" s="17" t="n"/>
       <c r="K62" s="46" t="n">
-        <v>1.25</v>
+        <v>1</v>
       </c>
       <c r="L62" s="17" t="n"/>
     </row>
@@ -18253,11 +18173,11 @@
       <c r="I63" s="46" t="n">
         <v>0.25</v>
       </c>
-      <c r="J63" s="46" t="n">
-        <v>0.5</v>
+      <c r="J63" s="92" t="n">
+        <v>1</v>
       </c>
       <c r="K63" s="46" t="n">
-        <v>2.25</v>
+        <v>1.75</v>
       </c>
       <c r="L63" s="92" t="n">
         <v>7.5</v>
@@ -18291,11 +18211,9 @@
       <c r="I64" s="46" t="n">
         <v>0.5</v>
       </c>
-      <c r="J64" s="46" t="n">
-        <v>0.25</v>
-      </c>
+      <c r="J64" s="17" t="n"/>
       <c r="K64" s="46" t="n">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="L64" s="17" t="n"/>
     </row>
@@ -18325,11 +18243,9 @@
       <c r="I65" s="46" t="n">
         <v>0.75</v>
       </c>
-      <c r="J65" s="46" t="n">
-        <v>0.25</v>
-      </c>
+      <c r="J65" s="17" t="n"/>
       <c r="K65" s="46" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="L65" s="17" t="n"/>
     </row>
@@ -18367,11 +18283,11 @@
       <c r="I66" s="46" t="n">
         <v>0.5</v>
       </c>
-      <c r="J66" s="46" t="n">
-        <v>0.25</v>
+      <c r="J66" s="92" t="n">
+        <v>0.5</v>
       </c>
       <c r="K66" s="46" t="n">
-        <v>2.75</v>
+        <v>2.5</v>
       </c>
       <c r="L66" s="92" t="n">
         <v>4</v>
@@ -18405,11 +18321,9 @@
       <c r="I67" s="46" t="n">
         <v>0.25</v>
       </c>
-      <c r="J67" s="46" t="n">
-        <v>0.25</v>
-      </c>
+      <c r="J67" s="17" t="n"/>
       <c r="K67" s="46" t="n">
-        <v>1.25</v>
+        <v>1</v>
       </c>
       <c r="L67" s="17" t="n"/>
     </row>
@@ -18447,14 +18361,14 @@
       <c r="I68" s="46" t="n">
         <v>0.5</v>
       </c>
-      <c r="J68" s="46" t="n">
-        <v>0.25</v>
+      <c r="J68" s="92" t="n">
+        <v>0.5</v>
       </c>
       <c r="K68" s="46" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="L68" s="92" t="n">
-        <v>6</v>
+        <v>5.75</v>
       </c>
     </row>
     <row r="69" ht="26" customHeight="1">
@@ -18485,11 +18399,9 @@
       <c r="I69" s="46" t="n">
         <v>0.75</v>
       </c>
-      <c r="J69" s="46" t="n">
-        <v>0.25</v>
-      </c>
+      <c r="J69" s="17" t="n"/>
       <c r="K69" s="46" t="n">
-        <v>2.75</v>
+        <v>2.5</v>
       </c>
       <c r="L69" s="17" t="n"/>
     </row>
@@ -18519,11 +18431,9 @@
       <c r="I70" s="46" t="n">
         <v>0.5</v>
       </c>
-      <c r="J70" s="46" t="n">
-        <v>0.25</v>
-      </c>
+      <c r="J70" s="17" t="n"/>
       <c r="K70" s="46" t="n">
-        <v>1.25</v>
+        <v>1</v>
       </c>
       <c r="L70" s="17" t="n"/>
     </row>
@@ -18559,14 +18469,14 @@
       <c r="I71" s="46" t="n">
         <v>0.25</v>
       </c>
-      <c r="J71" s="46" t="n">
+      <c r="J71" s="92" t="n">
         <v>0.25</v>
       </c>
       <c r="K71" s="46" t="n">
-        <v>1.5</v>
+        <v>1.25</v>
       </c>
       <c r="L71" s="92" t="n">
-        <v>3.25</v>
+        <v>3</v>
       </c>
     </row>
     <row r="72" ht="26" customHeight="1">
@@ -18597,11 +18507,9 @@
       <c r="I72" s="46" t="n">
         <v>0.5</v>
       </c>
-      <c r="J72" s="46" t="n">
-        <v>0.25</v>
-      </c>
+      <c r="J72" s="17" t="n"/>
       <c r="K72" s="46" t="n">
-        <v>1.75</v>
+        <v>1.5</v>
       </c>
       <c r="L72" s="17" t="n"/>
     </row>
@@ -18639,14 +18547,14 @@
       <c r="I73" s="46" t="n">
         <v>0.5</v>
       </c>
-      <c r="J73" s="46" t="n">
+      <c r="J73" s="92" t="n">
         <v>0.25</v>
       </c>
       <c r="K73" s="46" t="n">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="L73" s="92" t="n">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="74" ht="26" customHeight="1">
@@ -18675,11 +18583,9 @@
       <c r="I74" s="46" t="n">
         <v>0.5</v>
       </c>
-      <c r="J74" s="46" t="n">
-        <v>0.25</v>
-      </c>
+      <c r="J74" s="17" t="n"/>
       <c r="K74" s="46" t="n">
-        <v>1.5</v>
+        <v>1.25</v>
       </c>
       <c r="L74" s="17" t="n"/>
     </row>
@@ -18719,7 +18625,9 @@
       <c r="I75" s="46" t="n">
         <v>0.25</v>
       </c>
-      <c r="J75" s="46" t="n"/>
+      <c r="J75" s="86" t="n">
+        <v>0.5</v>
+      </c>
       <c r="K75" s="46" t="n">
         <v>1.5</v>
       </c>
@@ -18753,7 +18661,7 @@
       <c r="I76" s="46" t="n">
         <v>0.25</v>
       </c>
-      <c r="J76" s="46" t="n"/>
+      <c r="J76" s="17" t="n"/>
       <c r="K76" s="46" t="n">
         <v>1.75</v>
       </c>
@@ -18785,7 +18693,7 @@
       <c r="I77" s="46" t="n">
         <v>0.25</v>
       </c>
-      <c r="J77" s="46" t="n"/>
+      <c r="J77" s="17" t="n"/>
       <c r="K77" s="46" t="n">
         <v>1.75</v>
       </c>
@@ -18817,11 +18725,9 @@
         <v>0.25</v>
       </c>
       <c r="I78" s="46" t="n"/>
-      <c r="J78" s="46" t="n">
-        <v>0.25</v>
-      </c>
+      <c r="J78" s="17" t="n"/>
       <c r="K78" s="46" t="n">
-        <v>1.5</v>
+        <v>1.25</v>
       </c>
       <c r="L78" s="17" t="n"/>
     </row>
@@ -18853,11 +18759,9 @@
       <c r="I79" s="46" t="n">
         <v>0.5</v>
       </c>
-      <c r="J79" s="46" t="n">
-        <v>0.25</v>
-      </c>
+      <c r="J79" s="17" t="n"/>
       <c r="K79" s="46" t="n">
-        <v>4.25</v>
+        <v>4</v>
       </c>
       <c r="L79" s="17" t="n"/>
     </row>
@@ -18889,7 +18793,9 @@
       </c>
       <c r="H80" s="46" t="n"/>
       <c r="I80" s="46" t="n"/>
-      <c r="J80" s="46" t="n"/>
+      <c r="J80" s="86" t="n">
+        <v>0.25</v>
+      </c>
       <c r="K80" s="46" t="n">
         <v>1.5</v>
       </c>
@@ -18921,7 +18827,7 @@
         <v>1.5</v>
       </c>
       <c r="I81" s="46" t="n"/>
-      <c r="J81" s="46" t="n"/>
+      <c r="J81" s="17" t="n"/>
       <c r="K81" s="46" t="n">
         <v>1.5</v>
       </c>
@@ -18955,7 +18861,7 @@
       <c r="I82" s="46" t="n">
         <v>0.25</v>
       </c>
-      <c r="J82" s="46" t="n"/>
+      <c r="J82" s="17" t="n"/>
       <c r="K82" s="46" t="n">
         <v>2.25</v>
       </c>
@@ -18987,11 +18893,9 @@
         <v>0.5</v>
       </c>
       <c r="I83" s="46" t="n"/>
-      <c r="J83" s="46" t="n">
-        <v>0.25</v>
-      </c>
+      <c r="J83" s="17" t="n"/>
       <c r="K83" s="46" t="n">
-        <v>1.25</v>
+        <v>1</v>
       </c>
       <c r="L83" s="17" t="n"/>
     </row>
@@ -19023,7 +18927,7 @@
       <c r="I84" s="46" t="n">
         <v>0.25</v>
       </c>
-      <c r="J84" s="46" t="n"/>
+      <c r="J84" s="17" t="n"/>
       <c r="K84" s="46" t="n">
         <v>2.25</v>
       </c>
@@ -19059,12 +18963,12 @@
       <c r="I85" s="46" t="n">
         <v>0.5</v>
       </c>
-      <c r="J85" s="46" t="n"/>
+      <c r="J85" s="86" t="n"/>
       <c r="K85" s="46" t="n">
         <v>2</v>
       </c>
       <c r="L85" s="86" t="n">
-        <v>10.25</v>
+        <v>10</v>
       </c>
     </row>
     <row r="86" ht="26" customHeight="1">
@@ -19093,7 +18997,7 @@
       <c r="I86" s="46" t="n">
         <v>0.5</v>
       </c>
-      <c r="J86" s="46" t="n"/>
+      <c r="J86" s="17" t="n"/>
       <c r="K86" s="46" t="n">
         <v>2</v>
       </c>
@@ -19129,7 +19033,7 @@
       <c r="I87" s="46" t="n">
         <v>0.75</v>
       </c>
-      <c r="J87" s="46" t="n"/>
+      <c r="J87" s="17" t="n"/>
       <c r="K87" s="46" t="n">
         <v>3</v>
       </c>
@@ -19163,7 +19067,7 @@
       <c r="I88" s="46" t="n">
         <v>0.25</v>
       </c>
-      <c r="J88" s="46" t="n"/>
+      <c r="J88" s="17" t="n"/>
       <c r="K88" s="46" t="n">
         <v>1.5</v>
       </c>
@@ -19195,11 +19099,9 @@
       <c r="I89" s="46" t="n">
         <v>0.5</v>
       </c>
-      <c r="J89" s="46" t="n">
-        <v>0.25</v>
-      </c>
+      <c r="J89" s="17" t="n"/>
       <c r="K89" s="46" t="n">
-        <v>1.75</v>
+        <v>1.5</v>
       </c>
       <c r="L89" s="17" t="n"/>
     </row>
@@ -19233,11 +19135,11 @@
         <v>0.25</v>
       </c>
       <c r="I90" s="46" t="n"/>
-      <c r="J90" s="46" t="n">
-        <v>0.25</v>
+      <c r="J90" s="86" t="n">
+        <v>0.5</v>
       </c>
       <c r="K90" s="46" t="n">
-        <v>1.5</v>
+        <v>1.25</v>
       </c>
       <c r="L90" s="86" t="n">
         <v>5.5</v>
@@ -19271,7 +19173,7 @@
       <c r="I91" s="46" t="n">
         <v>0.25</v>
       </c>
-      <c r="J91" s="46" t="n"/>
+      <c r="J91" s="17" t="n"/>
       <c r="K91" s="46" t="n">
         <v>1.75</v>
       </c>
@@ -19283,7 +19185,7 @@
           <t>N4-3</t>
         </is>
       </c>
-      <c r="B92" s="103" t="n"/>
+      <c r="B92" s="102" t="n"/>
       <c r="C92" s="17" t="n"/>
       <c r="D92" s="32" t="inlineStr">
         <is>
@@ -19303,168 +19205,296 @@
         <v>1</v>
       </c>
       <c r="I92" s="46" t="n"/>
-      <c r="J92" s="46" t="n">
-        <v>0.25</v>
-      </c>
+      <c r="J92" s="17" t="n"/>
       <c r="K92" s="46" t="n">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="L92" s="17" t="n"/>
     </row>
-    <row r="93">
-      <c r="A93" s="8" t="inlineStr"/>
-      <c r="B93" s="8" t="inlineStr">
+    <row r="93" ht="26" customHeight="1">
+      <c r="A93" s="15" t="inlineStr">
+        <is>
+          <t>N5-1</t>
+        </is>
+      </c>
+      <c r="B93" s="102" t="n"/>
+      <c r="C93" s="99" t="inlineStr">
+        <is>
+          <t>开发侧文档（架构/设计/接口）</t>
+        </is>
+      </c>
+      <c r="D93" s="32" t="inlineStr">
+        <is>
+          <t>架构与总体设计文档</t>
+        </is>
+      </c>
+      <c r="E93" s="32" t="inlineStr">
+        <is>
+          <t>架构图/部署视图/ADR汇编成文（Wade提供）</t>
+        </is>
+      </c>
+      <c r="F93" s="46" t="n"/>
+      <c r="G93" s="46" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H93" s="46" t="n"/>
+      <c r="I93" s="46" t="n"/>
+      <c r="J93" s="86" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K93" s="46" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="L93" s="86" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="94" ht="26" customHeight="1">
+      <c r="A94" s="15" t="inlineStr">
+        <is>
+          <t>N5-2</t>
+        </is>
+      </c>
+      <c r="B94" s="102" t="n"/>
+      <c r="C94" s="17" t="n"/>
+      <c r="D94" s="32" t="inlineStr">
+        <is>
+          <t>应用接口与模块设计文档</t>
+        </is>
+      </c>
+      <c r="E94" s="32" t="inlineStr">
+        <is>
+          <t>OpenAPI导出+模块设计说明（Wade提供）</t>
+        </is>
+      </c>
+      <c r="F94" s="46" t="n"/>
+      <c r="G94" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="H94" s="46" t="n"/>
+      <c r="I94" s="46" t="n"/>
+      <c r="J94" s="17" t="n"/>
+      <c r="K94" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="L94" s="17" t="n"/>
+    </row>
+    <row r="95" ht="26" customHeight="1">
+      <c r="A95" s="15" t="inlineStr">
+        <is>
+          <t>N5-3</t>
+        </is>
+      </c>
+      <c r="B95" s="103" t="n"/>
+      <c r="C95" s="17" t="n"/>
+      <c r="D95" s="32" t="inlineStr">
+        <is>
+          <t>数据设计与ETL/作业文档</t>
+        </is>
+      </c>
+      <c r="E95" s="32" t="inlineStr">
+        <is>
+          <t>分层设计/数据字典/ETL与作业说明（DevB提供）</t>
+        </is>
+      </c>
+      <c r="F95" s="46" t="n"/>
+      <c r="G95" s="46" t="n"/>
+      <c r="H95" s="46" t="n">
+        <v>2</v>
+      </c>
+      <c r="I95" s="46" t="n"/>
+      <c r="J95" s="17" t="n"/>
+      <c r="K95" s="46" t="n">
+        <v>2</v>
+      </c>
+      <c r="L95" s="17" t="n"/>
+    </row>
+    <row r="96">
+      <c r="A96" s="8" t="inlineStr"/>
+      <c r="B96" s="8" t="inlineStr">
         <is>
           <t>总计</t>
         </is>
       </c>
-      <c r="C93" s="8" t="inlineStr"/>
-      <c r="D93" s="93" t="inlineStr">
-        <is>
-          <t>25项功能×72子任务 + 非功能工程×18子任务（F04-04=Azure原生能力，不计开发）</t>
-        </is>
-      </c>
-      <c r="E93" s="93" t="inlineStr">
+      <c r="C96" s="8" t="inlineStr"/>
+      <c r="D96" s="93" t="inlineStr">
+        <is>
+          <t>25项功能×72子任务 + 非功能工程×21子任务（F04-04=Azure原生能力，不计开发）</t>
+        </is>
+      </c>
+      <c r="E96" s="93" t="inlineStr">
         <is>
           <t>独立直估（另含少量需求/PM等工作未列入本表）</t>
         </is>
       </c>
-      <c r="F93" s="44" t="n">
+      <c r="F96" s="44" t="n">
         <v>12.5</v>
       </c>
-      <c r="G93" s="44" t="n">
-        <v>58.25</v>
-      </c>
-      <c r="H93" s="44" t="n">
-        <v>67.25</v>
-      </c>
-      <c r="I93" s="44" t="n">
+      <c r="G96" s="44" t="n">
+        <v>60.75</v>
+      </c>
+      <c r="H96" s="44" t="n">
+        <v>69.25</v>
+      </c>
+      <c r="I96" s="44" t="n">
         <v>38.75</v>
       </c>
-      <c r="J93" s="44" t="n">
-        <v>20.75</v>
-      </c>
-      <c r="K93" s="44" t="n">
-        <v>197.5</v>
-      </c>
-      <c r="L93" s="8" t="inlineStr"/>
-    </row>
-    <row r="95" ht="56" customHeight="1">
-      <c r="A95" s="94" t="inlineStr">
-        <is>
-          <t>对照说明（四个口径）：① 功能直估 162.25 人天（BA 12.25 / Wade 41.75 / DevB 54.75 / 测试 34.25 / SLC 19.25）——已按配置界面/动态表单复杂度上调前端工作量；② 非功能与工程支撑直估 35.25 人天（N1初始化与基座/N2 ESLint·SonarLint·SAST·依赖治理/N3性能·鉴权掩码·可观测·容量/N4部署运维）；③ 已识别原生组件能力（按配置+验证计价，子任务标注【原生】/【中间件】）：ADLS SSE/CMK加密、ADLS GRS异地冗余、Key Vault密钥管理、SQL DB PITR备份与Monitor告警、Entra ID+MSAL单点登录、App Insights/Log Analytics可观测性、Unity Catalog授权、Azure DevOps扫描门禁；④ 合计 197.5 人天 vs 计划185：Wade 58.25（计划60，有余量）；DevB 67.25（超计划60约7.25）；Mandy三职 72.0（BA 12.5 + 测试 38.75 + SLC 20.75，超计划50约22.0）——角色级差异的吸收路径见下方「AI Native提效折算对照」。</t>
-        </is>
-      </c>
-    </row>
-    <row r="97" ht="16" customHeight="1">
-      <c r="A97" s="114" t="inlineStr">
+      <c r="J96" s="44" t="n">
+        <v>13.75</v>
+      </c>
+      <c r="K96" s="44" t="n">
+        <v>195</v>
+      </c>
+      <c r="L96" s="8" t="inlineStr"/>
+    </row>
+    <row r="98" ht="56" customHeight="1">
+      <c r="A98" s="94" t="inlineStr">
+        <is>
+          <t>对照说明（四个口径）：① 功能直估 155.0 人天（BA 12.25 / Wade 41.75 / DevB 54.75 / 测试 34.25 / SLC 12.0）——已按配置界面/动态表单复杂度上调前端工作量；② 非功能与工程支撑直估 40.0 人天（N1初始化与基座/N2 ESLint·SonarLint·SAST·依赖治理/N3性能·鉴权掩码·可观测·容量/N4部署运维）；③ 已识别原生组件能力（按配置+验证计价，子任务标注【原生】/【中间件】）：ADLS SSE/CMK加密、ADLS GRS异地冗余、Key Vault密钥管理、SQL DB PITR备份与Monitor告警、Entra ID+MSAL单点登录、App Insights/Log Analytics可观测性、Unity Catalog授权、Azure DevOps扫描门禁；④ 合计 195.0 人天 vs 计划185：Wade 60.75（计划60，有余量）；DevB 69.25（超计划60约9.25）；Mandy三职 65.0（BA 12.5 + 测试 38.75 + SLC 13.75，超计划50约15.0）——角色级差异的吸收路径见下方「AI Native提效折算对照」。</t>
+        </is>
+      </c>
+    </row>
+    <row r="100" ht="16" customHeight="1">
+      <c r="A100" s="114" t="inlineStr">
         <is>
           <t>AI Native提效折算对照（直估→计划185的吸收路径）：</t>
-        </is>
-      </c>
-    </row>
-    <row r="98" ht="16" customHeight="1">
-      <c r="A98" s="115" t="inlineStr">
-        <is>
-          <t>· Mandy：直估 72.0（BA 12.5 + 测试 38.75 + SLC 20.75）→ 测试×0.65（AI生成用例+人工审校执行）、SLC×0.6（AI反生成+人工润色）、BA不折减 → ≈50.14 ≈ 计划50 ✓</t>
-        </is>
-      </c>
-    </row>
-    <row r="99" ht="16" customHeight="1">
-      <c r="A99" s="115" t="inlineStr">
-        <is>
-          <t>· Wade：直估 58.25 → 无需折减 → 计划60，余 1.75 缓冲 ✓</t>
-        </is>
-      </c>
-    </row>
-    <row r="100" ht="16" customHeight="1">
-      <c r="A100" s="115" t="inlineStr">
-        <is>
-          <t>· DevB：直估 67.25 → ETL/SQL/作业配置AI生成×0.85 → ≈57.16 ≈ 计划60 ✓（最大风险假设：AI生成ETL需有效落地，纳入风险跟踪）</t>
         </is>
       </c>
     </row>
     <row r="101" ht="16" customHeight="1">
       <c r="A101" s="115" t="inlineStr">
         <is>
-          <t>· 合计：直估 197.5 → 折算 ≈165.55 + PM 15 = 180.55 ≤ 185，余 ≈4.45 人天缓冲；若提效不达标，启用备用赶工日（9/20、10/10）</t>
+          <t>· Mandy：直估 65.0（BA 12.5 + 测试 38.75 + SLC 13.75，SLC已按功能级预估且开发侧文档移至N5）→ 测试×0.65（AI生成用例+人工审校执行）、SLC×0.8（合稿评审）、BA不折减 → ≈48.69 ≈ 计划50 ✓</t>
+        </is>
+      </c>
+    </row>
+    <row r="102" ht="16" customHeight="1">
+      <c r="A102" s="115" t="inlineStr">
+        <is>
+          <t>· Wade：直估 60.75（含N5开发侧文档2.5）≈ 计划60，基本持平 ✓</t>
+        </is>
+      </c>
+    </row>
+    <row r="103" ht="16" customHeight="1">
+      <c r="A103" s="115" t="inlineStr">
+        <is>
+          <t>· DevB：直估 69.25 → ETL/SQL/作业配置AI生成×0.85 → ≈58.86 ≈ 计划60 ✓（最大风险假设：AI生成ETL需有效落地，纳入风险跟踪）</t>
+        </is>
+      </c>
+    </row>
+    <row r="104" ht="16" customHeight="1">
+      <c r="A104" s="115" t="inlineStr">
+        <is>
+          <t>· 合计：直估 195.0 → 折算 ≈168.3 + PM 15 = 183.3 ≤ 185，余 ≈1.7 人天缓冲；若提效不达标，启用备用赶工日（9/20、10/10）</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="73">
-    <mergeCell ref="C56:C58"/>
+  <mergeCells count="105">
+    <mergeCell ref="J35:J37"/>
     <mergeCell ref="C14:C17"/>
     <mergeCell ref="L35:L37"/>
-    <mergeCell ref="L66:L67"/>
-    <mergeCell ref="L26:L28"/>
     <mergeCell ref="L44:L46"/>
-    <mergeCell ref="C73:C74"/>
-    <mergeCell ref="L71:L72"/>
-    <mergeCell ref="L47:L48"/>
-    <mergeCell ref="A99:L99"/>
-    <mergeCell ref="L56:L58"/>
-    <mergeCell ref="L63:L65"/>
-    <mergeCell ref="L41:L43"/>
-    <mergeCell ref="L85:L89"/>
     <mergeCell ref="C23:C25"/>
     <mergeCell ref="C32:C34"/>
     <mergeCell ref="C38:C40"/>
+    <mergeCell ref="J59:J60"/>
+    <mergeCell ref="B63:B74"/>
+    <mergeCell ref="C71:C72"/>
+    <mergeCell ref="B75:B95"/>
+    <mergeCell ref="J3:J9"/>
+    <mergeCell ref="L14:L17"/>
+    <mergeCell ref="C18:C20"/>
+    <mergeCell ref="A100:L100"/>
+    <mergeCell ref="C66:C67"/>
+    <mergeCell ref="J29:J31"/>
+    <mergeCell ref="J47:J48"/>
+    <mergeCell ref="J38:J40"/>
+    <mergeCell ref="A102:L102"/>
+    <mergeCell ref="C63:C65"/>
+    <mergeCell ref="C41:C43"/>
+    <mergeCell ref="L75:L79"/>
+    <mergeCell ref="B35:B43"/>
+    <mergeCell ref="C35:C37"/>
+    <mergeCell ref="J71:J72"/>
+    <mergeCell ref="C93:C95"/>
+    <mergeCell ref="C44:C46"/>
+    <mergeCell ref="J51:J52"/>
+    <mergeCell ref="J73:J74"/>
+    <mergeCell ref="L38:L40"/>
+    <mergeCell ref="J32:J34"/>
+    <mergeCell ref="J26:J28"/>
+    <mergeCell ref="L66:L67"/>
+    <mergeCell ref="L26:L28"/>
+    <mergeCell ref="L63:L65"/>
+    <mergeCell ref="L41:L43"/>
+    <mergeCell ref="J90:J92"/>
+    <mergeCell ref="J10:J13"/>
     <mergeCell ref="L90:L92"/>
-    <mergeCell ref="C10:C13"/>
+    <mergeCell ref="J49:J50"/>
+    <mergeCell ref="J18:J20"/>
+    <mergeCell ref="A104:L104"/>
+    <mergeCell ref="C47:C48"/>
+    <mergeCell ref="C51:C52"/>
+    <mergeCell ref="J44:J46"/>
+    <mergeCell ref="J53:J55"/>
+    <mergeCell ref="L53:L55"/>
+    <mergeCell ref="J21:J22"/>
+    <mergeCell ref="L21:L22"/>
+    <mergeCell ref="L93:L95"/>
+    <mergeCell ref="B3:B22"/>
+    <mergeCell ref="C26:C28"/>
+    <mergeCell ref="L3:L9"/>
+    <mergeCell ref="C90:C92"/>
+    <mergeCell ref="L29:L31"/>
+    <mergeCell ref="C49:C50"/>
+    <mergeCell ref="J14:J17"/>
+    <mergeCell ref="L23:L25"/>
+    <mergeCell ref="C73:C74"/>
+    <mergeCell ref="L71:L72"/>
+    <mergeCell ref="L56:L58"/>
     <mergeCell ref="C59:C60"/>
-    <mergeCell ref="B63:B74"/>
-    <mergeCell ref="A95:L95"/>
-    <mergeCell ref="A101:L101"/>
     <mergeCell ref="C53:C55"/>
-    <mergeCell ref="C71:C72"/>
-    <mergeCell ref="C47:C48"/>
-    <mergeCell ref="L73:L74"/>
+    <mergeCell ref="J56:J58"/>
     <mergeCell ref="C21:C22"/>
     <mergeCell ref="C68:C70"/>
     <mergeCell ref="L80:L84"/>
-    <mergeCell ref="A97:L97"/>
-    <mergeCell ref="L14:L17"/>
+    <mergeCell ref="L10:L13"/>
+    <mergeCell ref="J66:J67"/>
+    <mergeCell ref="B56:B62"/>
+    <mergeCell ref="C29:C31"/>
+    <mergeCell ref="L59:L60"/>
+    <mergeCell ref="A98:L98"/>
+    <mergeCell ref="J61:J62"/>
+    <mergeCell ref="J68:J70"/>
+    <mergeCell ref="L61:L62"/>
+    <mergeCell ref="L68:L70"/>
+    <mergeCell ref="C56:C58"/>
+    <mergeCell ref="L47:L48"/>
+    <mergeCell ref="J85:J89"/>
+    <mergeCell ref="L85:L89"/>
+    <mergeCell ref="C10:C13"/>
+    <mergeCell ref="A101:L101"/>
+    <mergeCell ref="J75:J79"/>
+    <mergeCell ref="L73:L74"/>
     <mergeCell ref="B29:B34"/>
-    <mergeCell ref="C18:C20"/>
+    <mergeCell ref="J23:J25"/>
     <mergeCell ref="B23:B28"/>
     <mergeCell ref="L32:L34"/>
-    <mergeCell ref="A100:L100"/>
-    <mergeCell ref="L10:L13"/>
     <mergeCell ref="C61:C62"/>
-    <mergeCell ref="C51:C52"/>
-    <mergeCell ref="B75:B92"/>
     <mergeCell ref="L51:L52"/>
     <mergeCell ref="C3:C9"/>
-    <mergeCell ref="L53:L55"/>
-    <mergeCell ref="C66:C67"/>
-    <mergeCell ref="B56:B62"/>
-    <mergeCell ref="C29:C31"/>
-    <mergeCell ref="L21:L22"/>
-    <mergeCell ref="L59:L60"/>
-    <mergeCell ref="C41:C43"/>
-    <mergeCell ref="C63:C65"/>
-    <mergeCell ref="L75:L79"/>
-    <mergeCell ref="C35:C37"/>
     <mergeCell ref="L49:L50"/>
-    <mergeCell ref="B3:B22"/>
-    <mergeCell ref="C26:C28"/>
-    <mergeCell ref="C44:C46"/>
-    <mergeCell ref="B35:B43"/>
+    <mergeCell ref="J93:J95"/>
+    <mergeCell ref="J41:J43"/>
     <mergeCell ref="L18:L20"/>
-    <mergeCell ref="A98:L98"/>
-    <mergeCell ref="L3:L9"/>
-    <mergeCell ref="L61:L62"/>
-    <mergeCell ref="L68:L70"/>
+    <mergeCell ref="B44:B55"/>
+    <mergeCell ref="C80:C84"/>
     <mergeCell ref="A1:L1"/>
-    <mergeCell ref="C80:C84"/>
-    <mergeCell ref="B44:B55"/>
+    <mergeCell ref="A103:L103"/>
     <mergeCell ref="C85:C89"/>
-    <mergeCell ref="C90:C92"/>
-    <mergeCell ref="L38:L40"/>
-    <mergeCell ref="L29:L31"/>
-    <mergeCell ref="C49:C50"/>
-    <mergeCell ref="L23:L25"/>
+    <mergeCell ref="J80:J84"/>
+    <mergeCell ref="J63:J65"/>
     <mergeCell ref="C75:C79"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/RIMS项目WBS工作分解_AI Native版.xlsx
+++ b/RIMS项目WBS工作分解_AI Native版.xlsx
@@ -972,7 +972,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="20" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -13536,8 +13535,9 @@
       <c r="M3" s="49" t="n">
         <v>0.5</v>
       </c>
-      <c r="N3" s="49" t="n">
-        <v>3.65</v>
+      <c r="N3" s="49">
+        <f>ROUND(E3+G3+I3+K3+M3,2)</f>
+        <v/>
       </c>
       <c r="O3" s="31" t="inlineStr">
         <is>
@@ -13606,8 +13606,9 @@
       <c r="M4" s="49" t="n">
         <v>0.5</v>
       </c>
-      <c r="N4" s="49" t="n">
-        <v>2.65</v>
+      <c r="N4" s="49">
+        <f>ROUND(E4+G4+I4+K4+M4,2)</f>
+        <v/>
       </c>
       <c r="O4" s="31" t="inlineStr">
         <is>
@@ -13674,8 +13675,9 @@
       <c r="M5" s="49" t="n">
         <v>0.5</v>
       </c>
-      <c r="N5" s="49" t="n">
-        <v>2.15</v>
+      <c r="N5" s="49">
+        <f>ROUND(E5+G5+I5+K5+M5,2)</f>
+        <v/>
       </c>
       <c r="O5" s="31" t="inlineStr">
         <is>
@@ -13738,8 +13740,9 @@
         </is>
       </c>
       <c r="M6" s="49" t="n"/>
-      <c r="N6" s="49" t="n">
-        <v>1.4</v>
+      <c r="N6" s="49">
+        <f>ROUND(E6+G6+I6+K6+M6,2)</f>
+        <v/>
       </c>
       <c r="O6" s="31" t="inlineStr">
         <is>
@@ -13802,8 +13805,9 @@
         </is>
       </c>
       <c r="M7" s="49" t="n"/>
-      <c r="N7" s="49" t="n">
-        <v>1.4</v>
+      <c r="N7" s="49">
+        <f>ROUND(E7+G7+I7+K7+M7,2)</f>
+        <v/>
       </c>
       <c r="O7" s="31" t="inlineStr">
         <is>
@@ -13870,8 +13874,9 @@
       <c r="M8" s="52" t="n">
         <v>0.25</v>
       </c>
-      <c r="N8" s="52" t="n">
-        <v>2.5</v>
+      <c r="N8" s="52">
+        <f>ROUND(E8+G8+I8+K8+M8,2)</f>
+        <v/>
       </c>
       <c r="O8" s="51" t="inlineStr">
         <is>
@@ -13934,8 +13939,9 @@
         </is>
       </c>
       <c r="M9" s="52" t="n"/>
-      <c r="N9" s="52" t="n">
-        <v>2.25</v>
+      <c r="N9" s="52">
+        <f>ROUND(E9+G9+I9+K9+M9,2)</f>
+        <v/>
       </c>
       <c r="O9" s="51" t="inlineStr">
         <is>
@@ -14004,8 +14010,9 @@
       <c r="M10" s="48" t="n">
         <v>0.25</v>
       </c>
-      <c r="N10" s="48" t="n">
-        <v>4</v>
+      <c r="N10" s="48">
+        <f>ROUND(E10+G10+I10+K10+M10,2)</f>
+        <v/>
       </c>
       <c r="O10" s="33" t="inlineStr">
         <is>
@@ -14070,8 +14077,9 @@
         </is>
       </c>
       <c r="M11" s="48" t="n"/>
-      <c r="N11" s="48" t="n">
-        <v>2.25</v>
+      <c r="N11" s="48">
+        <f>ROUND(E11+G11+I11+K11+M11,2)</f>
+        <v/>
       </c>
       <c r="O11" s="33" t="inlineStr">
         <is>
@@ -14136,8 +14144,9 @@
         </is>
       </c>
       <c r="M12" s="55" t="n"/>
-      <c r="N12" s="55" t="n">
-        <v>2.75</v>
+      <c r="N12" s="55">
+        <f>ROUND(E12+G12+I12+K12+M12,2)</f>
+        <v/>
       </c>
       <c r="O12" s="54" t="inlineStr">
         <is>
@@ -14200,8 +14209,9 @@
         </is>
       </c>
       <c r="M13" s="55" t="n"/>
-      <c r="N13" s="55" t="n">
-        <v>2.25</v>
+      <c r="N13" s="55">
+        <f>ROUND(E13+G13+I13+K13+M13,2)</f>
+        <v/>
       </c>
       <c r="O13" s="54" t="inlineStr">
         <is>
@@ -14262,8 +14272,9 @@
         </is>
       </c>
       <c r="M14" s="55" t="n"/>
-      <c r="N14" s="55" t="n">
-        <v>1</v>
+      <c r="N14" s="55">
+        <f>ROUND(E14+G14+I14+K14+M14,2)</f>
+        <v/>
       </c>
       <c r="O14" s="54" t="inlineStr">
         <is>
@@ -14324,8 +14335,9 @@
         </is>
       </c>
       <c r="M15" s="55" t="n"/>
-      <c r="N15" s="55" t="n">
-        <v>1</v>
+      <c r="N15" s="55">
+        <f>ROUND(E15+G15+I15+K15+M15,2)</f>
+        <v/>
       </c>
       <c r="O15" s="54" t="inlineStr">
         <is>
@@ -14390,8 +14402,9 @@
         </is>
       </c>
       <c r="M16" s="58" t="n"/>
-      <c r="N16" s="58" t="n">
-        <v>1.58</v>
+      <c r="N16" s="58">
+        <f>ROUND(E16+G16+I16+K16+M16,2)</f>
+        <v/>
       </c>
       <c r="O16" s="57" t="inlineStr">
         <is>
@@ -14454,8 +14467,9 @@
         </is>
       </c>
       <c r="M17" s="58" t="n"/>
-      <c r="N17" s="58" t="n">
-        <v>1.08</v>
+      <c r="N17" s="58">
+        <f>ROUND(E17+G17+I17+K17+M17,2)</f>
+        <v/>
       </c>
       <c r="O17" s="57" t="inlineStr">
         <is>
@@ -14518,8 +14532,9 @@
         </is>
       </c>
       <c r="M18" s="58" t="n"/>
-      <c r="N18" s="58" t="n">
-        <v>0.83</v>
+      <c r="N18" s="58">
+        <f>ROUND(E18+G18+I18+K18+M18,2)</f>
+        <v/>
       </c>
       <c r="O18" s="57" t="inlineStr">
         <is>
@@ -14582,8 +14597,9 @@
         </is>
       </c>
       <c r="M19" s="58" t="n"/>
-      <c r="N19" s="58" t="n">
-        <v>3.25</v>
+      <c r="N19" s="58">
+        <f>ROUND(E19+G19+I19+K19+M19,2)</f>
+        <v/>
       </c>
       <c r="O19" s="57" t="inlineStr">
         <is>
@@ -14644,8 +14660,9 @@
         </is>
       </c>
       <c r="M20" s="58" t="n"/>
-      <c r="N20" s="58" t="n">
-        <v>3</v>
+      <c r="N20" s="58">
+        <f>ROUND(E20+G20+I20+K20+M20,2)</f>
+        <v/>
       </c>
       <c r="O20" s="57" t="inlineStr">
         <is>
@@ -14710,8 +14727,9 @@
         </is>
       </c>
       <c r="M21" s="61" t="n"/>
-      <c r="N21" s="61" t="n">
-        <v>1.67</v>
+      <c r="N21" s="61">
+        <f>ROUND(E21+G21+I21+K21+M21,2)</f>
+        <v/>
       </c>
       <c r="O21" s="60" t="inlineStr">
         <is>
@@ -14774,8 +14792,9 @@
         </is>
       </c>
       <c r="M22" s="61" t="n"/>
-      <c r="N22" s="61" t="n">
-        <v>1.42</v>
+      <c r="N22" s="61">
+        <f>ROUND(E22+G22+I22+K22+M22,2)</f>
+        <v/>
       </c>
       <c r="O22" s="60" t="inlineStr">
         <is>
@@ -14838,8 +14857,9 @@
         </is>
       </c>
       <c r="M23" s="61" t="n"/>
-      <c r="N23" s="61" t="n">
-        <v>1.42</v>
+      <c r="N23" s="61">
+        <f>ROUND(E23+G23+I23+K23+M23,2)</f>
+        <v/>
       </c>
       <c r="O23" s="60" t="inlineStr">
         <is>
@@ -14906,8 +14926,9 @@
       <c r="M24" s="64" t="n">
         <v>0.5</v>
       </c>
-      <c r="N24" s="64" t="n">
-        <v>2.75</v>
+      <c r="N24" s="64">
+        <f>ROUND(E24+G24+I24+K24+M24,2)</f>
+        <v/>
       </c>
       <c r="O24" s="63" t="inlineStr">
         <is>
@@ -14972,8 +14993,9 @@
       <c r="M25" s="64" t="n">
         <v>0.5</v>
       </c>
-      <c r="N25" s="64" t="n">
-        <v>2.5</v>
+      <c r="N25" s="64">
+        <f>ROUND(E25+G25+I25+K25+M25,2)</f>
+        <v/>
       </c>
       <c r="O25" s="63" t="inlineStr">
         <is>
@@ -15038,8 +15060,9 @@
       <c r="M26" s="64" t="n">
         <v>0.5</v>
       </c>
-      <c r="N26" s="64" t="n">
-        <v>3.75</v>
+      <c r="N26" s="64">
+        <f>ROUND(E26+G26+I26+K26+M26,2)</f>
+        <v/>
       </c>
       <c r="O26" s="63" t="inlineStr">
         <is>
@@ -15100,8 +15123,9 @@
         </is>
       </c>
       <c r="M27" s="64" t="n"/>
-      <c r="N27" s="64" t="n">
-        <v>1</v>
+      <c r="N27" s="64">
+        <f>ROUND(E27+G27+I27+K27+M27,2)</f>
+        <v/>
       </c>
       <c r="O27" s="63" t="inlineStr">
         <is>
@@ -15162,8 +15186,9 @@
         </is>
       </c>
       <c r="M28" s="64" t="n"/>
-      <c r="N28" s="64" t="n">
-        <v>1</v>
+      <c r="N28" s="64">
+        <f>ROUND(E28+G28+I28+K28+M28,2)</f>
+        <v/>
       </c>
       <c r="O28" s="63" t="inlineStr">
         <is>
@@ -15224,8 +15249,9 @@
         </is>
       </c>
       <c r="M29" s="67" t="n"/>
-      <c r="N29" s="67" t="n">
-        <v>8.5</v>
+      <c r="N29" s="67">
+        <f>ROUND(E29+G29+I29+K29+M29,2)</f>
+        <v/>
       </c>
       <c r="O29" s="66" t="inlineStr">
         <is>
@@ -15288,8 +15314,9 @@
         </is>
       </c>
       <c r="M30" s="67" t="n"/>
-      <c r="N30" s="67" t="n">
-        <v>9</v>
+      <c r="N30" s="67">
+        <f>ROUND(E30+G30+I30+K30+M30,2)</f>
+        <v/>
       </c>
       <c r="O30" s="66" t="inlineStr">
         <is>
@@ -15352,8 +15379,9 @@
         </is>
       </c>
       <c r="M31" s="67" t="n"/>
-      <c r="N31" s="67" t="n">
-        <v>16.5</v>
+      <c r="N31" s="67">
+        <f>ROUND(E31+G31+I31+K31+M31,2)</f>
+        <v/>
       </c>
       <c r="O31" s="66" t="inlineStr">
         <is>
@@ -15420,8 +15448,9 @@
       <c r="M32" s="67" t="n">
         <v>1.5</v>
       </c>
-      <c r="N32" s="67" t="n">
-        <v>7.5</v>
+      <c r="N32" s="67">
+        <f>ROUND(E32+G32+I32+K32+M32,2)</f>
+        <v/>
       </c>
       <c r="O32" s="66" t="inlineStr">
         <is>
@@ -15486,8 +15515,9 @@
         </is>
       </c>
       <c r="M33" s="67" t="n"/>
-      <c r="N33" s="67" t="n">
-        <v>32</v>
+      <c r="N33" s="67">
+        <f>ROUND(E33+G33+I33+K33+M33,2)</f>
+        <v/>
       </c>
       <c r="O33" s="66" t="inlineStr">
         <is>
@@ -15554,8 +15584,9 @@
       <c r="M34" s="67" t="n">
         <v>3</v>
       </c>
-      <c r="N34" s="67" t="n">
-        <v>16.5</v>
+      <c r="N34" s="67">
+        <f>ROUND(E34+G34+I34+K34+M34,2)</f>
+        <v/>
       </c>
       <c r="O34" s="66" t="inlineStr">
         <is>
@@ -15618,8 +15649,9 @@
         </is>
       </c>
       <c r="M35" s="67" t="n"/>
-      <c r="N35" s="67" t="n">
-        <v>12</v>
+      <c r="N35" s="67">
+        <f>ROUND(E35+G35+I35+K35+M35,2)</f>
+        <v/>
       </c>
       <c r="O35" s="66" t="inlineStr">
         <is>
@@ -15686,8 +15718,9 @@
       <c r="M36" s="67" t="n">
         <v>1</v>
       </c>
-      <c r="N36" s="67" t="n">
-        <v>12.5</v>
+      <c r="N36" s="67">
+        <f>ROUND(E36+G36+I36+K36+M36,2)</f>
+        <v/>
       </c>
       <c r="O36" s="66" t="inlineStr">
         <is>
@@ -15748,8 +15781,9 @@
       <c r="M37" s="67" t="n">
         <v>1</v>
       </c>
-      <c r="N37" s="67" t="n">
-        <v>16</v>
+      <c r="N37" s="67">
+        <f>ROUND(E37+G37+I37+K37+M37+15.0,2)</f>
+        <v/>
       </c>
       <c r="O37" s="66" t="inlineStr">
         <is>
@@ -15779,43 +15813,49 @@
           <t>Mandy·BA</t>
         </is>
       </c>
-      <c r="E38" s="44" t="n">
-        <v>10.5</v>
+      <c r="E38" s="44">
+        <f>ROUND(SUM(E3:E37),2)</f>
+        <v/>
       </c>
       <c r="F38" s="8" t="inlineStr">
         <is>
           <t>Wade（开发A）</t>
         </is>
       </c>
-      <c r="G38" s="44" t="n">
-        <v>60</v>
+      <c r="G38" s="44">
+        <f>ROUND(SUM(G3:G37),2)</f>
+        <v/>
       </c>
       <c r="H38" s="8" t="inlineStr">
         <is>
           <t>DevB（开发B）</t>
         </is>
       </c>
-      <c r="I38" s="44" t="n">
-        <v>60</v>
+      <c r="I38" s="44">
+        <f>ROUND(SUM(I3:I37),2)</f>
+        <v/>
       </c>
       <c r="J38" s="8" t="inlineStr">
         <is>
           <t>Mandy·测试</t>
         </is>
       </c>
-      <c r="K38" s="44" t="n">
-        <v>29.5</v>
+      <c r="K38" s="44">
+        <f>ROUND(SUM(K3:K37),2)</f>
+        <v/>
       </c>
       <c r="L38" s="8" t="inlineStr">
         <is>
           <t>Mandy·文档</t>
         </is>
       </c>
-      <c r="M38" s="44" t="n">
-        <v>10</v>
-      </c>
-      <c r="N38" s="44" t="n">
-        <v>185</v>
+      <c r="M38" s="44">
+        <f>ROUND(SUM(M3:M37),2)</f>
+        <v/>
+      </c>
+      <c r="N38" s="44">
+        <f>ROUND(SUM(N3:N37),2)</f>
+        <v/>
       </c>
       <c r="O38" s="8" t="inlineStr"/>
       <c r="P38" s="8" t="inlineStr">
@@ -15974,11 +16014,13 @@
       <c r="J3" s="74" t="n">
         <v>1</v>
       </c>
-      <c r="K3" s="46" t="n">
-        <v>3</v>
-      </c>
-      <c r="L3" s="74" t="n">
-        <v>21.5</v>
+      <c r="K3" s="46">
+        <f>ROUND(SUM(F3:I3),2)</f>
+        <v/>
+      </c>
+      <c r="L3" s="74">
+        <f>ROUND(SUM(F3:I9)+J3,2)</f>
+        <v/>
       </c>
     </row>
     <row r="4" ht="26" customHeight="1">
@@ -15988,7 +16030,7 @@
         </is>
       </c>
       <c r="B4" s="102" t="n"/>
-      <c r="C4" s="17" t="n"/>
+      <c r="C4" s="102" t="n"/>
       <c r="D4" s="32" t="inlineStr">
         <is>
           <t>源库DB连接配置</t>
@@ -16011,11 +16053,12 @@
       <c r="I4" s="46" t="n">
         <v>0.5</v>
       </c>
-      <c r="J4" s="17" t="n"/>
-      <c r="K4" s="46" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="L4" s="17" t="n"/>
+      <c r="J4" s="102" t="n"/>
+      <c r="K4" s="46">
+        <f>ROUND(SUM(F4:I4),2)</f>
+        <v/>
+      </c>
+      <c r="L4" s="102" t="n"/>
     </row>
     <row r="5" ht="26" customHeight="1">
       <c r="A5" s="15" t="inlineStr">
@@ -16024,7 +16067,7 @@
         </is>
       </c>
       <c r="B5" s="102" t="n"/>
-      <c r="C5" s="17" t="n"/>
+      <c r="C5" s="102" t="n"/>
       <c r="D5" s="32" t="inlineStr">
         <is>
           <t>同步表勾选</t>
@@ -16047,11 +16090,12 @@
       <c r="I5" s="46" t="n">
         <v>0.5</v>
       </c>
-      <c r="J5" s="17" t="n"/>
-      <c r="K5" s="46" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="L5" s="17" t="n"/>
+      <c r="J5" s="102" t="n"/>
+      <c r="K5" s="46">
+        <f>ROUND(SUM(F5:I5),2)</f>
+        <v/>
+      </c>
+      <c r="L5" s="102" t="n"/>
     </row>
     <row r="6" ht="26" customHeight="1">
       <c r="A6" s="15" t="inlineStr">
@@ -16060,7 +16104,7 @@
         </is>
       </c>
       <c r="B6" s="102" t="n"/>
-      <c r="C6" s="17" t="n"/>
+      <c r="C6" s="102" t="n"/>
       <c r="D6" s="32" t="inlineStr">
         <is>
           <t>保留期限与迁移参数配置</t>
@@ -16083,11 +16127,12 @@
       <c r="I6" s="46" t="n">
         <v>0.25</v>
       </c>
-      <c r="J6" s="17" t="n"/>
-      <c r="K6" s="46" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="L6" s="17" t="n"/>
+      <c r="J6" s="102" t="n"/>
+      <c r="K6" s="46">
+        <f>ROUND(SUM(F6:I6),2)</f>
+        <v/>
+      </c>
+      <c r="L6" s="102" t="n"/>
     </row>
     <row r="7" ht="26" customHeight="1">
       <c r="A7" s="15" t="inlineStr">
@@ -16096,7 +16141,7 @@
         </is>
       </c>
       <c r="B7" s="102" t="n"/>
-      <c r="C7" s="17" t="n"/>
+      <c r="C7" s="102" t="n"/>
       <c r="D7" s="32" t="inlineStr">
         <is>
           <t>存储落地实现（Iceberg/UC）</t>
@@ -16117,11 +16162,12 @@
       <c r="I7" s="46" t="n">
         <v>0.5</v>
       </c>
-      <c r="J7" s="17" t="n"/>
-      <c r="K7" s="46" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="L7" s="17" t="n"/>
+      <c r="J7" s="102" t="n"/>
+      <c r="K7" s="46">
+        <f>ROUND(SUM(F7:I7),2)</f>
+        <v/>
+      </c>
+      <c r="L7" s="102" t="n"/>
     </row>
     <row r="8" ht="26" customHeight="1">
       <c r="A8" s="15" t="inlineStr">
@@ -16130,7 +16176,7 @@
         </is>
       </c>
       <c r="B8" s="102" t="n"/>
-      <c r="C8" s="17" t="n"/>
+      <c r="C8" s="102" t="n"/>
       <c r="D8" s="32" t="inlineStr">
         <is>
           <t>SeaTunnel批量导入作业</t>
@@ -16151,11 +16197,12 @@
       <c r="I8" s="46" t="n">
         <v>1</v>
       </c>
-      <c r="J8" s="17" t="n"/>
-      <c r="K8" s="46" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="L8" s="17" t="n"/>
+      <c r="J8" s="102" t="n"/>
+      <c r="K8" s="46">
+        <f>ROUND(SUM(F8:I8),2)</f>
+        <v/>
+      </c>
+      <c r="L8" s="102" t="n"/>
     </row>
     <row r="9" ht="26" customHeight="1">
       <c r="A9" s="15" t="inlineStr">
@@ -16164,7 +16211,7 @@
         </is>
       </c>
       <c r="B9" s="102" t="n"/>
-      <c r="C9" s="17" t="n"/>
+      <c r="C9" s="103" t="n"/>
       <c r="D9" s="32" t="inlineStr">
         <is>
           <t>导入执行与监控</t>
@@ -16185,11 +16232,12 @@
       <c r="I9" s="46" t="n">
         <v>0.5</v>
       </c>
-      <c r="J9" s="17" t="n"/>
-      <c r="K9" s="46" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="L9" s="17" t="n"/>
+      <c r="J9" s="103" t="n"/>
+      <c r="K9" s="46">
+        <f>ROUND(SUM(F9:I9),2)</f>
+        <v/>
+      </c>
+      <c r="L9" s="103" t="n"/>
     </row>
     <row r="10" ht="26" customHeight="1">
       <c r="A10" s="15" t="inlineStr">
@@ -16228,11 +16276,13 @@
       <c r="J10" s="74" t="n">
         <v>0.5</v>
       </c>
-      <c r="K10" s="46" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="L10" s="74" t="n">
-        <v>12.75</v>
+      <c r="K10" s="46">
+        <f>ROUND(SUM(F10:I10),2)</f>
+        <v/>
+      </c>
+      <c r="L10" s="74">
+        <f>ROUND(SUM(F10:I13)+J10,2)</f>
+        <v/>
       </c>
     </row>
     <row r="11" ht="26" customHeight="1">
@@ -16242,7 +16292,7 @@
         </is>
       </c>
       <c r="B11" s="102" t="n"/>
-      <c r="C11" s="17" t="n"/>
+      <c r="C11" s="102" t="n"/>
       <c r="D11" s="32" t="inlineStr">
         <is>
           <t>大文件分片上传与断点续传</t>
@@ -16263,11 +16313,12 @@
       <c r="I11" s="46" t="n">
         <v>1</v>
       </c>
-      <c r="J11" s="17" t="n"/>
-      <c r="K11" s="46" t="n">
-        <v>4</v>
-      </c>
-      <c r="L11" s="17" t="n"/>
+      <c r="J11" s="102" t="n"/>
+      <c r="K11" s="46">
+        <f>ROUND(SUM(F11:I11),2)</f>
+        <v/>
+      </c>
+      <c r="L11" s="102" t="n"/>
     </row>
     <row r="12" ht="26" customHeight="1">
       <c r="A12" s="15" t="inlineStr">
@@ -16276,7 +16327,7 @@
         </is>
       </c>
       <c r="B12" s="102" t="n"/>
-      <c r="C12" s="17" t="n"/>
+      <c r="C12" s="102" t="n"/>
       <c r="D12" s="32" t="inlineStr">
         <is>
           <t>文件包解析</t>
@@ -16295,11 +16346,12 @@
       <c r="I12" s="46" t="n">
         <v>0.75</v>
       </c>
-      <c r="J12" s="17" t="n"/>
-      <c r="K12" s="46" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="L12" s="17" t="n"/>
+      <c r="J12" s="102" t="n"/>
+      <c r="K12" s="46">
+        <f>ROUND(SUM(F12:I12),2)</f>
+        <v/>
+      </c>
+      <c r="L12" s="102" t="n"/>
     </row>
     <row r="13" ht="26" customHeight="1">
       <c r="A13" s="15" t="inlineStr">
@@ -16308,7 +16360,7 @@
         </is>
       </c>
       <c r="B13" s="102" t="n"/>
-      <c r="C13" s="17" t="n"/>
+      <c r="C13" s="103" t="n"/>
       <c r="D13" s="32" t="inlineStr">
         <is>
           <t>附件元数据与Blob存储布局</t>
@@ -16329,11 +16381,12 @@
       <c r="I13" s="46" t="n">
         <v>0.5</v>
       </c>
-      <c r="J13" s="17" t="n"/>
-      <c r="K13" s="46" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="L13" s="17" t="n"/>
+      <c r="J13" s="103" t="n"/>
+      <c r="K13" s="46">
+        <f>ROUND(SUM(F13:I13),2)</f>
+        <v/>
+      </c>
+      <c r="L13" s="103" t="n"/>
     </row>
     <row r="14" ht="26" customHeight="1">
       <c r="A14" s="15" t="inlineStr">
@@ -16372,11 +16425,13 @@
       <c r="J14" s="74" t="n">
         <v>0.5</v>
       </c>
-      <c r="K14" s="46" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="L14" s="74" t="n">
-        <v>11.25</v>
+      <c r="K14" s="46">
+        <f>ROUND(SUM(F14:I14),2)</f>
+        <v/>
+      </c>
+      <c r="L14" s="74">
+        <f>ROUND(SUM(F14:I17)+J14,2)</f>
+        <v/>
       </c>
     </row>
     <row r="15" ht="26" customHeight="1">
@@ -16386,7 +16441,7 @@
         </is>
       </c>
       <c r="B15" s="102" t="n"/>
-      <c r="C15" s="17" t="n"/>
+      <c r="C15" s="102" t="n"/>
       <c r="D15" s="32" t="inlineStr">
         <is>
           <t>格式转换与清洗规则</t>
@@ -16407,11 +16462,12 @@
       <c r="I15" s="46" t="n">
         <v>0.75</v>
       </c>
-      <c r="J15" s="17" t="n"/>
-      <c r="K15" s="46" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="L15" s="17" t="n"/>
+      <c r="J15" s="102" t="n"/>
+      <c r="K15" s="46">
+        <f>ROUND(SUM(F15:I15),2)</f>
+        <v/>
+      </c>
+      <c r="L15" s="102" t="n"/>
     </row>
     <row r="16" ht="26" customHeight="1">
       <c r="A16" s="15" t="inlineStr">
@@ -16420,7 +16476,7 @@
         </is>
       </c>
       <c r="B16" s="102" t="n"/>
-      <c r="C16" s="17" t="n"/>
+      <c r="C16" s="102" t="n"/>
       <c r="D16" s="32" t="inlineStr">
         <is>
           <t>校验规则配置</t>
@@ -16441,11 +16497,12 @@
       <c r="I16" s="46" t="n">
         <v>0.5</v>
       </c>
-      <c r="J16" s="17" t="n"/>
-      <c r="K16" s="46" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="L16" s="17" t="n"/>
+      <c r="J16" s="102" t="n"/>
+      <c r="K16" s="46">
+        <f>ROUND(SUM(F16:I16),2)</f>
+        <v/>
+      </c>
+      <c r="L16" s="102" t="n"/>
     </row>
     <row r="17" ht="26" customHeight="1">
       <c r="A17" s="15" t="inlineStr">
@@ -16454,7 +16511,7 @@
         </is>
       </c>
       <c r="B17" s="102" t="n"/>
-      <c r="C17" s="17" t="n"/>
+      <c r="C17" s="103" t="n"/>
       <c r="D17" s="32" t="inlineStr">
         <is>
           <t>规则版本与试跑预览</t>
@@ -16475,11 +16532,12 @@
       <c r="I17" s="46" t="n">
         <v>0.5</v>
       </c>
-      <c r="J17" s="17" t="n"/>
-      <c r="K17" s="46" t="n">
-        <v>2</v>
-      </c>
-      <c r="L17" s="17" t="n"/>
+      <c r="J17" s="103" t="n"/>
+      <c r="K17" s="46">
+        <f>ROUND(SUM(F17:I17),2)</f>
+        <v/>
+      </c>
+      <c r="L17" s="103" t="n"/>
     </row>
     <row r="18" ht="26" customHeight="1">
       <c r="A18" s="15" t="inlineStr">
@@ -16516,11 +16574,13 @@
       <c r="J18" s="74" t="n">
         <v>0.5</v>
       </c>
-      <c r="K18" s="46" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="L18" s="74" t="n">
-        <v>5.25</v>
+      <c r="K18" s="46">
+        <f>ROUND(SUM(F18:I18),2)</f>
+        <v/>
+      </c>
+      <c r="L18" s="74">
+        <f>ROUND(SUM(F18:I20)+J18,2)</f>
+        <v/>
       </c>
     </row>
     <row r="19" ht="26" customHeight="1">
@@ -16530,7 +16590,7 @@
         </is>
       </c>
       <c r="B19" s="102" t="n"/>
-      <c r="C19" s="17" t="n"/>
+      <c r="C19" s="102" t="n"/>
       <c r="D19" s="32" t="inlineStr">
         <is>
           <t>基准采集作业与存储</t>
@@ -16549,11 +16609,12 @@
       <c r="I19" s="46" t="n">
         <v>0.5</v>
       </c>
-      <c r="J19" s="17" t="n"/>
-      <c r="K19" s="46" t="n">
-        <v>2</v>
-      </c>
-      <c r="L19" s="17" t="n"/>
+      <c r="J19" s="102" t="n"/>
+      <c r="K19" s="46">
+        <f>ROUND(SUM(F19:I19),2)</f>
+        <v/>
+      </c>
+      <c r="L19" s="102" t="n"/>
     </row>
     <row r="20" ht="26" customHeight="1">
       <c r="A20" s="15" t="inlineStr">
@@ -16562,7 +16623,7 @@
         </is>
       </c>
       <c r="B20" s="102" t="n"/>
-      <c r="C20" s="17" t="n"/>
+      <c r="C20" s="103" t="n"/>
       <c r="D20" s="32" t="inlineStr">
         <is>
           <t>基准报告查询展示</t>
@@ -16583,11 +16644,12 @@
       <c r="I20" s="46" t="n">
         <v>0.25</v>
       </c>
-      <c r="J20" s="17" t="n"/>
-      <c r="K20" s="46" t="n">
-        <v>1</v>
-      </c>
-      <c r="L20" s="17" t="n"/>
+      <c r="J20" s="103" t="n"/>
+      <c r="K20" s="46">
+        <f>ROUND(SUM(F20:I20),2)</f>
+        <v/>
+      </c>
+      <c r="L20" s="103" t="n"/>
     </row>
     <row r="21" ht="26" customHeight="1">
       <c r="A21" s="15" t="inlineStr">
@@ -16622,11 +16684,13 @@
       <c r="J21" s="74" t="n">
         <v>0.5</v>
       </c>
-      <c r="K21" s="46" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="L21" s="74" t="n">
-        <v>5.5</v>
+      <c r="K21" s="46">
+        <f>ROUND(SUM(F21:I21),2)</f>
+        <v/>
+      </c>
+      <c r="L21" s="74">
+        <f>ROUND(SUM(F21:I22)+J21,2)</f>
+        <v/>
       </c>
     </row>
     <row r="22" ht="26" customHeight="1">
@@ -16636,7 +16700,7 @@
         </is>
       </c>
       <c r="B22" s="103" t="n"/>
-      <c r="C22" s="17" t="n"/>
+      <c r="C22" s="103" t="n"/>
       <c r="D22" s="32" t="inlineStr">
         <is>
           <t>差异报告与处理流程</t>
@@ -16659,11 +16723,12 @@
       <c r="I22" s="46" t="n">
         <v>0.5</v>
       </c>
-      <c r="J22" s="17" t="n"/>
-      <c r="K22" s="46" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="L22" s="17" t="n"/>
+      <c r="J22" s="103" t="n"/>
+      <c r="K22" s="46">
+        <f>ROUND(SUM(F22:I22),2)</f>
+        <v/>
+      </c>
+      <c r="L22" s="103" t="n"/>
     </row>
     <row r="23" ht="26" customHeight="1">
       <c r="A23" s="15" t="inlineStr">
@@ -16704,11 +16769,13 @@
       <c r="J23" s="77" t="n">
         <v>0.5</v>
       </c>
-      <c r="K23" s="46" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="L23" s="77" t="n">
-        <v>8.5</v>
+      <c r="K23" s="46">
+        <f>ROUND(SUM(F23:I23),2)</f>
+        <v/>
+      </c>
+      <c r="L23" s="77">
+        <f>ROUND(SUM(F23:I25)+J23,2)</f>
+        <v/>
       </c>
     </row>
     <row r="24" ht="26" customHeight="1">
@@ -16718,7 +16785,7 @@
         </is>
       </c>
       <c r="B24" s="102" t="n"/>
-      <c r="C24" s="17" t="n"/>
+      <c r="C24" s="102" t="n"/>
       <c r="D24" s="32" t="inlineStr">
         <is>
           <t>元数据核心表与API</t>
@@ -16737,11 +16804,12 @@
       <c r="I24" s="46" t="n">
         <v>0.5</v>
       </c>
-      <c r="J24" s="17" t="n"/>
-      <c r="K24" s="46" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="L24" s="17" t="n"/>
+      <c r="J24" s="102" t="n"/>
+      <c r="K24" s="46">
+        <f>ROUND(SUM(F24:I24),2)</f>
+        <v/>
+      </c>
+      <c r="L24" s="102" t="n"/>
     </row>
     <row r="25" ht="26" customHeight="1">
       <c r="A25" s="15" t="inlineStr">
@@ -16750,7 +16818,7 @@
         </is>
       </c>
       <c r="B25" s="102" t="n"/>
-      <c r="C25" s="17" t="n"/>
+      <c r="C25" s="103" t="n"/>
       <c r="D25" s="32" t="inlineStr">
         <is>
           <t>元数据驱动配置机制</t>
@@ -16773,11 +16841,12 @@
       <c r="I25" s="46" t="n">
         <v>0.5</v>
       </c>
-      <c r="J25" s="17" t="n"/>
-      <c r="K25" s="46" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="L25" s="17" t="n"/>
+      <c r="J25" s="103" t="n"/>
+      <c r="K25" s="46">
+        <f>ROUND(SUM(F25:I25),2)</f>
+        <v/>
+      </c>
+      <c r="L25" s="103" t="n"/>
     </row>
     <row r="26" ht="26" customHeight="1">
       <c r="A26" s="15" t="inlineStr">
@@ -16814,11 +16883,13 @@
       <c r="J26" s="77" t="n">
         <v>0.5</v>
       </c>
-      <c r="K26" s="46" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="L26" s="77" t="n">
-        <v>5.5</v>
+      <c r="K26" s="46">
+        <f>ROUND(SUM(F26:I26),2)</f>
+        <v/>
+      </c>
+      <c r="L26" s="77">
+        <f>ROUND(SUM(F26:I28)+J26,2)</f>
+        <v/>
       </c>
     </row>
     <row r="27" ht="26" customHeight="1">
@@ -16828,7 +16899,7 @@
         </is>
       </c>
       <c r="B27" s="102" t="n"/>
-      <c r="C27" s="17" t="n"/>
+      <c r="C27" s="102" t="n"/>
       <c r="D27" s="32" t="inlineStr">
         <is>
           <t>接入时自动绑定</t>
@@ -16847,11 +16918,12 @@
       <c r="I27" s="46" t="n">
         <v>0.5</v>
       </c>
-      <c r="J27" s="17" t="n"/>
-      <c r="K27" s="46" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="L27" s="17" t="n"/>
+      <c r="J27" s="102" t="n"/>
+      <c r="K27" s="46">
+        <f>ROUND(SUM(F27:I27),2)</f>
+        <v/>
+      </c>
+      <c r="L27" s="102" t="n"/>
     </row>
     <row r="28" ht="26" customHeight="1">
       <c r="A28" s="15" t="inlineStr">
@@ -16860,7 +16932,7 @@
         </is>
       </c>
       <c r="B28" s="103" t="n"/>
-      <c r="C28" s="17" t="n"/>
+      <c r="C28" s="103" t="n"/>
       <c r="D28" s="32" t="inlineStr">
         <is>
           <t>按来源检索与统计</t>
@@ -16881,11 +16953,12 @@
       <c r="I28" s="46" t="n">
         <v>0.5</v>
       </c>
-      <c r="J28" s="17" t="n"/>
-      <c r="K28" s="46" t="n">
-        <v>2</v>
-      </c>
-      <c r="L28" s="17" t="n"/>
+      <c r="J28" s="103" t="n"/>
+      <c r="K28" s="46">
+        <f>ROUND(SUM(F28:I28),2)</f>
+        <v/>
+      </c>
+      <c r="L28" s="103" t="n"/>
     </row>
     <row r="29" ht="26" customHeight="1">
       <c r="A29" s="15" t="inlineStr">
@@ -16928,11 +17001,13 @@
       <c r="J29" s="80" t="n">
         <v>0.5</v>
       </c>
-      <c r="K29" s="46" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="L29" s="80" t="n">
-        <v>9.5</v>
+      <c r="K29" s="46">
+        <f>ROUND(SUM(F29:I29),2)</f>
+        <v/>
+      </c>
+      <c r="L29" s="80">
+        <f>ROUND(SUM(F29:I31)+J29,2)</f>
+        <v/>
       </c>
     </row>
     <row r="30" ht="26" customHeight="1">
@@ -16942,7 +17017,7 @@
         </is>
       </c>
       <c r="B30" s="102" t="n"/>
-      <c r="C30" s="17" t="n"/>
+      <c r="C30" s="102" t="n"/>
       <c r="D30" s="32" t="inlineStr">
         <is>
           <t>处置引擎</t>
@@ -16961,11 +17036,12 @@
       <c r="I30" s="46" t="n">
         <v>1</v>
       </c>
-      <c r="J30" s="17" t="n"/>
-      <c r="K30" s="46" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="L30" s="17" t="n"/>
+      <c r="J30" s="102" t="n"/>
+      <c r="K30" s="46">
+        <f>ROUND(SUM(F30:I30),2)</f>
+        <v/>
+      </c>
+      <c r="L30" s="102" t="n"/>
     </row>
     <row r="31" ht="26" customHeight="1">
       <c r="A31" s="15" t="inlineStr">
@@ -16974,7 +17050,7 @@
         </is>
       </c>
       <c r="B31" s="102" t="n"/>
-      <c r="C31" s="17" t="n"/>
+      <c r="C31" s="103" t="n"/>
       <c r="D31" s="32" t="inlineStr">
         <is>
           <t>处置计划审批与台账</t>
@@ -16997,11 +17073,12 @@
       <c r="I31" s="46" t="n">
         <v>0.5</v>
       </c>
-      <c r="J31" s="17" t="n"/>
-      <c r="K31" s="46" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="L31" s="17" t="n"/>
+      <c r="J31" s="103" t="n"/>
+      <c r="K31" s="46">
+        <f>ROUND(SUM(F31:I31),2)</f>
+        <v/>
+      </c>
+      <c r="L31" s="103" t="n"/>
     </row>
     <row r="32" ht="26" customHeight="1">
       <c r="A32" s="15" t="inlineStr">
@@ -17040,11 +17117,13 @@
       <c r="J32" s="80" t="n">
         <v>0.5</v>
       </c>
-      <c r="K32" s="46" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="L32" s="80" t="n">
-        <v>6.25</v>
+      <c r="K32" s="46">
+        <f>ROUND(SUM(F32:I32),2)</f>
+        <v/>
+      </c>
+      <c r="L32" s="80">
+        <f>ROUND(SUM(F32:I34)+J32,2)</f>
+        <v/>
       </c>
     </row>
     <row r="33" ht="26" customHeight="1">
@@ -17054,7 +17133,7 @@
         </is>
       </c>
       <c r="B33" s="102" t="n"/>
-      <c r="C33" s="17" t="n"/>
+      <c r="C33" s="102" t="n"/>
       <c r="D33" s="32" t="inlineStr">
         <is>
           <t>Hold生效与解除实现</t>
@@ -17073,11 +17152,12 @@
       <c r="I33" s="46" t="n">
         <v>0.75</v>
       </c>
-      <c r="J33" s="17" t="n"/>
-      <c r="K33" s="46" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="L33" s="17" t="n"/>
+      <c r="J33" s="102" t="n"/>
+      <c r="K33" s="46">
+        <f>ROUND(SUM(F33:I33),2)</f>
+        <v/>
+      </c>
+      <c r="L33" s="102" t="n"/>
     </row>
     <row r="34" ht="26" customHeight="1">
       <c r="A34" s="15" t="inlineStr">
@@ -17086,7 +17166,7 @@
         </is>
       </c>
       <c r="B34" s="103" t="n"/>
-      <c r="C34" s="17" t="n"/>
+      <c r="C34" s="103" t="n"/>
       <c r="D34" s="32" t="inlineStr">
         <is>
           <t>Hold清单管理与提醒</t>
@@ -17107,11 +17187,12 @@
       <c r="I34" s="46" t="n">
         <v>0.25</v>
       </c>
-      <c r="J34" s="17" t="n"/>
-      <c r="K34" s="46" t="n">
-        <v>1</v>
-      </c>
-      <c r="L34" s="17" t="n"/>
+      <c r="J34" s="103" t="n"/>
+      <c r="K34" s="46">
+        <f>ROUND(SUM(F34:I34),2)</f>
+        <v/>
+      </c>
+      <c r="L34" s="103" t="n"/>
     </row>
     <row r="35" ht="26" customHeight="1">
       <c r="A35" s="15" t="inlineStr">
@@ -17152,11 +17233,13 @@
       <c r="J35" s="83" t="n">
         <v>0.5</v>
       </c>
-      <c r="K35" s="46" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="L35" s="83" t="n">
-        <v>5.25</v>
+      <c r="K35" s="46">
+        <f>ROUND(SUM(F35:I35),2)</f>
+        <v/>
+      </c>
+      <c r="L35" s="83">
+        <f>ROUND(SUM(F35:I37)+J35,2)</f>
+        <v/>
       </c>
     </row>
     <row r="36" ht="26" customHeight="1">
@@ -17166,7 +17249,7 @@
         </is>
       </c>
       <c r="B36" s="102" t="n"/>
-      <c r="C36" s="17" t="n"/>
+      <c r="C36" s="102" t="n"/>
       <c r="D36" s="32" t="inlineStr">
         <is>
           <t>存储层加密落地【原生】</t>
@@ -17185,11 +17268,12 @@
       <c r="I36" s="46" t="n">
         <v>0.5</v>
       </c>
-      <c r="J36" s="17" t="n"/>
-      <c r="K36" s="46" t="n">
-        <v>1</v>
-      </c>
-      <c r="L36" s="17" t="n"/>
+      <c r="J36" s="102" t="n"/>
+      <c r="K36" s="46">
+        <f>ROUND(SUM(F36:I36),2)</f>
+        <v/>
+      </c>
+      <c r="L36" s="102" t="n"/>
     </row>
     <row r="37" ht="26" customHeight="1">
       <c r="A37" s="15" t="inlineStr">
@@ -17198,7 +17282,7 @@
         </is>
       </c>
       <c r="B37" s="102" t="n"/>
-      <c r="C37" s="17" t="n"/>
+      <c r="C37" s="103" t="n"/>
       <c r="D37" s="32" t="inlineStr">
         <is>
           <t>PII字段级加密服务</t>
@@ -17217,11 +17301,12 @@
       <c r="I37" s="46" t="n">
         <v>0.75</v>
       </c>
-      <c r="J37" s="17" t="n"/>
-      <c r="K37" s="46" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="L37" s="17" t="n"/>
+      <c r="J37" s="103" t="n"/>
+      <c r="K37" s="46">
+        <f>ROUND(SUM(F37:I37),2)</f>
+        <v/>
+      </c>
+      <c r="L37" s="103" t="n"/>
     </row>
     <row r="38" ht="26" customHeight="1">
       <c r="A38" s="15" t="inlineStr">
@@ -17258,11 +17343,13 @@
       <c r="J38" s="83" t="n">
         <v>0.5</v>
       </c>
-      <c r="K38" s="46" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="L38" s="83" t="n">
-        <v>3.25</v>
+      <c r="K38" s="46">
+        <f>ROUND(SUM(F38:I38),2)</f>
+        <v/>
+      </c>
+      <c r="L38" s="83">
+        <f>ROUND(SUM(F38:I40)+J38,2)</f>
+        <v/>
       </c>
     </row>
     <row r="39" ht="26" customHeight="1">
@@ -17272,7 +17359,7 @@
         </is>
       </c>
       <c r="B39" s="102" t="n"/>
-      <c r="C39" s="17" t="n"/>
+      <c r="C39" s="102" t="n"/>
       <c r="D39" s="32" t="inlineStr">
         <is>
           <t>密钥操作审计与告警【原生】</t>
@@ -17293,11 +17380,12 @@
       <c r="I39" s="46" t="n">
         <v>0.5</v>
       </c>
-      <c r="J39" s="17" t="n"/>
-      <c r="K39" s="46" t="n">
-        <v>1</v>
-      </c>
-      <c r="L39" s="17" t="n"/>
+      <c r="J39" s="102" t="n"/>
+      <c r="K39" s="46">
+        <f>ROUND(SUM(F39:I39),2)</f>
+        <v/>
+      </c>
+      <c r="L39" s="102" t="n"/>
     </row>
     <row r="40" ht="26" customHeight="1">
       <c r="A40" s="15" t="inlineStr">
@@ -17306,7 +17394,7 @@
         </is>
       </c>
       <c r="B40" s="102" t="n"/>
-      <c r="C40" s="17" t="n"/>
+      <c r="C40" s="103" t="n"/>
       <c r="D40" s="32" t="inlineStr">
         <is>
           <t>密钥状态展示（不自研管理界面）【原生】</t>
@@ -17325,11 +17413,12 @@
       <c r="I40" s="46" t="n">
         <v>0.25</v>
       </c>
-      <c r="J40" s="17" t="n"/>
-      <c r="K40" s="46" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="L40" s="17" t="n"/>
+      <c r="J40" s="103" t="n"/>
+      <c r="K40" s="46">
+        <f>ROUND(SUM(F40:I40),2)</f>
+        <v/>
+      </c>
+      <c r="L40" s="103" t="n"/>
     </row>
     <row r="41" ht="26" customHeight="1">
       <c r="A41" s="15" t="inlineStr">
@@ -17368,11 +17457,13 @@
       <c r="J41" s="83" t="n">
         <v>0.5</v>
       </c>
-      <c r="K41" s="46" t="n">
-        <v>2</v>
-      </c>
-      <c r="L41" s="83" t="n">
-        <v>4.5</v>
+      <c r="K41" s="46">
+        <f>ROUND(SUM(F41:I41),2)</f>
+        <v/>
+      </c>
+      <c r="L41" s="83">
+        <f>ROUND(SUM(F41:I43)+J41,2)</f>
+        <v/>
       </c>
     </row>
     <row r="42" ht="26" customHeight="1">
@@ -17382,7 +17473,7 @@
         </is>
       </c>
       <c r="B42" s="102" t="n"/>
-      <c r="C42" s="17" t="n"/>
+      <c r="C42" s="102" t="n"/>
       <c r="D42" s="32" t="inlineStr">
         <is>
           <t>备份作业与副本创建【原生】</t>
@@ -17401,11 +17492,12 @@
       <c r="I42" s="46" t="n">
         <v>0.5</v>
       </c>
-      <c r="J42" s="17" t="n"/>
-      <c r="K42" s="46" t="n">
-        <v>1</v>
-      </c>
-      <c r="L42" s="17" t="n"/>
+      <c r="J42" s="102" t="n"/>
+      <c r="K42" s="46">
+        <f>ROUND(SUM(F42:I42),2)</f>
+        <v/>
+      </c>
+      <c r="L42" s="102" t="n"/>
     </row>
     <row r="43" ht="26" customHeight="1">
       <c r="A43" s="15" t="inlineStr">
@@ -17414,7 +17506,7 @@
         </is>
       </c>
       <c r="B43" s="103" t="n"/>
-      <c r="C43" s="17" t="n"/>
+      <c r="C43" s="103" t="n"/>
       <c r="D43" s="32" t="inlineStr">
         <is>
           <t>备份监控与恢复操作【原生】</t>
@@ -17435,11 +17527,12 @@
       <c r="I43" s="46" t="n">
         <v>0.5</v>
       </c>
-      <c r="J43" s="17" t="n"/>
-      <c r="K43" s="46" t="n">
-        <v>1</v>
-      </c>
-      <c r="L43" s="17" t="n"/>
+      <c r="J43" s="103" t="n"/>
+      <c r="K43" s="46">
+        <f>ROUND(SUM(F43:I43),2)</f>
+        <v/>
+      </c>
+      <c r="L43" s="103" t="n"/>
     </row>
     <row r="44" ht="26" customHeight="1">
       <c r="A44" s="15" t="inlineStr">
@@ -17482,11 +17575,13 @@
       <c r="J44" s="105" t="n">
         <v>0.5</v>
       </c>
-      <c r="K44" s="46" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="L44" s="105" t="n">
-        <v>7.5</v>
+      <c r="K44" s="46">
+        <f>ROUND(SUM(F44:I44),2)</f>
+        <v/>
+      </c>
+      <c r="L44" s="105">
+        <f>ROUND(SUM(F44:I46)+J44,2)</f>
+        <v/>
       </c>
     </row>
     <row r="45" ht="26" customHeight="1">
@@ -17496,7 +17591,7 @@
         </is>
       </c>
       <c r="B45" s="102" t="n"/>
-      <c r="C45" s="17" t="n"/>
+      <c r="C45" s="102" t="n"/>
       <c r="D45" s="32" t="inlineStr">
         <is>
           <t>检索页动态表单</t>
@@ -17517,11 +17612,12 @@
       <c r="I45" s="46" t="n">
         <v>0.5</v>
       </c>
-      <c r="J45" s="17" t="n"/>
-      <c r="K45" s="46" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="L45" s="17" t="n"/>
+      <c r="J45" s="102" t="n"/>
+      <c r="K45" s="46">
+        <f>ROUND(SUM(F45:I45),2)</f>
+        <v/>
+      </c>
+      <c r="L45" s="102" t="n"/>
     </row>
     <row r="46" ht="26" customHeight="1">
       <c r="A46" s="15" t="inlineStr">
@@ -17530,7 +17626,7 @@
         </is>
       </c>
       <c r="B46" s="102" t="n"/>
-      <c r="C46" s="17" t="n"/>
+      <c r="C46" s="103" t="n"/>
       <c r="D46" s="32" t="inlineStr">
         <is>
           <t>查询代理与SERVE层对接</t>
@@ -17549,11 +17645,12 @@
       <c r="I46" s="46" t="n">
         <v>0.75</v>
       </c>
-      <c r="J46" s="17" t="n"/>
-      <c r="K46" s="46" t="n">
-        <v>2</v>
-      </c>
-      <c r="L46" s="17" t="n"/>
+      <c r="J46" s="103" t="n"/>
+      <c r="K46" s="46">
+        <f>ROUND(SUM(F46:I46),2)</f>
+        <v/>
+      </c>
+      <c r="L46" s="103" t="n"/>
     </row>
     <row r="47" ht="26" customHeight="1">
       <c r="A47" s="15" t="inlineStr">
@@ -17588,11 +17685,13 @@
       <c r="J47" s="105" t="n">
         <v>0.25</v>
       </c>
-      <c r="K47" s="46" t="n">
-        <v>1</v>
-      </c>
-      <c r="L47" s="105" t="n">
-        <v>2</v>
+      <c r="K47" s="46">
+        <f>ROUND(SUM(F47:I47),2)</f>
+        <v/>
+      </c>
+      <c r="L47" s="105">
+        <f>ROUND(SUM(F47:I48)+J47,2)</f>
+        <v/>
       </c>
     </row>
     <row r="48" ht="26" customHeight="1">
@@ -17602,7 +17701,7 @@
         </is>
       </c>
       <c r="B48" s="102" t="n"/>
-      <c r="C48" s="17" t="n"/>
+      <c r="C48" s="103" t="n"/>
       <c r="D48" s="32" t="inlineStr">
         <is>
           <t>来源维度查询下推</t>
@@ -17621,11 +17720,12 @@
       <c r="I48" s="46" t="n">
         <v>0.25</v>
       </c>
-      <c r="J48" s="17" t="n"/>
-      <c r="K48" s="46" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="L48" s="17" t="n"/>
+      <c r="J48" s="103" t="n"/>
+      <c r="K48" s="46">
+        <f>ROUND(SUM(F48:I48),2)</f>
+        <v/>
+      </c>
+      <c r="L48" s="103" t="n"/>
     </row>
     <row r="49" ht="26" customHeight="1">
       <c r="A49" s="15" t="inlineStr">
@@ -17660,11 +17760,13 @@
       <c r="J49" s="105" t="n">
         <v>0.25</v>
       </c>
-      <c r="K49" s="46" t="n">
-        <v>1</v>
-      </c>
-      <c r="L49" s="105" t="n">
-        <v>2</v>
+      <c r="K49" s="46">
+        <f>ROUND(SUM(F49:I49),2)</f>
+        <v/>
+      </c>
+      <c r="L49" s="105">
+        <f>ROUND(SUM(F49:I50)+J49,2)</f>
+        <v/>
       </c>
     </row>
     <row r="50" ht="26" customHeight="1">
@@ -17674,7 +17776,7 @@
         </is>
       </c>
       <c r="B50" s="102" t="n"/>
-      <c r="C50" s="17" t="n"/>
+      <c r="C50" s="103" t="n"/>
       <c r="D50" s="32" t="inlineStr">
         <is>
           <t>时间分区下推与索引</t>
@@ -17693,11 +17795,12 @@
       <c r="I50" s="46" t="n">
         <v>0.25</v>
       </c>
-      <c r="J50" s="17" t="n"/>
-      <c r="K50" s="46" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="L50" s="17" t="n"/>
+      <c r="J50" s="103" t="n"/>
+      <c r="K50" s="46">
+        <f>ROUND(SUM(F50:I50),2)</f>
+        <v/>
+      </c>
+      <c r="L50" s="103" t="n"/>
     </row>
     <row r="51" ht="26" customHeight="1">
       <c r="A51" s="15" t="inlineStr">
@@ -17732,11 +17835,13 @@
       <c r="J51" s="105" t="n">
         <v>0.5</v>
       </c>
-      <c r="K51" s="46" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="L51" s="105" t="n">
-        <v>4.5</v>
+      <c r="K51" s="46">
+        <f>ROUND(SUM(F51:I51),2)</f>
+        <v/>
+      </c>
+      <c r="L51" s="105">
+        <f>ROUND(SUM(F51:I52)+J51,2)</f>
+        <v/>
       </c>
     </row>
     <row r="52" ht="26" customHeight="1">
@@ -17746,7 +17851,7 @@
         </is>
       </c>
       <c r="B52" s="102" t="n"/>
-      <c r="C52" s="17" t="n"/>
+      <c r="C52" s="103" t="n"/>
       <c r="D52" s="32" t="inlineStr">
         <is>
           <t>大批量结果性能</t>
@@ -17767,11 +17872,12 @@
       <c r="I52" s="46" t="n">
         <v>0.5</v>
       </c>
-      <c r="J52" s="17" t="n"/>
-      <c r="K52" s="46" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="L52" s="17" t="n"/>
+      <c r="J52" s="103" t="n"/>
+      <c r="K52" s="46">
+        <f>ROUND(SUM(F52:I52),2)</f>
+        <v/>
+      </c>
+      <c r="L52" s="103" t="n"/>
     </row>
     <row r="53" ht="26" customHeight="1">
       <c r="A53" s="15" t="inlineStr">
@@ -17806,11 +17912,13 @@
       <c r="J53" s="105" t="n">
         <v>0.5</v>
       </c>
-      <c r="K53" s="46" t="n">
-        <v>2</v>
-      </c>
-      <c r="L53" s="105" t="n">
-        <v>6.25</v>
+      <c r="K53" s="46">
+        <f>ROUND(SUM(F53:I53),2)</f>
+        <v/>
+      </c>
+      <c r="L53" s="105">
+        <f>ROUND(SUM(F53:I55)+J53,2)</f>
+        <v/>
       </c>
     </row>
     <row r="54" ht="26" customHeight="1">
@@ -17820,7 +17928,7 @@
         </is>
       </c>
       <c r="B54" s="102" t="n"/>
-      <c r="C54" s="17" t="n"/>
+      <c r="C54" s="102" t="n"/>
       <c r="D54" s="32" t="inlineStr">
         <is>
           <t>SAS直连与流式加载</t>
@@ -17841,11 +17949,12 @@
       <c r="I54" s="46" t="n">
         <v>0.5</v>
       </c>
-      <c r="J54" s="17" t="n"/>
-      <c r="K54" s="46" t="n">
-        <v>2</v>
-      </c>
-      <c r="L54" s="17" t="n"/>
+      <c r="J54" s="102" t="n"/>
+      <c r="K54" s="46">
+        <f>ROUND(SUM(F54:I54),2)</f>
+        <v/>
+      </c>
+      <c r="L54" s="102" t="n"/>
     </row>
     <row r="55" ht="26" customHeight="1">
       <c r="A55" s="15" t="inlineStr">
@@ -17854,7 +17963,7 @@
         </is>
       </c>
       <c r="B55" s="103" t="n"/>
-      <c r="C55" s="17" t="n"/>
+      <c r="C55" s="103" t="n"/>
       <c r="D55" s="32" t="inlineStr">
         <is>
           <t>前端预览组件</t>
@@ -17873,11 +17982,12 @@
       <c r="I55" s="46" t="n">
         <v>0.25</v>
       </c>
-      <c r="J55" s="17" t="n"/>
-      <c r="K55" s="46" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="L55" s="17" t="n"/>
+      <c r="J55" s="103" t="n"/>
+      <c r="K55" s="46">
+        <f>ROUND(SUM(F55:I55),2)</f>
+        <v/>
+      </c>
+      <c r="L55" s="103" t="n"/>
     </row>
     <row r="56" ht="26" customHeight="1">
       <c r="A56" s="15" t="inlineStr">
@@ -17918,11 +18028,13 @@
       <c r="J56" s="89" t="n">
         <v>0.5</v>
       </c>
-      <c r="K56" s="46" t="n">
-        <v>1</v>
-      </c>
-      <c r="L56" s="89" t="n">
-        <v>5.25</v>
+      <c r="K56" s="46">
+        <f>ROUND(SUM(F56:I56),2)</f>
+        <v/>
+      </c>
+      <c r="L56" s="89">
+        <f>ROUND(SUM(F56:I58)+J56,2)</f>
+        <v/>
       </c>
     </row>
     <row r="57" ht="26" customHeight="1">
@@ -17932,7 +18044,7 @@
         </is>
       </c>
       <c r="B57" s="102" t="n"/>
-      <c r="C57" s="17" t="n"/>
+      <c r="C57" s="102" t="n"/>
       <c r="D57" s="32" t="inlineStr">
         <is>
           <t>操作拦截与落库</t>
@@ -17951,11 +18063,12 @@
       <c r="I57" s="46" t="n">
         <v>0.5</v>
       </c>
-      <c r="J57" s="17" t="n"/>
-      <c r="K57" s="46" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="L57" s="17" t="n"/>
+      <c r="J57" s="102" t="n"/>
+      <c r="K57" s="46">
+        <f>ROUND(SUM(F57:I57),2)</f>
+        <v/>
+      </c>
+      <c r="L57" s="102" t="n"/>
     </row>
     <row r="58" ht="26" customHeight="1">
       <c r="A58" s="15" t="inlineStr">
@@ -17964,7 +18077,7 @@
         </is>
       </c>
       <c r="B58" s="102" t="n"/>
-      <c r="C58" s="17" t="n"/>
+      <c r="C58" s="103" t="n"/>
       <c r="D58" s="32" t="inlineStr">
         <is>
           <t>审计查询界面</t>
@@ -17985,11 +18098,12 @@
       <c r="I58" s="46" t="n">
         <v>0.5</v>
       </c>
-      <c r="J58" s="17" t="n"/>
-      <c r="K58" s="46" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="L58" s="17" t="n"/>
+      <c r="J58" s="103" t="n"/>
+      <c r="K58" s="46">
+        <f>ROUND(SUM(F58:I58),2)</f>
+        <v/>
+      </c>
+      <c r="L58" s="103" t="n"/>
     </row>
     <row r="59" ht="26" customHeight="1">
       <c r="A59" s="15" t="inlineStr">
@@ -18024,11 +18138,13 @@
       <c r="J59" s="89" t="n">
         <v>0.25</v>
       </c>
-      <c r="K59" s="46" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="L59" s="89" t="n">
-        <v>2.25</v>
+      <c r="K59" s="46">
+        <f>ROUND(SUM(F59:I59),2)</f>
+        <v/>
+      </c>
+      <c r="L59" s="89">
+        <f>ROUND(SUM(F59:I60)+J59,2)</f>
+        <v/>
       </c>
     </row>
     <row r="60" ht="26" customHeight="1">
@@ -18038,7 +18154,7 @@
         </is>
       </c>
       <c r="B60" s="102" t="n"/>
-      <c r="C60" s="17" t="n"/>
+      <c r="C60" s="103" t="n"/>
       <c r="D60" s="32" t="inlineStr">
         <is>
           <t>异步批量写入</t>
@@ -18057,11 +18173,12 @@
       <c r="I60" s="46" t="n">
         <v>0.25</v>
       </c>
-      <c r="J60" s="17" t="n"/>
-      <c r="K60" s="46" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="L60" s="17" t="n"/>
+      <c r="J60" s="103" t="n"/>
+      <c r="K60" s="46">
+        <f>ROUND(SUM(F60:I60),2)</f>
+        <v/>
+      </c>
+      <c r="L60" s="103" t="n"/>
     </row>
     <row r="61" ht="26" customHeight="1">
       <c r="A61" s="15" t="inlineStr">
@@ -18096,11 +18213,13 @@
       <c r="J61" s="89" t="n">
         <v>0.25</v>
       </c>
-      <c r="K61" s="46" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="L61" s="89" t="n">
-        <v>2.5</v>
+      <c r="K61" s="46">
+        <f>ROUND(SUM(F61:I61),2)</f>
+        <v/>
+      </c>
+      <c r="L61" s="89">
+        <f>ROUND(SUM(F61:I62)+J61,2)</f>
+        <v/>
       </c>
     </row>
     <row r="62" ht="26" customHeight="1">
@@ -18110,7 +18229,7 @@
         </is>
       </c>
       <c r="B62" s="103" t="n"/>
-      <c r="C62" s="17" t="n"/>
+      <c r="C62" s="103" t="n"/>
       <c r="D62" s="32" t="inlineStr">
         <is>
           <t>大批量导出告警</t>
@@ -18131,11 +18250,12 @@
       <c r="I62" s="46" t="n">
         <v>0.25</v>
       </c>
-      <c r="J62" s="17" t="n"/>
-      <c r="K62" s="46" t="n">
-        <v>1</v>
-      </c>
-      <c r="L62" s="17" t="n"/>
+      <c r="J62" s="103" t="n"/>
+      <c r="K62" s="46">
+        <f>ROUND(SUM(F62:I62),2)</f>
+        <v/>
+      </c>
+      <c r="L62" s="103" t="n"/>
     </row>
     <row r="63" ht="26" customHeight="1">
       <c r="A63" s="15" t="inlineStr">
@@ -18176,11 +18296,13 @@
       <c r="J63" s="92" t="n">
         <v>1</v>
       </c>
-      <c r="K63" s="46" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="L63" s="92" t="n">
-        <v>7.5</v>
+      <c r="K63" s="46">
+        <f>ROUND(SUM(F63:I63),2)</f>
+        <v/>
+      </c>
+      <c r="L63" s="92">
+        <f>ROUND(SUM(F63:I65)+J63,2)</f>
+        <v/>
       </c>
     </row>
     <row r="64" ht="26" customHeight="1">
@@ -18190,7 +18312,7 @@
         </is>
       </c>
       <c r="B64" s="102" t="n"/>
-      <c r="C64" s="17" t="n"/>
+      <c r="C64" s="102" t="n"/>
       <c r="D64" s="32" t="inlineStr">
         <is>
           <t>角色管理界面与API</t>
@@ -18211,11 +18333,12 @@
       <c r="I64" s="46" t="n">
         <v>0.5</v>
       </c>
-      <c r="J64" s="17" t="n"/>
-      <c r="K64" s="46" t="n">
-        <v>3</v>
-      </c>
-      <c r="L64" s="17" t="n"/>
+      <c r="J64" s="102" t="n"/>
+      <c r="K64" s="46">
+        <f>ROUND(SUM(F64:I64),2)</f>
+        <v/>
+      </c>
+      <c r="L64" s="102" t="n"/>
     </row>
     <row r="65" ht="26" customHeight="1">
       <c r="A65" s="15" t="inlineStr">
@@ -18224,7 +18347,7 @@
         </is>
       </c>
       <c r="B65" s="102" t="n"/>
-      <c r="C65" s="17" t="n"/>
+      <c r="C65" s="103" t="n"/>
       <c r="D65" s="32" t="inlineStr">
         <is>
           <t>权限校验与UC授权映射</t>
@@ -18243,11 +18366,12 @@
       <c r="I65" s="46" t="n">
         <v>0.75</v>
       </c>
-      <c r="J65" s="17" t="n"/>
-      <c r="K65" s="46" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="L65" s="17" t="n"/>
+      <c r="J65" s="103" t="n"/>
+      <c r="K65" s="46">
+        <f>ROUND(SUM(F65:I65),2)</f>
+        <v/>
+      </c>
+      <c r="L65" s="103" t="n"/>
     </row>
     <row r="66" ht="26" customHeight="1">
       <c r="A66" s="15" t="inlineStr">
@@ -18286,11 +18410,13 @@
       <c r="J66" s="92" t="n">
         <v>0.5</v>
       </c>
-      <c r="K66" s="46" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="L66" s="92" t="n">
-        <v>4</v>
+      <c r="K66" s="46">
+        <f>ROUND(SUM(F66:I66),2)</f>
+        <v/>
+      </c>
+      <c r="L66" s="92">
+        <f>ROUND(SUM(F66:I67)+J66,2)</f>
+        <v/>
       </c>
     </row>
     <row r="67" ht="26" customHeight="1">
@@ -18300,7 +18426,7 @@
         </is>
       </c>
       <c r="B67" s="102" t="n"/>
-      <c r="C67" s="17" t="n"/>
+      <c r="C67" s="103" t="n"/>
       <c r="D67" s="32" t="inlineStr">
         <is>
           <t>账号与角色绑定</t>
@@ -18321,11 +18447,12 @@
       <c r="I67" s="46" t="n">
         <v>0.25</v>
       </c>
-      <c r="J67" s="17" t="n"/>
-      <c r="K67" s="46" t="n">
-        <v>1</v>
-      </c>
-      <c r="L67" s="17" t="n"/>
+      <c r="J67" s="103" t="n"/>
+      <c r="K67" s="46">
+        <f>ROUND(SUM(F67:I67),2)</f>
+        <v/>
+      </c>
+      <c r="L67" s="103" t="n"/>
     </row>
     <row r="68" ht="26" customHeight="1">
       <c r="A68" s="15" t="inlineStr">
@@ -18364,11 +18491,13 @@
       <c r="J68" s="92" t="n">
         <v>0.5</v>
       </c>
-      <c r="K68" s="46" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="L68" s="92" t="n">
-        <v>5.75</v>
+      <c r="K68" s="46">
+        <f>ROUND(SUM(F68:I68),2)</f>
+        <v/>
+      </c>
+      <c r="L68" s="92">
+        <f>ROUND(SUM(F68:I70)+J68,2)</f>
+        <v/>
       </c>
     </row>
     <row r="69" ht="26" customHeight="1">
@@ -18378,7 +18507,7 @@
         </is>
       </c>
       <c r="B69" s="102" t="n"/>
-      <c r="C69" s="17" t="n"/>
+      <c r="C69" s="102" t="n"/>
       <c r="D69" s="32" t="inlineStr">
         <is>
           <t>SSO登录链路【中间件】</t>
@@ -18399,11 +18528,12 @@
       <c r="I69" s="46" t="n">
         <v>0.75</v>
       </c>
-      <c r="J69" s="17" t="n"/>
-      <c r="K69" s="46" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="L69" s="17" t="n"/>
+      <c r="J69" s="102" t="n"/>
+      <c r="K69" s="46">
+        <f>ROUND(SUM(F69:I69),2)</f>
+        <v/>
+      </c>
+      <c r="L69" s="102" t="n"/>
     </row>
     <row r="70" ht="26" customHeight="1">
       <c r="A70" s="15" t="inlineStr">
@@ -18412,7 +18542,7 @@
         </is>
       </c>
       <c r="B70" s="102" t="n"/>
-      <c r="C70" s="17" t="n"/>
+      <c r="C70" s="103" t="n"/>
       <c r="D70" s="32" t="inlineStr">
         <is>
           <t>认证异常场景处理</t>
@@ -18431,11 +18561,12 @@
       <c r="I70" s="46" t="n">
         <v>0.5</v>
       </c>
-      <c r="J70" s="17" t="n"/>
-      <c r="K70" s="46" t="n">
-        <v>1</v>
-      </c>
-      <c r="L70" s="17" t="n"/>
+      <c r="J70" s="103" t="n"/>
+      <c r="K70" s="46">
+        <f>ROUND(SUM(F70:I70),2)</f>
+        <v/>
+      </c>
+      <c r="L70" s="103" t="n"/>
     </row>
     <row r="71" ht="26" customHeight="1">
       <c r="A71" s="15" t="inlineStr">
@@ -18472,11 +18603,13 @@
       <c r="J71" s="92" t="n">
         <v>0.25</v>
       </c>
-      <c r="K71" s="46" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="L71" s="92" t="n">
-        <v>3</v>
+      <c r="K71" s="46">
+        <f>ROUND(SUM(F71:I71),2)</f>
+        <v/>
+      </c>
+      <c r="L71" s="92">
+        <f>ROUND(SUM(F71:I72)+J71,2)</f>
+        <v/>
       </c>
     </row>
     <row r="72" ht="26" customHeight="1">
@@ -18486,7 +18619,7 @@
         </is>
       </c>
       <c r="B72" s="102" t="n"/>
-      <c r="C72" s="17" t="n"/>
+      <c r="C72" s="103" t="n"/>
       <c r="D72" s="32" t="inlineStr">
         <is>
           <t>首登自动关联与角色赋予</t>
@@ -18507,11 +18640,12 @@
       <c r="I72" s="46" t="n">
         <v>0.5</v>
       </c>
-      <c r="J72" s="17" t="n"/>
-      <c r="K72" s="46" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="L72" s="17" t="n"/>
+      <c r="J72" s="103" t="n"/>
+      <c r="K72" s="46">
+        <f>ROUND(SUM(F72:I72),2)</f>
+        <v/>
+      </c>
+      <c r="L72" s="103" t="n"/>
     </row>
     <row r="73" ht="26" customHeight="1">
       <c r="A73" s="15" t="inlineStr">
@@ -18550,11 +18684,13 @@
       <c r="J73" s="92" t="n">
         <v>0.25</v>
       </c>
-      <c r="K73" s="46" t="n">
-        <v>2</v>
-      </c>
-      <c r="L73" s="92" t="n">
-        <v>3.5</v>
+      <c r="K73" s="46">
+        <f>ROUND(SUM(F73:I73),2)</f>
+        <v/>
+      </c>
+      <c r="L73" s="92">
+        <f>ROUND(SUM(F73:I74)+J73,2)</f>
+        <v/>
       </c>
     </row>
     <row r="74" ht="26" customHeight="1">
@@ -18564,7 +18700,7 @@
         </is>
       </c>
       <c r="B74" s="103" t="n"/>
-      <c r="C74" s="17" t="n"/>
+      <c r="C74" s="103" t="n"/>
       <c r="D74" s="32" t="inlineStr">
         <is>
           <t>异常访问控制</t>
@@ -18583,11 +18719,12 @@
       <c r="I74" s="46" t="n">
         <v>0.5</v>
       </c>
-      <c r="J74" s="17" t="n"/>
-      <c r="K74" s="46" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="L74" s="17" t="n"/>
+      <c r="J74" s="103" t="n"/>
+      <c r="K74" s="46">
+        <f>ROUND(SUM(F74:I74),2)</f>
+        <v/>
+      </c>
+      <c r="L74" s="103" t="n"/>
     </row>
     <row r="75" ht="26" customHeight="1">
       <c r="A75" s="15" t="inlineStr">
@@ -18628,11 +18765,13 @@
       <c r="J75" s="86" t="n">
         <v>0.5</v>
       </c>
-      <c r="K75" s="46" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="L75" s="86" t="n">
-        <v>10.75</v>
+      <c r="K75" s="46">
+        <f>ROUND(SUM(F75:I75),2)</f>
+        <v/>
+      </c>
+      <c r="L75" s="86">
+        <f>ROUND(SUM(F75:I79)+J75,2)</f>
+        <v/>
       </c>
     </row>
     <row r="76" ht="26" customHeight="1">
@@ -18642,7 +18781,7 @@
         </is>
       </c>
       <c r="B76" s="102" t="n"/>
-      <c r="C76" s="17" t="n"/>
+      <c r="C76" s="102" t="n"/>
       <c r="D76" s="32" t="inlineStr">
         <is>
           <t>前端工程初始化</t>
@@ -18661,11 +18800,12 @@
       <c r="I76" s="46" t="n">
         <v>0.25</v>
       </c>
-      <c r="J76" s="17" t="n"/>
-      <c r="K76" s="46" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="L76" s="17" t="n"/>
+      <c r="J76" s="102" t="n"/>
+      <c r="K76" s="46">
+        <f>ROUND(SUM(F76:I76),2)</f>
+        <v/>
+      </c>
+      <c r="L76" s="102" t="n"/>
     </row>
     <row r="77" ht="26" customHeight="1">
       <c r="A77" s="15" t="inlineStr">
@@ -18674,7 +18814,7 @@
         </is>
       </c>
       <c r="B77" s="102" t="n"/>
-      <c r="C77" s="17" t="n"/>
+      <c r="C77" s="102" t="n"/>
       <c r="D77" s="32" t="inlineStr">
         <is>
           <t>后端工程初始化</t>
@@ -18693,11 +18833,12 @@
       <c r="I77" s="46" t="n">
         <v>0.25</v>
       </c>
-      <c r="J77" s="17" t="n"/>
-      <c r="K77" s="46" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="L77" s="17" t="n"/>
+      <c r="J77" s="102" t="n"/>
+      <c r="K77" s="46">
+        <f>ROUND(SUM(F77:I77),2)</f>
+        <v/>
+      </c>
+      <c r="L77" s="102" t="n"/>
     </row>
     <row r="78" ht="26" customHeight="1">
       <c r="A78" s="15" t="inlineStr">
@@ -18706,7 +18847,7 @@
         </is>
       </c>
       <c r="B78" s="102" t="n"/>
-      <c r="C78" s="17" t="n"/>
+      <c r="C78" s="102" t="n"/>
       <c r="D78" s="32" t="inlineStr">
         <is>
           <t>AI开发工具链与编码规范</t>
@@ -18725,11 +18866,12 @@
         <v>0.25</v>
       </c>
       <c r="I78" s="46" t="n"/>
-      <c r="J78" s="17" t="n"/>
-      <c r="K78" s="46" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="L78" s="17" t="n"/>
+      <c r="J78" s="102" t="n"/>
+      <c r="K78" s="46">
+        <f>ROUND(SUM(F78:I78),2)</f>
+        <v/>
+      </c>
+      <c r="L78" s="102" t="n"/>
     </row>
     <row r="79" ht="26" customHeight="1">
       <c r="A79" s="15" t="inlineStr">
@@ -18738,7 +18880,7 @@
         </is>
       </c>
       <c r="B79" s="102" t="n"/>
-      <c r="C79" s="17" t="n"/>
+      <c r="C79" s="103" t="n"/>
       <c r="D79" s="32" t="inlineStr">
         <is>
           <t>四道安全门禁CI/CD</t>
@@ -18759,11 +18901,12 @@
       <c r="I79" s="46" t="n">
         <v>0.5</v>
       </c>
-      <c r="J79" s="17" t="n"/>
-      <c r="K79" s="46" t="n">
-        <v>4</v>
-      </c>
-      <c r="L79" s="17" t="n"/>
+      <c r="J79" s="103" t="n"/>
+      <c r="K79" s="46">
+        <f>ROUND(SUM(F79:I79),2)</f>
+        <v/>
+      </c>
+      <c r="L79" s="103" t="n"/>
     </row>
     <row r="80" ht="26" customHeight="1">
       <c r="A80" s="15" t="inlineStr">
@@ -18796,11 +18939,13 @@
       <c r="J80" s="86" t="n">
         <v>0.25</v>
       </c>
-      <c r="K80" s="46" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="L80" s="86" t="n">
-        <v>8.75</v>
+      <c r="K80" s="46">
+        <f>ROUND(SUM(F80:I80),2)</f>
+        <v/>
+      </c>
+      <c r="L80" s="86">
+        <f>ROUND(SUM(F80:I84)+J80,2)</f>
+        <v/>
       </c>
     </row>
     <row r="81" ht="26" customHeight="1">
@@ -18810,7 +18955,7 @@
         </is>
       </c>
       <c r="B81" s="102" t="n"/>
-      <c r="C81" s="17" t="n"/>
+      <c r="C81" s="102" t="n"/>
       <c r="D81" s="32" t="inlineStr">
         <is>
           <t>后端SonarLint规约</t>
@@ -18827,11 +18972,12 @@
         <v>1.5</v>
       </c>
       <c r="I81" s="46" t="n"/>
-      <c r="J81" s="17" t="n"/>
-      <c r="K81" s="46" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="L81" s="17" t="n"/>
+      <c r="J81" s="102" t="n"/>
+      <c r="K81" s="46">
+        <f>ROUND(SUM(F81:I81),2)</f>
+        <v/>
+      </c>
+      <c r="L81" s="102" t="n"/>
     </row>
     <row r="82" ht="26" customHeight="1">
       <c r="A82" s="15" t="inlineStr">
@@ -18840,7 +18986,7 @@
         </is>
       </c>
       <c r="B82" s="102" t="n"/>
-      <c r="C82" s="17" t="n"/>
+      <c r="C82" s="102" t="n"/>
       <c r="D82" s="32" t="inlineStr">
         <is>
           <t>SAST安全告警修复</t>
@@ -18861,11 +19007,12 @@
       <c r="I82" s="46" t="n">
         <v>0.25</v>
       </c>
-      <c r="J82" s="17" t="n"/>
-      <c r="K82" s="46" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="L82" s="17" t="n"/>
+      <c r="J82" s="102" t="n"/>
+      <c r="K82" s="46">
+        <f>ROUND(SUM(F82:I82),2)</f>
+        <v/>
+      </c>
+      <c r="L82" s="102" t="n"/>
     </row>
     <row r="83" ht="26" customHeight="1">
       <c r="A83" s="15" t="inlineStr">
@@ -18874,7 +19021,7 @@
         </is>
       </c>
       <c r="B83" s="102" t="n"/>
-      <c r="C83" s="17" t="n"/>
+      <c r="C83" s="102" t="n"/>
       <c r="D83" s="32" t="inlineStr">
         <is>
           <t>依赖漏洞治理（SCA）</t>
@@ -18893,11 +19040,12 @@
         <v>0.5</v>
       </c>
       <c r="I83" s="46" t="n"/>
-      <c r="J83" s="17" t="n"/>
-      <c r="K83" s="46" t="n">
-        <v>1</v>
-      </c>
-      <c r="L83" s="17" t="n"/>
+      <c r="J83" s="102" t="n"/>
+      <c r="K83" s="46">
+        <f>ROUND(SUM(F83:I83),2)</f>
+        <v/>
+      </c>
+      <c r="L83" s="102" t="n"/>
     </row>
     <row r="84" ht="26" customHeight="1">
       <c r="A84" s="15" t="inlineStr">
@@ -18906,7 +19054,7 @@
         </is>
       </c>
       <c r="B84" s="102" t="n"/>
-      <c r="C84" s="17" t="n"/>
+      <c r="C84" s="103" t="n"/>
       <c r="D84" s="32" t="inlineStr">
         <is>
           <t>技术债偿还与外部评审落实</t>
@@ -18927,11 +19075,12 @@
       <c r="I84" s="46" t="n">
         <v>0.25</v>
       </c>
-      <c r="J84" s="17" t="n"/>
-      <c r="K84" s="46" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="L84" s="17" t="n"/>
+      <c r="J84" s="103" t="n"/>
+      <c r="K84" s="46">
+        <f>ROUND(SUM(F84:I84),2)</f>
+        <v/>
+      </c>
+      <c r="L84" s="103" t="n"/>
     </row>
     <row r="85" ht="26" customHeight="1">
       <c r="A85" s="15" t="inlineStr">
@@ -18964,11 +19113,13 @@
         <v>0.5</v>
       </c>
       <c r="J85" s="86" t="n"/>
-      <c r="K85" s="46" t="n">
-        <v>2</v>
-      </c>
-      <c r="L85" s="86" t="n">
-        <v>10</v>
+      <c r="K85" s="46">
+        <f>ROUND(SUM(F85:I85),2)</f>
+        <v/>
+      </c>
+      <c r="L85" s="86">
+        <f>ROUND(SUM(F85:I89)+J85,2)</f>
+        <v/>
       </c>
     </row>
     <row r="86" ht="26" customHeight="1">
@@ -18978,7 +19129,7 @@
         </is>
       </c>
       <c r="B86" s="102" t="n"/>
-      <c r="C86" s="17" t="n"/>
+      <c r="C86" s="102" t="n"/>
       <c r="D86" s="32" t="inlineStr">
         <is>
           <t>查询与数据性能</t>
@@ -18997,11 +19148,12 @@
       <c r="I86" s="46" t="n">
         <v>0.5</v>
       </c>
-      <c r="J86" s="17" t="n"/>
-      <c r="K86" s="46" t="n">
-        <v>2</v>
-      </c>
-      <c r="L86" s="17" t="n"/>
+      <c r="J86" s="102" t="n"/>
+      <c r="K86" s="46">
+        <f>ROUND(SUM(F86:I86),2)</f>
+        <v/>
+      </c>
+      <c r="L86" s="102" t="n"/>
     </row>
     <row r="87" ht="26" customHeight="1">
       <c r="A87" s="15" t="inlineStr">
@@ -19010,7 +19162,7 @@
         </is>
       </c>
       <c r="B87" s="102" t="n"/>
-      <c r="C87" s="17" t="n"/>
+      <c r="C87" s="102" t="n"/>
       <c r="D87" s="32" t="inlineStr">
         <is>
           <t>统一鉴权与数据掩码中间件</t>
@@ -19033,11 +19185,12 @@
       <c r="I87" s="46" t="n">
         <v>0.75</v>
       </c>
-      <c r="J87" s="17" t="n"/>
-      <c r="K87" s="46" t="n">
-        <v>3</v>
-      </c>
-      <c r="L87" s="17" t="n"/>
+      <c r="J87" s="102" t="n"/>
+      <c r="K87" s="46">
+        <f>ROUND(SUM(F87:I87),2)</f>
+        <v/>
+      </c>
+      <c r="L87" s="102" t="n"/>
     </row>
     <row r="88" ht="26" customHeight="1">
       <c r="A88" s="15" t="inlineStr">
@@ -19046,7 +19199,7 @@
         </is>
       </c>
       <c r="B88" s="102" t="n"/>
-      <c r="C88" s="17" t="n"/>
+      <c r="C88" s="102" t="n"/>
       <c r="D88" s="32" t="inlineStr">
         <is>
           <t>可观测性（日志/监控/告警）【原生】</t>
@@ -19067,11 +19220,12 @@
       <c r="I88" s="46" t="n">
         <v>0.25</v>
       </c>
-      <c r="J88" s="17" t="n"/>
-      <c r="K88" s="46" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="L88" s="17" t="n"/>
+      <c r="J88" s="102" t="n"/>
+      <c r="K88" s="46">
+        <f>ROUND(SUM(F88:I88),2)</f>
+        <v/>
+      </c>
+      <c r="L88" s="102" t="n"/>
     </row>
     <row r="89" ht="26" customHeight="1">
       <c r="A89" s="15" t="inlineStr">
@@ -19080,7 +19234,7 @@
         </is>
       </c>
       <c r="B89" s="102" t="n"/>
-      <c r="C89" s="17" t="n"/>
+      <c r="C89" s="103" t="n"/>
       <c r="D89" s="32" t="inlineStr">
         <is>
           <t>容量与增长验证</t>
@@ -19099,11 +19253,12 @@
       <c r="I89" s="46" t="n">
         <v>0.5</v>
       </c>
-      <c r="J89" s="17" t="n"/>
-      <c r="K89" s="46" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="L89" s="17" t="n"/>
+      <c r="J89" s="103" t="n"/>
+      <c r="K89" s="46">
+        <f>ROUND(SUM(F89:I89),2)</f>
+        <v/>
+      </c>
+      <c r="L89" s="103" t="n"/>
     </row>
     <row r="90" ht="26" customHeight="1">
       <c r="A90" s="15" t="inlineStr">
@@ -19138,11 +19293,13 @@
       <c r="J90" s="86" t="n">
         <v>0.5</v>
       </c>
-      <c r="K90" s="46" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="L90" s="86" t="n">
-        <v>5.5</v>
+      <c r="K90" s="46">
+        <f>ROUND(SUM(F90:I90),2)</f>
+        <v/>
+      </c>
+      <c r="L90" s="86">
+        <f>ROUND(SUM(F90:I92)+J90,2)</f>
+        <v/>
       </c>
     </row>
     <row r="91" ht="26" customHeight="1">
@@ -19152,7 +19309,7 @@
         </is>
       </c>
       <c r="B91" s="102" t="n"/>
-      <c r="C91" s="17" t="n"/>
+      <c r="C91" s="102" t="n"/>
       <c r="D91" s="32" t="inlineStr">
         <is>
           <t>部署预演与回退预案</t>
@@ -19173,11 +19330,12 @@
       <c r="I91" s="46" t="n">
         <v>0.25</v>
       </c>
-      <c r="J91" s="17" t="n"/>
-      <c r="K91" s="46" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="L91" s="17" t="n"/>
+      <c r="J91" s="102" t="n"/>
+      <c r="K91" s="46">
+        <f>ROUND(SUM(F91:I91),2)</f>
+        <v/>
+      </c>
+      <c r="L91" s="102" t="n"/>
     </row>
     <row r="92" ht="26" customHeight="1">
       <c r="A92" s="15" t="inlineStr">
@@ -19186,7 +19344,7 @@
         </is>
       </c>
       <c r="B92" s="102" t="n"/>
-      <c r="C92" s="17" t="n"/>
+      <c r="C92" s="103" t="n"/>
       <c r="D92" s="32" t="inlineStr">
         <is>
           <t>上线值守与运维交接</t>
@@ -19205,11 +19363,12 @@
         <v>1</v>
       </c>
       <c r="I92" s="46" t="n"/>
-      <c r="J92" s="17" t="n"/>
-      <c r="K92" s="46" t="n">
-        <v>2</v>
-      </c>
-      <c r="L92" s="17" t="n"/>
+      <c r="J92" s="103" t="n"/>
+      <c r="K92" s="46">
+        <f>ROUND(SUM(F92:I92),2)</f>
+        <v/>
+      </c>
+      <c r="L92" s="103" t="n"/>
     </row>
     <row r="93" ht="26" customHeight="1">
       <c r="A93" s="15" t="inlineStr">
@@ -19242,11 +19401,13 @@
       <c r="J93" s="86" t="n">
         <v>0.5</v>
       </c>
-      <c r="K93" s="46" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="L93" s="86" t="n">
-        <v>5</v>
+      <c r="K93" s="46">
+        <f>ROUND(SUM(F93:I93),2)</f>
+        <v/>
+      </c>
+      <c r="L93" s="86">
+        <f>ROUND(SUM(F93:I95)+J93,2)</f>
+        <v/>
       </c>
     </row>
     <row r="94" ht="26" customHeight="1">
@@ -19256,7 +19417,7 @@
         </is>
       </c>
       <c r="B94" s="102" t="n"/>
-      <c r="C94" s="17" t="n"/>
+      <c r="C94" s="102" t="n"/>
       <c r="D94" s="32" t="inlineStr">
         <is>
           <t>应用接口与模块设计文档</t>
@@ -19273,11 +19434,12 @@
       </c>
       <c r="H94" s="46" t="n"/>
       <c r="I94" s="46" t="n"/>
-      <c r="J94" s="17" t="n"/>
-      <c r="K94" s="46" t="n">
-        <v>1</v>
-      </c>
-      <c r="L94" s="17" t="n"/>
+      <c r="J94" s="102" t="n"/>
+      <c r="K94" s="46">
+        <f>ROUND(SUM(F94:I94),2)</f>
+        <v/>
+      </c>
+      <c r="L94" s="102" t="n"/>
     </row>
     <row r="95" ht="26" customHeight="1">
       <c r="A95" s="15" t="inlineStr">
@@ -19286,7 +19448,7 @@
         </is>
       </c>
       <c r="B95" s="103" t="n"/>
-      <c r="C95" s="17" t="n"/>
+      <c r="C95" s="103" t="n"/>
       <c r="D95" s="32" t="inlineStr">
         <is>
           <t>数据设计与ETL/作业文档</t>
@@ -19303,11 +19465,12 @@
         <v>2</v>
       </c>
       <c r="I95" s="46" t="n"/>
-      <c r="J95" s="17" t="n"/>
-      <c r="K95" s="46" t="n">
-        <v>2</v>
-      </c>
-      <c r="L95" s="17" t="n"/>
+      <c r="J95" s="103" t="n"/>
+      <c r="K95" s="46">
+        <f>ROUND(SUM(F95:I95),2)</f>
+        <v/>
+      </c>
+      <c r="L95" s="103" t="n"/>
     </row>
     <row r="96">
       <c r="A96" s="8" t="inlineStr"/>
@@ -19327,23 +19490,29 @@
           <t>独立直估（另含少量需求/PM等工作未列入本表）</t>
         </is>
       </c>
-      <c r="F96" s="44" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="G96" s="44" t="n">
-        <v>60.75</v>
-      </c>
-      <c r="H96" s="44" t="n">
-        <v>69.25</v>
-      </c>
-      <c r="I96" s="44" t="n">
-        <v>38.75</v>
-      </c>
-      <c r="J96" s="44" t="n">
-        <v>13.75</v>
-      </c>
-      <c r="K96" s="44" t="n">
-        <v>195</v>
+      <c r="F96" s="44">
+        <f>ROUND(SUM(F3:F95),2)</f>
+        <v/>
+      </c>
+      <c r="G96" s="44">
+        <f>ROUND(SUM(G3:G95),2)</f>
+        <v/>
+      </c>
+      <c r="H96" s="44">
+        <f>ROUND(SUM(H3:H95),2)</f>
+        <v/>
+      </c>
+      <c r="I96" s="44">
+        <f>ROUND(SUM(I3:I95),2)</f>
+        <v/>
+      </c>
+      <c r="J96" s="44">
+        <f>ROUND(SUM(J3:J95),2)</f>
+        <v/>
+      </c>
+      <c r="K96" s="44">
+        <f>ROUND(SUM(F96:J96),2)</f>
+        <v/>
       </c>
       <c r="L96" s="8" t="inlineStr"/>
     </row>
@@ -19397,8 +19566,8 @@
     <mergeCell ref="L44:L46"/>
     <mergeCell ref="C23:C25"/>
     <mergeCell ref="C32:C34"/>
+    <mergeCell ref="J59:J60"/>
     <mergeCell ref="C38:C40"/>
-    <mergeCell ref="J59:J60"/>
     <mergeCell ref="B63:B74"/>
     <mergeCell ref="C71:C72"/>
     <mergeCell ref="B75:B95"/>
@@ -19860,18 +20029,41 @@
           <t>Mark</t>
         </is>
       </c>
-      <c r="B3" s="46" t="n">
-        <v>15</v>
-      </c>
-      <c r="C3" s="46" t="n"/>
-      <c r="D3" s="46" t="n"/>
-      <c r="E3" s="46" t="n"/>
-      <c r="F3" s="46" t="n"/>
-      <c r="G3" s="46" t="n"/>
-      <c r="H3" s="46" t="n"/>
-      <c r="I3" s="46" t="n"/>
-      <c r="J3" s="69" t="n">
-        <v>15</v>
+      <c r="B3" s="46">
+        <f>IF(ROUND(SUMPRODUCT(('WBS分解'!$C$4:$C$164=3)*('WBS分解'!$E$4:$E$164="Mark")*(LEFT('WBS分解'!$A$4:$A$164,1)="1")*'WBS分解'!$I$4:$I$164),2)=0,"",ROUND(SUMPRODUCT(('WBS分解'!$C$4:$C$164=3)*('WBS分解'!$E$4:$E$164="Mark")*(LEFT('WBS分解'!$A$4:$A$164,1)="1")*'WBS分解'!$I$4:$I$164),2))</f>
+        <v/>
+      </c>
+      <c r="C3" s="46">
+        <f>IF(ROUND(SUMPRODUCT(('WBS分解'!$C$4:$C$164=3)*('WBS分解'!$E$4:$E$164="Mark")*(LEFT('WBS分解'!$A$4:$A$164,1)="2")*'WBS分解'!$I$4:$I$164),2)=0,"",ROUND(SUMPRODUCT(('WBS分解'!$C$4:$C$164=3)*('WBS分解'!$E$4:$E$164="Mark")*(LEFT('WBS分解'!$A$4:$A$164,1)="2")*'WBS分解'!$I$4:$I$164),2))</f>
+        <v/>
+      </c>
+      <c r="D3" s="46">
+        <f>IF(ROUND(SUMPRODUCT(('WBS分解'!$C$4:$C$164=3)*('WBS分解'!$E$4:$E$164="Mark")*(LEFT('WBS分解'!$A$4:$A$164,1)="3")*'WBS分解'!$I$4:$I$164),2)=0,"",ROUND(SUMPRODUCT(('WBS分解'!$C$4:$C$164=3)*('WBS分解'!$E$4:$E$164="Mark")*(LEFT('WBS分解'!$A$4:$A$164,1)="3")*'WBS分解'!$I$4:$I$164),2))</f>
+        <v/>
+      </c>
+      <c r="E3" s="46">
+        <f>IF(ROUND(SUMPRODUCT(('WBS分解'!$C$4:$C$164=3)*('WBS分解'!$E$4:$E$164="Mark")*(LEFT('WBS分解'!$A$4:$A$164,1)="4")*'WBS分解'!$I$4:$I$164),2)=0,"",ROUND(SUMPRODUCT(('WBS分解'!$C$4:$C$164=3)*('WBS分解'!$E$4:$E$164="Mark")*(LEFT('WBS分解'!$A$4:$A$164,1)="4")*'WBS分解'!$I$4:$I$164),2))</f>
+        <v/>
+      </c>
+      <c r="F3" s="46">
+        <f>IF(ROUND(SUMPRODUCT(('WBS分解'!$C$4:$C$164=3)*('WBS分解'!$E$4:$E$164="Mark")*(LEFT('WBS分解'!$A$4:$A$164,1)="5")*'WBS分解'!$I$4:$I$164),2)=0,"",ROUND(SUMPRODUCT(('WBS分解'!$C$4:$C$164=3)*('WBS分解'!$E$4:$E$164="Mark")*(LEFT('WBS分解'!$A$4:$A$164,1)="5")*'WBS分解'!$I$4:$I$164),2))</f>
+        <v/>
+      </c>
+      <c r="G3" s="46">
+        <f>IF(ROUND(SUMPRODUCT(('WBS分解'!$C$4:$C$164=3)*('WBS分解'!$E$4:$E$164="Mark")*(LEFT('WBS分解'!$A$4:$A$164,1)="6")*'WBS分解'!$I$4:$I$164),2)=0,"",ROUND(SUMPRODUCT(('WBS分解'!$C$4:$C$164=3)*('WBS分解'!$E$4:$E$164="Mark")*(LEFT('WBS分解'!$A$4:$A$164,1)="6")*'WBS分解'!$I$4:$I$164),2))</f>
+        <v/>
+      </c>
+      <c r="H3" s="46">
+        <f>IF(ROUND(SUMPRODUCT(('WBS分解'!$C$4:$C$164=3)*('WBS分解'!$E$4:$E$164="Mark")*(LEFT('WBS分解'!$A$4:$A$164,1)="7")*'WBS分解'!$I$4:$I$164),2)=0,"",ROUND(SUMPRODUCT(('WBS分解'!$C$4:$C$164=3)*('WBS分解'!$E$4:$E$164="Mark")*(LEFT('WBS分解'!$A$4:$A$164,1)="7")*'WBS分解'!$I$4:$I$164),2))</f>
+        <v/>
+      </c>
+      <c r="I3" s="46">
+        <f>IF(ROUND(SUMPRODUCT(('WBS分解'!$C$4:$C$164=3)*('WBS分解'!$E$4:$E$164="Mark")*(LEFT('WBS分解'!$A$4:$A$164,1)="8")*'WBS分解'!$I$4:$I$164),2)=0,"",ROUND(SUMPRODUCT(('WBS分解'!$C$4:$C$164=3)*('WBS分解'!$E$4:$E$164="Mark")*(LEFT('WBS分解'!$A$4:$A$164,1)="8")*'WBS分解'!$I$4:$I$164),2))</f>
+        <v/>
+      </c>
+      <c r="J3" s="69">
+        <f>ROUND(SUM(B3:I3),2)</f>
+        <v/>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -19885,30 +20077,41 @@
           <t>Mandy</t>
         </is>
       </c>
-      <c r="B4" s="46" t="n">
-        <v>1</v>
-      </c>
-      <c r="C4" s="46" t="n">
-        <v>13</v>
-      </c>
-      <c r="D4" s="46" t="n"/>
-      <c r="E4" s="46" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="F4" s="46" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="G4" s="46" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="H4" s="46" t="n">
-        <v>5</v>
-      </c>
-      <c r="I4" s="46" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="J4" s="69" t="n">
-        <v>50</v>
+      <c r="B4" s="46">
+        <f>IF(ROUND(SUMPRODUCT(('WBS分解'!$C$4:$C$164=3)*('WBS分解'!$E$4:$E$164="Mandy")*(LEFT('WBS分解'!$A$4:$A$164,1)="1")*'WBS分解'!$I$4:$I$164),2)=0,"",ROUND(SUMPRODUCT(('WBS分解'!$C$4:$C$164=3)*('WBS分解'!$E$4:$E$164="Mandy")*(LEFT('WBS分解'!$A$4:$A$164,1)="1")*'WBS分解'!$I$4:$I$164),2))</f>
+        <v/>
+      </c>
+      <c r="C4" s="46">
+        <f>IF(ROUND(SUMPRODUCT(('WBS分解'!$C$4:$C$164=3)*('WBS分解'!$E$4:$E$164="Mandy")*(LEFT('WBS分解'!$A$4:$A$164,1)="2")*'WBS分解'!$I$4:$I$164),2)=0,"",ROUND(SUMPRODUCT(('WBS分解'!$C$4:$C$164=3)*('WBS分解'!$E$4:$E$164="Mandy")*(LEFT('WBS分解'!$A$4:$A$164,1)="2")*'WBS分解'!$I$4:$I$164),2))</f>
+        <v/>
+      </c>
+      <c r="D4" s="46">
+        <f>IF(ROUND(SUMPRODUCT(('WBS分解'!$C$4:$C$164=3)*('WBS分解'!$E$4:$E$164="Mandy")*(LEFT('WBS分解'!$A$4:$A$164,1)="3")*'WBS分解'!$I$4:$I$164),2)=0,"",ROUND(SUMPRODUCT(('WBS分解'!$C$4:$C$164=3)*('WBS分解'!$E$4:$E$164="Mandy")*(LEFT('WBS分解'!$A$4:$A$164,1)="3")*'WBS分解'!$I$4:$I$164),2))</f>
+        <v/>
+      </c>
+      <c r="E4" s="46">
+        <f>IF(ROUND(SUMPRODUCT(('WBS分解'!$C$4:$C$164=3)*('WBS分解'!$E$4:$E$164="Mandy")*(LEFT('WBS分解'!$A$4:$A$164,1)="4")*'WBS分解'!$I$4:$I$164),2)=0,"",ROUND(SUMPRODUCT(('WBS分解'!$C$4:$C$164=3)*('WBS分解'!$E$4:$E$164="Mandy")*(LEFT('WBS分解'!$A$4:$A$164,1)="4")*'WBS分解'!$I$4:$I$164),2))</f>
+        <v/>
+      </c>
+      <c r="F4" s="46">
+        <f>IF(ROUND(SUMPRODUCT(('WBS分解'!$C$4:$C$164=3)*('WBS分解'!$E$4:$E$164="Mandy")*(LEFT('WBS分解'!$A$4:$A$164,1)="5")*'WBS分解'!$I$4:$I$164),2)=0,"",ROUND(SUMPRODUCT(('WBS分解'!$C$4:$C$164=3)*('WBS分解'!$E$4:$E$164="Mandy")*(LEFT('WBS分解'!$A$4:$A$164,1)="5")*'WBS分解'!$I$4:$I$164),2))</f>
+        <v/>
+      </c>
+      <c r="G4" s="46">
+        <f>IF(ROUND(SUMPRODUCT(('WBS分解'!$C$4:$C$164=3)*('WBS分解'!$E$4:$E$164="Mandy")*(LEFT('WBS分解'!$A$4:$A$164,1)="6")*'WBS分解'!$I$4:$I$164),2)=0,"",ROUND(SUMPRODUCT(('WBS分解'!$C$4:$C$164=3)*('WBS分解'!$E$4:$E$164="Mandy")*(LEFT('WBS分解'!$A$4:$A$164,1)="6")*'WBS分解'!$I$4:$I$164),2))</f>
+        <v/>
+      </c>
+      <c r="H4" s="46">
+        <f>IF(ROUND(SUMPRODUCT(('WBS分解'!$C$4:$C$164=3)*('WBS分解'!$E$4:$E$164="Mandy")*(LEFT('WBS分解'!$A$4:$A$164,1)="7")*'WBS分解'!$I$4:$I$164),2)=0,"",ROUND(SUMPRODUCT(('WBS分解'!$C$4:$C$164=3)*('WBS分解'!$E$4:$E$164="Mandy")*(LEFT('WBS分解'!$A$4:$A$164,1)="7")*'WBS分解'!$I$4:$I$164),2))</f>
+        <v/>
+      </c>
+      <c r="I4" s="46">
+        <f>IF(ROUND(SUMPRODUCT(('WBS分解'!$C$4:$C$164=3)*('WBS分解'!$E$4:$E$164="Mandy")*(LEFT('WBS分解'!$A$4:$A$164,1)="8")*'WBS分解'!$I$4:$I$164),2)=0,"",ROUND(SUMPRODUCT(('WBS分解'!$C$4:$C$164=3)*('WBS分解'!$E$4:$E$164="Mandy")*(LEFT('WBS分解'!$A$4:$A$164,1)="8")*'WBS分解'!$I$4:$I$164),2))</f>
+        <v/>
+      </c>
+      <c r="J4" s="69">
+        <f>ROUND(SUM(B4:I4),2)</f>
+        <v/>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -19922,28 +20125,41 @@
           <t>Wade</t>
         </is>
       </c>
-      <c r="B5" s="46" t="n"/>
-      <c r="C5" s="46" t="n"/>
-      <c r="D5" s="46" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="E5" s="46" t="n">
-        <v>10</v>
-      </c>
-      <c r="F5" s="46" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="G5" s="46" t="n">
-        <v>11</v>
-      </c>
-      <c r="H5" s="46" t="n">
-        <v>6</v>
-      </c>
-      <c r="I5" s="46" t="n">
-        <v>5</v>
-      </c>
-      <c r="J5" s="69" t="n">
-        <v>60</v>
+      <c r="B5" s="46">
+        <f>IF(ROUND(SUMPRODUCT(('WBS分解'!$C$4:$C$164=3)*('WBS分解'!$E$4:$E$164="Wade")*(LEFT('WBS分解'!$A$4:$A$164,1)="1")*'WBS分解'!$I$4:$I$164),2)=0,"",ROUND(SUMPRODUCT(('WBS分解'!$C$4:$C$164=3)*('WBS分解'!$E$4:$E$164="Wade")*(LEFT('WBS分解'!$A$4:$A$164,1)="1")*'WBS分解'!$I$4:$I$164),2))</f>
+        <v/>
+      </c>
+      <c r="C5" s="46">
+        <f>IF(ROUND(SUMPRODUCT(('WBS分解'!$C$4:$C$164=3)*('WBS分解'!$E$4:$E$164="Wade")*(LEFT('WBS分解'!$A$4:$A$164,1)="2")*'WBS分解'!$I$4:$I$164),2)=0,"",ROUND(SUMPRODUCT(('WBS分解'!$C$4:$C$164=3)*('WBS分解'!$E$4:$E$164="Wade")*(LEFT('WBS分解'!$A$4:$A$164,1)="2")*'WBS分解'!$I$4:$I$164),2))</f>
+        <v/>
+      </c>
+      <c r="D5" s="46">
+        <f>IF(ROUND(SUMPRODUCT(('WBS分解'!$C$4:$C$164=3)*('WBS分解'!$E$4:$E$164="Wade")*(LEFT('WBS分解'!$A$4:$A$164,1)="3")*'WBS分解'!$I$4:$I$164),2)=0,"",ROUND(SUMPRODUCT(('WBS分解'!$C$4:$C$164=3)*('WBS分解'!$E$4:$E$164="Wade")*(LEFT('WBS分解'!$A$4:$A$164,1)="3")*'WBS分解'!$I$4:$I$164),2))</f>
+        <v/>
+      </c>
+      <c r="E5" s="46">
+        <f>IF(ROUND(SUMPRODUCT(('WBS分解'!$C$4:$C$164=3)*('WBS分解'!$E$4:$E$164="Wade")*(LEFT('WBS分解'!$A$4:$A$164,1)="4")*'WBS分解'!$I$4:$I$164),2)=0,"",ROUND(SUMPRODUCT(('WBS分解'!$C$4:$C$164=3)*('WBS分解'!$E$4:$E$164="Wade")*(LEFT('WBS分解'!$A$4:$A$164,1)="4")*'WBS分解'!$I$4:$I$164),2))</f>
+        <v/>
+      </c>
+      <c r="F5" s="46">
+        <f>IF(ROUND(SUMPRODUCT(('WBS分解'!$C$4:$C$164=3)*('WBS分解'!$E$4:$E$164="Wade")*(LEFT('WBS分解'!$A$4:$A$164,1)="5")*'WBS分解'!$I$4:$I$164),2)=0,"",ROUND(SUMPRODUCT(('WBS分解'!$C$4:$C$164=3)*('WBS分解'!$E$4:$E$164="Wade")*(LEFT('WBS分解'!$A$4:$A$164,1)="5")*'WBS分解'!$I$4:$I$164),2))</f>
+        <v/>
+      </c>
+      <c r="G5" s="46">
+        <f>IF(ROUND(SUMPRODUCT(('WBS分解'!$C$4:$C$164=3)*('WBS分解'!$E$4:$E$164="Wade")*(LEFT('WBS分解'!$A$4:$A$164,1)="6")*'WBS分解'!$I$4:$I$164),2)=0,"",ROUND(SUMPRODUCT(('WBS分解'!$C$4:$C$164=3)*('WBS分解'!$E$4:$E$164="Wade")*(LEFT('WBS分解'!$A$4:$A$164,1)="6")*'WBS分解'!$I$4:$I$164),2))</f>
+        <v/>
+      </c>
+      <c r="H5" s="46">
+        <f>IF(ROUND(SUMPRODUCT(('WBS分解'!$C$4:$C$164=3)*('WBS分解'!$E$4:$E$164="Wade")*(LEFT('WBS分解'!$A$4:$A$164,1)="7")*'WBS分解'!$I$4:$I$164),2)=0,"",ROUND(SUMPRODUCT(('WBS分解'!$C$4:$C$164=3)*('WBS分解'!$E$4:$E$164="Wade")*(LEFT('WBS分解'!$A$4:$A$164,1)="7")*'WBS分解'!$I$4:$I$164),2))</f>
+        <v/>
+      </c>
+      <c r="I5" s="46">
+        <f>IF(ROUND(SUMPRODUCT(('WBS分解'!$C$4:$C$164=3)*('WBS分解'!$E$4:$E$164="Wade")*(LEFT('WBS分解'!$A$4:$A$164,1)="8")*'WBS分解'!$I$4:$I$164),2)=0,"",ROUND(SUMPRODUCT(('WBS分解'!$C$4:$C$164=3)*('WBS分解'!$E$4:$E$164="Wade")*(LEFT('WBS分解'!$A$4:$A$164,1)="8")*'WBS分解'!$I$4:$I$164),2))</f>
+        <v/>
+      </c>
+      <c r="J5" s="69">
+        <f>ROUND(SUM(B5:I5),2)</f>
+        <v/>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -19957,28 +20173,41 @@
           <t>DevB</t>
         </is>
       </c>
-      <c r="B6" s="46" t="n"/>
-      <c r="C6" s="46" t="n"/>
-      <c r="D6" s="46" t="n">
-        <v>14</v>
-      </c>
-      <c r="E6" s="46" t="n">
-        <v>10</v>
-      </c>
-      <c r="F6" s="46" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="G6" s="46" t="n">
-        <v>11</v>
-      </c>
-      <c r="H6" s="46" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="I6" s="46" t="n">
-        <v>5</v>
-      </c>
-      <c r="J6" s="69" t="n">
-        <v>60</v>
+      <c r="B6" s="46">
+        <f>IF(ROUND(SUMPRODUCT(('WBS分解'!$C$4:$C$164=3)*('WBS分解'!$E$4:$E$164="DevB")*(LEFT('WBS分解'!$A$4:$A$164,1)="1")*'WBS分解'!$I$4:$I$164),2)=0,"",ROUND(SUMPRODUCT(('WBS分解'!$C$4:$C$164=3)*('WBS分解'!$E$4:$E$164="DevB")*(LEFT('WBS分解'!$A$4:$A$164,1)="1")*'WBS分解'!$I$4:$I$164),2))</f>
+        <v/>
+      </c>
+      <c r="C6" s="46">
+        <f>IF(ROUND(SUMPRODUCT(('WBS分解'!$C$4:$C$164=3)*('WBS分解'!$E$4:$E$164="DevB")*(LEFT('WBS分解'!$A$4:$A$164,1)="2")*'WBS分解'!$I$4:$I$164),2)=0,"",ROUND(SUMPRODUCT(('WBS分解'!$C$4:$C$164=3)*('WBS分解'!$E$4:$E$164="DevB")*(LEFT('WBS分解'!$A$4:$A$164,1)="2")*'WBS分解'!$I$4:$I$164),2))</f>
+        <v/>
+      </c>
+      <c r="D6" s="46">
+        <f>IF(ROUND(SUMPRODUCT(('WBS分解'!$C$4:$C$164=3)*('WBS分解'!$E$4:$E$164="DevB")*(LEFT('WBS分解'!$A$4:$A$164,1)="3")*'WBS分解'!$I$4:$I$164),2)=0,"",ROUND(SUMPRODUCT(('WBS分解'!$C$4:$C$164=3)*('WBS分解'!$E$4:$E$164="DevB")*(LEFT('WBS分解'!$A$4:$A$164,1)="3")*'WBS分解'!$I$4:$I$164),2))</f>
+        <v/>
+      </c>
+      <c r="E6" s="46">
+        <f>IF(ROUND(SUMPRODUCT(('WBS分解'!$C$4:$C$164=3)*('WBS分解'!$E$4:$E$164="DevB")*(LEFT('WBS分解'!$A$4:$A$164,1)="4")*'WBS分解'!$I$4:$I$164),2)=0,"",ROUND(SUMPRODUCT(('WBS分解'!$C$4:$C$164=3)*('WBS分解'!$E$4:$E$164="DevB")*(LEFT('WBS分解'!$A$4:$A$164,1)="4")*'WBS分解'!$I$4:$I$164),2))</f>
+        <v/>
+      </c>
+      <c r="F6" s="46">
+        <f>IF(ROUND(SUMPRODUCT(('WBS分解'!$C$4:$C$164=3)*('WBS分解'!$E$4:$E$164="DevB")*(LEFT('WBS分解'!$A$4:$A$164,1)="5")*'WBS分解'!$I$4:$I$164),2)=0,"",ROUND(SUMPRODUCT(('WBS分解'!$C$4:$C$164=3)*('WBS分解'!$E$4:$E$164="DevB")*(LEFT('WBS分解'!$A$4:$A$164,1)="5")*'WBS分解'!$I$4:$I$164),2))</f>
+        <v/>
+      </c>
+      <c r="G6" s="46">
+        <f>IF(ROUND(SUMPRODUCT(('WBS分解'!$C$4:$C$164=3)*('WBS分解'!$E$4:$E$164="DevB")*(LEFT('WBS分解'!$A$4:$A$164,1)="6")*'WBS分解'!$I$4:$I$164),2)=0,"",ROUND(SUMPRODUCT(('WBS分解'!$C$4:$C$164=3)*('WBS分解'!$E$4:$E$164="DevB")*(LEFT('WBS分解'!$A$4:$A$164,1)="6")*'WBS分解'!$I$4:$I$164),2))</f>
+        <v/>
+      </c>
+      <c r="H6" s="46">
+        <f>IF(ROUND(SUMPRODUCT(('WBS分解'!$C$4:$C$164=3)*('WBS分解'!$E$4:$E$164="DevB")*(LEFT('WBS分解'!$A$4:$A$164,1)="7")*'WBS分解'!$I$4:$I$164),2)=0,"",ROUND(SUMPRODUCT(('WBS分解'!$C$4:$C$164=3)*('WBS分解'!$E$4:$E$164="DevB")*(LEFT('WBS分解'!$A$4:$A$164,1)="7")*'WBS分解'!$I$4:$I$164),2))</f>
+        <v/>
+      </c>
+      <c r="I6" s="46">
+        <f>IF(ROUND(SUMPRODUCT(('WBS分解'!$C$4:$C$164=3)*('WBS分解'!$E$4:$E$164="DevB")*(LEFT('WBS分解'!$A$4:$A$164,1)="8")*'WBS分解'!$I$4:$I$164),2)=0,"",ROUND(SUMPRODUCT(('WBS分解'!$C$4:$C$164=3)*('WBS分解'!$E$4:$E$164="DevB")*(LEFT('WBS分解'!$A$4:$A$164,1)="8")*'WBS分解'!$I$4:$I$164),2))</f>
+        <v/>
+      </c>
+      <c r="J6" s="69">
+        <f>ROUND(SUM(B6:I6),2)</f>
+        <v/>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -19992,8 +20221,41 @@
           <t>合计</t>
         </is>
       </c>
-      <c r="J7" s="70" t="n">
-        <v>185</v>
+      <c r="B7">
+        <f>ROUND(SUM(B3:B6),2)</f>
+        <v/>
+      </c>
+      <c r="C7">
+        <f>ROUND(SUM(C3:C6),2)</f>
+        <v/>
+      </c>
+      <c r="D7">
+        <f>ROUND(SUM(D3:D6),2)</f>
+        <v/>
+      </c>
+      <c r="E7">
+        <f>ROUND(SUM(E3:E6),2)</f>
+        <v/>
+      </c>
+      <c r="F7">
+        <f>ROUND(SUM(F3:F6),2)</f>
+        <v/>
+      </c>
+      <c r="G7">
+        <f>ROUND(SUM(G3:G6),2)</f>
+        <v/>
+      </c>
+      <c r="H7">
+        <f>ROUND(SUM(H3:H6),2)</f>
+        <v/>
+      </c>
+      <c r="I7">
+        <f>ROUND(SUM(I3:I6),2)</f>
+        <v/>
+      </c>
+      <c r="J7" s="70">
+        <f>ROUND(SUM(J3:J6),2)</f>
+        <v/>
       </c>
       <c r="K7" t="inlineStr">
         <is>

--- a/RIMS项目WBS工作分解_AI Native版.xlsx
+++ b/RIMS项目WBS工作分解_AI Native版.xlsx
@@ -972,6 +972,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3" ht="20" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -1121,7 +1122,7 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>项目启动即前置（3.1.1~3.1.4、3.2.1）：代码仓库/分支策略/开发环境统一/AI工具账号→AI开发规范→四道门禁CI/CD→前后端工程初始化，先立环境与规矩再生成代码</t>
+          <t>项目启动即前置（3.1.1~3.1.4、3.2.1）：代码仓库/分支策略/开发环境统一/AI工具账号→AI开发规范→四道门禁CI/CD（含Azure DevOps连接K8s、测试环境部署流水线）→前后端工程初始化，先立环境与规矩再生成代码。部署节奏：测试环境早期先部署（联调/测试用，流水线自动更新）、生产环境终期部署（12/10，带审批）</t>
         </is>
       </c>
     </row>
@@ -1312,7 +1313,7 @@
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>子任务级直估：模块→功能→子任务三层结构（模块列与功能列均为纵向合并单元格），26项功能×75子任务 + 非功能与工程支撑×21子任务（N1框架初始化与基座/N2 ESLint·SonarLint·SAST代码质量治理/N3性能·鉴权·可观测·容量/N4部署运维），按BA/开发A/开发B/测试/SLC文档独立估人天；底部附与计划口径对照</t>
+          <t>子任务级直估：模块→功能→子任务三层结构（模块列与功能列均为纵向合并单元格），26项功能×75子任务 + 非功能与工程支撑×23子任务（N1框架初始化与基座/N2 ESLint·SonarLint·SAST代码质量治理/N3性能·鉴权·可观测·容量/N4部署运维），按BA/开发A/开发B/测试/SLC文档独立估人天；底部附与计划口径对照</t>
         </is>
       </c>
     </row>
@@ -3344,7 +3345,7 @@
       </c>
       <c r="B33" s="22" t="inlineStr">
         <is>
-          <t>四道安全门禁CI/CD搭建（构建+镜像+SAST/依赖/密钥扫描/越权用例门禁，4人天：流水线搭建/扫描工具接入/越权用例门禁/拦截样例演示）</t>
+          <t>四道安全门禁CI/CD搭建（Azure DevOps：构建+镜像+SAST/依赖/密钥扫描/越权用例门禁，并Service Connection连接K8s、配测试环境部署流水线，4人天：流水线搭建/扫描工具接入/越权用例门禁/拦截样例演示）</t>
         </is>
       </c>
       <c r="C33" s="15" t="n">
@@ -3352,7 +3353,7 @@
       </c>
       <c r="D33" s="17" t="inlineStr">
         <is>
-          <t>CI/CD流水线（4道硬门禁）</t>
+          <t>CI/CD流水线（4道硬门禁+K8s部署）</t>
         </is>
       </c>
       <c r="E33" s="15" t="inlineStr">
@@ -8910,7 +8911,7 @@
       </c>
       <c r="B121" s="22" t="inlineStr">
         <is>
-          <t>上线发布包（Helm生产values+部署Runbook）</t>
+          <t>上线发布包（K8s发布清单+生产部署流水线+部署Runbook）</t>
         </is>
       </c>
       <c r="C121" s="15" t="n">
@@ -10953,7 +10954,7 @@
       </c>
       <c r="B153" s="22" t="inlineStr">
         <is>
-          <t>生产部署执行（服务+前端+UC初始配置）</t>
+          <t>生产部署执行（K8s生产环境：服务+前端+UC初始配置）</t>
         </is>
       </c>
       <c r="C153" s="15" t="n">
@@ -15887,7 +15888,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L104"/>
+  <dimension ref="A1:L106"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -15907,7 +15908,7 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>功能拆解估算（子任务级直估）：模块→功能→子任务三层结构，25项功能×72子任务 + 非功能与工程支撑×21子任务（F04-04异地灾备=Azure Blob原生能力，不计开发）— 独立估算，不锚定排期185人天</t>
+          <t>功能拆解估算（子任务级直估）：模块→功能→子任务三层结构，25项功能×72子任务 + 非功能与工程支撑×23子任务（F04-04异地灾备=Azure Blob原生能力，不计开发）— 独立估算，不锚定排期185人天</t>
         </is>
       </c>
     </row>
@@ -16030,7 +16031,7 @@
         </is>
       </c>
       <c r="B4" s="102" t="n"/>
-      <c r="C4" s="102" t="n"/>
+      <c r="C4" s="17" t="n"/>
       <c r="D4" s="32" t="inlineStr">
         <is>
           <t>源库DB连接配置</t>
@@ -16053,12 +16054,12 @@
       <c r="I4" s="46" t="n">
         <v>0.5</v>
       </c>
-      <c r="J4" s="102" t="n"/>
+      <c r="J4" s="17" t="n"/>
       <c r="K4" s="46">
         <f>ROUND(SUM(F4:I4),2)</f>
         <v/>
       </c>
-      <c r="L4" s="102" t="n"/>
+      <c r="L4" s="17" t="n"/>
     </row>
     <row r="5" ht="26" customHeight="1">
       <c r="A5" s="15" t="inlineStr">
@@ -16067,7 +16068,7 @@
         </is>
       </c>
       <c r="B5" s="102" t="n"/>
-      <c r="C5" s="102" t="n"/>
+      <c r="C5" s="17" t="n"/>
       <c r="D5" s="32" t="inlineStr">
         <is>
           <t>同步表勾选</t>
@@ -16090,12 +16091,12 @@
       <c r="I5" s="46" t="n">
         <v>0.5</v>
       </c>
-      <c r="J5" s="102" t="n"/>
+      <c r="J5" s="17" t="n"/>
       <c r="K5" s="46">
         <f>ROUND(SUM(F5:I5),2)</f>
         <v/>
       </c>
-      <c r="L5" s="102" t="n"/>
+      <c r="L5" s="17" t="n"/>
     </row>
     <row r="6" ht="26" customHeight="1">
       <c r="A6" s="15" t="inlineStr">
@@ -16104,7 +16105,7 @@
         </is>
       </c>
       <c r="B6" s="102" t="n"/>
-      <c r="C6" s="102" t="n"/>
+      <c r="C6" s="17" t="n"/>
       <c r="D6" s="32" t="inlineStr">
         <is>
           <t>保留期限与迁移参数配置</t>
@@ -16127,12 +16128,12 @@
       <c r="I6" s="46" t="n">
         <v>0.25</v>
       </c>
-      <c r="J6" s="102" t="n"/>
+      <c r="J6" s="17" t="n"/>
       <c r="K6" s="46">
         <f>ROUND(SUM(F6:I6),2)</f>
         <v/>
       </c>
-      <c r="L6" s="102" t="n"/>
+      <c r="L6" s="17" t="n"/>
     </row>
     <row r="7" ht="26" customHeight="1">
       <c r="A7" s="15" t="inlineStr">
@@ -16141,7 +16142,7 @@
         </is>
       </c>
       <c r="B7" s="102" t="n"/>
-      <c r="C7" s="102" t="n"/>
+      <c r="C7" s="17" t="n"/>
       <c r="D7" s="32" t="inlineStr">
         <is>
           <t>存储落地实现（Iceberg/UC）</t>
@@ -16162,12 +16163,12 @@
       <c r="I7" s="46" t="n">
         <v>0.5</v>
       </c>
-      <c r="J7" s="102" t="n"/>
+      <c r="J7" s="17" t="n"/>
       <c r="K7" s="46">
         <f>ROUND(SUM(F7:I7),2)</f>
         <v/>
       </c>
-      <c r="L7" s="102" t="n"/>
+      <c r="L7" s="17" t="n"/>
     </row>
     <row r="8" ht="26" customHeight="1">
       <c r="A8" s="15" t="inlineStr">
@@ -16176,7 +16177,7 @@
         </is>
       </c>
       <c r="B8" s="102" t="n"/>
-      <c r="C8" s="102" t="n"/>
+      <c r="C8" s="17" t="n"/>
       <c r="D8" s="32" t="inlineStr">
         <is>
           <t>SeaTunnel批量导入作业</t>
@@ -16197,12 +16198,12 @@
       <c r="I8" s="46" t="n">
         <v>1</v>
       </c>
-      <c r="J8" s="102" t="n"/>
+      <c r="J8" s="17" t="n"/>
       <c r="K8" s="46">
         <f>ROUND(SUM(F8:I8),2)</f>
         <v/>
       </c>
-      <c r="L8" s="102" t="n"/>
+      <c r="L8" s="17" t="n"/>
     </row>
     <row r="9" ht="26" customHeight="1">
       <c r="A9" s="15" t="inlineStr">
@@ -16211,7 +16212,7 @@
         </is>
       </c>
       <c r="B9" s="102" t="n"/>
-      <c r="C9" s="103" t="n"/>
+      <c r="C9" s="17" t="n"/>
       <c r="D9" s="32" t="inlineStr">
         <is>
           <t>导入执行与监控</t>
@@ -16232,12 +16233,12 @@
       <c r="I9" s="46" t="n">
         <v>0.5</v>
       </c>
-      <c r="J9" s="103" t="n"/>
+      <c r="J9" s="17" t="n"/>
       <c r="K9" s="46">
         <f>ROUND(SUM(F9:I9),2)</f>
         <v/>
       </c>
-      <c r="L9" s="103" t="n"/>
+      <c r="L9" s="17" t="n"/>
     </row>
     <row r="10" ht="26" customHeight="1">
       <c r="A10" s="15" t="inlineStr">
@@ -16292,7 +16293,7 @@
         </is>
       </c>
       <c r="B11" s="102" t="n"/>
-      <c r="C11" s="102" t="n"/>
+      <c r="C11" s="17" t="n"/>
       <c r="D11" s="32" t="inlineStr">
         <is>
           <t>大文件分片上传与断点续传</t>
@@ -16313,12 +16314,12 @@
       <c r="I11" s="46" t="n">
         <v>1</v>
       </c>
-      <c r="J11" s="102" t="n"/>
+      <c r="J11" s="17" t="n"/>
       <c r="K11" s="46">
         <f>ROUND(SUM(F11:I11),2)</f>
         <v/>
       </c>
-      <c r="L11" s="102" t="n"/>
+      <c r="L11" s="17" t="n"/>
     </row>
     <row r="12" ht="26" customHeight="1">
       <c r="A12" s="15" t="inlineStr">
@@ -16327,7 +16328,7 @@
         </is>
       </c>
       <c r="B12" s="102" t="n"/>
-      <c r="C12" s="102" t="n"/>
+      <c r="C12" s="17" t="n"/>
       <c r="D12" s="32" t="inlineStr">
         <is>
           <t>文件包解析</t>
@@ -16346,12 +16347,12 @@
       <c r="I12" s="46" t="n">
         <v>0.75</v>
       </c>
-      <c r="J12" s="102" t="n"/>
+      <c r="J12" s="17" t="n"/>
       <c r="K12" s="46">
         <f>ROUND(SUM(F12:I12),2)</f>
         <v/>
       </c>
-      <c r="L12" s="102" t="n"/>
+      <c r="L12" s="17" t="n"/>
     </row>
     <row r="13" ht="26" customHeight="1">
       <c r="A13" s="15" t="inlineStr">
@@ -16360,7 +16361,7 @@
         </is>
       </c>
       <c r="B13" s="102" t="n"/>
-      <c r="C13" s="103" t="n"/>
+      <c r="C13" s="17" t="n"/>
       <c r="D13" s="32" t="inlineStr">
         <is>
           <t>附件元数据与Blob存储布局</t>
@@ -16381,12 +16382,12 @@
       <c r="I13" s="46" t="n">
         <v>0.5</v>
       </c>
-      <c r="J13" s="103" t="n"/>
+      <c r="J13" s="17" t="n"/>
       <c r="K13" s="46">
         <f>ROUND(SUM(F13:I13),2)</f>
         <v/>
       </c>
-      <c r="L13" s="103" t="n"/>
+      <c r="L13" s="17" t="n"/>
     </row>
     <row r="14" ht="26" customHeight="1">
       <c r="A14" s="15" t="inlineStr">
@@ -16441,7 +16442,7 @@
         </is>
       </c>
       <c r="B15" s="102" t="n"/>
-      <c r="C15" s="102" t="n"/>
+      <c r="C15" s="17" t="n"/>
       <c r="D15" s="32" t="inlineStr">
         <is>
           <t>格式转换与清洗规则</t>
@@ -16462,12 +16463,12 @@
       <c r="I15" s="46" t="n">
         <v>0.75</v>
       </c>
-      <c r="J15" s="102" t="n"/>
+      <c r="J15" s="17" t="n"/>
       <c r="K15" s="46">
         <f>ROUND(SUM(F15:I15),2)</f>
         <v/>
       </c>
-      <c r="L15" s="102" t="n"/>
+      <c r="L15" s="17" t="n"/>
     </row>
     <row r="16" ht="26" customHeight="1">
       <c r="A16" s="15" t="inlineStr">
@@ -16476,7 +16477,7 @@
         </is>
       </c>
       <c r="B16" s="102" t="n"/>
-      <c r="C16" s="102" t="n"/>
+      <c r="C16" s="17" t="n"/>
       <c r="D16" s="32" t="inlineStr">
         <is>
           <t>校验规则配置</t>
@@ -16497,12 +16498,12 @@
       <c r="I16" s="46" t="n">
         <v>0.5</v>
       </c>
-      <c r="J16" s="102" t="n"/>
+      <c r="J16" s="17" t="n"/>
       <c r="K16" s="46">
         <f>ROUND(SUM(F16:I16),2)</f>
         <v/>
       </c>
-      <c r="L16" s="102" t="n"/>
+      <c r="L16" s="17" t="n"/>
     </row>
     <row r="17" ht="26" customHeight="1">
       <c r="A17" s="15" t="inlineStr">
@@ -16511,7 +16512,7 @@
         </is>
       </c>
       <c r="B17" s="102" t="n"/>
-      <c r="C17" s="103" t="n"/>
+      <c r="C17" s="17" t="n"/>
       <c r="D17" s="32" t="inlineStr">
         <is>
           <t>规则版本与试跑预览</t>
@@ -16532,12 +16533,12 @@
       <c r="I17" s="46" t="n">
         <v>0.5</v>
       </c>
-      <c r="J17" s="103" t="n"/>
+      <c r="J17" s="17" t="n"/>
       <c r="K17" s="46">
         <f>ROUND(SUM(F17:I17),2)</f>
         <v/>
       </c>
-      <c r="L17" s="103" t="n"/>
+      <c r="L17" s="17" t="n"/>
     </row>
     <row r="18" ht="26" customHeight="1">
       <c r="A18" s="15" t="inlineStr">
@@ -16590,7 +16591,7 @@
         </is>
       </c>
       <c r="B19" s="102" t="n"/>
-      <c r="C19" s="102" t="n"/>
+      <c r="C19" s="17" t="n"/>
       <c r="D19" s="32" t="inlineStr">
         <is>
           <t>基准采集作业与存储</t>
@@ -16609,12 +16610,12 @@
       <c r="I19" s="46" t="n">
         <v>0.5</v>
       </c>
-      <c r="J19" s="102" t="n"/>
+      <c r="J19" s="17" t="n"/>
       <c r="K19" s="46">
         <f>ROUND(SUM(F19:I19),2)</f>
         <v/>
       </c>
-      <c r="L19" s="102" t="n"/>
+      <c r="L19" s="17" t="n"/>
     </row>
     <row r="20" ht="26" customHeight="1">
       <c r="A20" s="15" t="inlineStr">
@@ -16623,7 +16624,7 @@
         </is>
       </c>
       <c r="B20" s="102" t="n"/>
-      <c r="C20" s="103" t="n"/>
+      <c r="C20" s="17" t="n"/>
       <c r="D20" s="32" t="inlineStr">
         <is>
           <t>基准报告查询展示</t>
@@ -16644,12 +16645,12 @@
       <c r="I20" s="46" t="n">
         <v>0.25</v>
       </c>
-      <c r="J20" s="103" t="n"/>
+      <c r="J20" s="17" t="n"/>
       <c r="K20" s="46">
         <f>ROUND(SUM(F20:I20),2)</f>
         <v/>
       </c>
-      <c r="L20" s="103" t="n"/>
+      <c r="L20" s="17" t="n"/>
     </row>
     <row r="21" ht="26" customHeight="1">
       <c r="A21" s="15" t="inlineStr">
@@ -16700,7 +16701,7 @@
         </is>
       </c>
       <c r="B22" s="103" t="n"/>
-      <c r="C22" s="103" t="n"/>
+      <c r="C22" s="17" t="n"/>
       <c r="D22" s="32" t="inlineStr">
         <is>
           <t>差异报告与处理流程</t>
@@ -16723,12 +16724,12 @@
       <c r="I22" s="46" t="n">
         <v>0.5</v>
       </c>
-      <c r="J22" s="103" t="n"/>
+      <c r="J22" s="17" t="n"/>
       <c r="K22" s="46">
         <f>ROUND(SUM(F22:I22),2)</f>
         <v/>
       </c>
-      <c r="L22" s="103" t="n"/>
+      <c r="L22" s="17" t="n"/>
     </row>
     <row r="23" ht="26" customHeight="1">
       <c r="A23" s="15" t="inlineStr">
@@ -16785,7 +16786,7 @@
         </is>
       </c>
       <c r="B24" s="102" t="n"/>
-      <c r="C24" s="102" t="n"/>
+      <c r="C24" s="17" t="n"/>
       <c r="D24" s="32" t="inlineStr">
         <is>
           <t>元数据核心表与API</t>
@@ -16804,12 +16805,12 @@
       <c r="I24" s="46" t="n">
         <v>0.5</v>
       </c>
-      <c r="J24" s="102" t="n"/>
+      <c r="J24" s="17" t="n"/>
       <c r="K24" s="46">
         <f>ROUND(SUM(F24:I24),2)</f>
         <v/>
       </c>
-      <c r="L24" s="102" t="n"/>
+      <c r="L24" s="17" t="n"/>
     </row>
     <row r="25" ht="26" customHeight="1">
       <c r="A25" s="15" t="inlineStr">
@@ -16818,7 +16819,7 @@
         </is>
       </c>
       <c r="B25" s="102" t="n"/>
-      <c r="C25" s="103" t="n"/>
+      <c r="C25" s="17" t="n"/>
       <c r="D25" s="32" t="inlineStr">
         <is>
           <t>元数据驱动配置机制</t>
@@ -16841,12 +16842,12 @@
       <c r="I25" s="46" t="n">
         <v>0.5</v>
       </c>
-      <c r="J25" s="103" t="n"/>
+      <c r="J25" s="17" t="n"/>
       <c r="K25" s="46">
         <f>ROUND(SUM(F25:I25),2)</f>
         <v/>
       </c>
-      <c r="L25" s="103" t="n"/>
+      <c r="L25" s="17" t="n"/>
     </row>
     <row r="26" ht="26" customHeight="1">
       <c r="A26" s="15" t="inlineStr">
@@ -16899,7 +16900,7 @@
         </is>
       </c>
       <c r="B27" s="102" t="n"/>
-      <c r="C27" s="102" t="n"/>
+      <c r="C27" s="17" t="n"/>
       <c r="D27" s="32" t="inlineStr">
         <is>
           <t>接入时自动绑定</t>
@@ -16918,12 +16919,12 @@
       <c r="I27" s="46" t="n">
         <v>0.5</v>
       </c>
-      <c r="J27" s="102" t="n"/>
+      <c r="J27" s="17" t="n"/>
       <c r="K27" s="46">
         <f>ROUND(SUM(F27:I27),2)</f>
         <v/>
       </c>
-      <c r="L27" s="102" t="n"/>
+      <c r="L27" s="17" t="n"/>
     </row>
     <row r="28" ht="26" customHeight="1">
       <c r="A28" s="15" t="inlineStr">
@@ -16932,7 +16933,7 @@
         </is>
       </c>
       <c r="B28" s="103" t="n"/>
-      <c r="C28" s="103" t="n"/>
+      <c r="C28" s="17" t="n"/>
       <c r="D28" s="32" t="inlineStr">
         <is>
           <t>按来源检索与统计</t>
@@ -16953,12 +16954,12 @@
       <c r="I28" s="46" t="n">
         <v>0.5</v>
       </c>
-      <c r="J28" s="103" t="n"/>
+      <c r="J28" s="17" t="n"/>
       <c r="K28" s="46">
         <f>ROUND(SUM(F28:I28),2)</f>
         <v/>
       </c>
-      <c r="L28" s="103" t="n"/>
+      <c r="L28" s="17" t="n"/>
     </row>
     <row r="29" ht="26" customHeight="1">
       <c r="A29" s="15" t="inlineStr">
@@ -17017,7 +17018,7 @@
         </is>
       </c>
       <c r="B30" s="102" t="n"/>
-      <c r="C30" s="102" t="n"/>
+      <c r="C30" s="17" t="n"/>
       <c r="D30" s="32" t="inlineStr">
         <is>
           <t>处置引擎</t>
@@ -17036,12 +17037,12 @@
       <c r="I30" s="46" t="n">
         <v>1</v>
       </c>
-      <c r="J30" s="102" t="n"/>
+      <c r="J30" s="17" t="n"/>
       <c r="K30" s="46">
         <f>ROUND(SUM(F30:I30),2)</f>
         <v/>
       </c>
-      <c r="L30" s="102" t="n"/>
+      <c r="L30" s="17" t="n"/>
     </row>
     <row r="31" ht="26" customHeight="1">
       <c r="A31" s="15" t="inlineStr">
@@ -17050,7 +17051,7 @@
         </is>
       </c>
       <c r="B31" s="102" t="n"/>
-      <c r="C31" s="103" t="n"/>
+      <c r="C31" s="17" t="n"/>
       <c r="D31" s="32" t="inlineStr">
         <is>
           <t>处置计划审批与台账</t>
@@ -17073,12 +17074,12 @@
       <c r="I31" s="46" t="n">
         <v>0.5</v>
       </c>
-      <c r="J31" s="103" t="n"/>
+      <c r="J31" s="17" t="n"/>
       <c r="K31" s="46">
         <f>ROUND(SUM(F31:I31),2)</f>
         <v/>
       </c>
-      <c r="L31" s="103" t="n"/>
+      <c r="L31" s="17" t="n"/>
     </row>
     <row r="32" ht="26" customHeight="1">
       <c r="A32" s="15" t="inlineStr">
@@ -17133,7 +17134,7 @@
         </is>
       </c>
       <c r="B33" s="102" t="n"/>
-      <c r="C33" s="102" t="n"/>
+      <c r="C33" s="17" t="n"/>
       <c r="D33" s="32" t="inlineStr">
         <is>
           <t>Hold生效与解除实现</t>
@@ -17152,12 +17153,12 @@
       <c r="I33" s="46" t="n">
         <v>0.75</v>
       </c>
-      <c r="J33" s="102" t="n"/>
+      <c r="J33" s="17" t="n"/>
       <c r="K33" s="46">
         <f>ROUND(SUM(F33:I33),2)</f>
         <v/>
       </c>
-      <c r="L33" s="102" t="n"/>
+      <c r="L33" s="17" t="n"/>
     </row>
     <row r="34" ht="26" customHeight="1">
       <c r="A34" s="15" t="inlineStr">
@@ -17166,7 +17167,7 @@
         </is>
       </c>
       <c r="B34" s="103" t="n"/>
-      <c r="C34" s="103" t="n"/>
+      <c r="C34" s="17" t="n"/>
       <c r="D34" s="32" t="inlineStr">
         <is>
           <t>Hold清单管理与提醒</t>
@@ -17187,12 +17188,12 @@
       <c r="I34" s="46" t="n">
         <v>0.25</v>
       </c>
-      <c r="J34" s="103" t="n"/>
+      <c r="J34" s="17" t="n"/>
       <c r="K34" s="46">
         <f>ROUND(SUM(F34:I34),2)</f>
         <v/>
       </c>
-      <c r="L34" s="103" t="n"/>
+      <c r="L34" s="17" t="n"/>
     </row>
     <row r="35" ht="26" customHeight="1">
       <c r="A35" s="15" t="inlineStr">
@@ -17249,7 +17250,7 @@
         </is>
       </c>
       <c r="B36" s="102" t="n"/>
-      <c r="C36" s="102" t="n"/>
+      <c r="C36" s="17" t="n"/>
       <c r="D36" s="32" t="inlineStr">
         <is>
           <t>存储层加密落地【原生】</t>
@@ -17268,12 +17269,12 @@
       <c r="I36" s="46" t="n">
         <v>0.5</v>
       </c>
-      <c r="J36" s="102" t="n"/>
+      <c r="J36" s="17" t="n"/>
       <c r="K36" s="46">
         <f>ROUND(SUM(F36:I36),2)</f>
         <v/>
       </c>
-      <c r="L36" s="102" t="n"/>
+      <c r="L36" s="17" t="n"/>
     </row>
     <row r="37" ht="26" customHeight="1">
       <c r="A37" s="15" t="inlineStr">
@@ -17282,7 +17283,7 @@
         </is>
       </c>
       <c r="B37" s="102" t="n"/>
-      <c r="C37" s="103" t="n"/>
+      <c r="C37" s="17" t="n"/>
       <c r="D37" s="32" t="inlineStr">
         <is>
           <t>PII字段级加密服务</t>
@@ -17301,12 +17302,12 @@
       <c r="I37" s="46" t="n">
         <v>0.75</v>
       </c>
-      <c r="J37" s="103" t="n"/>
+      <c r="J37" s="17" t="n"/>
       <c r="K37" s="46">
         <f>ROUND(SUM(F37:I37),2)</f>
         <v/>
       </c>
-      <c r="L37" s="103" t="n"/>
+      <c r="L37" s="17" t="n"/>
     </row>
     <row r="38" ht="26" customHeight="1">
       <c r="A38" s="15" t="inlineStr">
@@ -17359,7 +17360,7 @@
         </is>
       </c>
       <c r="B39" s="102" t="n"/>
-      <c r="C39" s="102" t="n"/>
+      <c r="C39" s="17" t="n"/>
       <c r="D39" s="32" t="inlineStr">
         <is>
           <t>密钥操作审计与告警【原生】</t>
@@ -17380,12 +17381,12 @@
       <c r="I39" s="46" t="n">
         <v>0.5</v>
       </c>
-      <c r="J39" s="102" t="n"/>
+      <c r="J39" s="17" t="n"/>
       <c r="K39" s="46">
         <f>ROUND(SUM(F39:I39),2)</f>
         <v/>
       </c>
-      <c r="L39" s="102" t="n"/>
+      <c r="L39" s="17" t="n"/>
     </row>
     <row r="40" ht="26" customHeight="1">
       <c r="A40" s="15" t="inlineStr">
@@ -17394,7 +17395,7 @@
         </is>
       </c>
       <c r="B40" s="102" t="n"/>
-      <c r="C40" s="103" t="n"/>
+      <c r="C40" s="17" t="n"/>
       <c r="D40" s="32" t="inlineStr">
         <is>
           <t>密钥状态展示（不自研管理界面）【原生】</t>
@@ -17413,12 +17414,12 @@
       <c r="I40" s="46" t="n">
         <v>0.25</v>
       </c>
-      <c r="J40" s="103" t="n"/>
+      <c r="J40" s="17" t="n"/>
       <c r="K40" s="46">
         <f>ROUND(SUM(F40:I40),2)</f>
         <v/>
       </c>
-      <c r="L40" s="103" t="n"/>
+      <c r="L40" s="17" t="n"/>
     </row>
     <row r="41" ht="26" customHeight="1">
       <c r="A41" s="15" t="inlineStr">
@@ -17473,7 +17474,7 @@
         </is>
       </c>
       <c r="B42" s="102" t="n"/>
-      <c r="C42" s="102" t="n"/>
+      <c r="C42" s="17" t="n"/>
       <c r="D42" s="32" t="inlineStr">
         <is>
           <t>备份作业与副本创建【原生】</t>
@@ -17492,12 +17493,12 @@
       <c r="I42" s="46" t="n">
         <v>0.5</v>
       </c>
-      <c r="J42" s="102" t="n"/>
+      <c r="J42" s="17" t="n"/>
       <c r="K42" s="46">
         <f>ROUND(SUM(F42:I42),2)</f>
         <v/>
       </c>
-      <c r="L42" s="102" t="n"/>
+      <c r="L42" s="17" t="n"/>
     </row>
     <row r="43" ht="26" customHeight="1">
       <c r="A43" s="15" t="inlineStr">
@@ -17506,7 +17507,7 @@
         </is>
       </c>
       <c r="B43" s="103" t="n"/>
-      <c r="C43" s="103" t="n"/>
+      <c r="C43" s="17" t="n"/>
       <c r="D43" s="32" t="inlineStr">
         <is>
           <t>备份监控与恢复操作【原生】</t>
@@ -17527,12 +17528,12 @@
       <c r="I43" s="46" t="n">
         <v>0.5</v>
       </c>
-      <c r="J43" s="103" t="n"/>
+      <c r="J43" s="17" t="n"/>
       <c r="K43" s="46">
         <f>ROUND(SUM(F43:I43),2)</f>
         <v/>
       </c>
-      <c r="L43" s="103" t="n"/>
+      <c r="L43" s="17" t="n"/>
     </row>
     <row r="44" ht="26" customHeight="1">
       <c r="A44" s="15" t="inlineStr">
@@ -17591,7 +17592,7 @@
         </is>
       </c>
       <c r="B45" s="102" t="n"/>
-      <c r="C45" s="102" t="n"/>
+      <c r="C45" s="17" t="n"/>
       <c r="D45" s="32" t="inlineStr">
         <is>
           <t>检索页动态表单</t>
@@ -17612,12 +17613,12 @@
       <c r="I45" s="46" t="n">
         <v>0.5</v>
       </c>
-      <c r="J45" s="102" t="n"/>
+      <c r="J45" s="17" t="n"/>
       <c r="K45" s="46">
         <f>ROUND(SUM(F45:I45),2)</f>
         <v/>
       </c>
-      <c r="L45" s="102" t="n"/>
+      <c r="L45" s="17" t="n"/>
     </row>
     <row r="46" ht="26" customHeight="1">
       <c r="A46" s="15" t="inlineStr">
@@ -17626,7 +17627,7 @@
         </is>
       </c>
       <c r="B46" s="102" t="n"/>
-      <c r="C46" s="103" t="n"/>
+      <c r="C46" s="17" t="n"/>
       <c r="D46" s="32" t="inlineStr">
         <is>
           <t>查询代理与SERVE层对接</t>
@@ -17645,12 +17646,12 @@
       <c r="I46" s="46" t="n">
         <v>0.75</v>
       </c>
-      <c r="J46" s="103" t="n"/>
+      <c r="J46" s="17" t="n"/>
       <c r="K46" s="46">
         <f>ROUND(SUM(F46:I46),2)</f>
         <v/>
       </c>
-      <c r="L46" s="103" t="n"/>
+      <c r="L46" s="17" t="n"/>
     </row>
     <row r="47" ht="26" customHeight="1">
       <c r="A47" s="15" t="inlineStr">
@@ -17701,7 +17702,7 @@
         </is>
       </c>
       <c r="B48" s="102" t="n"/>
-      <c r="C48" s="103" t="n"/>
+      <c r="C48" s="17" t="n"/>
       <c r="D48" s="32" t="inlineStr">
         <is>
           <t>来源维度查询下推</t>
@@ -17720,12 +17721,12 @@
       <c r="I48" s="46" t="n">
         <v>0.25</v>
       </c>
-      <c r="J48" s="103" t="n"/>
+      <c r="J48" s="17" t="n"/>
       <c r="K48" s="46">
         <f>ROUND(SUM(F48:I48),2)</f>
         <v/>
       </c>
-      <c r="L48" s="103" t="n"/>
+      <c r="L48" s="17" t="n"/>
     </row>
     <row r="49" ht="26" customHeight="1">
       <c r="A49" s="15" t="inlineStr">
@@ -17776,7 +17777,7 @@
         </is>
       </c>
       <c r="B50" s="102" t="n"/>
-      <c r="C50" s="103" t="n"/>
+      <c r="C50" s="17" t="n"/>
       <c r="D50" s="32" t="inlineStr">
         <is>
           <t>时间分区下推与索引</t>
@@ -17795,12 +17796,12 @@
       <c r="I50" s="46" t="n">
         <v>0.25</v>
       </c>
-      <c r="J50" s="103" t="n"/>
+      <c r="J50" s="17" t="n"/>
       <c r="K50" s="46">
         <f>ROUND(SUM(F50:I50),2)</f>
         <v/>
       </c>
-      <c r="L50" s="103" t="n"/>
+      <c r="L50" s="17" t="n"/>
     </row>
     <row r="51" ht="26" customHeight="1">
       <c r="A51" s="15" t="inlineStr">
@@ -17851,7 +17852,7 @@
         </is>
       </c>
       <c r="B52" s="102" t="n"/>
-      <c r="C52" s="103" t="n"/>
+      <c r="C52" s="17" t="n"/>
       <c r="D52" s="32" t="inlineStr">
         <is>
           <t>大批量结果性能</t>
@@ -17872,12 +17873,12 @@
       <c r="I52" s="46" t="n">
         <v>0.5</v>
       </c>
-      <c r="J52" s="103" t="n"/>
+      <c r="J52" s="17" t="n"/>
       <c r="K52" s="46">
         <f>ROUND(SUM(F52:I52),2)</f>
         <v/>
       </c>
-      <c r="L52" s="103" t="n"/>
+      <c r="L52" s="17" t="n"/>
     </row>
     <row r="53" ht="26" customHeight="1">
       <c r="A53" s="15" t="inlineStr">
@@ -17928,7 +17929,7 @@
         </is>
       </c>
       <c r="B54" s="102" t="n"/>
-      <c r="C54" s="102" t="n"/>
+      <c r="C54" s="17" t="n"/>
       <c r="D54" s="32" t="inlineStr">
         <is>
           <t>SAS直连与流式加载</t>
@@ -17949,12 +17950,12 @@
       <c r="I54" s="46" t="n">
         <v>0.5</v>
       </c>
-      <c r="J54" s="102" t="n"/>
+      <c r="J54" s="17" t="n"/>
       <c r="K54" s="46">
         <f>ROUND(SUM(F54:I54),2)</f>
         <v/>
       </c>
-      <c r="L54" s="102" t="n"/>
+      <c r="L54" s="17" t="n"/>
     </row>
     <row r="55" ht="26" customHeight="1">
       <c r="A55" s="15" t="inlineStr">
@@ -17963,7 +17964,7 @@
         </is>
       </c>
       <c r="B55" s="103" t="n"/>
-      <c r="C55" s="103" t="n"/>
+      <c r="C55" s="17" t="n"/>
       <c r="D55" s="32" t="inlineStr">
         <is>
           <t>前端预览组件</t>
@@ -17982,12 +17983,12 @@
       <c r="I55" s="46" t="n">
         <v>0.25</v>
       </c>
-      <c r="J55" s="103" t="n"/>
+      <c r="J55" s="17" t="n"/>
       <c r="K55" s="46">
         <f>ROUND(SUM(F55:I55),2)</f>
         <v/>
       </c>
-      <c r="L55" s="103" t="n"/>
+      <c r="L55" s="17" t="n"/>
     </row>
     <row r="56" ht="26" customHeight="1">
       <c r="A56" s="15" t="inlineStr">
@@ -18044,7 +18045,7 @@
         </is>
       </c>
       <c r="B57" s="102" t="n"/>
-      <c r="C57" s="102" t="n"/>
+      <c r="C57" s="17" t="n"/>
       <c r="D57" s="32" t="inlineStr">
         <is>
           <t>操作拦截与落库</t>
@@ -18063,12 +18064,12 @@
       <c r="I57" s="46" t="n">
         <v>0.5</v>
       </c>
-      <c r="J57" s="102" t="n"/>
+      <c r="J57" s="17" t="n"/>
       <c r="K57" s="46">
         <f>ROUND(SUM(F57:I57),2)</f>
         <v/>
       </c>
-      <c r="L57" s="102" t="n"/>
+      <c r="L57" s="17" t="n"/>
     </row>
     <row r="58" ht="26" customHeight="1">
       <c r="A58" s="15" t="inlineStr">
@@ -18077,7 +18078,7 @@
         </is>
       </c>
       <c r="B58" s="102" t="n"/>
-      <c r="C58" s="103" t="n"/>
+      <c r="C58" s="17" t="n"/>
       <c r="D58" s="32" t="inlineStr">
         <is>
           <t>审计查询界面</t>
@@ -18098,12 +18099,12 @@
       <c r="I58" s="46" t="n">
         <v>0.5</v>
       </c>
-      <c r="J58" s="103" t="n"/>
+      <c r="J58" s="17" t="n"/>
       <c r="K58" s="46">
         <f>ROUND(SUM(F58:I58),2)</f>
         <v/>
       </c>
-      <c r="L58" s="103" t="n"/>
+      <c r="L58" s="17" t="n"/>
     </row>
     <row r="59" ht="26" customHeight="1">
       <c r="A59" s="15" t="inlineStr">
@@ -18154,7 +18155,7 @@
         </is>
       </c>
       <c r="B60" s="102" t="n"/>
-      <c r="C60" s="103" t="n"/>
+      <c r="C60" s="17" t="n"/>
       <c r="D60" s="32" t="inlineStr">
         <is>
           <t>异步批量写入</t>
@@ -18173,12 +18174,12 @@
       <c r="I60" s="46" t="n">
         <v>0.25</v>
       </c>
-      <c r="J60" s="103" t="n"/>
+      <c r="J60" s="17" t="n"/>
       <c r="K60" s="46">
         <f>ROUND(SUM(F60:I60),2)</f>
         <v/>
       </c>
-      <c r="L60" s="103" t="n"/>
+      <c r="L60" s="17" t="n"/>
     </row>
     <row r="61" ht="26" customHeight="1">
       <c r="A61" s="15" t="inlineStr">
@@ -18229,7 +18230,7 @@
         </is>
       </c>
       <c r="B62" s="103" t="n"/>
-      <c r="C62" s="103" t="n"/>
+      <c r="C62" s="17" t="n"/>
       <c r="D62" s="32" t="inlineStr">
         <is>
           <t>大批量导出告警</t>
@@ -18250,12 +18251,12 @@
       <c r="I62" s="46" t="n">
         <v>0.25</v>
       </c>
-      <c r="J62" s="103" t="n"/>
+      <c r="J62" s="17" t="n"/>
       <c r="K62" s="46">
         <f>ROUND(SUM(F62:I62),2)</f>
         <v/>
       </c>
-      <c r="L62" s="103" t="n"/>
+      <c r="L62" s="17" t="n"/>
     </row>
     <row r="63" ht="26" customHeight="1">
       <c r="A63" s="15" t="inlineStr">
@@ -18312,7 +18313,7 @@
         </is>
       </c>
       <c r="B64" s="102" t="n"/>
-      <c r="C64" s="102" t="n"/>
+      <c r="C64" s="17" t="n"/>
       <c r="D64" s="32" t="inlineStr">
         <is>
           <t>角色管理界面与API</t>
@@ -18333,12 +18334,12 @@
       <c r="I64" s="46" t="n">
         <v>0.5</v>
       </c>
-      <c r="J64" s="102" t="n"/>
+      <c r="J64" s="17" t="n"/>
       <c r="K64" s="46">
         <f>ROUND(SUM(F64:I64),2)</f>
         <v/>
       </c>
-      <c r="L64" s="102" t="n"/>
+      <c r="L64" s="17" t="n"/>
     </row>
     <row r="65" ht="26" customHeight="1">
       <c r="A65" s="15" t="inlineStr">
@@ -18347,7 +18348,7 @@
         </is>
       </c>
       <c r="B65" s="102" t="n"/>
-      <c r="C65" s="103" t="n"/>
+      <c r="C65" s="17" t="n"/>
       <c r="D65" s="32" t="inlineStr">
         <is>
           <t>权限校验与UC授权映射</t>
@@ -18366,12 +18367,12 @@
       <c r="I65" s="46" t="n">
         <v>0.75</v>
       </c>
-      <c r="J65" s="103" t="n"/>
+      <c r="J65" s="17" t="n"/>
       <c r="K65" s="46">
         <f>ROUND(SUM(F65:I65),2)</f>
         <v/>
       </c>
-      <c r="L65" s="103" t="n"/>
+      <c r="L65" s="17" t="n"/>
     </row>
     <row r="66" ht="26" customHeight="1">
       <c r="A66" s="15" t="inlineStr">
@@ -18426,7 +18427,7 @@
         </is>
       </c>
       <c r="B67" s="102" t="n"/>
-      <c r="C67" s="103" t="n"/>
+      <c r="C67" s="17" t="n"/>
       <c r="D67" s="32" t="inlineStr">
         <is>
           <t>账号与角色绑定</t>
@@ -18447,12 +18448,12 @@
       <c r="I67" s="46" t="n">
         <v>0.25</v>
       </c>
-      <c r="J67" s="103" t="n"/>
+      <c r="J67" s="17" t="n"/>
       <c r="K67" s="46">
         <f>ROUND(SUM(F67:I67),2)</f>
         <v/>
       </c>
-      <c r="L67" s="103" t="n"/>
+      <c r="L67" s="17" t="n"/>
     </row>
     <row r="68" ht="26" customHeight="1">
       <c r="A68" s="15" t="inlineStr">
@@ -18507,7 +18508,7 @@
         </is>
       </c>
       <c r="B69" s="102" t="n"/>
-      <c r="C69" s="102" t="n"/>
+      <c r="C69" s="17" t="n"/>
       <c r="D69" s="32" t="inlineStr">
         <is>
           <t>SSO登录链路【中间件】</t>
@@ -18528,12 +18529,12 @@
       <c r="I69" s="46" t="n">
         <v>0.75</v>
       </c>
-      <c r="J69" s="102" t="n"/>
+      <c r="J69" s="17" t="n"/>
       <c r="K69" s="46">
         <f>ROUND(SUM(F69:I69),2)</f>
         <v/>
       </c>
-      <c r="L69" s="102" t="n"/>
+      <c r="L69" s="17" t="n"/>
     </row>
     <row r="70" ht="26" customHeight="1">
       <c r="A70" s="15" t="inlineStr">
@@ -18542,7 +18543,7 @@
         </is>
       </c>
       <c r="B70" s="102" t="n"/>
-      <c r="C70" s="103" t="n"/>
+      <c r="C70" s="17" t="n"/>
       <c r="D70" s="32" t="inlineStr">
         <is>
           <t>认证异常场景处理</t>
@@ -18561,12 +18562,12 @@
       <c r="I70" s="46" t="n">
         <v>0.5</v>
       </c>
-      <c r="J70" s="103" t="n"/>
+      <c r="J70" s="17" t="n"/>
       <c r="K70" s="46">
         <f>ROUND(SUM(F70:I70),2)</f>
         <v/>
       </c>
-      <c r="L70" s="103" t="n"/>
+      <c r="L70" s="17" t="n"/>
     </row>
     <row r="71" ht="26" customHeight="1">
       <c r="A71" s="15" t="inlineStr">
@@ -18619,7 +18620,7 @@
         </is>
       </c>
       <c r="B72" s="102" t="n"/>
-      <c r="C72" s="103" t="n"/>
+      <c r="C72" s="17" t="n"/>
       <c r="D72" s="32" t="inlineStr">
         <is>
           <t>首登自动关联与角色赋予</t>
@@ -18640,12 +18641,12 @@
       <c r="I72" s="46" t="n">
         <v>0.5</v>
       </c>
-      <c r="J72" s="103" t="n"/>
+      <c r="J72" s="17" t="n"/>
       <c r="K72" s="46">
         <f>ROUND(SUM(F72:I72),2)</f>
         <v/>
       </c>
-      <c r="L72" s="103" t="n"/>
+      <c r="L72" s="17" t="n"/>
     </row>
     <row r="73" ht="26" customHeight="1">
       <c r="A73" s="15" t="inlineStr">
@@ -18700,7 +18701,7 @@
         </is>
       </c>
       <c r="B74" s="103" t="n"/>
-      <c r="C74" s="103" t="n"/>
+      <c r="C74" s="17" t="n"/>
       <c r="D74" s="32" t="inlineStr">
         <is>
           <t>异常访问控制</t>
@@ -18719,12 +18720,12 @@
       <c r="I74" s="46" t="n">
         <v>0.5</v>
       </c>
-      <c r="J74" s="103" t="n"/>
+      <c r="J74" s="17" t="n"/>
       <c r="K74" s="46">
         <f>ROUND(SUM(F74:I74),2)</f>
         <v/>
       </c>
-      <c r="L74" s="103" t="n"/>
+      <c r="L74" s="17" t="n"/>
     </row>
     <row r="75" ht="26" customHeight="1">
       <c r="A75" s="15" t="inlineStr">
@@ -18781,7 +18782,7 @@
         </is>
       </c>
       <c r="B76" s="102" t="n"/>
-      <c r="C76" s="102" t="n"/>
+      <c r="C76" s="17" t="n"/>
       <c r="D76" s="32" t="inlineStr">
         <is>
           <t>前端工程初始化</t>
@@ -18800,12 +18801,12 @@
       <c r="I76" s="46" t="n">
         <v>0.25</v>
       </c>
-      <c r="J76" s="102" t="n"/>
+      <c r="J76" s="17" t="n"/>
       <c r="K76" s="46">
         <f>ROUND(SUM(F76:I76),2)</f>
         <v/>
       </c>
-      <c r="L76" s="102" t="n"/>
+      <c r="L76" s="17" t="n"/>
     </row>
     <row r="77" ht="26" customHeight="1">
       <c r="A77" s="15" t="inlineStr">
@@ -18814,7 +18815,7 @@
         </is>
       </c>
       <c r="B77" s="102" t="n"/>
-      <c r="C77" s="102" t="n"/>
+      <c r="C77" s="17" t="n"/>
       <c r="D77" s="32" t="inlineStr">
         <is>
           <t>后端工程初始化</t>
@@ -18833,12 +18834,12 @@
       <c r="I77" s="46" t="n">
         <v>0.25</v>
       </c>
-      <c r="J77" s="102" t="n"/>
+      <c r="J77" s="17" t="n"/>
       <c r="K77" s="46">
         <f>ROUND(SUM(F77:I77),2)</f>
         <v/>
       </c>
-      <c r="L77" s="102" t="n"/>
+      <c r="L77" s="17" t="n"/>
     </row>
     <row r="78" ht="26" customHeight="1">
       <c r="A78" s="15" t="inlineStr">
@@ -18847,7 +18848,7 @@
         </is>
       </c>
       <c r="B78" s="102" t="n"/>
-      <c r="C78" s="102" t="n"/>
+      <c r="C78" s="17" t="n"/>
       <c r="D78" s="32" t="inlineStr">
         <is>
           <t>AI开发工具链与编码规范</t>
@@ -18866,12 +18867,12 @@
         <v>0.25</v>
       </c>
       <c r="I78" s="46" t="n"/>
-      <c r="J78" s="102" t="n"/>
+      <c r="J78" s="17" t="n"/>
       <c r="K78" s="46">
         <f>ROUND(SUM(F78:I78),2)</f>
         <v/>
       </c>
-      <c r="L78" s="102" t="n"/>
+      <c r="L78" s="17" t="n"/>
     </row>
     <row r="79" ht="26" customHeight="1">
       <c r="A79" s="15" t="inlineStr">
@@ -18880,7 +18881,7 @@
         </is>
       </c>
       <c r="B79" s="102" t="n"/>
-      <c r="C79" s="103" t="n"/>
+      <c r="C79" s="17" t="n"/>
       <c r="D79" s="32" t="inlineStr">
         <is>
           <t>四道安全门禁CI/CD</t>
@@ -18901,12 +18902,12 @@
       <c r="I79" s="46" t="n">
         <v>0.5</v>
       </c>
-      <c r="J79" s="103" t="n"/>
+      <c r="J79" s="17" t="n"/>
       <c r="K79" s="46">
         <f>ROUND(SUM(F79:I79),2)</f>
         <v/>
       </c>
-      <c r="L79" s="103" t="n"/>
+      <c r="L79" s="17" t="n"/>
     </row>
     <row r="80" ht="26" customHeight="1">
       <c r="A80" s="15" t="inlineStr">
@@ -18955,7 +18956,7 @@
         </is>
       </c>
       <c r="B81" s="102" t="n"/>
-      <c r="C81" s="102" t="n"/>
+      <c r="C81" s="17" t="n"/>
       <c r="D81" s="32" t="inlineStr">
         <is>
           <t>后端SonarLint规约</t>
@@ -18972,12 +18973,12 @@
         <v>1.5</v>
       </c>
       <c r="I81" s="46" t="n"/>
-      <c r="J81" s="102" t="n"/>
+      <c r="J81" s="17" t="n"/>
       <c r="K81" s="46">
         <f>ROUND(SUM(F81:I81),2)</f>
         <v/>
       </c>
-      <c r="L81" s="102" t="n"/>
+      <c r="L81" s="17" t="n"/>
     </row>
     <row r="82" ht="26" customHeight="1">
       <c r="A82" s="15" t="inlineStr">
@@ -18986,7 +18987,7 @@
         </is>
       </c>
       <c r="B82" s="102" t="n"/>
-      <c r="C82" s="102" t="n"/>
+      <c r="C82" s="17" t="n"/>
       <c r="D82" s="32" t="inlineStr">
         <is>
           <t>SAST安全告警修复</t>
@@ -19007,12 +19008,12 @@
       <c r="I82" s="46" t="n">
         <v>0.25</v>
       </c>
-      <c r="J82" s="102" t="n"/>
+      <c r="J82" s="17" t="n"/>
       <c r="K82" s="46">
         <f>ROUND(SUM(F82:I82),2)</f>
         <v/>
       </c>
-      <c r="L82" s="102" t="n"/>
+      <c r="L82" s="17" t="n"/>
     </row>
     <row r="83" ht="26" customHeight="1">
       <c r="A83" s="15" t="inlineStr">
@@ -19021,7 +19022,7 @@
         </is>
       </c>
       <c r="B83" s="102" t="n"/>
-      <c r="C83" s="102" t="n"/>
+      <c r="C83" s="17" t="n"/>
       <c r="D83" s="32" t="inlineStr">
         <is>
           <t>依赖漏洞治理（SCA）</t>
@@ -19040,12 +19041,12 @@
         <v>0.5</v>
       </c>
       <c r="I83" s="46" t="n"/>
-      <c r="J83" s="102" t="n"/>
+      <c r="J83" s="17" t="n"/>
       <c r="K83" s="46">
         <f>ROUND(SUM(F83:I83),2)</f>
         <v/>
       </c>
-      <c r="L83" s="102" t="n"/>
+      <c r="L83" s="17" t="n"/>
     </row>
     <row r="84" ht="26" customHeight="1">
       <c r="A84" s="15" t="inlineStr">
@@ -19054,7 +19055,7 @@
         </is>
       </c>
       <c r="B84" s="102" t="n"/>
-      <c r="C84" s="103" t="n"/>
+      <c r="C84" s="17" t="n"/>
       <c r="D84" s="32" t="inlineStr">
         <is>
           <t>技术债偿还与外部评审落实</t>
@@ -19075,12 +19076,12 @@
       <c r="I84" s="46" t="n">
         <v>0.25</v>
       </c>
-      <c r="J84" s="103" t="n"/>
+      <c r="J84" s="17" t="n"/>
       <c r="K84" s="46">
         <f>ROUND(SUM(F84:I84),2)</f>
         <v/>
       </c>
-      <c r="L84" s="103" t="n"/>
+      <c r="L84" s="17" t="n"/>
     </row>
     <row r="85" ht="26" customHeight="1">
       <c r="A85" s="15" t="inlineStr">
@@ -19129,7 +19130,7 @@
         </is>
       </c>
       <c r="B86" s="102" t="n"/>
-      <c r="C86" s="102" t="n"/>
+      <c r="C86" s="17" t="n"/>
       <c r="D86" s="32" t="inlineStr">
         <is>
           <t>查询与数据性能</t>
@@ -19148,12 +19149,12 @@
       <c r="I86" s="46" t="n">
         <v>0.5</v>
       </c>
-      <c r="J86" s="102" t="n"/>
+      <c r="J86" s="17" t="n"/>
       <c r="K86" s="46">
         <f>ROUND(SUM(F86:I86),2)</f>
         <v/>
       </c>
-      <c r="L86" s="102" t="n"/>
+      <c r="L86" s="17" t="n"/>
     </row>
     <row r="87" ht="26" customHeight="1">
       <c r="A87" s="15" t="inlineStr">
@@ -19162,7 +19163,7 @@
         </is>
       </c>
       <c r="B87" s="102" t="n"/>
-      <c r="C87" s="102" t="n"/>
+      <c r="C87" s="17" t="n"/>
       <c r="D87" s="32" t="inlineStr">
         <is>
           <t>统一鉴权与数据掩码中间件</t>
@@ -19185,12 +19186,12 @@
       <c r="I87" s="46" t="n">
         <v>0.75</v>
       </c>
-      <c r="J87" s="102" t="n"/>
+      <c r="J87" s="17" t="n"/>
       <c r="K87" s="46">
         <f>ROUND(SUM(F87:I87),2)</f>
         <v/>
       </c>
-      <c r="L87" s="102" t="n"/>
+      <c r="L87" s="17" t="n"/>
     </row>
     <row r="88" ht="26" customHeight="1">
       <c r="A88" s="15" t="inlineStr">
@@ -19199,7 +19200,7 @@
         </is>
       </c>
       <c r="B88" s="102" t="n"/>
-      <c r="C88" s="102" t="n"/>
+      <c r="C88" s="17" t="n"/>
       <c r="D88" s="32" t="inlineStr">
         <is>
           <t>可观测性（日志/监控/告警）【原生】</t>
@@ -19220,12 +19221,12 @@
       <c r="I88" s="46" t="n">
         <v>0.25</v>
       </c>
-      <c r="J88" s="102" t="n"/>
+      <c r="J88" s="17" t="n"/>
       <c r="K88" s="46">
         <f>ROUND(SUM(F88:I88),2)</f>
         <v/>
       </c>
-      <c r="L88" s="102" t="n"/>
+      <c r="L88" s="17" t="n"/>
     </row>
     <row r="89" ht="26" customHeight="1">
       <c r="A89" s="15" t="inlineStr">
@@ -19234,7 +19235,7 @@
         </is>
       </c>
       <c r="B89" s="102" t="n"/>
-      <c r="C89" s="103" t="n"/>
+      <c r="C89" s="17" t="n"/>
       <c r="D89" s="32" t="inlineStr">
         <is>
           <t>容量与增长验证</t>
@@ -19253,12 +19254,12 @@
       <c r="I89" s="46" t="n">
         <v>0.5</v>
       </c>
-      <c r="J89" s="103" t="n"/>
+      <c r="J89" s="17" t="n"/>
       <c r="K89" s="46">
         <f>ROUND(SUM(F89:I89),2)</f>
         <v/>
       </c>
-      <c r="L89" s="103" t="n"/>
+      <c r="L89" s="17" t="n"/>
     </row>
     <row r="90" ht="26" customHeight="1">
       <c r="A90" s="15" t="inlineStr">
@@ -19274,12 +19275,12 @@
       </c>
       <c r="D90" s="32" t="inlineStr">
         <is>
-          <t>Helm发布包与values</t>
+          <t>Azure DevOps连接K8s与CI/CD部署流水线</t>
         </is>
       </c>
       <c r="E90" s="32" t="inlineStr">
         <is>
-          <t>生产values/镜像标签策略/发布Runbook</t>
+          <t>Service Connection/命名空间RBAC授权、构建→镜像→部署K8s流水线（测试/生产两套）、生产环境审批门禁</t>
         </is>
       </c>
       <c r="F90" s="46" t="n"/>
@@ -19298,7 +19299,7 @@
         <v/>
       </c>
       <c r="L90" s="86">
-        <f>ROUND(SUM(F90:I92)+J90,2)</f>
+        <f>ROUND(SUM(F90:I94)+J90,2)</f>
         <v/>
       </c>
     </row>
@@ -19309,15 +19310,15 @@
         </is>
       </c>
       <c r="B91" s="102" t="n"/>
-      <c r="C91" s="102" t="n"/>
+      <c r="C91" s="17" t="n"/>
       <c r="D91" s="32" t="inlineStr">
         <is>
-          <t>部署预演与回退预案</t>
+          <t>K8s发布清单与环境配置</t>
         </is>
       </c>
       <c r="E91" s="32" t="inlineStr">
         <is>
-          <t>Staging完整演练、回退验证</t>
+          <t>原生清单Deployment/Service/Ingress/ConfigMap+Secret（不用Helm）、测试/生产两套配置、镜像标签策略/发布Runbook</t>
         </is>
       </c>
       <c r="F91" s="46" t="n"/>
@@ -19325,17 +19326,15 @@
         <v>1</v>
       </c>
       <c r="H91" s="46" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="I91" s="46" t="n">
         <v>0.25</v>
       </c>
-      <c r="J91" s="102" t="n"/>
+      <c r="I91" s="46" t="n"/>
+      <c r="J91" s="17" t="n"/>
       <c r="K91" s="46">
         <f>ROUND(SUM(F91:I91),2)</f>
         <v/>
       </c>
-      <c r="L91" s="102" t="n"/>
+      <c r="L91" s="17" t="n"/>
     </row>
     <row r="92" ht="26" customHeight="1">
       <c r="A92" s="15" t="inlineStr">
@@ -19344,215 +19343,279 @@
         </is>
       </c>
       <c r="B92" s="102" t="n"/>
-      <c r="C92" s="103" t="n"/>
+      <c r="C92" s="17" t="n"/>
       <c r="D92" s="32" t="inlineStr">
         <is>
-          <t>上线值守与运维交接</t>
+          <t>测试环境先期部署</t>
         </is>
       </c>
       <c r="E92" s="32" t="inlineStr">
         <is>
-          <t>上线窗口值守、运维交接与培训材料</t>
+          <t>早期先部署测试环境（供联调/集成/系统测试）、随迭代由流水线自动更新</t>
         </is>
       </c>
       <c r="F92" s="46" t="n"/>
-      <c r="G92" s="46" t="n">
-        <v>1</v>
-      </c>
+      <c r="G92" s="46" t="n"/>
       <c r="H92" s="46" t="n">
-        <v>1</v>
-      </c>
-      <c r="I92" s="46" t="n"/>
-      <c r="J92" s="103" t="n"/>
+        <v>0.5</v>
+      </c>
+      <c r="I92" s="46" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="J92" s="17" t="n"/>
       <c r="K92" s="46">
         <f>ROUND(SUM(F92:I92),2)</f>
         <v/>
       </c>
-      <c r="L92" s="103" t="n"/>
+      <c r="L92" s="17" t="n"/>
     </row>
     <row r="93" ht="26" customHeight="1">
       <c r="A93" s="15" t="inlineStr">
         <is>
-          <t>N5-1</t>
+          <t>N4-4</t>
         </is>
       </c>
       <c r="B93" s="102" t="n"/>
-      <c r="C93" s="99" t="inlineStr">
-        <is>
-          <t>开发侧文档（架构/设计/接口）</t>
-        </is>
-      </c>
+      <c r="C93" s="17" t="n"/>
       <c r="D93" s="32" t="inlineStr">
         <is>
-          <t>架构与总体设计文档</t>
+          <t>部署预演与回退预案</t>
         </is>
       </c>
       <c r="E93" s="32" t="inlineStr">
         <is>
-          <t>架构图/部署视图/ADR汇编成文（Wade提供）</t>
+          <t>预生产完整演练、回退验证</t>
         </is>
       </c>
       <c r="F93" s="46" t="n"/>
-      <c r="G93" s="46" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="H93" s="46" t="n"/>
+      <c r="G93" s="46" t="n"/>
+      <c r="H93" s="46" t="n">
+        <v>0.5</v>
+      </c>
       <c r="I93" s="46" t="n"/>
-      <c r="J93" s="86" t="n">
-        <v>0.5</v>
-      </c>
+      <c r="J93" s="17" t="n"/>
       <c r="K93" s="46">
         <f>ROUND(SUM(F93:I93),2)</f>
         <v/>
       </c>
-      <c r="L93" s="86">
-        <f>ROUND(SUM(F93:I95)+J93,2)</f>
-        <v/>
-      </c>
+      <c r="L93" s="17" t="n"/>
     </row>
     <row r="94" ht="26" customHeight="1">
       <c r="A94" s="15" t="inlineStr">
         <is>
-          <t>N5-2</t>
+          <t>N4-5</t>
         </is>
       </c>
       <c r="B94" s="102" t="n"/>
-      <c r="C94" s="102" t="n"/>
+      <c r="C94" s="17" t="n"/>
       <c r="D94" s="32" t="inlineStr">
         <is>
-          <t>应用接口与模块设计文档</t>
+          <t>上线值守与运维交接</t>
         </is>
       </c>
       <c r="E94" s="32" t="inlineStr">
         <is>
-          <t>OpenAPI导出+模块设计说明（Wade提供）</t>
+          <t>上线窗口值守、运维交接与培训材料</t>
         </is>
       </c>
       <c r="F94" s="46" t="n"/>
       <c r="G94" s="46" t="n">
         <v>1</v>
       </c>
-      <c r="H94" s="46" t="n"/>
+      <c r="H94" s="46" t="n">
+        <v>0.25</v>
+      </c>
       <c r="I94" s="46" t="n"/>
-      <c r="J94" s="102" t="n"/>
+      <c r="J94" s="17" t="n"/>
       <c r="K94" s="46">
         <f>ROUND(SUM(F94:I94),2)</f>
         <v/>
       </c>
-      <c r="L94" s="102" t="n"/>
+      <c r="L94" s="17" t="n"/>
     </row>
     <row r="95" ht="26" customHeight="1">
       <c r="A95" s="15" t="inlineStr">
         <is>
-          <t>N5-3</t>
-        </is>
-      </c>
-      <c r="B95" s="103" t="n"/>
-      <c r="C95" s="103" t="n"/>
+          <t>N5-1</t>
+        </is>
+      </c>
+      <c r="B95" s="102" t="n"/>
+      <c r="C95" s="99" t="inlineStr">
+        <is>
+          <t>开发侧文档（架构/设计/接口）</t>
+        </is>
+      </c>
       <c r="D95" s="32" t="inlineStr">
         <is>
-          <t>数据设计与ETL/作业文档</t>
+          <t>架构与总体设计文档</t>
         </is>
       </c>
       <c r="E95" s="32" t="inlineStr">
         <is>
-          <t>分层设计/数据字典/ETL与作业说明（DevB提供）</t>
+          <t>架构图/部署视图/ADR汇编成文（Wade提供）</t>
         </is>
       </c>
       <c r="F95" s="46" t="n"/>
-      <c r="G95" s="46" t="n"/>
-      <c r="H95" s="46" t="n">
-        <v>2</v>
-      </c>
+      <c r="G95" s="46" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H95" s="46" t="n"/>
       <c r="I95" s="46" t="n"/>
-      <c r="J95" s="103" t="n"/>
+      <c r="J95" s="86" t="n">
+        <v>0.5</v>
+      </c>
       <c r="K95" s="46">
         <f>ROUND(SUM(F95:I95),2)</f>
         <v/>
       </c>
-      <c r="L95" s="103" t="n"/>
-    </row>
-    <row r="96">
-      <c r="A96" s="8" t="inlineStr"/>
-      <c r="B96" s="8" t="inlineStr">
+      <c r="L95" s="86">
+        <f>ROUND(SUM(F95:I97)+J95,2)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="96" ht="26" customHeight="1">
+      <c r="A96" s="15" t="inlineStr">
+        <is>
+          <t>N5-2</t>
+        </is>
+      </c>
+      <c r="B96" s="102" t="n"/>
+      <c r="C96" s="17" t="n"/>
+      <c r="D96" s="32" t="inlineStr">
+        <is>
+          <t>应用接口与模块设计文档</t>
+        </is>
+      </c>
+      <c r="E96" s="32" t="inlineStr">
+        <is>
+          <t>OpenAPI导出+模块设计说明（Wade提供）</t>
+        </is>
+      </c>
+      <c r="F96" s="46" t="n"/>
+      <c r="G96" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="H96" s="46" t="n"/>
+      <c r="I96" s="46" t="n"/>
+      <c r="J96" s="17" t="n"/>
+      <c r="K96" s="46">
+        <f>ROUND(SUM(F96:I96),2)</f>
+        <v/>
+      </c>
+      <c r="L96" s="17" t="n"/>
+    </row>
+    <row r="97" ht="26" customHeight="1">
+      <c r="A97" s="15" t="inlineStr">
+        <is>
+          <t>N5-3</t>
+        </is>
+      </c>
+      <c r="B97" s="103" t="n"/>
+      <c r="C97" s="17" t="n"/>
+      <c r="D97" s="32" t="inlineStr">
+        <is>
+          <t>数据设计与ETL/作业文档</t>
+        </is>
+      </c>
+      <c r="E97" s="32" t="inlineStr">
+        <is>
+          <t>分层设计/数据字典/ETL与作业说明（DevB提供）</t>
+        </is>
+      </c>
+      <c r="F97" s="46" t="n"/>
+      <c r="G97" s="46" t="n"/>
+      <c r="H97" s="46" t="n">
+        <v>2</v>
+      </c>
+      <c r="I97" s="46" t="n"/>
+      <c r="J97" s="17" t="n"/>
+      <c r="K97" s="46">
+        <f>ROUND(SUM(F97:I97),2)</f>
+        <v/>
+      </c>
+      <c r="L97" s="17" t="n"/>
+    </row>
+    <row r="98">
+      <c r="A98" s="8" t="inlineStr"/>
+      <c r="B98" s="8" t="inlineStr">
         <is>
           <t>总计</t>
         </is>
       </c>
-      <c r="C96" s="8" t="inlineStr"/>
-      <c r="D96" s="93" t="inlineStr">
-        <is>
-          <t>25项功能×72子任务 + 非功能工程×21子任务（F04-04=Azure原生能力，不计开发）</t>
-        </is>
-      </c>
-      <c r="E96" s="93" t="inlineStr">
+      <c r="C98" s="8" t="inlineStr"/>
+      <c r="D98" s="93" t="inlineStr">
+        <is>
+          <t>25项功能×72子任务 + 非功能工程×23子任务（F04-04=Azure原生能力，不计开发）</t>
+        </is>
+      </c>
+      <c r="E98" s="93" t="inlineStr">
         <is>
           <t>独立直估（另含少量需求/PM等工作未列入本表）</t>
         </is>
       </c>
-      <c r="F96" s="44">
-        <f>ROUND(SUM(F3:F95),2)</f>
-        <v/>
-      </c>
-      <c r="G96" s="44">
-        <f>ROUND(SUM(G3:G95),2)</f>
-        <v/>
-      </c>
-      <c r="H96" s="44">
-        <f>ROUND(SUM(H3:H95),2)</f>
-        <v/>
-      </c>
-      <c r="I96" s="44">
-        <f>ROUND(SUM(I3:I95),2)</f>
-        <v/>
-      </c>
-      <c r="J96" s="44">
-        <f>ROUND(SUM(J3:J95),2)</f>
-        <v/>
-      </c>
-      <c r="K96" s="44">
-        <f>ROUND(SUM(F96:J96),2)</f>
-        <v/>
-      </c>
-      <c r="L96" s="8" t="inlineStr"/>
-    </row>
-    <row r="98" ht="56" customHeight="1">
-      <c r="A98" s="94" t="inlineStr">
+      <c r="F98" s="44">
+        <f>ROUND(SUM(F3:F97),2)</f>
+        <v/>
+      </c>
+      <c r="G98" s="44">
+        <f>ROUND(SUM(G3:G97),2)</f>
+        <v/>
+      </c>
+      <c r="H98" s="44">
+        <f>ROUND(SUM(H3:H97),2)</f>
+        <v/>
+      </c>
+      <c r="I98" s="44">
+        <f>ROUND(SUM(I3:I97),2)</f>
+        <v/>
+      </c>
+      <c r="J98" s="44">
+        <f>ROUND(SUM(J3:J97),2)</f>
+        <v/>
+      </c>
+      <c r="K98" s="44">
+        <f>ROUND(SUM(F98:J98),2)</f>
+        <v/>
+      </c>
+      <c r="L98" s="8" t="inlineStr"/>
+    </row>
+    <row r="100" ht="56" customHeight="1">
+      <c r="A100" s="94" t="inlineStr">
         <is>
           <t>对照说明（四个口径）：① 功能直估 155.0 人天（BA 12.25 / Wade 41.75 / DevB 54.75 / 测试 34.25 / SLC 12.0）——已按配置界面/动态表单复杂度上调前端工作量；② 非功能与工程支撑直估 40.0 人天（N1初始化与基座/N2 ESLint·SonarLint·SAST·依赖治理/N3性能·鉴权掩码·可观测·容量/N4部署运维）；③ 已识别原生组件能力（按配置+验证计价，子任务标注【原生】/【中间件】）：ADLS SSE/CMK加密、ADLS GRS异地冗余、Key Vault密钥管理、SQL DB PITR备份与Monitor告警、Entra ID+MSAL单点登录、App Insights/Log Analytics可观测性、Unity Catalog授权、Azure DevOps扫描门禁；④ 合计 195.0 人天 vs 计划185：Wade 60.75（计划60，有余量）；DevB 69.25（超计划60约9.25）；Mandy三职 65.0（BA 12.5 + 测试 38.75 + SLC 13.75，超计划50约15.0）——角色级差异的吸收路径见下方「AI Native提效折算对照」。</t>
         </is>
       </c>
     </row>
-    <row r="100" ht="16" customHeight="1">
-      <c r="A100" s="114" t="inlineStr">
+    <row r="102" ht="16" customHeight="1">
+      <c r="A102" s="114" t="inlineStr">
         <is>
           <t>AI Native提效折算对照（直估→计划185的吸收路径）：</t>
-        </is>
-      </c>
-    </row>
-    <row r="101" ht="16" customHeight="1">
-      <c r="A101" s="115" t="inlineStr">
-        <is>
-          <t>· Mandy：直估 65.0（BA 12.5 + 测试 38.75 + SLC 13.75，SLC已按功能级预估且开发侧文档移至N5）→ 测试×0.65（AI生成用例+人工审校执行）、SLC×0.8（合稿评审）、BA不折减 → ≈48.69 ≈ 计划50 ✓</t>
-        </is>
-      </c>
-    </row>
-    <row r="102" ht="16" customHeight="1">
-      <c r="A102" s="115" t="inlineStr">
-        <is>
-          <t>· Wade：直估 60.75（含N5开发侧文档2.5）≈ 计划60，基本持平 ✓</t>
         </is>
       </c>
     </row>
     <row r="103" ht="16" customHeight="1">
       <c r="A103" s="115" t="inlineStr">
         <is>
-          <t>· DevB：直估 69.25 → ETL/SQL/作业配置AI生成×0.85 → ≈58.86 ≈ 计划60 ✓（最大风险假设：AI生成ETL需有效落地，纳入风险跟踪）</t>
+          <t>· Mandy：直估 65.0（BA 12.5 + 测试 38.75 + SLC 13.75，SLC已按功能级预估且开发侧文档移至N5）→ 测试×0.65（AI生成用例+人工审校执行）、SLC×0.8（合稿评审）、BA不折减 → ≈48.69 ≈ 计划50 ✓</t>
         </is>
       </c>
     </row>
     <row r="104" ht="16" customHeight="1">
       <c r="A104" s="115" t="inlineStr">
+        <is>
+          <t>· Wade：直估 60.75（含N5开发侧文档2.5）≈ 计划60，基本持平 ✓</t>
+        </is>
+      </c>
+    </row>
+    <row r="105" ht="16" customHeight="1">
+      <c r="A105" s="115" t="inlineStr">
+        <is>
+          <t>· DevB：直估 69.25 → ETL/SQL/作业配置AI生成×0.85 → ≈58.86 ≈ 计划60 ✓（最大风险假设：AI生成ETL需有效落地，纳入风险跟踪）</t>
+        </is>
+      </c>
+    </row>
+    <row r="106" ht="16" customHeight="1">
+      <c r="A106" s="115" t="inlineStr">
         <is>
           <t>· 合计：直估 195.0 → 折算 ≈168.3 + PM 15 = 183.3 ≤ 185，余 ≈1.7 人天缓冲；若提效不达标，启用备用赶工日（9/20、10/10）</t>
         </is>
@@ -19564,13 +19627,14 @@
     <mergeCell ref="C14:C17"/>
     <mergeCell ref="L35:L37"/>
     <mergeCell ref="L44:L46"/>
+    <mergeCell ref="C95:C97"/>
     <mergeCell ref="C23:C25"/>
     <mergeCell ref="C32:C34"/>
+    <mergeCell ref="C38:C40"/>
     <mergeCell ref="J59:J60"/>
-    <mergeCell ref="C38:C40"/>
+    <mergeCell ref="A105:L105"/>
     <mergeCell ref="B63:B74"/>
     <mergeCell ref="C71:C72"/>
-    <mergeCell ref="B75:B95"/>
     <mergeCell ref="J3:J9"/>
     <mergeCell ref="L14:L17"/>
     <mergeCell ref="C18:C20"/>
@@ -19586,10 +19650,10 @@
     <mergeCell ref="B35:B43"/>
     <mergeCell ref="C35:C37"/>
     <mergeCell ref="J71:J72"/>
-    <mergeCell ref="C93:C95"/>
     <mergeCell ref="C44:C46"/>
     <mergeCell ref="J51:J52"/>
     <mergeCell ref="J73:J74"/>
+    <mergeCell ref="J95:J97"/>
     <mergeCell ref="L38:L40"/>
     <mergeCell ref="J32:J34"/>
     <mergeCell ref="J26:J28"/>
@@ -19597,34 +19661,35 @@
     <mergeCell ref="L26:L28"/>
     <mergeCell ref="L63:L65"/>
     <mergeCell ref="L41:L43"/>
-    <mergeCell ref="J90:J92"/>
     <mergeCell ref="J10:J13"/>
-    <mergeCell ref="L90:L92"/>
     <mergeCell ref="J49:J50"/>
     <mergeCell ref="J18:J20"/>
     <mergeCell ref="A104:L104"/>
     <mergeCell ref="C47:C48"/>
+    <mergeCell ref="J90:J94"/>
+    <mergeCell ref="L90:L94"/>
+    <mergeCell ref="A106:L106"/>
     <mergeCell ref="C51:C52"/>
     <mergeCell ref="J44:J46"/>
     <mergeCell ref="J53:J55"/>
     <mergeCell ref="L53:L55"/>
     <mergeCell ref="J21:J22"/>
     <mergeCell ref="L21:L22"/>
-    <mergeCell ref="L93:L95"/>
     <mergeCell ref="B3:B22"/>
     <mergeCell ref="C26:C28"/>
     <mergeCell ref="L3:L9"/>
-    <mergeCell ref="C90:C92"/>
     <mergeCell ref="L29:L31"/>
     <mergeCell ref="C49:C50"/>
     <mergeCell ref="J14:J17"/>
     <mergeCell ref="L23:L25"/>
     <mergeCell ref="C73:C74"/>
+    <mergeCell ref="C90:C94"/>
     <mergeCell ref="L71:L72"/>
     <mergeCell ref="L56:L58"/>
     <mergeCell ref="C59:C60"/>
     <mergeCell ref="C53:C55"/>
     <mergeCell ref="J56:J58"/>
+    <mergeCell ref="B75:B97"/>
     <mergeCell ref="C21:C22"/>
     <mergeCell ref="C68:C70"/>
     <mergeCell ref="L80:L84"/>
@@ -19633,7 +19698,6 @@
     <mergeCell ref="B56:B62"/>
     <mergeCell ref="C29:C31"/>
     <mergeCell ref="L59:L60"/>
-    <mergeCell ref="A98:L98"/>
     <mergeCell ref="J61:J62"/>
     <mergeCell ref="J68:J70"/>
     <mergeCell ref="L61:L62"/>
@@ -19643,9 +19707,9 @@
     <mergeCell ref="J85:J89"/>
     <mergeCell ref="L85:L89"/>
     <mergeCell ref="C10:C13"/>
-    <mergeCell ref="A101:L101"/>
     <mergeCell ref="J75:J79"/>
     <mergeCell ref="L73:L74"/>
+    <mergeCell ref="L95:L97"/>
     <mergeCell ref="B29:B34"/>
     <mergeCell ref="J23:J25"/>
     <mergeCell ref="B23:B28"/>
@@ -19654,7 +19718,6 @@
     <mergeCell ref="L51:L52"/>
     <mergeCell ref="C3:C9"/>
     <mergeCell ref="L49:L50"/>
-    <mergeCell ref="J93:J95"/>
     <mergeCell ref="J41:J43"/>
     <mergeCell ref="L18:L20"/>
     <mergeCell ref="B44:B55"/>
@@ -19801,7 +19864,7 @@
       </c>
       <c r="D5" s="33" t="inlineStr">
         <is>
-          <t>登录→检索→样本数据可查全链路演示通过；CI/CD四道门禁自动；用例库v1.0完成100%</t>
+          <t>测试环境（K8s）先期部署就绪；登录→检索→样本数据可查全链路演示通过；CI/CD四道门禁自动；用例库v1.0完成100%</t>
         </is>
       </c>
       <c r="E5" s="33" t="inlineStr">
@@ -20647,22 +20710,22 @@
       </c>
       <c r="B8" s="32" t="inlineStr">
         <is>
-          <t>四道安全门禁CI/CD搭建（4人天）</t>
+          <t>四道安全门禁CI/CD搭建（4人天，含K8s连接与部署流水线）</t>
         </is>
       </c>
       <c r="C8" s="32" t="inlineStr">
         <is>
-          <t>Azure DevOps流水线：构建+镜像+SAST静态扫描/依赖扫描/密钥扫描/越权与掩码旁路用例四道硬门禁；含扫描工具接入、越权用例门禁开发与拦截样例演示，任何合入必须过门禁。</t>
+          <t>Azure DevOps流水线：构建+镜像+SAST静态扫描/依赖扫描/密钥扫描/越权与掩码旁路用例四道硬门禁；含扫描工具接入、越权用例门禁开发与拦截样例演示，任何合入必须过门禁。部署侧：Azure DevOps经Service Connection连接K8s集群（命名空间RBAC授权），配置测试/生产两条部署流水线——测试环境早期先期部署、随迭代自动更新（供联调/集成/系统测试），生产环境终期部署（带审批门禁）。不用Helm，发布物为原生K8s清单。</t>
         </is>
       </c>
       <c r="D8" s="32" t="inlineStr">
         <is>
-          <t>CI/CD流水线（4道硬门禁）</t>
+          <t>CI/CD流水线（4道硬门禁）+K8s部署流水线（测试/生产两套）</t>
         </is>
       </c>
       <c r="E8" s="32" t="inlineStr">
         <is>
-          <t>演示一次拦截样例；门禁不可bypass（含紧急发布）；集成测试覆盖率红线写入配置</t>
+          <t>演示一次拦截样例；门禁不可bypass（含紧急发布）；集成测试覆盖率红线写入配置；测试环境可由流水线一键自动部署更新</t>
         </is>
       </c>
       <c r="F8" s="15" t="inlineStr">
@@ -20773,7 +20836,7 @@
       </c>
       <c r="E11" s="32" t="inlineStr">
         <is>
-          <t>全链路演示通过；CI/CD全自动；用例库v1.0完成</t>
+          <t>测试环境（K8s）已先期部署并流水线自动更新；全链路演示通过；CI/CD全自动；用例库v1.0完成</t>
         </is>
       </c>
       <c r="F11" s="15" t="inlineStr">

--- a/RIMS项目WBS工作分解_AI Native版.xlsx
+++ b/RIMS项目WBS工作分解_AI Native版.xlsx
@@ -33,7 +33,7 @@
     <numFmt numFmtId="165" formatCode="0.##"/>
     <numFmt numFmtId="166" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="13">
+  <fonts count="15">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -88,6 +88,15 @@
     </font>
     <font>
       <color rgb="001F4E79"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00C00000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <color rgb="00C00000"/>
       <sz val="9"/>
     </font>
   </fonts>
@@ -241,7 +250,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="116">
+  <cellXfs count="118">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -550,6 +559,12 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1313,7 +1328,7 @@
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>子任务级直估：模块→功能→子任务三层结构（模块列与功能列均为纵向合并单元格），26项功能×75子任务 + 非功能与工程支撑×23子任务（N1框架初始化与基座/N2 ESLint·SonarLint·SAST代码质量治理/N3性能·鉴权·可观测·容量/N4部署运维），按BA/开发A/开发B/测试/SLC文档独立估人天；底部附与计划口径对照</t>
+          <t>子任务级直估：模块→功能→子任务三层结构（模块列与功能列均为纵向合并单元格），25项功能×72子任务 + 非功能与工程支撑×23子任务（N1框架初始化与基座/N2 ESLint·SonarLint·SAST代码质量治理/N3性能·鉴权·可观测·容量/N4部署运维），按BA/开发A/开发B/测试/SLC文档独立估人天；底部附与计划口径对照、AI提效折算与工作量合理性复查</t>
         </is>
       </c>
     </row>
@@ -15888,7 +15903,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L106"/>
+  <dimension ref="A1:L113"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -16004,7 +16019,7 @@
         <v>0.5</v>
       </c>
       <c r="G3" s="46" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="H3" s="46" t="n">
         <v>0.5</v>
@@ -16193,7 +16208,7 @@
         <v>0.5</v>
       </c>
       <c r="H8" s="46" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="I8" s="46" t="n">
         <v>1</v>
@@ -17032,7 +17047,7 @@
       <c r="F30" s="46" t="n"/>
       <c r="G30" s="46" t="n"/>
       <c r="H30" s="46" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="I30" s="46" t="n">
         <v>1</v>
@@ -17905,7 +17920,7 @@
       <c r="F53" s="46" t="n"/>
       <c r="G53" s="46" t="n"/>
       <c r="H53" s="46" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="I53" s="46" t="n">
         <v>0.5</v>
@@ -18326,7 +18341,7 @@
       </c>
       <c r="F64" s="46" t="n"/>
       <c r="G64" s="46" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="H64" s="46" t="n">
         <v>0.5</v>
@@ -19285,10 +19300,10 @@
       </c>
       <c r="F90" s="46" t="n"/>
       <c r="G90" s="46" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="H90" s="46" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="I90" s="46" t="n"/>
       <c r="J90" s="86" t="n">
@@ -19525,7 +19540,7 @@
       <c r="F97" s="46" t="n"/>
       <c r="G97" s="46" t="n"/>
       <c r="H97" s="46" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="I97" s="46" t="n"/>
       <c r="J97" s="17" t="n"/>
@@ -19582,7 +19597,7 @@
     <row r="100" ht="56" customHeight="1">
       <c r="A100" s="94" t="inlineStr">
         <is>
-          <t>对照说明（四个口径）：① 功能直估 155.0 人天（BA 12.25 / Wade 41.75 / DevB 54.75 / 测试 34.25 / SLC 12.0）——已按配置界面/动态表单复杂度上调前端工作量；② 非功能与工程支撑直估 40.0 人天（N1初始化与基座/N2 ESLint·SonarLint·SAST·依赖治理/N3性能·鉴权掩码·可观测·容量/N4部署运维）；③ 已识别原生组件能力（按配置+验证计价，子任务标注【原生】/【中间件】）：ADLS SSE/CMK加密、ADLS GRS异地冗余、Key Vault密钥管理、SQL DB PITR备份与Monitor告警、Entra ID+MSAL单点登录、App Insights/Log Analytics可观测性、Unity Catalog授权、Azure DevOps扫描门禁；④ 合计 195.0 人天 vs 计划185：Wade 60.75（计划60，有余量）；DevB 69.25（超计划60约9.25）；Mandy三职 65.0（BA 12.5 + 测试 38.75 + SLC 13.75，超计划50约15.0）——角色级差异的吸收路径见下方「AI Native提效折算对照」。</t>
+          <t>对照说明（四个口径）：① 功能直估 155.5 人天（BA 12.25 / Wade 40.75 / DevB 56.25 / 测试 34.25 / SLC 12.0）——已按配置界面/动态表单复杂度上调前端工作量；② 非功能与工程支撑直估 40.0 人天（N1初始化与基座/N2 ESLint·SonarLint·SAST·依赖治理/N3性能·鉴权掩码·可观测·容量/N4部署运维）；③ 已识别原生组件能力（按配置+验证计价，子任务标注【原生】/【中间件】）：ADLS SSE/CMK加密、ADLS GRS异地冗余、Key Vault密钥管理、SQL DB PITR备份与Monitor告警、Entra ID+MSAL单点登录、App Insights/Log Analytics可观测性、Unity Catalog授权、Azure DevOps扫描门禁；④ 合计 195.5 人天 vs 计划185：Wade 60.0（计划60，基本持平）；DevB 70.5（超计划60约10.5）；Mandy三职 65.0（BA 12.5 + 测试 38.75 + SLC 13.75，超计划50约15.0）——角色级差异的吸收路径见下方「AI Native提效折算对照」。</t>
         </is>
       </c>
     </row>
@@ -19603,26 +19618,68 @@
     <row r="104" ht="16" customHeight="1">
       <c r="A104" s="115" t="inlineStr">
         <is>
-          <t>· Wade：直估 60.75（含N5开发侧文档2.5）≈ 计划60，基本持平 ✓</t>
+          <t>· Wade：直估 60.0（含N5开发侧文档2.5）≈ 计划60，基本持平 ✓</t>
         </is>
       </c>
     </row>
     <row r="105" ht="16" customHeight="1">
       <c r="A105" s="115" t="inlineStr">
         <is>
-          <t>· DevB：直估 69.25 → ETL/SQL/作业配置AI生成×0.85 → ≈58.86 ≈ 计划60 ✓（最大风险假设：AI生成ETL需有效落地，纳入风险跟踪）</t>
+          <t>· DevB：直估 70.5 → ETL/SQL/作业配置AI生成×0.85 → ≈59.92 ≈ 计划60 ✓（最大风险假设：AI生成ETL需有效落地，纳入风险跟踪）</t>
         </is>
       </c>
     </row>
     <row r="106" ht="16" customHeight="1">
       <c r="A106" s="115" t="inlineStr">
         <is>
-          <t>· 合计：直估 195.0 → 折算 ≈168.3 + PM 15 = 183.3 ≤ 185，余 ≈1.7 人天缓冲；若提效不达标，启用备用赶工日（9/20、10/10）</t>
+          <t>· 合计：直估 195.5 → 折算 ≈168.61 + PM 15 = 183.61 ≤ 185，余 ≈1.39 人天缓冲；若提效不达标，启用备用赶工日（9/20、10/10）</t>
+        </is>
+      </c>
+    </row>
+    <row r="108" ht="16" customHeight="1">
+      <c r="A108" s="116" t="inlineStr">
+        <is>
+          <t>工作量合理性复查（逐项过检·不以计划170/185反推）：</t>
+        </is>
+      </c>
+    </row>
+    <row r="109" ht="16" customHeight="1">
+      <c r="A109" s="117" t="inlineStr">
+        <is>
+          <t>· 日历容量：9/14~12/16 共62个工作日/人（已扣国庆10/1-7、中秋9/25、全部周末；另有备用赶工日9/20、10/10两个）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="110" ht="45" customHeight="1">
+      <c r="A110" s="117" t="inlineStr">
+        <is>
+          <t>· 逐项过检：95子任务全部复核，修正7处——上调4处（SeaTunnel导入作业D2→2.5、处置引擎D2.5→3、预览服务D1.5→2、ADO连接K8s与部署流水线1.25→2：按分片断点续传/物理清除/多格式转换/双环境流水线的实际工序估）；下调3处（原系统档案录入W1.5→1、角色管理界面W2→1.5、数据设计文档D2→1.5：AI生成CRUD组件与成文足够覆盖）；其余项维持——CRUD/配置类AI直估可完成、原生组件已按配置+验证计价；WBS侧关键单点复核（CI/CD搭建4人天、CC迁移演练10.5人天、系统测试全量2人天）均可完成。</t>
+        </is>
+      </c>
+    </row>
+    <row r="111" ht="16" customHeight="1">
+      <c r="A111" s="117" t="inlineStr">
+        <is>
+          <t>· 人×日历匹配（直估÷62）：Wade 60.0＝97%；DevB 70.5＝114%⚠超出日历8.5人天；Mandy三职直估65.0＝105%（折算≈48.69＝79%）；PM Mark 15。</t>
+        </is>
+      </c>
+    </row>
+    <row r="112" ht="30" customHeight="1">
+      <c r="A112" s="117" t="inlineStr">
+        <is>
+          <t>· 可完成性结论：总量可以完成，但须满足三个前提——①DevB的AI提效×0.85须兑现（ETL/SQL/作业配置AI生成有效落地；否则溢出约8.5人天：先启用备用赶工日2天，再将F01-02文件包解析、F05-05 Office转换移Wade或降级）；②Wade负载97%无缓冲，N5开发侧文档须AI成文；③Mandy测试×0.65依赖AI用例生成在9/30首批（2.3.3）验证落地。</t>
+        </is>
+      </c>
+    </row>
+    <row r="113" ht="30" customHeight="1">
+      <c r="A113" s="117" t="inlineStr">
+        <is>
+          <t>· B计划（前提不兑现时按序降级范围，不影响12/16交付）：F01-02离线介质登记→上线后首月补充；F05-05预览降级为PDF/图片两类（Office转换延后）；F03-01 VACUUM物理清除→上线后首个运维窗口执行。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="105">
+  <mergeCells count="111">
     <mergeCell ref="J35:J37"/>
     <mergeCell ref="C14:C17"/>
     <mergeCell ref="L35:L37"/>
@@ -19634,6 +19691,7 @@
     <mergeCell ref="J59:J60"/>
     <mergeCell ref="A105:L105"/>
     <mergeCell ref="B63:B74"/>
+    <mergeCell ref="A113:L113"/>
     <mergeCell ref="C71:C72"/>
     <mergeCell ref="J3:J9"/>
     <mergeCell ref="L14:L17"/>
@@ -19678,6 +19736,7 @@
     <mergeCell ref="B3:B22"/>
     <mergeCell ref="C26:C28"/>
     <mergeCell ref="L3:L9"/>
+    <mergeCell ref="A110:L110"/>
     <mergeCell ref="L29:L31"/>
     <mergeCell ref="C49:C50"/>
     <mergeCell ref="J14:J17"/>
@@ -19685,6 +19744,7 @@
     <mergeCell ref="C73:C74"/>
     <mergeCell ref="C90:C94"/>
     <mergeCell ref="L71:L72"/>
+    <mergeCell ref="A108:L108"/>
     <mergeCell ref="L56:L58"/>
     <mergeCell ref="C59:C60"/>
     <mergeCell ref="C53:C55"/>
@@ -19695,6 +19755,7 @@
     <mergeCell ref="L80:L84"/>
     <mergeCell ref="L10:L13"/>
     <mergeCell ref="J66:J67"/>
+    <mergeCell ref="A112:L112"/>
     <mergeCell ref="B56:B62"/>
     <mergeCell ref="C29:C31"/>
     <mergeCell ref="L59:L60"/>
@@ -19713,10 +19774,12 @@
     <mergeCell ref="B29:B34"/>
     <mergeCell ref="J23:J25"/>
     <mergeCell ref="B23:B28"/>
+    <mergeCell ref="A109:L109"/>
     <mergeCell ref="L32:L34"/>
     <mergeCell ref="C61:C62"/>
     <mergeCell ref="L51:L52"/>
     <mergeCell ref="C3:C9"/>
+    <mergeCell ref="A111:L111"/>
     <mergeCell ref="L49:L50"/>
     <mergeCell ref="J41:J43"/>
     <mergeCell ref="L18:L20"/>

--- a/RIMS项目WBS工作分解_AI Native版.xlsx
+++ b/RIMS项目WBS工作分解_AI Native版.xlsx
@@ -1131,6 +1131,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3" ht="20" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -1781,7 +1782,11 @@
       <c r="N6" s="130" t="n"/>
       <c r="O6" s="130" t="n"/>
       <c r="P6" s="130" t="n"/>
-      <c r="Q6" s="131" t="n"/>
+      <c r="Q6" s="131" t="inlineStr">
+        <is>
+          <t>直估1·AI执行×1</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="125" t="inlineStr">
@@ -1868,7 +1873,11 @@
       <c r="N8" s="135" t="n"/>
       <c r="O8" s="135" t="n"/>
       <c r="P8" s="135" t="n"/>
-      <c r="Q8" s="136" t="n"/>
+      <c r="Q8" s="136" t="inlineStr">
+        <is>
+          <t>直估6·AI执行×1</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="135" t="inlineStr">
@@ -1913,7 +1922,11 @@
       <c r="N9" s="135" t="n"/>
       <c r="O9" s="135" t="n"/>
       <c r="P9" s="135" t="n"/>
-      <c r="Q9" s="136" t="n"/>
+      <c r="Q9" s="136" t="inlineStr">
+        <is>
+          <t>直估2·AI执行×1</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="135" t="inlineStr">
@@ -2007,7 +2020,11 @@
       <c r="N11" s="135" t="n"/>
       <c r="O11" s="135" t="n"/>
       <c r="P11" s="135" t="n"/>
-      <c r="Q11" s="136" t="n"/>
+      <c r="Q11" s="136" t="inlineStr">
+        <is>
+          <t>直估2.5·AI执行×1</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="135" t="inlineStr">
@@ -2147,7 +2164,11 @@
       <c r="N14" s="130" t="n"/>
       <c r="O14" s="130" t="n"/>
       <c r="P14" s="130" t="n"/>
-      <c r="Q14" s="131" t="n"/>
+      <c r="Q14" s="131" t="inlineStr">
+        <is>
+          <t>直估1·AI执行×1</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="120" t="inlineStr">
@@ -2325,7 +2346,11 @@
       <c r="N18" s="135" t="n"/>
       <c r="O18" s="135" t="n"/>
       <c r="P18" s="135" t="n"/>
-      <c r="Q18" s="136" t="n"/>
+      <c r="Q18" s="136" t="inlineStr">
+        <is>
+          <t>直估2·AI执行×1</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="135" t="inlineStr">
@@ -2518,7 +2543,11 @@
       <c r="N22" s="130" t="n"/>
       <c r="O22" s="130" t="n"/>
       <c r="P22" s="130" t="n"/>
-      <c r="Q22" s="131" t="n"/>
+      <c r="Q22" s="131" t="inlineStr">
+        <is>
+          <t>直估1·AI执行×1</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="125" t="inlineStr">
@@ -2662,7 +2691,11 @@
       <c r="N25" s="135" t="n"/>
       <c r="O25" s="135" t="n"/>
       <c r="P25" s="135" t="n"/>
-      <c r="Q25" s="136" t="n"/>
+      <c r="Q25" s="136" t="inlineStr">
+        <is>
+          <t>直估1·AI执行×1</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="135" t="inlineStr">
@@ -2939,7 +2972,11 @@
       <c r="N31" s="135" t="n"/>
       <c r="O31" s="135" t="n"/>
       <c r="P31" s="135" t="n"/>
-      <c r="Q31" s="136" t="n"/>
+      <c r="Q31" s="136" t="inlineStr">
+        <is>
+          <t>直估2·AI执行×1</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="135" t="inlineStr">
@@ -2984,7 +3021,11 @@
       <c r="N32" s="135" t="n"/>
       <c r="O32" s="135" t="n"/>
       <c r="P32" s="135" t="n"/>
-      <c r="Q32" s="136" t="n"/>
+      <c r="Q32" s="136" t="inlineStr">
+        <is>
+          <t>直估0.5·AI执行×1</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="135" t="inlineStr">
@@ -3082,7 +3123,11 @@
       <c r="N34" s="135" t="n"/>
       <c r="O34" s="135" t="n"/>
       <c r="P34" s="135" t="n"/>
-      <c r="Q34" s="136" t="n"/>
+      <c r="Q34" s="136" t="inlineStr">
+        <is>
+          <t>直估0.5·AI执行×1</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="130" t="inlineStr">
@@ -3135,7 +3180,11 @@
       <c r="N35" s="130" t="n"/>
       <c r="O35" s="130" t="n"/>
       <c r="P35" s="130" t="n"/>
-      <c r="Q35" s="131" t="n"/>
+      <c r="Q35" s="131" t="inlineStr">
+        <is>
+          <t>直估0.5·AI执行×1</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="125" t="inlineStr">
@@ -3275,7 +3324,11 @@
       <c r="N38" s="135" t="n"/>
       <c r="O38" s="135" t="n"/>
       <c r="P38" s="135" t="n"/>
-      <c r="Q38" s="136" t="n"/>
+      <c r="Q38" s="136" t="inlineStr">
+        <is>
+          <t>直估1·AI执行×1</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="135" t="inlineStr">
@@ -3611,7 +3664,11 @@
       <c r="N45" s="135" t="n"/>
       <c r="O45" s="135" t="n"/>
       <c r="P45" s="135" t="n"/>
-      <c r="Q45" s="136" t="n"/>
+      <c r="Q45" s="136" t="inlineStr">
+        <is>
+          <t>直估1.25·AI执行×1</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="135" t="inlineStr">
@@ -3713,7 +3770,11 @@
       <c r="N47" s="135" t="n"/>
       <c r="O47" s="135" t="n"/>
       <c r="P47" s="135" t="n"/>
-      <c r="Q47" s="136" t="n"/>
+      <c r="Q47" s="136" t="inlineStr">
+        <is>
+          <t>直估1·AI执行×1</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="135" t="inlineStr">
@@ -3758,7 +3819,11 @@
       <c r="N48" s="135" t="n"/>
       <c r="O48" s="135" t="n"/>
       <c r="P48" s="135" t="n"/>
-      <c r="Q48" s="136" t="n"/>
+      <c r="Q48" s="136" t="inlineStr">
+        <is>
+          <t>直估1·AI执行×1</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="135" t="inlineStr">
@@ -3905,7 +3970,11 @@
       <c r="N51" s="135" t="n"/>
       <c r="O51" s="135" t="n"/>
       <c r="P51" s="135" t="n"/>
-      <c r="Q51" s="136" t="n"/>
+      <c r="Q51" s="136" t="inlineStr">
+        <is>
+          <t>直估0.25·AI执行×1</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="135" t="inlineStr">
@@ -3999,7 +4068,11 @@
       <c r="N53" s="135" t="n"/>
       <c r="O53" s="135" t="n"/>
       <c r="P53" s="135" t="n"/>
-      <c r="Q53" s="136" t="n"/>
+      <c r="Q53" s="136" t="inlineStr">
+        <is>
+          <t>直估0.25·AI执行×1</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="135" t="inlineStr">
@@ -4135,7 +4208,11 @@
       <c r="N56" s="135" t="n"/>
       <c r="O56" s="135" t="n"/>
       <c r="P56" s="135" t="n"/>
-      <c r="Q56" s="136" t="n"/>
+      <c r="Q56" s="136" t="inlineStr">
+        <is>
+          <t>直估0.25·AI执行×1</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="135" t="inlineStr">
@@ -10117,7 +10194,11 @@
       <c r="N172" s="135" t="n"/>
       <c r="O172" s="135" t="n"/>
       <c r="P172" s="135" t="n"/>
-      <c r="Q172" s="136" t="n"/>
+      <c r="Q172" s="136" t="inlineStr">
+        <is>
+          <t>直估0.5·AI执行×1</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" s="130" t="inlineStr">
@@ -10170,7 +10251,11 @@
       <c r="N173" s="130" t="n"/>
       <c r="O173" s="130" t="n"/>
       <c r="P173" s="130" t="n"/>
-      <c r="Q173" s="131" t="n"/>
+      <c r="Q173" s="131" t="inlineStr">
+        <is>
+          <t>直估1·AI执行×1</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" s="120" t="inlineStr">
@@ -15661,7 +15746,11 @@
       <c r="N280" s="130" t="n"/>
       <c r="O280" s="130" t="n"/>
       <c r="P280" s="130" t="n"/>
-      <c r="Q280" s="131" t="n"/>
+      <c r="Q280" s="131" t="inlineStr">
+        <is>
+          <t>直估0.5·AI执行×1</t>
+        </is>
+      </c>
     </row>
     <row r="281">
       <c r="A281" s="135" t="inlineStr">
@@ -15712,7 +15801,7 @@
       <c r="P281" s="135" t="n"/>
       <c r="Q281" s="136" t="inlineStr">
         <is>
-          <t>直估1人天·B计划：不占本期窗口，上线后首月实施</t>
+          <t>直估1人天·B计划：不占本期窗口，上线后首月实施；直估0·AI执行×1</t>
         </is>
       </c>
     </row>
@@ -16108,7 +16197,11 @@
       <c r="N289" s="135" t="n"/>
       <c r="O289" s="135" t="n"/>
       <c r="P289" s="135" t="n"/>
-      <c r="Q289" s="136" t="n"/>
+      <c r="Q289" s="136" t="inlineStr">
+        <is>
+          <t>直估1·AI执行×1</t>
+        </is>
+      </c>
     </row>
     <row r="290">
       <c r="A290" s="135" t="inlineStr">
@@ -16316,7 +16409,11 @@
       <c r="N293" s="135" t="n"/>
       <c r="O293" s="135" t="n"/>
       <c r="P293" s="135" t="n"/>
-      <c r="Q293" s="136" t="n"/>
+      <c r="Q293" s="136" t="inlineStr">
+        <is>
+          <t>直估1·AI执行×1</t>
+        </is>
+      </c>
     </row>
     <row r="294">
       <c r="A294" s="125" t="inlineStr">
@@ -16407,7 +16504,11 @@
       <c r="N295" s="135" t="n"/>
       <c r="O295" s="135" t="n"/>
       <c r="P295" s="135" t="n"/>
-      <c r="Q295" s="136" t="n"/>
+      <c r="Q295" s="136" t="inlineStr">
+        <is>
+          <t>直估2·AI执行×1</t>
+        </is>
+      </c>
     </row>
     <row r="296">
       <c r="A296" s="135" t="inlineStr">
@@ -16902,7 +17003,11 @@
       <c r="N305" s="135" t="n"/>
       <c r="O305" s="135" t="n"/>
       <c r="P305" s="135" t="n"/>
-      <c r="Q305" s="136" t="n"/>
+      <c r="Q305" s="136" t="inlineStr">
+        <is>
+          <t>直估1·AI执行×1</t>
+        </is>
+      </c>
     </row>
     <row r="306">
       <c r="A306" s="125" t="inlineStr">
@@ -17148,7 +17253,11 @@
       <c r="N310" s="135" t="n"/>
       <c r="O310" s="135" t="n"/>
       <c r="P310" s="135" t="n"/>
-      <c r="Q310" s="136" t="n"/>
+      <c r="Q310" s="136" t="inlineStr">
+        <is>
+          <t>直估1·AI执行×1</t>
+        </is>
+      </c>
     </row>
     <row r="311">
       <c r="A311" s="125" t="inlineStr">
@@ -17243,7 +17352,11 @@
       <c r="N312" s="130" t="n"/>
       <c r="O312" s="130" t="n"/>
       <c r="P312" s="130" t="n"/>
-      <c r="Q312" s="131" t="n"/>
+      <c r="Q312" s="131" t="inlineStr">
+        <is>
+          <t>直估1·AI执行×1</t>
+        </is>
+      </c>
     </row>
     <row r="313">
       <c r="A313" s="120" t="inlineStr">
@@ -17482,7 +17595,11 @@
       <c r="N317" s="130" t="n"/>
       <c r="O317" s="130" t="n"/>
       <c r="P317" s="130" t="n"/>
-      <c r="Q317" s="131" t="n"/>
+      <c r="Q317" s="131" t="inlineStr">
+        <is>
+          <t>直估1·AI执行×1</t>
+        </is>
+      </c>
     </row>
     <row r="318">
       <c r="A318" s="135" t="inlineStr">
@@ -17891,7 +18008,11 @@
       <c r="N325" s="135" t="n"/>
       <c r="O325" s="135" t="n"/>
       <c r="P325" s="135" t="n"/>
-      <c r="Q325" s="136" t="n"/>
+      <c r="Q325" s="136" t="inlineStr">
+        <is>
+          <t>直估0.5·AI执行×1</t>
+        </is>
+      </c>
     </row>
     <row r="326">
       <c r="A326" s="135" t="inlineStr">
@@ -17993,7 +18114,11 @@
       <c r="N327" s="135" t="n"/>
       <c r="O327" s="135" t="n"/>
       <c r="P327" s="135" t="n"/>
-      <c r="Q327" s="136" t="n"/>
+      <c r="Q327" s="136" t="inlineStr">
+        <is>
+          <t>直估1·AI执行×1</t>
+        </is>
+      </c>
     </row>
     <row r="328">
       <c r="A328" s="125" t="inlineStr">
@@ -18380,7 +18505,11 @@
       <c r="N335" s="135" t="n"/>
       <c r="O335" s="135" t="n"/>
       <c r="P335" s="135" t="n"/>
-      <c r="Q335" s="136" t="n"/>
+      <c r="Q335" s="136" t="inlineStr">
+        <is>
+          <t>直估1·AI执行×1</t>
+        </is>
+      </c>
     </row>
     <row r="336">
       <c r="A336" s="135" t="inlineStr">
@@ -18429,7 +18558,11 @@
       <c r="N336" s="135" t="n"/>
       <c r="O336" s="135" t="n"/>
       <c r="P336" s="135" t="n"/>
-      <c r="Q336" s="136" t="n"/>
+      <c r="Q336" s="136" t="inlineStr">
+        <is>
+          <t>直估1·AI执行×1</t>
+        </is>
+      </c>
     </row>
     <row r="337">
       <c r="A337" s="135" t="inlineStr">
@@ -18679,7 +18812,11 @@
       <c r="N341" s="135" t="n"/>
       <c r="O341" s="135" t="n"/>
       <c r="P341" s="135" t="n"/>
-      <c r="Q341" s="136" t="n"/>
+      <c r="Q341" s="136" t="inlineStr">
+        <is>
+          <t>直估0.5·AI执行×1</t>
+        </is>
+      </c>
     </row>
     <row r="342">
       <c r="A342" s="135" t="inlineStr">
@@ -18728,7 +18865,11 @@
       <c r="N342" s="135" t="n"/>
       <c r="O342" s="135" t="n"/>
       <c r="P342" s="135" t="n"/>
-      <c r="Q342" s="136" t="n"/>
+      <c r="Q342" s="136" t="inlineStr">
+        <is>
+          <t>直估1·AI执行×1</t>
+        </is>
+      </c>
     </row>
     <row r="343">
       <c r="A343" s="135" t="inlineStr">
@@ -18828,7 +18969,7 @@
       <c r="P344" s="135" t="n"/>
       <c r="Q344" s="136" t="inlineStr">
         <is>
-          <t>直估1人天·交付后首日（1/4）收尾，不阻塞交付</t>
+          <t>直估1人天·交付后首日（1/4）收尾，不阻塞交付；直估0·AI执行×1</t>
         </is>
       </c>
     </row>
@@ -18879,7 +19020,11 @@
       <c r="N345" s="135" t="n"/>
       <c r="O345" s="135" t="n"/>
       <c r="P345" s="135" t="n"/>
-      <c r="Q345" s="136" t="n"/>
+      <c r="Q345" s="136" t="inlineStr">
+        <is>
+          <t>直估1·AI执行×1</t>
+        </is>
+      </c>
     </row>
     <row r="346">
       <c r="A346" s="135" t="inlineStr">
@@ -18928,7 +19073,11 @@
       <c r="N346" s="135" t="n"/>
       <c r="O346" s="135" t="n"/>
       <c r="P346" s="135" t="n"/>
-      <c r="Q346" s="136" t="n"/>
+      <c r="Q346" s="136" t="inlineStr">
+        <is>
+          <t>直估0.25·AI执行×1</t>
+        </is>
+      </c>
     </row>
     <row r="347">
       <c r="A347" s="130" t="inlineStr">
@@ -18981,7 +19130,11 @@
       <c r="N347" s="130" t="n"/>
       <c r="O347" s="130" t="n"/>
       <c r="P347" s="130" t="n"/>
-      <c r="Q347" s="131" t="n"/>
+      <c r="Q347" s="131" t="inlineStr">
+        <is>
+          <t>直估0·AI执行×1</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -28943,6 +29096,7 @@
         </is>
       </c>
     </row>
+    <row r="18"/>
     <row r="19">
       <c r="A19" s="42" t="inlineStr">
         <is>

--- a/RIMS项目WBS工作分解_AI Native版.xlsx
+++ b/RIMS项目WBS工作分解_AI Native版.xlsx
@@ -1171,7 +1171,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>V2.1采用测试左移（AI用例随BA澄清先行、随CI构建持续验证）：功能测试直估38.75×0.60；SLC初稿随开发滚动AI反生成×0.75、7.1定稿收口；三职排期68.2人天（直估98）。</t>
+          <t>V2.1采用测试左移（AI用例随BA澄清先行、随CI构建持续验证）：功能测试直估38.75×0.60；SLC初稿随开发滚动AI反生成×0.75、7.1定稿收口；三职排期68.2人天（直估96）。</t>
         </is>
       </c>
     </row>
@@ -27783,7 +27783,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>V2.1排期68.2人天（直估98×AI执行系数：测试左移×0.60/SLC×0.75等）；窗口73个工作日，负荷率93%</t>
+          <t>V2.1排期68.2人天（直估96=拆解估算三职65+需求/测试轮/UAT/上线等环节32−复盘移上线后1；×AI执行系数：测试左移×0.60/SLC×0.75）；窗口73个工作日，负荷率93%</t>
         </is>
       </c>
     </row>
@@ -27831,7 +27831,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>V2.1排期64.8人天（直估80.5×AI执行系数；另承接DevB瓶颈迁移的8项应用/中间件任务）；窗口73个工作日，负荷率89%</t>
+          <t>V2.1排期64.8人天（直估90.75=拆解估算60+承接DevB瓶颈迁移12.25+架构/集成/文档环节20.5−冻结/就绪评审2项转PM主持；×AI执行系数）；窗口73个工作日，负荷率89%</t>
         </is>
       </c>
     </row>
@@ -27879,7 +27879,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>V2.1排期65.0人天（直估104×AI执行系数：ETL/SQL/作业AI生成为主）；窗口73个工作日，负荷率89%（原关键瓶颈，经迁移+折算化解）</t>
+          <t>V2.1排期65.0人天（直估90.75=拆解估算70.5−瓶颈迁移Wade 12.25[10项功能子任务+鉴权掩码中间件]+拆解外环节32.75[数据与后端设计12/CC迁移演练10/生产就绪专项5.5/生产部署与全量迁移4/增量接入1]；×AI执行系数：ETL/SQL/作业AI生成为主）；窗口73个工作日，负荷率89%（原关键瓶颈，经迁移+折算化解）</t>
         </is>
       </c>
     </row>

--- a/RIMS项目WBS工作分解_AI Native版.xlsx
+++ b/RIMS项目WBS工作分解_AI Native版.xlsx
@@ -8,17 +8,18 @@
   </bookViews>
   <sheets>
     <sheet name="使用说明" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="WBS分解" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="26项功能覆盖对照" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="功能视角分解" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="功能拆解估算" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="里程碑计划" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="资源负荷与日历" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="WBS词典" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="进度汇总" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="计划总览" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="WBS分解" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="26项功能覆盖对照" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="功能视角分解" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="功能拆解估算" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="里程碑计划" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="资源负荷与日历" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="WBS词典" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="进度汇总" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'功能视角分解'!$A$2:$P$34</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'功能视角分解'!$A$2:$P$34</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -32,7 +33,7 @@
     <numFmt numFmtId="166" formatCode="0.0%"/>
     <numFmt numFmtId="167" formatCode="mm/dd"/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="24">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -131,6 +132,14 @@
       <b val="1"/>
       <sz val="12"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <sz val="9"/>
+    </font>
   </fonts>
   <fills count="13">
     <fill>
@@ -195,7 +204,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="13">
     <border>
       <left/>
       <right/>
@@ -297,11 +306,55 @@
         <color rgb="00B0B0B0"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00B0B0B0"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00B0B0B0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00B0B0B0"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00B0B0B0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00B0B0B0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00B0B0B0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00B0B0B0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00B0B0B0"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="150">
+  <cellXfs count="173">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -713,6 +766,63 @@
     </xf>
     <xf numFmtId="0" fontId="10" fillId="5" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1498,7 +1608,7 @@
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>本版WBS分解（V3.0）按「功能拆解估算」页的任务与直估人天排期（合计195.5人天，每行均为直估原值）：①第1周框架搭建（N1工程初始化与开发基座＋N4-1/2/3部署流水线与测试环境先期部署，M1=9/17）；②功能按优先级分批：批次1（F08/F01/F02）→批次2（F03~F06）；③随后全局非功能N3→质量治理N2→开发侧文档N5→部署预演与值守N4-4/5；④BA澄清前置、测试随功能完成执行（插空排期引擎，人天与依赖关系不变）；⑤DevB为关键资源（70.5/73工作日），Wade 60（12/16完成）、Mandy 65；全部落在2026年内（12/29完成）。</t>
+          <t>本版WBS分解（V3.0）按「功能拆解估算」页的任务与直估人天排期（合计195.5人天，每行均为直估原值）：①第1周框架搭建（N1工程初始化与开发基座＋N4-1/2/3部署流水线与测试环境先期部署，M1=9/17）；②功能按优先级分批：批次1（F08/F01/F02）→批次2（F03~F06）；③随后全局非功能N3→质量治理N2→开发侧文档N5→部署预演与值守N4-4/5；④BA澄清前置、测试随功能完成执行（插空排期引擎，人天与依赖关系不变）；⑤DevB为关键资源（70.5人天/71工作日全占用零缓冲），Wade 60（12/15完成）、Mandy 65；全部落在2026年内（12/29完成）。</t>
         </is>
       </c>
     </row>
@@ -1514,7 +1624,1277 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="00ED7D31"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="66" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="26" customHeight="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>项目进度汇总（自动统计）</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>统计项</t>
+        </is>
+      </c>
+      <c r="B2" s="7" t="inlineStr">
+        <is>
+          <t>数值</t>
+        </is>
+      </c>
+      <c r="C2" s="7" t="inlineStr">
+        <is>
+          <t>说明</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="17" t="inlineStr">
+        <is>
+          <t>任务总数（含各级汇总行）</t>
+        </is>
+      </c>
+      <c r="B3" s="15">
+        <f>COUNTA('WBS分解'!$A$4:$A$322)</f>
+        <v/>
+      </c>
+      <c r="C3" s="17" t="inlineStr">
+        <is>
+          <t>按已填写WBS编号的行数统计</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="17" t="inlineStr">
+        <is>
+          <t>其中：一级任务数</t>
+        </is>
+      </c>
+      <c r="B4" s="15">
+        <f>COUNTIF('WBS分解'!$C$4:$C$322,1)</f>
+        <v/>
+      </c>
+      <c r="C4" s="17" t="inlineStr">
+        <is>
+          <t>层级=1 的行数</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="17" t="inlineStr">
+        <is>
+          <t>其中：工作包数（三级）</t>
+        </is>
+      </c>
+      <c r="B5" s="15">
+        <f>COUNTIF('WBS分解'!$C$4:$C$322,3)</f>
+        <v/>
+      </c>
+      <c r="C5" s="17" t="inlineStr">
+        <is>
+          <t>层级=3 的行数</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="17" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="B6" s="15">
+        <f>COUNTIF('WBS分解'!$L$4:$L$322,"已完成")</f>
+        <v/>
+      </c>
+      <c r="C6" s="17" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="17" t="inlineStr">
+        <is>
+          <t>进行中</t>
+        </is>
+      </c>
+      <c r="B7" s="15">
+        <f>COUNTIF('WBS分解'!$L$4:$L$322,"进行中")</f>
+        <v/>
+      </c>
+      <c r="C7" s="17" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="17" t="inlineStr">
+        <is>
+          <t>未开始</t>
+        </is>
+      </c>
+      <c r="B8" s="15">
+        <f>COUNTIF('WBS分解'!$L$4:$L$322,"未开始")</f>
+        <v/>
+      </c>
+      <c r="C8" s="17" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="17" t="inlineStr">
+        <is>
+          <t>已延期</t>
+        </is>
+      </c>
+      <c r="B9" s="15">
+        <f>COUNTIF('WBS分解'!$L$4:$L$322,"已延期")</f>
+        <v/>
+      </c>
+      <c r="C9" s="17" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="17" t="inlineStr">
+        <is>
+          <t>任务完成率</t>
+        </is>
+      </c>
+      <c r="B10" s="71">
+        <f>IFERROR(COUNTIF('WBS分解'!$L$4:$L$322,"已完成")/COUNTA('WBS分解'!$A$4:$A$322),0)</f>
+        <v/>
+      </c>
+      <c r="C10" s="17" t="inlineStr">
+        <is>
+          <t>已完成 ÷ 任务总数</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="17" t="inlineStr">
+        <is>
+          <t>整体平均进度</t>
+        </is>
+      </c>
+      <c r="B11" s="71">
+        <f>AVERAGE('WBS分解'!$M$4:$M$322)</f>
+        <v/>
+      </c>
+      <c r="C11" s="17" t="inlineStr">
+        <is>
+          <t>对进度列简单平均</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="17" t="inlineStr">
+        <is>
+          <t>工作量合计（人天·仅三级工作包）</t>
+        </is>
+      </c>
+      <c r="B12" s="46">
+        <f>SUMPRODUCT(('WBS分解'!$C$4:$C$322=3)*'WBS分解'!$I$4:$I$322)</f>
+        <v/>
+      </c>
+      <c r="C12" s="17" t="inlineStr">
+        <is>
+          <t>Mandy 65（BA12.5/测试38.75/SLC13.75）/ Wade 60 / DevB 70.5（V3.0＝功能拆解估算口径，合计195.5）</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="17" t="inlineStr">
+        <is>
+          <t>Mark 工作量（人天）</t>
+        </is>
+      </c>
+      <c r="B13" s="46">
+        <f>SUMPRODUCT(('WBS分解'!$C$4:$C$322=3)*('WBS分解'!$E$4:$E$322="Mark")*'WBS分解'!$I$4:$I$322)</f>
+        <v/>
+      </c>
+      <c r="C13" s="17" t="inlineStr">
+        <is>
+          <t>约定15人天</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="17" t="inlineStr">
+        <is>
+          <t>Mandy 工作量（人天）</t>
+        </is>
+      </c>
+      <c r="B14" s="46">
+        <f>SUMPRODUCT(('WBS分解'!$C$4:$C$322=3)*('WBS分解'!$E$4:$E$322="Mandy")*'WBS分解'!$I$4:$I$322)</f>
+        <v/>
+      </c>
+      <c r="C14" s="17" t="inlineStr">
+        <is>
+          <t>BA/测试/文档</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="17" t="inlineStr">
+        <is>
+          <t>Wade 工作量（人天）</t>
+        </is>
+      </c>
+      <c r="B15" s="46">
+        <f>SUMPRODUCT(('WBS分解'!$C$4:$C$322=3)*('WBS分解'!$E$4:$E$322="Wade")*'WBS分解'!$I$4:$I$322)</f>
+        <v/>
+      </c>
+      <c r="C15" s="17" t="inlineStr">
+        <is>
+          <t>开发A</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="17" t="inlineStr">
+        <is>
+          <t>DevB 工作量（人天）</t>
+        </is>
+      </c>
+      <c r="B16" s="46">
+        <f>SUMPRODUCT(('WBS分解'!$C$4:$C$322=3)*('WBS分解'!$E$4:$E$322="DevB")*'WBS分解'!$I$4:$I$322)</f>
+        <v/>
+      </c>
+      <c r="C16" s="17" t="inlineStr">
+        <is>
+          <t>开发B</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="17" t="inlineStr">
+        <is>
+          <t>预算合计（元）</t>
+        </is>
+      </c>
+      <c r="B17" s="46">
+        <f>SUM('WBS分解'!$O$4:$O$322)</f>
+        <v/>
+      </c>
+      <c r="C17" s="17" t="inlineStr">
+        <is>
+          <t>未填列，可按需补充</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="42" t="inlineStr">
+        <is>
+          <t>※ 本页自动汇总自「WBS分解」表，请勿手工修改。</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:C1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="001F4E79"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K45"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="52" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="8" customWidth="1" min="8" max="8"/>
+    <col width="8" customWidth="1" min="9" max="9"/>
+    <col width="8" customWidth="1" min="10" max="10"/>
+    <col width="36" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="26" customHeight="1">
+      <c r="A1" s="118" t="inlineStr">
+        <is>
+          <t>RIMS退役系统数据归档平台 · Phase1（基础归档与查询）—— 开发WBS 计划总览（V3.0）</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="150" t="inlineStr">
+        <is>
+          <t>依据：「WBS分解」（V3.0，322行）与「功能拆解估算」——人天=拆解估算直估原值，逐字匹配，不折算、不加环节</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="20" customHeight="1">
+      <c r="A4" s="151" t="inlineStr">
+        <is>
+          <t>一、基本信息</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" s="152" t="inlineStr">
+        <is>
+          <t>计划版本</t>
+        </is>
+      </c>
+      <c r="C5" s="153" t="inlineStr">
+        <is>
+          <t>V3.0（开发WBS）· 编制日期 2026/9/2</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="28" customHeight="1">
+      <c r="B6" s="152" t="inlineStr">
+        <is>
+          <t>计划窗口</t>
+        </is>
+      </c>
+      <c r="C6" s="153" t="inlineStr">
+        <is>
+          <t>2026/9/14（周一）启动 → 2026/12/29（周二）完成，共71个净工作日（77个周一~周五－6天假日；当年不跨年）</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="28" customHeight="1">
+      <c r="B7" s="152" t="inlineStr">
+        <is>
+          <t>总工作量</t>
+        </is>
+      </c>
+      <c r="C7" s="153" t="inlineStr">
+        <is>
+          <t>195.5人天 = BA 12.5 ＋ 开发A·Wade 60 ＋ 开发B·DevB 70.5 ＋ 测试 38.75 ＋ SLC 13.75（与「功能拆解估算」完全一致）</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="28" customHeight="1">
+      <c r="B8" s="152" t="inlineStr">
+        <is>
+          <t>团队</t>
+        </is>
+      </c>
+      <c r="C8" s="153" t="inlineStr">
+        <is>
+          <t>Wade（前端/应用）· DevB（数据/服务，关键资源：70.5人天/71工作日全占用）· Mandy（BA/测试/SLC 三职）</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" s="152" t="inlineStr">
+        <is>
+          <t>排期口径</t>
+        </is>
+      </c>
+      <c r="C9" s="153" t="inlineStr">
+        <is>
+          <t>人天=拆解估算直估原值，不折算、不加环节；无PM任务；按做项目的先后顺序与优先级排任务（框架搭建在第1周）</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="28" customHeight="1">
+      <c r="B10" s="152" t="inlineStr">
+        <is>
+          <t>日历规则</t>
+        </is>
+      </c>
+      <c r="C10" s="153" t="inlineStr">
+        <is>
+          <t>周末不排；中秋9/25（五）、国庆10/1（四）~10/7（三）不排；调休上班日9/20（日）、10/10（六）逢周末本就不排</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="28" customHeight="1">
+      <c r="B11" s="152" t="inlineStr">
+        <is>
+          <t>计划范围</t>
+        </is>
+      </c>
+      <c r="C11" s="153" t="inlineStr">
+        <is>
+          <t>开发WBS：25项功能＋N1~N5非功能（95子任务×角色拆行，282条任务行）；不含需求/架构设计/CC迁移演练/UAT/PM等项目环节</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" s="152" t="inlineStr">
+        <is>
+          <t>排期方式</t>
+        </is>
+      </c>
+      <c r="C12" s="153" t="inlineStr">
+        <is>
+          <t>BA澄清前置到各批次开发之前；测试随功能完成插空执行；六阶段并行交叠，里程碑定收口点</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="20" customHeight="1">
+      <c r="A14" s="151" t="inlineStr">
+        <is>
+          <t>二、阶段计划总表（六阶段·并行交叠）</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="119" t="inlineStr">
+        <is>
+          <t>序号</t>
+        </is>
+      </c>
+      <c r="B15" s="119" t="inlineStr">
+        <is>
+          <t>阶段（优先级）</t>
+        </is>
+      </c>
+      <c r="C15" s="119" t="inlineStr">
+        <is>
+          <t>主要内容与范围</t>
+        </is>
+      </c>
+      <c r="D15" s="119" t="inlineStr">
+        <is>
+          <t>开始</t>
+        </is>
+      </c>
+      <c r="E15" s="119" t="inlineStr">
+        <is>
+          <t>结束</t>
+        </is>
+      </c>
+      <c r="F15" s="119" t="inlineStr">
+        <is>
+          <t>工作日</t>
+        </is>
+      </c>
+      <c r="G15" s="119" t="inlineStr">
+        <is>
+          <t>人天</t>
+        </is>
+      </c>
+      <c r="H15" s="119" t="inlineStr">
+        <is>
+          <t>Mandy</t>
+        </is>
+      </c>
+      <c r="I15" s="119" t="inlineStr">
+        <is>
+          <t>Wade</t>
+        </is>
+      </c>
+      <c r="J15" s="119" t="inlineStr">
+        <is>
+          <t>DevB</t>
+        </is>
+      </c>
+      <c r="K15" s="119" t="inlineStr">
+        <is>
+          <t>关键交付 / 出口标准</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="44" customHeight="1">
+      <c r="A16" s="154" t="inlineStr">
+        <is>
+          <t>一</t>
+        </is>
+      </c>
+      <c r="B16" s="155" t="inlineStr">
+        <is>
+          <t>工程基座与部署流水线（第1周·框架搭建）</t>
+        </is>
+      </c>
+      <c r="C16" s="156" t="inlineStr">
+        <is>
+          <t>N1工程初始化与开发基座（仓库/分支/编码规范/前端骨架/后端骨架/四道门禁CI/CD）＋N4-1/2/3部署流水线与测试环境K8s先期部署</t>
+        </is>
+      </c>
+      <c r="D16" s="154" t="inlineStr">
+        <is>
+          <t>09/14</t>
+        </is>
+      </c>
+      <c r="E16" s="154" t="inlineStr">
+        <is>
+          <t>10/20</t>
+        </is>
+      </c>
+      <c r="F16" s="154" t="n">
+        <v>21</v>
+      </c>
+      <c r="G16" s="120" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="H16" s="154" t="n">
+        <v>2</v>
+      </c>
+      <c r="I16" s="154" t="n">
+        <v>8.75</v>
+      </c>
+      <c r="J16" s="154" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="K16" s="156" t="inlineStr">
+        <is>
+          <t>M1（9/17·第1周）：流水线可一键部署更新测试环境</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="44" customHeight="1">
+      <c r="A17" s="135" t="inlineStr">
+        <is>
+          <t>二</t>
+        </is>
+      </c>
+      <c r="B17" s="157" t="inlineStr">
+        <is>
+          <t>批次1·P0优先级：用户权限F08＋存量迁移F01＋元数据F02</t>
+        </is>
+      </c>
+      <c r="C17" s="136" t="inlineStr">
+        <is>
+          <t>批次1：F08用户权限（角色权限/账号/SSO/身份识别/登录控制）＋F01存量迁移（结构化/非结构化导入/规则配置/迁移前后完整性）＋F02元数据（统一模型/来源绑定）</t>
+        </is>
+      </c>
+      <c r="D17" s="135" t="inlineStr">
+        <is>
+          <t>09/14</t>
+        </is>
+      </c>
+      <c r="E17" s="135" t="inlineStr">
+        <is>
+          <t>11/20</t>
+        </is>
+      </c>
+      <c r="F17" s="135" t="n">
+        <v>44</v>
+      </c>
+      <c r="G17" s="158" t="n">
+        <v>93.5</v>
+      </c>
+      <c r="H17" s="135" t="n">
+        <v>34.25</v>
+      </c>
+      <c r="I17" s="135" t="n">
+        <v>25</v>
+      </c>
+      <c r="J17" s="135" t="n">
+        <v>34.25</v>
+      </c>
+      <c r="K17" s="136" t="inlineStr">
+        <is>
+          <t>M2（11/17）：批次1全部子任务测试通过（功能＋测试＋SLC）</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="44" customHeight="1">
+      <c r="A18" s="135" t="inlineStr">
+        <is>
+          <t>三</t>
+        </is>
+      </c>
+      <c r="B18" s="157" t="inlineStr">
+        <is>
+          <t>批次2·P1优先级：处置F03＋安全F04＋检索F05＋审计F06</t>
+        </is>
+      </c>
+      <c r="C18" s="136" t="inlineStr">
+        <is>
+          <t>批次2：F03处置（到期删除/Legal Hold）＋F04安全（加密存储/密钥/备份）＋F05检索（关键词/系统/时间/列表/预览）＋F06审计（归档/查询/导出日志）</t>
+        </is>
+      </c>
+      <c r="D18" s="135" t="inlineStr">
+        <is>
+          <t>09/23</t>
+        </is>
+      </c>
+      <c r="E18" s="135" t="inlineStr">
+        <is>
+          <t>12/21</t>
+        </is>
+      </c>
+      <c r="F18" s="135" t="n">
+        <v>58</v>
+      </c>
+      <c r="G18" s="158" t="n">
+        <v>62</v>
+      </c>
+      <c r="H18" s="135" t="n">
+        <v>24.25</v>
+      </c>
+      <c r="I18" s="135" t="n">
+        <v>15.75</v>
+      </c>
+      <c r="J18" s="135" t="n">
+        <v>22</v>
+      </c>
+      <c r="K18" s="136" t="inlineStr">
+        <is>
+          <t>M3（12/18）：批次2全部子任务测试通过（功能＋测试＋SLC）</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="44" customHeight="1">
+      <c r="A19" s="135" t="inlineStr">
+        <is>
+          <t>四</t>
+        </is>
+      </c>
+      <c r="B19" s="157" t="inlineStr">
+        <is>
+          <t>全局非功能实现与优化（N3）</t>
+        </is>
+      </c>
+      <c r="C19" s="136" t="inlineStr">
+        <is>
+          <t>N3全局非功能：性能压测与优化/统一鉴权与敏感掩码/可观测性（日志监控告警）/容量评估，随批次并行启动、全局达标收口</t>
+        </is>
+      </c>
+      <c r="D19" s="135" t="inlineStr">
+        <is>
+          <t>11/13</t>
+        </is>
+      </c>
+      <c r="E19" s="135" t="inlineStr">
+        <is>
+          <t>12/29</t>
+        </is>
+      </c>
+      <c r="F19" s="135" t="n">
+        <v>33</v>
+      </c>
+      <c r="G19" s="158" t="n">
+        <v>10</v>
+      </c>
+      <c r="H19" s="135" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="I19" s="135" t="n">
+        <v>3</v>
+      </c>
+      <c r="J19" s="135" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="K19" s="136" t="inlineStr">
+        <is>
+          <t>NFR指标达标（并入M4）</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="44" customHeight="1">
+      <c r="A20" s="135" t="inlineStr">
+        <is>
+          <t>五</t>
+        </is>
+      </c>
+      <c r="B20" s="157" t="inlineStr">
+        <is>
+          <t>代码质量与静态扫描治理（N2）</t>
+        </is>
+      </c>
+      <c r="C20" s="136" t="inlineStr">
+        <is>
+          <t>N2代码质量治理：ESLint/SonarLint接入、SAST/SCA静态扫描随批次1启动、技术债偿还与外部评审，全部代码完成后清零</t>
+        </is>
+      </c>
+      <c r="D20" s="135" t="inlineStr">
+        <is>
+          <t>11/16</t>
+        </is>
+      </c>
+      <c r="E20" s="135" t="inlineStr">
+        <is>
+          <t>12/23</t>
+        </is>
+      </c>
+      <c r="F20" s="135" t="n">
+        <v>28</v>
+      </c>
+      <c r="G20" s="158" t="n">
+        <v>8.75</v>
+      </c>
+      <c r="H20" s="135" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="I20" s="135" t="n">
+        <v>4</v>
+      </c>
+      <c r="J20" s="135" t="n">
+        <v>4</v>
+      </c>
+      <c r="K20" s="136" t="inlineStr">
+        <is>
+          <t>M4（12/29）：静态扫描清零（与N3共同收口）</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="44" customHeight="1">
+      <c r="A21" s="135" t="inlineStr">
+        <is>
+          <t>六</t>
+        </is>
+      </c>
+      <c r="B21" s="157" t="inlineStr">
+        <is>
+          <t>开发侧文档与部署收尾（N5＋N4-4/5）</t>
+        </is>
+      </c>
+      <c r="C21" s="136" t="inlineStr">
+        <is>
+          <t>N5开发侧文档（架构/接口/数据/SLC合稿）＋N4-4/5部署预演与上线值守、运维交接</t>
+        </is>
+      </c>
+      <c r="D21" s="135" t="inlineStr">
+        <is>
+          <t>12/10</t>
+        </is>
+      </c>
+      <c r="E21" s="135" t="inlineStr">
+        <is>
+          <t>12/24</t>
+        </is>
+      </c>
+      <c r="F21" s="135" t="n">
+        <v>11</v>
+      </c>
+      <c r="G21" s="158" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="H21" s="135" t="n">
+        <v>1</v>
+      </c>
+      <c r="I21" s="135" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="J21" s="135" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="K21" s="136" t="inlineStr">
+        <is>
+          <t>M5（12/29）：文档定稿、预演通过、195.5人天全部完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="159" t="inlineStr"/>
+      <c r="B22" s="160" t="inlineStr">
+        <is>
+          <t>合计</t>
+        </is>
+      </c>
+      <c r="C22" s="160" t="inlineStr">
+        <is>
+          <t>六阶段并行交叠（测试插空执行，工作日列含重叠不可加总）</t>
+        </is>
+      </c>
+      <c r="D22" s="159" t="inlineStr">
+        <is>
+          <t>09/14</t>
+        </is>
+      </c>
+      <c r="E22" s="159" t="inlineStr">
+        <is>
+          <t>12/29</t>
+        </is>
+      </c>
+      <c r="F22" s="159" t="n">
+        <v>71</v>
+      </c>
+      <c r="G22" s="159" t="n">
+        <v>195.5</v>
+      </c>
+      <c r="H22" s="159" t="n">
+        <v>65</v>
+      </c>
+      <c r="I22" s="159" t="n">
+        <v>60</v>
+      </c>
+      <c r="J22" s="159" t="n">
+        <v>70.5</v>
+      </c>
+      <c r="K22" s="160" t="inlineStr">
+        <is>
+          <t>M1~M5 全部达成</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="20" customHeight="1">
+      <c r="A24" s="151" t="inlineStr">
+        <is>
+          <t>三、里程碑计划</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" s="119" t="inlineStr">
+        <is>
+          <t>里程碑</t>
+        </is>
+      </c>
+      <c r="C25" s="119" t="inlineStr">
+        <is>
+          <t>日期</t>
+        </is>
+      </c>
+      <c r="D25" s="119" t="inlineStr">
+        <is>
+          <t>交付物 / 成果</t>
+        </is>
+      </c>
+      <c r="E25" s="161" t="n"/>
+      <c r="F25" s="161" t="n"/>
+      <c r="G25" s="162" t="n"/>
+      <c r="H25" s="119" t="inlineStr">
+        <is>
+          <t>退出条件</t>
+        </is>
+      </c>
+      <c r="I25" s="161" t="n"/>
+      <c r="J25" s="161" t="n"/>
+      <c r="K25" s="162" t="n"/>
+    </row>
+    <row r="26" ht="30" customHeight="1">
+      <c r="B26" s="163" t="inlineStr">
+        <is>
+          <t>M1 框架与基座就绪（第1周）</t>
+        </is>
+      </c>
+      <c r="C26" s="158" t="inlineStr">
+        <is>
+          <t>2026/09/17（周四）</t>
+        </is>
+      </c>
+      <c r="D26" s="136" t="inlineStr">
+        <is>
+          <t>CI/CD四道门禁＋部署流水线＋测试环境（K8s）先期部署</t>
+        </is>
+      </c>
+      <c r="E26" s="161" t="n"/>
+      <c r="F26" s="161" t="n"/>
+      <c r="G26" s="162" t="n"/>
+      <c r="H26" s="136" t="inlineStr">
+        <is>
+          <t>流水线可一键部署更新测试环境</t>
+        </is>
+      </c>
+      <c r="I26" s="161" t="n"/>
+      <c r="J26" s="161" t="n"/>
+      <c r="K26" s="162" t="n"/>
+    </row>
+    <row r="27" ht="30" customHeight="1">
+      <c r="B27" s="163" t="inlineStr">
+        <is>
+          <t>M2 批次1完成（F08/F01/F02）</t>
+        </is>
+      </c>
+      <c r="C27" s="158" t="inlineStr">
+        <is>
+          <t>2026/11/17（周二）</t>
+        </is>
+      </c>
+      <c r="D27" s="136" t="inlineStr">
+        <is>
+          <t>登录权限/存量迁移/元数据：功能＋测试＋SLC</t>
+        </is>
+      </c>
+      <c r="E27" s="161" t="n"/>
+      <c r="F27" s="161" t="n"/>
+      <c r="G27" s="162" t="n"/>
+      <c r="H27" s="136" t="inlineStr">
+        <is>
+          <t>批次1全部子任务测试通过</t>
+        </is>
+      </c>
+      <c r="I27" s="161" t="n"/>
+      <c r="J27" s="161" t="n"/>
+      <c r="K27" s="162" t="n"/>
+    </row>
+    <row r="28" ht="30" customHeight="1">
+      <c r="B28" s="163" t="inlineStr">
+        <is>
+          <t>M3 批次2完成（F03~F06）</t>
+        </is>
+      </c>
+      <c r="C28" s="158" t="inlineStr">
+        <is>
+          <t>2026/12/18（周五）</t>
+        </is>
+      </c>
+      <c r="D28" s="136" t="inlineStr">
+        <is>
+          <t>处置/安全/检索/审计：功能＋测试＋SLC</t>
+        </is>
+      </c>
+      <c r="E28" s="161" t="n"/>
+      <c r="F28" s="161" t="n"/>
+      <c r="G28" s="162" t="n"/>
+      <c r="H28" s="136" t="inlineStr">
+        <is>
+          <t>批次2全部子任务测试通过</t>
+        </is>
+      </c>
+      <c r="I28" s="161" t="n"/>
+      <c r="J28" s="161" t="n"/>
+      <c r="K28" s="162" t="n"/>
+    </row>
+    <row r="29" ht="30" customHeight="1">
+      <c r="B29" s="163" t="inlineStr">
+        <is>
+          <t>M4 全局非功能与质量收口（N3＋N2）</t>
+        </is>
+      </c>
+      <c r="C29" s="158" t="inlineStr">
+        <is>
+          <t>2026/12/29（周二）</t>
+        </is>
+      </c>
+      <c r="D29" s="136" t="inlineStr">
+        <is>
+          <t>性能/鉴权掩码/可观测/容量＋ESLint/SonarLint/SAST/SCA清零</t>
+        </is>
+      </c>
+      <c r="E29" s="161" t="n"/>
+      <c r="F29" s="161" t="n"/>
+      <c r="G29" s="162" t="n"/>
+      <c r="H29" s="136" t="inlineStr">
+        <is>
+          <t>NFR指标达标、静态扫描清零</t>
+        </is>
+      </c>
+      <c r="I29" s="161" t="n"/>
+      <c r="J29" s="161" t="n"/>
+      <c r="K29" s="162" t="n"/>
+    </row>
+    <row r="30" ht="30" customHeight="1">
+      <c r="B30" s="163" t="inlineStr">
+        <is>
+          <t>M5 开发WBS完成（文档定稿＋部署收尾）</t>
+        </is>
+      </c>
+      <c r="C30" s="158" t="inlineStr">
+        <is>
+          <t>2026/12/29（周二）</t>
+        </is>
+      </c>
+      <c r="D30" s="136" t="inlineStr">
+        <is>
+          <t>架构/接口/数据文档＋部署预演＋运维交接＋SLC合稿</t>
+        </is>
+      </c>
+      <c r="E30" s="161" t="n"/>
+      <c r="F30" s="161" t="n"/>
+      <c r="G30" s="162" t="n"/>
+      <c r="H30" s="136" t="inlineStr">
+        <is>
+          <t>全部195.5人天任务完成、文档定稿、预演通过</t>
+        </is>
+      </c>
+      <c r="I30" s="161" t="n"/>
+      <c r="J30" s="161" t="n"/>
+      <c r="K30" s="162" t="n"/>
+    </row>
+    <row r="32" ht="20" customHeight="1">
+      <c r="A32" s="151" t="inlineStr">
+        <is>
+          <t>四、资源投入与负荷</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" s="119" t="inlineStr">
+        <is>
+          <t>成员（角色）</t>
+        </is>
+      </c>
+      <c r="C33" s="119" t="inlineStr">
+        <is>
+          <t>职责与投入区间</t>
+        </is>
+      </c>
+      <c r="D33" s="119" t="inlineStr">
+        <is>
+          <t>任务数</t>
+        </is>
+      </c>
+      <c r="E33" s="119" t="inlineStr">
+        <is>
+          <t>人天</t>
+        </is>
+      </c>
+      <c r="F33" s="119" t="inlineStr">
+        <is>
+          <t>首次投入</t>
+        </is>
+      </c>
+      <c r="G33" s="119" t="inlineStr">
+        <is>
+          <t>最后任务</t>
+        </is>
+      </c>
+      <c r="H33" s="119" t="inlineStr">
+        <is>
+          <t>负荷说明</t>
+        </is>
+      </c>
+      <c r="I33" s="161" t="n"/>
+      <c r="J33" s="161" t="n"/>
+      <c r="K33" s="162" t="n"/>
+    </row>
+    <row r="34" ht="30" customHeight="1">
+      <c r="B34" s="163" t="inlineStr">
+        <is>
+          <t>Wade（前端/应用）</t>
+        </is>
+      </c>
+      <c r="C34" s="136" t="inlineStr">
+        <is>
+          <t>页面/交互/应用侧开发，兼部署预演与值守</t>
+        </is>
+      </c>
+      <c r="D34" s="135" t="n">
+        <v>57</v>
+      </c>
+      <c r="E34" s="158" t="n">
+        <v>60</v>
+      </c>
+      <c r="F34" s="135" t="inlineStr">
+        <is>
+          <t>09/14</t>
+        </is>
+      </c>
+      <c r="G34" s="135" t="inlineStr">
+        <is>
+          <t>12/15</t>
+        </is>
+      </c>
+      <c r="H34" s="136" t="inlineStr">
+        <is>
+          <t>60.0人天＝拆解估算原值；12/15完成全部任务，末段可支援联调</t>
+        </is>
+      </c>
+      <c r="I34" s="161" t="n"/>
+      <c r="J34" s="161" t="n"/>
+      <c r="K34" s="162" t="n"/>
+    </row>
+    <row r="35" ht="30" customHeight="1">
+      <c r="B35" s="165" t="inlineStr">
+        <is>
+          <t>DevB（数据/服务）</t>
+        </is>
+      </c>
+      <c r="C35" s="143" t="inlineStr">
+        <is>
+          <t>数据模型/迁移/服务端开发，兼测试环境与N3容量</t>
+        </is>
+      </c>
+      <c r="D35" s="142" t="n">
+        <v>84</v>
+      </c>
+      <c r="E35" s="166" t="n">
+        <v>70.5</v>
+      </c>
+      <c r="F35" s="142" t="inlineStr">
+        <is>
+          <t>09/14</t>
+        </is>
+      </c>
+      <c r="G35" s="142" t="inlineStr">
+        <is>
+          <t>12/29</t>
+        </is>
+      </c>
+      <c r="H35" s="143" t="inlineStr">
+        <is>
+          <t>70.5人天/71工作日＝窗口内全占用（零缓冲，12/29收口）；请假/阻塞一天即顺延一天</t>
+        </is>
+      </c>
+      <c r="I35" s="161" t="n"/>
+      <c r="J35" s="161" t="n"/>
+      <c r="K35" s="162" t="n"/>
+    </row>
+    <row r="36" ht="30" customHeight="1">
+      <c r="B36" s="163" t="inlineStr">
+        <is>
+          <t>Mandy（BA/测试/SLC）</t>
+        </is>
+      </c>
+      <c r="C36" s="136" t="inlineStr">
+        <is>
+          <t>BA规则澄清前置、测试随功能完成插空执行、SLC按组汇编</t>
+        </is>
+      </c>
+      <c r="D36" s="135" t="n">
+        <v>141</v>
+      </c>
+      <c r="E36" s="158" t="n">
+        <v>65</v>
+      </c>
+      <c r="F36" s="135" t="inlineStr">
+        <is>
+          <t>09/14</t>
+        </is>
+      </c>
+      <c r="G36" s="135" t="inlineStr">
+        <is>
+          <t>12/25</t>
+        </is>
+      </c>
+      <c r="H36" s="136" t="inlineStr">
+        <is>
+          <t>65.0人天（BA12.5＋测试38.75＋SLC13.75）；12/25完成</t>
+        </is>
+      </c>
+      <c r="I36" s="161" t="n"/>
+      <c r="J36" s="161" t="n"/>
+      <c r="K36" s="162" t="n"/>
+    </row>
+    <row r="37">
+      <c r="B37" s="168" t="inlineStr">
+        <is>
+          <t>合计</t>
+        </is>
+      </c>
+      <c r="C37" s="169" t="inlineStr">
+        <is>
+          <t>三人小队，无PM/环节行</t>
+        </is>
+      </c>
+      <c r="D37" s="170" t="n">
+        <v>282</v>
+      </c>
+      <c r="E37" s="159" t="n">
+        <v>195.5</v>
+      </c>
+      <c r="F37" s="170" t="inlineStr">
+        <is>
+          <t>09/14</t>
+        </is>
+      </c>
+      <c r="G37" s="170" t="inlineStr">
+        <is>
+          <t>12/29</t>
+        </is>
+      </c>
+      <c r="H37" s="169" t="inlineStr">
+        <is>
+          <t>195.5人天＝BA12.5/Wade60/DevB70.5/测试38.75/SLC13.75</t>
+        </is>
+      </c>
+      <c r="I37" s="161" t="n"/>
+      <c r="J37" s="161" t="n"/>
+      <c r="K37" s="162" t="n"/>
+    </row>
+    <row r="39" ht="20" customHeight="1">
+      <c r="A39" s="151" t="inlineStr">
+        <is>
+          <t>五、排期原则与阅读说明</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="24" customHeight="1">
+      <c r="A40" s="172" t="inlineStr">
+        <is>
+          <t>1. 人天口径：每行任务人天=「功能拆解估算」直估原值（未乘AI执行系数、未加管理环节），WBS分解末行322，层级3任务行282条合计195.5人天。</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="24" customHeight="1">
+      <c r="A41" s="172" t="inlineStr">
+        <is>
+          <t>2. 顺序与优先级：第1周框架搭建（N1基座＋N4流水线/测试环境先期部署）→批次1·P0（F08/F01/F02，登录与迁移主链最先可用）→批次2·P1（F03~F06）→全局非功能N3→质量治理N2→文档N5＋部署收尾。</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="24" customHeight="1">
+      <c r="A42" s="172" t="inlineStr">
+        <is>
+          <t>3. 并行交叠：阶段日期区间有重叠属正常——BA澄清前置、测试随功能完成插空执行、N2静态扫描随批次1启动、N3随批次2启动；里程碑（M1~M5）为各阶段收口点，详见表三。</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="24" customHeight="1">
+      <c r="A43" s="172" t="inlineStr">
+        <is>
+          <t>4. 关键资源：DevB 70.5人天在71个工作日内全占用（零缓冲）——决定12/29完工；Wade 61天占用（12/15完成）、Mandy 69天（12/25完成），末段可支援。</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="24" customHeight="1">
+      <c r="A44" s="172" t="inlineStr">
+        <is>
+          <t>5. 日历：周末与中秋9/25、国庆10/1~10/7不排；如需提前，可启用周末赶工（约可压缩2~3周）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="24" customHeight="1">
+      <c r="A45" s="172" t="inlineStr">
+        <is>
+          <t>6. 范围外：需求确认、架构评审、CC迁移演练、UAT、PM等项目环节不在本开发WBS内（195.5人天不含），需另行叠加项目级排期。</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="41">
+    <mergeCell ref="H28:K28"/>
+    <mergeCell ref="C10:K10"/>
+    <mergeCell ref="H27:K27"/>
+    <mergeCell ref="A39:K39"/>
+    <mergeCell ref="D25:G25"/>
+    <mergeCell ref="A24:K24"/>
+    <mergeCell ref="C9:K9"/>
+    <mergeCell ref="D30:G30"/>
+    <mergeCell ref="D29:G29"/>
+    <mergeCell ref="H33:K33"/>
+    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="A45:K45"/>
+    <mergeCell ref="C12:K12"/>
+    <mergeCell ref="C11:K11"/>
+    <mergeCell ref="D26:G26"/>
+    <mergeCell ref="H30:K30"/>
+    <mergeCell ref="C34"/>
+    <mergeCell ref="H26:K26"/>
+    <mergeCell ref="H35:K35"/>
+    <mergeCell ref="A41:K41"/>
+    <mergeCell ref="H29:K29"/>
+    <mergeCell ref="C8:K8"/>
+    <mergeCell ref="C7:K7"/>
+    <mergeCell ref="C35"/>
+    <mergeCell ref="H25:K25"/>
+    <mergeCell ref="H34:K34"/>
+    <mergeCell ref="A2:K2"/>
+    <mergeCell ref="A42:K42"/>
+    <mergeCell ref="A32:K32"/>
+    <mergeCell ref="D27:G27"/>
+    <mergeCell ref="A14:K14"/>
+    <mergeCell ref="C6:K6"/>
+    <mergeCell ref="H36:K36"/>
+    <mergeCell ref="A4:K4"/>
+    <mergeCell ref="C5:K5"/>
+    <mergeCell ref="A43:K43"/>
+    <mergeCell ref="C36"/>
+    <mergeCell ref="A44:K44"/>
+    <mergeCell ref="A40:K40"/>
+    <mergeCell ref="D28:G28"/>
+    <mergeCell ref="H37:K37"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -16609,7 +17989,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="007030A0"/>
@@ -18194,7 +19574,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00C00000"/>
@@ -20581,7 +21961,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="008FA9DB"/>
@@ -24489,7 +25869,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00FFC000"/>
@@ -24734,7 +26114,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="0070AD47"/>
@@ -24918,7 +26298,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>V3.0＝65.0人天（BA 12.5＋测试38.75＋SLC13.75）＝功能拆解估算完全一致；窗口73个工作日</t>
+          <t>V3.0＝65.0人天（BA 12.5＋测试38.75＋SLC 13.75）＝功能拆解估算完全一致；69天占用，12/25完成（窗口71个净工作日）</t>
         </is>
       </c>
     </row>
@@ -24966,7 +26346,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>V3.0＝60.0人天＝功能拆解估算完全一致；12/16完成，窗口73个工作日</t>
+          <t>V3.0＝60.0人天＝功能拆解估算完全一致；61天占用，12/15完成（窗口71个净工作日）</t>
         </is>
       </c>
     </row>
@@ -25014,7 +26394,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>V3.0＝70.5人天＝功能拆解估算完全一致（关键资源）；12/29完成，窗口73个工作日</t>
+          <t>V3.0＝70.5人天＝功能拆解估算完全一致（关键资源：71工作日全占用零缓冲）；12/29完成</t>
         </is>
       </c>
     </row>
@@ -25194,7 +26574,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00A6A6A6"/>
@@ -25646,283 +27026,4 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <tabColor rgb="00ED7D31"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C19"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="66" customWidth="1" min="3" max="3"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="5" t="inlineStr">
-        <is>
-          <t>项目进度汇总（自动统计）</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="7" t="inlineStr">
-        <is>
-          <t>统计项</t>
-        </is>
-      </c>
-      <c r="B2" s="7" t="inlineStr">
-        <is>
-          <t>数值</t>
-        </is>
-      </c>
-      <c r="C2" s="7" t="inlineStr">
-        <is>
-          <t>说明</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="17" t="inlineStr">
-        <is>
-          <t>任务总数（含各级汇总行）</t>
-        </is>
-      </c>
-      <c r="B3" s="15">
-        <f>COUNTA('WBS分解'!$A$4:$A$322)</f>
-        <v/>
-      </c>
-      <c r="C3" s="17" t="inlineStr">
-        <is>
-          <t>按已填写WBS编号的行数统计</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="17" t="inlineStr">
-        <is>
-          <t>其中：一级任务数</t>
-        </is>
-      </c>
-      <c r="B4" s="15">
-        <f>COUNTIF('WBS分解'!$C$4:$C$322,1)</f>
-        <v/>
-      </c>
-      <c r="C4" s="17" t="inlineStr">
-        <is>
-          <t>层级=1 的行数</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="17" t="inlineStr">
-        <is>
-          <t>其中：工作包数（三级）</t>
-        </is>
-      </c>
-      <c r="B5" s="15">
-        <f>COUNTIF('WBS分解'!$C$4:$C$322,3)</f>
-        <v/>
-      </c>
-      <c r="C5" s="17" t="inlineStr">
-        <is>
-          <t>层级=3 的行数</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="17" t="inlineStr">
-        <is>
-          <t>已完成</t>
-        </is>
-      </c>
-      <c r="B6" s="15">
-        <f>COUNTIF('WBS分解'!$L$4:$L$322,"已完成")</f>
-        <v/>
-      </c>
-      <c r="C6" s="17" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="17" t="inlineStr">
-        <is>
-          <t>进行中</t>
-        </is>
-      </c>
-      <c r="B7" s="15">
-        <f>COUNTIF('WBS分解'!$L$4:$L$322,"进行中")</f>
-        <v/>
-      </c>
-      <c r="C7" s="17" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="17" t="inlineStr">
-        <is>
-          <t>未开始</t>
-        </is>
-      </c>
-      <c r="B8" s="15">
-        <f>COUNTIF('WBS分解'!$L$4:$L$322,"未开始")</f>
-        <v/>
-      </c>
-      <c r="C8" s="17" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="17" t="inlineStr">
-        <is>
-          <t>已延期</t>
-        </is>
-      </c>
-      <c r="B9" s="15">
-        <f>COUNTIF('WBS分解'!$L$4:$L$322,"已延期")</f>
-        <v/>
-      </c>
-      <c r="C9" s="17" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="17" t="inlineStr">
-        <is>
-          <t>任务完成率</t>
-        </is>
-      </c>
-      <c r="B10" s="71">
-        <f>IFERROR(COUNTIF('WBS分解'!$L$4:$L$322,"已完成")/COUNTA('WBS分解'!$A$4:$A$322),0)</f>
-        <v/>
-      </c>
-      <c r="C10" s="17" t="inlineStr">
-        <is>
-          <t>已完成 ÷ 任务总数</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="17" t="inlineStr">
-        <is>
-          <t>整体平均进度</t>
-        </is>
-      </c>
-      <c r="B11" s="71">
-        <f>AVERAGE('WBS分解'!$M$4:$M$322)</f>
-        <v/>
-      </c>
-      <c r="C11" s="17" t="inlineStr">
-        <is>
-          <t>对进度列简单平均</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="17" t="inlineStr">
-        <is>
-          <t>工作量合计（人天·仅三级工作包）</t>
-        </is>
-      </c>
-      <c r="B12" s="46">
-        <f>SUMPRODUCT(('WBS分解'!$C$4:$C$322=3)*'WBS分解'!$I$4:$I$322)</f>
-        <v/>
-      </c>
-      <c r="C12" s="17" t="inlineStr">
-        <is>
-          <t>Mandy 65（BA12.5/测试38.75/SLC13.75）/ Wade 60 / DevB 70.5（V3.0＝功能拆解估算口径，合计195.5）</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="17" t="inlineStr">
-        <is>
-          <t>Mark 工作量（人天）</t>
-        </is>
-      </c>
-      <c r="B13" s="46">
-        <f>SUMPRODUCT(('WBS分解'!$C$4:$C$322=3)*('WBS分解'!$E$4:$E$322="Mark")*'WBS分解'!$I$4:$I$322)</f>
-        <v/>
-      </c>
-      <c r="C13" s="17" t="inlineStr">
-        <is>
-          <t>约定15人天</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="17" t="inlineStr">
-        <is>
-          <t>Mandy 工作量（人天）</t>
-        </is>
-      </c>
-      <c r="B14" s="46">
-        <f>SUMPRODUCT(('WBS分解'!$C$4:$C$322=3)*('WBS分解'!$E$4:$E$322="Mandy")*'WBS分解'!$I$4:$I$322)</f>
-        <v/>
-      </c>
-      <c r="C14" s="17" t="inlineStr">
-        <is>
-          <t>BA/测试/文档</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="17" t="inlineStr">
-        <is>
-          <t>Wade 工作量（人天）</t>
-        </is>
-      </c>
-      <c r="B15" s="46">
-        <f>SUMPRODUCT(('WBS分解'!$C$4:$C$322=3)*('WBS分解'!$E$4:$E$322="Wade")*'WBS分解'!$I$4:$I$322)</f>
-        <v/>
-      </c>
-      <c r="C15" s="17" t="inlineStr">
-        <is>
-          <t>开发A</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="17" t="inlineStr">
-        <is>
-          <t>DevB 工作量（人天）</t>
-        </is>
-      </c>
-      <c r="B16" s="46">
-        <f>SUMPRODUCT(('WBS分解'!$C$4:$C$322=3)*('WBS分解'!$E$4:$E$322="DevB")*'WBS分解'!$I$4:$I$322)</f>
-        <v/>
-      </c>
-      <c r="C16" s="17" t="inlineStr">
-        <is>
-          <t>开发B</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="17" t="inlineStr">
-        <is>
-          <t>预算合计（元）</t>
-        </is>
-      </c>
-      <c r="B17" s="46">
-        <f>SUM('WBS分解'!$O$4:$O$322)</f>
-        <v/>
-      </c>
-      <c r="C17" s="17" t="inlineStr">
-        <is>
-          <t>未填列，可按需补充</t>
-        </is>
-      </c>
-    </row>
-    <row r="18"/>
-    <row r="19">
-      <c r="A19" s="42" t="inlineStr">
-        <is>
-          <t>※ 本页自动汇总自「WBS分解」表，请勿手工修改。</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:C1"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>